--- a/base/base_0.xlsx
+++ b/base/base_0.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\ELIECER\scripts\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2C8846-C972-4471-9E5E-A78CACD57B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC75576-1B93-4F4E-A94F-AD83089DDF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_0" sheetId="2" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">base_0!$B$1:$AN$193</definedName>
@@ -1136,7 +1137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1380,9 +1381,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1449,11 +1447,125 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1467,35 +1579,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1515,154 +1648,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1698,112 +1693,115 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="3" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -12888,14 +12886,14 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="165" x14ac:dyDescent="2.35"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
-    <col min="2" max="2" width="192" style="107" customWidth="1"/>
+    <col min="2" max="2" width="192" style="106" customWidth="1"/>
     <col min="3" max="22" width="58.7109375" style="54" customWidth="1"/>
     <col min="23" max="23" width="84.28515625" style="54" customWidth="1"/>
-    <col min="24" max="24" width="95.7109375" style="125" customWidth="1"/>
+    <col min="24" max="24" width="95.7109375" style="124" customWidth="1"/>
     <col min="25" max="25" width="73" style="54" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="115.42578125" style="54" customWidth="1"/>
-    <col min="27" max="27" width="177.5703125" style="110" customWidth="1"/>
-    <col min="28" max="29" width="63" style="110" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="177.5703125" style="109" customWidth="1"/>
+    <col min="28" max="29" width="63" style="109" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="132" style="102" customWidth="1"/>
     <col min="31" max="31" width="33.28515625" style="102" customWidth="1"/>
     <col min="32" max="32" width="22.7109375" style="2" customWidth="1"/>
@@ -12908,103 +12906,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B1" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-      <c r="K1" s="133"/>
-      <c r="L1" s="133"/>
-      <c r="M1" s="133"/>
-      <c r="N1" s="133"/>
-      <c r="O1" s="133"/>
-      <c r="P1" s="133"/>
-      <c r="Q1" s="133"/>
-      <c r="R1" s="133"/>
-      <c r="S1" s="133"/>
-      <c r="T1" s="133"/>
-      <c r="U1" s="133"/>
-      <c r="V1" s="133"/>
-      <c r="W1" s="133"/>
-      <c r="X1" s="133"/>
-      <c r="Y1" s="133"/>
-      <c r="Z1" s="133"/>
-      <c r="AA1" s="133"/>
-      <c r="AB1" s="133"/>
-      <c r="AC1" s="133"/>
-      <c r="AD1" s="133"/>
+      <c r="B1" s="169" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="L1" s="170"/>
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="170"/>
+      <c r="W1" s="170"/>
+      <c r="X1" s="170"/>
+      <c r="Y1" s="170"/>
+      <c r="Z1" s="170"/>
+      <c r="AA1" s="170"/>
+      <c r="AB1" s="170"/>
+      <c r="AC1" s="170"/>
+      <c r="AD1" s="170"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B2" s="130" t="s">
+      <c r="B2" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="128" t="s">
+      <c r="C2" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="129"/>
-      <c r="E2" s="128" t="s">
+      <c r="D2" s="136"/>
+      <c r="E2" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="129"/>
-      <c r="G2" s="128" t="s">
+      <c r="F2" s="136"/>
+      <c r="G2" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="129"/>
-      <c r="I2" s="128" t="s">
+      <c r="H2" s="136"/>
+      <c r="I2" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="129"/>
-      <c r="K2" s="128" t="s">
+      <c r="J2" s="136"/>
+      <c r="K2" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="129"/>
-      <c r="M2" s="128" t="s">
+      <c r="L2" s="136"/>
+      <c r="M2" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="129"/>
-      <c r="O2" s="128" t="s">
+      <c r="N2" s="136"/>
+      <c r="O2" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="129"/>
-      <c r="Q2" s="128" t="s">
+      <c r="P2" s="136"/>
+      <c r="Q2" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="129"/>
-      <c r="S2" s="128" t="s">
+      <c r="R2" s="136"/>
+      <c r="S2" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="129"/>
-      <c r="U2" s="128" t="s">
+      <c r="T2" s="136"/>
+      <c r="U2" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="129"/>
-      <c r="W2" s="130" t="s">
+      <c r="V2" s="136"/>
+      <c r="W2" s="167" t="s">
         <v>12</v>
       </c>
-      <c r="X2" s="136" t="s">
+      <c r="X2" s="242" t="s">
         <v>209</v>
       </c>
-      <c r="Y2" s="130" t="s">
+      <c r="Y2" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="130" t="s">
+      <c r="Z2" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="130" t="s">
+      <c r="AA2" s="167" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="134" t="s">
+      <c r="AB2" s="139" t="s">
         <v>15</v>
       </c>
-      <c r="AC2" s="135"/>
+      <c r="AC2" s="140"/>
       <c r="AD2" s="6" t="s">
         <v>16</v>
       </c>
@@ -13018,7 +13016,7 @@
       <c r="AL2" s="8"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B3" s="131"/>
+      <c r="B3" s="168"/>
       <c r="C3" s="9" t="s">
         <v>17</v>
       </c>
@@ -13079,11 +13077,11 @@
       <c r="V3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="131"/>
-      <c r="X3" s="137"/>
-      <c r="Y3" s="131"/>
-      <c r="Z3" s="131"/>
-      <c r="AA3" s="131"/>
+      <c r="W3" s="168"/>
+      <c r="X3" s="243"/>
+      <c r="Y3" s="168"/>
+      <c r="Z3" s="168"/>
+      <c r="AA3" s="168"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="11"/>
       <c r="AD3" s="6"/>
@@ -13163,21 +13161,21 @@
       <c r="W4" s="14">
         <v>0</v>
       </c>
-      <c r="X4" s="113">
+      <c r="X4" s="112">
         <v>0</v>
       </c>
       <c r="Y4" s="14">
         <f>SUM(C4,E4,G4,I4,K4,,M4,O4,Q4,S4,U4,W4)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="138">
+      <c r="Z4" s="226">
         <f>SUM(D9,F9,H9,J9,L9,,N9,P9,R9,T9,V9)</f>
         <v>0</v>
       </c>
       <c r="AA4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AC4" s="141">
+      <c r="AC4" s="155">
         <f>SUM(Y4,AB5,AB6,AB7,AB8)</f>
         <v>0</v>
       </c>
@@ -13186,18 +13184,18 @@
         <v>0</v>
       </c>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="144" t="s">
+      <c r="AF4" s="188" t="s">
         <v>20</v>
       </c>
-      <c r="AG4" s="145"/>
-      <c r="AH4" s="145"/>
-      <c r="AI4" s="145"/>
-      <c r="AJ4" s="146"/>
-      <c r="AK4" s="150">
+      <c r="AG4" s="189"/>
+      <c r="AH4" s="189"/>
+      <c r="AI4" s="189"/>
+      <c r="AJ4" s="190"/>
+      <c r="AK4" s="229">
         <f>SUM(AD4:AD59)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="151"/>
+      <c r="AL4" s="230"/>
     </row>
     <row r="5" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B5" s="13" t="s">
@@ -13246,14 +13244,14 @@
       <c r="W5" s="14">
         <v>0</v>
       </c>
-      <c r="X5" s="113">
+      <c r="X5" s="112">
         <v>0</v>
       </c>
       <c r="Y5" s="14">
         <f>SUM(C5:W5)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="139"/>
+      <c r="Z5" s="227"/>
       <c r="AA5" s="13" t="s">
         <v>21</v>
       </c>
@@ -13261,19 +13259,19 @@
         <f>Y5*4</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="142"/>
+      <c r="AC5" s="157"/>
       <c r="AD5" s="16">
         <f>X5</f>
         <v>0</v>
       </c>
       <c r="AE5" s="17"/>
-      <c r="AF5" s="147"/>
-      <c r="AG5" s="148"/>
-      <c r="AH5" s="148"/>
-      <c r="AI5" s="148"/>
-      <c r="AJ5" s="149"/>
-      <c r="AK5" s="152"/>
-      <c r="AL5" s="151"/>
+      <c r="AF5" s="191"/>
+      <c r="AG5" s="192"/>
+      <c r="AH5" s="192"/>
+      <c r="AI5" s="192"/>
+      <c r="AJ5" s="193"/>
+      <c r="AK5" s="231"/>
+      <c r="AL5" s="230"/>
     </row>
     <row r="6" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B6" s="13" t="s">
@@ -13322,14 +13320,14 @@
       <c r="W6" s="14">
         <v>0</v>
       </c>
-      <c r="X6" s="113">
+      <c r="X6" s="112">
         <v>0</v>
       </c>
       <c r="Y6" s="14">
         <f>SUM(C6:W6)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="139"/>
+      <c r="Z6" s="227"/>
       <c r="AA6" s="15" t="s">
         <v>23</v>
       </c>
@@ -13337,19 +13335,19 @@
         <f>Y6*8</f>
         <v>0</v>
       </c>
-      <c r="AC6" s="142"/>
+      <c r="AC6" s="157"/>
       <c r="AD6" s="16">
         <f t="shared" ref="AD6:AD7" si="0">X6</f>
         <v>0</v>
       </c>
       <c r="AE6" s="17"/>
-      <c r="AF6" s="147"/>
-      <c r="AG6" s="148"/>
-      <c r="AH6" s="148"/>
-      <c r="AI6" s="148"/>
-      <c r="AJ6" s="149"/>
-      <c r="AK6" s="152"/>
-      <c r="AL6" s="151"/>
+      <c r="AF6" s="191"/>
+      <c r="AG6" s="192"/>
+      <c r="AH6" s="192"/>
+      <c r="AI6" s="192"/>
+      <c r="AJ6" s="193"/>
+      <c r="AK6" s="231"/>
+      <c r="AL6" s="230"/>
     </row>
     <row r="7" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B7" s="13" t="s">
@@ -13398,14 +13396,14 @@
       <c r="W7" s="14">
         <v>0</v>
       </c>
-      <c r="X7" s="113">
+      <c r="X7" s="112">
         <v>0</v>
       </c>
       <c r="Y7" s="14">
         <f>SUM(C7:W7)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="139"/>
+      <c r="Z7" s="227"/>
       <c r="AA7" s="15" t="s">
         <v>25</v>
       </c>
@@ -13413,22 +13411,22 @@
         <f>Y7*12</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="142"/>
+      <c r="AC7" s="157"/>
       <c r="AD7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE7" s="17"/>
-      <c r="AF7" s="153">
+      <c r="AF7" s="166">
         <f>SUM(AD4:AD8)</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="154"/>
-      <c r="AH7" s="154"/>
-      <c r="AI7" s="154"/>
-      <c r="AJ7" s="155"/>
-      <c r="AK7" s="152"/>
-      <c r="AL7" s="151"/>
+      <c r="AG7" s="164"/>
+      <c r="AH7" s="164"/>
+      <c r="AI7" s="164"/>
+      <c r="AJ7" s="165"/>
+      <c r="AK7" s="231"/>
+      <c r="AL7" s="230"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B8" s="13" t="s">
@@ -13477,14 +13475,14 @@
       <c r="W8" s="14">
         <v>0</v>
       </c>
-      <c r="X8" s="113">
+      <c r="X8" s="112">
         <v>0</v>
       </c>
       <c r="Y8" s="14">
         <f>SUM(C8:W8)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="140"/>
+      <c r="Z8" s="228"/>
       <c r="AA8" s="15" t="s">
         <v>27</v>
       </c>
@@ -13492,7 +13490,7 @@
         <f>Y8*16</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="143"/>
+      <c r="AC8" s="159"/>
       <c r="AD8" s="16">
         <f>X8</f>
         <v>0</v>
@@ -13503,8 +13501,8 @@
       <c r="AH8" s="27"/>
       <c r="AI8" s="27"/>
       <c r="AJ8" s="28"/>
-      <c r="AK8" s="152"/>
-      <c r="AL8" s="151"/>
+      <c r="AK8" s="231"/>
+      <c r="AL8" s="230"/>
       <c r="AM8" s="29"/>
       <c r="AN8" s="29"/>
     </row>
@@ -13594,7 +13592,7 @@
         <f>W4+(W5*4)+(W6*8)+(W7*12)+(W8*16)</f>
         <v>0</v>
       </c>
-      <c r="X9" s="114"/>
+      <c r="X9" s="113"/>
       <c r="Y9" s="14"/>
       <c r="Z9" s="14"/>
       <c r="AA9" s="15"/>
@@ -13610,8 +13608,8 @@
       <c r="AH9" s="35"/>
       <c r="AI9" s="35"/>
       <c r="AJ9" s="36"/>
-      <c r="AK9" s="152"/>
-      <c r="AL9" s="151"/>
+      <c r="AK9" s="231"/>
+      <c r="AL9" s="230"/>
       <c r="AM9" s="29"/>
       <c r="AN9" s="29"/>
     </row>
@@ -13682,7 +13680,7 @@
       <c r="W10" s="14">
         <v>0</v>
       </c>
-      <c r="X10" s="113">
+      <c r="X10" s="112">
         <v>0</v>
       </c>
       <c r="Y10" s="14">
@@ -13696,11 +13694,11 @@
       <c r="AA10" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="AB10" s="156">
+      <c r="AB10" s="232">
         <f>SUM(Y10:Y13)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="159">
+      <c r="AC10" s="219">
         <f>SUM(AB10,AB15)</f>
         <v>0</v>
       </c>
@@ -13709,15 +13707,15 @@
         <v>0</v>
       </c>
       <c r="AE10" s="17"/>
-      <c r="AF10" s="162" t="s">
+      <c r="AF10" s="160" t="s">
         <v>29</v>
       </c>
-      <c r="AG10" s="163"/>
-      <c r="AH10" s="163"/>
-      <c r="AI10" s="163"/>
-      <c r="AJ10" s="164"/>
-      <c r="AK10" s="152"/>
-      <c r="AL10" s="151"/>
+      <c r="AG10" s="161"/>
+      <c r="AH10" s="161"/>
+      <c r="AI10" s="161"/>
+      <c r="AJ10" s="162"/>
+      <c r="AK10" s="231"/>
+      <c r="AL10" s="230"/>
       <c r="AM10" s="12"/>
       <c r="AN10" s="12"/>
     </row>
@@ -13791,7 +13789,7 @@
       <c r="W11" s="14">
         <v>0</v>
       </c>
-      <c r="X11" s="113">
+      <c r="X11" s="112">
         <v>0</v>
       </c>
       <c r="Y11" s="14">
@@ -13805,20 +13803,20 @@
       <c r="AA11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AB11" s="157"/>
-      <c r="AC11" s="160"/>
+      <c r="AB11" s="233"/>
+      <c r="AC11" s="235"/>
       <c r="AD11" s="16">
         <f t="shared" ref="AD11:AD13" si="1">X11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="17"/>
-      <c r="AF11" s="165"/>
-      <c r="AG11" s="154"/>
-      <c r="AH11" s="154"/>
-      <c r="AI11" s="154"/>
-      <c r="AJ11" s="155"/>
-      <c r="AK11" s="152"/>
-      <c r="AL11" s="151"/>
+      <c r="AF11" s="163"/>
+      <c r="AG11" s="164"/>
+      <c r="AH11" s="164"/>
+      <c r="AI11" s="164"/>
+      <c r="AJ11" s="165"/>
+      <c r="AK11" s="231"/>
+      <c r="AL11" s="230"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B12" s="13" t="s">
@@ -13887,7 +13885,7 @@
       <c r="W12" s="14">
         <v>0</v>
       </c>
-      <c r="X12" s="113">
+      <c r="X12" s="112">
         <v>0</v>
       </c>
       <c r="Y12" s="14">
@@ -13901,20 +13899,20 @@
       <c r="AA12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AB12" s="157"/>
-      <c r="AC12" s="160"/>
+      <c r="AB12" s="233"/>
+      <c r="AC12" s="235"/>
       <c r="AD12" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE12" s="17"/>
-      <c r="AF12" s="165"/>
-      <c r="AG12" s="154"/>
-      <c r="AH12" s="154"/>
-      <c r="AI12" s="154"/>
-      <c r="AJ12" s="155"/>
-      <c r="AK12" s="152"/>
-      <c r="AL12" s="151"/>
+      <c r="AF12" s="163"/>
+      <c r="AG12" s="164"/>
+      <c r="AH12" s="164"/>
+      <c r="AI12" s="164"/>
+      <c r="AJ12" s="165"/>
+      <c r="AK12" s="231"/>
+      <c r="AL12" s="230"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B13" s="13" t="s">
@@ -13983,7 +13981,7 @@
       <c r="W13" s="14">
         <v>0</v>
       </c>
-      <c r="X13" s="113">
+      <c r="X13" s="112">
         <v>0</v>
       </c>
       <c r="Y13" s="14">
@@ -13997,20 +13995,20 @@
       <c r="AA13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AB13" s="158"/>
-      <c r="AC13" s="160"/>
+      <c r="AB13" s="234"/>
+      <c r="AC13" s="235"/>
       <c r="AD13" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE13" s="17"/>
-      <c r="AF13" s="165"/>
-      <c r="AG13" s="154"/>
-      <c r="AH13" s="154"/>
-      <c r="AI13" s="154"/>
-      <c r="AJ13" s="155"/>
-      <c r="AK13" s="152"/>
-      <c r="AL13" s="151"/>
+      <c r="AF13" s="163"/>
+      <c r="AG13" s="164"/>
+      <c r="AH13" s="164"/>
+      <c r="AI13" s="164"/>
+      <c r="AJ13" s="165"/>
+      <c r="AK13" s="231"/>
+      <c r="AL13" s="230"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B14" s="13"/>
@@ -14098,21 +14096,21 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="X14" s="114"/>
+      <c r="X14" s="113"/>
       <c r="Y14" s="14"/>
       <c r="Z14" s="41"/>
       <c r="AA14" s="42"/>
       <c r="AB14" s="13"/>
-      <c r="AC14" s="160"/>
+      <c r="AC14" s="235"/>
       <c r="AD14" s="33"/>
       <c r="AE14" s="17"/>
-      <c r="AF14" s="165"/>
-      <c r="AG14" s="154"/>
-      <c r="AH14" s="154"/>
-      <c r="AI14" s="154"/>
-      <c r="AJ14" s="155"/>
-      <c r="AK14" s="152"/>
-      <c r="AL14" s="151"/>
+      <c r="AF14" s="163"/>
+      <c r="AG14" s="164"/>
+      <c r="AH14" s="164"/>
+      <c r="AI14" s="164"/>
+      <c r="AJ14" s="165"/>
+      <c r="AK14" s="231"/>
+      <c r="AL14" s="230"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B15" s="13" t="s">
@@ -14181,7 +14179,7 @@
       <c r="W15" s="43">
         <v>0</v>
       </c>
-      <c r="X15" s="115">
+      <c r="X15" s="114">
         <v>0</v>
       </c>
       <c r="Y15" s="14">
@@ -14195,26 +14193,26 @@
       <c r="AA15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AB15" s="156">
+      <c r="AB15" s="232">
         <f>SUM(Y15:Y18)</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="160"/>
+      <c r="AC15" s="235"/>
       <c r="AD15" s="16">
         <f>X15</f>
         <v>0</v>
       </c>
       <c r="AE15" s="17"/>
-      <c r="AF15" s="153">
+      <c r="AF15" s="166">
         <f>SUM(AD10:AD20)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="154"/>
-      <c r="AH15" s="154"/>
-      <c r="AI15" s="154"/>
-      <c r="AJ15" s="155"/>
-      <c r="AK15" s="152"/>
-      <c r="AL15" s="151"/>
+      <c r="AG15" s="164"/>
+      <c r="AH15" s="164"/>
+      <c r="AI15" s="164"/>
+      <c r="AJ15" s="165"/>
+      <c r="AK15" s="231"/>
+      <c r="AL15" s="230"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B16" s="13" t="s">
@@ -14283,7 +14281,7 @@
       <c r="W16" s="43">
         <v>0</v>
       </c>
-      <c r="X16" s="116">
+      <c r="X16" s="115">
         <v>0</v>
       </c>
       <c r="Y16" s="14">
@@ -14297,8 +14295,8 @@
       <c r="AA16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AB16" s="157"/>
-      <c r="AC16" s="160"/>
+      <c r="AB16" s="233"/>
+      <c r="AC16" s="235"/>
       <c r="AD16" s="16">
         <f t="shared" ref="AD16:AD20" si="5">X16</f>
         <v>0</v>
@@ -14309,8 +14307,8 @@
       <c r="AH16" s="27"/>
       <c r="AI16" s="27"/>
       <c r="AJ16" s="28"/>
-      <c r="AK16" s="152"/>
-      <c r="AL16" s="151"/>
+      <c r="AK16" s="231"/>
+      <c r="AL16" s="230"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B17" s="13" t="s">
@@ -14379,7 +14377,7 @@
       <c r="W17" s="43">
         <v>0</v>
       </c>
-      <c r="X17" s="116">
+      <c r="X17" s="115">
         <v>0</v>
       </c>
       <c r="Y17" s="14">
@@ -14393,8 +14391,8 @@
       <c r="AA17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AB17" s="157"/>
-      <c r="AC17" s="160"/>
+      <c r="AB17" s="233"/>
+      <c r="AC17" s="235"/>
       <c r="AD17" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14405,8 +14403,8 @@
       <c r="AH17" s="27"/>
       <c r="AI17" s="27"/>
       <c r="AJ17" s="28"/>
-      <c r="AK17" s="152"/>
-      <c r="AL17" s="151"/>
+      <c r="AK17" s="231"/>
+      <c r="AL17" s="230"/>
     </row>
     <row r="18" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B18" s="13" t="s">
@@ -14475,7 +14473,7 @@
       <c r="W18" s="43">
         <v>0</v>
       </c>
-      <c r="X18" s="115">
+      <c r="X18" s="114">
         <v>0</v>
       </c>
       <c r="Y18" s="14">
@@ -14489,8 +14487,8 @@
       <c r="AA18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AB18" s="157"/>
-      <c r="AC18" s="160"/>
+      <c r="AB18" s="233"/>
+      <c r="AC18" s="235"/>
       <c r="AD18" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14501,8 +14499,8 @@
       <c r="AH18" s="27"/>
       <c r="AI18" s="27"/>
       <c r="AJ18" s="28"/>
-      <c r="AK18" s="152"/>
-      <c r="AL18" s="151"/>
+      <c r="AK18" s="231"/>
+      <c r="AL18" s="230"/>
     </row>
     <row r="19" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B19" s="13" t="s">
@@ -14571,7 +14569,7 @@
       <c r="W19" s="43">
         <v>0</v>
       </c>
-      <c r="X19" s="116">
+      <c r="X19" s="115">
         <v>0</v>
       </c>
       <c r="Y19" s="14">
@@ -14585,8 +14583,8 @@
       <c r="AA19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AB19" s="157"/>
-      <c r="AC19" s="160"/>
+      <c r="AB19" s="233"/>
+      <c r="AC19" s="235"/>
       <c r="AD19" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14597,8 +14595,8 @@
       <c r="AH19" s="27"/>
       <c r="AI19" s="27"/>
       <c r="AJ19" s="28"/>
-      <c r="AK19" s="152"/>
-      <c r="AL19" s="151"/>
+      <c r="AK19" s="231"/>
+      <c r="AL19" s="230"/>
     </row>
     <row r="20" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B20" s="13" t="s">
@@ -14667,7 +14665,7 @@
       <c r="W20" s="43">
         <v>0</v>
       </c>
-      <c r="X20" s="115">
+      <c r="X20" s="114">
         <v>0</v>
       </c>
       <c r="Y20" s="14">
@@ -14681,8 +14679,8 @@
       <c r="AA20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AB20" s="158"/>
-      <c r="AC20" s="161"/>
+      <c r="AB20" s="234"/>
+      <c r="AC20" s="220"/>
       <c r="AD20" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14693,8 +14691,8 @@
       <c r="AH20" s="27"/>
       <c r="AI20" s="27"/>
       <c r="AJ20" s="28"/>
-      <c r="AK20" s="152"/>
-      <c r="AL20" s="151"/>
+      <c r="AK20" s="231"/>
+      <c r="AL20" s="230"/>
     </row>
     <row r="21" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B21" s="13"/>
@@ -14782,23 +14780,23 @@
         <f>SUM(W15:W20)</f>
         <v>0</v>
       </c>
-      <c r="X21" s="114"/>
+      <c r="X21" s="113"/>
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
       <c r="AA21" s="42"/>
-      <c r="AB21" s="181"/>
-      <c r="AC21" s="182"/>
+      <c r="AB21" s="186"/>
+      <c r="AC21" s="187"/>
       <c r="AD21" s="33"/>
       <c r="AE21" s="17"/>
-      <c r="AF21" s="162" t="s">
+      <c r="AF21" s="160" t="s">
         <v>39</v>
       </c>
-      <c r="AG21" s="163"/>
-      <c r="AH21" s="163"/>
-      <c r="AI21" s="163"/>
-      <c r="AJ21" s="164"/>
-      <c r="AK21" s="152"/>
-      <c r="AL21" s="151"/>
+      <c r="AG21" s="161"/>
+      <c r="AH21" s="161"/>
+      <c r="AI21" s="161"/>
+      <c r="AJ21" s="162"/>
+      <c r="AK21" s="231"/>
+      <c r="AL21" s="230"/>
     </row>
     <row r="22" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B22" s="13" t="s">
@@ -14867,7 +14865,7 @@
       <c r="W22" s="14">
         <v>0</v>
       </c>
-      <c r="X22" s="117">
+      <c r="X22" s="116">
         <v>0</v>
       </c>
       <c r="Y22" s="14">
@@ -14881,21 +14879,21 @@
       <c r="AA22" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AB22" s="183"/>
-      <c r="AC22" s="184"/>
+      <c r="AB22" s="221"/>
+      <c r="AC22" s="222"/>
       <c r="AD22" s="16">
         <f>X22</f>
         <v>0</v>
       </c>
       <c r="AE22" s="17"/>
-      <c r="AF22" s="185">
+      <c r="AF22" s="239">
         <f>SUM(AD22:AE22)</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="186"/>
-      <c r="AH22" s="186"/>
-      <c r="AI22" s="186"/>
-      <c r="AJ22" s="187"/>
+      <c r="AG22" s="240"/>
+      <c r="AH22" s="240"/>
+      <c r="AI22" s="240"/>
+      <c r="AJ22" s="241"/>
       <c r="AK22" s="22"/>
       <c r="AL22" s="18"/>
     </row>
@@ -14985,12 +14983,12 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="X23" s="114"/>
+      <c r="X23" s="113"/>
       <c r="Y23" s="14"/>
       <c r="Z23" s="14"/>
       <c r="AA23" s="42"/>
-      <c r="AB23" s="172"/>
-      <c r="AC23" s="173"/>
+      <c r="AB23" s="149"/>
+      <c r="AC23" s="150"/>
       <c r="AD23" s="16">
         <f t="shared" ref="AD23:AD39" si="8">X23</f>
         <v>0</v>
@@ -15074,7 +15072,7 @@
       <c r="W24" s="14">
         <v>0</v>
       </c>
-      <c r="X24" s="113">
+      <c r="X24" s="112">
         <v>0</v>
       </c>
       <c r="Y24" s="14">
@@ -15088,27 +15086,27 @@
       <c r="AA24" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AB24" s="174">
+      <c r="AB24" s="171">
         <f>SUM(Y24:Y25)</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="175"/>
+      <c r="AC24" s="172"/>
       <c r="AD24" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE24" s="17"/>
-      <c r="AF24" s="178" t="s">
+      <c r="AF24" s="175" t="s">
         <v>42</v>
       </c>
-      <c r="AG24" s="179"/>
-      <c r="AH24" s="179"/>
-      <c r="AI24" s="179"/>
-      <c r="AJ24" s="180"/>
-      <c r="AK24" s="166" t="s">
+      <c r="AG24" s="176"/>
+      <c r="AH24" s="176"/>
+      <c r="AI24" s="176"/>
+      <c r="AJ24" s="223"/>
+      <c r="AK24" s="236" t="s">
         <v>43</v>
       </c>
-      <c r="AL24" s="167"/>
+      <c r="AL24" s="237"/>
     </row>
     <row r="25" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A25" s="12">
@@ -15180,7 +15178,7 @@
       <c r="W25" s="14">
         <v>0</v>
       </c>
-      <c r="X25" s="113">
+      <c r="X25" s="112">
         <v>0</v>
       </c>
       <c r="Y25" s="14">
@@ -15194,23 +15192,23 @@
       <c r="AA25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AB25" s="176"/>
-      <c r="AC25" s="177"/>
+      <c r="AB25" s="173"/>
+      <c r="AC25" s="174"/>
       <c r="AD25" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE25" s="17"/>
-      <c r="AF25" s="169">
+      <c r="AF25" s="197">
         <f>SUM(AD24:AD25)</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="170"/>
-      <c r="AH25" s="170"/>
-      <c r="AI25" s="170"/>
-      <c r="AJ25" s="171"/>
-      <c r="AK25" s="166"/>
-      <c r="AL25" s="167"/>
+      <c r="AG25" s="224"/>
+      <c r="AH25" s="224"/>
+      <c r="AI25" s="224"/>
+      <c r="AJ25" s="225"/>
+      <c r="AK25" s="236"/>
+      <c r="AL25" s="237"/>
     </row>
     <row r="26" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B26" s="13"/>
@@ -15298,12 +15296,12 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X26" s="114"/>
+      <c r="X26" s="113"/>
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
       <c r="AA26" s="13"/>
-      <c r="AB26" s="172"/>
-      <c r="AC26" s="173"/>
+      <c r="AB26" s="149"/>
+      <c r="AC26" s="150"/>
       <c r="AD26" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15314,8 +15312,8 @@
       <c r="AH26" s="45"/>
       <c r="AI26" s="45"/>
       <c r="AJ26" s="46"/>
-      <c r="AK26" s="166"/>
-      <c r="AL26" s="167"/>
+      <c r="AK26" s="236"/>
+      <c r="AL26" s="237"/>
     </row>
     <row r="27" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A27" s="12">
@@ -15387,7 +15385,7 @@
       <c r="W27" s="14">
         <v>0</v>
       </c>
-      <c r="X27" s="113">
+      <c r="X27" s="112">
         <v>0</v>
       </c>
       <c r="Y27" s="14">
@@ -15401,25 +15399,25 @@
       <c r="AA27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AB27" s="174">
+      <c r="AB27" s="171">
         <f>SUM(Y26:Y28)</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="175"/>
+      <c r="AC27" s="172"/>
       <c r="AD27" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE27" s="17"/>
-      <c r="AF27" s="178" t="s">
+      <c r="AF27" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="AG27" s="179"/>
-      <c r="AH27" s="179"/>
-      <c r="AI27" s="179"/>
-      <c r="AJ27" s="180"/>
-      <c r="AK27" s="166"/>
-      <c r="AL27" s="167"/>
+      <c r="AG27" s="176"/>
+      <c r="AH27" s="176"/>
+      <c r="AI27" s="176"/>
+      <c r="AJ27" s="223"/>
+      <c r="AK27" s="236"/>
+      <c r="AL27" s="237"/>
     </row>
     <row r="28" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A28" s="12">
@@ -15491,7 +15489,7 @@
       <c r="W28" s="14">
         <v>0</v>
       </c>
-      <c r="X28" s="113">
+      <c r="X28" s="112">
         <v>0</v>
       </c>
       <c r="Y28" s="14">
@@ -15505,23 +15503,23 @@
       <c r="AA28" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AB28" s="176"/>
-      <c r="AC28" s="177"/>
+      <c r="AB28" s="173"/>
+      <c r="AC28" s="174"/>
       <c r="AD28" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE28" s="17"/>
-      <c r="AF28" s="169">
+      <c r="AF28" s="197">
         <f>+AD27+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="170"/>
-      <c r="AH28" s="170"/>
-      <c r="AI28" s="170"/>
-      <c r="AJ28" s="171"/>
-      <c r="AK28" s="166"/>
-      <c r="AL28" s="167"/>
+      <c r="AG28" s="224"/>
+      <c r="AH28" s="224"/>
+      <c r="AI28" s="224"/>
+      <c r="AJ28" s="225"/>
+      <c r="AK28" s="236"/>
+      <c r="AL28" s="237"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B29" s="13"/>
@@ -15609,12 +15607,12 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="X29" s="114"/>
+      <c r="X29" s="113"/>
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
       <c r="AA29" s="13"/>
-      <c r="AB29" s="172"/>
-      <c r="AC29" s="173"/>
+      <c r="AB29" s="149"/>
+      <c r="AC29" s="150"/>
       <c r="AD29" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15625,8 +15623,8 @@
       <c r="AH29" s="45"/>
       <c r="AI29" s="45"/>
       <c r="AJ29" s="45"/>
-      <c r="AK29" s="166"/>
-      <c r="AL29" s="167"/>
+      <c r="AK29" s="236"/>
+      <c r="AL29" s="237"/>
     </row>
     <row r="30" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A30" s="12">
@@ -15698,7 +15696,7 @@
       <c r="W30" s="14">
         <v>0</v>
       </c>
-      <c r="X30" s="113">
+      <c r="X30" s="112">
         <v>0</v>
       </c>
       <c r="Y30" s="14">
@@ -15712,25 +15710,25 @@
       <c r="AA30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AB30" s="174">
+      <c r="AB30" s="171">
         <f>SUM(Y29:Y31)</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="175"/>
+      <c r="AC30" s="172"/>
       <c r="AD30" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE30" s="17"/>
-      <c r="AF30" s="178" t="s">
+      <c r="AF30" s="175" t="s">
         <v>49</v>
       </c>
-      <c r="AG30" s="179"/>
-      <c r="AH30" s="179"/>
-      <c r="AI30" s="179"/>
-      <c r="AJ30" s="179"/>
-      <c r="AK30" s="166"/>
-      <c r="AL30" s="167"/>
+      <c r="AG30" s="176"/>
+      <c r="AH30" s="176"/>
+      <c r="AI30" s="176"/>
+      <c r="AJ30" s="176"/>
+      <c r="AK30" s="236"/>
+      <c r="AL30" s="237"/>
     </row>
     <row r="31" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A31" s="12">
@@ -15802,7 +15800,7 @@
       <c r="W31" s="14">
         <v>0</v>
       </c>
-      <c r="X31" s="113">
+      <c r="X31" s="112">
         <v>0</v>
       </c>
       <c r="Y31" s="14">
@@ -15816,23 +15814,23 @@
       <c r="AA31" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AB31" s="176"/>
-      <c r="AC31" s="177"/>
+      <c r="AB31" s="173"/>
+      <c r="AC31" s="174"/>
       <c r="AD31" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE31" s="17"/>
-      <c r="AF31" s="169">
+      <c r="AF31" s="197">
         <f>+AD30+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG31" s="170"/>
-      <c r="AH31" s="170"/>
-      <c r="AI31" s="170"/>
-      <c r="AJ31" s="171"/>
-      <c r="AK31" s="166"/>
-      <c r="AL31" s="167"/>
+      <c r="AG31" s="224"/>
+      <c r="AH31" s="224"/>
+      <c r="AI31" s="224"/>
+      <c r="AJ31" s="225"/>
+      <c r="AK31" s="236"/>
+      <c r="AL31" s="237"/>
     </row>
     <row r="32" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B32" s="13"/>
@@ -15920,12 +15918,12 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="X32" s="114"/>
+      <c r="X32" s="113"/>
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
       <c r="AA32" s="13"/>
-      <c r="AB32" s="172"/>
-      <c r="AC32" s="173"/>
+      <c r="AB32" s="149"/>
+      <c r="AC32" s="150"/>
       <c r="AD32" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15936,8 +15934,8 @@
       <c r="AH32" s="45"/>
       <c r="AI32" s="45"/>
       <c r="AJ32" s="45"/>
-      <c r="AK32" s="166"/>
-      <c r="AL32" s="167"/>
+      <c r="AK32" s="236"/>
+      <c r="AL32" s="237"/>
     </row>
     <row r="33" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A33" s="12">
@@ -16009,7 +16007,7 @@
       <c r="W33" s="14">
         <v>0</v>
       </c>
-      <c r="X33" s="113">
+      <c r="X33" s="112">
         <v>0</v>
       </c>
       <c r="Y33" s="14">
@@ -16023,25 +16021,25 @@
       <c r="AA33" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AB33" s="174">
+      <c r="AB33" s="171">
         <f>SUM(Y32:Y34)</f>
         <v>0</v>
       </c>
-      <c r="AC33" s="175"/>
+      <c r="AC33" s="172"/>
       <c r="AD33" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE33" s="17"/>
-      <c r="AF33" s="178" t="s">
+      <c r="AF33" s="175" t="s">
         <v>52</v>
       </c>
-      <c r="AG33" s="179"/>
-      <c r="AH33" s="179"/>
-      <c r="AI33" s="179"/>
-      <c r="AJ33" s="179"/>
-      <c r="AK33" s="166"/>
-      <c r="AL33" s="167"/>
+      <c r="AG33" s="176"/>
+      <c r="AH33" s="176"/>
+      <c r="AI33" s="176"/>
+      <c r="AJ33" s="176"/>
+      <c r="AK33" s="236"/>
+      <c r="AL33" s="237"/>
     </row>
     <row r="34" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A34" s="12">
@@ -16113,7 +16111,7 @@
       <c r="W34" s="14">
         <v>0</v>
       </c>
-      <c r="X34" s="113">
+      <c r="X34" s="112">
         <v>0</v>
       </c>
       <c r="Y34" s="14">
@@ -16127,23 +16125,23 @@
       <c r="AA34" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AB34" s="176"/>
-      <c r="AC34" s="177"/>
+      <c r="AB34" s="173"/>
+      <c r="AC34" s="174"/>
       <c r="AD34" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE34" s="17"/>
-      <c r="AF34" s="169">
+      <c r="AF34" s="197">
         <f>+AD33+AD34</f>
         <v>0</v>
       </c>
-      <c r="AG34" s="170"/>
-      <c r="AH34" s="170"/>
-      <c r="AI34" s="170"/>
-      <c r="AJ34" s="171"/>
-      <c r="AK34" s="166"/>
-      <c r="AL34" s="167"/>
+      <c r="AG34" s="224"/>
+      <c r="AH34" s="224"/>
+      <c r="AI34" s="224"/>
+      <c r="AJ34" s="225"/>
+      <c r="AK34" s="236"/>
+      <c r="AL34" s="237"/>
     </row>
     <row r="35" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B35" s="13"/>
@@ -16231,12 +16229,12 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X35" s="114"/>
+      <c r="X35" s="113"/>
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
       <c r="AA35" s="13"/>
-      <c r="AB35" s="172"/>
-      <c r="AC35" s="173"/>
+      <c r="AB35" s="149"/>
+      <c r="AC35" s="150"/>
       <c r="AD35" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16247,8 +16245,8 @@
       <c r="AH35" s="45"/>
       <c r="AI35" s="45"/>
       <c r="AJ35" s="45"/>
-      <c r="AK35" s="166"/>
-      <c r="AL35" s="167"/>
+      <c r="AK35" s="236"/>
+      <c r="AL35" s="237"/>
     </row>
     <row r="36" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B36" s="13" t="s">
@@ -16317,7 +16315,7 @@
       <c r="W36" s="14">
         <v>0</v>
       </c>
-      <c r="X36" s="113">
+      <c r="X36" s="112">
         <v>0</v>
       </c>
       <c r="Y36" s="14">
@@ -16331,25 +16329,25 @@
       <c r="AA36" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="AB36" s="174">
+      <c r="AB36" s="171">
         <f>SUM(Y35:Y37)</f>
         <v>0</v>
       </c>
-      <c r="AC36" s="175"/>
+      <c r="AC36" s="172"/>
       <c r="AD36" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE36" s="17"/>
-      <c r="AF36" s="178" t="s">
+      <c r="AF36" s="175" t="s">
         <v>55</v>
       </c>
-      <c r="AG36" s="179"/>
-      <c r="AH36" s="179"/>
-      <c r="AI36" s="179"/>
-      <c r="AJ36" s="179"/>
-      <c r="AK36" s="166"/>
-      <c r="AL36" s="167"/>
+      <c r="AG36" s="176"/>
+      <c r="AH36" s="176"/>
+      <c r="AI36" s="176"/>
+      <c r="AJ36" s="176"/>
+      <c r="AK36" s="236"/>
+      <c r="AL36" s="237"/>
     </row>
     <row r="37" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B37" s="13" t="s">
@@ -16418,7 +16416,7 @@
       <c r="W37" s="14">
         <v>0</v>
       </c>
-      <c r="X37" s="117">
+      <c r="X37" s="116">
         <v>0</v>
       </c>
       <c r="Y37" s="14">
@@ -16432,23 +16430,23 @@
       <c r="AA37" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="AB37" s="176"/>
-      <c r="AC37" s="177"/>
+      <c r="AB37" s="173"/>
+      <c r="AC37" s="174"/>
       <c r="AD37" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE37" s="17"/>
-      <c r="AF37" s="169">
+      <c r="AF37" s="197">
         <f>+AD36+AD37</f>
         <v>0</v>
       </c>
-      <c r="AG37" s="170"/>
-      <c r="AH37" s="170"/>
-      <c r="AI37" s="170"/>
-      <c r="AJ37" s="171"/>
-      <c r="AK37" s="166"/>
-      <c r="AL37" s="167"/>
+      <c r="AG37" s="224"/>
+      <c r="AH37" s="224"/>
+      <c r="AI37" s="224"/>
+      <c r="AJ37" s="225"/>
+      <c r="AK37" s="236"/>
+      <c r="AL37" s="237"/>
       <c r="AM37" s="47"/>
       <c r="AN37" s="47"/>
     </row>
@@ -16538,12 +16536,12 @@
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X38" s="114"/>
+      <c r="X38" s="113"/>
       <c r="Y38" s="14"/>
       <c r="Z38" s="14"/>
       <c r="AA38" s="13"/>
-      <c r="AB38" s="172"/>
-      <c r="AC38" s="173"/>
+      <c r="AB38" s="149"/>
+      <c r="AC38" s="150"/>
       <c r="AD38" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16554,8 +16552,8 @@
       <c r="AH38" s="45"/>
       <c r="AI38" s="45"/>
       <c r="AJ38" s="45"/>
-      <c r="AK38" s="166"/>
-      <c r="AL38" s="167"/>
+      <c r="AK38" s="236"/>
+      <c r="AL38" s="237"/>
       <c r="AM38" s="47"/>
       <c r="AN38" s="47"/>
     </row>
@@ -16626,7 +16624,7 @@
       <c r="W39" s="14">
         <v>0</v>
       </c>
-      <c r="X39" s="117">
+      <c r="X39" s="116">
         <v>0</v>
       </c>
       <c r="Y39" s="14">
@@ -16640,8 +16638,8 @@
       <c r="AA39" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="AB39" s="172"/>
-      <c r="AC39" s="173"/>
+      <c r="AB39" s="149"/>
+      <c r="AC39" s="150"/>
       <c r="AD39" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16652,8 +16650,8 @@
       <c r="AH39" s="45"/>
       <c r="AI39" s="45"/>
       <c r="AJ39" s="45"/>
-      <c r="AK39" s="166"/>
-      <c r="AL39" s="167"/>
+      <c r="AK39" s="236"/>
+      <c r="AL39" s="237"/>
       <c r="AM39" s="47"/>
       <c r="AN39" s="47"/>
     </row>
@@ -16661,50 +16659,50 @@
       <c r="B40" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="128" t="s">
+      <c r="C40" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="129"/>
-      <c r="E40" s="128" t="s">
+      <c r="D40" s="136"/>
+      <c r="E40" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F40" s="129"/>
-      <c r="G40" s="128" t="s">
+      <c r="F40" s="136"/>
+      <c r="G40" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H40" s="129"/>
-      <c r="I40" s="128" t="s">
+      <c r="H40" s="136"/>
+      <c r="I40" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J40" s="129"/>
-      <c r="K40" s="128" t="s">
+      <c r="J40" s="136"/>
+      <c r="K40" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L40" s="129"/>
-      <c r="M40" s="128" t="s">
+      <c r="L40" s="136"/>
+      <c r="M40" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N40" s="129"/>
-      <c r="O40" s="128" t="s">
+      <c r="N40" s="136"/>
+      <c r="O40" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P40" s="129"/>
-      <c r="Q40" s="128" t="s">
+      <c r="P40" s="136"/>
+      <c r="Q40" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R40" s="129"/>
-      <c r="S40" s="128" t="s">
+      <c r="R40" s="136"/>
+      <c r="S40" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T40" s="129"/>
-      <c r="U40" s="128" t="s">
+      <c r="T40" s="136"/>
+      <c r="U40" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V40" s="129"/>
+      <c r="V40" s="136"/>
       <c r="W40" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="X40" s="118"/>
+      <c r="X40" s="117"/>
       <c r="Y40" s="49" t="s">
         <v>13</v>
       </c>
@@ -16714,8 +16712,8 @@
       <c r="AA40" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="AB40" s="134"/>
-      <c r="AC40" s="135"/>
+      <c r="AB40" s="139"/>
+      <c r="AC40" s="140"/>
       <c r="AD40" s="6">
         <v>0</v>
       </c>
@@ -16725,8 +16723,8 @@
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
-      <c r="AK40" s="166"/>
-      <c r="AL40" s="167"/>
+      <c r="AK40" s="236"/>
+      <c r="AL40" s="237"/>
       <c r="AM40" s="12"/>
       <c r="AN40" s="12"/>
     </row>
@@ -16798,7 +16796,7 @@
       <c r="W41" s="14">
         <v>0</v>
       </c>
-      <c r="X41" s="113">
+      <c r="X41" s="112">
         <v>0</v>
       </c>
       <c r="Y41" s="14">
@@ -16824,8 +16822,8 @@
       <c r="AH41" s="52"/>
       <c r="AI41" s="52"/>
       <c r="AJ41" s="52"/>
-      <c r="AK41" s="166"/>
-      <c r="AL41" s="167"/>
+      <c r="AK41" s="236"/>
+      <c r="AL41" s="237"/>
     </row>
     <row r="42" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A42" s="12"/>
@@ -16895,7 +16893,7 @@
       <c r="W42" s="14">
         <v>0</v>
       </c>
-      <c r="X42" s="113">
+      <c r="X42" s="112">
         <v>0</v>
       </c>
       <c r="Y42" s="14">
@@ -16909,25 +16907,25 @@
       <c r="AA42" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AB42" s="188">
+      <c r="AB42" s="211">
         <f>SUM(Y40:Y53)</f>
         <v>0</v>
       </c>
-      <c r="AC42" s="189"/>
+      <c r="AC42" s="212"/>
       <c r="AD42" s="16">
         <f t="shared" ref="AD42:AD59" si="16">X42</f>
         <v>0</v>
       </c>
       <c r="AE42" s="17"/>
-      <c r="AF42" s="178" t="s">
+      <c r="AF42" s="175" t="s">
         <v>61</v>
       </c>
-      <c r="AG42" s="179"/>
-      <c r="AH42" s="179"/>
-      <c r="AI42" s="179"/>
-      <c r="AJ42" s="180"/>
-      <c r="AK42" s="168"/>
-      <c r="AL42" s="167"/>
+      <c r="AG42" s="176"/>
+      <c r="AH42" s="176"/>
+      <c r="AI42" s="176"/>
+      <c r="AJ42" s="223"/>
+      <c r="AK42" s="238"/>
+      <c r="AL42" s="237"/>
     </row>
     <row r="43" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A43" s="12"/>
@@ -16997,7 +16995,7 @@
       <c r="W43" s="14">
         <v>0</v>
       </c>
-      <c r="X43" s="113">
+      <c r="X43" s="112">
         <v>0</v>
       </c>
       <c r="Y43" s="14">
@@ -17011,8 +17009,8 @@
       <c r="AA43" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="AB43" s="188"/>
-      <c r="AC43" s="189"/>
+      <c r="AB43" s="211"/>
+      <c r="AC43" s="212"/>
       <c r="AD43" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17023,8 +17021,8 @@
       <c r="AH43" s="54"/>
       <c r="AI43" s="54"/>
       <c r="AJ43" s="55"/>
-      <c r="AK43" s="168"/>
-      <c r="AL43" s="167"/>
+      <c r="AK43" s="238"/>
+      <c r="AL43" s="237"/>
     </row>
     <row r="44" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A44" s="12"/>
@@ -17094,7 +17092,7 @@
       <c r="W44" s="14">
         <v>0</v>
       </c>
-      <c r="X44" s="113">
+      <c r="X44" s="112">
         <v>0</v>
       </c>
       <c r="Y44" s="14">
@@ -17108,8 +17106,8 @@
       <c r="AA44" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="AB44" s="188"/>
-      <c r="AC44" s="189"/>
+      <c r="AB44" s="211"/>
+      <c r="AC44" s="212"/>
       <c r="AD44" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17120,8 +17118,8 @@
       <c r="AH44" s="54"/>
       <c r="AI44" s="54"/>
       <c r="AJ44" s="55"/>
-      <c r="AK44" s="168"/>
-      <c r="AL44" s="167"/>
+      <c r="AK44" s="238"/>
+      <c r="AL44" s="237"/>
     </row>
     <row r="45" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A45" s="12"/>
@@ -17191,7 +17189,7 @@
       <c r="W45" s="14">
         <v>0</v>
       </c>
-      <c r="X45" s="113">
+      <c r="X45" s="112">
         <v>0</v>
       </c>
       <c r="Y45" s="14">
@@ -17205,8 +17203,8 @@
       <c r="AA45" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="AB45" s="188"/>
-      <c r="AC45" s="189"/>
+      <c r="AB45" s="211"/>
+      <c r="AC45" s="212"/>
       <c r="AD45" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17217,8 +17215,8 @@
       <c r="AH45" s="54"/>
       <c r="AI45" s="54"/>
       <c r="AJ45" s="55"/>
-      <c r="AK45" s="168"/>
-      <c r="AL45" s="167"/>
+      <c r="AK45" s="238"/>
+      <c r="AL45" s="237"/>
     </row>
     <row r="46" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A46" s="12"/>
@@ -17288,7 +17286,7 @@
       <c r="W46" s="14">
         <v>0</v>
       </c>
-      <c r="X46" s="113">
+      <c r="X46" s="112">
         <v>0</v>
       </c>
       <c r="Y46" s="14">
@@ -17302,8 +17300,8 @@
       <c r="AA46" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="AB46" s="188"/>
-      <c r="AC46" s="189"/>
+      <c r="AB46" s="211"/>
+      <c r="AC46" s="212"/>
       <c r="AD46" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17314,8 +17312,8 @@
       <c r="AH46" s="54"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="55"/>
-      <c r="AK46" s="168"/>
-      <c r="AL46" s="167"/>
+      <c r="AK46" s="238"/>
+      <c r="AL46" s="237"/>
     </row>
     <row r="47" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A47" s="12"/>
@@ -17385,7 +17383,7 @@
       <c r="W47" s="14">
         <v>0</v>
       </c>
-      <c r="X47" s="113">
+      <c r="X47" s="112">
         <v>0</v>
       </c>
       <c r="Y47" s="14">
@@ -17399,23 +17397,23 @@
       <c r="AA47" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AB47" s="188"/>
-      <c r="AC47" s="189"/>
+      <c r="AB47" s="211"/>
+      <c r="AC47" s="212"/>
       <c r="AD47" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE47" s="17"/>
-      <c r="AF47" s="190">
+      <c r="AF47" s="216">
         <f>SUM(AD41:AD53)</f>
         <v>0</v>
       </c>
-      <c r="AG47" s="191"/>
-      <c r="AH47" s="191"/>
-      <c r="AI47" s="191"/>
-      <c r="AJ47" s="192"/>
-      <c r="AK47" s="168"/>
-      <c r="AL47" s="167"/>
+      <c r="AG47" s="214"/>
+      <c r="AH47" s="214"/>
+      <c r="AI47" s="214"/>
+      <c r="AJ47" s="215"/>
+      <c r="AK47" s="238"/>
+      <c r="AL47" s="237"/>
     </row>
     <row r="48" spans="1:40" s="47" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A48" s="12"/>
@@ -17485,7 +17483,7 @@
       <c r="W48" s="14">
         <v>0</v>
       </c>
-      <c r="X48" s="113">
+      <c r="X48" s="112">
         <v>0</v>
       </c>
       <c r="Y48" s="14">
@@ -17499,8 +17497,8 @@
       <c r="AA48" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AB48" s="188"/>
-      <c r="AC48" s="189"/>
+      <c r="AB48" s="211"/>
+      <c r="AC48" s="212"/>
       <c r="AD48" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17511,8 +17509,8 @@
       <c r="AH48" s="54"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="55"/>
-      <c r="AK48" s="168"/>
-      <c r="AL48" s="167"/>
+      <c r="AK48" s="238"/>
+      <c r="AL48" s="237"/>
     </row>
     <row r="49" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A49" s="12"/>
@@ -17582,7 +17580,7 @@
       <c r="W49" s="14">
         <v>0</v>
       </c>
-      <c r="X49" s="117">
+      <c r="X49" s="116">
         <v>0</v>
       </c>
       <c r="Y49" s="14">
@@ -17596,8 +17594,8 @@
       <c r="AA49" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AB49" s="188"/>
-      <c r="AC49" s="189"/>
+      <c r="AB49" s="211"/>
+      <c r="AC49" s="212"/>
       <c r="AD49" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17608,8 +17606,8 @@
       <c r="AH49" s="54"/>
       <c r="AI49" s="54"/>
       <c r="AJ49" s="55"/>
-      <c r="AK49" s="168"/>
-      <c r="AL49" s="167"/>
+      <c r="AK49" s="238"/>
+      <c r="AL49" s="237"/>
     </row>
     <row r="50" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A50" s="12"/>
@@ -17679,7 +17677,7 @@
       <c r="W50" s="14">
         <v>0</v>
       </c>
-      <c r="X50" s="117">
+      <c r="X50" s="116">
         <v>0</v>
       </c>
       <c r="Y50" s="14">
@@ -17693,8 +17691,8 @@
       <c r="AA50" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AB50" s="188"/>
-      <c r="AC50" s="189"/>
+      <c r="AB50" s="211"/>
+      <c r="AC50" s="212"/>
       <c r="AD50" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17705,8 +17703,8 @@
       <c r="AH50" s="54"/>
       <c r="AI50" s="54"/>
       <c r="AJ50" s="55"/>
-      <c r="AK50" s="168"/>
-      <c r="AL50" s="167"/>
+      <c r="AK50" s="238"/>
+      <c r="AL50" s="237"/>
     </row>
     <row r="51" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A51" s="12"/>
@@ -17776,7 +17774,7 @@
       <c r="W51" s="14">
         <v>0</v>
       </c>
-      <c r="X51" s="113">
+      <c r="X51" s="112">
         <v>0</v>
       </c>
       <c r="Y51" s="14">
@@ -17790,8 +17788,8 @@
       <c r="AA51" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AB51" s="188"/>
-      <c r="AC51" s="189"/>
+      <c r="AB51" s="211"/>
+      <c r="AC51" s="212"/>
       <c r="AD51" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17802,8 +17800,8 @@
       <c r="AH51" s="54"/>
       <c r="AI51" s="54"/>
       <c r="AJ51" s="55"/>
-      <c r="AK51" s="168"/>
-      <c r="AL51" s="167"/>
+      <c r="AK51" s="238"/>
+      <c r="AL51" s="237"/>
     </row>
     <row r="52" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A52" s="12"/>
@@ -17873,7 +17871,7 @@
       <c r="W52" s="14">
         <v>0</v>
       </c>
-      <c r="X52" s="113">
+      <c r="X52" s="112">
         <v>0</v>
       </c>
       <c r="Y52" s="14">
@@ -17899,8 +17897,8 @@
       <c r="AH52" s="54"/>
       <c r="AI52" s="54"/>
       <c r="AJ52" s="55"/>
-      <c r="AK52" s="168"/>
-      <c r="AL52" s="167"/>
+      <c r="AK52" s="238"/>
+      <c r="AL52" s="237"/>
     </row>
     <row r="53" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A53" s="12"/>
@@ -17970,7 +17968,7 @@
       <c r="W53" s="14">
         <v>0</v>
       </c>
-      <c r="X53" s="113">
+      <c r="X53" s="112">
         <v>0</v>
       </c>
       <c r="Y53" s="14">
@@ -17996,8 +17994,8 @@
       <c r="AH53" s="62"/>
       <c r="AI53" s="62"/>
       <c r="AJ53" s="63"/>
-      <c r="AK53" s="168"/>
-      <c r="AL53" s="167"/>
+      <c r="AK53" s="238"/>
+      <c r="AL53" s="237"/>
     </row>
     <row r="54" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A54" s="12"/>
@@ -18086,14 +18084,14 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="X54" s="114">
+      <c r="X54" s="113">
         <v>0</v>
       </c>
       <c r="Y54" s="14"/>
       <c r="Z54" s="14"/>
       <c r="AA54" s="13"/>
-      <c r="AB54" s="183"/>
-      <c r="AC54" s="184"/>
+      <c r="AB54" s="221"/>
+      <c r="AC54" s="222"/>
       <c r="AD54" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -18104,8 +18102,8 @@
       <c r="AH54" s="54"/>
       <c r="AI54" s="54"/>
       <c r="AJ54" s="54"/>
-      <c r="AK54" s="166"/>
-      <c r="AL54" s="167"/>
+      <c r="AK54" s="236"/>
+      <c r="AL54" s="237"/>
     </row>
     <row r="55" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B55" s="13" t="s">
@@ -18174,7 +18172,7 @@
       <c r="W55" s="14">
         <v>0</v>
       </c>
-      <c r="X55" s="113">
+      <c r="X55" s="112">
         <v>0</v>
       </c>
       <c r="Y55" s="14">
@@ -18188,8 +18186,8 @@
       <c r="AA55" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="AB55" s="172"/>
-      <c r="AC55" s="173"/>
+      <c r="AB55" s="149"/>
+      <c r="AC55" s="150"/>
       <c r="AD55" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -18200,8 +18198,8 @@
       <c r="AH55" s="2"/>
       <c r="AI55" s="2"/>
       <c r="AJ55" s="2"/>
-      <c r="AK55" s="166"/>
-      <c r="AL55" s="167"/>
+      <c r="AK55" s="236"/>
+      <c r="AL55" s="237"/>
       <c r="AM55" s="4"/>
       <c r="AN55" s="4"/>
     </row>
@@ -18250,7 +18248,7 @@
       <c r="W56" s="14">
         <v>0</v>
       </c>
-      <c r="X56" s="113">
+      <c r="X56" s="112">
         <v>0</v>
       </c>
       <c r="Y56" s="14">
@@ -18274,8 +18272,8 @@
       <c r="AH56" s="2"/>
       <c r="AI56" s="2"/>
       <c r="AJ56" s="2"/>
-      <c r="AK56" s="166"/>
-      <c r="AL56" s="167"/>
+      <c r="AK56" s="236"/>
+      <c r="AL56" s="237"/>
       <c r="AM56" s="67"/>
       <c r="AN56" s="67"/>
     </row>
@@ -18346,7 +18344,7 @@
       <c r="W57" s="14">
         <v>0</v>
       </c>
-      <c r="X57" s="113">
+      <c r="X57" s="112">
         <v>0</v>
       </c>
       <c r="Y57" s="14">
@@ -18364,7 +18362,7 @@
         <f>Y57*4</f>
         <v>0</v>
       </c>
-      <c r="AC57" s="159">
+      <c r="AC57" s="219">
         <f>SUM(C59:W59)</f>
         <v>0</v>
       </c>
@@ -18375,8 +18373,8 @@
       <c r="AE57" s="17"/>
       <c r="AF57" s="69"/>
       <c r="AG57" s="69"/>
-      <c r="AK57" s="166"/>
-      <c r="AL57" s="167"/>
+      <c r="AK57" s="236"/>
+      <c r="AL57" s="237"/>
     </row>
     <row r="58" spans="1:40" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B58" s="15" t="s">
@@ -18445,7 +18443,7 @@
       <c r="W58" s="14">
         <v>0</v>
       </c>
-      <c r="X58" s="113">
+      <c r="X58" s="112">
         <v>0</v>
       </c>
       <c r="Y58" s="14">
@@ -18463,14 +18461,14 @@
         <f>Y58*4</f>
         <v>0</v>
       </c>
-      <c r="AC58" s="161"/>
+      <c r="AC58" s="220"/>
       <c r="AD58" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE58" s="17"/>
-      <c r="AK58" s="166"/>
-      <c r="AL58" s="167"/>
+      <c r="AK58" s="236"/>
+      <c r="AL58" s="237"/>
     </row>
     <row r="59" spans="1:40" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B59" s="15"/>
@@ -18558,79 +18556,79 @@
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="X59" s="114"/>
+      <c r="X59" s="113"/>
       <c r="Y59" s="14"/>
       <c r="Z59" s="14"/>
       <c r="AA59" s="68"/>
-      <c r="AB59" s="193"/>
-      <c r="AC59" s="194"/>
+      <c r="AB59" s="143"/>
+      <c r="AC59" s="144"/>
       <c r="AD59" s="33">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE59" s="17"/>
-      <c r="AK59" s="166"/>
-      <c r="AL59" s="167"/>
+      <c r="AK59" s="236"/>
+      <c r="AL59" s="237"/>
     </row>
     <row r="60" spans="1:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B60" s="130" t="s">
+      <c r="B60" s="167" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="128" t="s">
+      <c r="C60" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="129"/>
-      <c r="E60" s="128" t="s">
+      <c r="D60" s="136"/>
+      <c r="E60" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F60" s="129"/>
-      <c r="G60" s="128" t="s">
+      <c r="F60" s="136"/>
+      <c r="G60" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H60" s="129"/>
-      <c r="I60" s="128" t="s">
+      <c r="H60" s="136"/>
+      <c r="I60" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J60" s="129"/>
-      <c r="K60" s="128" t="s">
+      <c r="J60" s="136"/>
+      <c r="K60" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L60" s="129"/>
-      <c r="M60" s="128" t="s">
+      <c r="L60" s="136"/>
+      <c r="M60" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N60" s="129"/>
-      <c r="O60" s="128" t="s">
+      <c r="N60" s="136"/>
+      <c r="O60" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P60" s="129"/>
-      <c r="Q60" s="128" t="s">
+      <c r="P60" s="136"/>
+      <c r="Q60" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R60" s="129"/>
-      <c r="S60" s="128" t="s">
+      <c r="R60" s="136"/>
+      <c r="S60" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T60" s="129"/>
-      <c r="U60" s="128" t="s">
+      <c r="T60" s="136"/>
+      <c r="U60" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V60" s="129"/>
-      <c r="W60" s="130" t="s">
+      <c r="V60" s="136"/>
+      <c r="W60" s="167" t="s">
         <v>12</v>
       </c>
-      <c r="X60" s="111"/>
-      <c r="Y60" s="130" t="s">
+      <c r="X60" s="110"/>
+      <c r="Y60" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="Z60" s="130" t="s">
+      <c r="Z60" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="AA60" s="130" t="s">
+      <c r="AA60" s="167" t="s">
         <v>77</v>
       </c>
-      <c r="AB60" s="134"/>
-      <c r="AC60" s="135"/>
+      <c r="AB60" s="139"/>
+      <c r="AC60" s="140"/>
       <c r="AD60" s="6" t="s">
         <v>16</v>
       </c>
@@ -18639,7 +18637,7 @@
       <c r="AL60" s="71"/>
     </row>
     <row r="61" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B61" s="131"/>
+      <c r="B61" s="168"/>
       <c r="C61" s="9" t="s">
         <v>17</v>
       </c>
@@ -18700,11 +18698,11 @@
       <c r="V61" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W61" s="131"/>
-      <c r="X61" s="112"/>
-      <c r="Y61" s="131"/>
-      <c r="Z61" s="131"/>
-      <c r="AA61" s="131"/>
+      <c r="W61" s="168"/>
+      <c r="X61" s="111"/>
+      <c r="Y61" s="168"/>
+      <c r="Z61" s="168"/>
+      <c r="AA61" s="168"/>
       <c r="AB61" s="10"/>
       <c r="AC61" s="11"/>
       <c r="AD61" s="6"/>
@@ -18784,7 +18782,7 @@
       <c r="W62" s="14">
         <v>0</v>
       </c>
-      <c r="X62" s="113">
+      <c r="X62" s="112">
         <v>0</v>
       </c>
       <c r="Y62" s="14">
@@ -18798,11 +18796,11 @@
       <c r="AA62" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AB62" s="174">
+      <c r="AB62" s="171">
         <f>SUM(Y62:Y68)</f>
         <v>0</v>
       </c>
-      <c r="AC62" s="175"/>
+      <c r="AC62" s="172"/>
       <c r="AD62" s="16">
         <f>X62</f>
         <v>0</v>
@@ -18883,7 +18881,7 @@
       <c r="W63" s="14">
         <v>0</v>
       </c>
-      <c r="X63" s="113">
+      <c r="X63" s="112">
         <v>0</v>
       </c>
       <c r="Y63" s="14">
@@ -18897,20 +18895,20 @@
       <c r="AA63" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AB63" s="188"/>
-      <c r="AC63" s="189"/>
+      <c r="AB63" s="211"/>
+      <c r="AC63" s="212"/>
       <c r="AD63" s="16">
         <f t="shared" ref="AD63:AD68" si="21">X63</f>
         <v>0</v>
       </c>
       <c r="AE63" s="17"/>
-      <c r="AF63" s="195" t="s">
+      <c r="AF63" s="213" t="s">
         <v>77</v>
       </c>
-      <c r="AG63" s="191"/>
-      <c r="AH63" s="191"/>
-      <c r="AI63" s="191"/>
-      <c r="AJ63" s="192"/>
+      <c r="AG63" s="214"/>
+      <c r="AH63" s="214"/>
+      <c r="AI63" s="214"/>
+      <c r="AJ63" s="215"/>
       <c r="AK63" s="70"/>
       <c r="AL63" s="71"/>
     </row>
@@ -18981,7 +18979,7 @@
       <c r="W64" s="14">
         <v>0</v>
       </c>
-      <c r="X64" s="113">
+      <c r="X64" s="112">
         <v>0</v>
       </c>
       <c r="Y64" s="14">
@@ -18995,21 +18993,21 @@
       <c r="AA64" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AB64" s="188"/>
-      <c r="AC64" s="189"/>
+      <c r="AB64" s="211"/>
+      <c r="AC64" s="212"/>
       <c r="AD64" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE64" s="17"/>
-      <c r="AF64" s="190">
+      <c r="AF64" s="216">
         <f>SUM(AD62:AD68)</f>
         <v>0</v>
       </c>
-      <c r="AG64" s="196"/>
-      <c r="AH64" s="196"/>
-      <c r="AI64" s="196"/>
-      <c r="AJ64" s="197"/>
+      <c r="AG64" s="217"/>
+      <c r="AH64" s="217"/>
+      <c r="AI64" s="217"/>
+      <c r="AJ64" s="218"/>
       <c r="AK64" s="70"/>
       <c r="AL64" s="71"/>
     </row>
@@ -19080,7 +19078,7 @@
       <c r="W65" s="14">
         <v>0</v>
       </c>
-      <c r="X65" s="113">
+      <c r="X65" s="112">
         <v>0</v>
       </c>
       <c r="Y65" s="14">
@@ -19094,8 +19092,8 @@
       <c r="AA65" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AB65" s="188"/>
-      <c r="AC65" s="189"/>
+      <c r="AB65" s="211"/>
+      <c r="AC65" s="212"/>
       <c r="AD65" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19176,7 +19174,7 @@
       <c r="W66" s="14">
         <v>0</v>
       </c>
-      <c r="X66" s="113">
+      <c r="X66" s="112">
         <v>0</v>
       </c>
       <c r="Y66" s="14">
@@ -19190,8 +19188,8 @@
       <c r="AA66" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AB66" s="188"/>
-      <c r="AC66" s="189"/>
+      <c r="AB66" s="211"/>
+      <c r="AC66" s="212"/>
       <c r="AD66" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19272,7 +19270,7 @@
       <c r="W67" s="14">
         <v>0</v>
       </c>
-      <c r="X67" s="113">
+      <c r="X67" s="112">
         <v>0</v>
       </c>
       <c r="Y67" s="14">
@@ -19286,8 +19284,8 @@
       <c r="AA67" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AB67" s="176"/>
-      <c r="AC67" s="177"/>
+      <c r="AB67" s="173"/>
+      <c r="AC67" s="174"/>
       <c r="AD67" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19368,7 +19366,7 @@
       <c r="W68" s="14">
         <v>0</v>
       </c>
-      <c r="X68" s="113">
+      <c r="X68" s="112">
         <v>0</v>
       </c>
       <c r="Y68" s="14">
@@ -19382,8 +19380,8 @@
       <c r="AA68" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AB68" s="172"/>
-      <c r="AC68" s="173"/>
+      <c r="AB68" s="149"/>
+      <c r="AC68" s="150"/>
       <c r="AD68" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19483,12 +19481,12 @@
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="X69" s="114"/>
+      <c r="X69" s="113"/>
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
       <c r="AA69" s="13"/>
-      <c r="AB69" s="172"/>
-      <c r="AC69" s="173"/>
+      <c r="AB69" s="149"/>
+      <c r="AC69" s="150"/>
       <c r="AD69" s="16">
         <v>0</v>
       </c>
@@ -19505,50 +19503,50 @@
       <c r="B70" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="128" t="s">
+      <c r="C70" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="129"/>
-      <c r="E70" s="128" t="s">
+      <c r="D70" s="136"/>
+      <c r="E70" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F70" s="129"/>
-      <c r="G70" s="128" t="s">
+      <c r="F70" s="136"/>
+      <c r="G70" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H70" s="129"/>
-      <c r="I70" s="128" t="s">
+      <c r="H70" s="136"/>
+      <c r="I70" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J70" s="129"/>
-      <c r="K70" s="128" t="s">
+      <c r="J70" s="136"/>
+      <c r="K70" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L70" s="129"/>
-      <c r="M70" s="128" t="s">
+      <c r="L70" s="136"/>
+      <c r="M70" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N70" s="129"/>
-      <c r="O70" s="128" t="s">
+      <c r="N70" s="136"/>
+      <c r="O70" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P70" s="129"/>
-      <c r="Q70" s="128" t="s">
+      <c r="P70" s="136"/>
+      <c r="Q70" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R70" s="129"/>
-      <c r="S70" s="128" t="s">
+      <c r="R70" s="136"/>
+      <c r="S70" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T70" s="129"/>
-      <c r="U70" s="128" t="s">
+      <c r="T70" s="136"/>
+      <c r="U70" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V70" s="129"/>
+      <c r="V70" s="136"/>
       <c r="W70" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X70" s="119"/>
+      <c r="X70" s="118"/>
       <c r="Y70" s="49" t="s">
         <v>13</v>
       </c>
@@ -19558,8 +19556,8 @@
       <c r="AA70" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AB70" s="134"/>
-      <c r="AC70" s="135"/>
+      <c r="AB70" s="139"/>
+      <c r="AC70" s="140"/>
       <c r="AD70" s="6" t="s">
         <v>16</v>
       </c>
@@ -19641,7 +19639,7 @@
       <c r="W71" s="14">
         <v>0</v>
       </c>
-      <c r="X71" s="113">
+      <c r="X71" s="112">
         <v>0</v>
       </c>
       <c r="Y71" s="14">
@@ -19655,28 +19653,28 @@
       <c r="AA71" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AB71" s="174">
+      <c r="AB71" s="171">
         <f>SUM(Y71:Y72)</f>
         <v>0</v>
       </c>
-      <c r="AC71" s="175"/>
+      <c r="AC71" s="172"/>
       <c r="AD71" s="16">
         <f>X71</f>
         <v>0</v>
       </c>
       <c r="AE71" s="17"/>
-      <c r="AF71" s="198" t="s">
+      <c r="AF71" s="209" t="s">
         <v>86</v>
       </c>
-      <c r="AG71" s="199"/>
-      <c r="AH71" s="199"/>
-      <c r="AI71" s="199"/>
-      <c r="AJ71" s="199"/>
-      <c r="AK71" s="203">
+      <c r="AG71" s="210"/>
+      <c r="AH71" s="210"/>
+      <c r="AI71" s="210"/>
+      <c r="AJ71" s="210"/>
+      <c r="AK71" s="201">
         <f>SUM(AD71:AD81)</f>
         <v>0</v>
       </c>
-      <c r="AL71" s="204"/>
+      <c r="AL71" s="202"/>
       <c r="AM71" s="29"/>
       <c r="AN71" s="29"/>
     </row>
@@ -19747,7 +19745,7 @@
       <c r="W72" s="14">
         <v>0</v>
       </c>
-      <c r="X72" s="113">
+      <c r="X72" s="112">
         <v>0</v>
       </c>
       <c r="Y72" s="14">
@@ -19761,23 +19759,23 @@
       <c r="AA72" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="AB72" s="176"/>
-      <c r="AC72" s="177"/>
+      <c r="AB72" s="173"/>
+      <c r="AC72" s="174"/>
       <c r="AD72" s="16">
         <f t="shared" ref="AD72:AD86" si="23">X72</f>
         <v>0</v>
       </c>
       <c r="AE72" s="75"/>
-      <c r="AF72" s="169">
+      <c r="AF72" s="197">
         <f>+AD71+AD72</f>
         <v>0</v>
       </c>
-      <c r="AG72" s="200"/>
-      <c r="AH72" s="200"/>
-      <c r="AI72" s="200"/>
-      <c r="AJ72" s="200"/>
-      <c r="AK72" s="205"/>
-      <c r="AL72" s="206"/>
+      <c r="AG72" s="198"/>
+      <c r="AH72" s="198"/>
+      <c r="AI72" s="198"/>
+      <c r="AJ72" s="198"/>
+      <c r="AK72" s="203"/>
+      <c r="AL72" s="204"/>
       <c r="AM72" s="12"/>
       <c r="AN72" s="12"/>
     </row>
@@ -19867,14 +19865,14 @@
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="X73" s="114">
+      <c r="X73" s="113">
         <v>0</v>
       </c>
       <c r="Y73" s="14"/>
       <c r="Z73" s="14"/>
       <c r="AA73" s="38"/>
-      <c r="AB73" s="207"/>
-      <c r="AC73" s="208"/>
+      <c r="AB73" s="205"/>
+      <c r="AC73" s="206"/>
       <c r="AD73" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -19885,8 +19883,8 @@
       <c r="AH73" s="76"/>
       <c r="AI73" s="76"/>
       <c r="AJ73" s="76"/>
-      <c r="AK73" s="205"/>
-      <c r="AL73" s="206"/>
+      <c r="AK73" s="203"/>
+      <c r="AL73" s="204"/>
       <c r="AM73" s="12"/>
       <c r="AN73" s="12"/>
     </row>
@@ -19957,7 +19955,7 @@
       <c r="W74" s="14">
         <v>0</v>
       </c>
-      <c r="X74" s="117">
+      <c r="X74" s="116">
         <v>0</v>
       </c>
       <c r="Y74" s="14">
@@ -19971,25 +19969,25 @@
       <c r="AA74" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="AB74" s="174">
+      <c r="AB74" s="171">
         <f>SUM(Y74:Y75)</f>
         <v>0</v>
       </c>
-      <c r="AC74" s="175"/>
+      <c r="AC74" s="172"/>
       <c r="AD74" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE74" s="17"/>
-      <c r="AF74" s="178" t="s">
+      <c r="AF74" s="175" t="s">
         <v>89</v>
       </c>
-      <c r="AG74" s="179"/>
-      <c r="AH74" s="179"/>
-      <c r="AI74" s="179"/>
-      <c r="AJ74" s="179"/>
-      <c r="AK74" s="205"/>
-      <c r="AL74" s="206"/>
+      <c r="AG74" s="176"/>
+      <c r="AH74" s="176"/>
+      <c r="AI74" s="176"/>
+      <c r="AJ74" s="176"/>
+      <c r="AK74" s="203"/>
+      <c r="AL74" s="204"/>
     </row>
     <row r="75" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B75" s="13" t="s">
@@ -20058,7 +20056,7 @@
       <c r="W75" s="14">
         <v>0</v>
       </c>
-      <c r="X75" s="117">
+      <c r="X75" s="116">
         <v>0</v>
       </c>
       <c r="Y75" s="14">
@@ -20072,23 +20070,23 @@
       <c r="AA75" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AB75" s="176"/>
-      <c r="AC75" s="177"/>
+      <c r="AB75" s="173"/>
+      <c r="AC75" s="174"/>
       <c r="AD75" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE75" s="17"/>
-      <c r="AF75" s="169">
+      <c r="AF75" s="197">
         <f>+AD74+AD75</f>
         <v>0</v>
       </c>
-      <c r="AG75" s="200"/>
-      <c r="AH75" s="200"/>
-      <c r="AI75" s="200"/>
-      <c r="AJ75" s="200"/>
-      <c r="AK75" s="205"/>
-      <c r="AL75" s="206"/>
+      <c r="AG75" s="198"/>
+      <c r="AH75" s="198"/>
+      <c r="AI75" s="198"/>
+      <c r="AJ75" s="198"/>
+      <c r="AK75" s="203"/>
+      <c r="AL75" s="204"/>
     </row>
     <row r="76" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B76" s="13" t="s">
@@ -20157,7 +20155,7 @@
       <c r="W76" s="14">
         <v>0</v>
       </c>
-      <c r="X76" s="113">
+      <c r="X76" s="112">
         <v>0</v>
       </c>
       <c r="Y76" s="14">
@@ -20171,25 +20169,25 @@
       <c r="AA76" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AB76" s="174">
+      <c r="AB76" s="171">
         <f>SUM(Y76:Y77)</f>
         <v>0</v>
       </c>
-      <c r="AC76" s="175"/>
+      <c r="AC76" s="172"/>
       <c r="AD76" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE76" s="17"/>
-      <c r="AF76" s="178" t="s">
+      <c r="AF76" s="175" t="s">
         <v>92</v>
       </c>
-      <c r="AG76" s="179"/>
-      <c r="AH76" s="179"/>
-      <c r="AI76" s="179"/>
-      <c r="AJ76" s="179"/>
-      <c r="AK76" s="205"/>
-      <c r="AL76" s="206"/>
+      <c r="AG76" s="176"/>
+      <c r="AH76" s="176"/>
+      <c r="AI76" s="176"/>
+      <c r="AJ76" s="176"/>
+      <c r="AK76" s="203"/>
+      <c r="AL76" s="204"/>
     </row>
     <row r="77" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B77" s="13" t="s">
@@ -20258,7 +20256,7 @@
       <c r="W77" s="14">
         <v>0</v>
       </c>
-      <c r="X77" s="113">
+      <c r="X77" s="112">
         <v>0</v>
       </c>
       <c r="Y77" s="14">
@@ -20272,23 +20270,23 @@
       <c r="AA77" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB77" s="176"/>
-      <c r="AC77" s="177"/>
+      <c r="AB77" s="173"/>
+      <c r="AC77" s="174"/>
       <c r="AD77" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE77" s="17"/>
-      <c r="AF77" s="169">
+      <c r="AF77" s="197">
         <f>+AD76+AD77</f>
         <v>0</v>
       </c>
-      <c r="AG77" s="200"/>
-      <c r="AH77" s="200"/>
-      <c r="AI77" s="200"/>
-      <c r="AJ77" s="200"/>
-      <c r="AK77" s="205"/>
-      <c r="AL77" s="206"/>
+      <c r="AG77" s="198"/>
+      <c r="AH77" s="198"/>
+      <c r="AI77" s="198"/>
+      <c r="AJ77" s="198"/>
+      <c r="AK77" s="203"/>
+      <c r="AL77" s="204"/>
     </row>
     <row r="78" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B78" s="13" t="s">
@@ -20357,7 +20355,7 @@
       <c r="W78" s="14">
         <v>0</v>
       </c>
-      <c r="X78" s="117">
+      <c r="X78" s="116">
         <v>0</v>
       </c>
       <c r="Y78" s="14">
@@ -20371,25 +20369,25 @@
       <c r="AA78" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AB78" s="174">
+      <c r="AB78" s="171">
         <f>SUM(Y78:Y79)</f>
         <v>0</v>
       </c>
-      <c r="AC78" s="175"/>
+      <c r="AC78" s="172"/>
       <c r="AD78" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE78" s="17"/>
-      <c r="AF78" s="178" t="s">
+      <c r="AF78" s="175" t="s">
         <v>95</v>
       </c>
-      <c r="AG78" s="179"/>
-      <c r="AH78" s="179"/>
-      <c r="AI78" s="179"/>
-      <c r="AJ78" s="179"/>
-      <c r="AK78" s="205"/>
-      <c r="AL78" s="206"/>
+      <c r="AG78" s="176"/>
+      <c r="AH78" s="176"/>
+      <c r="AI78" s="176"/>
+      <c r="AJ78" s="176"/>
+      <c r="AK78" s="203"/>
+      <c r="AL78" s="204"/>
     </row>
     <row r="79" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B79" s="13" t="s">
@@ -20458,7 +20456,7 @@
       <c r="W79" s="14">
         <v>0</v>
       </c>
-      <c r="X79" s="113">
+      <c r="X79" s="112">
         <v>0</v>
       </c>
       <c r="Y79" s="14">
@@ -20472,21 +20470,21 @@
       <c r="AA79" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AB79" s="176"/>
-      <c r="AC79" s="177"/>
+      <c r="AB79" s="173"/>
+      <c r="AC79" s="174"/>
       <c r="AD79" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE79" s="17"/>
-      <c r="AF79" s="169">
+      <c r="AF79" s="197">
         <f>+AD78+AD79</f>
         <v>0</v>
       </c>
-      <c r="AG79" s="200"/>
-      <c r="AH79" s="200"/>
-      <c r="AI79" s="200"/>
-      <c r="AJ79" s="200"/>
+      <c r="AG79" s="198"/>
+      <c r="AH79" s="198"/>
+      <c r="AI79" s="198"/>
+      <c r="AJ79" s="198"/>
       <c r="AK79" s="77"/>
       <c r="AL79" s="78"/>
     </row>
@@ -20557,7 +20555,7 @@
       <c r="W80" s="14">
         <v>0</v>
       </c>
-      <c r="X80" s="113">
+      <c r="X80" s="112">
         <v>0</v>
       </c>
       <c r="Y80" s="14">
@@ -20571,27 +20569,27 @@
       <c r="AA80" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AB80" s="174">
+      <c r="AB80" s="171">
         <f>SUM(Y80:Y81)</f>
         <v>0</v>
       </c>
-      <c r="AC80" s="175"/>
+      <c r="AC80" s="172"/>
       <c r="AD80" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE80" s="17"/>
-      <c r="AF80" s="178" t="s">
+      <c r="AF80" s="175" t="s">
         <v>98</v>
       </c>
-      <c r="AG80" s="179"/>
-      <c r="AH80" s="179"/>
-      <c r="AI80" s="179"/>
-      <c r="AJ80" s="179"/>
-      <c r="AK80" s="201" t="s">
+      <c r="AG80" s="176"/>
+      <c r="AH80" s="176"/>
+      <c r="AI80" s="176"/>
+      <c r="AJ80" s="176"/>
+      <c r="AK80" s="199" t="s">
         <v>99</v>
       </c>
-      <c r="AL80" s="202"/>
+      <c r="AL80" s="200"/>
     </row>
     <row r="81" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B81" s="13" t="s">
@@ -20660,7 +20658,7 @@
       <c r="W81" s="14">
         <v>0</v>
       </c>
-      <c r="X81" s="113">
+      <c r="X81" s="112">
         <v>0</v>
       </c>
       <c r="Y81" s="14">
@@ -20674,23 +20672,23 @@
       <c r="AA81" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB81" s="176"/>
-      <c r="AC81" s="177"/>
+      <c r="AB81" s="173"/>
+      <c r="AC81" s="174"/>
       <c r="AD81" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE81" s="17"/>
-      <c r="AF81" s="169">
+      <c r="AF81" s="197">
         <f>+AD80+AD81</f>
         <v>0</v>
       </c>
-      <c r="AG81" s="200"/>
-      <c r="AH81" s="200"/>
-      <c r="AI81" s="200"/>
-      <c r="AJ81" s="200"/>
-      <c r="AK81" s="201"/>
-      <c r="AL81" s="202"/>
+      <c r="AG81" s="198"/>
+      <c r="AH81" s="198"/>
+      <c r="AI81" s="198"/>
+      <c r="AJ81" s="198"/>
+      <c r="AK81" s="199"/>
+      <c r="AL81" s="200"/>
     </row>
     <row r="82" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B82" s="13" t="s">
@@ -20759,7 +20757,7 @@
       <c r="W82" s="14">
         <v>0</v>
       </c>
-      <c r="X82" s="113">
+      <c r="X82" s="112">
         <v>0</v>
       </c>
       <c r="Y82" s="14">
@@ -20773,8 +20771,8 @@
       <c r="AA82" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="AB82" s="172"/>
-      <c r="AC82" s="173"/>
+      <c r="AB82" s="149"/>
+      <c r="AC82" s="150"/>
       <c r="AD82" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20785,8 +20783,8 @@
       <c r="AH82" s="76"/>
       <c r="AI82" s="76"/>
       <c r="AJ82" s="76"/>
-      <c r="AK82" s="201"/>
-      <c r="AL82" s="202"/>
+      <c r="AK82" s="199"/>
+      <c r="AL82" s="200"/>
     </row>
     <row r="83" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B83" s="13" t="s">
@@ -20855,7 +20853,7 @@
       <c r="W83" s="14">
         <v>0</v>
       </c>
-      <c r="X83" s="113">
+      <c r="X83" s="112">
         <v>0</v>
       </c>
       <c r="Y83" s="14">
@@ -20869,8 +20867,8 @@
       <c r="AA83" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AB83" s="172"/>
-      <c r="AC83" s="173"/>
+      <c r="AB83" s="149"/>
+      <c r="AC83" s="150"/>
       <c r="AD83" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20881,8 +20879,8 @@
       <c r="AH83" s="76"/>
       <c r="AI83" s="76"/>
       <c r="AJ83" s="76"/>
-      <c r="AK83" s="201"/>
-      <c r="AL83" s="202"/>
+      <c r="AK83" s="199"/>
+      <c r="AL83" s="200"/>
     </row>
     <row r="84" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B84" s="13" t="s">
@@ -20951,7 +20949,7 @@
       <c r="W84" s="14">
         <v>0</v>
       </c>
-      <c r="X84" s="113">
+      <c r="X84" s="112">
         <v>0</v>
       </c>
       <c r="Y84" s="14">
@@ -20965,8 +20963,8 @@
       <c r="AA84" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="AB84" s="172"/>
-      <c r="AC84" s="173"/>
+      <c r="AB84" s="149"/>
+      <c r="AC84" s="150"/>
       <c r="AD84" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20977,8 +20975,8 @@
       <c r="AH84" s="76"/>
       <c r="AI84" s="76"/>
       <c r="AJ84" s="76"/>
-      <c r="AK84" s="201"/>
-      <c r="AL84" s="202"/>
+      <c r="AK84" s="199"/>
+      <c r="AL84" s="200"/>
     </row>
     <row r="85" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B85" s="13" t="s">
@@ -21047,7 +21045,7 @@
       <c r="W85" s="14">
         <v>0</v>
       </c>
-      <c r="X85" s="113">
+      <c r="X85" s="112">
         <v>0</v>
       </c>
       <c r="Y85" s="14">
@@ -21061,8 +21059,8 @@
       <c r="AA85" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AB85" s="172"/>
-      <c r="AC85" s="173"/>
+      <c r="AB85" s="149"/>
+      <c r="AC85" s="150"/>
       <c r="AD85" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21073,8 +21071,8 @@
       <c r="AH85" s="76"/>
       <c r="AI85" s="76"/>
       <c r="AJ85" s="76"/>
-      <c r="AK85" s="201"/>
-      <c r="AL85" s="202"/>
+      <c r="AK85" s="199"/>
+      <c r="AL85" s="200"/>
     </row>
     <row r="86" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B86" s="13" t="s">
@@ -21143,7 +21141,7 @@
       <c r="W86" s="14">
         <v>0</v>
       </c>
-      <c r="X86" s="113">
+      <c r="X86" s="112">
         <v>0</v>
       </c>
       <c r="Y86" s="14">
@@ -21157,11 +21155,11 @@
       <c r="AA86" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AB86" s="209">
+      <c r="AB86" s="207">
         <f>SUM(Y86:Y86)</f>
         <v>0</v>
       </c>
-      <c r="AC86" s="210"/>
+      <c r="AC86" s="208"/>
       <c r="AD86" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21172,57 +21170,57 @@
       <c r="AH86" s="2"/>
       <c r="AI86" s="2"/>
       <c r="AJ86" s="2"/>
-      <c r="AK86" s="201"/>
-      <c r="AL86" s="202"/>
+      <c r="AK86" s="199"/>
+      <c r="AL86" s="200"/>
     </row>
     <row r="87" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B87" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="C87" s="128" t="s">
+      <c r="C87" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D87" s="129"/>
-      <c r="E87" s="128" t="s">
+      <c r="D87" s="136"/>
+      <c r="E87" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F87" s="129"/>
-      <c r="G87" s="128" t="s">
+      <c r="F87" s="136"/>
+      <c r="G87" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H87" s="129"/>
-      <c r="I87" s="128" t="s">
+      <c r="H87" s="136"/>
+      <c r="I87" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J87" s="129"/>
-      <c r="K87" s="128" t="s">
+      <c r="J87" s="136"/>
+      <c r="K87" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L87" s="129"/>
-      <c r="M87" s="128" t="s">
+      <c r="L87" s="136"/>
+      <c r="M87" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N87" s="129"/>
-      <c r="O87" s="128" t="s">
+      <c r="N87" s="136"/>
+      <c r="O87" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P87" s="129"/>
-      <c r="Q87" s="128" t="s">
+      <c r="P87" s="136"/>
+      <c r="Q87" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R87" s="129"/>
-      <c r="S87" s="128" t="s">
+      <c r="R87" s="136"/>
+      <c r="S87" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T87" s="129"/>
-      <c r="U87" s="128" t="s">
+      <c r="T87" s="136"/>
+      <c r="U87" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V87" s="129"/>
+      <c r="V87" s="136"/>
       <c r="W87" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X87" s="119"/>
+      <c r="X87" s="118"/>
       <c r="Y87" s="49" t="s">
         <v>13</v>
       </c>
@@ -21232,17 +21230,17 @@
       <c r="AA87" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="AB87" s="134"/>
-      <c r="AC87" s="135"/>
+      <c r="AB87" s="139"/>
+      <c r="AC87" s="140"/>
       <c r="AD87" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AE87" s="7"/>
-      <c r="AK87" s="211">
+      <c r="AK87" s="194">
         <f>SUM(AD88:AD137)</f>
         <v>0</v>
       </c>
-      <c r="AL87" s="212"/>
+      <c r="AL87" s="195"/>
     </row>
     <row r="88" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B88" s="15" t="s">
@@ -21311,7 +21309,7 @@
       <c r="W88" s="14">
         <v>0</v>
       </c>
-      <c r="X88" s="113">
+      <c r="X88" s="112">
         <v>0</v>
       </c>
       <c r="Y88" s="14">
@@ -21325,15 +21323,15 @@
       <c r="AA88" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="AB88" s="214"/>
-      <c r="AC88" s="215"/>
+      <c r="AB88" s="145"/>
+      <c r="AC88" s="146"/>
       <c r="AD88" s="16">
         <f>X88</f>
         <v>0</v>
       </c>
       <c r="AE88" s="7"/>
-      <c r="AK88" s="213"/>
-      <c r="AL88" s="212"/>
+      <c r="AK88" s="196"/>
+      <c r="AL88" s="195"/>
     </row>
     <row r="89" spans="1:38" s="64" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B89" s="65"/>
@@ -21358,7 +21356,7 @@
       <c r="U89" s="65"/>
       <c r="V89" s="65"/>
       <c r="W89" s="65"/>
-      <c r="X89" s="120">
+      <c r="X89" s="119">
         <v>0</v>
       </c>
       <c r="Y89" s="80"/>
@@ -21376,8 +21374,8 @@
       <c r="AH89" s="2"/>
       <c r="AI89" s="2"/>
       <c r="AJ89" s="2"/>
-      <c r="AK89" s="213"/>
-      <c r="AL89" s="212"/>
+      <c r="AK89" s="196"/>
+      <c r="AL89" s="195"/>
     </row>
     <row r="90" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B90" s="13" t="s">
@@ -21446,7 +21444,7 @@
       <c r="W90" s="14">
         <v>0</v>
       </c>
-      <c r="X90" s="113">
+      <c r="X90" s="112">
         <v>0</v>
       </c>
       <c r="Y90" s="14">
@@ -21460,8 +21458,8 @@
       <c r="AA90" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB90" s="172"/>
-      <c r="AC90" s="173"/>
+      <c r="AB90" s="149"/>
+      <c r="AC90" s="150"/>
       <c r="AD90" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21472,8 +21470,8 @@
       <c r="AH90" s="2"/>
       <c r="AI90" s="2"/>
       <c r="AJ90" s="2"/>
-      <c r="AK90" s="213"/>
-      <c r="AL90" s="212"/>
+      <c r="AK90" s="196"/>
+      <c r="AL90" s="195"/>
     </row>
     <row r="91" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B91" s="13" t="s">
@@ -21542,7 +21540,7 @@
       <c r="W91" s="14">
         <v>0</v>
       </c>
-      <c r="X91" s="113">
+      <c r="X91" s="112">
         <v>0</v>
       </c>
       <c r="Y91" s="14">
@@ -21556,8 +21554,8 @@
       <c r="AA91" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AB91" s="172"/>
-      <c r="AC91" s="173"/>
+      <c r="AB91" s="149"/>
+      <c r="AC91" s="150"/>
       <c r="AD91" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21568,8 +21566,8 @@
       <c r="AH91" s="2"/>
       <c r="AI91" s="2"/>
       <c r="AJ91" s="2"/>
-      <c r="AK91" s="213"/>
-      <c r="AL91" s="212"/>
+      <c r="AK91" s="196"/>
+      <c r="AL91" s="195"/>
     </row>
     <row r="92" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B92" s="13" t="s">
@@ -21638,7 +21636,7 @@
       <c r="W92" s="14">
         <v>0</v>
       </c>
-      <c r="X92" s="113">
+      <c r="X92" s="112">
         <v>0</v>
       </c>
       <c r="Y92" s="14">
@@ -21652,8 +21650,8 @@
       <c r="AA92" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="AB92" s="172"/>
-      <c r="AC92" s="173"/>
+      <c r="AB92" s="149"/>
+      <c r="AC92" s="150"/>
       <c r="AD92" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21664,8 +21662,8 @@
       <c r="AH92" s="2"/>
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
-      <c r="AK92" s="213"/>
-      <c r="AL92" s="212"/>
+      <c r="AK92" s="196"/>
+      <c r="AL92" s="195"/>
     </row>
     <row r="93" spans="1:38" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B93" s="13" t="s">
@@ -21734,7 +21732,7 @@
       <c r="W93" s="14">
         <v>0</v>
       </c>
-      <c r="X93" s="113">
+      <c r="X93" s="112">
         <v>0</v>
       </c>
       <c r="Y93" s="14">
@@ -21748,25 +21746,25 @@
       <c r="AA93" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="AB93" s="216">
+      <c r="AB93" s="154">
         <f>SUM(Y93:Y102)</f>
         <v>0</v>
       </c>
-      <c r="AC93" s="141"/>
+      <c r="AC93" s="155"/>
       <c r="AD93" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE93" s="17"/>
-      <c r="AF93" s="162" t="s">
+      <c r="AF93" s="160" t="s">
         <v>112</v>
       </c>
-      <c r="AG93" s="163"/>
-      <c r="AH93" s="163"/>
-      <c r="AI93" s="163"/>
-      <c r="AJ93" s="164"/>
-      <c r="AK93" s="213"/>
-      <c r="AL93" s="212"/>
+      <c r="AG93" s="161"/>
+      <c r="AH93" s="161"/>
+      <c r="AI93" s="161"/>
+      <c r="AJ93" s="162"/>
+      <c r="AK93" s="196"/>
+      <c r="AL93" s="195"/>
     </row>
     <row r="94" spans="1:38" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A94" s="12"/>
@@ -21836,7 +21834,7 @@
       <c r="W94" s="14">
         <v>0</v>
       </c>
-      <c r="X94" s="113">
+      <c r="X94" s="112">
         <v>0</v>
       </c>
       <c r="Y94" s="14">
@@ -21850,20 +21848,20 @@
       <c r="AA94" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="AB94" s="217"/>
-      <c r="AC94" s="142"/>
+      <c r="AB94" s="156"/>
+      <c r="AC94" s="157"/>
       <c r="AD94" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE94" s="17"/>
-      <c r="AF94" s="165"/>
-      <c r="AG94" s="154"/>
-      <c r="AH94" s="154"/>
-      <c r="AI94" s="154"/>
-      <c r="AJ94" s="155"/>
-      <c r="AK94" s="213"/>
-      <c r="AL94" s="212"/>
+      <c r="AF94" s="163"/>
+      <c r="AG94" s="164"/>
+      <c r="AH94" s="164"/>
+      <c r="AI94" s="164"/>
+      <c r="AJ94" s="165"/>
+      <c r="AK94" s="196"/>
+      <c r="AL94" s="195"/>
     </row>
     <row r="95" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A95" s="12"/>
@@ -21933,7 +21931,7 @@
       <c r="W95" s="14">
         <v>0</v>
       </c>
-      <c r="X95" s="113">
+      <c r="X95" s="112">
         <v>0</v>
       </c>
       <c r="Y95" s="14">
@@ -21947,20 +21945,20 @@
       <c r="AA95" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="AB95" s="217"/>
-      <c r="AC95" s="142"/>
+      <c r="AB95" s="156"/>
+      <c r="AC95" s="157"/>
       <c r="AD95" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE95" s="17"/>
-      <c r="AF95" s="165"/>
-      <c r="AG95" s="154"/>
-      <c r="AH95" s="154"/>
-      <c r="AI95" s="154"/>
-      <c r="AJ95" s="155"/>
-      <c r="AK95" s="213"/>
-      <c r="AL95" s="212"/>
+      <c r="AF95" s="163"/>
+      <c r="AG95" s="164"/>
+      <c r="AH95" s="164"/>
+      <c r="AI95" s="164"/>
+      <c r="AJ95" s="165"/>
+      <c r="AK95" s="196"/>
+      <c r="AL95" s="195"/>
     </row>
     <row r="96" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A96" s="12"/>
@@ -22030,7 +22028,7 @@
       <c r="W96" s="14">
         <v>0</v>
       </c>
-      <c r="X96" s="113">
+      <c r="X96" s="112">
         <v>0</v>
       </c>
       <c r="Y96" s="14">
@@ -22044,20 +22042,20 @@
       <c r="AA96" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="AB96" s="217"/>
-      <c r="AC96" s="142"/>
+      <c r="AB96" s="156"/>
+      <c r="AC96" s="157"/>
       <c r="AD96" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE96" s="17"/>
-      <c r="AF96" s="165"/>
-      <c r="AG96" s="154"/>
-      <c r="AH96" s="154"/>
-      <c r="AI96" s="154"/>
-      <c r="AJ96" s="155"/>
-      <c r="AK96" s="213"/>
-      <c r="AL96" s="212"/>
+      <c r="AF96" s="163"/>
+      <c r="AG96" s="164"/>
+      <c r="AH96" s="164"/>
+      <c r="AI96" s="164"/>
+      <c r="AJ96" s="165"/>
+      <c r="AK96" s="196"/>
+      <c r="AL96" s="195"/>
     </row>
     <row r="97" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A97" s="12"/>
@@ -22127,7 +22125,7 @@
       <c r="W97" s="14">
         <v>0</v>
       </c>
-      <c r="X97" s="113">
+      <c r="X97" s="112">
         <v>0</v>
       </c>
       <c r="Y97" s="14">
@@ -22141,20 +22139,20 @@
       <c r="AA97" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AB97" s="217"/>
-      <c r="AC97" s="142"/>
+      <c r="AB97" s="156"/>
+      <c r="AC97" s="157"/>
       <c r="AD97" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE97" s="17"/>
-      <c r="AF97" s="165"/>
-      <c r="AG97" s="154"/>
-      <c r="AH97" s="154"/>
-      <c r="AI97" s="154"/>
-      <c r="AJ97" s="155"/>
-      <c r="AK97" s="213"/>
-      <c r="AL97" s="212"/>
+      <c r="AF97" s="163"/>
+      <c r="AG97" s="164"/>
+      <c r="AH97" s="164"/>
+      <c r="AI97" s="164"/>
+      <c r="AJ97" s="165"/>
+      <c r="AK97" s="196"/>
+      <c r="AL97" s="195"/>
     </row>
     <row r="98" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A98" s="12"/>
@@ -22224,7 +22222,7 @@
       <c r="W98" s="14">
         <v>0</v>
       </c>
-      <c r="X98" s="113">
+      <c r="X98" s="112">
         <v>0</v>
       </c>
       <c r="Y98" s="14">
@@ -22238,23 +22236,23 @@
       <c r="AA98" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AB98" s="217"/>
-      <c r="AC98" s="142"/>
+      <c r="AB98" s="156"/>
+      <c r="AC98" s="157"/>
       <c r="AD98" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE98" s="17"/>
-      <c r="AF98" s="219">
+      <c r="AF98" s="183">
         <f>SUM(AD93:AD102)</f>
         <v>0</v>
       </c>
-      <c r="AG98" s="220"/>
-      <c r="AH98" s="220"/>
-      <c r="AI98" s="220"/>
-      <c r="AJ98" s="221"/>
-      <c r="AK98" s="213"/>
-      <c r="AL98" s="212"/>
+      <c r="AG98" s="184"/>
+      <c r="AH98" s="184"/>
+      <c r="AI98" s="184"/>
+      <c r="AJ98" s="185"/>
+      <c r="AK98" s="196"/>
+      <c r="AL98" s="195"/>
     </row>
     <row r="99" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A99" s="12"/>
@@ -22324,7 +22322,7 @@
       <c r="W99" s="14">
         <v>0</v>
       </c>
-      <c r="X99" s="113">
+      <c r="X99" s="112">
         <v>0</v>
       </c>
       <c r="Y99" s="14">
@@ -22338,8 +22336,8 @@
       <c r="AA99" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AB99" s="217"/>
-      <c r="AC99" s="142"/>
+      <c r="AB99" s="156"/>
+      <c r="AC99" s="157"/>
       <c r="AD99" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22350,8 +22348,8 @@
       <c r="AH99" s="24"/>
       <c r="AI99" s="24"/>
       <c r="AJ99" s="25"/>
-      <c r="AK99" s="213"/>
-      <c r="AL99" s="212"/>
+      <c r="AK99" s="196"/>
+      <c r="AL99" s="195"/>
     </row>
     <row r="100" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A100" s="12"/>
@@ -22421,7 +22419,7 @@
       <c r="W100" s="14">
         <v>0</v>
       </c>
-      <c r="X100" s="113">
+      <c r="X100" s="112">
         <v>0</v>
       </c>
       <c r="Y100" s="14">
@@ -22435,20 +22433,20 @@
       <c r="AA100" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AB100" s="217"/>
-      <c r="AC100" s="142"/>
+      <c r="AB100" s="156"/>
+      <c r="AC100" s="157"/>
       <c r="AD100" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE100" s="17"/>
-      <c r="AF100" s="153"/>
-      <c r="AG100" s="154"/>
-      <c r="AH100" s="154"/>
-      <c r="AI100" s="154"/>
-      <c r="AJ100" s="155"/>
-      <c r="AK100" s="213"/>
-      <c r="AL100" s="212"/>
+      <c r="AF100" s="166"/>
+      <c r="AG100" s="164"/>
+      <c r="AH100" s="164"/>
+      <c r="AI100" s="164"/>
+      <c r="AJ100" s="165"/>
+      <c r="AK100" s="196"/>
+      <c r="AL100" s="195"/>
     </row>
     <row r="101" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A101" s="12"/>
@@ -22518,7 +22516,7 @@
       <c r="W101" s="14">
         <v>0</v>
       </c>
-      <c r="X101" s="113">
+      <c r="X101" s="112">
         <v>0</v>
       </c>
       <c r="Y101" s="14">
@@ -22532,8 +22530,8 @@
       <c r="AA101" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="AB101" s="217"/>
-      <c r="AC101" s="142"/>
+      <c r="AB101" s="156"/>
+      <c r="AC101" s="157"/>
       <c r="AD101" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22544,8 +22542,8 @@
       <c r="AH101" s="27"/>
       <c r="AI101" s="27"/>
       <c r="AJ101" s="28"/>
-      <c r="AK101" s="213"/>
-      <c r="AL101" s="212"/>
+      <c r="AK101" s="196"/>
+      <c r="AL101" s="195"/>
     </row>
     <row r="102" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A102" s="12"/>
@@ -22615,7 +22613,7 @@
       <c r="W102" s="14">
         <v>0</v>
       </c>
-      <c r="X102" s="113">
+      <c r="X102" s="112">
         <v>0</v>
       </c>
       <c r="Y102" s="14">
@@ -22629,8 +22627,8 @@
       <c r="AA102" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="AB102" s="218"/>
-      <c r="AC102" s="143"/>
+      <c r="AB102" s="158"/>
+      <c r="AC102" s="159"/>
       <c r="AD102" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22641,8 +22639,8 @@
       <c r="AH102" s="84"/>
       <c r="AI102" s="84"/>
       <c r="AJ102" s="85"/>
-      <c r="AK102" s="213"/>
-      <c r="AL102" s="212"/>
+      <c r="AK102" s="196"/>
+      <c r="AL102" s="195"/>
     </row>
     <row r="103" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A103" s="12"/>
@@ -22731,136 +22729,136 @@
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="X103" s="114"/>
+      <c r="X103" s="113"/>
       <c r="Y103" s="14"/>
       <c r="Z103" s="14"/>
       <c r="AA103" s="13"/>
-      <c r="AB103" s="181"/>
-      <c r="AC103" s="182"/>
+      <c r="AB103" s="186"/>
+      <c r="AC103" s="187"/>
       <c r="AD103" s="33"/>
       <c r="AE103" s="17"/>
-      <c r="AF103" s="144"/>
-      <c r="AG103" s="145"/>
-      <c r="AH103" s="145"/>
-      <c r="AI103" s="145"/>
-      <c r="AJ103" s="146"/>
-      <c r="AK103" s="213"/>
-      <c r="AL103" s="212"/>
+      <c r="AF103" s="188"/>
+      <c r="AG103" s="189"/>
+      <c r="AH103" s="189"/>
+      <c r="AI103" s="189"/>
+      <c r="AJ103" s="190"/>
+      <c r="AK103" s="196"/>
+      <c r="AL103" s="195"/>
     </row>
     <row r="104" spans="1:38" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="C104" s="133"/>
-      <c r="D104" s="133"/>
-      <c r="E104" s="133"/>
-      <c r="F104" s="133"/>
-      <c r="G104" s="133"/>
-      <c r="H104" s="133"/>
-      <c r="I104" s="133"/>
-      <c r="J104" s="133"/>
-      <c r="K104" s="133"/>
-      <c r="L104" s="133"/>
-      <c r="M104" s="133"/>
-      <c r="N104" s="133"/>
-      <c r="O104" s="133"/>
-      <c r="P104" s="133"/>
-      <c r="Q104" s="133"/>
-      <c r="R104" s="133"/>
-      <c r="S104" s="133"/>
-      <c r="T104" s="133"/>
-      <c r="U104" s="133"/>
-      <c r="V104" s="133"/>
-      <c r="W104" s="133"/>
-      <c r="X104" s="133"/>
-      <c r="Y104" s="133"/>
-      <c r="Z104" s="133"/>
-      <c r="AA104" s="133"/>
-      <c r="AB104" s="133"/>
-      <c r="AC104" s="133"/>
-      <c r="AD104" s="133"/>
+      <c r="B104" s="169" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="170"/>
+      <c r="D104" s="170"/>
+      <c r="E104" s="170"/>
+      <c r="F104" s="170"/>
+      <c r="G104" s="170"/>
+      <c r="H104" s="170"/>
+      <c r="I104" s="170"/>
+      <c r="J104" s="170"/>
+      <c r="K104" s="170"/>
+      <c r="L104" s="170"/>
+      <c r="M104" s="170"/>
+      <c r="N104" s="170"/>
+      <c r="O104" s="170"/>
+      <c r="P104" s="170"/>
+      <c r="Q104" s="170"/>
+      <c r="R104" s="170"/>
+      <c r="S104" s="170"/>
+      <c r="T104" s="170"/>
+      <c r="U104" s="170"/>
+      <c r="V104" s="170"/>
+      <c r="W104" s="170"/>
+      <c r="X104" s="170"/>
+      <c r="Y104" s="170"/>
+      <c r="Z104" s="170"/>
+      <c r="AA104" s="170"/>
+      <c r="AB104" s="170"/>
+      <c r="AC104" s="170"/>
+      <c r="AD104" s="170"/>
       <c r="AE104" s="1"/>
-      <c r="AF104" s="147"/>
-      <c r="AG104" s="148"/>
-      <c r="AH104" s="148"/>
-      <c r="AI104" s="148"/>
-      <c r="AJ104" s="149"/>
-      <c r="AK104" s="213"/>
-      <c r="AL104" s="212"/>
+      <c r="AF104" s="191"/>
+      <c r="AG104" s="192"/>
+      <c r="AH104" s="192"/>
+      <c r="AI104" s="192"/>
+      <c r="AJ104" s="193"/>
+      <c r="AK104" s="196"/>
+      <c r="AL104" s="195"/>
     </row>
     <row r="105" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B105" s="130" t="s">
+      <c r="B105" s="167" t="s">
         <v>122</v>
       </c>
-      <c r="C105" s="128" t="s">
+      <c r="C105" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D105" s="129"/>
-      <c r="E105" s="128" t="s">
+      <c r="D105" s="136"/>
+      <c r="E105" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F105" s="129"/>
-      <c r="G105" s="128" t="s">
+      <c r="F105" s="136"/>
+      <c r="G105" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H105" s="129"/>
-      <c r="I105" s="128" t="s">
+      <c r="H105" s="136"/>
+      <c r="I105" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J105" s="129"/>
-      <c r="K105" s="128" t="s">
+      <c r="J105" s="136"/>
+      <c r="K105" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L105" s="129"/>
-      <c r="M105" s="128" t="s">
+      <c r="L105" s="136"/>
+      <c r="M105" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N105" s="129"/>
-      <c r="O105" s="128" t="s">
+      <c r="N105" s="136"/>
+      <c r="O105" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P105" s="129"/>
-      <c r="Q105" s="128" t="s">
+      <c r="P105" s="136"/>
+      <c r="Q105" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R105" s="129"/>
-      <c r="S105" s="128" t="s">
+      <c r="R105" s="136"/>
+      <c r="S105" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T105" s="129"/>
-      <c r="U105" s="128" t="s">
+      <c r="T105" s="136"/>
+      <c r="U105" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V105" s="129"/>
-      <c r="W105" s="130" t="s">
+      <c r="V105" s="136"/>
+      <c r="W105" s="167" t="s">
         <v>12</v>
       </c>
-      <c r="X105" s="111"/>
-      <c r="Y105" s="130" t="s">
+      <c r="X105" s="110"/>
+      <c r="Y105" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="Z105" s="130" t="s">
+      <c r="Z105" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="AA105" s="130" t="s">
+      <c r="AA105" s="167" t="s">
         <v>122</v>
       </c>
-      <c r="AB105" s="134"/>
-      <c r="AC105" s="135"/>
+      <c r="AB105" s="139"/>
+      <c r="AC105" s="140"/>
       <c r="AD105" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AE105" s="7"/>
-      <c r="AF105" s="147"/>
-      <c r="AG105" s="148"/>
-      <c r="AH105" s="148"/>
-      <c r="AI105" s="148"/>
-      <c r="AJ105" s="149"/>
-      <c r="AK105" s="213"/>
-      <c r="AL105" s="212"/>
+      <c r="AF105" s="191"/>
+      <c r="AG105" s="192"/>
+      <c r="AH105" s="192"/>
+      <c r="AI105" s="192"/>
+      <c r="AJ105" s="193"/>
+      <c r="AK105" s="196"/>
+      <c r="AL105" s="195"/>
     </row>
     <row r="106" spans="1:38" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B106" s="131"/>
+      <c r="B106" s="168"/>
       <c r="C106" s="9" t="s">
         <v>17</v>
       </c>
@@ -22921,22 +22919,22 @@
       <c r="V106" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W106" s="131"/>
-      <c r="X106" s="112"/>
-      <c r="Y106" s="131"/>
-      <c r="Z106" s="131"/>
-      <c r="AA106" s="131"/>
+      <c r="W106" s="168"/>
+      <c r="X106" s="111"/>
+      <c r="Y106" s="168"/>
+      <c r="Z106" s="168"/>
+      <c r="AA106" s="168"/>
       <c r="AB106" s="10"/>
       <c r="AC106" s="11"/>
       <c r="AD106" s="6"/>
       <c r="AE106" s="7"/>
-      <c r="AF106" s="147"/>
-      <c r="AG106" s="148"/>
-      <c r="AH106" s="148"/>
-      <c r="AI106" s="148"/>
-      <c r="AJ106" s="149"/>
-      <c r="AK106" s="213"/>
-      <c r="AL106" s="212"/>
+      <c r="AF106" s="191"/>
+      <c r="AG106" s="192"/>
+      <c r="AH106" s="192"/>
+      <c r="AI106" s="192"/>
+      <c r="AJ106" s="193"/>
+      <c r="AK106" s="196"/>
+      <c r="AL106" s="195"/>
     </row>
     <row r="107" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A107" s="12"/>
@@ -23006,7 +23004,7 @@
       <c r="W107" s="14">
         <v>0</v>
       </c>
-      <c r="X107" s="113">
+      <c r="X107" s="112">
         <v>0</v>
       </c>
       <c r="Y107" s="14">
@@ -23020,23 +23018,23 @@
       <c r="AA107" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AB107" s="216">
+      <c r="AB107" s="154">
         <f>SUM(Y107:Y110)</f>
         <v>0</v>
       </c>
-      <c r="AC107" s="141"/>
+      <c r="AC107" s="155"/>
       <c r="AD107" s="16">
         <f>X107</f>
         <v>0</v>
       </c>
       <c r="AE107" s="17"/>
-      <c r="AF107" s="147"/>
-      <c r="AG107" s="148"/>
-      <c r="AH107" s="148"/>
-      <c r="AI107" s="148"/>
-      <c r="AJ107" s="149"/>
-      <c r="AK107" s="213"/>
-      <c r="AL107" s="212"/>
+      <c r="AF107" s="191"/>
+      <c r="AG107" s="192"/>
+      <c r="AH107" s="192"/>
+      <c r="AI107" s="192"/>
+      <c r="AJ107" s="193"/>
+      <c r="AK107" s="196"/>
+      <c r="AL107" s="195"/>
     </row>
     <row r="108" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A108" s="12"/>
@@ -23106,7 +23104,7 @@
       <c r="W108" s="14">
         <v>0</v>
       </c>
-      <c r="X108" s="113">
+      <c r="X108" s="112">
         <v>0</v>
       </c>
       <c r="Y108" s="14">
@@ -23120,8 +23118,8 @@
       <c r="AA108" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AB108" s="217"/>
-      <c r="AC108" s="142"/>
+      <c r="AB108" s="156"/>
+      <c r="AC108" s="157"/>
       <c r="AD108" s="16">
         <f t="shared" ref="AD108:AD136" si="31">X108</f>
         <v>0</v>
@@ -23132,8 +23130,8 @@
       <c r="AH108" s="24"/>
       <c r="AI108" s="24"/>
       <c r="AJ108" s="25"/>
-      <c r="AK108" s="213"/>
-      <c r="AL108" s="212"/>
+      <c r="AK108" s="196"/>
+      <c r="AL108" s="195"/>
     </row>
     <row r="109" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A109" s="12"/>
@@ -23203,7 +23201,7 @@
       <c r="W109" s="14">
         <v>0</v>
       </c>
-      <c r="X109" s="113">
+      <c r="X109" s="112">
         <v>0</v>
       </c>
       <c r="Y109" s="14">
@@ -23217,8 +23215,8 @@
       <c r="AA109" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AB109" s="217"/>
-      <c r="AC109" s="142"/>
+      <c r="AB109" s="156"/>
+      <c r="AC109" s="157"/>
       <c r="AD109" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23229,8 +23227,8 @@
       <c r="AH109" s="24"/>
       <c r="AI109" s="24"/>
       <c r="AJ109" s="25"/>
-      <c r="AK109" s="213"/>
-      <c r="AL109" s="212"/>
+      <c r="AK109" s="196"/>
+      <c r="AL109" s="195"/>
     </row>
     <row r="110" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A110" s="12"/>
@@ -23300,7 +23298,7 @@
       <c r="W110" s="14">
         <v>0</v>
       </c>
-      <c r="X110" s="113">
+      <c r="X110" s="112">
         <v>0</v>
       </c>
       <c r="Y110" s="14">
@@ -23314,8 +23312,8 @@
       <c r="AA110" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="AB110" s="217"/>
-      <c r="AC110" s="142"/>
+      <c r="AB110" s="156"/>
+      <c r="AC110" s="157"/>
       <c r="AD110" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23326,8 +23324,8 @@
       <c r="AH110" s="24"/>
       <c r="AI110" s="24"/>
       <c r="AJ110" s="25"/>
-      <c r="AK110" s="213"/>
-      <c r="AL110" s="212"/>
+      <c r="AK110" s="196"/>
+      <c r="AL110" s="195"/>
     </row>
     <row r="111" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A111" s="12"/>
@@ -23416,24 +23414,24 @@
         <f t="shared" si="32"/>
         <v>0</v>
       </c>
-      <c r="X111" s="114"/>
+      <c r="X111" s="113"/>
       <c r="Y111" s="14"/>
       <c r="Z111" s="14"/>
       <c r="AA111" s="13"/>
-      <c r="AB111" s="218"/>
-      <c r="AC111" s="143"/>
+      <c r="AB111" s="158"/>
+      <c r="AC111" s="159"/>
       <c r="AD111" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE111" s="17"/>
-      <c r="AF111" s="224"/>
-      <c r="AG111" s="225"/>
-      <c r="AH111" s="225"/>
-      <c r="AI111" s="225"/>
-      <c r="AJ111" s="226"/>
-      <c r="AK111" s="213"/>
-      <c r="AL111" s="212"/>
+      <c r="AF111" s="178"/>
+      <c r="AG111" s="179"/>
+      <c r="AH111" s="179"/>
+      <c r="AI111" s="179"/>
+      <c r="AJ111" s="180"/>
+      <c r="AK111" s="196"/>
+      <c r="AL111" s="195"/>
     </row>
     <row r="112" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B112" s="13" t="s">
@@ -23502,7 +23500,7 @@
       <c r="W112" s="14">
         <v>0</v>
       </c>
-      <c r="X112" s="113">
+      <c r="X112" s="112">
         <v>0</v>
       </c>
       <c r="Y112" s="14">
@@ -23516,25 +23514,25 @@
       <c r="AA112" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AB112" s="216">
+      <c r="AB112" s="154">
         <f>SUM(Y112:Y124)</f>
         <v>0</v>
       </c>
-      <c r="AC112" s="141"/>
+      <c r="AC112" s="155"/>
       <c r="AD112" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE112" s="17"/>
-      <c r="AF112" s="162" t="s">
+      <c r="AF112" s="160" t="s">
         <v>128</v>
       </c>
-      <c r="AG112" s="163"/>
-      <c r="AH112" s="163"/>
-      <c r="AI112" s="163"/>
-      <c r="AJ112" s="164"/>
-      <c r="AK112" s="213"/>
-      <c r="AL112" s="212"/>
+      <c r="AG112" s="161"/>
+      <c r="AH112" s="161"/>
+      <c r="AI112" s="161"/>
+      <c r="AJ112" s="162"/>
+      <c r="AK112" s="196"/>
+      <c r="AL112" s="195"/>
     </row>
     <row r="113" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B113" s="13" t="s">
@@ -23603,7 +23601,7 @@
       <c r="W113" s="14">
         <v>0</v>
       </c>
-      <c r="X113" s="113">
+      <c r="X113" s="112">
         <v>0</v>
       </c>
       <c r="Y113" s="14">
@@ -23617,22 +23615,22 @@
       <c r="AA113" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AB113" s="217"/>
-      <c r="AC113" s="142"/>
+      <c r="AB113" s="156"/>
+      <c r="AC113" s="157"/>
       <c r="AD113" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE113" s="17"/>
-      <c r="AF113" s="165"/>
-      <c r="AG113" s="154"/>
-      <c r="AH113" s="154"/>
-      <c r="AI113" s="154"/>
-      <c r="AJ113" s="155"/>
-      <c r="AK113" s="222" t="s">
+      <c r="AF113" s="163"/>
+      <c r="AG113" s="164"/>
+      <c r="AH113" s="164"/>
+      <c r="AI113" s="164"/>
+      <c r="AJ113" s="165"/>
+      <c r="AK113" s="181" t="s">
         <v>130</v>
       </c>
-      <c r="AL113" s="223"/>
+      <c r="AL113" s="182"/>
     </row>
     <row r="114" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B114" s="13" t="s">
@@ -23701,7 +23699,7 @@
       <c r="W114" s="14">
         <v>0</v>
       </c>
-      <c r="X114" s="113">
+      <c r="X114" s="112">
         <v>0</v>
       </c>
       <c r="Y114" s="14">
@@ -23715,20 +23713,20 @@
       <c r="AA114" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="AB114" s="217"/>
-      <c r="AC114" s="142"/>
+      <c r="AB114" s="156"/>
+      <c r="AC114" s="157"/>
       <c r="AD114" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE114" s="17"/>
-      <c r="AF114" s="165"/>
-      <c r="AG114" s="154"/>
-      <c r="AH114" s="154"/>
-      <c r="AI114" s="154"/>
-      <c r="AJ114" s="155"/>
-      <c r="AK114" s="222"/>
-      <c r="AL114" s="223"/>
+      <c r="AF114" s="163"/>
+      <c r="AG114" s="164"/>
+      <c r="AH114" s="164"/>
+      <c r="AI114" s="164"/>
+      <c r="AJ114" s="165"/>
+      <c r="AK114" s="181"/>
+      <c r="AL114" s="182"/>
     </row>
     <row r="115" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B115" s="13" t="s">
@@ -23797,7 +23795,7 @@
       <c r="W115" s="14">
         <v>0</v>
       </c>
-      <c r="X115" s="113">
+      <c r="X115" s="112">
         <v>0</v>
       </c>
       <c r="Y115" s="14">
@@ -23811,20 +23809,20 @@
       <c r="AA115" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AB115" s="217"/>
-      <c r="AC115" s="142"/>
+      <c r="AB115" s="156"/>
+      <c r="AC115" s="157"/>
       <c r="AD115" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE115" s="17"/>
-      <c r="AF115" s="165"/>
-      <c r="AG115" s="154"/>
-      <c r="AH115" s="154"/>
-      <c r="AI115" s="154"/>
-      <c r="AJ115" s="155"/>
-      <c r="AK115" s="222"/>
-      <c r="AL115" s="223"/>
+      <c r="AF115" s="163"/>
+      <c r="AG115" s="164"/>
+      <c r="AH115" s="164"/>
+      <c r="AI115" s="164"/>
+      <c r="AJ115" s="165"/>
+      <c r="AK115" s="181"/>
+      <c r="AL115" s="182"/>
     </row>
     <row r="116" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B116" s="13" t="s">
@@ -23893,7 +23891,7 @@
       <c r="W116" s="14">
         <v>0</v>
       </c>
-      <c r="X116" s="113">
+      <c r="X116" s="112">
         <v>0</v>
       </c>
       <c r="Y116" s="14">
@@ -23907,20 +23905,20 @@
       <c r="AA116" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AB116" s="217"/>
-      <c r="AC116" s="142"/>
+      <c r="AB116" s="156"/>
+      <c r="AC116" s="157"/>
       <c r="AD116" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE116" s="17"/>
-      <c r="AF116" s="165"/>
-      <c r="AG116" s="154"/>
-      <c r="AH116" s="154"/>
-      <c r="AI116" s="154"/>
-      <c r="AJ116" s="155"/>
-      <c r="AK116" s="222"/>
-      <c r="AL116" s="223"/>
+      <c r="AF116" s="163"/>
+      <c r="AG116" s="164"/>
+      <c r="AH116" s="164"/>
+      <c r="AI116" s="164"/>
+      <c r="AJ116" s="165"/>
+      <c r="AK116" s="181"/>
+      <c r="AL116" s="182"/>
     </row>
     <row r="117" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B117" s="13" t="s">
@@ -23989,7 +23987,7 @@
       <c r="W117" s="14">
         <v>0</v>
       </c>
-      <c r="X117" s="113">
+      <c r="X117" s="112">
         <v>0</v>
       </c>
       <c r="Y117" s="14">
@@ -24003,20 +24001,20 @@
       <c r="AA117" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AB117" s="217"/>
-      <c r="AC117" s="142"/>
+      <c r="AB117" s="156"/>
+      <c r="AC117" s="157"/>
       <c r="AD117" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE117" s="17"/>
-      <c r="AF117" s="165"/>
-      <c r="AG117" s="154"/>
-      <c r="AH117" s="154"/>
-      <c r="AI117" s="154"/>
-      <c r="AJ117" s="155"/>
-      <c r="AK117" s="222"/>
-      <c r="AL117" s="223"/>
+      <c r="AF117" s="163"/>
+      <c r="AG117" s="164"/>
+      <c r="AH117" s="164"/>
+      <c r="AI117" s="164"/>
+      <c r="AJ117" s="165"/>
+      <c r="AK117" s="181"/>
+      <c r="AL117" s="182"/>
     </row>
     <row r="118" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A118" s="12"/>
@@ -24086,7 +24084,7 @@
       <c r="W118" s="14">
         <v>0</v>
       </c>
-      <c r="X118" s="113">
+      <c r="X118" s="112">
         <v>0</v>
       </c>
       <c r="Y118" s="14">
@@ -24100,23 +24098,23 @@
       <c r="AA118" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="AB118" s="217"/>
-      <c r="AC118" s="142"/>
+      <c r="AB118" s="156"/>
+      <c r="AC118" s="157"/>
       <c r="AD118" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE118" s="17"/>
-      <c r="AF118" s="153">
+      <c r="AF118" s="166">
         <f>SUM(AD112:AD124)</f>
         <v>0</v>
       </c>
-      <c r="AG118" s="154"/>
-      <c r="AH118" s="154"/>
-      <c r="AI118" s="154"/>
-      <c r="AJ118" s="155"/>
-      <c r="AK118" s="222"/>
-      <c r="AL118" s="223"/>
+      <c r="AG118" s="164"/>
+      <c r="AH118" s="164"/>
+      <c r="AI118" s="164"/>
+      <c r="AJ118" s="165"/>
+      <c r="AK118" s="181"/>
+      <c r="AL118" s="182"/>
     </row>
     <row r="119" spans="1:38" s="47" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A119" s="12"/>
@@ -24186,7 +24184,7 @@
       <c r="W119" s="14">
         <v>0</v>
       </c>
-      <c r="X119" s="113">
+      <c r="X119" s="112">
         <v>0</v>
       </c>
       <c r="Y119" s="14">
@@ -24200,20 +24198,20 @@
       <c r="AA119" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="AB119" s="217"/>
-      <c r="AC119" s="142"/>
+      <c r="AB119" s="156"/>
+      <c r="AC119" s="157"/>
       <c r="AD119" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE119" s="17"/>
-      <c r="AF119" s="153"/>
-      <c r="AG119" s="154"/>
-      <c r="AH119" s="154"/>
-      <c r="AI119" s="154"/>
-      <c r="AJ119" s="155"/>
-      <c r="AK119" s="222"/>
-      <c r="AL119" s="223"/>
+      <c r="AF119" s="166"/>
+      <c r="AG119" s="164"/>
+      <c r="AH119" s="164"/>
+      <c r="AI119" s="164"/>
+      <c r="AJ119" s="165"/>
+      <c r="AK119" s="181"/>
+      <c r="AL119" s="182"/>
     </row>
     <row r="120" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B120" s="13" t="s">
@@ -24282,7 +24280,7 @@
       <c r="W120" s="14">
         <v>0</v>
       </c>
-      <c r="X120" s="113">
+      <c r="X120" s="112">
         <v>0</v>
       </c>
       <c r="Y120" s="14">
@@ -24296,8 +24294,8 @@
       <c r="AA120" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="AB120" s="217"/>
-      <c r="AC120" s="142"/>
+      <c r="AB120" s="156"/>
+      <c r="AC120" s="157"/>
       <c r="AD120" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24308,8 +24306,8 @@
       <c r="AH120" s="27"/>
       <c r="AI120" s="27"/>
       <c r="AJ120" s="28"/>
-      <c r="AK120" s="222"/>
-      <c r="AL120" s="223"/>
+      <c r="AK120" s="181"/>
+      <c r="AL120" s="182"/>
     </row>
     <row r="121" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B121" s="13" t="s">
@@ -24378,7 +24376,7 @@
       <c r="W121" s="14">
         <v>0</v>
       </c>
-      <c r="X121" s="113">
+      <c r="X121" s="112">
         <v>0</v>
       </c>
       <c r="Y121" s="14">
@@ -24392,8 +24390,8 @@
       <c r="AA121" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AB121" s="217"/>
-      <c r="AC121" s="142"/>
+      <c r="AB121" s="156"/>
+      <c r="AC121" s="157"/>
       <c r="AD121" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24404,8 +24402,8 @@
       <c r="AH121" s="27"/>
       <c r="AI121" s="27"/>
       <c r="AJ121" s="28"/>
-      <c r="AK121" s="222"/>
-      <c r="AL121" s="223"/>
+      <c r="AK121" s="181"/>
+      <c r="AL121" s="182"/>
     </row>
     <row r="122" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B122" s="13" t="s">
@@ -24474,7 +24472,7 @@
       <c r="W122" s="14">
         <v>0</v>
       </c>
-      <c r="X122" s="113">
+      <c r="X122" s="112">
         <v>0</v>
       </c>
       <c r="Y122" s="14">
@@ -24488,8 +24486,8 @@
       <c r="AA122" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AB122" s="217"/>
-      <c r="AC122" s="142"/>
+      <c r="AB122" s="156"/>
+      <c r="AC122" s="157"/>
       <c r="AD122" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24500,8 +24498,8 @@
       <c r="AH122" s="27"/>
       <c r="AI122" s="27"/>
       <c r="AJ122" s="28"/>
-      <c r="AK122" s="222"/>
-      <c r="AL122" s="223"/>
+      <c r="AK122" s="181"/>
+      <c r="AL122" s="182"/>
     </row>
     <row r="123" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B123" s="13" t="s">
@@ -24570,7 +24568,7 @@
       <c r="W123" s="14">
         <v>0</v>
       </c>
-      <c r="X123" s="113">
+      <c r="X123" s="112">
         <v>0</v>
       </c>
       <c r="Y123" s="14">
@@ -24584,8 +24582,8 @@
       <c r="AA123" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AB123" s="217"/>
-      <c r="AC123" s="142"/>
+      <c r="AB123" s="156"/>
+      <c r="AC123" s="157"/>
       <c r="AD123" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24596,8 +24594,8 @@
       <c r="AH123" s="84"/>
       <c r="AI123" s="84"/>
       <c r="AJ123" s="85"/>
-      <c r="AK123" s="222"/>
-      <c r="AL123" s="223"/>
+      <c r="AK123" s="181"/>
+      <c r="AL123" s="182"/>
     </row>
     <row r="124" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B124" s="13" t="s">
@@ -24666,7 +24664,7 @@
       <c r="W124" s="14">
         <v>0</v>
       </c>
-      <c r="X124" s="113">
+      <c r="X124" s="112">
         <v>0</v>
       </c>
       <c r="Y124" s="14">
@@ -24680,8 +24678,8 @@
       <c r="AA124" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AB124" s="217"/>
-      <c r="AC124" s="142"/>
+      <c r="AB124" s="156"/>
+      <c r="AC124" s="157"/>
       <c r="AD124" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24692,8 +24690,8 @@
       <c r="AH124" s="84"/>
       <c r="AI124" s="84"/>
       <c r="AJ124" s="85"/>
-      <c r="AK124" s="222"/>
-      <c r="AL124" s="223"/>
+      <c r="AK124" s="181"/>
+      <c r="AL124" s="182"/>
     </row>
     <row r="125" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B125" s="13"/>
@@ -24781,14 +24779,14 @@
         <f t="shared" si="35"/>
         <v>0</v>
       </c>
-      <c r="X125" s="114">
+      <c r="X125" s="113">
         <v>0</v>
       </c>
       <c r="Y125" s="14"/>
       <c r="Z125" s="14"/>
       <c r="AA125" s="13"/>
-      <c r="AB125" s="218"/>
-      <c r="AC125" s="143"/>
+      <c r="AB125" s="158"/>
+      <c r="AC125" s="159"/>
       <c r="AD125" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24799,8 +24797,8 @@
       <c r="AH125" s="24"/>
       <c r="AI125" s="24"/>
       <c r="AJ125" s="25"/>
-      <c r="AK125" s="222"/>
-      <c r="AL125" s="223"/>
+      <c r="AK125" s="181"/>
+      <c r="AL125" s="182"/>
     </row>
     <row r="126" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B126" s="13" t="s">
@@ -24869,7 +24867,7 @@
       <c r="W126" s="14">
         <v>0</v>
       </c>
-      <c r="X126" s="113">
+      <c r="X126" s="112">
         <v>0</v>
       </c>
       <c r="Y126" s="14">
@@ -24883,25 +24881,25 @@
       <c r="AA126" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AB126" s="216">
+      <c r="AB126" s="154">
         <f>SUM(Y126:Y135)</f>
         <v>0</v>
       </c>
-      <c r="AC126" s="141"/>
+      <c r="AC126" s="155"/>
       <c r="AD126" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE126" s="17"/>
-      <c r="AF126" s="162" t="s">
+      <c r="AF126" s="160" t="s">
         <v>143</v>
       </c>
-      <c r="AG126" s="163"/>
-      <c r="AH126" s="163"/>
-      <c r="AI126" s="163"/>
-      <c r="AJ126" s="164"/>
-      <c r="AK126" s="222"/>
-      <c r="AL126" s="223"/>
+      <c r="AG126" s="161"/>
+      <c r="AH126" s="161"/>
+      <c r="AI126" s="161"/>
+      <c r="AJ126" s="162"/>
+      <c r="AK126" s="181"/>
+      <c r="AL126" s="182"/>
     </row>
     <row r="127" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B127" s="13" t="s">
@@ -24970,7 +24968,7 @@
       <c r="W127" s="14">
         <v>0</v>
       </c>
-      <c r="X127" s="113">
+      <c r="X127" s="112">
         <v>0</v>
       </c>
       <c r="Y127" s="14">
@@ -24984,20 +24982,20 @@
       <c r="AA127" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="AB127" s="217"/>
-      <c r="AC127" s="142"/>
+      <c r="AB127" s="156"/>
+      <c r="AC127" s="157"/>
       <c r="AD127" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE127" s="17"/>
-      <c r="AF127" s="165"/>
-      <c r="AG127" s="154"/>
-      <c r="AH127" s="154"/>
-      <c r="AI127" s="154"/>
-      <c r="AJ127" s="155"/>
-      <c r="AK127" s="222"/>
-      <c r="AL127" s="223"/>
+      <c r="AF127" s="163"/>
+      <c r="AG127" s="164"/>
+      <c r="AH127" s="164"/>
+      <c r="AI127" s="164"/>
+      <c r="AJ127" s="165"/>
+      <c r="AK127" s="181"/>
+      <c r="AL127" s="182"/>
     </row>
     <row r="128" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B128" s="13" t="s">
@@ -25066,7 +25064,7 @@
       <c r="W128" s="14">
         <v>0</v>
       </c>
-      <c r="X128" s="113">
+      <c r="X128" s="112">
         <v>0</v>
       </c>
       <c r="Y128" s="14">
@@ -25080,8 +25078,8 @@
       <c r="AA128" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="AB128" s="217"/>
-      <c r="AC128" s="142"/>
+      <c r="AB128" s="156"/>
+      <c r="AC128" s="157"/>
       <c r="AD128" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25092,8 +25090,8 @@
       <c r="AH128" s="24"/>
       <c r="AI128" s="24"/>
       <c r="AJ128" s="25"/>
-      <c r="AK128" s="222"/>
-      <c r="AL128" s="223"/>
+      <c r="AK128" s="181"/>
+      <c r="AL128" s="182"/>
     </row>
     <row r="129" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B129" s="13" t="s">
@@ -25162,7 +25160,7 @@
       <c r="W129" s="14">
         <v>0</v>
       </c>
-      <c r="X129" s="113">
+      <c r="X129" s="112">
         <v>0</v>
       </c>
       <c r="Y129" s="14">
@@ -25176,23 +25174,23 @@
       <c r="AA129" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="AB129" s="217"/>
-      <c r="AC129" s="142"/>
+      <c r="AB129" s="156"/>
+      <c r="AC129" s="157"/>
       <c r="AD129" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE129" s="17"/>
-      <c r="AF129" s="153">
+      <c r="AF129" s="166">
         <f>SUM(AD126:AD135)</f>
         <v>0</v>
       </c>
-      <c r="AG129" s="154"/>
-      <c r="AH129" s="154"/>
-      <c r="AI129" s="154"/>
-      <c r="AJ129" s="155"/>
-      <c r="AK129" s="222"/>
-      <c r="AL129" s="223"/>
+      <c r="AG129" s="164"/>
+      <c r="AH129" s="164"/>
+      <c r="AI129" s="164"/>
+      <c r="AJ129" s="165"/>
+      <c r="AK129" s="181"/>
+      <c r="AL129" s="182"/>
     </row>
     <row r="130" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B130" s="13" t="s">
@@ -25261,7 +25259,7 @@
       <c r="W130" s="14">
         <v>0</v>
       </c>
-      <c r="X130" s="113">
+      <c r="X130" s="112">
         <v>0</v>
       </c>
       <c r="Y130" s="14">
@@ -25275,8 +25273,8 @@
       <c r="AA130" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="AB130" s="217"/>
-      <c r="AC130" s="142"/>
+      <c r="AB130" s="156"/>
+      <c r="AC130" s="157"/>
       <c r="AD130" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25287,8 +25285,8 @@
       <c r="AH130" s="24"/>
       <c r="AI130" s="24"/>
       <c r="AJ130" s="25"/>
-      <c r="AK130" s="222"/>
-      <c r="AL130" s="223"/>
+      <c r="AK130" s="181"/>
+      <c r="AL130" s="182"/>
     </row>
     <row r="131" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B131" s="13" t="s">
@@ -25357,7 +25355,7 @@
       <c r="W131" s="14">
         <v>0</v>
       </c>
-      <c r="X131" s="113">
+      <c r="X131" s="112">
         <v>0</v>
       </c>
       <c r="Y131" s="14">
@@ -25371,8 +25369,8 @@
       <c r="AA131" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AB131" s="217"/>
-      <c r="AC131" s="142"/>
+      <c r="AB131" s="156"/>
+      <c r="AC131" s="157"/>
       <c r="AD131" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25383,8 +25381,8 @@
       <c r="AH131" s="27"/>
       <c r="AI131" s="27"/>
       <c r="AJ131" s="28"/>
-      <c r="AK131" s="222"/>
-      <c r="AL131" s="223"/>
+      <c r="AK131" s="181"/>
+      <c r="AL131" s="182"/>
     </row>
     <row r="132" spans="1:40" s="12" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B132" s="13" t="s">
@@ -25453,7 +25451,7 @@
       <c r="W132" s="14">
         <v>0</v>
       </c>
-      <c r="X132" s="113">
+      <c r="X132" s="112">
         <v>0</v>
       </c>
       <c r="Y132" s="14">
@@ -25467,8 +25465,8 @@
       <c r="AA132" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AB132" s="217"/>
-      <c r="AC132" s="142"/>
+      <c r="AB132" s="156"/>
+      <c r="AC132" s="157"/>
       <c r="AD132" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25479,8 +25477,8 @@
       <c r="AH132"/>
       <c r="AI132"/>
       <c r="AJ132"/>
-      <c r="AK132" s="222"/>
-      <c r="AL132" s="223"/>
+      <c r="AK132" s="181"/>
+      <c r="AL132" s="182"/>
     </row>
     <row r="133" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B133" s="13" t="s">
@@ -25549,7 +25547,7 @@
       <c r="W133" s="14">
         <v>0</v>
       </c>
-      <c r="X133" s="113">
+      <c r="X133" s="112">
         <v>0</v>
       </c>
       <c r="Y133" s="14">
@@ -25563,8 +25561,8 @@
       <c r="AA133" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="AB133" s="217"/>
-      <c r="AC133" s="142"/>
+      <c r="AB133" s="156"/>
+      <c r="AC133" s="157"/>
       <c r="AD133" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25575,8 +25573,8 @@
       <c r="AH133" s="27"/>
       <c r="AI133" s="27"/>
       <c r="AJ133" s="28"/>
-      <c r="AK133" s="222"/>
-      <c r="AL133" s="223"/>
+      <c r="AK133" s="181"/>
+      <c r="AL133" s="182"/>
     </row>
     <row r="134" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B134" s="13" t="s">
@@ -25645,7 +25643,7 @@
       <c r="W134" s="14">
         <v>0</v>
       </c>
-      <c r="X134" s="113">
+      <c r="X134" s="112">
         <v>0</v>
       </c>
       <c r="Y134" s="14">
@@ -25659,8 +25657,8 @@
       <c r="AA134" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="AB134" s="217"/>
-      <c r="AC134" s="142"/>
+      <c r="AB134" s="156"/>
+      <c r="AC134" s="157"/>
       <c r="AD134" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25671,8 +25669,8 @@
       <c r="AH134" s="27"/>
       <c r="AI134" s="27"/>
       <c r="AJ134" s="28"/>
-      <c r="AK134" s="222"/>
-      <c r="AL134" s="223"/>
+      <c r="AK134" s="181"/>
+      <c r="AL134" s="182"/>
     </row>
     <row r="135" spans="1:40" s="12" customFormat="1" ht="147" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B135" s="13" t="s">
@@ -25741,7 +25739,7 @@
       <c r="W135" s="14">
         <v>0</v>
       </c>
-      <c r="X135" s="113">
+      <c r="X135" s="112">
         <v>0</v>
       </c>
       <c r="Y135" s="14">
@@ -25755,8 +25753,8 @@
       <c r="AA135" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="AB135" s="217"/>
-      <c r="AC135" s="142"/>
+      <c r="AB135" s="156"/>
+      <c r="AC135" s="157"/>
       <c r="AD135" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25767,8 +25765,8 @@
       <c r="AH135" s="84"/>
       <c r="AI135" s="84"/>
       <c r="AJ135" s="85"/>
-      <c r="AK135" s="222"/>
-      <c r="AL135" s="223"/>
+      <c r="AK135" s="181"/>
+      <c r="AL135" s="182"/>
     </row>
     <row r="136" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B136" s="13"/>
@@ -25856,28 +25854,28 @@
         <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="X136" s="114">
+      <c r="X136" s="113">
         <v>0</v>
       </c>
       <c r="Y136" s="14"/>
       <c r="Z136" s="14"/>
       <c r="AA136" s="13"/>
-      <c r="AB136" s="218"/>
-      <c r="AC136" s="143"/>
+      <c r="AB136" s="158"/>
+      <c r="AC136" s="159"/>
       <c r="AD136" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE136" s="17"/>
-      <c r="AF136" s="178" t="s">
+      <c r="AF136" s="175" t="s">
         <v>153</v>
       </c>
-      <c r="AG136" s="179"/>
-      <c r="AH136" s="179"/>
-      <c r="AI136" s="179"/>
-      <c r="AJ136" s="179"/>
-      <c r="AK136" s="222"/>
-      <c r="AL136" s="223"/>
+      <c r="AG136" s="176"/>
+      <c r="AH136" s="176"/>
+      <c r="AI136" s="176"/>
+      <c r="AJ136" s="176"/>
+      <c r="AK136" s="181"/>
+      <c r="AL136" s="182"/>
     </row>
     <row r="137" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B137" s="13" t="s">
@@ -25946,7 +25944,7 @@
       <c r="W137" s="14">
         <v>0</v>
       </c>
-      <c r="X137" s="113">
+      <c r="X137" s="112">
         <v>0</v>
       </c>
       <c r="Y137" s="14">
@@ -25960,73 +25958,73 @@
       <c r="AA137" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="AB137" s="172"/>
-      <c r="AC137" s="173"/>
+      <c r="AB137" s="149"/>
+      <c r="AC137" s="150"/>
       <c r="AD137" s="16">
         <f>X137</f>
         <v>0</v>
       </c>
       <c r="AE137" s="17"/>
-      <c r="AF137" s="229">
+      <c r="AF137" s="177">
         <f>AD137</f>
         <v>0</v>
       </c>
-      <c r="AG137" s="179"/>
-      <c r="AH137" s="179"/>
-      <c r="AI137" s="179"/>
-      <c r="AJ137" s="179"/>
-      <c r="AK137" s="222"/>
-      <c r="AL137" s="223"/>
+      <c r="AG137" s="176"/>
+      <c r="AH137" s="176"/>
+      <c r="AI137" s="176"/>
+      <c r="AJ137" s="176"/>
+      <c r="AK137" s="181"/>
+      <c r="AL137" s="182"/>
     </row>
     <row r="138" spans="1:40" s="88" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A138"/>
       <c r="B138" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="C138" s="128" t="s">
+      <c r="C138" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D138" s="129"/>
-      <c r="E138" s="128" t="s">
+      <c r="D138" s="136"/>
+      <c r="E138" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F138" s="129"/>
-      <c r="G138" s="128" t="s">
+      <c r="F138" s="136"/>
+      <c r="G138" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H138" s="129"/>
-      <c r="I138" s="128" t="s">
+      <c r="H138" s="136"/>
+      <c r="I138" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J138" s="129"/>
-      <c r="K138" s="128" t="s">
+      <c r="J138" s="136"/>
+      <c r="K138" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L138" s="129"/>
-      <c r="M138" s="128" t="s">
+      <c r="L138" s="136"/>
+      <c r="M138" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N138" s="129"/>
-      <c r="O138" s="128" t="s">
+      <c r="N138" s="136"/>
+      <c r="O138" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P138" s="129"/>
-      <c r="Q138" s="128" t="s">
+      <c r="P138" s="136"/>
+      <c r="Q138" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R138" s="129"/>
-      <c r="S138" s="128" t="s">
+      <c r="R138" s="136"/>
+      <c r="S138" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T138" s="129"/>
-      <c r="U138" s="128" t="s">
+      <c r="T138" s="136"/>
+      <c r="U138" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V138" s="129"/>
+      <c r="V138" s="136"/>
       <c r="W138" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X138" s="119"/>
+      <c r="X138" s="118"/>
       <c r="Y138" s="49" t="s">
         <v>13</v>
       </c>
@@ -26036,8 +26034,8 @@
       <c r="AA138" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="AB138" s="227"/>
-      <c r="AC138" s="228"/>
+      <c r="AB138" s="152"/>
+      <c r="AC138" s="153"/>
       <c r="AD138" s="6" t="s">
         <v>16</v>
       </c>
@@ -26120,7 +26118,7 @@
       <c r="W139" s="14">
         <v>0</v>
       </c>
-      <c r="X139" s="113">
+      <c r="X139" s="112">
         <v>0</v>
       </c>
       <c r="Y139" s="14">
@@ -26134,11 +26132,11 @@
       <c r="AA139" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="AB139" s="174">
+      <c r="AB139" s="171">
         <f>SUM(Y139:Y140)</f>
         <v>0</v>
       </c>
-      <c r="AC139" s="175"/>
+      <c r="AC139" s="172"/>
       <c r="AD139" s="16">
         <f>X139</f>
         <v>0</v>
@@ -26220,7 +26218,7 @@
       <c r="W140" s="14">
         <v>0</v>
       </c>
-      <c r="X140" s="113">
+      <c r="X140" s="112">
         <v>0</v>
       </c>
       <c r="Y140" s="14">
@@ -26234,8 +26232,8 @@
       <c r="AA140" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AB140" s="176"/>
-      <c r="AC140" s="177"/>
+      <c r="AB140" s="173"/>
+      <c r="AC140" s="174"/>
       <c r="AD140" s="16">
         <f>X140</f>
         <v>0</v>
@@ -26256,50 +26254,50 @@
       <c r="B141" s="86" t="s">
         <v>212</v>
       </c>
-      <c r="C141" s="128" t="s">
+      <c r="C141" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D141" s="129"/>
-      <c r="E141" s="128" t="s">
+      <c r="D141" s="136"/>
+      <c r="E141" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F141" s="129"/>
-      <c r="G141" s="128" t="s">
+      <c r="F141" s="136"/>
+      <c r="G141" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H141" s="129"/>
-      <c r="I141" s="128" t="s">
+      <c r="H141" s="136"/>
+      <c r="I141" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J141" s="129"/>
-      <c r="K141" s="128" t="s">
+      <c r="J141" s="136"/>
+      <c r="K141" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L141" s="129"/>
-      <c r="M141" s="128" t="s">
+      <c r="L141" s="136"/>
+      <c r="M141" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N141" s="129"/>
-      <c r="O141" s="128" t="s">
+      <c r="N141" s="136"/>
+      <c r="O141" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P141" s="129"/>
-      <c r="Q141" s="128" t="s">
+      <c r="P141" s="136"/>
+      <c r="Q141" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R141" s="129"/>
-      <c r="S141" s="128" t="s">
+      <c r="R141" s="136"/>
+      <c r="S141" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T141" s="129"/>
-      <c r="U141" s="128" t="s">
+      <c r="T141" s="136"/>
+      <c r="U141" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V141" s="129"/>
+      <c r="V141" s="136"/>
       <c r="W141" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X141" s="119"/>
+      <c r="X141" s="118"/>
       <c r="Y141" s="49" t="s">
         <v>13</v>
       </c>
@@ -26309,8 +26307,8 @@
       <c r="AA141" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="AB141" s="227"/>
-      <c r="AC141" s="228"/>
+      <c r="AB141" s="152"/>
+      <c r="AC141" s="153"/>
       <c r="AD141" s="6" t="s">
         <v>16</v>
       </c>
@@ -26393,7 +26391,7 @@
       <c r="W142" s="14">
         <v>0</v>
       </c>
-      <c r="X142" s="113">
+      <c r="X142" s="112">
         <v>0</v>
       </c>
       <c r="Y142" s="14">
@@ -26407,11 +26405,11 @@
       <c r="AA142" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AB142" s="216">
+      <c r="AB142" s="154">
         <f>SUM(Y142:Y152)</f>
         <v>0</v>
       </c>
-      <c r="AC142" s="141"/>
+      <c r="AC142" s="155"/>
       <c r="AD142" s="16">
         <f>X142</f>
         <v>0</v>
@@ -26493,7 +26491,7 @@
       <c r="W143" s="14">
         <v>0</v>
       </c>
-      <c r="X143" s="113">
+      <c r="X143" s="112">
         <v>0</v>
       </c>
       <c r="Y143" s="14">
@@ -26507,8 +26505,8 @@
       <c r="AA143" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AB143" s="217"/>
-      <c r="AC143" s="142"/>
+      <c r="AB143" s="156"/>
+      <c r="AC143" s="157"/>
       <c r="AD143" s="16">
         <f t="shared" ref="AD143:AD152" si="41">X143</f>
         <v>0</v>
@@ -26590,7 +26588,7 @@
       <c r="W144" s="14">
         <v>0</v>
       </c>
-      <c r="X144" s="113">
+      <c r="X144" s="112">
         <v>0</v>
       </c>
       <c r="Y144" s="14">
@@ -26604,8 +26602,8 @@
       <c r="AA144" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AB144" s="217"/>
-      <c r="AC144" s="142"/>
+      <c r="AB144" s="156"/>
+      <c r="AC144" s="157"/>
       <c r="AD144" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26687,7 +26685,7 @@
       <c r="W145" s="14">
         <v>0</v>
       </c>
-      <c r="X145" s="113">
+      <c r="X145" s="112">
         <v>0</v>
       </c>
       <c r="Y145" s="14">
@@ -26701,8 +26699,8 @@
       <c r="AA145" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AB145" s="217"/>
-      <c r="AC145" s="142"/>
+      <c r="AB145" s="156"/>
+      <c r="AC145" s="157"/>
       <c r="AD145" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26784,7 +26782,7 @@
       <c r="W146" s="14">
         <v>0</v>
       </c>
-      <c r="X146" s="113">
+      <c r="X146" s="112">
         <v>0</v>
       </c>
       <c r="Y146" s="14">
@@ -26798,8 +26796,8 @@
       <c r="AA146" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="AB146" s="217"/>
-      <c r="AC146" s="142"/>
+      <c r="AB146" s="156"/>
+      <c r="AC146" s="157"/>
       <c r="AD146" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26881,7 +26879,7 @@
       <c r="W147" s="14">
         <v>0</v>
       </c>
-      <c r="X147" s="113">
+      <c r="X147" s="112">
         <v>0</v>
       </c>
       <c r="Y147" s="14">
@@ -26895,8 +26893,8 @@
       <c r="AA147" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AB147" s="217"/>
-      <c r="AC147" s="142"/>
+      <c r="AB147" s="156"/>
+      <c r="AC147" s="157"/>
       <c r="AD147" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26978,7 +26976,7 @@
       <c r="W148" s="14">
         <v>0</v>
       </c>
-      <c r="X148" s="113">
+      <c r="X148" s="112">
         <v>0</v>
       </c>
       <c r="Y148" s="14">
@@ -26992,8 +26990,8 @@
       <c r="AA148" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="AB148" s="217"/>
-      <c r="AC148" s="142"/>
+      <c r="AB148" s="156"/>
+      <c r="AC148" s="157"/>
       <c r="AD148" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27075,7 +27073,7 @@
       <c r="W149" s="14">
         <v>0</v>
       </c>
-      <c r="X149" s="113">
+      <c r="X149" s="112">
         <v>0</v>
       </c>
       <c r="Y149" s="14">
@@ -27089,8 +27087,8 @@
       <c r="AA149" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AB149" s="217"/>
-      <c r="AC149" s="142"/>
+      <c r="AB149" s="156"/>
+      <c r="AC149" s="157"/>
       <c r="AD149" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27172,7 +27170,7 @@
       <c r="W150" s="14">
         <v>0</v>
       </c>
-      <c r="X150" s="113">
+      <c r="X150" s="112">
         <v>0</v>
       </c>
       <c r="Y150" s="14">
@@ -27186,8 +27184,8 @@
       <c r="AA150" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="AB150" s="217"/>
-      <c r="AC150" s="142"/>
+      <c r="AB150" s="156"/>
+      <c r="AC150" s="157"/>
       <c r="AD150" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27269,7 +27267,7 @@
       <c r="W151" s="14">
         <v>0</v>
       </c>
-      <c r="X151" s="113">
+      <c r="X151" s="112">
         <v>0</v>
       </c>
       <c r="Y151" s="14">
@@ -27283,8 +27281,8 @@
       <c r="AA151" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="AB151" s="217"/>
-      <c r="AC151" s="142"/>
+      <c r="AB151" s="156"/>
+      <c r="AC151" s="157"/>
       <c r="AD151" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27366,7 +27364,7 @@
       <c r="W152" s="14">
         <v>0</v>
       </c>
-      <c r="X152" s="113">
+      <c r="X152" s="112">
         <v>0</v>
       </c>
       <c r="Y152" s="14">
@@ -27380,8 +27378,8 @@
       <c r="AA152" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="AB152" s="218"/>
-      <c r="AC152" s="143"/>
+      <c r="AB152" s="158"/>
+      <c r="AC152" s="159"/>
       <c r="AD152" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27483,12 +27481,12 @@
         <f t="shared" si="42"/>
         <v>0</v>
       </c>
-      <c r="X153" s="114"/>
+      <c r="X153" s="113"/>
       <c r="Y153" s="14"/>
       <c r="Z153" s="14"/>
       <c r="AA153" s="13"/>
-      <c r="AB153" s="172"/>
-      <c r="AC153" s="173"/>
+      <c r="AB153" s="149"/>
+      <c r="AC153" s="150"/>
       <c r="AD153" s="16">
         <v>0</v>
       </c>
@@ -27502,101 +27500,101 @@
       <c r="AL153" s="92"/>
     </row>
     <row r="154" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="1.85">
-      <c r="B154" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="C154" s="133"/>
-      <c r="D154" s="133"/>
-      <c r="E154" s="133"/>
-      <c r="F154" s="133"/>
-      <c r="G154" s="133"/>
-      <c r="H154" s="133"/>
-      <c r="I154" s="133"/>
-      <c r="J154" s="133"/>
-      <c r="K154" s="133"/>
-      <c r="L154" s="133"/>
-      <c r="M154" s="133"/>
-      <c r="N154" s="133"/>
-      <c r="O154" s="133"/>
-      <c r="P154" s="133"/>
-      <c r="Q154" s="133"/>
-      <c r="R154" s="133"/>
-      <c r="S154" s="133"/>
-      <c r="T154" s="133"/>
-      <c r="U154" s="133"/>
-      <c r="V154" s="133"/>
-      <c r="W154" s="133"/>
-      <c r="X154" s="133"/>
-      <c r="Y154" s="133"/>
-      <c r="Z154" s="133"/>
-      <c r="AA154" s="133"/>
-      <c r="AB154" s="133"/>
-      <c r="AC154" s="133"/>
-      <c r="AD154" s="133"/>
+      <c r="B154" s="169" t="s">
+        <v>0</v>
+      </c>
+      <c r="C154" s="170"/>
+      <c r="D154" s="170"/>
+      <c r="E154" s="170"/>
+      <c r="F154" s="170"/>
+      <c r="G154" s="170"/>
+      <c r="H154" s="170"/>
+      <c r="I154" s="170"/>
+      <c r="J154" s="170"/>
+      <c r="K154" s="170"/>
+      <c r="L154" s="170"/>
+      <c r="M154" s="170"/>
+      <c r="N154" s="170"/>
+      <c r="O154" s="170"/>
+      <c r="P154" s="170"/>
+      <c r="Q154" s="170"/>
+      <c r="R154" s="170"/>
+      <c r="S154" s="170"/>
+      <c r="T154" s="170"/>
+      <c r="U154" s="170"/>
+      <c r="V154" s="170"/>
+      <c r="W154" s="170"/>
+      <c r="X154" s="170"/>
+      <c r="Y154" s="170"/>
+      <c r="Z154" s="170"/>
+      <c r="AA154" s="170"/>
+      <c r="AB154" s="170"/>
+      <c r="AC154" s="170"/>
+      <c r="AD154" s="170"/>
       <c r="AE154" s="1"/>
       <c r="AK154" s="92"/>
       <c r="AL154" s="92"/>
     </row>
     <row r="155" spans="1:40" s="88" customFormat="1" ht="138.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A155"/>
-      <c r="B155" s="130" t="s">
+      <c r="B155" s="167" t="s">
         <v>170</v>
       </c>
-      <c r="C155" s="128" t="s">
+      <c r="C155" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D155" s="129"/>
-      <c r="E155" s="128" t="s">
+      <c r="D155" s="136"/>
+      <c r="E155" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F155" s="129"/>
-      <c r="G155" s="128" t="s">
+      <c r="F155" s="136"/>
+      <c r="G155" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H155" s="129"/>
-      <c r="I155" s="128" t="s">
+      <c r="H155" s="136"/>
+      <c r="I155" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J155" s="129"/>
-      <c r="K155" s="128" t="s">
+      <c r="J155" s="136"/>
+      <c r="K155" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L155" s="129"/>
-      <c r="M155" s="128" t="s">
+      <c r="L155" s="136"/>
+      <c r="M155" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N155" s="129"/>
-      <c r="O155" s="128" t="s">
+      <c r="N155" s="136"/>
+      <c r="O155" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P155" s="129"/>
-      <c r="Q155" s="128" t="s">
+      <c r="P155" s="136"/>
+      <c r="Q155" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R155" s="129"/>
-      <c r="S155" s="128" t="s">
+      <c r="R155" s="136"/>
+      <c r="S155" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T155" s="129"/>
-      <c r="U155" s="128" t="s">
+      <c r="T155" s="136"/>
+      <c r="U155" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V155" s="129"/>
-      <c r="W155" s="130" t="s">
+      <c r="V155" s="136"/>
+      <c r="W155" s="167" t="s">
         <v>12</v>
       </c>
-      <c r="X155" s="111"/>
-      <c r="Y155" s="130" t="s">
+      <c r="X155" s="110"/>
+      <c r="Y155" s="167" t="s">
         <v>13</v>
       </c>
-      <c r="Z155" s="130" t="s">
+      <c r="Z155" s="167" t="s">
         <v>14</v>
       </c>
-      <c r="AA155" s="130" t="s">
+      <c r="AA155" s="167" t="s">
         <v>170</v>
       </c>
-      <c r="AB155" s="227"/>
-      <c r="AC155" s="228"/>
+      <c r="AB155" s="152"/>
+      <c r="AC155" s="153"/>
       <c r="AD155" s="6" t="s">
         <v>16</v>
       </c>
@@ -27612,7 +27610,7 @@
       <c r="AN155" s="12"/>
     </row>
     <row r="156" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B156" s="131"/>
+      <c r="B156" s="168"/>
       <c r="C156" s="9" t="s">
         <v>17</v>
       </c>
@@ -27673,11 +27671,11 @@
       <c r="V156" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W156" s="131"/>
-      <c r="X156" s="112"/>
-      <c r="Y156" s="131"/>
-      <c r="Z156" s="131"/>
-      <c r="AA156" s="131"/>
+      <c r="W156" s="168"/>
+      <c r="X156" s="111"/>
+      <c r="Y156" s="168"/>
+      <c r="Z156" s="168"/>
+      <c r="AA156" s="168"/>
       <c r="AB156" s="10"/>
       <c r="AC156" s="11"/>
       <c r="AD156" s="6">
@@ -27759,7 +27757,7 @@
       <c r="W157" s="14">
         <v>0</v>
       </c>
-      <c r="X157" s="113">
+      <c r="X157" s="112">
         <v>0</v>
       </c>
       <c r="Y157" s="14">
@@ -27773,11 +27771,11 @@
       <c r="AA157" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AB157" s="216">
+      <c r="AB157" s="154">
         <f>SUM(Y157:Y162)</f>
         <v>0</v>
       </c>
-      <c r="AC157" s="141"/>
+      <c r="AC157" s="155"/>
       <c r="AD157" s="16">
         <f>X157</f>
         <v>0</v>
@@ -27858,7 +27856,7 @@
       <c r="W158" s="14">
         <v>0</v>
       </c>
-      <c r="X158" s="113">
+      <c r="X158" s="112">
         <v>0</v>
       </c>
       <c r="Y158" s="14">
@@ -27872,8 +27870,8 @@
       <c r="AA158" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AB158" s="217"/>
-      <c r="AC158" s="142"/>
+      <c r="AB158" s="156"/>
+      <c r="AC158" s="157"/>
       <c r="AD158" s="16">
         <f t="shared" ref="AD158:AD162" si="45">X158</f>
         <v>0</v>
@@ -27954,7 +27952,7 @@
       <c r="W159" s="14">
         <v>0</v>
       </c>
-      <c r="X159" s="113">
+      <c r="X159" s="112">
         <v>0</v>
       </c>
       <c r="Y159" s="14">
@@ -27968,8 +27966,8 @@
       <c r="AA159" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AB159" s="217"/>
-      <c r="AC159" s="142"/>
+      <c r="AB159" s="156"/>
+      <c r="AC159" s="157"/>
       <c r="AD159" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28050,7 +28048,7 @@
       <c r="W160" s="14">
         <v>0</v>
       </c>
-      <c r="X160" s="113">
+      <c r="X160" s="112">
         <v>0</v>
       </c>
       <c r="Y160" s="14">
@@ -28064,8 +28062,8 @@
       <c r="AA160" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AB160" s="217"/>
-      <c r="AC160" s="142"/>
+      <c r="AB160" s="156"/>
+      <c r="AC160" s="157"/>
       <c r="AD160" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28146,7 +28144,7 @@
       <c r="W161" s="14">
         <v>0</v>
       </c>
-      <c r="X161" s="113">
+      <c r="X161" s="112">
         <v>0</v>
       </c>
       <c r="Y161" s="14">
@@ -28160,8 +28158,8 @@
       <c r="AA161" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AB161" s="217"/>
-      <c r="AC161" s="142"/>
+      <c r="AB161" s="156"/>
+      <c r="AC161" s="157"/>
       <c r="AD161" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28242,7 +28240,7 @@
       <c r="W162" s="14">
         <v>0</v>
       </c>
-      <c r="X162" s="113">
+      <c r="X162" s="112">
         <v>0</v>
       </c>
       <c r="Y162" s="14">
@@ -28256,8 +28254,8 @@
       <c r="AA162" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AB162" s="218"/>
-      <c r="AC162" s="143"/>
+      <c r="AB162" s="158"/>
+      <c r="AC162" s="159"/>
       <c r="AD162" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28277,59 +28275,59 @@
       <c r="B163" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="C163" s="128" t="s">
+      <c r="C163" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D163" s="129"/>
-      <c r="E163" s="128" t="s">
+      <c r="D163" s="136"/>
+      <c r="E163" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F163" s="129"/>
-      <c r="G163" s="128" t="s">
+      <c r="F163" s="136"/>
+      <c r="G163" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H163" s="129"/>
-      <c r="I163" s="128" t="s">
+      <c r="H163" s="136"/>
+      <c r="I163" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J163" s="129"/>
-      <c r="K163" s="128" t="s">
+      <c r="J163" s="136"/>
+      <c r="K163" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L163" s="129"/>
-      <c r="M163" s="128" t="s">
+      <c r="L163" s="136"/>
+      <c r="M163" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N163" s="129"/>
-      <c r="O163" s="128" t="s">
+      <c r="N163" s="136"/>
+      <c r="O163" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P163" s="129"/>
-      <c r="Q163" s="128" t="s">
+      <c r="P163" s="136"/>
+      <c r="Q163" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R163" s="129"/>
-      <c r="S163" s="128" t="s">
+      <c r="R163" s="136"/>
+      <c r="S163" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T163" s="129"/>
-      <c r="U163" s="128" t="s">
+      <c r="T163" s="136"/>
+      <c r="U163" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V163" s="129"/>
+      <c r="V163" s="136"/>
       <c r="W163" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X163" s="118"/>
-      <c r="Y163" s="232" t="s">
+      <c r="X163" s="117"/>
+      <c r="Y163" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="Z163" s="233"/>
+      <c r="Z163" s="148"/>
       <c r="AA163" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="AB163" s="134"/>
-      <c r="AC163" s="135"/>
+      <c r="AB163" s="139"/>
+      <c r="AC163" s="140"/>
       <c r="AD163" s="6" t="s">
         <v>16</v>
       </c>
@@ -28388,34 +28386,34 @@
       <c r="W164" s="14">
         <v>0</v>
       </c>
-      <c r="X164" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y164" s="230">
+      <c r="X164" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y164" s="141">
         <f t="shared" ref="Y164:Y187" si="46">SUM(C164:W164)</f>
         <v>0</v>
       </c>
-      <c r="Z164" s="231"/>
+      <c r="Z164" s="142"/>
       <c r="AA164" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AB164" s="216">
+      <c r="AB164" s="154">
         <f>SUM(Y164:Y171)</f>
         <v>0</v>
       </c>
-      <c r="AC164" s="141"/>
+      <c r="AC164" s="155"/>
       <c r="AD164" s="16">
         <f>X164</f>
         <v>0</v>
       </c>
       <c r="AE164" s="94"/>
-      <c r="AF164" s="162" t="s">
+      <c r="AF164" s="160" t="s">
         <v>180</v>
       </c>
-      <c r="AG164" s="163"/>
-      <c r="AH164" s="163"/>
-      <c r="AI164" s="163"/>
-      <c r="AJ164" s="164"/>
+      <c r="AG164" s="161"/>
+      <c r="AH164" s="161"/>
+      <c r="AI164" s="161"/>
+      <c r="AJ164" s="162"/>
       <c r="AK164" s="8"/>
       <c r="AL164" s="8"/>
     </row>
@@ -28466,29 +28464,29 @@
       <c r="W165" s="14">
         <v>0</v>
       </c>
-      <c r="X165" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y165" s="230">
+      <c r="X165" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y165" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z165" s="231"/>
+      <c r="Z165" s="142"/>
       <c r="AA165" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="AB165" s="217"/>
-      <c r="AC165" s="142"/>
+      <c r="AB165" s="156"/>
+      <c r="AC165" s="157"/>
       <c r="AD165" s="16">
         <f t="shared" ref="AD165:AD170" si="47">X165</f>
         <v>0</v>
       </c>
       <c r="AE165" s="94"/>
-      <c r="AF165" s="165"/>
-      <c r="AG165" s="154"/>
-      <c r="AH165" s="154"/>
-      <c r="AI165" s="154"/>
-      <c r="AJ165" s="155"/>
+      <c r="AF165" s="163"/>
+      <c r="AG165" s="164"/>
+      <c r="AH165" s="164"/>
+      <c r="AI165" s="164"/>
+      <c r="AJ165" s="165"/>
       <c r="AK165" s="8"/>
       <c r="AL165" s="8"/>
     </row>
@@ -28539,29 +28537,29 @@
       <c r="W166" s="14">
         <v>0</v>
       </c>
-      <c r="X166" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y166" s="230">
+      <c r="X166" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y166" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z166" s="231"/>
+      <c r="Z166" s="142"/>
       <c r="AA166" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="AB166" s="217"/>
-      <c r="AC166" s="142"/>
+      <c r="AB166" s="156"/>
+      <c r="AC166" s="157"/>
       <c r="AD166" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE166" s="94"/>
-      <c r="AF166" s="165"/>
-      <c r="AG166" s="154"/>
-      <c r="AH166" s="154"/>
-      <c r="AI166" s="154"/>
-      <c r="AJ166" s="155"/>
+      <c r="AF166" s="163"/>
+      <c r="AG166" s="164"/>
+      <c r="AH166" s="164"/>
+      <c r="AI166" s="164"/>
+      <c r="AJ166" s="165"/>
       <c r="AK166" s="8"/>
       <c r="AL166" s="8"/>
     </row>
@@ -28612,29 +28610,29 @@
       <c r="W167" s="14">
         <v>0</v>
       </c>
-      <c r="X167" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y167" s="230">
+      <c r="X167" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y167" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z167" s="231"/>
+      <c r="Z167" s="142"/>
       <c r="AA167" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="AB167" s="217"/>
-      <c r="AC167" s="142"/>
+      <c r="AB167" s="156"/>
+      <c r="AC167" s="157"/>
       <c r="AD167" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE167" s="94"/>
-      <c r="AF167" s="165"/>
-      <c r="AG167" s="154"/>
-      <c r="AH167" s="154"/>
-      <c r="AI167" s="154"/>
-      <c r="AJ167" s="155"/>
+      <c r="AF167" s="163"/>
+      <c r="AG167" s="164"/>
+      <c r="AH167" s="164"/>
+      <c r="AI167" s="164"/>
+      <c r="AJ167" s="165"/>
       <c r="AK167" s="8"/>
       <c r="AL167" s="8"/>
     </row>
@@ -28685,32 +28683,32 @@
       <c r="W168" s="14">
         <v>0</v>
       </c>
-      <c r="X168" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y168" s="230">
+      <c r="X168" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y168" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z168" s="231"/>
+      <c r="Z168" s="142"/>
       <c r="AA168" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="AB168" s="217"/>
-      <c r="AC168" s="142"/>
+      <c r="AB168" s="156"/>
+      <c r="AC168" s="157"/>
       <c r="AD168" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE168" s="94"/>
-      <c r="AF168" s="153">
+      <c r="AF168" s="166">
         <f>SUM(AD164:AD171)</f>
         <v>0</v>
       </c>
-      <c r="AG168" s="154"/>
-      <c r="AH168" s="154"/>
-      <c r="AI168" s="154"/>
-      <c r="AJ168" s="155"/>
+      <c r="AG168" s="164"/>
+      <c r="AH168" s="164"/>
+      <c r="AI168" s="164"/>
+      <c r="AJ168" s="165"/>
       <c r="AK168" s="8"/>
       <c r="AL168" s="8"/>
     </row>
@@ -28761,19 +28759,19 @@
       <c r="W169" s="14">
         <v>0</v>
       </c>
-      <c r="X169" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y169" s="230">
+      <c r="X169" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y169" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z169" s="231"/>
+      <c r="Z169" s="142"/>
       <c r="AA169" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="AB169" s="217"/>
-      <c r="AC169" s="142"/>
+      <c r="AB169" s="156"/>
+      <c r="AC169" s="157"/>
       <c r="AD169" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -28834,19 +28832,19 @@
       <c r="W170" s="14">
         <v>0</v>
       </c>
-      <c r="X170" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y170" s="230">
+      <c r="X170" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y170" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z170" s="231"/>
+      <c r="Z170" s="142"/>
       <c r="AA170" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="AB170" s="217"/>
-      <c r="AC170" s="142"/>
+      <c r="AB170" s="156"/>
+      <c r="AC170" s="157"/>
       <c r="AD170" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -28907,19 +28905,19 @@
       <c r="W171" s="14">
         <v>0</v>
       </c>
-      <c r="X171" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y171" s="230">
+      <c r="X171" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y171" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z171" s="231"/>
+      <c r="Z171" s="142"/>
       <c r="AA171" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="AB171" s="218"/>
-      <c r="AC171" s="143"/>
+      <c r="AB171" s="158"/>
+      <c r="AC171" s="159"/>
       <c r="AD171" s="16">
         <f>X171</f>
         <v>0</v>
@@ -28991,17 +28989,17 @@
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="X172" s="122"/>
-      <c r="Y172" s="232">
+      <c r="X172" s="121"/>
+      <c r="Y172" s="147">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z172" s="233"/>
+      <c r="Z172" s="148"/>
       <c r="AA172" s="86" t="s">
         <v>189</v>
       </c>
-      <c r="AB172" s="227"/>
-      <c r="AC172" s="228"/>
+      <c r="AB172" s="152"/>
+      <c r="AC172" s="153"/>
       <c r="AD172" s="6" t="s">
         <v>16</v>
       </c>
@@ -29054,19 +29052,19 @@
       <c r="W173" s="14">
         <v>0</v>
       </c>
-      <c r="X173" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y173" s="230">
+      <c r="X173" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y173" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z173" s="231"/>
+      <c r="Z173" s="142"/>
       <c r="AA173" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="AB173" s="172"/>
-      <c r="AC173" s="173"/>
+      <c r="AB173" s="149"/>
+      <c r="AC173" s="150"/>
       <c r="AD173" s="16">
         <f>X173</f>
         <v>0</v>
@@ -29127,19 +29125,19 @@
       <c r="W174" s="14">
         <v>0</v>
       </c>
-      <c r="X174" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y174" s="230">
+      <c r="X174" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y174" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z174" s="231"/>
+      <c r="Z174" s="142"/>
       <c r="AA174" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AB174" s="172"/>
-      <c r="AC174" s="173"/>
+      <c r="AB174" s="149"/>
+      <c r="AC174" s="150"/>
       <c r="AD174" s="16">
         <f>X174</f>
         <v>0</v>
@@ -29200,19 +29198,19 @@
       <c r="W175" s="14">
         <v>0</v>
       </c>
-      <c r="X175" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y175" s="230">
+      <c r="X175" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z175" s="231"/>
+      <c r="Z175" s="142"/>
       <c r="AA175" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="AB175" s="172"/>
-      <c r="AC175" s="173"/>
+      <c r="AB175" s="149"/>
+      <c r="AC175" s="150"/>
       <c r="AD175" s="16">
         <f>X175</f>
         <v>0</v>
@@ -29273,19 +29271,19 @@
       <c r="W176" s="14">
         <v>0</v>
       </c>
-      <c r="X176" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y176" s="230">
+      <c r="X176" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y176" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z176" s="231"/>
+      <c r="Z176" s="142"/>
       <c r="AA176" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="AB176" s="172"/>
-      <c r="AC176" s="173"/>
+      <c r="AB176" s="149"/>
+      <c r="AC176" s="150"/>
       <c r="AD176" s="16">
         <f t="shared" ref="AD176:AD187" si="49">X176</f>
         <v>0</v>
@@ -29346,19 +29344,19 @@
       <c r="W177" s="14">
         <v>0</v>
       </c>
-      <c r="X177" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y177" s="230">
+      <c r="X177" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y177" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z177" s="231"/>
+      <c r="Z177" s="142"/>
       <c r="AA177" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="AB177" s="172"/>
-      <c r="AC177" s="173"/>
+      <c r="AB177" s="149"/>
+      <c r="AC177" s="150"/>
       <c r="AD177" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29419,28 +29417,28 @@
       <c r="W178" s="14">
         <v>0</v>
       </c>
-      <c r="X178" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y178" s="230">
+      <c r="X178" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y178" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z178" s="231"/>
+      <c r="Z178" s="142"/>
       <c r="AA178" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="AB178" s="172"/>
-      <c r="AC178" s="173"/>
+      <c r="AB178" s="149"/>
+      <c r="AC178" s="150"/>
       <c r="AD178" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE178" s="98"/>
       <c r="AF178" s="99"/>
-      <c r="AG178" s="234"/>
-      <c r="AH178" s="234"/>
-      <c r="AI178" s="234"/>
+      <c r="AG178" s="151"/>
+      <c r="AH178" s="151"/>
+      <c r="AI178" s="151"/>
       <c r="AJ178" s="99"/>
       <c r="AK178" s="8"/>
       <c r="AL178" s="8"/>
@@ -29492,19 +29490,19 @@
       <c r="W179" s="14">
         <v>0</v>
       </c>
-      <c r="X179" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y179" s="230">
+      <c r="X179" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z179" s="231"/>
+      <c r="Z179" s="142"/>
       <c r="AA179" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="AB179" s="172"/>
-      <c r="AC179" s="173"/>
+      <c r="AB179" s="149"/>
+      <c r="AC179" s="150"/>
       <c r="AD179" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29565,19 +29563,19 @@
       <c r="W180" s="14">
         <v>0</v>
       </c>
-      <c r="X180" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y180" s="230">
+      <c r="X180" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z180" s="231"/>
+      <c r="Z180" s="142"/>
       <c r="AA180" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="AB180" s="172"/>
-      <c r="AC180" s="173"/>
+      <c r="AB180" s="149"/>
+      <c r="AC180" s="150"/>
       <c r="AD180" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29638,19 +29636,19 @@
       <c r="W181" s="14">
         <v>0</v>
       </c>
-      <c r="X181" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y181" s="230">
+      <c r="X181" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z181" s="231"/>
+      <c r="Z181" s="142"/>
       <c r="AA181" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AB181" s="172"/>
-      <c r="AC181" s="173"/>
+      <c r="AB181" s="149"/>
+      <c r="AC181" s="150"/>
       <c r="AD181" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29711,21 +29709,21 @@
       <c r="W182" s="14">
         <v>0</v>
       </c>
-      <c r="X182" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y182" s="230">
+      <c r="X182" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y182" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z182" s="231"/>
+      <c r="Z182" s="142"/>
       <c r="AA182" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="AB182" s="126" t="s">
+      <c r="AB182" s="125" t="s">
         <v>211</v>
       </c>
-      <c r="AC182" s="127"/>
+      <c r="AC182" s="126"/>
       <c r="AD182" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29786,19 +29784,19 @@
       <c r="W183" s="14">
         <v>0</v>
       </c>
-      <c r="X183" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y183" s="230">
+      <c r="X183" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y183" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z183" s="231"/>
+      <c r="Z183" s="142"/>
       <c r="AA183" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="AB183" s="172"/>
-      <c r="AC183" s="173"/>
+      <c r="AB183" s="149"/>
+      <c r="AC183" s="150"/>
       <c r="AD183" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29859,19 +29857,19 @@
       <c r="W184" s="14">
         <v>0</v>
       </c>
-      <c r="X184" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y184" s="230">
+      <c r="X184" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y184" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z184" s="231"/>
+      <c r="Z184" s="142"/>
       <c r="AA184" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="AB184" s="172"/>
-      <c r="AC184" s="173"/>
+      <c r="AB184" s="149"/>
+      <c r="AC184" s="150"/>
       <c r="AD184" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29932,19 +29930,19 @@
       <c r="W185" s="14">
         <v>0</v>
       </c>
-      <c r="X185" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y185" s="230">
+      <c r="X185" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y185" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z185" s="231"/>
+      <c r="Z185" s="142"/>
       <c r="AA185" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="AB185" s="172"/>
-      <c r="AC185" s="173"/>
+      <c r="AB185" s="149"/>
+      <c r="AC185" s="150"/>
       <c r="AD185" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30005,19 +30003,19 @@
       <c r="W186" s="14">
         <v>0</v>
       </c>
-      <c r="X186" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y186" s="230">
+      <c r="X186" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z186" s="231"/>
+      <c r="Z186" s="142"/>
       <c r="AA186" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="AB186" s="172"/>
-      <c r="AC186" s="173"/>
+      <c r="AB186" s="149"/>
+      <c r="AC186" s="150"/>
       <c r="AD186" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30078,19 +30076,19 @@
       <c r="W187" s="14">
         <v>0</v>
       </c>
-      <c r="X187" s="121">
-        <v>0</v>
-      </c>
-      <c r="Y187" s="230">
+      <c r="X187" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="141">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z187" s="231"/>
+      <c r="Z187" s="142"/>
       <c r="AA187" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="AB187" s="172"/>
-      <c r="AC187" s="173"/>
+      <c r="AB187" s="149"/>
+      <c r="AC187" s="150"/>
       <c r="AD187" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30108,59 +30106,59 @@
       <c r="B188" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="C188" s="128" t="s">
+      <c r="C188" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D188" s="129"/>
-      <c r="E188" s="128" t="s">
+      <c r="D188" s="136"/>
+      <c r="E188" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F188" s="129"/>
-      <c r="G188" s="128" t="s">
+      <c r="F188" s="136"/>
+      <c r="G188" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H188" s="129"/>
-      <c r="I188" s="128" t="s">
+      <c r="H188" s="136"/>
+      <c r="I188" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J188" s="129"/>
-      <c r="K188" s="128" t="s">
+      <c r="J188" s="136"/>
+      <c r="K188" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L188" s="129"/>
-      <c r="M188" s="128" t="s">
+      <c r="L188" s="136"/>
+      <c r="M188" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N188" s="129"/>
-      <c r="O188" s="128" t="s">
+      <c r="N188" s="136"/>
+      <c r="O188" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P188" s="129"/>
-      <c r="Q188" s="128" t="s">
+      <c r="P188" s="136"/>
+      <c r="Q188" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R188" s="129"/>
-      <c r="S188" s="128" t="s">
+      <c r="R188" s="136"/>
+      <c r="S188" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T188" s="129"/>
-      <c r="U188" s="128" t="s">
+      <c r="T188" s="136"/>
+      <c r="U188" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V188" s="129"/>
+      <c r="V188" s="136"/>
       <c r="W188" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X188" s="118"/>
-      <c r="Y188" s="232" t="s">
+      <c r="X188" s="117"/>
+      <c r="Y188" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="Z188" s="233"/>
+      <c r="Z188" s="148"/>
       <c r="AA188" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="AB188" s="134"/>
-      <c r="AC188" s="135"/>
+      <c r="AB188" s="139"/>
+      <c r="AC188" s="140"/>
       <c r="AD188" s="6" t="s">
         <v>16</v>
       </c>
@@ -30172,60 +30170,60 @@
       <c r="B189" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C189" s="230">
-        <v>0</v>
-      </c>
-      <c r="D189" s="231"/>
-      <c r="E189" s="230">
-        <v>0</v>
-      </c>
-      <c r="F189" s="231"/>
-      <c r="G189" s="230">
-        <v>0</v>
-      </c>
-      <c r="H189" s="231"/>
-      <c r="I189" s="230">
-        <v>0</v>
-      </c>
-      <c r="J189" s="231"/>
-      <c r="K189" s="230">
-        <v>0</v>
-      </c>
-      <c r="L189" s="231"/>
-      <c r="M189" s="230">
-        <v>0</v>
-      </c>
-      <c r="N189" s="231"/>
-      <c r="O189" s="230">
-        <v>0</v>
-      </c>
-      <c r="P189" s="231"/>
-      <c r="Q189" s="230">
-        <v>0</v>
-      </c>
-      <c r="R189" s="231"/>
-      <c r="S189" s="230">
-        <v>0</v>
-      </c>
-      <c r="T189" s="231"/>
-      <c r="U189" s="230">
-        <v>0</v>
-      </c>
-      <c r="V189" s="231"/>
+      <c r="C189" s="141">
+        <v>0</v>
+      </c>
+      <c r="D189" s="142"/>
+      <c r="E189" s="141">
+        <v>0</v>
+      </c>
+      <c r="F189" s="142"/>
+      <c r="G189" s="141">
+        <v>0</v>
+      </c>
+      <c r="H189" s="142"/>
+      <c r="I189" s="141">
+        <v>0</v>
+      </c>
+      <c r="J189" s="142"/>
+      <c r="K189" s="141">
+        <v>0</v>
+      </c>
+      <c r="L189" s="142"/>
+      <c r="M189" s="141">
+        <v>0</v>
+      </c>
+      <c r="N189" s="142"/>
+      <c r="O189" s="141">
+        <v>0</v>
+      </c>
+      <c r="P189" s="142"/>
+      <c r="Q189" s="141">
+        <v>0</v>
+      </c>
+      <c r="R189" s="142"/>
+      <c r="S189" s="141">
+        <v>0</v>
+      </c>
+      <c r="T189" s="142"/>
+      <c r="U189" s="141">
+        <v>0</v>
+      </c>
+      <c r="V189" s="142"/>
       <c r="W189" s="14">
         <v>0</v>
       </c>
-      <c r="X189" s="121"/>
-      <c r="Y189" s="230">
+      <c r="X189" s="120"/>
+      <c r="Y189" s="141">
         <f>SUM(C189:W189)</f>
         <v>0</v>
       </c>
-      <c r="Z189" s="231"/>
+      <c r="Z189" s="142"/>
       <c r="AA189" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AB189" s="214"/>
-      <c r="AC189" s="215"/>
+      <c r="AB189" s="145"/>
+      <c r="AC189" s="146"/>
       <c r="AD189" s="16">
         <f>X189</f>
         <v>0</v>
@@ -30238,59 +30236,59 @@
       <c r="B190" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="C190" s="128" t="s">
+      <c r="C190" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D190" s="129"/>
-      <c r="E190" s="128" t="s">
+      <c r="D190" s="136"/>
+      <c r="E190" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F190" s="129"/>
-      <c r="G190" s="128" t="s">
+      <c r="F190" s="136"/>
+      <c r="G190" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H190" s="129"/>
-      <c r="I190" s="128" t="s">
+      <c r="H190" s="136"/>
+      <c r="I190" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J190" s="129"/>
-      <c r="K190" s="128" t="s">
+      <c r="J190" s="136"/>
+      <c r="K190" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L190" s="129"/>
-      <c r="M190" s="128" t="s">
+      <c r="L190" s="136"/>
+      <c r="M190" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N190" s="129"/>
-      <c r="O190" s="128" t="s">
+      <c r="N190" s="136"/>
+      <c r="O190" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P190" s="129"/>
-      <c r="Q190" s="128" t="s">
+      <c r="P190" s="136"/>
+      <c r="Q190" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R190" s="129"/>
-      <c r="S190" s="128" t="s">
+      <c r="R190" s="136"/>
+      <c r="S190" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T190" s="129"/>
-      <c r="U190" s="128" t="s">
+      <c r="T190" s="136"/>
+      <c r="U190" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V190" s="129"/>
+      <c r="V190" s="136"/>
       <c r="W190" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X190" s="118"/>
-      <c r="Y190" s="232" t="s">
+      <c r="X190" s="117"/>
+      <c r="Y190" s="147" t="s">
         <v>13</v>
       </c>
-      <c r="Z190" s="233"/>
+      <c r="Z190" s="148"/>
       <c r="AA190" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="AB190" s="134"/>
-      <c r="AC190" s="135"/>
+      <c r="AB190" s="139"/>
+      <c r="AC190" s="140"/>
       <c r="AD190" s="6" t="s">
         <v>16</v>
       </c>
@@ -30352,19 +30350,19 @@
       <c r="W191" s="14">
         <v>0</v>
       </c>
-      <c r="X191" s="123">
-        <v>0</v>
-      </c>
-      <c r="Y191" s="230">
+      <c r="X191" s="122">
+        <v>0</v>
+      </c>
+      <c r="Y191" s="141">
         <f>SUM(C191:W191)</f>
         <v>0</v>
       </c>
-      <c r="Z191" s="231"/>
+      <c r="Z191" s="142"/>
       <c r="AA191" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="AB191" s="193"/>
-      <c r="AC191" s="194"/>
+      <c r="AB191" s="143"/>
+      <c r="AC191" s="144"/>
       <c r="AD191" s="16">
         <f>X191</f>
         <v>0</v>
@@ -30374,58 +30372,58 @@
       <c r="AN191" s="2"/>
     </row>
     <row r="192" spans="2:40" s="2" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B192" s="235" t="s">
+      <c r="B192" s="137" t="s">
         <v>207</v>
       </c>
-      <c r="C192" s="128" t="s">
+      <c r="C192" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="D192" s="129"/>
-      <c r="E192" s="128" t="s">
+      <c r="D192" s="136"/>
+      <c r="E192" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="F192" s="129"/>
-      <c r="G192" s="128" t="s">
+      <c r="F192" s="136"/>
+      <c r="G192" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="H192" s="129"/>
-      <c r="I192" s="128" t="s">
+      <c r="H192" s="136"/>
+      <c r="I192" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="J192" s="129"/>
-      <c r="K192" s="128" t="s">
+      <c r="J192" s="136"/>
+      <c r="K192" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="L192" s="129"/>
-      <c r="M192" s="128" t="s">
+      <c r="L192" s="136"/>
+      <c r="M192" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="N192" s="129"/>
-      <c r="O192" s="128" t="s">
+      <c r="N192" s="136"/>
+      <c r="O192" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="P192" s="129"/>
-      <c r="Q192" s="128" t="s">
+      <c r="P192" s="136"/>
+      <c r="Q192" s="135" t="s">
         <v>9</v>
       </c>
-      <c r="R192" s="129"/>
-      <c r="S192" s="128" t="s">
+      <c r="R192" s="136"/>
+      <c r="S192" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="T192" s="129"/>
-      <c r="U192" s="128" t="s">
+      <c r="T192" s="136"/>
+      <c r="U192" s="135" t="s">
         <v>11</v>
       </c>
-      <c r="V192" s="129"/>
+      <c r="V192" s="136"/>
       <c r="W192" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="X192" s="118"/>
-      <c r="Y192" s="244" t="s">
+      <c r="X192" s="117"/>
+      <c r="Y192" s="132" t="s">
         <v>208</v>
       </c>
-      <c r="Z192" s="245"/>
-      <c r="AA192" s="246"/>
+      <c r="Z192" s="133"/>
+      <c r="AA192" s="134"/>
       <c r="AB192" s="101"/>
       <c r="AC192" s="101"/>
       <c r="AD192" s="102"/>
@@ -30435,61 +30433,39 @@
       <c r="AM192"/>
       <c r="AN192"/>
     </row>
-    <row r="193" spans="2:40" s="106" customFormat="1" ht="255" x14ac:dyDescent="3.65">
-      <c r="B193" s="236"/>
-      <c r="C193" s="237">
-        <v>8319500</v>
-      </c>
-      <c r="D193" s="238"/>
-      <c r="E193" s="237">
-        <v>10059900</v>
-      </c>
-      <c r="F193" s="238"/>
-      <c r="G193" s="237">
-        <v>10881150</v>
-      </c>
-      <c r="H193" s="238"/>
-      <c r="I193" s="237">
-        <v>11016520</v>
-      </c>
-      <c r="J193" s="238"/>
-      <c r="K193" s="237">
-        <v>5523300</v>
-      </c>
-      <c r="L193" s="238"/>
-      <c r="M193" s="237">
-        <v>8189250</v>
-      </c>
-      <c r="N193" s="238"/>
-      <c r="O193" s="237">
-        <v>5946240</v>
-      </c>
-      <c r="P193" s="238"/>
-      <c r="Q193" s="237">
-        <v>7096050</v>
-      </c>
-      <c r="R193" s="238"/>
-      <c r="S193" s="237">
-        <v>14518700</v>
-      </c>
-      <c r="T193" s="238"/>
-      <c r="U193" s="237">
-        <v>12829220</v>
-      </c>
-      <c r="V193" s="238"/>
-      <c r="W193" s="103">
-        <v>8463700</v>
-      </c>
-      <c r="X193" s="124"/>
-      <c r="Y193" s="239">
+    <row r="193" spans="2:40" s="105" customFormat="1" ht="255" x14ac:dyDescent="3.65">
+      <c r="B193" s="138"/>
+      <c r="C193" s="244"/>
+      <c r="D193" s="244"/>
+      <c r="E193" s="244"/>
+      <c r="F193" s="244"/>
+      <c r="G193" s="244"/>
+      <c r="H193" s="244"/>
+      <c r="I193" s="244"/>
+      <c r="J193" s="244"/>
+      <c r="K193" s="244"/>
+      <c r="L193" s="244"/>
+      <c r="M193" s="244"/>
+      <c r="N193" s="244"/>
+      <c r="O193" s="244"/>
+      <c r="P193" s="244"/>
+      <c r="Q193" s="244"/>
+      <c r="R193" s="244"/>
+      <c r="S193" s="244"/>
+      <c r="T193" s="244"/>
+      <c r="U193" s="244"/>
+      <c r="V193" s="244"/>
+      <c r="W193" s="245"/>
+      <c r="X193" s="123"/>
+      <c r="Y193" s="127">
         <f>SUM(C193:W193)</f>
-        <v>102843530</v>
-      </c>
-      <c r="Z193" s="240"/>
-      <c r="AA193" s="241"/>
-      <c r="AB193" s="104"/>
-      <c r="AC193" s="104"/>
-      <c r="AD193" s="105"/>
+        <v>0</v>
+      </c>
+      <c r="Z193" s="128"/>
+      <c r="AA193" s="129"/>
+      <c r="AB193" s="103"/>
+      <c r="AC193" s="103"/>
+      <c r="AD193" s="104"/>
       <c r="AE193" s="102"/>
       <c r="AF193" s="2"/>
       <c r="AG193" s="2"/>
@@ -30502,318 +30478,36 @@
       <c r="AN193" s="2"/>
     </row>
     <row r="195" spans="2:40" x14ac:dyDescent="2.35">
-      <c r="C195" s="242"/>
-      <c r="D195" s="242"/>
-      <c r="O195" s="243"/>
-      <c r="P195" s="243"/>
-      <c r="R195" s="108"/>
-      <c r="AA195" s="109"/>
+      <c r="C195" s="130"/>
+      <c r="D195" s="130"/>
+      <c r="O195" s="131"/>
+      <c r="P195" s="131"/>
+      <c r="R195" s="107"/>
+      <c r="AA195" s="108"/>
     </row>
     <row r="196" spans="2:40" x14ac:dyDescent="2.35">
-      <c r="AA196" s="109"/>
+      <c r="AA196" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="342">
-    <mergeCell ref="Y193:AA193"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="O195:P195"/>
-    <mergeCell ref="Y192:AA192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="E193:F193"/>
-    <mergeCell ref="G193:H193"/>
-    <mergeCell ref="I193:J193"/>
-    <mergeCell ref="K193:L193"/>
-    <mergeCell ref="M193:N193"/>
-    <mergeCell ref="O193:P193"/>
-    <mergeCell ref="Q193:R193"/>
-    <mergeCell ref="M192:N192"/>
-    <mergeCell ref="O192:P192"/>
-    <mergeCell ref="Q192:R192"/>
-    <mergeCell ref="S192:T192"/>
-    <mergeCell ref="U192:V192"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="E192:F192"/>
-    <mergeCell ref="G192:H192"/>
-    <mergeCell ref="I192:J192"/>
-    <mergeCell ref="K192:L192"/>
-    <mergeCell ref="Q190:R190"/>
-    <mergeCell ref="S190:T190"/>
-    <mergeCell ref="U190:V190"/>
-    <mergeCell ref="S193:T193"/>
-    <mergeCell ref="U193:V193"/>
-    <mergeCell ref="AB190:AC190"/>
-    <mergeCell ref="Y191:Z191"/>
-    <mergeCell ref="AB191:AC191"/>
-    <mergeCell ref="Y189:Z189"/>
-    <mergeCell ref="AB189:AC189"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="E190:F190"/>
-    <mergeCell ref="G190:H190"/>
-    <mergeCell ref="I190:J190"/>
-    <mergeCell ref="K190:L190"/>
-    <mergeCell ref="M190:N190"/>
-    <mergeCell ref="O190:P190"/>
-    <mergeCell ref="M189:N189"/>
-    <mergeCell ref="O189:P189"/>
-    <mergeCell ref="Q189:R189"/>
-    <mergeCell ref="S189:T189"/>
-    <mergeCell ref="U189:V189"/>
-    <mergeCell ref="Y190:Z190"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="E189:F189"/>
-    <mergeCell ref="G189:H189"/>
-    <mergeCell ref="I189:J189"/>
-    <mergeCell ref="K189:L189"/>
-    <mergeCell ref="Y187:Z187"/>
-    <mergeCell ref="AB187:AC187"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="E188:F188"/>
-    <mergeCell ref="G188:H188"/>
-    <mergeCell ref="I188:J188"/>
-    <mergeCell ref="K188:L188"/>
-    <mergeCell ref="M188:N188"/>
-    <mergeCell ref="O188:P188"/>
-    <mergeCell ref="S188:T188"/>
-    <mergeCell ref="U188:V188"/>
-    <mergeCell ref="Y188:Z188"/>
-    <mergeCell ref="AB188:AC188"/>
-    <mergeCell ref="Q188:R188"/>
-    <mergeCell ref="Y184:Z184"/>
-    <mergeCell ref="AB184:AC184"/>
-    <mergeCell ref="Y185:Z185"/>
-    <mergeCell ref="AB185:AC185"/>
-    <mergeCell ref="Y186:Z186"/>
-    <mergeCell ref="AB186:AC186"/>
-    <mergeCell ref="Y180:Z180"/>
-    <mergeCell ref="AB180:AC180"/>
-    <mergeCell ref="Y181:Z181"/>
-    <mergeCell ref="AB181:AC181"/>
-    <mergeCell ref="Y183:Z183"/>
-    <mergeCell ref="AB183:AC183"/>
-    <mergeCell ref="Y182:Z182"/>
-    <mergeCell ref="Y177:Z177"/>
-    <mergeCell ref="AB177:AC177"/>
-    <mergeCell ref="Y178:Z178"/>
-    <mergeCell ref="AB178:AC178"/>
-    <mergeCell ref="AG178:AI178"/>
-    <mergeCell ref="Y179:Z179"/>
-    <mergeCell ref="AB179:AC179"/>
-    <mergeCell ref="Y174:Z174"/>
-    <mergeCell ref="AB174:AC174"/>
-    <mergeCell ref="Y175:Z175"/>
-    <mergeCell ref="AB175:AC175"/>
-    <mergeCell ref="Y176:Z176"/>
-    <mergeCell ref="AB176:AC176"/>
-    <mergeCell ref="Y169:Z169"/>
-    <mergeCell ref="Y170:Z170"/>
-    <mergeCell ref="Y171:Z171"/>
-    <mergeCell ref="Y172:Z172"/>
-    <mergeCell ref="AB172:AC172"/>
-    <mergeCell ref="Y173:Z173"/>
-    <mergeCell ref="AB173:AC173"/>
-    <mergeCell ref="Y163:Z163"/>
-    <mergeCell ref="AB163:AC163"/>
-    <mergeCell ref="Y164:Z164"/>
-    <mergeCell ref="AB164:AC171"/>
-    <mergeCell ref="AF164:AJ167"/>
-    <mergeCell ref="Y165:Z165"/>
-    <mergeCell ref="Y166:Z166"/>
-    <mergeCell ref="Y167:Z167"/>
-    <mergeCell ref="Y168:Z168"/>
-    <mergeCell ref="AF168:AJ168"/>
-    <mergeCell ref="M163:N163"/>
-    <mergeCell ref="O163:P163"/>
-    <mergeCell ref="Q163:R163"/>
-    <mergeCell ref="S163:T163"/>
-    <mergeCell ref="U163:V163"/>
-    <mergeCell ref="AB157:AC162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="M155:N155"/>
-    <mergeCell ref="O155:P155"/>
-    <mergeCell ref="Q155:R155"/>
-    <mergeCell ref="S155:T155"/>
-    <mergeCell ref="U155:V155"/>
-    <mergeCell ref="W155:W156"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="G141:H141"/>
-    <mergeCell ref="I141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="AB142:AC152"/>
-    <mergeCell ref="AB153:AC153"/>
-    <mergeCell ref="B154:AD154"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="E155:F155"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="I155:J155"/>
-    <mergeCell ref="K155:L155"/>
-    <mergeCell ref="Y155:Y156"/>
-    <mergeCell ref="Z155:Z156"/>
-    <mergeCell ref="AA155:AA156"/>
-    <mergeCell ref="AB155:AC155"/>
-    <mergeCell ref="AB139:AC140"/>
-    <mergeCell ref="AF136:AJ136"/>
-    <mergeCell ref="AB137:AC137"/>
-    <mergeCell ref="AF137:AJ137"/>
-    <mergeCell ref="M141:N141"/>
-    <mergeCell ref="O141:P141"/>
-    <mergeCell ref="Q141:R141"/>
-    <mergeCell ref="S141:T141"/>
-    <mergeCell ref="U141:V141"/>
-    <mergeCell ref="AB141:AC141"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="G138:H138"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="M138:N138"/>
-    <mergeCell ref="AB107:AC111"/>
-    <mergeCell ref="AF111:AJ111"/>
-    <mergeCell ref="AB112:AC125"/>
-    <mergeCell ref="AF112:AJ117"/>
-    <mergeCell ref="O138:P138"/>
-    <mergeCell ref="Q138:R138"/>
-    <mergeCell ref="S138:T138"/>
-    <mergeCell ref="U138:V138"/>
-    <mergeCell ref="AB138:AC138"/>
-    <mergeCell ref="AK113:AL137"/>
-    <mergeCell ref="AF118:AJ118"/>
-    <mergeCell ref="AF119:AJ119"/>
-    <mergeCell ref="AB126:AC136"/>
-    <mergeCell ref="AF126:AJ127"/>
-    <mergeCell ref="AF129:AJ129"/>
-    <mergeCell ref="U105:V105"/>
-    <mergeCell ref="W105:W106"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="Z105:Z106"/>
-    <mergeCell ref="AA105:AA106"/>
-    <mergeCell ref="AB105:AC105"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="M105:N105"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="Q105:R105"/>
-    <mergeCell ref="S105:T105"/>
-    <mergeCell ref="AF98:AJ98"/>
-    <mergeCell ref="AF100:AJ100"/>
-    <mergeCell ref="AB103:AC103"/>
-    <mergeCell ref="AF103:AJ107"/>
-    <mergeCell ref="B104:AD104"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="U87:V87"/>
-    <mergeCell ref="AB87:AC87"/>
-    <mergeCell ref="AK87:AL112"/>
-    <mergeCell ref="AB88:AC88"/>
-    <mergeCell ref="AB90:AC90"/>
-    <mergeCell ref="AB91:AC91"/>
-    <mergeCell ref="AB92:AC92"/>
-    <mergeCell ref="AB93:AC102"/>
-    <mergeCell ref="AF93:AJ97"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="M87:N87"/>
-    <mergeCell ref="O87:P87"/>
-    <mergeCell ref="Q87:R87"/>
-    <mergeCell ref="S87:T87"/>
-    <mergeCell ref="AF78:AJ78"/>
-    <mergeCell ref="AF79:AJ79"/>
-    <mergeCell ref="AB80:AC81"/>
-    <mergeCell ref="AF80:AJ80"/>
-    <mergeCell ref="AK80:AL86"/>
-    <mergeCell ref="AF81:AJ81"/>
-    <mergeCell ref="AB82:AC82"/>
-    <mergeCell ref="AB83:AC83"/>
-    <mergeCell ref="AB84:AC84"/>
-    <mergeCell ref="AB85:AC85"/>
-    <mergeCell ref="AK71:AL78"/>
-    <mergeCell ref="AF72:AJ72"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AB74:AC75"/>
-    <mergeCell ref="AF74:AJ74"/>
-    <mergeCell ref="AF75:AJ75"/>
-    <mergeCell ref="AB76:AC77"/>
-    <mergeCell ref="AF76:AJ76"/>
-    <mergeCell ref="AF77:AJ77"/>
-    <mergeCell ref="AB78:AC79"/>
-    <mergeCell ref="AB86:AC86"/>
-    <mergeCell ref="Q70:R70"/>
-    <mergeCell ref="S70:T70"/>
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="AB70:AC70"/>
-    <mergeCell ref="AB71:AC72"/>
-    <mergeCell ref="AF71:AJ71"/>
-    <mergeCell ref="AB68:AC68"/>
-    <mergeCell ref="AB69:AC69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="M70:N70"/>
-    <mergeCell ref="O70:P70"/>
-    <mergeCell ref="AB62:AC67"/>
-    <mergeCell ref="AF63:AJ63"/>
-    <mergeCell ref="AF64:AJ64"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:R60"/>
-    <mergeCell ref="S60:T60"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="W60:W61"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="AC57:AC58"/>
-    <mergeCell ref="AB59:AC59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="Y60:Y61"/>
-    <mergeCell ref="Z60:Z61"/>
-    <mergeCell ref="AA60:AA61"/>
-    <mergeCell ref="AB60:AC60"/>
-    <mergeCell ref="AB48:AC51"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="AB42:AC47"/>
-    <mergeCell ref="AF42:AJ42"/>
-    <mergeCell ref="AF47:AJ47"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="AB40:AC40"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="AB33:AC34"/>
-    <mergeCell ref="AF33:AJ33"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AB24:AC25"/>
-    <mergeCell ref="AF24:AJ24"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AB36:AC37"/>
-    <mergeCell ref="AF36:AJ36"/>
-    <mergeCell ref="AF37:AJ37"/>
-    <mergeCell ref="AB38:AC38"/>
-    <mergeCell ref="AB39:AC39"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="B1:AD1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="X2:X3"/>
     <mergeCell ref="Z4:Z8"/>
     <mergeCell ref="AC4:AC8"/>
     <mergeCell ref="AF4:AJ6"/>
@@ -30838,24 +30532,306 @@
     <mergeCell ref="AB30:AC31"/>
     <mergeCell ref="AF30:AJ30"/>
     <mergeCell ref="AF31:AJ31"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="B1:AD1"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="AB33:AC34"/>
+    <mergeCell ref="AF33:AJ33"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AB24:AC25"/>
+    <mergeCell ref="AF24:AJ24"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AB36:AC37"/>
+    <mergeCell ref="AF36:AJ36"/>
+    <mergeCell ref="AF37:AJ37"/>
+    <mergeCell ref="AB38:AC38"/>
+    <mergeCell ref="AB39:AC39"/>
+    <mergeCell ref="AB48:AC51"/>
+    <mergeCell ref="AB54:AC54"/>
+    <mergeCell ref="AB42:AC47"/>
+    <mergeCell ref="AF42:AJ42"/>
+    <mergeCell ref="AF47:AJ47"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="AB40:AC40"/>
+    <mergeCell ref="AB55:AC55"/>
+    <mergeCell ref="AC57:AC58"/>
+    <mergeCell ref="AB59:AC59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="Y60:Y61"/>
+    <mergeCell ref="Z60:Z61"/>
+    <mergeCell ref="AA60:AA61"/>
+    <mergeCell ref="AB60:AC60"/>
+    <mergeCell ref="AB62:AC67"/>
+    <mergeCell ref="AF63:AJ63"/>
+    <mergeCell ref="AF64:AJ64"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="S60:T60"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="W60:W61"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="S70:T70"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="AB70:AC70"/>
+    <mergeCell ref="AB71:AC72"/>
+    <mergeCell ref="AF71:AJ71"/>
+    <mergeCell ref="AB68:AC68"/>
+    <mergeCell ref="AB69:AC69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="O70:P70"/>
+    <mergeCell ref="AF78:AJ78"/>
+    <mergeCell ref="AF79:AJ79"/>
+    <mergeCell ref="AB80:AC81"/>
+    <mergeCell ref="AF80:AJ80"/>
+    <mergeCell ref="AK80:AL86"/>
+    <mergeCell ref="AF81:AJ81"/>
+    <mergeCell ref="AB82:AC82"/>
+    <mergeCell ref="AB83:AC83"/>
+    <mergeCell ref="AB84:AC84"/>
+    <mergeCell ref="AB85:AC85"/>
+    <mergeCell ref="AK71:AL78"/>
+    <mergeCell ref="AF72:AJ72"/>
+    <mergeCell ref="AB73:AC73"/>
+    <mergeCell ref="AB74:AC75"/>
+    <mergeCell ref="AF74:AJ74"/>
+    <mergeCell ref="AF75:AJ75"/>
+    <mergeCell ref="AB76:AC77"/>
+    <mergeCell ref="AF76:AJ76"/>
+    <mergeCell ref="AF77:AJ77"/>
+    <mergeCell ref="AB78:AC79"/>
+    <mergeCell ref="AB86:AC86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="Q87:R87"/>
+    <mergeCell ref="S87:T87"/>
+    <mergeCell ref="U87:V87"/>
+    <mergeCell ref="AB87:AC87"/>
+    <mergeCell ref="AK87:AL112"/>
+    <mergeCell ref="AB88:AC88"/>
+    <mergeCell ref="AB90:AC90"/>
+    <mergeCell ref="AB91:AC91"/>
+    <mergeCell ref="AB92:AC92"/>
+    <mergeCell ref="AB93:AC102"/>
+    <mergeCell ref="AF93:AJ97"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="M105:N105"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="Q105:R105"/>
+    <mergeCell ref="S105:T105"/>
+    <mergeCell ref="AF98:AJ98"/>
+    <mergeCell ref="AF100:AJ100"/>
+    <mergeCell ref="AB103:AC103"/>
+    <mergeCell ref="AF103:AJ107"/>
+    <mergeCell ref="B104:AD104"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="AK113:AL137"/>
+    <mergeCell ref="AF118:AJ118"/>
+    <mergeCell ref="AF119:AJ119"/>
+    <mergeCell ref="AB126:AC136"/>
+    <mergeCell ref="AF126:AJ127"/>
+    <mergeCell ref="AF129:AJ129"/>
+    <mergeCell ref="U105:V105"/>
+    <mergeCell ref="W105:W106"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="Z105:Z106"/>
+    <mergeCell ref="AA105:AA106"/>
+    <mergeCell ref="AB105:AC105"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="M138:N138"/>
+    <mergeCell ref="AB107:AC111"/>
+    <mergeCell ref="AF111:AJ111"/>
+    <mergeCell ref="AB112:AC125"/>
+    <mergeCell ref="AF112:AJ117"/>
+    <mergeCell ref="O138:P138"/>
+    <mergeCell ref="Q138:R138"/>
+    <mergeCell ref="S138:T138"/>
+    <mergeCell ref="U138:V138"/>
+    <mergeCell ref="AB138:AC138"/>
+    <mergeCell ref="AB139:AC140"/>
+    <mergeCell ref="AF136:AJ136"/>
+    <mergeCell ref="AB137:AC137"/>
+    <mergeCell ref="AF137:AJ137"/>
+    <mergeCell ref="M141:N141"/>
+    <mergeCell ref="O141:P141"/>
+    <mergeCell ref="Q141:R141"/>
+    <mergeCell ref="S141:T141"/>
+    <mergeCell ref="U141:V141"/>
+    <mergeCell ref="AB141:AC141"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="I141:J141"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="AB142:AC152"/>
+    <mergeCell ref="AB153:AC153"/>
+    <mergeCell ref="B154:AD154"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="I155:J155"/>
+    <mergeCell ref="K155:L155"/>
+    <mergeCell ref="Y155:Y156"/>
+    <mergeCell ref="Z155:Z156"/>
+    <mergeCell ref="AA155:AA156"/>
+    <mergeCell ref="AB155:AC155"/>
+    <mergeCell ref="AB157:AC162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="M155:N155"/>
+    <mergeCell ref="O155:P155"/>
+    <mergeCell ref="Q155:R155"/>
+    <mergeCell ref="S155:T155"/>
+    <mergeCell ref="U155:V155"/>
+    <mergeCell ref="W155:W156"/>
+    <mergeCell ref="AF164:AJ167"/>
+    <mergeCell ref="Y165:Z165"/>
+    <mergeCell ref="Y166:Z166"/>
+    <mergeCell ref="Y167:Z167"/>
+    <mergeCell ref="Y168:Z168"/>
+    <mergeCell ref="AF168:AJ168"/>
+    <mergeCell ref="M163:N163"/>
+    <mergeCell ref="O163:P163"/>
+    <mergeCell ref="Q163:R163"/>
+    <mergeCell ref="S163:T163"/>
+    <mergeCell ref="U163:V163"/>
+    <mergeCell ref="Y169:Z169"/>
+    <mergeCell ref="Y170:Z170"/>
+    <mergeCell ref="Y171:Z171"/>
+    <mergeCell ref="Y172:Z172"/>
+    <mergeCell ref="AB172:AC172"/>
+    <mergeCell ref="Y173:Z173"/>
+    <mergeCell ref="AB173:AC173"/>
+    <mergeCell ref="Y163:Z163"/>
+    <mergeCell ref="AB163:AC163"/>
+    <mergeCell ref="Y164:Z164"/>
+    <mergeCell ref="AB164:AC171"/>
+    <mergeCell ref="Y177:Z177"/>
+    <mergeCell ref="AB177:AC177"/>
+    <mergeCell ref="Y178:Z178"/>
+    <mergeCell ref="AB178:AC178"/>
+    <mergeCell ref="AG178:AI178"/>
+    <mergeCell ref="Y179:Z179"/>
+    <mergeCell ref="AB179:AC179"/>
+    <mergeCell ref="Y174:Z174"/>
+    <mergeCell ref="AB174:AC174"/>
+    <mergeCell ref="Y175:Z175"/>
+    <mergeCell ref="AB175:AC175"/>
+    <mergeCell ref="Y176:Z176"/>
+    <mergeCell ref="AB176:AC176"/>
+    <mergeCell ref="Y184:Z184"/>
+    <mergeCell ref="AB184:AC184"/>
+    <mergeCell ref="Y185:Z185"/>
+    <mergeCell ref="AB185:AC185"/>
+    <mergeCell ref="Y186:Z186"/>
+    <mergeCell ref="AB186:AC186"/>
+    <mergeCell ref="Y180:Z180"/>
+    <mergeCell ref="AB180:AC180"/>
+    <mergeCell ref="Y181:Z181"/>
+    <mergeCell ref="AB181:AC181"/>
+    <mergeCell ref="Y183:Z183"/>
+    <mergeCell ref="AB183:AC183"/>
+    <mergeCell ref="Y182:Z182"/>
+    <mergeCell ref="Y187:Z187"/>
+    <mergeCell ref="AB187:AC187"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="E188:F188"/>
+    <mergeCell ref="G188:H188"/>
+    <mergeCell ref="I188:J188"/>
+    <mergeCell ref="K188:L188"/>
+    <mergeCell ref="M188:N188"/>
+    <mergeCell ref="O188:P188"/>
+    <mergeCell ref="S188:T188"/>
+    <mergeCell ref="U188:V188"/>
+    <mergeCell ref="Y188:Z188"/>
+    <mergeCell ref="AB188:AC188"/>
+    <mergeCell ref="Q188:R188"/>
+    <mergeCell ref="AB190:AC190"/>
+    <mergeCell ref="Y191:Z191"/>
+    <mergeCell ref="AB191:AC191"/>
+    <mergeCell ref="Y189:Z189"/>
+    <mergeCell ref="AB189:AC189"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="E190:F190"/>
+    <mergeCell ref="G190:H190"/>
+    <mergeCell ref="I190:J190"/>
+    <mergeCell ref="K190:L190"/>
+    <mergeCell ref="M190:N190"/>
+    <mergeCell ref="O190:P190"/>
+    <mergeCell ref="M189:N189"/>
+    <mergeCell ref="O189:P189"/>
+    <mergeCell ref="Q189:R189"/>
+    <mergeCell ref="S189:T189"/>
+    <mergeCell ref="U189:V189"/>
+    <mergeCell ref="Y190:Z190"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="E189:F189"/>
+    <mergeCell ref="G189:H189"/>
+    <mergeCell ref="I189:J189"/>
+    <mergeCell ref="K189:L189"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="G192:H192"/>
+    <mergeCell ref="I192:J192"/>
+    <mergeCell ref="K192:L192"/>
+    <mergeCell ref="Q190:R190"/>
+    <mergeCell ref="S190:T190"/>
+    <mergeCell ref="U190:V190"/>
+    <mergeCell ref="S193:T193"/>
+    <mergeCell ref="U193:V193"/>
+    <mergeCell ref="Y193:AA193"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="O195:P195"/>
+    <mergeCell ref="Y192:AA192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="E193:F193"/>
+    <mergeCell ref="G193:H193"/>
+    <mergeCell ref="I193:J193"/>
+    <mergeCell ref="K193:L193"/>
+    <mergeCell ref="M193:N193"/>
+    <mergeCell ref="O193:P193"/>
+    <mergeCell ref="Q193:R193"/>
+    <mergeCell ref="M192:N192"/>
+    <mergeCell ref="O192:P192"/>
+    <mergeCell ref="Q192:R192"/>
+    <mergeCell ref="S192:T192"/>
+    <mergeCell ref="U192:V192"/>
   </mergeCells>
   <pageMargins left="1.1023622047244095" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="10" orientation="landscape" verticalDpi="0" r:id="rId1"/>
@@ -30867,4 +30843,19 @@
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC23D8A-2430-4671-8DAB-D122AE188670}">
+  <dimension ref="D7"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>2342343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/base/base_0.xlsx
+++ b/base/base_0.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\ELIECER\scripts\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBC75576-1B93-4F4E-A94F-AD83089DDF5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BDA7A4-FE0B-4E2D-80ED-C96E7B07F96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_0" sheetId="2" r:id="rId1"/>
-    <sheet name="Hoja1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">base_0!$B$1:$AN$193</definedName>
@@ -1447,28 +1446,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1477,11 +1455,17 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1489,61 +1473,82 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1558,26 +1563,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1597,32 +1605,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1630,34 +1614,55 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1693,115 +1698,109 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -12906,103 +12905,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B1" s="169" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="170"/>
-      <c r="W1" s="170"/>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="170"/>
-      <c r="Z1" s="170"/>
-      <c r="AA1" s="170"/>
-      <c r="AB1" s="170"/>
-      <c r="AC1" s="170"/>
-      <c r="AD1" s="170"/>
+      <c r="B1" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+      <c r="W1" s="133"/>
+      <c r="X1" s="133"/>
+      <c r="Y1" s="133"/>
+      <c r="Z1" s="133"/>
+      <c r="AA1" s="133"/>
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="133"/>
+      <c r="AD1" s="133"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B2" s="167" t="s">
+      <c r="B2" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="135" t="s">
+      <c r="C2" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="136"/>
-      <c r="E2" s="135" t="s">
+      <c r="D2" s="129"/>
+      <c r="E2" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="136"/>
-      <c r="G2" s="135" t="s">
+      <c r="F2" s="129"/>
+      <c r="G2" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="136"/>
-      <c r="I2" s="135" t="s">
+      <c r="H2" s="129"/>
+      <c r="I2" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="136"/>
-      <c r="K2" s="135" t="s">
+      <c r="J2" s="129"/>
+      <c r="K2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="136"/>
-      <c r="M2" s="135" t="s">
+      <c r="L2" s="129"/>
+      <c r="M2" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="136"/>
-      <c r="O2" s="135" t="s">
+      <c r="N2" s="129"/>
+      <c r="O2" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="136"/>
-      <c r="Q2" s="135" t="s">
+      <c r="P2" s="129"/>
+      <c r="Q2" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="136"/>
-      <c r="S2" s="135" t="s">
+      <c r="R2" s="129"/>
+      <c r="S2" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="136"/>
-      <c r="U2" s="135" t="s">
+      <c r="T2" s="129"/>
+      <c r="U2" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="136"/>
-      <c r="W2" s="167" t="s">
+      <c r="V2" s="129"/>
+      <c r="W2" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="X2" s="242" t="s">
+      <c r="X2" s="136" t="s">
         <v>209</v>
       </c>
-      <c r="Y2" s="167" t="s">
+      <c r="Y2" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="167" t="s">
+      <c r="Z2" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="167" t="s">
+      <c r="AA2" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="139" t="s">
+      <c r="AB2" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="AC2" s="140"/>
+      <c r="AC2" s="135"/>
       <c r="AD2" s="6" t="s">
         <v>16</v>
       </c>
@@ -13016,7 +13015,7 @@
       <c r="AL2" s="8"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B3" s="168"/>
+      <c r="B3" s="131"/>
       <c r="C3" s="9" t="s">
         <v>17</v>
       </c>
@@ -13077,11 +13076,11 @@
       <c r="V3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="168"/>
-      <c r="X3" s="243"/>
-      <c r="Y3" s="168"/>
-      <c r="Z3" s="168"/>
-      <c r="AA3" s="168"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="137"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="11"/>
       <c r="AD3" s="6"/>
@@ -13168,14 +13167,14 @@
         <f>SUM(C4,E4,G4,I4,K4,,M4,O4,Q4,S4,U4,W4)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="226">
+      <c r="Z4" s="138">
         <f>SUM(D9,F9,H9,J9,L9,,N9,P9,R9,T9,V9)</f>
         <v>0</v>
       </c>
       <c r="AA4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AC4" s="155">
+      <c r="AC4" s="141">
         <f>SUM(Y4,AB5,AB6,AB7,AB8)</f>
         <v>0</v>
       </c>
@@ -13184,18 +13183,18 @@
         <v>0</v>
       </c>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="188" t="s">
+      <c r="AF4" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="AG4" s="189"/>
-      <c r="AH4" s="189"/>
-      <c r="AI4" s="189"/>
-      <c r="AJ4" s="190"/>
-      <c r="AK4" s="229">
+      <c r="AG4" s="145"/>
+      <c r="AH4" s="145"/>
+      <c r="AI4" s="145"/>
+      <c r="AJ4" s="146"/>
+      <c r="AK4" s="150">
         <f>SUM(AD4:AD59)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="230"/>
+      <c r="AL4" s="151"/>
     </row>
     <row r="5" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B5" s="13" t="s">
@@ -13251,7 +13250,7 @@
         <f>SUM(C5:W5)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="227"/>
+      <c r="Z5" s="139"/>
       <c r="AA5" s="13" t="s">
         <v>21</v>
       </c>
@@ -13259,19 +13258,19 @@
         <f>Y5*4</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="157"/>
+      <c r="AC5" s="142"/>
       <c r="AD5" s="16">
         <f>X5</f>
         <v>0</v>
       </c>
       <c r="AE5" s="17"/>
-      <c r="AF5" s="191"/>
-      <c r="AG5" s="192"/>
-      <c r="AH5" s="192"/>
-      <c r="AI5" s="192"/>
-      <c r="AJ5" s="193"/>
-      <c r="AK5" s="231"/>
-      <c r="AL5" s="230"/>
+      <c r="AF5" s="147"/>
+      <c r="AG5" s="148"/>
+      <c r="AH5" s="148"/>
+      <c r="AI5" s="148"/>
+      <c r="AJ5" s="149"/>
+      <c r="AK5" s="152"/>
+      <c r="AL5" s="151"/>
     </row>
     <row r="6" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B6" s="13" t="s">
@@ -13327,7 +13326,7 @@
         <f>SUM(C6:W6)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="227"/>
+      <c r="Z6" s="139"/>
       <c r="AA6" s="15" t="s">
         <v>23</v>
       </c>
@@ -13335,19 +13334,19 @@
         <f>Y6*8</f>
         <v>0</v>
       </c>
-      <c r="AC6" s="157"/>
+      <c r="AC6" s="142"/>
       <c r="AD6" s="16">
         <f t="shared" ref="AD6:AD7" si="0">X6</f>
         <v>0</v>
       </c>
       <c r="AE6" s="17"/>
-      <c r="AF6" s="191"/>
-      <c r="AG6" s="192"/>
-      <c r="AH6" s="192"/>
-      <c r="AI6" s="192"/>
-      <c r="AJ6" s="193"/>
-      <c r="AK6" s="231"/>
-      <c r="AL6" s="230"/>
+      <c r="AF6" s="147"/>
+      <c r="AG6" s="148"/>
+      <c r="AH6" s="148"/>
+      <c r="AI6" s="148"/>
+      <c r="AJ6" s="149"/>
+      <c r="AK6" s="152"/>
+      <c r="AL6" s="151"/>
     </row>
     <row r="7" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B7" s="13" t="s">
@@ -13403,7 +13402,7 @@
         <f>SUM(C7:W7)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="227"/>
+      <c r="Z7" s="139"/>
       <c r="AA7" s="15" t="s">
         <v>25</v>
       </c>
@@ -13411,22 +13410,22 @@
         <f>Y7*12</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="157"/>
+      <c r="AC7" s="142"/>
       <c r="AD7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE7" s="17"/>
-      <c r="AF7" s="166">
+      <c r="AF7" s="153">
         <f>SUM(AD4:AD8)</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="164"/>
-      <c r="AH7" s="164"/>
-      <c r="AI7" s="164"/>
-      <c r="AJ7" s="165"/>
-      <c r="AK7" s="231"/>
-      <c r="AL7" s="230"/>
+      <c r="AG7" s="154"/>
+      <c r="AH7" s="154"/>
+      <c r="AI7" s="154"/>
+      <c r="AJ7" s="155"/>
+      <c r="AK7" s="152"/>
+      <c r="AL7" s="151"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B8" s="13" t="s">
@@ -13482,7 +13481,7 @@
         <f>SUM(C8:W8)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="228"/>
+      <c r="Z8" s="140"/>
       <c r="AA8" s="15" t="s">
         <v>27</v>
       </c>
@@ -13490,7 +13489,7 @@
         <f>Y8*16</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="159"/>
+      <c r="AC8" s="143"/>
       <c r="AD8" s="16">
         <f>X8</f>
         <v>0</v>
@@ -13501,8 +13500,8 @@
       <c r="AH8" s="27"/>
       <c r="AI8" s="27"/>
       <c r="AJ8" s="28"/>
-      <c r="AK8" s="231"/>
-      <c r="AL8" s="230"/>
+      <c r="AK8" s="152"/>
+      <c r="AL8" s="151"/>
       <c r="AM8" s="29"/>
       <c r="AN8" s="29"/>
     </row>
@@ -13608,8 +13607,8 @@
       <c r="AH9" s="35"/>
       <c r="AI9" s="35"/>
       <c r="AJ9" s="36"/>
-      <c r="AK9" s="231"/>
-      <c r="AL9" s="230"/>
+      <c r="AK9" s="152"/>
+      <c r="AL9" s="151"/>
       <c r="AM9" s="29"/>
       <c r="AN9" s="29"/>
     </row>
@@ -13694,11 +13693,11 @@
       <c r="AA10" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="AB10" s="232">
+      <c r="AB10" s="156">
         <f>SUM(Y10:Y13)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="219">
+      <c r="AC10" s="159">
         <f>SUM(AB10,AB15)</f>
         <v>0</v>
       </c>
@@ -13707,15 +13706,15 @@
         <v>0</v>
       </c>
       <c r="AE10" s="17"/>
-      <c r="AF10" s="160" t="s">
+      <c r="AF10" s="162" t="s">
         <v>29</v>
       </c>
-      <c r="AG10" s="161"/>
-      <c r="AH10" s="161"/>
-      <c r="AI10" s="161"/>
-      <c r="AJ10" s="162"/>
-      <c r="AK10" s="231"/>
-      <c r="AL10" s="230"/>
+      <c r="AG10" s="163"/>
+      <c r="AH10" s="163"/>
+      <c r="AI10" s="163"/>
+      <c r="AJ10" s="164"/>
+      <c r="AK10" s="152"/>
+      <c r="AL10" s="151"/>
       <c r="AM10" s="12"/>
       <c r="AN10" s="12"/>
     </row>
@@ -13803,20 +13802,20 @@
       <c r="AA11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AB11" s="233"/>
-      <c r="AC11" s="235"/>
+      <c r="AB11" s="157"/>
+      <c r="AC11" s="160"/>
       <c r="AD11" s="16">
         <f t="shared" ref="AD11:AD13" si="1">X11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="17"/>
-      <c r="AF11" s="163"/>
-      <c r="AG11" s="164"/>
-      <c r="AH11" s="164"/>
-      <c r="AI11" s="164"/>
-      <c r="AJ11" s="165"/>
-      <c r="AK11" s="231"/>
-      <c r="AL11" s="230"/>
+      <c r="AF11" s="165"/>
+      <c r="AG11" s="154"/>
+      <c r="AH11" s="154"/>
+      <c r="AI11" s="154"/>
+      <c r="AJ11" s="155"/>
+      <c r="AK11" s="152"/>
+      <c r="AL11" s="151"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B12" s="13" t="s">
@@ -13899,20 +13898,20 @@
       <c r="AA12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AB12" s="233"/>
-      <c r="AC12" s="235"/>
+      <c r="AB12" s="157"/>
+      <c r="AC12" s="160"/>
       <c r="AD12" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE12" s="17"/>
-      <c r="AF12" s="163"/>
-      <c r="AG12" s="164"/>
-      <c r="AH12" s="164"/>
-      <c r="AI12" s="164"/>
-      <c r="AJ12" s="165"/>
-      <c r="AK12" s="231"/>
-      <c r="AL12" s="230"/>
+      <c r="AF12" s="165"/>
+      <c r="AG12" s="154"/>
+      <c r="AH12" s="154"/>
+      <c r="AI12" s="154"/>
+      <c r="AJ12" s="155"/>
+      <c r="AK12" s="152"/>
+      <c r="AL12" s="151"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B13" s="13" t="s">
@@ -13995,20 +13994,20 @@
       <c r="AA13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AB13" s="234"/>
-      <c r="AC13" s="235"/>
+      <c r="AB13" s="158"/>
+      <c r="AC13" s="160"/>
       <c r="AD13" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE13" s="17"/>
-      <c r="AF13" s="163"/>
-      <c r="AG13" s="164"/>
-      <c r="AH13" s="164"/>
-      <c r="AI13" s="164"/>
-      <c r="AJ13" s="165"/>
-      <c r="AK13" s="231"/>
-      <c r="AL13" s="230"/>
+      <c r="AF13" s="165"/>
+      <c r="AG13" s="154"/>
+      <c r="AH13" s="154"/>
+      <c r="AI13" s="154"/>
+      <c r="AJ13" s="155"/>
+      <c r="AK13" s="152"/>
+      <c r="AL13" s="151"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B14" s="13"/>
@@ -14101,16 +14100,16 @@
       <c r="Z14" s="41"/>
       <c r="AA14" s="42"/>
       <c r="AB14" s="13"/>
-      <c r="AC14" s="235"/>
+      <c r="AC14" s="160"/>
       <c r="AD14" s="33"/>
       <c r="AE14" s="17"/>
-      <c r="AF14" s="163"/>
-      <c r="AG14" s="164"/>
-      <c r="AH14" s="164"/>
-      <c r="AI14" s="164"/>
-      <c r="AJ14" s="165"/>
-      <c r="AK14" s="231"/>
-      <c r="AL14" s="230"/>
+      <c r="AF14" s="165"/>
+      <c r="AG14" s="154"/>
+      <c r="AH14" s="154"/>
+      <c r="AI14" s="154"/>
+      <c r="AJ14" s="155"/>
+      <c r="AK14" s="152"/>
+      <c r="AL14" s="151"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B15" s="13" t="s">
@@ -14193,26 +14192,26 @@
       <c r="AA15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AB15" s="232">
+      <c r="AB15" s="156">
         <f>SUM(Y15:Y18)</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="235"/>
+      <c r="AC15" s="160"/>
       <c r="AD15" s="16">
         <f>X15</f>
         <v>0</v>
       </c>
       <c r="AE15" s="17"/>
-      <c r="AF15" s="166">
+      <c r="AF15" s="153">
         <f>SUM(AD10:AD20)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="164"/>
-      <c r="AH15" s="164"/>
-      <c r="AI15" s="164"/>
-      <c r="AJ15" s="165"/>
-      <c r="AK15" s="231"/>
-      <c r="AL15" s="230"/>
+      <c r="AG15" s="154"/>
+      <c r="AH15" s="154"/>
+      <c r="AI15" s="154"/>
+      <c r="AJ15" s="155"/>
+      <c r="AK15" s="152"/>
+      <c r="AL15" s="151"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B16" s="13" t="s">
@@ -14295,8 +14294,8 @@
       <c r="AA16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AB16" s="233"/>
-      <c r="AC16" s="235"/>
+      <c r="AB16" s="157"/>
+      <c r="AC16" s="160"/>
       <c r="AD16" s="16">
         <f t="shared" ref="AD16:AD20" si="5">X16</f>
         <v>0</v>
@@ -14307,8 +14306,8 @@
       <c r="AH16" s="27"/>
       <c r="AI16" s="27"/>
       <c r="AJ16" s="28"/>
-      <c r="AK16" s="231"/>
-      <c r="AL16" s="230"/>
+      <c r="AK16" s="152"/>
+      <c r="AL16" s="151"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B17" s="13" t="s">
@@ -14391,8 +14390,8 @@
       <c r="AA17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AB17" s="233"/>
-      <c r="AC17" s="235"/>
+      <c r="AB17" s="157"/>
+      <c r="AC17" s="160"/>
       <c r="AD17" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14403,8 +14402,8 @@
       <c r="AH17" s="27"/>
       <c r="AI17" s="27"/>
       <c r="AJ17" s="28"/>
-      <c r="AK17" s="231"/>
-      <c r="AL17" s="230"/>
+      <c r="AK17" s="152"/>
+      <c r="AL17" s="151"/>
     </row>
     <row r="18" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B18" s="13" t="s">
@@ -14487,8 +14486,8 @@
       <c r="AA18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AB18" s="233"/>
-      <c r="AC18" s="235"/>
+      <c r="AB18" s="157"/>
+      <c r="AC18" s="160"/>
       <c r="AD18" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14499,8 +14498,8 @@
       <c r="AH18" s="27"/>
       <c r="AI18" s="27"/>
       <c r="AJ18" s="28"/>
-      <c r="AK18" s="231"/>
-      <c r="AL18" s="230"/>
+      <c r="AK18" s="152"/>
+      <c r="AL18" s="151"/>
     </row>
     <row r="19" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B19" s="13" t="s">
@@ -14583,8 +14582,8 @@
       <c r="AA19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AB19" s="233"/>
-      <c r="AC19" s="235"/>
+      <c r="AB19" s="157"/>
+      <c r="AC19" s="160"/>
       <c r="AD19" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14595,8 +14594,8 @@
       <c r="AH19" s="27"/>
       <c r="AI19" s="27"/>
       <c r="AJ19" s="28"/>
-      <c r="AK19" s="231"/>
-      <c r="AL19" s="230"/>
+      <c r="AK19" s="152"/>
+      <c r="AL19" s="151"/>
     </row>
     <row r="20" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B20" s="13" t="s">
@@ -14679,8 +14678,8 @@
       <c r="AA20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AB20" s="234"/>
-      <c r="AC20" s="220"/>
+      <c r="AB20" s="158"/>
+      <c r="AC20" s="161"/>
       <c r="AD20" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14691,8 +14690,8 @@
       <c r="AH20" s="27"/>
       <c r="AI20" s="27"/>
       <c r="AJ20" s="28"/>
-      <c r="AK20" s="231"/>
-      <c r="AL20" s="230"/>
+      <c r="AK20" s="152"/>
+      <c r="AL20" s="151"/>
     </row>
     <row r="21" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B21" s="13"/>
@@ -14784,19 +14783,19 @@
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
       <c r="AA21" s="42"/>
-      <c r="AB21" s="186"/>
-      <c r="AC21" s="187"/>
+      <c r="AB21" s="181"/>
+      <c r="AC21" s="182"/>
       <c r="AD21" s="33"/>
       <c r="AE21" s="17"/>
-      <c r="AF21" s="160" t="s">
+      <c r="AF21" s="162" t="s">
         <v>39</v>
       </c>
-      <c r="AG21" s="161"/>
-      <c r="AH21" s="161"/>
-      <c r="AI21" s="161"/>
-      <c r="AJ21" s="162"/>
-      <c r="AK21" s="231"/>
-      <c r="AL21" s="230"/>
+      <c r="AG21" s="163"/>
+      <c r="AH21" s="163"/>
+      <c r="AI21" s="163"/>
+      <c r="AJ21" s="164"/>
+      <c r="AK21" s="152"/>
+      <c r="AL21" s="151"/>
     </row>
     <row r="22" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B22" s="13" t="s">
@@ -14879,21 +14878,21 @@
       <c r="AA22" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AB22" s="221"/>
-      <c r="AC22" s="222"/>
+      <c r="AB22" s="183"/>
+      <c r="AC22" s="184"/>
       <c r="AD22" s="16">
         <f>X22</f>
         <v>0</v>
       </c>
       <c r="AE22" s="17"/>
-      <c r="AF22" s="239">
+      <c r="AF22" s="185">
         <f>SUM(AD22:AE22)</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="240"/>
-      <c r="AH22" s="240"/>
-      <c r="AI22" s="240"/>
-      <c r="AJ22" s="241"/>
+      <c r="AG22" s="186"/>
+      <c r="AH22" s="186"/>
+      <c r="AI22" s="186"/>
+      <c r="AJ22" s="187"/>
       <c r="AK22" s="22"/>
       <c r="AL22" s="18"/>
     </row>
@@ -14987,8 +14986,8 @@
       <c r="Y23" s="14"/>
       <c r="Z23" s="14"/>
       <c r="AA23" s="42"/>
-      <c r="AB23" s="149"/>
-      <c r="AC23" s="150"/>
+      <c r="AB23" s="172"/>
+      <c r="AC23" s="173"/>
       <c r="AD23" s="16">
         <f t="shared" ref="AD23:AD39" si="8">X23</f>
         <v>0</v>
@@ -15086,27 +15085,27 @@
       <c r="AA24" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AB24" s="171">
+      <c r="AB24" s="174">
         <f>SUM(Y24:Y25)</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="172"/>
+      <c r="AC24" s="175"/>
       <c r="AD24" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE24" s="17"/>
-      <c r="AF24" s="175" t="s">
+      <c r="AF24" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="AG24" s="176"/>
-      <c r="AH24" s="176"/>
-      <c r="AI24" s="176"/>
-      <c r="AJ24" s="223"/>
-      <c r="AK24" s="236" t="s">
+      <c r="AG24" s="179"/>
+      <c r="AH24" s="179"/>
+      <c r="AI24" s="179"/>
+      <c r="AJ24" s="180"/>
+      <c r="AK24" s="166" t="s">
         <v>43</v>
       </c>
-      <c r="AL24" s="237"/>
+      <c r="AL24" s="167"/>
     </row>
     <row r="25" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A25" s="12">
@@ -15192,23 +15191,23 @@
       <c r="AA25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AB25" s="173"/>
-      <c r="AC25" s="174"/>
+      <c r="AB25" s="176"/>
+      <c r="AC25" s="177"/>
       <c r="AD25" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE25" s="17"/>
-      <c r="AF25" s="197">
+      <c r="AF25" s="169">
         <f>SUM(AD24:AD25)</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="224"/>
-      <c r="AH25" s="224"/>
-      <c r="AI25" s="224"/>
-      <c r="AJ25" s="225"/>
-      <c r="AK25" s="236"/>
-      <c r="AL25" s="237"/>
+      <c r="AG25" s="170"/>
+      <c r="AH25" s="170"/>
+      <c r="AI25" s="170"/>
+      <c r="AJ25" s="171"/>
+      <c r="AK25" s="166"/>
+      <c r="AL25" s="167"/>
     </row>
     <row r="26" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B26" s="13"/>
@@ -15300,8 +15299,8 @@
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
       <c r="AA26" s="13"/>
-      <c r="AB26" s="149"/>
-      <c r="AC26" s="150"/>
+      <c r="AB26" s="172"/>
+      <c r="AC26" s="173"/>
       <c r="AD26" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15312,8 +15311,8 @@
       <c r="AH26" s="45"/>
       <c r="AI26" s="45"/>
       <c r="AJ26" s="46"/>
-      <c r="AK26" s="236"/>
-      <c r="AL26" s="237"/>
+      <c r="AK26" s="166"/>
+      <c r="AL26" s="167"/>
     </row>
     <row r="27" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A27" s="12">
@@ -15399,25 +15398,25 @@
       <c r="AA27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AB27" s="171">
+      <c r="AB27" s="174">
         <f>SUM(Y26:Y28)</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="172"/>
+      <c r="AC27" s="175"/>
       <c r="AD27" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE27" s="17"/>
-      <c r="AF27" s="175" t="s">
+      <c r="AF27" s="178" t="s">
         <v>46</v>
       </c>
-      <c r="AG27" s="176"/>
-      <c r="AH27" s="176"/>
-      <c r="AI27" s="176"/>
-      <c r="AJ27" s="223"/>
-      <c r="AK27" s="236"/>
-      <c r="AL27" s="237"/>
+      <c r="AG27" s="179"/>
+      <c r="AH27" s="179"/>
+      <c r="AI27" s="179"/>
+      <c r="AJ27" s="180"/>
+      <c r="AK27" s="166"/>
+      <c r="AL27" s="167"/>
     </row>
     <row r="28" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A28" s="12">
@@ -15503,23 +15502,23 @@
       <c r="AA28" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AB28" s="173"/>
-      <c r="AC28" s="174"/>
+      <c r="AB28" s="176"/>
+      <c r="AC28" s="177"/>
       <c r="AD28" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE28" s="17"/>
-      <c r="AF28" s="197">
+      <c r="AF28" s="169">
         <f>+AD27+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="224"/>
-      <c r="AH28" s="224"/>
-      <c r="AI28" s="224"/>
-      <c r="AJ28" s="225"/>
-      <c r="AK28" s="236"/>
-      <c r="AL28" s="237"/>
+      <c r="AG28" s="170"/>
+      <c r="AH28" s="170"/>
+      <c r="AI28" s="170"/>
+      <c r="AJ28" s="171"/>
+      <c r="AK28" s="166"/>
+      <c r="AL28" s="167"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B29" s="13"/>
@@ -15611,8 +15610,8 @@
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
       <c r="AA29" s="13"/>
-      <c r="AB29" s="149"/>
-      <c r="AC29" s="150"/>
+      <c r="AB29" s="172"/>
+      <c r="AC29" s="173"/>
       <c r="AD29" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15623,8 +15622,8 @@
       <c r="AH29" s="45"/>
       <c r="AI29" s="45"/>
       <c r="AJ29" s="45"/>
-      <c r="AK29" s="236"/>
-      <c r="AL29" s="237"/>
+      <c r="AK29" s="166"/>
+      <c r="AL29" s="167"/>
     </row>
     <row r="30" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A30" s="12">
@@ -15710,25 +15709,25 @@
       <c r="AA30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AB30" s="171">
+      <c r="AB30" s="174">
         <f>SUM(Y29:Y31)</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="172"/>
+      <c r="AC30" s="175"/>
       <c r="AD30" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE30" s="17"/>
-      <c r="AF30" s="175" t="s">
+      <c r="AF30" s="178" t="s">
         <v>49</v>
       </c>
-      <c r="AG30" s="176"/>
-      <c r="AH30" s="176"/>
-      <c r="AI30" s="176"/>
-      <c r="AJ30" s="176"/>
-      <c r="AK30" s="236"/>
-      <c r="AL30" s="237"/>
+      <c r="AG30" s="179"/>
+      <c r="AH30" s="179"/>
+      <c r="AI30" s="179"/>
+      <c r="AJ30" s="179"/>
+      <c r="AK30" s="166"/>
+      <c r="AL30" s="167"/>
     </row>
     <row r="31" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A31" s="12">
@@ -15814,23 +15813,23 @@
       <c r="AA31" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AB31" s="173"/>
-      <c r="AC31" s="174"/>
+      <c r="AB31" s="176"/>
+      <c r="AC31" s="177"/>
       <c r="AD31" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE31" s="17"/>
-      <c r="AF31" s="197">
+      <c r="AF31" s="169">
         <f>+AD30+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG31" s="224"/>
-      <c r="AH31" s="224"/>
-      <c r="AI31" s="224"/>
-      <c r="AJ31" s="225"/>
-      <c r="AK31" s="236"/>
-      <c r="AL31" s="237"/>
+      <c r="AG31" s="170"/>
+      <c r="AH31" s="170"/>
+      <c r="AI31" s="170"/>
+      <c r="AJ31" s="171"/>
+      <c r="AK31" s="166"/>
+      <c r="AL31" s="167"/>
     </row>
     <row r="32" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B32" s="13"/>
@@ -15922,8 +15921,8 @@
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
       <c r="AA32" s="13"/>
-      <c r="AB32" s="149"/>
-      <c r="AC32" s="150"/>
+      <c r="AB32" s="172"/>
+      <c r="AC32" s="173"/>
       <c r="AD32" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15934,8 +15933,8 @@
       <c r="AH32" s="45"/>
       <c r="AI32" s="45"/>
       <c r="AJ32" s="45"/>
-      <c r="AK32" s="236"/>
-      <c r="AL32" s="237"/>
+      <c r="AK32" s="166"/>
+      <c r="AL32" s="167"/>
     </row>
     <row r="33" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A33" s="12">
@@ -16021,25 +16020,25 @@
       <c r="AA33" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AB33" s="171">
+      <c r="AB33" s="174">
         <f>SUM(Y32:Y34)</f>
         <v>0</v>
       </c>
-      <c r="AC33" s="172"/>
+      <c r="AC33" s="175"/>
       <c r="AD33" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE33" s="17"/>
-      <c r="AF33" s="175" t="s">
+      <c r="AF33" s="178" t="s">
         <v>52</v>
       </c>
-      <c r="AG33" s="176"/>
-      <c r="AH33" s="176"/>
-      <c r="AI33" s="176"/>
-      <c r="AJ33" s="176"/>
-      <c r="AK33" s="236"/>
-      <c r="AL33" s="237"/>
+      <c r="AG33" s="179"/>
+      <c r="AH33" s="179"/>
+      <c r="AI33" s="179"/>
+      <c r="AJ33" s="179"/>
+      <c r="AK33" s="166"/>
+      <c r="AL33" s="167"/>
     </row>
     <row r="34" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A34" s="12">
@@ -16125,23 +16124,23 @@
       <c r="AA34" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AB34" s="173"/>
-      <c r="AC34" s="174"/>
+      <c r="AB34" s="176"/>
+      <c r="AC34" s="177"/>
       <c r="AD34" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE34" s="17"/>
-      <c r="AF34" s="197">
+      <c r="AF34" s="169">
         <f>+AD33+AD34</f>
         <v>0</v>
       </c>
-      <c r="AG34" s="224"/>
-      <c r="AH34" s="224"/>
-      <c r="AI34" s="224"/>
-      <c r="AJ34" s="225"/>
-      <c r="AK34" s="236"/>
-      <c r="AL34" s="237"/>
+      <c r="AG34" s="170"/>
+      <c r="AH34" s="170"/>
+      <c r="AI34" s="170"/>
+      <c r="AJ34" s="171"/>
+      <c r="AK34" s="166"/>
+      <c r="AL34" s="167"/>
     </row>
     <row r="35" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B35" s="13"/>
@@ -16233,8 +16232,8 @@
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
       <c r="AA35" s="13"/>
-      <c r="AB35" s="149"/>
-      <c r="AC35" s="150"/>
+      <c r="AB35" s="172"/>
+      <c r="AC35" s="173"/>
       <c r="AD35" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16245,8 +16244,8 @@
       <c r="AH35" s="45"/>
       <c r="AI35" s="45"/>
       <c r="AJ35" s="45"/>
-      <c r="AK35" s="236"/>
-      <c r="AL35" s="237"/>
+      <c r="AK35" s="166"/>
+      <c r="AL35" s="167"/>
     </row>
     <row r="36" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B36" s="13" t="s">
@@ -16329,25 +16328,25 @@
       <c r="AA36" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="AB36" s="171">
+      <c r="AB36" s="174">
         <f>SUM(Y35:Y37)</f>
         <v>0</v>
       </c>
-      <c r="AC36" s="172"/>
+      <c r="AC36" s="175"/>
       <c r="AD36" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE36" s="17"/>
-      <c r="AF36" s="175" t="s">
+      <c r="AF36" s="178" t="s">
         <v>55</v>
       </c>
-      <c r="AG36" s="176"/>
-      <c r="AH36" s="176"/>
-      <c r="AI36" s="176"/>
-      <c r="AJ36" s="176"/>
-      <c r="AK36" s="236"/>
-      <c r="AL36" s="237"/>
+      <c r="AG36" s="179"/>
+      <c r="AH36" s="179"/>
+      <c r="AI36" s="179"/>
+      <c r="AJ36" s="179"/>
+      <c r="AK36" s="166"/>
+      <c r="AL36" s="167"/>
     </row>
     <row r="37" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B37" s="13" t="s">
@@ -16430,23 +16429,23 @@
       <c r="AA37" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="AB37" s="173"/>
-      <c r="AC37" s="174"/>
+      <c r="AB37" s="176"/>
+      <c r="AC37" s="177"/>
       <c r="AD37" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE37" s="17"/>
-      <c r="AF37" s="197">
+      <c r="AF37" s="169">
         <f>+AD36+AD37</f>
         <v>0</v>
       </c>
-      <c r="AG37" s="224"/>
-      <c r="AH37" s="224"/>
-      <c r="AI37" s="224"/>
-      <c r="AJ37" s="225"/>
-      <c r="AK37" s="236"/>
-      <c r="AL37" s="237"/>
+      <c r="AG37" s="170"/>
+      <c r="AH37" s="170"/>
+      <c r="AI37" s="170"/>
+      <c r="AJ37" s="171"/>
+      <c r="AK37" s="166"/>
+      <c r="AL37" s="167"/>
       <c r="AM37" s="47"/>
       <c r="AN37" s="47"/>
     </row>
@@ -16540,8 +16539,8 @@
       <c r="Y38" s="14"/>
       <c r="Z38" s="14"/>
       <c r="AA38" s="13"/>
-      <c r="AB38" s="149"/>
-      <c r="AC38" s="150"/>
+      <c r="AB38" s="172"/>
+      <c r="AC38" s="173"/>
       <c r="AD38" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16552,8 +16551,8 @@
       <c r="AH38" s="45"/>
       <c r="AI38" s="45"/>
       <c r="AJ38" s="45"/>
-      <c r="AK38" s="236"/>
-      <c r="AL38" s="237"/>
+      <c r="AK38" s="166"/>
+      <c r="AL38" s="167"/>
       <c r="AM38" s="47"/>
       <c r="AN38" s="47"/>
     </row>
@@ -16638,8 +16637,8 @@
       <c r="AA39" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="AB39" s="149"/>
-      <c r="AC39" s="150"/>
+      <c r="AB39" s="172"/>
+      <c r="AC39" s="173"/>
       <c r="AD39" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16650,8 +16649,8 @@
       <c r="AH39" s="45"/>
       <c r="AI39" s="45"/>
       <c r="AJ39" s="45"/>
-      <c r="AK39" s="236"/>
-      <c r="AL39" s="237"/>
+      <c r="AK39" s="166"/>
+      <c r="AL39" s="167"/>
       <c r="AM39" s="47"/>
       <c r="AN39" s="47"/>
     </row>
@@ -16659,46 +16658,46 @@
       <c r="B40" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="135" t="s">
+      <c r="C40" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="136"/>
-      <c r="E40" s="135" t="s">
+      <c r="D40" s="129"/>
+      <c r="E40" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F40" s="136"/>
-      <c r="G40" s="135" t="s">
+      <c r="F40" s="129"/>
+      <c r="G40" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H40" s="136"/>
-      <c r="I40" s="135" t="s">
+      <c r="H40" s="129"/>
+      <c r="I40" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J40" s="136"/>
-      <c r="K40" s="135" t="s">
+      <c r="J40" s="129"/>
+      <c r="K40" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L40" s="136"/>
-      <c r="M40" s="135" t="s">
+      <c r="L40" s="129"/>
+      <c r="M40" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N40" s="136"/>
-      <c r="O40" s="135" t="s">
+      <c r="N40" s="129"/>
+      <c r="O40" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P40" s="136"/>
-      <c r="Q40" s="135" t="s">
+      <c r="P40" s="129"/>
+      <c r="Q40" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R40" s="136"/>
-      <c r="S40" s="135" t="s">
+      <c r="R40" s="129"/>
+      <c r="S40" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T40" s="136"/>
-      <c r="U40" s="135" t="s">
+      <c r="T40" s="129"/>
+      <c r="U40" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V40" s="136"/>
+      <c r="V40" s="129"/>
       <c r="W40" s="5" t="s">
         <v>12</v>
       </c>
@@ -16712,8 +16711,8 @@
       <c r="AA40" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="AB40" s="139"/>
-      <c r="AC40" s="140"/>
+      <c r="AB40" s="134"/>
+      <c r="AC40" s="135"/>
       <c r="AD40" s="6">
         <v>0</v>
       </c>
@@ -16723,8 +16722,8 @@
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
-      <c r="AK40" s="236"/>
-      <c r="AL40" s="237"/>
+      <c r="AK40" s="166"/>
+      <c r="AL40" s="167"/>
       <c r="AM40" s="12"/>
       <c r="AN40" s="12"/>
     </row>
@@ -16822,8 +16821,8 @@
       <c r="AH41" s="52"/>
       <c r="AI41" s="52"/>
       <c r="AJ41" s="52"/>
-      <c r="AK41" s="236"/>
-      <c r="AL41" s="237"/>
+      <c r="AK41" s="166"/>
+      <c r="AL41" s="167"/>
     </row>
     <row r="42" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A42" s="12"/>
@@ -16907,25 +16906,25 @@
       <c r="AA42" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AB42" s="211">
+      <c r="AB42" s="188">
         <f>SUM(Y40:Y53)</f>
         <v>0</v>
       </c>
-      <c r="AC42" s="212"/>
+      <c r="AC42" s="189"/>
       <c r="AD42" s="16">
         <f t="shared" ref="AD42:AD59" si="16">X42</f>
         <v>0</v>
       </c>
       <c r="AE42" s="17"/>
-      <c r="AF42" s="175" t="s">
+      <c r="AF42" s="178" t="s">
         <v>61</v>
       </c>
-      <c r="AG42" s="176"/>
-      <c r="AH42" s="176"/>
-      <c r="AI42" s="176"/>
-      <c r="AJ42" s="223"/>
-      <c r="AK42" s="238"/>
-      <c r="AL42" s="237"/>
+      <c r="AG42" s="179"/>
+      <c r="AH42" s="179"/>
+      <c r="AI42" s="179"/>
+      <c r="AJ42" s="180"/>
+      <c r="AK42" s="168"/>
+      <c r="AL42" s="167"/>
     </row>
     <row r="43" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A43" s="12"/>
@@ -17009,8 +17008,8 @@
       <c r="AA43" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="AB43" s="211"/>
-      <c r="AC43" s="212"/>
+      <c r="AB43" s="188"/>
+      <c r="AC43" s="189"/>
       <c r="AD43" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17021,8 +17020,8 @@
       <c r="AH43" s="54"/>
       <c r="AI43" s="54"/>
       <c r="AJ43" s="55"/>
-      <c r="AK43" s="238"/>
-      <c r="AL43" s="237"/>
+      <c r="AK43" s="168"/>
+      <c r="AL43" s="167"/>
     </row>
     <row r="44" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A44" s="12"/>
@@ -17106,8 +17105,8 @@
       <c r="AA44" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="AB44" s="211"/>
-      <c r="AC44" s="212"/>
+      <c r="AB44" s="188"/>
+      <c r="AC44" s="189"/>
       <c r="AD44" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17118,8 +17117,8 @@
       <c r="AH44" s="54"/>
       <c r="AI44" s="54"/>
       <c r="AJ44" s="55"/>
-      <c r="AK44" s="238"/>
-      <c r="AL44" s="237"/>
+      <c r="AK44" s="168"/>
+      <c r="AL44" s="167"/>
     </row>
     <row r="45" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A45" s="12"/>
@@ -17203,8 +17202,8 @@
       <c r="AA45" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="AB45" s="211"/>
-      <c r="AC45" s="212"/>
+      <c r="AB45" s="188"/>
+      <c r="AC45" s="189"/>
       <c r="AD45" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17215,8 +17214,8 @@
       <c r="AH45" s="54"/>
       <c r="AI45" s="54"/>
       <c r="AJ45" s="55"/>
-      <c r="AK45" s="238"/>
-      <c r="AL45" s="237"/>
+      <c r="AK45" s="168"/>
+      <c r="AL45" s="167"/>
     </row>
     <row r="46" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A46" s="12"/>
@@ -17300,8 +17299,8 @@
       <c r="AA46" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="AB46" s="211"/>
-      <c r="AC46" s="212"/>
+      <c r="AB46" s="188"/>
+      <c r="AC46" s="189"/>
       <c r="AD46" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17312,8 +17311,8 @@
       <c r="AH46" s="54"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="55"/>
-      <c r="AK46" s="238"/>
-      <c r="AL46" s="237"/>
+      <c r="AK46" s="168"/>
+      <c r="AL46" s="167"/>
     </row>
     <row r="47" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A47" s="12"/>
@@ -17397,23 +17396,23 @@
       <c r="AA47" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AB47" s="211"/>
-      <c r="AC47" s="212"/>
+      <c r="AB47" s="188"/>
+      <c r="AC47" s="189"/>
       <c r="AD47" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE47" s="17"/>
-      <c r="AF47" s="216">
+      <c r="AF47" s="190">
         <f>SUM(AD41:AD53)</f>
         <v>0</v>
       </c>
-      <c r="AG47" s="214"/>
-      <c r="AH47" s="214"/>
-      <c r="AI47" s="214"/>
-      <c r="AJ47" s="215"/>
-      <c r="AK47" s="238"/>
-      <c r="AL47" s="237"/>
+      <c r="AG47" s="191"/>
+      <c r="AH47" s="191"/>
+      <c r="AI47" s="191"/>
+      <c r="AJ47" s="192"/>
+      <c r="AK47" s="168"/>
+      <c r="AL47" s="167"/>
     </row>
     <row r="48" spans="1:40" s="47" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A48" s="12"/>
@@ -17497,8 +17496,8 @@
       <c r="AA48" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AB48" s="211"/>
-      <c r="AC48" s="212"/>
+      <c r="AB48" s="188"/>
+      <c r="AC48" s="189"/>
       <c r="AD48" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17509,8 +17508,8 @@
       <c r="AH48" s="54"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="55"/>
-      <c r="AK48" s="238"/>
-      <c r="AL48" s="237"/>
+      <c r="AK48" s="168"/>
+      <c r="AL48" s="167"/>
     </row>
     <row r="49" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A49" s="12"/>
@@ -17594,8 +17593,8 @@
       <c r="AA49" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AB49" s="211"/>
-      <c r="AC49" s="212"/>
+      <c r="AB49" s="188"/>
+      <c r="AC49" s="189"/>
       <c r="AD49" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17606,8 +17605,8 @@
       <c r="AH49" s="54"/>
       <c r="AI49" s="54"/>
       <c r="AJ49" s="55"/>
-      <c r="AK49" s="238"/>
-      <c r="AL49" s="237"/>
+      <c r="AK49" s="168"/>
+      <c r="AL49" s="167"/>
     </row>
     <row r="50" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A50" s="12"/>
@@ -17691,8 +17690,8 @@
       <c r="AA50" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AB50" s="211"/>
-      <c r="AC50" s="212"/>
+      <c r="AB50" s="188"/>
+      <c r="AC50" s="189"/>
       <c r="AD50" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17703,8 +17702,8 @@
       <c r="AH50" s="54"/>
       <c r="AI50" s="54"/>
       <c r="AJ50" s="55"/>
-      <c r="AK50" s="238"/>
-      <c r="AL50" s="237"/>
+      <c r="AK50" s="168"/>
+      <c r="AL50" s="167"/>
     </row>
     <row r="51" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A51" s="12"/>
@@ -17788,8 +17787,8 @@
       <c r="AA51" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AB51" s="211"/>
-      <c r="AC51" s="212"/>
+      <c r="AB51" s="188"/>
+      <c r="AC51" s="189"/>
       <c r="AD51" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17800,8 +17799,8 @@
       <c r="AH51" s="54"/>
       <c r="AI51" s="54"/>
       <c r="AJ51" s="55"/>
-      <c r="AK51" s="238"/>
-      <c r="AL51" s="237"/>
+      <c r="AK51" s="168"/>
+      <c r="AL51" s="167"/>
     </row>
     <row r="52" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A52" s="12"/>
@@ -17897,8 +17896,8 @@
       <c r="AH52" s="54"/>
       <c r="AI52" s="54"/>
       <c r="AJ52" s="55"/>
-      <c r="AK52" s="238"/>
-      <c r="AL52" s="237"/>
+      <c r="AK52" s="168"/>
+      <c r="AL52" s="167"/>
     </row>
     <row r="53" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A53" s="12"/>
@@ -17994,8 +17993,8 @@
       <c r="AH53" s="62"/>
       <c r="AI53" s="62"/>
       <c r="AJ53" s="63"/>
-      <c r="AK53" s="238"/>
-      <c r="AL53" s="237"/>
+      <c r="AK53" s="168"/>
+      <c r="AL53" s="167"/>
     </row>
     <row r="54" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A54" s="12"/>
@@ -18090,8 +18089,8 @@
       <c r="Y54" s="14"/>
       <c r="Z54" s="14"/>
       <c r="AA54" s="13"/>
-      <c r="AB54" s="221"/>
-      <c r="AC54" s="222"/>
+      <c r="AB54" s="183"/>
+      <c r="AC54" s="184"/>
       <c r="AD54" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -18102,8 +18101,8 @@
       <c r="AH54" s="54"/>
       <c r="AI54" s="54"/>
       <c r="AJ54" s="54"/>
-      <c r="AK54" s="236"/>
-      <c r="AL54" s="237"/>
+      <c r="AK54" s="166"/>
+      <c r="AL54" s="167"/>
     </row>
     <row r="55" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B55" s="13" t="s">
@@ -18186,8 +18185,8 @@
       <c r="AA55" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="AB55" s="149"/>
-      <c r="AC55" s="150"/>
+      <c r="AB55" s="172"/>
+      <c r="AC55" s="173"/>
       <c r="AD55" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -18198,8 +18197,8 @@
       <c r="AH55" s="2"/>
       <c r="AI55" s="2"/>
       <c r="AJ55" s="2"/>
-      <c r="AK55" s="236"/>
-      <c r="AL55" s="237"/>
+      <c r="AK55" s="166"/>
+      <c r="AL55" s="167"/>
       <c r="AM55" s="4"/>
       <c r="AN55" s="4"/>
     </row>
@@ -18272,8 +18271,8 @@
       <c r="AH56" s="2"/>
       <c r="AI56" s="2"/>
       <c r="AJ56" s="2"/>
-      <c r="AK56" s="236"/>
-      <c r="AL56" s="237"/>
+      <c r="AK56" s="166"/>
+      <c r="AL56" s="167"/>
       <c r="AM56" s="67"/>
       <c r="AN56" s="67"/>
     </row>
@@ -18362,7 +18361,7 @@
         <f>Y57*4</f>
         <v>0</v>
       </c>
-      <c r="AC57" s="219">
+      <c r="AC57" s="159">
         <f>SUM(C59:W59)</f>
         <v>0</v>
       </c>
@@ -18373,8 +18372,8 @@
       <c r="AE57" s="17"/>
       <c r="AF57" s="69"/>
       <c r="AG57" s="69"/>
-      <c r="AK57" s="236"/>
-      <c r="AL57" s="237"/>
+      <c r="AK57" s="166"/>
+      <c r="AL57" s="167"/>
     </row>
     <row r="58" spans="1:40" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B58" s="15" t="s">
@@ -18461,14 +18460,14 @@
         <f>Y58*4</f>
         <v>0</v>
       </c>
-      <c r="AC58" s="220"/>
+      <c r="AC58" s="161"/>
       <c r="AD58" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE58" s="17"/>
-      <c r="AK58" s="236"/>
-      <c r="AL58" s="237"/>
+      <c r="AK58" s="166"/>
+      <c r="AL58" s="167"/>
     </row>
     <row r="59" spans="1:40" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B59" s="15"/>
@@ -18560,75 +18559,75 @@
       <c r="Y59" s="14"/>
       <c r="Z59" s="14"/>
       <c r="AA59" s="68"/>
-      <c r="AB59" s="143"/>
-      <c r="AC59" s="144"/>
+      <c r="AB59" s="193"/>
+      <c r="AC59" s="194"/>
       <c r="AD59" s="33">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE59" s="17"/>
-      <c r="AK59" s="236"/>
-      <c r="AL59" s="237"/>
+      <c r="AK59" s="166"/>
+      <c r="AL59" s="167"/>
     </row>
     <row r="60" spans="1:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B60" s="167" t="s">
+      <c r="B60" s="130" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="135" t="s">
+      <c r="C60" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="136"/>
-      <c r="E60" s="135" t="s">
+      <c r="D60" s="129"/>
+      <c r="E60" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F60" s="136"/>
-      <c r="G60" s="135" t="s">
+      <c r="F60" s="129"/>
+      <c r="G60" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H60" s="136"/>
-      <c r="I60" s="135" t="s">
+      <c r="H60" s="129"/>
+      <c r="I60" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J60" s="136"/>
-      <c r="K60" s="135" t="s">
+      <c r="J60" s="129"/>
+      <c r="K60" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L60" s="136"/>
-      <c r="M60" s="135" t="s">
+      <c r="L60" s="129"/>
+      <c r="M60" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N60" s="136"/>
-      <c r="O60" s="135" t="s">
+      <c r="N60" s="129"/>
+      <c r="O60" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P60" s="136"/>
-      <c r="Q60" s="135" t="s">
+      <c r="P60" s="129"/>
+      <c r="Q60" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R60" s="136"/>
-      <c r="S60" s="135" t="s">
+      <c r="R60" s="129"/>
+      <c r="S60" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T60" s="136"/>
-      <c r="U60" s="135" t="s">
+      <c r="T60" s="129"/>
+      <c r="U60" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V60" s="136"/>
-      <c r="W60" s="167" t="s">
+      <c r="V60" s="129"/>
+      <c r="W60" s="130" t="s">
         <v>12</v>
       </c>
       <c r="X60" s="110"/>
-      <c r="Y60" s="167" t="s">
+      <c r="Y60" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z60" s="167" t="s">
+      <c r="Z60" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA60" s="167" t="s">
+      <c r="AA60" s="130" t="s">
         <v>77</v>
       </c>
-      <c r="AB60" s="139"/>
-      <c r="AC60" s="140"/>
+      <c r="AB60" s="134"/>
+      <c r="AC60" s="135"/>
       <c r="AD60" s="6" t="s">
         <v>16</v>
       </c>
@@ -18637,7 +18636,7 @@
       <c r="AL60" s="71"/>
     </row>
     <row r="61" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B61" s="168"/>
+      <c r="B61" s="131"/>
       <c r="C61" s="9" t="s">
         <v>17</v>
       </c>
@@ -18698,11 +18697,11 @@
       <c r="V61" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W61" s="168"/>
+      <c r="W61" s="131"/>
       <c r="X61" s="111"/>
-      <c r="Y61" s="168"/>
-      <c r="Z61" s="168"/>
-      <c r="AA61" s="168"/>
+      <c r="Y61" s="131"/>
+      <c r="Z61" s="131"/>
+      <c r="AA61" s="131"/>
       <c r="AB61" s="10"/>
       <c r="AC61" s="11"/>
       <c r="AD61" s="6"/>
@@ -18796,11 +18795,11 @@
       <c r="AA62" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AB62" s="171">
+      <c r="AB62" s="174">
         <f>SUM(Y62:Y68)</f>
         <v>0</v>
       </c>
-      <c r="AC62" s="172"/>
+      <c r="AC62" s="175"/>
       <c r="AD62" s="16">
         <f>X62</f>
         <v>0</v>
@@ -18895,20 +18894,20 @@
       <c r="AA63" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AB63" s="211"/>
-      <c r="AC63" s="212"/>
+      <c r="AB63" s="188"/>
+      <c r="AC63" s="189"/>
       <c r="AD63" s="16">
         <f t="shared" ref="AD63:AD68" si="21">X63</f>
         <v>0</v>
       </c>
       <c r="AE63" s="17"/>
-      <c r="AF63" s="213" t="s">
+      <c r="AF63" s="195" t="s">
         <v>77</v>
       </c>
-      <c r="AG63" s="214"/>
-      <c r="AH63" s="214"/>
-      <c r="AI63" s="214"/>
-      <c r="AJ63" s="215"/>
+      <c r="AG63" s="191"/>
+      <c r="AH63" s="191"/>
+      <c r="AI63" s="191"/>
+      <c r="AJ63" s="192"/>
       <c r="AK63" s="70"/>
       <c r="AL63" s="71"/>
     </row>
@@ -18993,21 +18992,21 @@
       <c r="AA64" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AB64" s="211"/>
-      <c r="AC64" s="212"/>
+      <c r="AB64" s="188"/>
+      <c r="AC64" s="189"/>
       <c r="AD64" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE64" s="17"/>
-      <c r="AF64" s="216">
+      <c r="AF64" s="190">
         <f>SUM(AD62:AD68)</f>
         <v>0</v>
       </c>
-      <c r="AG64" s="217"/>
-      <c r="AH64" s="217"/>
-      <c r="AI64" s="217"/>
-      <c r="AJ64" s="218"/>
+      <c r="AG64" s="196"/>
+      <c r="AH64" s="196"/>
+      <c r="AI64" s="196"/>
+      <c r="AJ64" s="197"/>
       <c r="AK64" s="70"/>
       <c r="AL64" s="71"/>
     </row>
@@ -19092,8 +19091,8 @@
       <c r="AA65" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AB65" s="211"/>
-      <c r="AC65" s="212"/>
+      <c r="AB65" s="188"/>
+      <c r="AC65" s="189"/>
       <c r="AD65" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19188,8 +19187,8 @@
       <c r="AA66" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AB66" s="211"/>
-      <c r="AC66" s="212"/>
+      <c r="AB66" s="188"/>
+      <c r="AC66" s="189"/>
       <c r="AD66" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19284,8 +19283,8 @@
       <c r="AA67" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AB67" s="173"/>
-      <c r="AC67" s="174"/>
+      <c r="AB67" s="176"/>
+      <c r="AC67" s="177"/>
       <c r="AD67" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19380,8 +19379,8 @@
       <c r="AA68" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AB68" s="149"/>
-      <c r="AC68" s="150"/>
+      <c r="AB68" s="172"/>
+      <c r="AC68" s="173"/>
       <c r="AD68" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19485,8 +19484,8 @@
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
       <c r="AA69" s="13"/>
-      <c r="AB69" s="149"/>
-      <c r="AC69" s="150"/>
+      <c r="AB69" s="172"/>
+      <c r="AC69" s="173"/>
       <c r="AD69" s="16">
         <v>0</v>
       </c>
@@ -19503,46 +19502,46 @@
       <c r="B70" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="135" t="s">
+      <c r="C70" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="136"/>
-      <c r="E70" s="135" t="s">
+      <c r="D70" s="129"/>
+      <c r="E70" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F70" s="136"/>
-      <c r="G70" s="135" t="s">
+      <c r="F70" s="129"/>
+      <c r="G70" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H70" s="136"/>
-      <c r="I70" s="135" t="s">
+      <c r="H70" s="129"/>
+      <c r="I70" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J70" s="136"/>
-      <c r="K70" s="135" t="s">
+      <c r="J70" s="129"/>
+      <c r="K70" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L70" s="136"/>
-      <c r="M70" s="135" t="s">
+      <c r="L70" s="129"/>
+      <c r="M70" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N70" s="136"/>
-      <c r="O70" s="135" t="s">
+      <c r="N70" s="129"/>
+      <c r="O70" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P70" s="136"/>
-      <c r="Q70" s="135" t="s">
+      <c r="P70" s="129"/>
+      <c r="Q70" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R70" s="136"/>
-      <c r="S70" s="135" t="s">
+      <c r="R70" s="129"/>
+      <c r="S70" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T70" s="136"/>
-      <c r="U70" s="135" t="s">
+      <c r="T70" s="129"/>
+      <c r="U70" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V70" s="136"/>
+      <c r="V70" s="129"/>
       <c r="W70" s="9" t="s">
         <v>12</v>
       </c>
@@ -19556,8 +19555,8 @@
       <c r="AA70" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AB70" s="139"/>
-      <c r="AC70" s="140"/>
+      <c r="AB70" s="134"/>
+      <c r="AC70" s="135"/>
       <c r="AD70" s="6" t="s">
         <v>16</v>
       </c>
@@ -19653,28 +19652,28 @@
       <c r="AA71" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AB71" s="171">
+      <c r="AB71" s="174">
         <f>SUM(Y71:Y72)</f>
         <v>0</v>
       </c>
-      <c r="AC71" s="172"/>
+      <c r="AC71" s="175"/>
       <c r="AD71" s="16">
         <f>X71</f>
         <v>0</v>
       </c>
       <c r="AE71" s="17"/>
-      <c r="AF71" s="209" t="s">
+      <c r="AF71" s="198" t="s">
         <v>86</v>
       </c>
-      <c r="AG71" s="210"/>
-      <c r="AH71" s="210"/>
-      <c r="AI71" s="210"/>
-      <c r="AJ71" s="210"/>
-      <c r="AK71" s="201">
+      <c r="AG71" s="199"/>
+      <c r="AH71" s="199"/>
+      <c r="AI71" s="199"/>
+      <c r="AJ71" s="199"/>
+      <c r="AK71" s="203">
         <f>SUM(AD71:AD81)</f>
         <v>0</v>
       </c>
-      <c r="AL71" s="202"/>
+      <c r="AL71" s="204"/>
       <c r="AM71" s="29"/>
       <c r="AN71" s="29"/>
     </row>
@@ -19759,23 +19758,23 @@
       <c r="AA72" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="AB72" s="173"/>
-      <c r="AC72" s="174"/>
+      <c r="AB72" s="176"/>
+      <c r="AC72" s="177"/>
       <c r="AD72" s="16">
         <f t="shared" ref="AD72:AD86" si="23">X72</f>
         <v>0</v>
       </c>
       <c r="AE72" s="75"/>
-      <c r="AF72" s="197">
+      <c r="AF72" s="169">
         <f>+AD71+AD72</f>
         <v>0</v>
       </c>
-      <c r="AG72" s="198"/>
-      <c r="AH72" s="198"/>
-      <c r="AI72" s="198"/>
-      <c r="AJ72" s="198"/>
-      <c r="AK72" s="203"/>
-      <c r="AL72" s="204"/>
+      <c r="AG72" s="200"/>
+      <c r="AH72" s="200"/>
+      <c r="AI72" s="200"/>
+      <c r="AJ72" s="200"/>
+      <c r="AK72" s="205"/>
+      <c r="AL72" s="206"/>
       <c r="AM72" s="12"/>
       <c r="AN72" s="12"/>
     </row>
@@ -19871,8 +19870,8 @@
       <c r="Y73" s="14"/>
       <c r="Z73" s="14"/>
       <c r="AA73" s="38"/>
-      <c r="AB73" s="205"/>
-      <c r="AC73" s="206"/>
+      <c r="AB73" s="207"/>
+      <c r="AC73" s="208"/>
       <c r="AD73" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -19883,8 +19882,8 @@
       <c r="AH73" s="76"/>
       <c r="AI73" s="76"/>
       <c r="AJ73" s="76"/>
-      <c r="AK73" s="203"/>
-      <c r="AL73" s="204"/>
+      <c r="AK73" s="205"/>
+      <c r="AL73" s="206"/>
       <c r="AM73" s="12"/>
       <c r="AN73" s="12"/>
     </row>
@@ -19969,25 +19968,25 @@
       <c r="AA74" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="AB74" s="171">
+      <c r="AB74" s="174">
         <f>SUM(Y74:Y75)</f>
         <v>0</v>
       </c>
-      <c r="AC74" s="172"/>
+      <c r="AC74" s="175"/>
       <c r="AD74" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE74" s="17"/>
-      <c r="AF74" s="175" t="s">
+      <c r="AF74" s="178" t="s">
         <v>89</v>
       </c>
-      <c r="AG74" s="176"/>
-      <c r="AH74" s="176"/>
-      <c r="AI74" s="176"/>
-      <c r="AJ74" s="176"/>
-      <c r="AK74" s="203"/>
-      <c r="AL74" s="204"/>
+      <c r="AG74" s="179"/>
+      <c r="AH74" s="179"/>
+      <c r="AI74" s="179"/>
+      <c r="AJ74" s="179"/>
+      <c r="AK74" s="205"/>
+      <c r="AL74" s="206"/>
     </row>
     <row r="75" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B75" s="13" t="s">
@@ -20070,23 +20069,23 @@
       <c r="AA75" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AB75" s="173"/>
-      <c r="AC75" s="174"/>
+      <c r="AB75" s="176"/>
+      <c r="AC75" s="177"/>
       <c r="AD75" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE75" s="17"/>
-      <c r="AF75" s="197">
+      <c r="AF75" s="169">
         <f>+AD74+AD75</f>
         <v>0</v>
       </c>
-      <c r="AG75" s="198"/>
-      <c r="AH75" s="198"/>
-      <c r="AI75" s="198"/>
-      <c r="AJ75" s="198"/>
-      <c r="AK75" s="203"/>
-      <c r="AL75" s="204"/>
+      <c r="AG75" s="200"/>
+      <c r="AH75" s="200"/>
+      <c r="AI75" s="200"/>
+      <c r="AJ75" s="200"/>
+      <c r="AK75" s="205"/>
+      <c r="AL75" s="206"/>
     </row>
     <row r="76" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B76" s="13" t="s">
@@ -20169,25 +20168,25 @@
       <c r="AA76" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AB76" s="171">
+      <c r="AB76" s="174">
         <f>SUM(Y76:Y77)</f>
         <v>0</v>
       </c>
-      <c r="AC76" s="172"/>
+      <c r="AC76" s="175"/>
       <c r="AD76" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE76" s="17"/>
-      <c r="AF76" s="175" t="s">
+      <c r="AF76" s="178" t="s">
         <v>92</v>
       </c>
-      <c r="AG76" s="176"/>
-      <c r="AH76" s="176"/>
-      <c r="AI76" s="176"/>
-      <c r="AJ76" s="176"/>
-      <c r="AK76" s="203"/>
-      <c r="AL76" s="204"/>
+      <c r="AG76" s="179"/>
+      <c r="AH76" s="179"/>
+      <c r="AI76" s="179"/>
+      <c r="AJ76" s="179"/>
+      <c r="AK76" s="205"/>
+      <c r="AL76" s="206"/>
     </row>
     <row r="77" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B77" s="13" t="s">
@@ -20270,23 +20269,23 @@
       <c r="AA77" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB77" s="173"/>
-      <c r="AC77" s="174"/>
+      <c r="AB77" s="176"/>
+      <c r="AC77" s="177"/>
       <c r="AD77" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE77" s="17"/>
-      <c r="AF77" s="197">
+      <c r="AF77" s="169">
         <f>+AD76+AD77</f>
         <v>0</v>
       </c>
-      <c r="AG77" s="198"/>
-      <c r="AH77" s="198"/>
-      <c r="AI77" s="198"/>
-      <c r="AJ77" s="198"/>
-      <c r="AK77" s="203"/>
-      <c r="AL77" s="204"/>
+      <c r="AG77" s="200"/>
+      <c r="AH77" s="200"/>
+      <c r="AI77" s="200"/>
+      <c r="AJ77" s="200"/>
+      <c r="AK77" s="205"/>
+      <c r="AL77" s="206"/>
     </row>
     <row r="78" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B78" s="13" t="s">
@@ -20369,25 +20368,25 @@
       <c r="AA78" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AB78" s="171">
+      <c r="AB78" s="174">
         <f>SUM(Y78:Y79)</f>
         <v>0</v>
       </c>
-      <c r="AC78" s="172"/>
+      <c r="AC78" s="175"/>
       <c r="AD78" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE78" s="17"/>
-      <c r="AF78" s="175" t="s">
+      <c r="AF78" s="178" t="s">
         <v>95</v>
       </c>
-      <c r="AG78" s="176"/>
-      <c r="AH78" s="176"/>
-      <c r="AI78" s="176"/>
-      <c r="AJ78" s="176"/>
-      <c r="AK78" s="203"/>
-      <c r="AL78" s="204"/>
+      <c r="AG78" s="179"/>
+      <c r="AH78" s="179"/>
+      <c r="AI78" s="179"/>
+      <c r="AJ78" s="179"/>
+      <c r="AK78" s="205"/>
+      <c r="AL78" s="206"/>
     </row>
     <row r="79" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B79" s="13" t="s">
@@ -20470,21 +20469,21 @@
       <c r="AA79" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AB79" s="173"/>
-      <c r="AC79" s="174"/>
+      <c r="AB79" s="176"/>
+      <c r="AC79" s="177"/>
       <c r="AD79" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE79" s="17"/>
-      <c r="AF79" s="197">
+      <c r="AF79" s="169">
         <f>+AD78+AD79</f>
         <v>0</v>
       </c>
-      <c r="AG79" s="198"/>
-      <c r="AH79" s="198"/>
-      <c r="AI79" s="198"/>
-      <c r="AJ79" s="198"/>
+      <c r="AG79" s="200"/>
+      <c r="AH79" s="200"/>
+      <c r="AI79" s="200"/>
+      <c r="AJ79" s="200"/>
       <c r="AK79" s="77"/>
       <c r="AL79" s="78"/>
     </row>
@@ -20569,27 +20568,27 @@
       <c r="AA80" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AB80" s="171">
+      <c r="AB80" s="174">
         <f>SUM(Y80:Y81)</f>
         <v>0</v>
       </c>
-      <c r="AC80" s="172"/>
+      <c r="AC80" s="175"/>
       <c r="AD80" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE80" s="17"/>
-      <c r="AF80" s="175" t="s">
+      <c r="AF80" s="178" t="s">
         <v>98</v>
       </c>
-      <c r="AG80" s="176"/>
-      <c r="AH80" s="176"/>
-      <c r="AI80" s="176"/>
-      <c r="AJ80" s="176"/>
-      <c r="AK80" s="199" t="s">
+      <c r="AG80" s="179"/>
+      <c r="AH80" s="179"/>
+      <c r="AI80" s="179"/>
+      <c r="AJ80" s="179"/>
+      <c r="AK80" s="201" t="s">
         <v>99</v>
       </c>
-      <c r="AL80" s="200"/>
+      <c r="AL80" s="202"/>
     </row>
     <row r="81" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B81" s="13" t="s">
@@ -20672,23 +20671,23 @@
       <c r="AA81" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB81" s="173"/>
-      <c r="AC81" s="174"/>
+      <c r="AB81" s="176"/>
+      <c r="AC81" s="177"/>
       <c r="AD81" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE81" s="17"/>
-      <c r="AF81" s="197">
+      <c r="AF81" s="169">
         <f>+AD80+AD81</f>
         <v>0</v>
       </c>
-      <c r="AG81" s="198"/>
-      <c r="AH81" s="198"/>
-      <c r="AI81" s="198"/>
-      <c r="AJ81" s="198"/>
-      <c r="AK81" s="199"/>
-      <c r="AL81" s="200"/>
+      <c r="AG81" s="200"/>
+      <c r="AH81" s="200"/>
+      <c r="AI81" s="200"/>
+      <c r="AJ81" s="200"/>
+      <c r="AK81" s="201"/>
+      <c r="AL81" s="202"/>
     </row>
     <row r="82" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B82" s="13" t="s">
@@ -20771,8 +20770,8 @@
       <c r="AA82" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="AB82" s="149"/>
-      <c r="AC82" s="150"/>
+      <c r="AB82" s="172"/>
+      <c r="AC82" s="173"/>
       <c r="AD82" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20783,8 +20782,8 @@
       <c r="AH82" s="76"/>
       <c r="AI82" s="76"/>
       <c r="AJ82" s="76"/>
-      <c r="AK82" s="199"/>
-      <c r="AL82" s="200"/>
+      <c r="AK82" s="201"/>
+      <c r="AL82" s="202"/>
     </row>
     <row r="83" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B83" s="13" t="s">
@@ -20867,8 +20866,8 @@
       <c r="AA83" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AB83" s="149"/>
-      <c r="AC83" s="150"/>
+      <c r="AB83" s="172"/>
+      <c r="AC83" s="173"/>
       <c r="AD83" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20879,8 +20878,8 @@
       <c r="AH83" s="76"/>
       <c r="AI83" s="76"/>
       <c r="AJ83" s="76"/>
-      <c r="AK83" s="199"/>
-      <c r="AL83" s="200"/>
+      <c r="AK83" s="201"/>
+      <c r="AL83" s="202"/>
     </row>
     <row r="84" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B84" s="13" t="s">
@@ -20963,8 +20962,8 @@
       <c r="AA84" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="AB84" s="149"/>
-      <c r="AC84" s="150"/>
+      <c r="AB84" s="172"/>
+      <c r="AC84" s="173"/>
       <c r="AD84" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20975,8 +20974,8 @@
       <c r="AH84" s="76"/>
       <c r="AI84" s="76"/>
       <c r="AJ84" s="76"/>
-      <c r="AK84" s="199"/>
-      <c r="AL84" s="200"/>
+      <c r="AK84" s="201"/>
+      <c r="AL84" s="202"/>
     </row>
     <row r="85" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B85" s="13" t="s">
@@ -21059,8 +21058,8 @@
       <c r="AA85" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AB85" s="149"/>
-      <c r="AC85" s="150"/>
+      <c r="AB85" s="172"/>
+      <c r="AC85" s="173"/>
       <c r="AD85" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21071,8 +21070,8 @@
       <c r="AH85" s="76"/>
       <c r="AI85" s="76"/>
       <c r="AJ85" s="76"/>
-      <c r="AK85" s="199"/>
-      <c r="AL85" s="200"/>
+      <c r="AK85" s="201"/>
+      <c r="AL85" s="202"/>
     </row>
     <row r="86" spans="1:38" s="12" customFormat="1" ht="105.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B86" s="13" t="s">
@@ -21155,11 +21154,11 @@
       <c r="AA86" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="AB86" s="207">
+      <c r="AB86" s="209">
         <f>SUM(Y86:Y86)</f>
         <v>0</v>
       </c>
-      <c r="AC86" s="208"/>
+      <c r="AC86" s="210"/>
       <c r="AD86" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21170,53 +21169,53 @@
       <c r="AH86" s="2"/>
       <c r="AI86" s="2"/>
       <c r="AJ86" s="2"/>
-      <c r="AK86" s="199"/>
-      <c r="AL86" s="200"/>
+      <c r="AK86" s="201"/>
+      <c r="AL86" s="202"/>
     </row>
     <row r="87" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B87" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="C87" s="135" t="s">
+      <c r="C87" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D87" s="136"/>
-      <c r="E87" s="135" t="s">
+      <c r="D87" s="129"/>
+      <c r="E87" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F87" s="136"/>
-      <c r="G87" s="135" t="s">
+      <c r="F87" s="129"/>
+      <c r="G87" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H87" s="136"/>
-      <c r="I87" s="135" t="s">
+      <c r="H87" s="129"/>
+      <c r="I87" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J87" s="136"/>
-      <c r="K87" s="135" t="s">
+      <c r="J87" s="129"/>
+      <c r="K87" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L87" s="136"/>
-      <c r="M87" s="135" t="s">
+      <c r="L87" s="129"/>
+      <c r="M87" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N87" s="136"/>
-      <c r="O87" s="135" t="s">
+      <c r="N87" s="129"/>
+      <c r="O87" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P87" s="136"/>
-      <c r="Q87" s="135" t="s">
+      <c r="P87" s="129"/>
+      <c r="Q87" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R87" s="136"/>
-      <c r="S87" s="135" t="s">
+      <c r="R87" s="129"/>
+      <c r="S87" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T87" s="136"/>
-      <c r="U87" s="135" t="s">
+      <c r="T87" s="129"/>
+      <c r="U87" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V87" s="136"/>
+      <c r="V87" s="129"/>
       <c r="W87" s="9" t="s">
         <v>12</v>
       </c>
@@ -21230,17 +21229,17 @@
       <c r="AA87" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="AB87" s="139"/>
-      <c r="AC87" s="140"/>
+      <c r="AB87" s="134"/>
+      <c r="AC87" s="135"/>
       <c r="AD87" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AE87" s="7"/>
-      <c r="AK87" s="194">
+      <c r="AK87" s="211">
         <f>SUM(AD88:AD137)</f>
         <v>0</v>
       </c>
-      <c r="AL87" s="195"/>
+      <c r="AL87" s="212"/>
     </row>
     <row r="88" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B88" s="15" t="s">
@@ -21323,15 +21322,15 @@
       <c r="AA88" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="AB88" s="145"/>
-      <c r="AC88" s="146"/>
+      <c r="AB88" s="214"/>
+      <c r="AC88" s="215"/>
       <c r="AD88" s="16">
         <f>X88</f>
         <v>0</v>
       </c>
       <c r="AE88" s="7"/>
-      <c r="AK88" s="196"/>
-      <c r="AL88" s="195"/>
+      <c r="AK88" s="213"/>
+      <c r="AL88" s="212"/>
     </row>
     <row r="89" spans="1:38" s="64" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B89" s="65"/>
@@ -21374,8 +21373,8 @@
       <c r="AH89" s="2"/>
       <c r="AI89" s="2"/>
       <c r="AJ89" s="2"/>
-      <c r="AK89" s="196"/>
-      <c r="AL89" s="195"/>
+      <c r="AK89" s="213"/>
+      <c r="AL89" s="212"/>
     </row>
     <row r="90" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B90" s="13" t="s">
@@ -21458,8 +21457,8 @@
       <c r="AA90" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB90" s="149"/>
-      <c r="AC90" s="150"/>
+      <c r="AB90" s="172"/>
+      <c r="AC90" s="173"/>
       <c r="AD90" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21470,8 +21469,8 @@
       <c r="AH90" s="2"/>
       <c r="AI90" s="2"/>
       <c r="AJ90" s="2"/>
-      <c r="AK90" s="196"/>
-      <c r="AL90" s="195"/>
+      <c r="AK90" s="213"/>
+      <c r="AL90" s="212"/>
     </row>
     <row r="91" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B91" s="13" t="s">
@@ -21554,8 +21553,8 @@
       <c r="AA91" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AB91" s="149"/>
-      <c r="AC91" s="150"/>
+      <c r="AB91" s="172"/>
+      <c r="AC91" s="173"/>
       <c r="AD91" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21566,8 +21565,8 @@
       <c r="AH91" s="2"/>
       <c r="AI91" s="2"/>
       <c r="AJ91" s="2"/>
-      <c r="AK91" s="196"/>
-      <c r="AL91" s="195"/>
+      <c r="AK91" s="213"/>
+      <c r="AL91" s="212"/>
     </row>
     <row r="92" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B92" s="13" t="s">
@@ -21650,8 +21649,8 @@
       <c r="AA92" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="AB92" s="149"/>
-      <c r="AC92" s="150"/>
+      <c r="AB92" s="172"/>
+      <c r="AC92" s="173"/>
       <c r="AD92" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21662,8 +21661,8 @@
       <c r="AH92" s="2"/>
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
-      <c r="AK92" s="196"/>
-      <c r="AL92" s="195"/>
+      <c r="AK92" s="213"/>
+      <c r="AL92" s="212"/>
     </row>
     <row r="93" spans="1:38" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B93" s="13" t="s">
@@ -21746,25 +21745,25 @@
       <c r="AA93" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="AB93" s="154">
+      <c r="AB93" s="216">
         <f>SUM(Y93:Y102)</f>
         <v>0</v>
       </c>
-      <c r="AC93" s="155"/>
+      <c r="AC93" s="141"/>
       <c r="AD93" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE93" s="17"/>
-      <c r="AF93" s="160" t="s">
+      <c r="AF93" s="162" t="s">
         <v>112</v>
       </c>
-      <c r="AG93" s="161"/>
-      <c r="AH93" s="161"/>
-      <c r="AI93" s="161"/>
-      <c r="AJ93" s="162"/>
-      <c r="AK93" s="196"/>
-      <c r="AL93" s="195"/>
+      <c r="AG93" s="163"/>
+      <c r="AH93" s="163"/>
+      <c r="AI93" s="163"/>
+      <c r="AJ93" s="164"/>
+      <c r="AK93" s="213"/>
+      <c r="AL93" s="212"/>
     </row>
     <row r="94" spans="1:38" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A94" s="12"/>
@@ -21848,20 +21847,20 @@
       <c r="AA94" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="AB94" s="156"/>
-      <c r="AC94" s="157"/>
+      <c r="AB94" s="217"/>
+      <c r="AC94" s="142"/>
       <c r="AD94" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE94" s="17"/>
-      <c r="AF94" s="163"/>
-      <c r="AG94" s="164"/>
-      <c r="AH94" s="164"/>
-      <c r="AI94" s="164"/>
-      <c r="AJ94" s="165"/>
-      <c r="AK94" s="196"/>
-      <c r="AL94" s="195"/>
+      <c r="AF94" s="165"/>
+      <c r="AG94" s="154"/>
+      <c r="AH94" s="154"/>
+      <c r="AI94" s="154"/>
+      <c r="AJ94" s="155"/>
+      <c r="AK94" s="213"/>
+      <c r="AL94" s="212"/>
     </row>
     <row r="95" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A95" s="12"/>
@@ -21945,20 +21944,20 @@
       <c r="AA95" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="AB95" s="156"/>
-      <c r="AC95" s="157"/>
+      <c r="AB95" s="217"/>
+      <c r="AC95" s="142"/>
       <c r="AD95" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE95" s="17"/>
-      <c r="AF95" s="163"/>
-      <c r="AG95" s="164"/>
-      <c r="AH95" s="164"/>
-      <c r="AI95" s="164"/>
-      <c r="AJ95" s="165"/>
-      <c r="AK95" s="196"/>
-      <c r="AL95" s="195"/>
+      <c r="AF95" s="165"/>
+      <c r="AG95" s="154"/>
+      <c r="AH95" s="154"/>
+      <c r="AI95" s="154"/>
+      <c r="AJ95" s="155"/>
+      <c r="AK95" s="213"/>
+      <c r="AL95" s="212"/>
     </row>
     <row r="96" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A96" s="12"/>
@@ -22042,20 +22041,20 @@
       <c r="AA96" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="AB96" s="156"/>
-      <c r="AC96" s="157"/>
+      <c r="AB96" s="217"/>
+      <c r="AC96" s="142"/>
       <c r="AD96" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE96" s="17"/>
-      <c r="AF96" s="163"/>
-      <c r="AG96" s="164"/>
-      <c r="AH96" s="164"/>
-      <c r="AI96" s="164"/>
-      <c r="AJ96" s="165"/>
-      <c r="AK96" s="196"/>
-      <c r="AL96" s="195"/>
+      <c r="AF96" s="165"/>
+      <c r="AG96" s="154"/>
+      <c r="AH96" s="154"/>
+      <c r="AI96" s="154"/>
+      <c r="AJ96" s="155"/>
+      <c r="AK96" s="213"/>
+      <c r="AL96" s="212"/>
     </row>
     <row r="97" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A97" s="12"/>
@@ -22139,20 +22138,20 @@
       <c r="AA97" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AB97" s="156"/>
-      <c r="AC97" s="157"/>
+      <c r="AB97" s="217"/>
+      <c r="AC97" s="142"/>
       <c r="AD97" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE97" s="17"/>
-      <c r="AF97" s="163"/>
-      <c r="AG97" s="164"/>
-      <c r="AH97" s="164"/>
-      <c r="AI97" s="164"/>
-      <c r="AJ97" s="165"/>
-      <c r="AK97" s="196"/>
-      <c r="AL97" s="195"/>
+      <c r="AF97" s="165"/>
+      <c r="AG97" s="154"/>
+      <c r="AH97" s="154"/>
+      <c r="AI97" s="154"/>
+      <c r="AJ97" s="155"/>
+      <c r="AK97" s="213"/>
+      <c r="AL97" s="212"/>
     </row>
     <row r="98" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A98" s="12"/>
@@ -22236,23 +22235,23 @@
       <c r="AA98" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AB98" s="156"/>
-      <c r="AC98" s="157"/>
+      <c r="AB98" s="217"/>
+      <c r="AC98" s="142"/>
       <c r="AD98" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE98" s="17"/>
-      <c r="AF98" s="183">
+      <c r="AF98" s="219">
         <f>SUM(AD93:AD102)</f>
         <v>0</v>
       </c>
-      <c r="AG98" s="184"/>
-      <c r="AH98" s="184"/>
-      <c r="AI98" s="184"/>
-      <c r="AJ98" s="185"/>
-      <c r="AK98" s="196"/>
-      <c r="AL98" s="195"/>
+      <c r="AG98" s="220"/>
+      <c r="AH98" s="220"/>
+      <c r="AI98" s="220"/>
+      <c r="AJ98" s="221"/>
+      <c r="AK98" s="213"/>
+      <c r="AL98" s="212"/>
     </row>
     <row r="99" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A99" s="12"/>
@@ -22336,8 +22335,8 @@
       <c r="AA99" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AB99" s="156"/>
-      <c r="AC99" s="157"/>
+      <c r="AB99" s="217"/>
+      <c r="AC99" s="142"/>
       <c r="AD99" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22348,8 +22347,8 @@
       <c r="AH99" s="24"/>
       <c r="AI99" s="24"/>
       <c r="AJ99" s="25"/>
-      <c r="AK99" s="196"/>
-      <c r="AL99" s="195"/>
+      <c r="AK99" s="213"/>
+      <c r="AL99" s="212"/>
     </row>
     <row r="100" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A100" s="12"/>
@@ -22433,20 +22432,20 @@
       <c r="AA100" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AB100" s="156"/>
-      <c r="AC100" s="157"/>
+      <c r="AB100" s="217"/>
+      <c r="AC100" s="142"/>
       <c r="AD100" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE100" s="17"/>
-      <c r="AF100" s="166"/>
-      <c r="AG100" s="164"/>
-      <c r="AH100" s="164"/>
-      <c r="AI100" s="164"/>
-      <c r="AJ100" s="165"/>
-      <c r="AK100" s="196"/>
-      <c r="AL100" s="195"/>
+      <c r="AF100" s="153"/>
+      <c r="AG100" s="154"/>
+      <c r="AH100" s="154"/>
+      <c r="AI100" s="154"/>
+      <c r="AJ100" s="155"/>
+      <c r="AK100" s="213"/>
+      <c r="AL100" s="212"/>
     </row>
     <row r="101" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A101" s="12"/>
@@ -22530,8 +22529,8 @@
       <c r="AA101" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="AB101" s="156"/>
-      <c r="AC101" s="157"/>
+      <c r="AB101" s="217"/>
+      <c r="AC101" s="142"/>
       <c r="AD101" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22542,8 +22541,8 @@
       <c r="AH101" s="27"/>
       <c r="AI101" s="27"/>
       <c r="AJ101" s="28"/>
-      <c r="AK101" s="196"/>
-      <c r="AL101" s="195"/>
+      <c r="AK101" s="213"/>
+      <c r="AL101" s="212"/>
     </row>
     <row r="102" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A102" s="12"/>
@@ -22627,8 +22626,8 @@
       <c r="AA102" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="AB102" s="158"/>
-      <c r="AC102" s="159"/>
+      <c r="AB102" s="218"/>
+      <c r="AC102" s="143"/>
       <c r="AD102" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22639,8 +22638,8 @@
       <c r="AH102" s="84"/>
       <c r="AI102" s="84"/>
       <c r="AJ102" s="85"/>
-      <c r="AK102" s="196"/>
-      <c r="AL102" s="195"/>
+      <c r="AK102" s="213"/>
+      <c r="AL102" s="212"/>
     </row>
     <row r="103" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A103" s="12"/>
@@ -22733,132 +22732,132 @@
       <c r="Y103" s="14"/>
       <c r="Z103" s="14"/>
       <c r="AA103" s="13"/>
-      <c r="AB103" s="186"/>
-      <c r="AC103" s="187"/>
+      <c r="AB103" s="181"/>
+      <c r="AC103" s="182"/>
       <c r="AD103" s="33"/>
       <c r="AE103" s="17"/>
-      <c r="AF103" s="188"/>
-      <c r="AG103" s="189"/>
-      <c r="AH103" s="189"/>
-      <c r="AI103" s="189"/>
-      <c r="AJ103" s="190"/>
-      <c r="AK103" s="196"/>
-      <c r="AL103" s="195"/>
+      <c r="AF103" s="144"/>
+      <c r="AG103" s="145"/>
+      <c r="AH103" s="145"/>
+      <c r="AI103" s="145"/>
+      <c r="AJ103" s="146"/>
+      <c r="AK103" s="213"/>
+      <c r="AL103" s="212"/>
     </row>
     <row r="104" spans="1:38" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="169" t="s">
-        <v>0</v>
-      </c>
-      <c r="C104" s="170"/>
-      <c r="D104" s="170"/>
-      <c r="E104" s="170"/>
-      <c r="F104" s="170"/>
-      <c r="G104" s="170"/>
-      <c r="H104" s="170"/>
-      <c r="I104" s="170"/>
-      <c r="J104" s="170"/>
-      <c r="K104" s="170"/>
-      <c r="L104" s="170"/>
-      <c r="M104" s="170"/>
-      <c r="N104" s="170"/>
-      <c r="O104" s="170"/>
-      <c r="P104" s="170"/>
-      <c r="Q104" s="170"/>
-      <c r="R104" s="170"/>
-      <c r="S104" s="170"/>
-      <c r="T104" s="170"/>
-      <c r="U104" s="170"/>
-      <c r="V104" s="170"/>
-      <c r="W104" s="170"/>
-      <c r="X104" s="170"/>
-      <c r="Y104" s="170"/>
-      <c r="Z104" s="170"/>
-      <c r="AA104" s="170"/>
-      <c r="AB104" s="170"/>
-      <c r="AC104" s="170"/>
-      <c r="AD104" s="170"/>
+      <c r="B104" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="133"/>
+      <c r="D104" s="133"/>
+      <c r="E104" s="133"/>
+      <c r="F104" s="133"/>
+      <c r="G104" s="133"/>
+      <c r="H104" s="133"/>
+      <c r="I104" s="133"/>
+      <c r="J104" s="133"/>
+      <c r="K104" s="133"/>
+      <c r="L104" s="133"/>
+      <c r="M104" s="133"/>
+      <c r="N104" s="133"/>
+      <c r="O104" s="133"/>
+      <c r="P104" s="133"/>
+      <c r="Q104" s="133"/>
+      <c r="R104" s="133"/>
+      <c r="S104" s="133"/>
+      <c r="T104" s="133"/>
+      <c r="U104" s="133"/>
+      <c r="V104" s="133"/>
+      <c r="W104" s="133"/>
+      <c r="X104" s="133"/>
+      <c r="Y104" s="133"/>
+      <c r="Z104" s="133"/>
+      <c r="AA104" s="133"/>
+      <c r="AB104" s="133"/>
+      <c r="AC104" s="133"/>
+      <c r="AD104" s="133"/>
       <c r="AE104" s="1"/>
-      <c r="AF104" s="191"/>
-      <c r="AG104" s="192"/>
-      <c r="AH104" s="192"/>
-      <c r="AI104" s="192"/>
-      <c r="AJ104" s="193"/>
-      <c r="AK104" s="196"/>
-      <c r="AL104" s="195"/>
+      <c r="AF104" s="147"/>
+      <c r="AG104" s="148"/>
+      <c r="AH104" s="148"/>
+      <c r="AI104" s="148"/>
+      <c r="AJ104" s="149"/>
+      <c r="AK104" s="213"/>
+      <c r="AL104" s="212"/>
     </row>
     <row r="105" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B105" s="167" t="s">
+      <c r="B105" s="130" t="s">
         <v>122</v>
       </c>
-      <c r="C105" s="135" t="s">
+      <c r="C105" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D105" s="136"/>
-      <c r="E105" s="135" t="s">
+      <c r="D105" s="129"/>
+      <c r="E105" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F105" s="136"/>
-      <c r="G105" s="135" t="s">
+      <c r="F105" s="129"/>
+      <c r="G105" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H105" s="136"/>
-      <c r="I105" s="135" t="s">
+      <c r="H105" s="129"/>
+      <c r="I105" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J105" s="136"/>
-      <c r="K105" s="135" t="s">
+      <c r="J105" s="129"/>
+      <c r="K105" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L105" s="136"/>
-      <c r="M105" s="135" t="s">
+      <c r="L105" s="129"/>
+      <c r="M105" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N105" s="136"/>
-      <c r="O105" s="135" t="s">
+      <c r="N105" s="129"/>
+      <c r="O105" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P105" s="136"/>
-      <c r="Q105" s="135" t="s">
+      <c r="P105" s="129"/>
+      <c r="Q105" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R105" s="136"/>
-      <c r="S105" s="135" t="s">
+      <c r="R105" s="129"/>
+      <c r="S105" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T105" s="136"/>
-      <c r="U105" s="135" t="s">
+      <c r="T105" s="129"/>
+      <c r="U105" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V105" s="136"/>
-      <c r="W105" s="167" t="s">
+      <c r="V105" s="129"/>
+      <c r="W105" s="130" t="s">
         <v>12</v>
       </c>
       <c r="X105" s="110"/>
-      <c r="Y105" s="167" t="s">
+      <c r="Y105" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z105" s="167" t="s">
+      <c r="Z105" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA105" s="167" t="s">
+      <c r="AA105" s="130" t="s">
         <v>122</v>
       </c>
-      <c r="AB105" s="139"/>
-      <c r="AC105" s="140"/>
+      <c r="AB105" s="134"/>
+      <c r="AC105" s="135"/>
       <c r="AD105" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AE105" s="7"/>
-      <c r="AF105" s="191"/>
-      <c r="AG105" s="192"/>
-      <c r="AH105" s="192"/>
-      <c r="AI105" s="192"/>
-      <c r="AJ105" s="193"/>
-      <c r="AK105" s="196"/>
-      <c r="AL105" s="195"/>
+      <c r="AF105" s="147"/>
+      <c r="AG105" s="148"/>
+      <c r="AH105" s="148"/>
+      <c r="AI105" s="148"/>
+      <c r="AJ105" s="149"/>
+      <c r="AK105" s="213"/>
+      <c r="AL105" s="212"/>
     </row>
     <row r="106" spans="1:38" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B106" s="168"/>
+      <c r="B106" s="131"/>
       <c r="C106" s="9" t="s">
         <v>17</v>
       </c>
@@ -22919,22 +22918,22 @@
       <c r="V106" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W106" s="168"/>
+      <c r="W106" s="131"/>
       <c r="X106" s="111"/>
-      <c r="Y106" s="168"/>
-      <c r="Z106" s="168"/>
-      <c r="AA106" s="168"/>
+      <c r="Y106" s="131"/>
+      <c r="Z106" s="131"/>
+      <c r="AA106" s="131"/>
       <c r="AB106" s="10"/>
       <c r="AC106" s="11"/>
       <c r="AD106" s="6"/>
       <c r="AE106" s="7"/>
-      <c r="AF106" s="191"/>
-      <c r="AG106" s="192"/>
-      <c r="AH106" s="192"/>
-      <c r="AI106" s="192"/>
-      <c r="AJ106" s="193"/>
-      <c r="AK106" s="196"/>
-      <c r="AL106" s="195"/>
+      <c r="AF106" s="147"/>
+      <c r="AG106" s="148"/>
+      <c r="AH106" s="148"/>
+      <c r="AI106" s="148"/>
+      <c r="AJ106" s="149"/>
+      <c r="AK106" s="213"/>
+      <c r="AL106" s="212"/>
     </row>
     <row r="107" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A107" s="12"/>
@@ -23018,23 +23017,23 @@
       <c r="AA107" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AB107" s="154">
+      <c r="AB107" s="216">
         <f>SUM(Y107:Y110)</f>
         <v>0</v>
       </c>
-      <c r="AC107" s="155"/>
+      <c r="AC107" s="141"/>
       <c r="AD107" s="16">
         <f>X107</f>
         <v>0</v>
       </c>
       <c r="AE107" s="17"/>
-      <c r="AF107" s="191"/>
-      <c r="AG107" s="192"/>
-      <c r="AH107" s="192"/>
-      <c r="AI107" s="192"/>
-      <c r="AJ107" s="193"/>
-      <c r="AK107" s="196"/>
-      <c r="AL107" s="195"/>
+      <c r="AF107" s="147"/>
+      <c r="AG107" s="148"/>
+      <c r="AH107" s="148"/>
+      <c r="AI107" s="148"/>
+      <c r="AJ107" s="149"/>
+      <c r="AK107" s="213"/>
+      <c r="AL107" s="212"/>
     </row>
     <row r="108" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A108" s="12"/>
@@ -23118,8 +23117,8 @@
       <c r="AA108" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AB108" s="156"/>
-      <c r="AC108" s="157"/>
+      <c r="AB108" s="217"/>
+      <c r="AC108" s="142"/>
       <c r="AD108" s="16">
         <f t="shared" ref="AD108:AD136" si="31">X108</f>
         <v>0</v>
@@ -23130,8 +23129,8 @@
       <c r="AH108" s="24"/>
       <c r="AI108" s="24"/>
       <c r="AJ108" s="25"/>
-      <c r="AK108" s="196"/>
-      <c r="AL108" s="195"/>
+      <c r="AK108" s="213"/>
+      <c r="AL108" s="212"/>
     </row>
     <row r="109" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A109" s="12"/>
@@ -23215,8 +23214,8 @@
       <c r="AA109" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AB109" s="156"/>
-      <c r="AC109" s="157"/>
+      <c r="AB109" s="217"/>
+      <c r="AC109" s="142"/>
       <c r="AD109" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23227,8 +23226,8 @@
       <c r="AH109" s="24"/>
       <c r="AI109" s="24"/>
       <c r="AJ109" s="25"/>
-      <c r="AK109" s="196"/>
-      <c r="AL109" s="195"/>
+      <c r="AK109" s="213"/>
+      <c r="AL109" s="212"/>
     </row>
     <row r="110" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A110" s="12"/>
@@ -23312,8 +23311,8 @@
       <c r="AA110" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="AB110" s="156"/>
-      <c r="AC110" s="157"/>
+      <c r="AB110" s="217"/>
+      <c r="AC110" s="142"/>
       <c r="AD110" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23324,8 +23323,8 @@
       <c r="AH110" s="24"/>
       <c r="AI110" s="24"/>
       <c r="AJ110" s="25"/>
-      <c r="AK110" s="196"/>
-      <c r="AL110" s="195"/>
+      <c r="AK110" s="213"/>
+      <c r="AL110" s="212"/>
     </row>
     <row r="111" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A111" s="12"/>
@@ -23418,20 +23417,20 @@
       <c r="Y111" s="14"/>
       <c r="Z111" s="14"/>
       <c r="AA111" s="13"/>
-      <c r="AB111" s="158"/>
-      <c r="AC111" s="159"/>
+      <c r="AB111" s="218"/>
+      <c r="AC111" s="143"/>
       <c r="AD111" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE111" s="17"/>
-      <c r="AF111" s="178"/>
-      <c r="AG111" s="179"/>
-      <c r="AH111" s="179"/>
-      <c r="AI111" s="179"/>
-      <c r="AJ111" s="180"/>
-      <c r="AK111" s="196"/>
-      <c r="AL111" s="195"/>
+      <c r="AF111" s="224"/>
+      <c r="AG111" s="225"/>
+      <c r="AH111" s="225"/>
+      <c r="AI111" s="225"/>
+      <c r="AJ111" s="226"/>
+      <c r="AK111" s="213"/>
+      <c r="AL111" s="212"/>
     </row>
     <row r="112" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B112" s="13" t="s">
@@ -23514,25 +23513,25 @@
       <c r="AA112" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AB112" s="154">
+      <c r="AB112" s="216">
         <f>SUM(Y112:Y124)</f>
         <v>0</v>
       </c>
-      <c r="AC112" s="155"/>
+      <c r="AC112" s="141"/>
       <c r="AD112" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE112" s="17"/>
-      <c r="AF112" s="160" t="s">
+      <c r="AF112" s="162" t="s">
         <v>128</v>
       </c>
-      <c r="AG112" s="161"/>
-      <c r="AH112" s="161"/>
-      <c r="AI112" s="161"/>
-      <c r="AJ112" s="162"/>
-      <c r="AK112" s="196"/>
-      <c r="AL112" s="195"/>
+      <c r="AG112" s="163"/>
+      <c r="AH112" s="163"/>
+      <c r="AI112" s="163"/>
+      <c r="AJ112" s="164"/>
+      <c r="AK112" s="213"/>
+      <c r="AL112" s="212"/>
     </row>
     <row r="113" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B113" s="13" t="s">
@@ -23615,22 +23614,22 @@
       <c r="AA113" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AB113" s="156"/>
-      <c r="AC113" s="157"/>
+      <c r="AB113" s="217"/>
+      <c r="AC113" s="142"/>
       <c r="AD113" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE113" s="17"/>
-      <c r="AF113" s="163"/>
-      <c r="AG113" s="164"/>
-      <c r="AH113" s="164"/>
-      <c r="AI113" s="164"/>
-      <c r="AJ113" s="165"/>
-      <c r="AK113" s="181" t="s">
+      <c r="AF113" s="165"/>
+      <c r="AG113" s="154"/>
+      <c r="AH113" s="154"/>
+      <c r="AI113" s="154"/>
+      <c r="AJ113" s="155"/>
+      <c r="AK113" s="222" t="s">
         <v>130</v>
       </c>
-      <c r="AL113" s="182"/>
+      <c r="AL113" s="223"/>
     </row>
     <row r="114" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B114" s="13" t="s">
@@ -23713,20 +23712,20 @@
       <c r="AA114" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="AB114" s="156"/>
-      <c r="AC114" s="157"/>
+      <c r="AB114" s="217"/>
+      <c r="AC114" s="142"/>
       <c r="AD114" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE114" s="17"/>
-      <c r="AF114" s="163"/>
-      <c r="AG114" s="164"/>
-      <c r="AH114" s="164"/>
-      <c r="AI114" s="164"/>
-      <c r="AJ114" s="165"/>
-      <c r="AK114" s="181"/>
-      <c r="AL114" s="182"/>
+      <c r="AF114" s="165"/>
+      <c r="AG114" s="154"/>
+      <c r="AH114" s="154"/>
+      <c r="AI114" s="154"/>
+      <c r="AJ114" s="155"/>
+      <c r="AK114" s="222"/>
+      <c r="AL114" s="223"/>
     </row>
     <row r="115" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B115" s="13" t="s">
@@ -23809,20 +23808,20 @@
       <c r="AA115" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AB115" s="156"/>
-      <c r="AC115" s="157"/>
+      <c r="AB115" s="217"/>
+      <c r="AC115" s="142"/>
       <c r="AD115" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE115" s="17"/>
-      <c r="AF115" s="163"/>
-      <c r="AG115" s="164"/>
-      <c r="AH115" s="164"/>
-      <c r="AI115" s="164"/>
-      <c r="AJ115" s="165"/>
-      <c r="AK115" s="181"/>
-      <c r="AL115" s="182"/>
+      <c r="AF115" s="165"/>
+      <c r="AG115" s="154"/>
+      <c r="AH115" s="154"/>
+      <c r="AI115" s="154"/>
+      <c r="AJ115" s="155"/>
+      <c r="AK115" s="222"/>
+      <c r="AL115" s="223"/>
     </row>
     <row r="116" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B116" s="13" t="s">
@@ -23905,20 +23904,20 @@
       <c r="AA116" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AB116" s="156"/>
-      <c r="AC116" s="157"/>
+      <c r="AB116" s="217"/>
+      <c r="AC116" s="142"/>
       <c r="AD116" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE116" s="17"/>
-      <c r="AF116" s="163"/>
-      <c r="AG116" s="164"/>
-      <c r="AH116" s="164"/>
-      <c r="AI116" s="164"/>
-      <c r="AJ116" s="165"/>
-      <c r="AK116" s="181"/>
-      <c r="AL116" s="182"/>
+      <c r="AF116" s="165"/>
+      <c r="AG116" s="154"/>
+      <c r="AH116" s="154"/>
+      <c r="AI116" s="154"/>
+      <c r="AJ116" s="155"/>
+      <c r="AK116" s="222"/>
+      <c r="AL116" s="223"/>
     </row>
     <row r="117" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B117" s="13" t="s">
@@ -24001,20 +24000,20 @@
       <c r="AA117" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AB117" s="156"/>
-      <c r="AC117" s="157"/>
+      <c r="AB117" s="217"/>
+      <c r="AC117" s="142"/>
       <c r="AD117" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE117" s="17"/>
-      <c r="AF117" s="163"/>
-      <c r="AG117" s="164"/>
-      <c r="AH117" s="164"/>
-      <c r="AI117" s="164"/>
-      <c r="AJ117" s="165"/>
-      <c r="AK117" s="181"/>
-      <c r="AL117" s="182"/>
+      <c r="AF117" s="165"/>
+      <c r="AG117" s="154"/>
+      <c r="AH117" s="154"/>
+      <c r="AI117" s="154"/>
+      <c r="AJ117" s="155"/>
+      <c r="AK117" s="222"/>
+      <c r="AL117" s="223"/>
     </row>
     <row r="118" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A118" s="12"/>
@@ -24098,23 +24097,23 @@
       <c r="AA118" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="AB118" s="156"/>
-      <c r="AC118" s="157"/>
+      <c r="AB118" s="217"/>
+      <c r="AC118" s="142"/>
       <c r="AD118" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE118" s="17"/>
-      <c r="AF118" s="166">
+      <c r="AF118" s="153">
         <f>SUM(AD112:AD124)</f>
         <v>0</v>
       </c>
-      <c r="AG118" s="164"/>
-      <c r="AH118" s="164"/>
-      <c r="AI118" s="164"/>
-      <c r="AJ118" s="165"/>
-      <c r="AK118" s="181"/>
-      <c r="AL118" s="182"/>
+      <c r="AG118" s="154"/>
+      <c r="AH118" s="154"/>
+      <c r="AI118" s="154"/>
+      <c r="AJ118" s="155"/>
+      <c r="AK118" s="222"/>
+      <c r="AL118" s="223"/>
     </row>
     <row r="119" spans="1:38" s="47" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A119" s="12"/>
@@ -24198,20 +24197,20 @@
       <c r="AA119" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="AB119" s="156"/>
-      <c r="AC119" s="157"/>
+      <c r="AB119" s="217"/>
+      <c r="AC119" s="142"/>
       <c r="AD119" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE119" s="17"/>
-      <c r="AF119" s="166"/>
-      <c r="AG119" s="164"/>
-      <c r="AH119" s="164"/>
-      <c r="AI119" s="164"/>
-      <c r="AJ119" s="165"/>
-      <c r="AK119" s="181"/>
-      <c r="AL119" s="182"/>
+      <c r="AF119" s="153"/>
+      <c r="AG119" s="154"/>
+      <c r="AH119" s="154"/>
+      <c r="AI119" s="154"/>
+      <c r="AJ119" s="155"/>
+      <c r="AK119" s="222"/>
+      <c r="AL119" s="223"/>
     </row>
     <row r="120" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B120" s="13" t="s">
@@ -24294,8 +24293,8 @@
       <c r="AA120" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="AB120" s="156"/>
-      <c r="AC120" s="157"/>
+      <c r="AB120" s="217"/>
+      <c r="AC120" s="142"/>
       <c r="AD120" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24306,8 +24305,8 @@
       <c r="AH120" s="27"/>
       <c r="AI120" s="27"/>
       <c r="AJ120" s="28"/>
-      <c r="AK120" s="181"/>
-      <c r="AL120" s="182"/>
+      <c r="AK120" s="222"/>
+      <c r="AL120" s="223"/>
     </row>
     <row r="121" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B121" s="13" t="s">
@@ -24390,8 +24389,8 @@
       <c r="AA121" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AB121" s="156"/>
-      <c r="AC121" s="157"/>
+      <c r="AB121" s="217"/>
+      <c r="AC121" s="142"/>
       <c r="AD121" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24402,8 +24401,8 @@
       <c r="AH121" s="27"/>
       <c r="AI121" s="27"/>
       <c r="AJ121" s="28"/>
-      <c r="AK121" s="181"/>
-      <c r="AL121" s="182"/>
+      <c r="AK121" s="222"/>
+      <c r="AL121" s="223"/>
     </row>
     <row r="122" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B122" s="13" t="s">
@@ -24486,8 +24485,8 @@
       <c r="AA122" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AB122" s="156"/>
-      <c r="AC122" s="157"/>
+      <c r="AB122" s="217"/>
+      <c r="AC122" s="142"/>
       <c r="AD122" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24498,8 +24497,8 @@
       <c r="AH122" s="27"/>
       <c r="AI122" s="27"/>
       <c r="AJ122" s="28"/>
-      <c r="AK122" s="181"/>
-      <c r="AL122" s="182"/>
+      <c r="AK122" s="222"/>
+      <c r="AL122" s="223"/>
     </row>
     <row r="123" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B123" s="13" t="s">
@@ -24582,8 +24581,8 @@
       <c r="AA123" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AB123" s="156"/>
-      <c r="AC123" s="157"/>
+      <c r="AB123" s="217"/>
+      <c r="AC123" s="142"/>
       <c r="AD123" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24594,8 +24593,8 @@
       <c r="AH123" s="84"/>
       <c r="AI123" s="84"/>
       <c r="AJ123" s="85"/>
-      <c r="AK123" s="181"/>
-      <c r="AL123" s="182"/>
+      <c r="AK123" s="222"/>
+      <c r="AL123" s="223"/>
     </row>
     <row r="124" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B124" s="13" t="s">
@@ -24678,8 +24677,8 @@
       <c r="AA124" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AB124" s="156"/>
-      <c r="AC124" s="157"/>
+      <c r="AB124" s="217"/>
+      <c r="AC124" s="142"/>
       <c r="AD124" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24690,8 +24689,8 @@
       <c r="AH124" s="84"/>
       <c r="AI124" s="84"/>
       <c r="AJ124" s="85"/>
-      <c r="AK124" s="181"/>
-      <c r="AL124" s="182"/>
+      <c r="AK124" s="222"/>
+      <c r="AL124" s="223"/>
     </row>
     <row r="125" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B125" s="13"/>
@@ -24785,8 +24784,8 @@
       <c r="Y125" s="14"/>
       <c r="Z125" s="14"/>
       <c r="AA125" s="13"/>
-      <c r="AB125" s="158"/>
-      <c r="AC125" s="159"/>
+      <c r="AB125" s="218"/>
+      <c r="AC125" s="143"/>
       <c r="AD125" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24797,8 +24796,8 @@
       <c r="AH125" s="24"/>
       <c r="AI125" s="24"/>
       <c r="AJ125" s="25"/>
-      <c r="AK125" s="181"/>
-      <c r="AL125" s="182"/>
+      <c r="AK125" s="222"/>
+      <c r="AL125" s="223"/>
     </row>
     <row r="126" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B126" s="13" t="s">
@@ -24881,25 +24880,25 @@
       <c r="AA126" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AB126" s="154">
+      <c r="AB126" s="216">
         <f>SUM(Y126:Y135)</f>
         <v>0</v>
       </c>
-      <c r="AC126" s="155"/>
+      <c r="AC126" s="141"/>
       <c r="AD126" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE126" s="17"/>
-      <c r="AF126" s="160" t="s">
+      <c r="AF126" s="162" t="s">
         <v>143</v>
       </c>
-      <c r="AG126" s="161"/>
-      <c r="AH126" s="161"/>
-      <c r="AI126" s="161"/>
-      <c r="AJ126" s="162"/>
-      <c r="AK126" s="181"/>
-      <c r="AL126" s="182"/>
+      <c r="AG126" s="163"/>
+      <c r="AH126" s="163"/>
+      <c r="AI126" s="163"/>
+      <c r="AJ126" s="164"/>
+      <c r="AK126" s="222"/>
+      <c r="AL126" s="223"/>
     </row>
     <row r="127" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B127" s="13" t="s">
@@ -24982,20 +24981,20 @@
       <c r="AA127" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="AB127" s="156"/>
-      <c r="AC127" s="157"/>
+      <c r="AB127" s="217"/>
+      <c r="AC127" s="142"/>
       <c r="AD127" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE127" s="17"/>
-      <c r="AF127" s="163"/>
-      <c r="AG127" s="164"/>
-      <c r="AH127" s="164"/>
-      <c r="AI127" s="164"/>
-      <c r="AJ127" s="165"/>
-      <c r="AK127" s="181"/>
-      <c r="AL127" s="182"/>
+      <c r="AF127" s="165"/>
+      <c r="AG127" s="154"/>
+      <c r="AH127" s="154"/>
+      <c r="AI127" s="154"/>
+      <c r="AJ127" s="155"/>
+      <c r="AK127" s="222"/>
+      <c r="AL127" s="223"/>
     </row>
     <row r="128" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B128" s="13" t="s">
@@ -25078,8 +25077,8 @@
       <c r="AA128" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="AB128" s="156"/>
-      <c r="AC128" s="157"/>
+      <c r="AB128" s="217"/>
+      <c r="AC128" s="142"/>
       <c r="AD128" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25090,8 +25089,8 @@
       <c r="AH128" s="24"/>
       <c r="AI128" s="24"/>
       <c r="AJ128" s="25"/>
-      <c r="AK128" s="181"/>
-      <c r="AL128" s="182"/>
+      <c r="AK128" s="222"/>
+      <c r="AL128" s="223"/>
     </row>
     <row r="129" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B129" s="13" t="s">
@@ -25174,23 +25173,23 @@
       <c r="AA129" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="AB129" s="156"/>
-      <c r="AC129" s="157"/>
+      <c r="AB129" s="217"/>
+      <c r="AC129" s="142"/>
       <c r="AD129" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE129" s="17"/>
-      <c r="AF129" s="166">
+      <c r="AF129" s="153">
         <f>SUM(AD126:AD135)</f>
         <v>0</v>
       </c>
-      <c r="AG129" s="164"/>
-      <c r="AH129" s="164"/>
-      <c r="AI129" s="164"/>
-      <c r="AJ129" s="165"/>
-      <c r="AK129" s="181"/>
-      <c r="AL129" s="182"/>
+      <c r="AG129" s="154"/>
+      <c r="AH129" s="154"/>
+      <c r="AI129" s="154"/>
+      <c r="AJ129" s="155"/>
+      <c r="AK129" s="222"/>
+      <c r="AL129" s="223"/>
     </row>
     <row r="130" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B130" s="13" t="s">
@@ -25273,8 +25272,8 @@
       <c r="AA130" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="AB130" s="156"/>
-      <c r="AC130" s="157"/>
+      <c r="AB130" s="217"/>
+      <c r="AC130" s="142"/>
       <c r="AD130" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25285,8 +25284,8 @@
       <c r="AH130" s="24"/>
       <c r="AI130" s="24"/>
       <c r="AJ130" s="25"/>
-      <c r="AK130" s="181"/>
-      <c r="AL130" s="182"/>
+      <c r="AK130" s="222"/>
+      <c r="AL130" s="223"/>
     </row>
     <row r="131" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B131" s="13" t="s">
@@ -25369,8 +25368,8 @@
       <c r="AA131" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AB131" s="156"/>
-      <c r="AC131" s="157"/>
+      <c r="AB131" s="217"/>
+      <c r="AC131" s="142"/>
       <c r="AD131" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25381,8 +25380,8 @@
       <c r="AH131" s="27"/>
       <c r="AI131" s="27"/>
       <c r="AJ131" s="28"/>
-      <c r="AK131" s="181"/>
-      <c r="AL131" s="182"/>
+      <c r="AK131" s="222"/>
+      <c r="AL131" s="223"/>
     </row>
     <row r="132" spans="1:40" s="12" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B132" s="13" t="s">
@@ -25465,8 +25464,8 @@
       <c r="AA132" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AB132" s="156"/>
-      <c r="AC132" s="157"/>
+      <c r="AB132" s="217"/>
+      <c r="AC132" s="142"/>
       <c r="AD132" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25477,8 +25476,8 @@
       <c r="AH132"/>
       <c r="AI132"/>
       <c r="AJ132"/>
-      <c r="AK132" s="181"/>
-      <c r="AL132" s="182"/>
+      <c r="AK132" s="222"/>
+      <c r="AL132" s="223"/>
     </row>
     <row r="133" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B133" s="13" t="s">
@@ -25561,8 +25560,8 @@
       <c r="AA133" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="AB133" s="156"/>
-      <c r="AC133" s="157"/>
+      <c r="AB133" s="217"/>
+      <c r="AC133" s="142"/>
       <c r="AD133" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25573,8 +25572,8 @@
       <c r="AH133" s="27"/>
       <c r="AI133" s="27"/>
       <c r="AJ133" s="28"/>
-      <c r="AK133" s="181"/>
-      <c r="AL133" s="182"/>
+      <c r="AK133" s="222"/>
+      <c r="AL133" s="223"/>
     </row>
     <row r="134" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B134" s="13" t="s">
@@ -25657,8 +25656,8 @@
       <c r="AA134" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="AB134" s="156"/>
-      <c r="AC134" s="157"/>
+      <c r="AB134" s="217"/>
+      <c r="AC134" s="142"/>
       <c r="AD134" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25669,8 +25668,8 @@
       <c r="AH134" s="27"/>
       <c r="AI134" s="27"/>
       <c r="AJ134" s="28"/>
-      <c r="AK134" s="181"/>
-      <c r="AL134" s="182"/>
+      <c r="AK134" s="222"/>
+      <c r="AL134" s="223"/>
     </row>
     <row r="135" spans="1:40" s="12" customFormat="1" ht="147" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B135" s="13" t="s">
@@ -25753,8 +25752,8 @@
       <c r="AA135" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="AB135" s="156"/>
-      <c r="AC135" s="157"/>
+      <c r="AB135" s="217"/>
+      <c r="AC135" s="142"/>
       <c r="AD135" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25765,8 +25764,8 @@
       <c r="AH135" s="84"/>
       <c r="AI135" s="84"/>
       <c r="AJ135" s="85"/>
-      <c r="AK135" s="181"/>
-      <c r="AL135" s="182"/>
+      <c r="AK135" s="222"/>
+      <c r="AL135" s="223"/>
     </row>
     <row r="136" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B136" s="13"/>
@@ -25860,22 +25859,22 @@
       <c r="Y136" s="14"/>
       <c r="Z136" s="14"/>
       <c r="AA136" s="13"/>
-      <c r="AB136" s="158"/>
-      <c r="AC136" s="159"/>
+      <c r="AB136" s="218"/>
+      <c r="AC136" s="143"/>
       <c r="AD136" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE136" s="17"/>
-      <c r="AF136" s="175" t="s">
+      <c r="AF136" s="178" t="s">
         <v>153</v>
       </c>
-      <c r="AG136" s="176"/>
-      <c r="AH136" s="176"/>
-      <c r="AI136" s="176"/>
-      <c r="AJ136" s="176"/>
-      <c r="AK136" s="181"/>
-      <c r="AL136" s="182"/>
+      <c r="AG136" s="179"/>
+      <c r="AH136" s="179"/>
+      <c r="AI136" s="179"/>
+      <c r="AJ136" s="179"/>
+      <c r="AK136" s="222"/>
+      <c r="AL136" s="223"/>
     </row>
     <row r="137" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B137" s="13" t="s">
@@ -25958,69 +25957,69 @@
       <c r="AA137" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="AB137" s="149"/>
-      <c r="AC137" s="150"/>
+      <c r="AB137" s="172"/>
+      <c r="AC137" s="173"/>
       <c r="AD137" s="16">
         <f>X137</f>
         <v>0</v>
       </c>
       <c r="AE137" s="17"/>
-      <c r="AF137" s="177">
+      <c r="AF137" s="229">
         <f>AD137</f>
         <v>0</v>
       </c>
-      <c r="AG137" s="176"/>
-      <c r="AH137" s="176"/>
-      <c r="AI137" s="176"/>
-      <c r="AJ137" s="176"/>
-      <c r="AK137" s="181"/>
-      <c r="AL137" s="182"/>
+      <c r="AG137" s="179"/>
+      <c r="AH137" s="179"/>
+      <c r="AI137" s="179"/>
+      <c r="AJ137" s="179"/>
+      <c r="AK137" s="222"/>
+      <c r="AL137" s="223"/>
     </row>
     <row r="138" spans="1:40" s="88" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A138"/>
       <c r="B138" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="C138" s="135" t="s">
+      <c r="C138" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D138" s="136"/>
-      <c r="E138" s="135" t="s">
+      <c r="D138" s="129"/>
+      <c r="E138" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F138" s="136"/>
-      <c r="G138" s="135" t="s">
+      <c r="F138" s="129"/>
+      <c r="G138" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H138" s="136"/>
-      <c r="I138" s="135" t="s">
+      <c r="H138" s="129"/>
+      <c r="I138" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J138" s="136"/>
-      <c r="K138" s="135" t="s">
+      <c r="J138" s="129"/>
+      <c r="K138" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L138" s="136"/>
-      <c r="M138" s="135" t="s">
+      <c r="L138" s="129"/>
+      <c r="M138" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N138" s="136"/>
-      <c r="O138" s="135" t="s">
+      <c r="N138" s="129"/>
+      <c r="O138" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P138" s="136"/>
-      <c r="Q138" s="135" t="s">
+      <c r="P138" s="129"/>
+      <c r="Q138" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R138" s="136"/>
-      <c r="S138" s="135" t="s">
+      <c r="R138" s="129"/>
+      <c r="S138" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T138" s="136"/>
-      <c r="U138" s="135" t="s">
+      <c r="T138" s="129"/>
+      <c r="U138" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V138" s="136"/>
+      <c r="V138" s="129"/>
       <c r="W138" s="9" t="s">
         <v>12</v>
       </c>
@@ -26034,8 +26033,8 @@
       <c r="AA138" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="AB138" s="152"/>
-      <c r="AC138" s="153"/>
+      <c r="AB138" s="227"/>
+      <c r="AC138" s="228"/>
       <c r="AD138" s="6" t="s">
         <v>16</v>
       </c>
@@ -26132,11 +26131,11 @@
       <c r="AA139" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="AB139" s="171">
+      <c r="AB139" s="174">
         <f>SUM(Y139:Y140)</f>
         <v>0</v>
       </c>
-      <c r="AC139" s="172"/>
+      <c r="AC139" s="175"/>
       <c r="AD139" s="16">
         <f>X139</f>
         <v>0</v>
@@ -26232,8 +26231,8 @@
       <c r="AA140" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AB140" s="173"/>
-      <c r="AC140" s="174"/>
+      <c r="AB140" s="176"/>
+      <c r="AC140" s="177"/>
       <c r="AD140" s="16">
         <f>X140</f>
         <v>0</v>
@@ -26254,46 +26253,46 @@
       <c r="B141" s="86" t="s">
         <v>212</v>
       </c>
-      <c r="C141" s="135" t="s">
+      <c r="C141" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D141" s="136"/>
-      <c r="E141" s="135" t="s">
+      <c r="D141" s="129"/>
+      <c r="E141" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F141" s="136"/>
-      <c r="G141" s="135" t="s">
+      <c r="F141" s="129"/>
+      <c r="G141" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H141" s="136"/>
-      <c r="I141" s="135" t="s">
+      <c r="H141" s="129"/>
+      <c r="I141" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J141" s="136"/>
-      <c r="K141" s="135" t="s">
+      <c r="J141" s="129"/>
+      <c r="K141" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L141" s="136"/>
-      <c r="M141" s="135" t="s">
+      <c r="L141" s="129"/>
+      <c r="M141" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N141" s="136"/>
-      <c r="O141" s="135" t="s">
+      <c r="N141" s="129"/>
+      <c r="O141" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P141" s="136"/>
-      <c r="Q141" s="135" t="s">
+      <c r="P141" s="129"/>
+      <c r="Q141" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R141" s="136"/>
-      <c r="S141" s="135" t="s">
+      <c r="R141" s="129"/>
+      <c r="S141" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T141" s="136"/>
-      <c r="U141" s="135" t="s">
+      <c r="T141" s="129"/>
+      <c r="U141" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V141" s="136"/>
+      <c r="V141" s="129"/>
       <c r="W141" s="9" t="s">
         <v>12</v>
       </c>
@@ -26307,8 +26306,8 @@
       <c r="AA141" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="AB141" s="152"/>
-      <c r="AC141" s="153"/>
+      <c r="AB141" s="227"/>
+      <c r="AC141" s="228"/>
       <c r="AD141" s="6" t="s">
         <v>16</v>
       </c>
@@ -26405,11 +26404,11 @@
       <c r="AA142" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AB142" s="154">
+      <c r="AB142" s="216">
         <f>SUM(Y142:Y152)</f>
         <v>0</v>
       </c>
-      <c r="AC142" s="155"/>
+      <c r="AC142" s="141"/>
       <c r="AD142" s="16">
         <f>X142</f>
         <v>0</v>
@@ -26505,8 +26504,8 @@
       <c r="AA143" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AB143" s="156"/>
-      <c r="AC143" s="157"/>
+      <c r="AB143" s="217"/>
+      <c r="AC143" s="142"/>
       <c r="AD143" s="16">
         <f t="shared" ref="AD143:AD152" si="41">X143</f>
         <v>0</v>
@@ -26602,8 +26601,8 @@
       <c r="AA144" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AB144" s="156"/>
-      <c r="AC144" s="157"/>
+      <c r="AB144" s="217"/>
+      <c r="AC144" s="142"/>
       <c r="AD144" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26699,8 +26698,8 @@
       <c r="AA145" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AB145" s="156"/>
-      <c r="AC145" s="157"/>
+      <c r="AB145" s="217"/>
+      <c r="AC145" s="142"/>
       <c r="AD145" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26796,8 +26795,8 @@
       <c r="AA146" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="AB146" s="156"/>
-      <c r="AC146" s="157"/>
+      <c r="AB146" s="217"/>
+      <c r="AC146" s="142"/>
       <c r="AD146" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26893,8 +26892,8 @@
       <c r="AA147" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AB147" s="156"/>
-      <c r="AC147" s="157"/>
+      <c r="AB147" s="217"/>
+      <c r="AC147" s="142"/>
       <c r="AD147" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26990,8 +26989,8 @@
       <c r="AA148" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="AB148" s="156"/>
-      <c r="AC148" s="157"/>
+      <c r="AB148" s="217"/>
+      <c r="AC148" s="142"/>
       <c r="AD148" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27087,8 +27086,8 @@
       <c r="AA149" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AB149" s="156"/>
-      <c r="AC149" s="157"/>
+      <c r="AB149" s="217"/>
+      <c r="AC149" s="142"/>
       <c r="AD149" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27184,8 +27183,8 @@
       <c r="AA150" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="AB150" s="156"/>
-      <c r="AC150" s="157"/>
+      <c r="AB150" s="217"/>
+      <c r="AC150" s="142"/>
       <c r="AD150" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27281,8 +27280,8 @@
       <c r="AA151" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="AB151" s="156"/>
-      <c r="AC151" s="157"/>
+      <c r="AB151" s="217"/>
+      <c r="AC151" s="142"/>
       <c r="AD151" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27378,8 +27377,8 @@
       <c r="AA152" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="AB152" s="158"/>
-      <c r="AC152" s="159"/>
+      <c r="AB152" s="218"/>
+      <c r="AC152" s="143"/>
       <c r="AD152" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27485,8 +27484,8 @@
       <c r="Y153" s="14"/>
       <c r="Z153" s="14"/>
       <c r="AA153" s="13"/>
-      <c r="AB153" s="149"/>
-      <c r="AC153" s="150"/>
+      <c r="AB153" s="172"/>
+      <c r="AC153" s="173"/>
       <c r="AD153" s="16">
         <v>0</v>
       </c>
@@ -27500,101 +27499,101 @@
       <c r="AL153" s="92"/>
     </row>
     <row r="154" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="1.85">
-      <c r="B154" s="169" t="s">
-        <v>0</v>
-      </c>
-      <c r="C154" s="170"/>
-      <c r="D154" s="170"/>
-      <c r="E154" s="170"/>
-      <c r="F154" s="170"/>
-      <c r="G154" s="170"/>
-      <c r="H154" s="170"/>
-      <c r="I154" s="170"/>
-      <c r="J154" s="170"/>
-      <c r="K154" s="170"/>
-      <c r="L154" s="170"/>
-      <c r="M154" s="170"/>
-      <c r="N154" s="170"/>
-      <c r="O154" s="170"/>
-      <c r="P154" s="170"/>
-      <c r="Q154" s="170"/>
-      <c r="R154" s="170"/>
-      <c r="S154" s="170"/>
-      <c r="T154" s="170"/>
-      <c r="U154" s="170"/>
-      <c r="V154" s="170"/>
-      <c r="W154" s="170"/>
-      <c r="X154" s="170"/>
-      <c r="Y154" s="170"/>
-      <c r="Z154" s="170"/>
-      <c r="AA154" s="170"/>
-      <c r="AB154" s="170"/>
-      <c r="AC154" s="170"/>
-      <c r="AD154" s="170"/>
+      <c r="B154" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C154" s="133"/>
+      <c r="D154" s="133"/>
+      <c r="E154" s="133"/>
+      <c r="F154" s="133"/>
+      <c r="G154" s="133"/>
+      <c r="H154" s="133"/>
+      <c r="I154" s="133"/>
+      <c r="J154" s="133"/>
+      <c r="K154" s="133"/>
+      <c r="L154" s="133"/>
+      <c r="M154" s="133"/>
+      <c r="N154" s="133"/>
+      <c r="O154" s="133"/>
+      <c r="P154" s="133"/>
+      <c r="Q154" s="133"/>
+      <c r="R154" s="133"/>
+      <c r="S154" s="133"/>
+      <c r="T154" s="133"/>
+      <c r="U154" s="133"/>
+      <c r="V154" s="133"/>
+      <c r="W154" s="133"/>
+      <c r="X154" s="133"/>
+      <c r="Y154" s="133"/>
+      <c r="Z154" s="133"/>
+      <c r="AA154" s="133"/>
+      <c r="AB154" s="133"/>
+      <c r="AC154" s="133"/>
+      <c r="AD154" s="133"/>
       <c r="AE154" s="1"/>
       <c r="AK154" s="92"/>
       <c r="AL154" s="92"/>
     </row>
     <row r="155" spans="1:40" s="88" customFormat="1" ht="138.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A155"/>
-      <c r="B155" s="167" t="s">
+      <c r="B155" s="130" t="s">
         <v>170</v>
       </c>
-      <c r="C155" s="135" t="s">
+      <c r="C155" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D155" s="136"/>
-      <c r="E155" s="135" t="s">
+      <c r="D155" s="129"/>
+      <c r="E155" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F155" s="136"/>
-      <c r="G155" s="135" t="s">
+      <c r="F155" s="129"/>
+      <c r="G155" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H155" s="136"/>
-      <c r="I155" s="135" t="s">
+      <c r="H155" s="129"/>
+      <c r="I155" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J155" s="136"/>
-      <c r="K155" s="135" t="s">
+      <c r="J155" s="129"/>
+      <c r="K155" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L155" s="136"/>
-      <c r="M155" s="135" t="s">
+      <c r="L155" s="129"/>
+      <c r="M155" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N155" s="136"/>
-      <c r="O155" s="135" t="s">
+      <c r="N155" s="129"/>
+      <c r="O155" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P155" s="136"/>
-      <c r="Q155" s="135" t="s">
+      <c r="P155" s="129"/>
+      <c r="Q155" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R155" s="136"/>
-      <c r="S155" s="135" t="s">
+      <c r="R155" s="129"/>
+      <c r="S155" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T155" s="136"/>
-      <c r="U155" s="135" t="s">
+      <c r="T155" s="129"/>
+      <c r="U155" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V155" s="136"/>
-      <c r="W155" s="167" t="s">
+      <c r="V155" s="129"/>
+      <c r="W155" s="130" t="s">
         <v>12</v>
       </c>
       <c r="X155" s="110"/>
-      <c r="Y155" s="167" t="s">
+      <c r="Y155" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z155" s="167" t="s">
+      <c r="Z155" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA155" s="167" t="s">
+      <c r="AA155" s="130" t="s">
         <v>170</v>
       </c>
-      <c r="AB155" s="152"/>
-      <c r="AC155" s="153"/>
+      <c r="AB155" s="227"/>
+      <c r="AC155" s="228"/>
       <c r="AD155" s="6" t="s">
         <v>16</v>
       </c>
@@ -27610,7 +27609,7 @@
       <c r="AN155" s="12"/>
     </row>
     <row r="156" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B156" s="168"/>
+      <c r="B156" s="131"/>
       <c r="C156" s="9" t="s">
         <v>17</v>
       </c>
@@ -27671,11 +27670,11 @@
       <c r="V156" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W156" s="168"/>
+      <c r="W156" s="131"/>
       <c r="X156" s="111"/>
-      <c r="Y156" s="168"/>
-      <c r="Z156" s="168"/>
-      <c r="AA156" s="168"/>
+      <c r="Y156" s="131"/>
+      <c r="Z156" s="131"/>
+      <c r="AA156" s="131"/>
       <c r="AB156" s="10"/>
       <c r="AC156" s="11"/>
       <c r="AD156" s="6">
@@ -27771,11 +27770,11 @@
       <c r="AA157" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AB157" s="154">
+      <c r="AB157" s="216">
         <f>SUM(Y157:Y162)</f>
         <v>0</v>
       </c>
-      <c r="AC157" s="155"/>
+      <c r="AC157" s="141"/>
       <c r="AD157" s="16">
         <f>X157</f>
         <v>0</v>
@@ -27870,8 +27869,8 @@
       <c r="AA158" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AB158" s="156"/>
-      <c r="AC158" s="157"/>
+      <c r="AB158" s="217"/>
+      <c r="AC158" s="142"/>
       <c r="AD158" s="16">
         <f t="shared" ref="AD158:AD162" si="45">X158</f>
         <v>0</v>
@@ -27966,8 +27965,8 @@
       <c r="AA159" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AB159" s="156"/>
-      <c r="AC159" s="157"/>
+      <c r="AB159" s="217"/>
+      <c r="AC159" s="142"/>
       <c r="AD159" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28062,8 +28061,8 @@
       <c r="AA160" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AB160" s="156"/>
-      <c r="AC160" s="157"/>
+      <c r="AB160" s="217"/>
+      <c r="AC160" s="142"/>
       <c r="AD160" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28158,8 +28157,8 @@
       <c r="AA161" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AB161" s="156"/>
-      <c r="AC161" s="157"/>
+      <c r="AB161" s="217"/>
+      <c r="AC161" s="142"/>
       <c r="AD161" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28254,8 +28253,8 @@
       <c r="AA162" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AB162" s="158"/>
-      <c r="AC162" s="159"/>
+      <c r="AB162" s="218"/>
+      <c r="AC162" s="143"/>
       <c r="AD162" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28275,59 +28274,59 @@
       <c r="B163" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="C163" s="135" t="s">
+      <c r="C163" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D163" s="136"/>
-      <c r="E163" s="135" t="s">
+      <c r="D163" s="129"/>
+      <c r="E163" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F163" s="136"/>
-      <c r="G163" s="135" t="s">
+      <c r="F163" s="129"/>
+      <c r="G163" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H163" s="136"/>
-      <c r="I163" s="135" t="s">
+      <c r="H163" s="129"/>
+      <c r="I163" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J163" s="136"/>
-      <c r="K163" s="135" t="s">
+      <c r="J163" s="129"/>
+      <c r="K163" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L163" s="136"/>
-      <c r="M163" s="135" t="s">
+      <c r="L163" s="129"/>
+      <c r="M163" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N163" s="136"/>
-      <c r="O163" s="135" t="s">
+      <c r="N163" s="129"/>
+      <c r="O163" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P163" s="136"/>
-      <c r="Q163" s="135" t="s">
+      <c r="P163" s="129"/>
+      <c r="Q163" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R163" s="136"/>
-      <c r="S163" s="135" t="s">
+      <c r="R163" s="129"/>
+      <c r="S163" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T163" s="136"/>
-      <c r="U163" s="135" t="s">
+      <c r="T163" s="129"/>
+      <c r="U163" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V163" s="136"/>
+      <c r="V163" s="129"/>
       <c r="W163" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X163" s="117"/>
-      <c r="Y163" s="147" t="s">
+      <c r="Y163" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="Z163" s="148"/>
+      <c r="Z163" s="233"/>
       <c r="AA163" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="AB163" s="139"/>
-      <c r="AC163" s="140"/>
+      <c r="AB163" s="134"/>
+      <c r="AC163" s="135"/>
       <c r="AD163" s="6" t="s">
         <v>16</v>
       </c>
@@ -28389,31 +28388,31 @@
       <c r="X164" s="120">
         <v>0</v>
       </c>
-      <c r="Y164" s="141">
+      <c r="Y164" s="230">
         <f t="shared" ref="Y164:Y187" si="46">SUM(C164:W164)</f>
         <v>0</v>
       </c>
-      <c r="Z164" s="142"/>
+      <c r="Z164" s="231"/>
       <c r="AA164" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AB164" s="154">
+      <c r="AB164" s="216">
         <f>SUM(Y164:Y171)</f>
         <v>0</v>
       </c>
-      <c r="AC164" s="155"/>
+      <c r="AC164" s="141"/>
       <c r="AD164" s="16">
         <f>X164</f>
         <v>0</v>
       </c>
       <c r="AE164" s="94"/>
-      <c r="AF164" s="160" t="s">
+      <c r="AF164" s="162" t="s">
         <v>180</v>
       </c>
-      <c r="AG164" s="161"/>
-      <c r="AH164" s="161"/>
-      <c r="AI164" s="161"/>
-      <c r="AJ164" s="162"/>
+      <c r="AG164" s="163"/>
+      <c r="AH164" s="163"/>
+      <c r="AI164" s="163"/>
+      <c r="AJ164" s="164"/>
       <c r="AK164" s="8"/>
       <c r="AL164" s="8"/>
     </row>
@@ -28467,26 +28466,26 @@
       <c r="X165" s="120">
         <v>0</v>
       </c>
-      <c r="Y165" s="141">
+      <c r="Y165" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z165" s="142"/>
+      <c r="Z165" s="231"/>
       <c r="AA165" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="AB165" s="156"/>
-      <c r="AC165" s="157"/>
+      <c r="AB165" s="217"/>
+      <c r="AC165" s="142"/>
       <c r="AD165" s="16">
         <f t="shared" ref="AD165:AD170" si="47">X165</f>
         <v>0</v>
       </c>
       <c r="AE165" s="94"/>
-      <c r="AF165" s="163"/>
-      <c r="AG165" s="164"/>
-      <c r="AH165" s="164"/>
-      <c r="AI165" s="164"/>
-      <c r="AJ165" s="165"/>
+      <c r="AF165" s="165"/>
+      <c r="AG165" s="154"/>
+      <c r="AH165" s="154"/>
+      <c r="AI165" s="154"/>
+      <c r="AJ165" s="155"/>
       <c r="AK165" s="8"/>
       <c r="AL165" s="8"/>
     </row>
@@ -28540,26 +28539,26 @@
       <c r="X166" s="120">
         <v>0</v>
       </c>
-      <c r="Y166" s="141">
+      <c r="Y166" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z166" s="142"/>
+      <c r="Z166" s="231"/>
       <c r="AA166" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="AB166" s="156"/>
-      <c r="AC166" s="157"/>
+      <c r="AB166" s="217"/>
+      <c r="AC166" s="142"/>
       <c r="AD166" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE166" s="94"/>
-      <c r="AF166" s="163"/>
-      <c r="AG166" s="164"/>
-      <c r="AH166" s="164"/>
-      <c r="AI166" s="164"/>
-      <c r="AJ166" s="165"/>
+      <c r="AF166" s="165"/>
+      <c r="AG166" s="154"/>
+      <c r="AH166" s="154"/>
+      <c r="AI166" s="154"/>
+      <c r="AJ166" s="155"/>
       <c r="AK166" s="8"/>
       <c r="AL166" s="8"/>
     </row>
@@ -28613,26 +28612,26 @@
       <c r="X167" s="120">
         <v>0</v>
       </c>
-      <c r="Y167" s="141">
+      <c r="Y167" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z167" s="142"/>
+      <c r="Z167" s="231"/>
       <c r="AA167" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="AB167" s="156"/>
-      <c r="AC167" s="157"/>
+      <c r="AB167" s="217"/>
+      <c r="AC167" s="142"/>
       <c r="AD167" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE167" s="94"/>
-      <c r="AF167" s="163"/>
-      <c r="AG167" s="164"/>
-      <c r="AH167" s="164"/>
-      <c r="AI167" s="164"/>
-      <c r="AJ167" s="165"/>
+      <c r="AF167" s="165"/>
+      <c r="AG167" s="154"/>
+      <c r="AH167" s="154"/>
+      <c r="AI167" s="154"/>
+      <c r="AJ167" s="155"/>
       <c r="AK167" s="8"/>
       <c r="AL167" s="8"/>
     </row>
@@ -28686,29 +28685,29 @@
       <c r="X168" s="120">
         <v>0</v>
       </c>
-      <c r="Y168" s="141">
+      <c r="Y168" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z168" s="142"/>
+      <c r="Z168" s="231"/>
       <c r="AA168" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="AB168" s="156"/>
-      <c r="AC168" s="157"/>
+      <c r="AB168" s="217"/>
+      <c r="AC168" s="142"/>
       <c r="AD168" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE168" s="94"/>
-      <c r="AF168" s="166">
+      <c r="AF168" s="153">
         <f>SUM(AD164:AD171)</f>
         <v>0</v>
       </c>
-      <c r="AG168" s="164"/>
-      <c r="AH168" s="164"/>
-      <c r="AI168" s="164"/>
-      <c r="AJ168" s="165"/>
+      <c r="AG168" s="154"/>
+      <c r="AH168" s="154"/>
+      <c r="AI168" s="154"/>
+      <c r="AJ168" s="155"/>
       <c r="AK168" s="8"/>
       <c r="AL168" s="8"/>
     </row>
@@ -28762,16 +28761,16 @@
       <c r="X169" s="120">
         <v>0</v>
       </c>
-      <c r="Y169" s="141">
+      <c r="Y169" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z169" s="142"/>
+      <c r="Z169" s="231"/>
       <c r="AA169" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="AB169" s="156"/>
-      <c r="AC169" s="157"/>
+      <c r="AB169" s="217"/>
+      <c r="AC169" s="142"/>
       <c r="AD169" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -28835,16 +28834,16 @@
       <c r="X170" s="120">
         <v>0</v>
       </c>
-      <c r="Y170" s="141">
+      <c r="Y170" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z170" s="142"/>
+      <c r="Z170" s="231"/>
       <c r="AA170" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="AB170" s="156"/>
-      <c r="AC170" s="157"/>
+      <c r="AB170" s="217"/>
+      <c r="AC170" s="142"/>
       <c r="AD170" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -28908,16 +28907,16 @@
       <c r="X171" s="120">
         <v>0</v>
       </c>
-      <c r="Y171" s="141">
+      <c r="Y171" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z171" s="142"/>
+      <c r="Z171" s="231"/>
       <c r="AA171" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="AB171" s="158"/>
-      <c r="AC171" s="159"/>
+      <c r="AB171" s="218"/>
+      <c r="AC171" s="143"/>
       <c r="AD171" s="16">
         <f>X171</f>
         <v>0</v>
@@ -28990,16 +28989,16 @@
         <v>0</v>
       </c>
       <c r="X172" s="121"/>
-      <c r="Y172" s="147">
+      <c r="Y172" s="232">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z172" s="148"/>
+      <c r="Z172" s="233"/>
       <c r="AA172" s="86" t="s">
         <v>189</v>
       </c>
-      <c r="AB172" s="152"/>
-      <c r="AC172" s="153"/>
+      <c r="AB172" s="227"/>
+      <c r="AC172" s="228"/>
       <c r="AD172" s="6" t="s">
         <v>16</v>
       </c>
@@ -29055,16 +29054,16 @@
       <c r="X173" s="120">
         <v>0</v>
       </c>
-      <c r="Y173" s="141">
+      <c r="Y173" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z173" s="142"/>
+      <c r="Z173" s="231"/>
       <c r="AA173" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="AB173" s="149"/>
-      <c r="AC173" s="150"/>
+      <c r="AB173" s="172"/>
+      <c r="AC173" s="173"/>
       <c r="AD173" s="16">
         <f>X173</f>
         <v>0</v>
@@ -29128,16 +29127,16 @@
       <c r="X174" s="120">
         <v>0</v>
       </c>
-      <c r="Y174" s="141">
+      <c r="Y174" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z174" s="142"/>
+      <c r="Z174" s="231"/>
       <c r="AA174" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AB174" s="149"/>
-      <c r="AC174" s="150"/>
+      <c r="AB174" s="172"/>
+      <c r="AC174" s="173"/>
       <c r="AD174" s="16">
         <f>X174</f>
         <v>0</v>
@@ -29201,16 +29200,16 @@
       <c r="X175" s="120">
         <v>0</v>
       </c>
-      <c r="Y175" s="141">
+      <c r="Y175" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z175" s="142"/>
+      <c r="Z175" s="231"/>
       <c r="AA175" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="AB175" s="149"/>
-      <c r="AC175" s="150"/>
+      <c r="AB175" s="172"/>
+      <c r="AC175" s="173"/>
       <c r="AD175" s="16">
         <f>X175</f>
         <v>0</v>
@@ -29274,16 +29273,16 @@
       <c r="X176" s="120">
         <v>0</v>
       </c>
-      <c r="Y176" s="141">
+      <c r="Y176" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z176" s="142"/>
+      <c r="Z176" s="231"/>
       <c r="AA176" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="AB176" s="149"/>
-      <c r="AC176" s="150"/>
+      <c r="AB176" s="172"/>
+      <c r="AC176" s="173"/>
       <c r="AD176" s="16">
         <f t="shared" ref="AD176:AD187" si="49">X176</f>
         <v>0</v>
@@ -29347,16 +29346,16 @@
       <c r="X177" s="120">
         <v>0</v>
       </c>
-      <c r="Y177" s="141">
+      <c r="Y177" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z177" s="142"/>
+      <c r="Z177" s="231"/>
       <c r="AA177" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="AB177" s="149"/>
-      <c r="AC177" s="150"/>
+      <c r="AB177" s="172"/>
+      <c r="AC177" s="173"/>
       <c r="AD177" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29420,25 +29419,25 @@
       <c r="X178" s="120">
         <v>0</v>
       </c>
-      <c r="Y178" s="141">
+      <c r="Y178" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z178" s="142"/>
+      <c r="Z178" s="231"/>
       <c r="AA178" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="AB178" s="149"/>
-      <c r="AC178" s="150"/>
+      <c r="AB178" s="172"/>
+      <c r="AC178" s="173"/>
       <c r="AD178" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE178" s="98"/>
       <c r="AF178" s="99"/>
-      <c r="AG178" s="151"/>
-      <c r="AH178" s="151"/>
-      <c r="AI178" s="151"/>
+      <c r="AG178" s="234"/>
+      <c r="AH178" s="234"/>
+      <c r="AI178" s="234"/>
       <c r="AJ178" s="99"/>
       <c r="AK178" s="8"/>
       <c r="AL178" s="8"/>
@@ -29493,16 +29492,16 @@
       <c r="X179" s="120">
         <v>0</v>
       </c>
-      <c r="Y179" s="141">
+      <c r="Y179" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z179" s="142"/>
+      <c r="Z179" s="231"/>
       <c r="AA179" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="AB179" s="149"/>
-      <c r="AC179" s="150"/>
+      <c r="AB179" s="172"/>
+      <c r="AC179" s="173"/>
       <c r="AD179" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29566,16 +29565,16 @@
       <c r="X180" s="120">
         <v>0</v>
       </c>
-      <c r="Y180" s="141">
+      <c r="Y180" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z180" s="142"/>
+      <c r="Z180" s="231"/>
       <c r="AA180" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="AB180" s="149"/>
-      <c r="AC180" s="150"/>
+      <c r="AB180" s="172"/>
+      <c r="AC180" s="173"/>
       <c r="AD180" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29639,16 +29638,16 @@
       <c r="X181" s="120">
         <v>0</v>
       </c>
-      <c r="Y181" s="141">
+      <c r="Y181" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z181" s="142"/>
+      <c r="Z181" s="231"/>
       <c r="AA181" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AB181" s="149"/>
-      <c r="AC181" s="150"/>
+      <c r="AB181" s="172"/>
+      <c r="AC181" s="173"/>
       <c r="AD181" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29712,11 +29711,11 @@
       <c r="X182" s="120">
         <v>0</v>
       </c>
-      <c r="Y182" s="141">
+      <c r="Y182" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z182" s="142"/>
+      <c r="Z182" s="231"/>
       <c r="AA182" s="13" t="s">
         <v>210</v>
       </c>
@@ -29787,16 +29786,16 @@
       <c r="X183" s="120">
         <v>0</v>
       </c>
-      <c r="Y183" s="141">
+      <c r="Y183" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z183" s="142"/>
+      <c r="Z183" s="231"/>
       <c r="AA183" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="AB183" s="149"/>
-      <c r="AC183" s="150"/>
+      <c r="AB183" s="172"/>
+      <c r="AC183" s="173"/>
       <c r="AD183" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29860,16 +29859,16 @@
       <c r="X184" s="120">
         <v>0</v>
       </c>
-      <c r="Y184" s="141">
+      <c r="Y184" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z184" s="142"/>
+      <c r="Z184" s="231"/>
       <c r="AA184" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="AB184" s="149"/>
-      <c r="AC184" s="150"/>
+      <c r="AB184" s="172"/>
+      <c r="AC184" s="173"/>
       <c r="AD184" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29933,16 +29932,16 @@
       <c r="X185" s="120">
         <v>0</v>
       </c>
-      <c r="Y185" s="141">
+      <c r="Y185" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z185" s="142"/>
+      <c r="Z185" s="231"/>
       <c r="AA185" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="AB185" s="149"/>
-      <c r="AC185" s="150"/>
+      <c r="AB185" s="172"/>
+      <c r="AC185" s="173"/>
       <c r="AD185" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30006,16 +30005,16 @@
       <c r="X186" s="120">
         <v>0</v>
       </c>
-      <c r="Y186" s="141">
+      <c r="Y186" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z186" s="142"/>
+      <c r="Z186" s="231"/>
       <c r="AA186" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="AB186" s="149"/>
-      <c r="AC186" s="150"/>
+      <c r="AB186" s="172"/>
+      <c r="AC186" s="173"/>
       <c r="AD186" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30079,16 +30078,16 @@
       <c r="X187" s="120">
         <v>0</v>
       </c>
-      <c r="Y187" s="141">
+      <c r="Y187" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z187" s="142"/>
+      <c r="Z187" s="231"/>
       <c r="AA187" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="AB187" s="149"/>
-      <c r="AC187" s="150"/>
+      <c r="AB187" s="172"/>
+      <c r="AC187" s="173"/>
       <c r="AD187" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30106,59 +30105,59 @@
       <c r="B188" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="C188" s="135" t="s">
+      <c r="C188" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D188" s="136"/>
-      <c r="E188" s="135" t="s">
+      <c r="D188" s="129"/>
+      <c r="E188" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F188" s="136"/>
-      <c r="G188" s="135" t="s">
+      <c r="F188" s="129"/>
+      <c r="G188" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H188" s="136"/>
-      <c r="I188" s="135" t="s">
+      <c r="H188" s="129"/>
+      <c r="I188" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J188" s="136"/>
-      <c r="K188" s="135" t="s">
+      <c r="J188" s="129"/>
+      <c r="K188" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L188" s="136"/>
-      <c r="M188" s="135" t="s">
+      <c r="L188" s="129"/>
+      <c r="M188" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N188" s="136"/>
-      <c r="O188" s="135" t="s">
+      <c r="N188" s="129"/>
+      <c r="O188" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P188" s="136"/>
-      <c r="Q188" s="135" t="s">
+      <c r="P188" s="129"/>
+      <c r="Q188" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R188" s="136"/>
-      <c r="S188" s="135" t="s">
+      <c r="R188" s="129"/>
+      <c r="S188" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T188" s="136"/>
-      <c r="U188" s="135" t="s">
+      <c r="T188" s="129"/>
+      <c r="U188" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V188" s="136"/>
+      <c r="V188" s="129"/>
       <c r="W188" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X188" s="117"/>
-      <c r="Y188" s="147" t="s">
+      <c r="Y188" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="Z188" s="148"/>
+      <c r="Z188" s="233"/>
       <c r="AA188" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="AB188" s="139"/>
-      <c r="AC188" s="140"/>
+      <c r="AB188" s="134"/>
+      <c r="AC188" s="135"/>
       <c r="AD188" s="6" t="s">
         <v>16</v>
       </c>
@@ -30170,60 +30169,60 @@
       <c r="B189" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C189" s="141">
-        <v>0</v>
-      </c>
-      <c r="D189" s="142"/>
-      <c r="E189" s="141">
-        <v>0</v>
-      </c>
-      <c r="F189" s="142"/>
-      <c r="G189" s="141">
-        <v>0</v>
-      </c>
-      <c r="H189" s="142"/>
-      <c r="I189" s="141">
-        <v>0</v>
-      </c>
-      <c r="J189" s="142"/>
-      <c r="K189" s="141">
-        <v>0</v>
-      </c>
-      <c r="L189" s="142"/>
-      <c r="M189" s="141">
-        <v>0</v>
-      </c>
-      <c r="N189" s="142"/>
-      <c r="O189" s="141">
-        <v>0</v>
-      </c>
-      <c r="P189" s="142"/>
-      <c r="Q189" s="141">
-        <v>0</v>
-      </c>
-      <c r="R189" s="142"/>
-      <c r="S189" s="141">
-        <v>0</v>
-      </c>
-      <c r="T189" s="142"/>
-      <c r="U189" s="141">
-        <v>0</v>
-      </c>
-      <c r="V189" s="142"/>
+      <c r="C189" s="230">
+        <v>0</v>
+      </c>
+      <c r="D189" s="231"/>
+      <c r="E189" s="230">
+        <v>0</v>
+      </c>
+      <c r="F189" s="231"/>
+      <c r="G189" s="230">
+        <v>0</v>
+      </c>
+      <c r="H189" s="231"/>
+      <c r="I189" s="230">
+        <v>0</v>
+      </c>
+      <c r="J189" s="231"/>
+      <c r="K189" s="230">
+        <v>0</v>
+      </c>
+      <c r="L189" s="231"/>
+      <c r="M189" s="230">
+        <v>0</v>
+      </c>
+      <c r="N189" s="231"/>
+      <c r="O189" s="230">
+        <v>0</v>
+      </c>
+      <c r="P189" s="231"/>
+      <c r="Q189" s="230">
+        <v>0</v>
+      </c>
+      <c r="R189" s="231"/>
+      <c r="S189" s="230">
+        <v>0</v>
+      </c>
+      <c r="T189" s="231"/>
+      <c r="U189" s="230">
+        <v>0</v>
+      </c>
+      <c r="V189" s="231"/>
       <c r="W189" s="14">
         <v>0</v>
       </c>
       <c r="X189" s="120"/>
-      <c r="Y189" s="141">
+      <c r="Y189" s="230">
         <f>SUM(C189:W189)</f>
         <v>0</v>
       </c>
-      <c r="Z189" s="142"/>
+      <c r="Z189" s="231"/>
       <c r="AA189" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AB189" s="145"/>
-      <c r="AC189" s="146"/>
+      <c r="AB189" s="214"/>
+      <c r="AC189" s="215"/>
       <c r="AD189" s="16">
         <f>X189</f>
         <v>0</v>
@@ -30236,59 +30235,59 @@
       <c r="B190" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="C190" s="135" t="s">
+      <c r="C190" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D190" s="136"/>
-      <c r="E190" s="135" t="s">
+      <c r="D190" s="129"/>
+      <c r="E190" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F190" s="136"/>
-      <c r="G190" s="135" t="s">
+      <c r="F190" s="129"/>
+      <c r="G190" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H190" s="136"/>
-      <c r="I190" s="135" t="s">
+      <c r="H190" s="129"/>
+      <c r="I190" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J190" s="136"/>
-      <c r="K190" s="135" t="s">
+      <c r="J190" s="129"/>
+      <c r="K190" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L190" s="136"/>
-      <c r="M190" s="135" t="s">
+      <c r="L190" s="129"/>
+      <c r="M190" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N190" s="136"/>
-      <c r="O190" s="135" t="s">
+      <c r="N190" s="129"/>
+      <c r="O190" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P190" s="136"/>
-      <c r="Q190" s="135" t="s">
+      <c r="P190" s="129"/>
+      <c r="Q190" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R190" s="136"/>
-      <c r="S190" s="135" t="s">
+      <c r="R190" s="129"/>
+      <c r="S190" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T190" s="136"/>
-      <c r="U190" s="135" t="s">
+      <c r="T190" s="129"/>
+      <c r="U190" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V190" s="136"/>
+      <c r="V190" s="129"/>
       <c r="W190" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X190" s="117"/>
-      <c r="Y190" s="147" t="s">
+      <c r="Y190" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="Z190" s="148"/>
+      <c r="Z190" s="233"/>
       <c r="AA190" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="AB190" s="139"/>
-      <c r="AC190" s="140"/>
+      <c r="AB190" s="134"/>
+      <c r="AC190" s="135"/>
       <c r="AD190" s="6" t="s">
         <v>16</v>
       </c>
@@ -30353,16 +30352,16 @@
       <c r="X191" s="122">
         <v>0</v>
       </c>
-      <c r="Y191" s="141">
+      <c r="Y191" s="230">
         <f>SUM(C191:W191)</f>
         <v>0</v>
       </c>
-      <c r="Z191" s="142"/>
+      <c r="Z191" s="231"/>
       <c r="AA191" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="AB191" s="143"/>
-      <c r="AC191" s="144"/>
+      <c r="AB191" s="193"/>
+      <c r="AC191" s="194"/>
       <c r="AD191" s="16">
         <f>X191</f>
         <v>0</v>
@@ -30372,58 +30371,58 @@
       <c r="AN191" s="2"/>
     </row>
     <row r="192" spans="2:40" s="2" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B192" s="137" t="s">
+      <c r="B192" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C192" s="135" t="s">
+      <c r="C192" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D192" s="136"/>
-      <c r="E192" s="135" t="s">
+      <c r="D192" s="129"/>
+      <c r="E192" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F192" s="136"/>
-      <c r="G192" s="135" t="s">
+      <c r="F192" s="129"/>
+      <c r="G192" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H192" s="136"/>
-      <c r="I192" s="135" t="s">
+      <c r="H192" s="129"/>
+      <c r="I192" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J192" s="136"/>
-      <c r="K192" s="135" t="s">
+      <c r="J192" s="129"/>
+      <c r="K192" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L192" s="136"/>
-      <c r="M192" s="135" t="s">
+      <c r="L192" s="129"/>
+      <c r="M192" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N192" s="136"/>
-      <c r="O192" s="135" t="s">
+      <c r="N192" s="129"/>
+      <c r="O192" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P192" s="136"/>
-      <c r="Q192" s="135" t="s">
+      <c r="P192" s="129"/>
+      <c r="Q192" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R192" s="136"/>
-      <c r="S192" s="135" t="s">
+      <c r="R192" s="129"/>
+      <c r="S192" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T192" s="136"/>
-      <c r="U192" s="135" t="s">
+      <c r="T192" s="129"/>
+      <c r="U192" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V192" s="136"/>
+      <c r="V192" s="129"/>
       <c r="W192" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X192" s="117"/>
-      <c r="Y192" s="132" t="s">
+      <c r="Y192" s="243" t="s">
         <v>208</v>
       </c>
-      <c r="Z192" s="133"/>
-      <c r="AA192" s="134"/>
+      <c r="Z192" s="244"/>
+      <c r="AA192" s="245"/>
       <c r="AB192" s="101"/>
       <c r="AC192" s="101"/>
       <c r="AD192" s="102"/>
@@ -30434,35 +30433,35 @@
       <c r="AN192"/>
     </row>
     <row r="193" spans="2:40" s="105" customFormat="1" ht="255" x14ac:dyDescent="3.65">
-      <c r="B193" s="138"/>
-      <c r="C193" s="244"/>
-      <c r="D193" s="244"/>
-      <c r="E193" s="244"/>
-      <c r="F193" s="244"/>
-      <c r="G193" s="244"/>
-      <c r="H193" s="244"/>
-      <c r="I193" s="244"/>
-      <c r="J193" s="244"/>
-      <c r="K193" s="244"/>
-      <c r="L193" s="244"/>
-      <c r="M193" s="244"/>
-      <c r="N193" s="244"/>
-      <c r="O193" s="244"/>
-      <c r="P193" s="244"/>
-      <c r="Q193" s="244"/>
-      <c r="R193" s="244"/>
-      <c r="S193" s="244"/>
-      <c r="T193" s="244"/>
-      <c r="U193" s="244"/>
-      <c r="V193" s="244"/>
-      <c r="W193" s="245"/>
+      <c r="B193" s="236"/>
+      <c r="C193" s="237"/>
+      <c r="D193" s="237"/>
+      <c r="E193" s="237"/>
+      <c r="F193" s="237"/>
+      <c r="G193" s="237"/>
+      <c r="H193" s="237"/>
+      <c r="I193" s="237"/>
+      <c r="J193" s="237"/>
+      <c r="K193" s="237"/>
+      <c r="L193" s="237"/>
+      <c r="M193" s="237"/>
+      <c r="N193" s="237"/>
+      <c r="O193" s="237"/>
+      <c r="P193" s="237"/>
+      <c r="Q193" s="237"/>
+      <c r="R193" s="237"/>
+      <c r="S193" s="237"/>
+      <c r="T193" s="237"/>
+      <c r="U193" s="237"/>
+      <c r="V193" s="237"/>
+      <c r="W193" s="127"/>
       <c r="X193" s="123"/>
-      <c r="Y193" s="127">
+      <c r="Y193" s="238">
         <f>SUM(C193:W193)</f>
         <v>0</v>
       </c>
-      <c r="Z193" s="128"/>
-      <c r="AA193" s="129"/>
+      <c r="Z193" s="239"/>
+      <c r="AA193" s="240"/>
       <c r="AB193" s="103"/>
       <c r="AC193" s="103"/>
       <c r="AD193" s="104"/>
@@ -30478,10 +30477,10 @@
       <c r="AN193" s="2"/>
     </row>
     <row r="195" spans="2:40" x14ac:dyDescent="2.35">
-      <c r="C195" s="130"/>
-      <c r="D195" s="130"/>
-      <c r="O195" s="131"/>
-      <c r="P195" s="131"/>
+      <c r="C195" s="241"/>
+      <c r="D195" s="241"/>
+      <c r="O195" s="242"/>
+      <c r="P195" s="242"/>
       <c r="R195" s="107"/>
       <c r="AA195" s="108"/>
     </row>
@@ -30490,24 +30489,306 @@
     </row>
   </sheetData>
   <mergeCells count="342">
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="B1:AD1"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y193:AA193"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="O195:P195"/>
+    <mergeCell ref="Y192:AA192"/>
+    <mergeCell ref="C193:D193"/>
+    <mergeCell ref="E193:F193"/>
+    <mergeCell ref="G193:H193"/>
+    <mergeCell ref="I193:J193"/>
+    <mergeCell ref="K193:L193"/>
+    <mergeCell ref="M193:N193"/>
+    <mergeCell ref="O193:P193"/>
+    <mergeCell ref="Q193:R193"/>
+    <mergeCell ref="M192:N192"/>
+    <mergeCell ref="O192:P192"/>
+    <mergeCell ref="Q192:R192"/>
+    <mergeCell ref="S192:T192"/>
+    <mergeCell ref="U192:V192"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="G192:H192"/>
+    <mergeCell ref="I192:J192"/>
+    <mergeCell ref="K192:L192"/>
+    <mergeCell ref="Q190:R190"/>
+    <mergeCell ref="S190:T190"/>
+    <mergeCell ref="U190:V190"/>
+    <mergeCell ref="S193:T193"/>
+    <mergeCell ref="U193:V193"/>
+    <mergeCell ref="AB190:AC190"/>
+    <mergeCell ref="Y191:Z191"/>
+    <mergeCell ref="AB191:AC191"/>
+    <mergeCell ref="Y189:Z189"/>
+    <mergeCell ref="AB189:AC189"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="E190:F190"/>
+    <mergeCell ref="G190:H190"/>
+    <mergeCell ref="I190:J190"/>
+    <mergeCell ref="K190:L190"/>
+    <mergeCell ref="M190:N190"/>
+    <mergeCell ref="O190:P190"/>
+    <mergeCell ref="M189:N189"/>
+    <mergeCell ref="O189:P189"/>
+    <mergeCell ref="Q189:R189"/>
+    <mergeCell ref="S189:T189"/>
+    <mergeCell ref="U189:V189"/>
+    <mergeCell ref="Y190:Z190"/>
+    <mergeCell ref="C189:D189"/>
+    <mergeCell ref="E189:F189"/>
+    <mergeCell ref="G189:H189"/>
+    <mergeCell ref="I189:J189"/>
+    <mergeCell ref="K189:L189"/>
+    <mergeCell ref="Y187:Z187"/>
+    <mergeCell ref="AB187:AC187"/>
+    <mergeCell ref="C188:D188"/>
+    <mergeCell ref="E188:F188"/>
+    <mergeCell ref="G188:H188"/>
+    <mergeCell ref="I188:J188"/>
+    <mergeCell ref="K188:L188"/>
+    <mergeCell ref="M188:N188"/>
+    <mergeCell ref="O188:P188"/>
+    <mergeCell ref="S188:T188"/>
+    <mergeCell ref="U188:V188"/>
+    <mergeCell ref="Y188:Z188"/>
+    <mergeCell ref="AB188:AC188"/>
+    <mergeCell ref="Q188:R188"/>
+    <mergeCell ref="Y184:Z184"/>
+    <mergeCell ref="AB184:AC184"/>
+    <mergeCell ref="Y185:Z185"/>
+    <mergeCell ref="AB185:AC185"/>
+    <mergeCell ref="Y186:Z186"/>
+    <mergeCell ref="AB186:AC186"/>
+    <mergeCell ref="Y180:Z180"/>
+    <mergeCell ref="AB180:AC180"/>
+    <mergeCell ref="Y181:Z181"/>
+    <mergeCell ref="AB181:AC181"/>
+    <mergeCell ref="Y183:Z183"/>
+    <mergeCell ref="AB183:AC183"/>
+    <mergeCell ref="Y182:Z182"/>
+    <mergeCell ref="Y177:Z177"/>
+    <mergeCell ref="AB177:AC177"/>
+    <mergeCell ref="Y178:Z178"/>
+    <mergeCell ref="AB178:AC178"/>
+    <mergeCell ref="AG178:AI178"/>
+    <mergeCell ref="Y179:Z179"/>
+    <mergeCell ref="AB179:AC179"/>
+    <mergeCell ref="Y174:Z174"/>
+    <mergeCell ref="AB174:AC174"/>
+    <mergeCell ref="Y175:Z175"/>
+    <mergeCell ref="AB175:AC175"/>
+    <mergeCell ref="Y176:Z176"/>
+    <mergeCell ref="AB176:AC176"/>
+    <mergeCell ref="Y169:Z169"/>
+    <mergeCell ref="Y170:Z170"/>
+    <mergeCell ref="Y171:Z171"/>
+    <mergeCell ref="Y172:Z172"/>
+    <mergeCell ref="AB172:AC172"/>
+    <mergeCell ref="Y173:Z173"/>
+    <mergeCell ref="AB173:AC173"/>
+    <mergeCell ref="Y163:Z163"/>
+    <mergeCell ref="AB163:AC163"/>
+    <mergeCell ref="Y164:Z164"/>
+    <mergeCell ref="AB164:AC171"/>
+    <mergeCell ref="AF164:AJ167"/>
+    <mergeCell ref="Y165:Z165"/>
+    <mergeCell ref="Y166:Z166"/>
+    <mergeCell ref="Y167:Z167"/>
+    <mergeCell ref="Y168:Z168"/>
+    <mergeCell ref="AF168:AJ168"/>
+    <mergeCell ref="M163:N163"/>
+    <mergeCell ref="O163:P163"/>
+    <mergeCell ref="Q163:R163"/>
+    <mergeCell ref="S163:T163"/>
+    <mergeCell ref="U163:V163"/>
+    <mergeCell ref="AB157:AC162"/>
+    <mergeCell ref="C163:D163"/>
+    <mergeCell ref="E163:F163"/>
+    <mergeCell ref="G163:H163"/>
+    <mergeCell ref="I163:J163"/>
+    <mergeCell ref="K163:L163"/>
+    <mergeCell ref="M155:N155"/>
+    <mergeCell ref="O155:P155"/>
+    <mergeCell ref="Q155:R155"/>
+    <mergeCell ref="S155:T155"/>
+    <mergeCell ref="U155:V155"/>
+    <mergeCell ref="W155:W156"/>
+    <mergeCell ref="C141:D141"/>
+    <mergeCell ref="E141:F141"/>
+    <mergeCell ref="G141:H141"/>
+    <mergeCell ref="I141:J141"/>
+    <mergeCell ref="K141:L141"/>
+    <mergeCell ref="AB142:AC152"/>
+    <mergeCell ref="AB153:AC153"/>
+    <mergeCell ref="B154:AD154"/>
+    <mergeCell ref="B155:B156"/>
+    <mergeCell ref="C155:D155"/>
+    <mergeCell ref="E155:F155"/>
+    <mergeCell ref="G155:H155"/>
+    <mergeCell ref="I155:J155"/>
+    <mergeCell ref="K155:L155"/>
+    <mergeCell ref="Y155:Y156"/>
+    <mergeCell ref="Z155:Z156"/>
+    <mergeCell ref="AA155:AA156"/>
+    <mergeCell ref="AB155:AC155"/>
+    <mergeCell ref="AB139:AC140"/>
+    <mergeCell ref="AF136:AJ136"/>
+    <mergeCell ref="AB137:AC137"/>
+    <mergeCell ref="AF137:AJ137"/>
+    <mergeCell ref="M141:N141"/>
+    <mergeCell ref="O141:P141"/>
+    <mergeCell ref="Q141:R141"/>
+    <mergeCell ref="S141:T141"/>
+    <mergeCell ref="U141:V141"/>
+    <mergeCell ref="AB141:AC141"/>
+    <mergeCell ref="C138:D138"/>
+    <mergeCell ref="E138:F138"/>
+    <mergeCell ref="G138:H138"/>
+    <mergeCell ref="I138:J138"/>
+    <mergeCell ref="K138:L138"/>
+    <mergeCell ref="M138:N138"/>
+    <mergeCell ref="AB107:AC111"/>
+    <mergeCell ref="AF111:AJ111"/>
+    <mergeCell ref="AB112:AC125"/>
+    <mergeCell ref="AF112:AJ117"/>
+    <mergeCell ref="O138:P138"/>
+    <mergeCell ref="Q138:R138"/>
+    <mergeCell ref="S138:T138"/>
+    <mergeCell ref="U138:V138"/>
+    <mergeCell ref="AB138:AC138"/>
+    <mergeCell ref="AK113:AL137"/>
+    <mergeCell ref="AF118:AJ118"/>
+    <mergeCell ref="AF119:AJ119"/>
+    <mergeCell ref="AB126:AC136"/>
+    <mergeCell ref="AF126:AJ127"/>
+    <mergeCell ref="AF129:AJ129"/>
+    <mergeCell ref="U105:V105"/>
+    <mergeCell ref="W105:W106"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="Z105:Z106"/>
+    <mergeCell ref="AA105:AA106"/>
+    <mergeCell ref="AB105:AC105"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="M105:N105"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="Q105:R105"/>
+    <mergeCell ref="S105:T105"/>
+    <mergeCell ref="AF98:AJ98"/>
+    <mergeCell ref="AF100:AJ100"/>
+    <mergeCell ref="AB103:AC103"/>
+    <mergeCell ref="AF103:AJ107"/>
+    <mergeCell ref="B104:AD104"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="U87:V87"/>
+    <mergeCell ref="AB87:AC87"/>
+    <mergeCell ref="AK87:AL112"/>
+    <mergeCell ref="AB88:AC88"/>
+    <mergeCell ref="AB90:AC90"/>
+    <mergeCell ref="AB91:AC91"/>
+    <mergeCell ref="AB92:AC92"/>
+    <mergeCell ref="AB93:AC102"/>
+    <mergeCell ref="AF93:AJ97"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="Q87:R87"/>
+    <mergeCell ref="S87:T87"/>
+    <mergeCell ref="AF78:AJ78"/>
+    <mergeCell ref="AF79:AJ79"/>
+    <mergeCell ref="AB80:AC81"/>
+    <mergeCell ref="AF80:AJ80"/>
+    <mergeCell ref="AK80:AL86"/>
+    <mergeCell ref="AF81:AJ81"/>
+    <mergeCell ref="AB82:AC82"/>
+    <mergeCell ref="AB83:AC83"/>
+    <mergeCell ref="AB84:AC84"/>
+    <mergeCell ref="AB85:AC85"/>
+    <mergeCell ref="AK71:AL78"/>
+    <mergeCell ref="AF72:AJ72"/>
+    <mergeCell ref="AB73:AC73"/>
+    <mergeCell ref="AB74:AC75"/>
+    <mergeCell ref="AF74:AJ74"/>
+    <mergeCell ref="AF75:AJ75"/>
+    <mergeCell ref="AB76:AC77"/>
+    <mergeCell ref="AF76:AJ76"/>
+    <mergeCell ref="AF77:AJ77"/>
+    <mergeCell ref="AB78:AC79"/>
+    <mergeCell ref="AB86:AC86"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="S70:T70"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="AB70:AC70"/>
+    <mergeCell ref="AB71:AC72"/>
+    <mergeCell ref="AF71:AJ71"/>
+    <mergeCell ref="AB68:AC68"/>
+    <mergeCell ref="AB69:AC69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="O70:P70"/>
+    <mergeCell ref="AB62:AC67"/>
+    <mergeCell ref="AF63:AJ63"/>
+    <mergeCell ref="AF64:AJ64"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="S60:T60"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="W60:W61"/>
+    <mergeCell ref="AB55:AC55"/>
+    <mergeCell ref="AC57:AC58"/>
+    <mergeCell ref="AB59:AC59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="Y60:Y61"/>
+    <mergeCell ref="Z60:Z61"/>
+    <mergeCell ref="AA60:AA61"/>
+    <mergeCell ref="AB60:AC60"/>
+    <mergeCell ref="AB48:AC51"/>
+    <mergeCell ref="AB54:AC54"/>
+    <mergeCell ref="AB42:AC47"/>
+    <mergeCell ref="AF42:AJ42"/>
+    <mergeCell ref="AF47:AJ47"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="AB40:AC40"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="AB33:AC34"/>
+    <mergeCell ref="AF33:AJ33"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AB24:AC25"/>
+    <mergeCell ref="AF24:AJ24"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AB36:AC37"/>
+    <mergeCell ref="AF36:AJ36"/>
+    <mergeCell ref="AF37:AJ37"/>
+    <mergeCell ref="AB38:AC38"/>
+    <mergeCell ref="AB39:AC39"/>
     <mergeCell ref="Z4:Z8"/>
     <mergeCell ref="AC4:AC8"/>
     <mergeCell ref="AF4:AJ6"/>
@@ -30532,306 +30813,24 @@
     <mergeCell ref="AB30:AC31"/>
     <mergeCell ref="AF30:AJ30"/>
     <mergeCell ref="AF31:AJ31"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="AB33:AC34"/>
-    <mergeCell ref="AF33:AJ33"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AB24:AC25"/>
-    <mergeCell ref="AF24:AJ24"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AB36:AC37"/>
-    <mergeCell ref="AF36:AJ36"/>
-    <mergeCell ref="AF37:AJ37"/>
-    <mergeCell ref="AB38:AC38"/>
-    <mergeCell ref="AB39:AC39"/>
-    <mergeCell ref="AB48:AC51"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="AB42:AC47"/>
-    <mergeCell ref="AF42:AJ42"/>
-    <mergeCell ref="AF47:AJ47"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="AB40:AC40"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="AC57:AC58"/>
-    <mergeCell ref="AB59:AC59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="Y60:Y61"/>
-    <mergeCell ref="Z60:Z61"/>
-    <mergeCell ref="AA60:AA61"/>
-    <mergeCell ref="AB60:AC60"/>
-    <mergeCell ref="AB62:AC67"/>
-    <mergeCell ref="AF63:AJ63"/>
-    <mergeCell ref="AF64:AJ64"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:R60"/>
-    <mergeCell ref="S60:T60"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="W60:W61"/>
-    <mergeCell ref="Q70:R70"/>
-    <mergeCell ref="S70:T70"/>
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="AB70:AC70"/>
-    <mergeCell ref="AB71:AC72"/>
-    <mergeCell ref="AF71:AJ71"/>
-    <mergeCell ref="AB68:AC68"/>
-    <mergeCell ref="AB69:AC69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="M70:N70"/>
-    <mergeCell ref="O70:P70"/>
-    <mergeCell ref="AF78:AJ78"/>
-    <mergeCell ref="AF79:AJ79"/>
-    <mergeCell ref="AB80:AC81"/>
-    <mergeCell ref="AF80:AJ80"/>
-    <mergeCell ref="AK80:AL86"/>
-    <mergeCell ref="AF81:AJ81"/>
-    <mergeCell ref="AB82:AC82"/>
-    <mergeCell ref="AB83:AC83"/>
-    <mergeCell ref="AB84:AC84"/>
-    <mergeCell ref="AB85:AC85"/>
-    <mergeCell ref="AK71:AL78"/>
-    <mergeCell ref="AF72:AJ72"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AB74:AC75"/>
-    <mergeCell ref="AF74:AJ74"/>
-    <mergeCell ref="AF75:AJ75"/>
-    <mergeCell ref="AB76:AC77"/>
-    <mergeCell ref="AF76:AJ76"/>
-    <mergeCell ref="AF77:AJ77"/>
-    <mergeCell ref="AB78:AC79"/>
-    <mergeCell ref="AB86:AC86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="M87:N87"/>
-    <mergeCell ref="O87:P87"/>
-    <mergeCell ref="Q87:R87"/>
-    <mergeCell ref="S87:T87"/>
-    <mergeCell ref="U87:V87"/>
-    <mergeCell ref="AB87:AC87"/>
-    <mergeCell ref="AK87:AL112"/>
-    <mergeCell ref="AB88:AC88"/>
-    <mergeCell ref="AB90:AC90"/>
-    <mergeCell ref="AB91:AC91"/>
-    <mergeCell ref="AB92:AC92"/>
-    <mergeCell ref="AB93:AC102"/>
-    <mergeCell ref="AF93:AJ97"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="M105:N105"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="Q105:R105"/>
-    <mergeCell ref="S105:T105"/>
-    <mergeCell ref="AF98:AJ98"/>
-    <mergeCell ref="AF100:AJ100"/>
-    <mergeCell ref="AB103:AC103"/>
-    <mergeCell ref="AF103:AJ107"/>
-    <mergeCell ref="B104:AD104"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="AK113:AL137"/>
-    <mergeCell ref="AF118:AJ118"/>
-    <mergeCell ref="AF119:AJ119"/>
-    <mergeCell ref="AB126:AC136"/>
-    <mergeCell ref="AF126:AJ127"/>
-    <mergeCell ref="AF129:AJ129"/>
-    <mergeCell ref="U105:V105"/>
-    <mergeCell ref="W105:W106"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="Z105:Z106"/>
-    <mergeCell ref="AA105:AA106"/>
-    <mergeCell ref="AB105:AC105"/>
-    <mergeCell ref="C138:D138"/>
-    <mergeCell ref="E138:F138"/>
-    <mergeCell ref="G138:H138"/>
-    <mergeCell ref="I138:J138"/>
-    <mergeCell ref="K138:L138"/>
-    <mergeCell ref="M138:N138"/>
-    <mergeCell ref="AB107:AC111"/>
-    <mergeCell ref="AF111:AJ111"/>
-    <mergeCell ref="AB112:AC125"/>
-    <mergeCell ref="AF112:AJ117"/>
-    <mergeCell ref="O138:P138"/>
-    <mergeCell ref="Q138:R138"/>
-    <mergeCell ref="S138:T138"/>
-    <mergeCell ref="U138:V138"/>
-    <mergeCell ref="AB138:AC138"/>
-    <mergeCell ref="AB139:AC140"/>
-    <mergeCell ref="AF136:AJ136"/>
-    <mergeCell ref="AB137:AC137"/>
-    <mergeCell ref="AF137:AJ137"/>
-    <mergeCell ref="M141:N141"/>
-    <mergeCell ref="O141:P141"/>
-    <mergeCell ref="Q141:R141"/>
-    <mergeCell ref="S141:T141"/>
-    <mergeCell ref="U141:V141"/>
-    <mergeCell ref="AB141:AC141"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="E141:F141"/>
-    <mergeCell ref="G141:H141"/>
-    <mergeCell ref="I141:J141"/>
-    <mergeCell ref="K141:L141"/>
-    <mergeCell ref="AB142:AC152"/>
-    <mergeCell ref="AB153:AC153"/>
-    <mergeCell ref="B154:AD154"/>
-    <mergeCell ref="B155:B156"/>
-    <mergeCell ref="C155:D155"/>
-    <mergeCell ref="E155:F155"/>
-    <mergeCell ref="G155:H155"/>
-    <mergeCell ref="I155:J155"/>
-    <mergeCell ref="K155:L155"/>
-    <mergeCell ref="Y155:Y156"/>
-    <mergeCell ref="Z155:Z156"/>
-    <mergeCell ref="AA155:AA156"/>
-    <mergeCell ref="AB155:AC155"/>
-    <mergeCell ref="AB157:AC162"/>
-    <mergeCell ref="C163:D163"/>
-    <mergeCell ref="E163:F163"/>
-    <mergeCell ref="G163:H163"/>
-    <mergeCell ref="I163:J163"/>
-    <mergeCell ref="K163:L163"/>
-    <mergeCell ref="M155:N155"/>
-    <mergeCell ref="O155:P155"/>
-    <mergeCell ref="Q155:R155"/>
-    <mergeCell ref="S155:T155"/>
-    <mergeCell ref="U155:V155"/>
-    <mergeCell ref="W155:W156"/>
-    <mergeCell ref="AF164:AJ167"/>
-    <mergeCell ref="Y165:Z165"/>
-    <mergeCell ref="Y166:Z166"/>
-    <mergeCell ref="Y167:Z167"/>
-    <mergeCell ref="Y168:Z168"/>
-    <mergeCell ref="AF168:AJ168"/>
-    <mergeCell ref="M163:N163"/>
-    <mergeCell ref="O163:P163"/>
-    <mergeCell ref="Q163:R163"/>
-    <mergeCell ref="S163:T163"/>
-    <mergeCell ref="U163:V163"/>
-    <mergeCell ref="Y169:Z169"/>
-    <mergeCell ref="Y170:Z170"/>
-    <mergeCell ref="Y171:Z171"/>
-    <mergeCell ref="Y172:Z172"/>
-    <mergeCell ref="AB172:AC172"/>
-    <mergeCell ref="Y173:Z173"/>
-    <mergeCell ref="AB173:AC173"/>
-    <mergeCell ref="Y163:Z163"/>
-    <mergeCell ref="AB163:AC163"/>
-    <mergeCell ref="Y164:Z164"/>
-    <mergeCell ref="AB164:AC171"/>
-    <mergeCell ref="Y177:Z177"/>
-    <mergeCell ref="AB177:AC177"/>
-    <mergeCell ref="Y178:Z178"/>
-    <mergeCell ref="AB178:AC178"/>
-    <mergeCell ref="AG178:AI178"/>
-    <mergeCell ref="Y179:Z179"/>
-    <mergeCell ref="AB179:AC179"/>
-    <mergeCell ref="Y174:Z174"/>
-    <mergeCell ref="AB174:AC174"/>
-    <mergeCell ref="Y175:Z175"/>
-    <mergeCell ref="AB175:AC175"/>
-    <mergeCell ref="Y176:Z176"/>
-    <mergeCell ref="AB176:AC176"/>
-    <mergeCell ref="Y184:Z184"/>
-    <mergeCell ref="AB184:AC184"/>
-    <mergeCell ref="Y185:Z185"/>
-    <mergeCell ref="AB185:AC185"/>
-    <mergeCell ref="Y186:Z186"/>
-    <mergeCell ref="AB186:AC186"/>
-    <mergeCell ref="Y180:Z180"/>
-    <mergeCell ref="AB180:AC180"/>
-    <mergeCell ref="Y181:Z181"/>
-    <mergeCell ref="AB181:AC181"/>
-    <mergeCell ref="Y183:Z183"/>
-    <mergeCell ref="AB183:AC183"/>
-    <mergeCell ref="Y182:Z182"/>
-    <mergeCell ref="Y187:Z187"/>
-    <mergeCell ref="AB187:AC187"/>
-    <mergeCell ref="C188:D188"/>
-    <mergeCell ref="E188:F188"/>
-    <mergeCell ref="G188:H188"/>
-    <mergeCell ref="I188:J188"/>
-    <mergeCell ref="K188:L188"/>
-    <mergeCell ref="M188:N188"/>
-    <mergeCell ref="O188:P188"/>
-    <mergeCell ref="S188:T188"/>
-    <mergeCell ref="U188:V188"/>
-    <mergeCell ref="Y188:Z188"/>
-    <mergeCell ref="AB188:AC188"/>
-    <mergeCell ref="Q188:R188"/>
-    <mergeCell ref="AB190:AC190"/>
-    <mergeCell ref="Y191:Z191"/>
-    <mergeCell ref="AB191:AC191"/>
-    <mergeCell ref="Y189:Z189"/>
-    <mergeCell ref="AB189:AC189"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="E190:F190"/>
-    <mergeCell ref="G190:H190"/>
-    <mergeCell ref="I190:J190"/>
-    <mergeCell ref="K190:L190"/>
-    <mergeCell ref="M190:N190"/>
-    <mergeCell ref="O190:P190"/>
-    <mergeCell ref="M189:N189"/>
-    <mergeCell ref="O189:P189"/>
-    <mergeCell ref="Q189:R189"/>
-    <mergeCell ref="S189:T189"/>
-    <mergeCell ref="U189:V189"/>
-    <mergeCell ref="Y190:Z190"/>
-    <mergeCell ref="C189:D189"/>
-    <mergeCell ref="E189:F189"/>
-    <mergeCell ref="G189:H189"/>
-    <mergeCell ref="I189:J189"/>
-    <mergeCell ref="K189:L189"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="E192:F192"/>
-    <mergeCell ref="G192:H192"/>
-    <mergeCell ref="I192:J192"/>
-    <mergeCell ref="K192:L192"/>
-    <mergeCell ref="Q190:R190"/>
-    <mergeCell ref="S190:T190"/>
-    <mergeCell ref="U190:V190"/>
-    <mergeCell ref="S193:T193"/>
-    <mergeCell ref="U193:V193"/>
-    <mergeCell ref="Y193:AA193"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="O195:P195"/>
-    <mergeCell ref="Y192:AA192"/>
-    <mergeCell ref="C193:D193"/>
-    <mergeCell ref="E193:F193"/>
-    <mergeCell ref="G193:H193"/>
-    <mergeCell ref="I193:J193"/>
-    <mergeCell ref="K193:L193"/>
-    <mergeCell ref="M193:N193"/>
-    <mergeCell ref="O193:P193"/>
-    <mergeCell ref="Q193:R193"/>
-    <mergeCell ref="M192:N192"/>
-    <mergeCell ref="O192:P192"/>
-    <mergeCell ref="Q192:R192"/>
-    <mergeCell ref="S192:T192"/>
-    <mergeCell ref="U192:V192"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="B1:AD1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <pageMargins left="1.1023622047244095" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="10" orientation="landscape" verticalDpi="0" r:id="rId1"/>
@@ -30843,19 +30842,4 @@
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAC23D8A-2430-4671-8DAB-D122AE188670}">
-  <dimension ref="D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="7" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D7">
-        <v>2342343</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/base/base_0.xlsx
+++ b/base/base_0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\ELIECER\scripts\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26BA4343-88E6-4E91-A678-7D331879CE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF420D7-B9D7-4B35-B53F-2519F899B784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="219">
   <si>
     <t xml:space="preserve">       VENTAS DIARIAS POR PRODUCTO DEL 18,19,20 DE SEPTIEMBRE DEL 2026</t>
   </si>
@@ -680,6 +680,18 @@
   <si>
     <t>TORTA 12 PX S/AZÚCAR</t>
   </si>
+  <si>
+    <t>TARTALETA 12PX N</t>
+  </si>
+  <si>
+    <t>TARTALETA 12PX S/A</t>
+  </si>
+  <si>
+    <t>TARTALETA 18PX N</t>
+  </si>
+  <si>
+    <t>TARTALETA 18PX S/A</t>
+  </si>
 </sst>
 </file>
 
@@ -1142,7 +1154,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1455,44 +1467,23 @@
     <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1500,61 +1491,82 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1569,26 +1581,29 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1608,32 +1623,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1641,34 +1632,55 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1704,116 +1716,110 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12917,103 +12923,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B1" s="171" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="172"/>
-      <c r="D1" s="172"/>
-      <c r="E1" s="172"/>
-      <c r="F1" s="172"/>
-      <c r="G1" s="172"/>
-      <c r="H1" s="172"/>
-      <c r="I1" s="172"/>
-      <c r="J1" s="172"/>
-      <c r="K1" s="172"/>
-      <c r="L1" s="172"/>
-      <c r="M1" s="172"/>
-      <c r="N1" s="172"/>
-      <c r="O1" s="172"/>
-      <c r="P1" s="172"/>
-      <c r="Q1" s="172"/>
-      <c r="R1" s="172"/>
-      <c r="S1" s="172"/>
-      <c r="T1" s="172"/>
-      <c r="U1" s="172"/>
-      <c r="V1" s="172"/>
-      <c r="W1" s="172"/>
-      <c r="X1" s="172"/>
-      <c r="Y1" s="172"/>
-      <c r="Z1" s="172"/>
-      <c r="AA1" s="172"/>
-      <c r="AB1" s="172"/>
-      <c r="AC1" s="172"/>
-      <c r="AD1" s="172"/>
+      <c r="B1" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
+      <c r="I1" s="133"/>
+      <c r="J1" s="133"/>
+      <c r="K1" s="133"/>
+      <c r="L1" s="133"/>
+      <c r="M1" s="133"/>
+      <c r="N1" s="133"/>
+      <c r="O1" s="133"/>
+      <c r="P1" s="133"/>
+      <c r="Q1" s="133"/>
+      <c r="R1" s="133"/>
+      <c r="S1" s="133"/>
+      <c r="T1" s="133"/>
+      <c r="U1" s="133"/>
+      <c r="V1" s="133"/>
+      <c r="W1" s="133"/>
+      <c r="X1" s="133"/>
+      <c r="Y1" s="133"/>
+      <c r="Z1" s="133"/>
+      <c r="AA1" s="133"/>
+      <c r="AB1" s="133"/>
+      <c r="AC1" s="133"/>
+      <c r="AD1" s="133"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B2" s="169" t="s">
+      <c r="B2" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="137" t="s">
+      <c r="C2" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="138"/>
-      <c r="E2" s="137" t="s">
+      <c r="D2" s="129"/>
+      <c r="E2" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="138"/>
-      <c r="G2" s="137" t="s">
+      <c r="F2" s="129"/>
+      <c r="G2" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="138"/>
-      <c r="I2" s="137" t="s">
+      <c r="H2" s="129"/>
+      <c r="I2" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="138"/>
-      <c r="K2" s="137" t="s">
+      <c r="J2" s="129"/>
+      <c r="K2" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="138"/>
-      <c r="M2" s="137" t="s">
+      <c r="L2" s="129"/>
+      <c r="M2" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="138"/>
-      <c r="O2" s="137" t="s">
+      <c r="N2" s="129"/>
+      <c r="O2" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="138"/>
-      <c r="Q2" s="137" t="s">
+      <c r="P2" s="129"/>
+      <c r="Q2" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R2" s="138"/>
-      <c r="S2" s="137" t="s">
+      <c r="R2" s="129"/>
+      <c r="S2" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T2" s="138"/>
-      <c r="U2" s="137" t="s">
+      <c r="T2" s="129"/>
+      <c r="U2" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V2" s="138"/>
-      <c r="W2" s="169" t="s">
+      <c r="V2" s="129"/>
+      <c r="W2" s="130" t="s">
         <v>12</v>
       </c>
-      <c r="X2" s="244" t="s">
+      <c r="X2" s="136" t="s">
         <v>209</v>
       </c>
-      <c r="Y2" s="169" t="s">
+      <c r="Y2" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z2" s="169" t="s">
+      <c r="Z2" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="169" t="s">
+      <c r="AA2" s="130" t="s">
         <v>1</v>
       </c>
-      <c r="AB2" s="141" t="s">
+      <c r="AB2" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="AC2" s="142"/>
+      <c r="AC2" s="135"/>
       <c r="AD2" s="6" t="s">
         <v>16</v>
       </c>
@@ -13027,7 +13033,7 @@
       <c r="AL2" s="8"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B3" s="170"/>
+      <c r="B3" s="131"/>
       <c r="C3" s="9" t="s">
         <v>17</v>
       </c>
@@ -13088,11 +13094,11 @@
       <c r="V3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="170"/>
-      <c r="X3" s="245"/>
-      <c r="Y3" s="170"/>
-      <c r="Z3" s="170"/>
-      <c r="AA3" s="170"/>
+      <c r="W3" s="131"/>
+      <c r="X3" s="137"/>
+      <c r="Y3" s="131"/>
+      <c r="Z3" s="131"/>
+      <c r="AA3" s="131"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="11"/>
       <c r="AD3" s="6"/>
@@ -13179,14 +13185,14 @@
         <f>SUM(C4,E4,G4,I4,K4,,M4,O4,Q4,S4,U4,W4)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="228">
+      <c r="Z4" s="138">
         <f>SUM(D9,F9,H9,J9,L9,,N9,P9,R9,T9,V9)</f>
         <v>0</v>
       </c>
       <c r="AA4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AC4" s="157">
+      <c r="AC4" s="141">
         <f>SUM(Y4,AB5,AB6,AB7,AB8)</f>
         <v>0</v>
       </c>
@@ -13195,18 +13201,18 @@
         <v>0</v>
       </c>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="190" t="s">
+      <c r="AF4" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="AG4" s="191"/>
-      <c r="AH4" s="191"/>
-      <c r="AI4" s="191"/>
-      <c r="AJ4" s="192"/>
-      <c r="AK4" s="231">
+      <c r="AG4" s="145"/>
+      <c r="AH4" s="145"/>
+      <c r="AI4" s="145"/>
+      <c r="AJ4" s="146"/>
+      <c r="AK4" s="150">
         <f>SUM(AD4:AD59)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="232"/>
+      <c r="AL4" s="151"/>
     </row>
     <row r="5" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B5" s="13" t="s">
@@ -13262,7 +13268,7 @@
         <f>SUM(C5:W5)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="229"/>
+      <c r="Z5" s="139"/>
       <c r="AA5" s="13" t="s">
         <v>21</v>
       </c>
@@ -13270,19 +13276,19 @@
         <f>Y5*4</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="159"/>
+      <c r="AC5" s="142"/>
       <c r="AD5" s="16">
         <f>X5</f>
         <v>0</v>
       </c>
       <c r="AE5" s="17"/>
-      <c r="AF5" s="193"/>
-      <c r="AG5" s="194"/>
-      <c r="AH5" s="194"/>
-      <c r="AI5" s="194"/>
-      <c r="AJ5" s="195"/>
-      <c r="AK5" s="233"/>
-      <c r="AL5" s="232"/>
+      <c r="AF5" s="147"/>
+      <c r="AG5" s="148"/>
+      <c r="AH5" s="148"/>
+      <c r="AI5" s="148"/>
+      <c r="AJ5" s="149"/>
+      <c r="AK5" s="152"/>
+      <c r="AL5" s="151"/>
     </row>
     <row r="6" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B6" s="13" t="s">
@@ -13338,7 +13344,7 @@
         <f>SUM(C6:W6)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="229"/>
+      <c r="Z6" s="139"/>
       <c r="AA6" s="15" t="s">
         <v>23</v>
       </c>
@@ -13346,19 +13352,19 @@
         <f>Y6*8</f>
         <v>0</v>
       </c>
-      <c r="AC6" s="159"/>
+      <c r="AC6" s="142"/>
       <c r="AD6" s="16">
         <f t="shared" ref="AD6:AD7" si="0">X6</f>
         <v>0</v>
       </c>
       <c r="AE6" s="17"/>
-      <c r="AF6" s="193"/>
-      <c r="AG6" s="194"/>
-      <c r="AH6" s="194"/>
-      <c r="AI6" s="194"/>
-      <c r="AJ6" s="195"/>
-      <c r="AK6" s="233"/>
-      <c r="AL6" s="232"/>
+      <c r="AF6" s="147"/>
+      <c r="AG6" s="148"/>
+      <c r="AH6" s="148"/>
+      <c r="AI6" s="148"/>
+      <c r="AJ6" s="149"/>
+      <c r="AK6" s="152"/>
+      <c r="AL6" s="151"/>
     </row>
     <row r="7" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B7" s="13" t="s">
@@ -13414,7 +13420,7 @@
         <f>SUM(C7:W7)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="229"/>
+      <c r="Z7" s="139"/>
       <c r="AA7" s="15" t="s">
         <v>25</v>
       </c>
@@ -13422,22 +13428,22 @@
         <f>Y7*12</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="159"/>
+      <c r="AC7" s="142"/>
       <c r="AD7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE7" s="17"/>
-      <c r="AF7" s="168">
+      <c r="AF7" s="153">
         <f>SUM(AD4:AD8)</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="166"/>
-      <c r="AH7" s="166"/>
-      <c r="AI7" s="166"/>
-      <c r="AJ7" s="167"/>
-      <c r="AK7" s="233"/>
-      <c r="AL7" s="232"/>
+      <c r="AG7" s="154"/>
+      <c r="AH7" s="154"/>
+      <c r="AI7" s="154"/>
+      <c r="AJ7" s="155"/>
+      <c r="AK7" s="152"/>
+      <c r="AL7" s="151"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B8" s="13" t="s">
@@ -13493,7 +13499,7 @@
         <f>SUM(C8:W8)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="230"/>
+      <c r="Z8" s="140"/>
       <c r="AA8" s="15" t="s">
         <v>27</v>
       </c>
@@ -13501,7 +13507,7 @@
         <f>Y8*16</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="161"/>
+      <c r="AC8" s="143"/>
       <c r="AD8" s="16">
         <f>X8</f>
         <v>0</v>
@@ -13512,8 +13518,8 @@
       <c r="AH8" s="27"/>
       <c r="AI8" s="27"/>
       <c r="AJ8" s="28"/>
-      <c r="AK8" s="233"/>
-      <c r="AL8" s="232"/>
+      <c r="AK8" s="152"/>
+      <c r="AL8" s="151"/>
       <c r="AM8" s="29"/>
       <c r="AN8" s="29"/>
     </row>
@@ -13619,8 +13625,8 @@
       <c r="AH9" s="35"/>
       <c r="AI9" s="35"/>
       <c r="AJ9" s="36"/>
-      <c r="AK9" s="233"/>
-      <c r="AL9" s="232"/>
+      <c r="AK9" s="152"/>
+      <c r="AL9" s="151"/>
       <c r="AM9" s="29"/>
       <c r="AN9" s="29"/>
     </row>
@@ -13705,11 +13711,11 @@
       <c r="AA10" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="AB10" s="234">
+      <c r="AB10" s="156">
         <f>SUM(Y10:Y13)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="221">
+      <c r="AC10" s="159">
         <f>SUM(AB10,AB15)</f>
         <v>0</v>
       </c>
@@ -13725,8 +13731,8 @@
       <c r="AH10" s="163"/>
       <c r="AI10" s="163"/>
       <c r="AJ10" s="164"/>
-      <c r="AK10" s="233"/>
-      <c r="AL10" s="232"/>
+      <c r="AK10" s="152"/>
+      <c r="AL10" s="151"/>
       <c r="AM10" s="12"/>
       <c r="AN10" s="12"/>
     </row>
@@ -13814,20 +13820,20 @@
       <c r="AA11" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AB11" s="235"/>
-      <c r="AC11" s="237"/>
+      <c r="AB11" s="157"/>
+      <c r="AC11" s="160"/>
       <c r="AD11" s="16">
         <f t="shared" ref="AD11:AD13" si="1">X11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="17"/>
       <c r="AF11" s="165"/>
-      <c r="AG11" s="166"/>
-      <c r="AH11" s="166"/>
-      <c r="AI11" s="166"/>
-      <c r="AJ11" s="167"/>
-      <c r="AK11" s="233"/>
-      <c r="AL11" s="232"/>
+      <c r="AG11" s="154"/>
+      <c r="AH11" s="154"/>
+      <c r="AI11" s="154"/>
+      <c r="AJ11" s="155"/>
+      <c r="AK11" s="152"/>
+      <c r="AL11" s="151"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B12" s="13" t="s">
@@ -13910,20 +13916,20 @@
       <c r="AA12" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AB12" s="235"/>
-      <c r="AC12" s="237"/>
+      <c r="AB12" s="157"/>
+      <c r="AC12" s="160"/>
       <c r="AD12" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE12" s="17"/>
       <c r="AF12" s="165"/>
-      <c r="AG12" s="166"/>
-      <c r="AH12" s="166"/>
-      <c r="AI12" s="166"/>
-      <c r="AJ12" s="167"/>
-      <c r="AK12" s="233"/>
-      <c r="AL12" s="232"/>
+      <c r="AG12" s="154"/>
+      <c r="AH12" s="154"/>
+      <c r="AI12" s="154"/>
+      <c r="AJ12" s="155"/>
+      <c r="AK12" s="152"/>
+      <c r="AL12" s="151"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B13" s="13" t="s">
@@ -14006,20 +14012,20 @@
       <c r="AA13" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AB13" s="236"/>
-      <c r="AC13" s="237"/>
+      <c r="AB13" s="158"/>
+      <c r="AC13" s="160"/>
       <c r="AD13" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE13" s="17"/>
       <c r="AF13" s="165"/>
-      <c r="AG13" s="166"/>
-      <c r="AH13" s="166"/>
-      <c r="AI13" s="166"/>
-      <c r="AJ13" s="167"/>
-      <c r="AK13" s="233"/>
-      <c r="AL13" s="232"/>
+      <c r="AG13" s="154"/>
+      <c r="AH13" s="154"/>
+      <c r="AI13" s="154"/>
+      <c r="AJ13" s="155"/>
+      <c r="AK13" s="152"/>
+      <c r="AL13" s="151"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B14" s="13"/>
@@ -14112,16 +14118,16 @@
       <c r="Z14" s="41"/>
       <c r="AA14" s="42"/>
       <c r="AB14" s="13"/>
-      <c r="AC14" s="237"/>
+      <c r="AC14" s="160"/>
       <c r="AD14" s="33"/>
       <c r="AE14" s="17"/>
       <c r="AF14" s="165"/>
-      <c r="AG14" s="166"/>
-      <c r="AH14" s="166"/>
-      <c r="AI14" s="166"/>
-      <c r="AJ14" s="167"/>
-      <c r="AK14" s="233"/>
-      <c r="AL14" s="232"/>
+      <c r="AG14" s="154"/>
+      <c r="AH14" s="154"/>
+      <c r="AI14" s="154"/>
+      <c r="AJ14" s="155"/>
+      <c r="AK14" s="152"/>
+      <c r="AL14" s="151"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B15" s="13" t="s">
@@ -14204,26 +14210,26 @@
       <c r="AA15" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AB15" s="234">
+      <c r="AB15" s="156">
         <f>SUM(Y15:Y18)</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="237"/>
+      <c r="AC15" s="160"/>
       <c r="AD15" s="16">
         <f>X15</f>
         <v>0</v>
       </c>
       <c r="AE15" s="17"/>
-      <c r="AF15" s="168">
+      <c r="AF15" s="153">
         <f>SUM(AD10:AD20)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="166"/>
-      <c r="AH15" s="166"/>
-      <c r="AI15" s="166"/>
-      <c r="AJ15" s="167"/>
-      <c r="AK15" s="233"/>
-      <c r="AL15" s="232"/>
+      <c r="AG15" s="154"/>
+      <c r="AH15" s="154"/>
+      <c r="AI15" s="154"/>
+      <c r="AJ15" s="155"/>
+      <c r="AK15" s="152"/>
+      <c r="AL15" s="151"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B16" s="13" t="s">
@@ -14306,8 +14312,8 @@
       <c r="AA16" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AB16" s="235"/>
-      <c r="AC16" s="237"/>
+      <c r="AB16" s="157"/>
+      <c r="AC16" s="160"/>
       <c r="AD16" s="16">
         <f t="shared" ref="AD16:AD20" si="5">X16</f>
         <v>0</v>
@@ -14318,8 +14324,8 @@
       <c r="AH16" s="27"/>
       <c r="AI16" s="27"/>
       <c r="AJ16" s="28"/>
-      <c r="AK16" s="233"/>
-      <c r="AL16" s="232"/>
+      <c r="AK16" s="152"/>
+      <c r="AL16" s="151"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B17" s="13" t="s">
@@ -14402,8 +14408,8 @@
       <c r="AA17" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AB17" s="235"/>
-      <c r="AC17" s="237"/>
+      <c r="AB17" s="157"/>
+      <c r="AC17" s="160"/>
       <c r="AD17" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14414,8 +14420,8 @@
       <c r="AH17" s="27"/>
       <c r="AI17" s="27"/>
       <c r="AJ17" s="28"/>
-      <c r="AK17" s="233"/>
-      <c r="AL17" s="232"/>
+      <c r="AK17" s="152"/>
+      <c r="AL17" s="151"/>
     </row>
     <row r="18" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B18" s="13" t="s">
@@ -14498,8 +14504,8 @@
       <c r="AA18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AB18" s="235"/>
-      <c r="AC18" s="237"/>
+      <c r="AB18" s="157"/>
+      <c r="AC18" s="160"/>
       <c r="AD18" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14510,8 +14516,8 @@
       <c r="AH18" s="27"/>
       <c r="AI18" s="27"/>
       <c r="AJ18" s="28"/>
-      <c r="AK18" s="233"/>
-      <c r="AL18" s="232"/>
+      <c r="AK18" s="152"/>
+      <c r="AL18" s="151"/>
     </row>
     <row r="19" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B19" s="13" t="s">
@@ -14594,8 +14600,8 @@
       <c r="AA19" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AB19" s="235"/>
-      <c r="AC19" s="237"/>
+      <c r="AB19" s="157"/>
+      <c r="AC19" s="160"/>
       <c r="AD19" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14606,8 +14612,8 @@
       <c r="AH19" s="27"/>
       <c r="AI19" s="27"/>
       <c r="AJ19" s="28"/>
-      <c r="AK19" s="233"/>
-      <c r="AL19" s="232"/>
+      <c r="AK19" s="152"/>
+      <c r="AL19" s="151"/>
     </row>
     <row r="20" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B20" s="13" t="s">
@@ -14690,8 +14696,8 @@
       <c r="AA20" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AB20" s="236"/>
-      <c r="AC20" s="222"/>
+      <c r="AB20" s="158"/>
+      <c r="AC20" s="161"/>
       <c r="AD20" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14702,8 +14708,8 @@
       <c r="AH20" s="27"/>
       <c r="AI20" s="27"/>
       <c r="AJ20" s="28"/>
-      <c r="AK20" s="233"/>
-      <c r="AL20" s="232"/>
+      <c r="AK20" s="152"/>
+      <c r="AL20" s="151"/>
     </row>
     <row r="21" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B21" s="13"/>
@@ -14795,8 +14801,8 @@
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
       <c r="AA21" s="42"/>
-      <c r="AB21" s="188"/>
-      <c r="AC21" s="189"/>
+      <c r="AB21" s="181"/>
+      <c r="AC21" s="182"/>
       <c r="AD21" s="33"/>
       <c r="AE21" s="17"/>
       <c r="AF21" s="162" t="s">
@@ -14806,8 +14812,8 @@
       <c r="AH21" s="163"/>
       <c r="AI21" s="163"/>
       <c r="AJ21" s="164"/>
-      <c r="AK21" s="233"/>
-      <c r="AL21" s="232"/>
+      <c r="AK21" s="152"/>
+      <c r="AL21" s="151"/>
     </row>
     <row r="22" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B22" s="13" t="s">
@@ -14890,21 +14896,21 @@
       <c r="AA22" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AB22" s="223"/>
-      <c r="AC22" s="224"/>
+      <c r="AB22" s="183"/>
+      <c r="AC22" s="184"/>
       <c r="AD22" s="16">
         <f>X22</f>
         <v>0</v>
       </c>
       <c r="AE22" s="17"/>
-      <c r="AF22" s="241">
+      <c r="AF22" s="185">
         <f>SUM(AD22:AE22)</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="242"/>
-      <c r="AH22" s="242"/>
-      <c r="AI22" s="242"/>
-      <c r="AJ22" s="243"/>
+      <c r="AG22" s="186"/>
+      <c r="AH22" s="186"/>
+      <c r="AI22" s="186"/>
+      <c r="AJ22" s="187"/>
       <c r="AK22" s="22"/>
       <c r="AL22" s="18"/>
     </row>
@@ -14998,8 +15004,8 @@
       <c r="Y23" s="14"/>
       <c r="Z23" s="14"/>
       <c r="AA23" s="42"/>
-      <c r="AB23" s="151"/>
-      <c r="AC23" s="152"/>
+      <c r="AB23" s="172"/>
+      <c r="AC23" s="173"/>
       <c r="AD23" s="16">
         <f t="shared" ref="AD23:AD39" si="8">X23</f>
         <v>0</v>
@@ -15097,27 +15103,27 @@
       <c r="AA24" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="AB24" s="173">
+      <c r="AB24" s="174">
         <f>SUM(Y24:Y25)</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="174"/>
+      <c r="AC24" s="175"/>
       <c r="AD24" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE24" s="17"/>
-      <c r="AF24" s="177" t="s">
+      <c r="AF24" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="AG24" s="178"/>
-      <c r="AH24" s="178"/>
-      <c r="AI24" s="178"/>
-      <c r="AJ24" s="225"/>
-      <c r="AK24" s="238" t="s">
+      <c r="AG24" s="179"/>
+      <c r="AH24" s="179"/>
+      <c r="AI24" s="179"/>
+      <c r="AJ24" s="180"/>
+      <c r="AK24" s="166" t="s">
         <v>43</v>
       </c>
-      <c r="AL24" s="239"/>
+      <c r="AL24" s="167"/>
     </row>
     <row r="25" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A25" s="12">
@@ -15203,23 +15209,23 @@
       <c r="AA25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AB25" s="175"/>
-      <c r="AC25" s="176"/>
+      <c r="AB25" s="176"/>
+      <c r="AC25" s="177"/>
       <c r="AD25" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE25" s="17"/>
-      <c r="AF25" s="199">
+      <c r="AF25" s="169">
         <f>SUM(AD24:AD25)</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="226"/>
-      <c r="AH25" s="226"/>
-      <c r="AI25" s="226"/>
-      <c r="AJ25" s="227"/>
-      <c r="AK25" s="238"/>
-      <c r="AL25" s="239"/>
+      <c r="AG25" s="170"/>
+      <c r="AH25" s="170"/>
+      <c r="AI25" s="170"/>
+      <c r="AJ25" s="171"/>
+      <c r="AK25" s="166"/>
+      <c r="AL25" s="167"/>
     </row>
     <row r="26" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B26" s="13"/>
@@ -15311,8 +15317,8 @@
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
       <c r="AA26" s="13"/>
-      <c r="AB26" s="151"/>
-      <c r="AC26" s="152"/>
+      <c r="AB26" s="172"/>
+      <c r="AC26" s="173"/>
       <c r="AD26" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15323,8 +15329,8 @@
       <c r="AH26" s="45"/>
       <c r="AI26" s="45"/>
       <c r="AJ26" s="46"/>
-      <c r="AK26" s="238"/>
-      <c r="AL26" s="239"/>
+      <c r="AK26" s="166"/>
+      <c r="AL26" s="167"/>
     </row>
     <row r="27" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A27" s="12">
@@ -15410,25 +15416,25 @@
       <c r="AA27" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="AB27" s="173">
+      <c r="AB27" s="174">
         <f>SUM(Y26:Y28)</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="174"/>
+      <c r="AC27" s="175"/>
       <c r="AD27" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE27" s="17"/>
-      <c r="AF27" s="177" t="s">
+      <c r="AF27" s="178" t="s">
         <v>46</v>
       </c>
-      <c r="AG27" s="178"/>
-      <c r="AH27" s="178"/>
-      <c r="AI27" s="178"/>
-      <c r="AJ27" s="225"/>
-      <c r="AK27" s="238"/>
-      <c r="AL27" s="239"/>
+      <c r="AG27" s="179"/>
+      <c r="AH27" s="179"/>
+      <c r="AI27" s="179"/>
+      <c r="AJ27" s="180"/>
+      <c r="AK27" s="166"/>
+      <c r="AL27" s="167"/>
     </row>
     <row r="28" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A28" s="12">
@@ -15514,23 +15520,23 @@
       <c r="AA28" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AB28" s="175"/>
-      <c r="AC28" s="176"/>
+      <c r="AB28" s="176"/>
+      <c r="AC28" s="177"/>
       <c r="AD28" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE28" s="17"/>
-      <c r="AF28" s="199">
+      <c r="AF28" s="169">
         <f>+AD27+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="226"/>
-      <c r="AH28" s="226"/>
-      <c r="AI28" s="226"/>
-      <c r="AJ28" s="227"/>
-      <c r="AK28" s="238"/>
-      <c r="AL28" s="239"/>
+      <c r="AG28" s="170"/>
+      <c r="AH28" s="170"/>
+      <c r="AI28" s="170"/>
+      <c r="AJ28" s="171"/>
+      <c r="AK28" s="166"/>
+      <c r="AL28" s="167"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B29" s="13"/>
@@ -15622,8 +15628,8 @@
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
       <c r="AA29" s="13"/>
-      <c r="AB29" s="151"/>
-      <c r="AC29" s="152"/>
+      <c r="AB29" s="172"/>
+      <c r="AC29" s="173"/>
       <c r="AD29" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15634,8 +15640,8 @@
       <c r="AH29" s="45"/>
       <c r="AI29" s="45"/>
       <c r="AJ29" s="45"/>
-      <c r="AK29" s="238"/>
-      <c r="AL29" s="239"/>
+      <c r="AK29" s="166"/>
+      <c r="AL29" s="167"/>
     </row>
     <row r="30" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A30" s="12">
@@ -15721,25 +15727,25 @@
       <c r="AA30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="AB30" s="173">
+      <c r="AB30" s="174">
         <f>SUM(Y29:Y31)</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="174"/>
+      <c r="AC30" s="175"/>
       <c r="AD30" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE30" s="17"/>
-      <c r="AF30" s="177" t="s">
+      <c r="AF30" s="178" t="s">
         <v>49</v>
       </c>
-      <c r="AG30" s="178"/>
-      <c r="AH30" s="178"/>
-      <c r="AI30" s="178"/>
-      <c r="AJ30" s="178"/>
-      <c r="AK30" s="238"/>
-      <c r="AL30" s="239"/>
+      <c r="AG30" s="179"/>
+      <c r="AH30" s="179"/>
+      <c r="AI30" s="179"/>
+      <c r="AJ30" s="179"/>
+      <c r="AK30" s="166"/>
+      <c r="AL30" s="167"/>
     </row>
     <row r="31" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A31" s="12">
@@ -15825,23 +15831,23 @@
       <c r="AA31" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AB31" s="175"/>
-      <c r="AC31" s="176"/>
+      <c r="AB31" s="176"/>
+      <c r="AC31" s="177"/>
       <c r="AD31" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE31" s="17"/>
-      <c r="AF31" s="199">
+      <c r="AF31" s="169">
         <f>+AD30+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG31" s="226"/>
-      <c r="AH31" s="226"/>
-      <c r="AI31" s="226"/>
-      <c r="AJ31" s="227"/>
-      <c r="AK31" s="238"/>
-      <c r="AL31" s="239"/>
+      <c r="AG31" s="170"/>
+      <c r="AH31" s="170"/>
+      <c r="AI31" s="170"/>
+      <c r="AJ31" s="171"/>
+      <c r="AK31" s="166"/>
+      <c r="AL31" s="167"/>
     </row>
     <row r="32" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B32" s="13"/>
@@ -15933,8 +15939,8 @@
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
       <c r="AA32" s="13"/>
-      <c r="AB32" s="151"/>
-      <c r="AC32" s="152"/>
+      <c r="AB32" s="172"/>
+      <c r="AC32" s="173"/>
       <c r="AD32" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15945,8 +15951,8 @@
       <c r="AH32" s="45"/>
       <c r="AI32" s="45"/>
       <c r="AJ32" s="45"/>
-      <c r="AK32" s="238"/>
-      <c r="AL32" s="239"/>
+      <c r="AK32" s="166"/>
+      <c r="AL32" s="167"/>
     </row>
     <row r="33" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A33" s="12">
@@ -16032,25 +16038,25 @@
       <c r="AA33" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="AB33" s="173">
+      <c r="AB33" s="174">
         <f>SUM(Y32:Y34)</f>
         <v>0</v>
       </c>
-      <c r="AC33" s="174"/>
+      <c r="AC33" s="175"/>
       <c r="AD33" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE33" s="17"/>
-      <c r="AF33" s="177" t="s">
+      <c r="AF33" s="178" t="s">
         <v>52</v>
       </c>
-      <c r="AG33" s="178"/>
-      <c r="AH33" s="178"/>
-      <c r="AI33" s="178"/>
-      <c r="AJ33" s="178"/>
-      <c r="AK33" s="238"/>
-      <c r="AL33" s="239"/>
+      <c r="AG33" s="179"/>
+      <c r="AH33" s="179"/>
+      <c r="AI33" s="179"/>
+      <c r="AJ33" s="179"/>
+      <c r="AK33" s="166"/>
+      <c r="AL33" s="167"/>
     </row>
     <row r="34" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A34" s="12">
@@ -16136,23 +16142,23 @@
       <c r="AA34" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AB34" s="175"/>
-      <c r="AC34" s="176"/>
+      <c r="AB34" s="176"/>
+      <c r="AC34" s="177"/>
       <c r="AD34" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE34" s="17"/>
-      <c r="AF34" s="199">
+      <c r="AF34" s="169">
         <f>+AD33+AD34</f>
         <v>0</v>
       </c>
-      <c r="AG34" s="226"/>
-      <c r="AH34" s="226"/>
-      <c r="AI34" s="226"/>
-      <c r="AJ34" s="227"/>
-      <c r="AK34" s="238"/>
-      <c r="AL34" s="239"/>
+      <c r="AG34" s="170"/>
+      <c r="AH34" s="170"/>
+      <c r="AI34" s="170"/>
+      <c r="AJ34" s="171"/>
+      <c r="AK34" s="166"/>
+      <c r="AL34" s="167"/>
     </row>
     <row r="35" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B35" s="13"/>
@@ -16244,8 +16250,8 @@
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
       <c r="AA35" s="13"/>
-      <c r="AB35" s="151"/>
-      <c r="AC35" s="152"/>
+      <c r="AB35" s="172"/>
+      <c r="AC35" s="173"/>
       <c r="AD35" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16256,8 +16262,8 @@
       <c r="AH35" s="45"/>
       <c r="AI35" s="45"/>
       <c r="AJ35" s="45"/>
-      <c r="AK35" s="238"/>
-      <c r="AL35" s="239"/>
+      <c r="AK35" s="166"/>
+      <c r="AL35" s="167"/>
     </row>
     <row r="36" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B36" s="13" t="s">
@@ -16340,25 +16346,25 @@
       <c r="AA36" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="AB36" s="173">
+      <c r="AB36" s="174">
         <f>SUM(Y35:Y37)</f>
         <v>0</v>
       </c>
-      <c r="AC36" s="174"/>
+      <c r="AC36" s="175"/>
       <c r="AD36" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE36" s="17"/>
-      <c r="AF36" s="177" t="s">
+      <c r="AF36" s="178" t="s">
         <v>55</v>
       </c>
-      <c r="AG36" s="178"/>
-      <c r="AH36" s="178"/>
-      <c r="AI36" s="178"/>
-      <c r="AJ36" s="178"/>
-      <c r="AK36" s="238"/>
-      <c r="AL36" s="239"/>
+      <c r="AG36" s="179"/>
+      <c r="AH36" s="179"/>
+      <c r="AI36" s="179"/>
+      <c r="AJ36" s="179"/>
+      <c r="AK36" s="166"/>
+      <c r="AL36" s="167"/>
     </row>
     <row r="37" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B37" s="13" t="s">
@@ -16441,23 +16447,23 @@
       <c r="AA37" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="AB37" s="175"/>
-      <c r="AC37" s="176"/>
+      <c r="AB37" s="176"/>
+      <c r="AC37" s="177"/>
       <c r="AD37" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE37" s="17"/>
-      <c r="AF37" s="199">
+      <c r="AF37" s="169">
         <f>+AD36+AD37</f>
         <v>0</v>
       </c>
-      <c r="AG37" s="226"/>
-      <c r="AH37" s="226"/>
-      <c r="AI37" s="226"/>
-      <c r="AJ37" s="227"/>
-      <c r="AK37" s="238"/>
-      <c r="AL37" s="239"/>
+      <c r="AG37" s="170"/>
+      <c r="AH37" s="170"/>
+      <c r="AI37" s="170"/>
+      <c r="AJ37" s="171"/>
+      <c r="AK37" s="166"/>
+      <c r="AL37" s="167"/>
       <c r="AM37" s="47"/>
       <c r="AN37" s="47"/>
     </row>
@@ -16551,8 +16557,8 @@
       <c r="Y38" s="14"/>
       <c r="Z38" s="14"/>
       <c r="AA38" s="13"/>
-      <c r="AB38" s="151"/>
-      <c r="AC38" s="152"/>
+      <c r="AB38" s="172"/>
+      <c r="AC38" s="173"/>
       <c r="AD38" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16563,8 +16569,8 @@
       <c r="AH38" s="45"/>
       <c r="AI38" s="45"/>
       <c r="AJ38" s="45"/>
-      <c r="AK38" s="238"/>
-      <c r="AL38" s="239"/>
+      <c r="AK38" s="166"/>
+      <c r="AL38" s="167"/>
       <c r="AM38" s="47"/>
       <c r="AN38" s="47"/>
     </row>
@@ -16649,8 +16655,8 @@
       <c r="AA39" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="AB39" s="151"/>
-      <c r="AC39" s="152"/>
+      <c r="AB39" s="172"/>
+      <c r="AC39" s="173"/>
       <c r="AD39" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16661,8 +16667,8 @@
       <c r="AH39" s="45"/>
       <c r="AI39" s="45"/>
       <c r="AJ39" s="45"/>
-      <c r="AK39" s="238"/>
-      <c r="AL39" s="239"/>
+      <c r="AK39" s="166"/>
+      <c r="AL39" s="167"/>
       <c r="AM39" s="47"/>
       <c r="AN39" s="47"/>
     </row>
@@ -16670,46 +16676,46 @@
       <c r="B40" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="137" t="s">
+      <c r="C40" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D40" s="138"/>
-      <c r="E40" s="137" t="s">
+      <c r="D40" s="129"/>
+      <c r="E40" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F40" s="138"/>
-      <c r="G40" s="137" t="s">
+      <c r="F40" s="129"/>
+      <c r="G40" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H40" s="138"/>
-      <c r="I40" s="137" t="s">
+      <c r="H40" s="129"/>
+      <c r="I40" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J40" s="138"/>
-      <c r="K40" s="137" t="s">
+      <c r="J40" s="129"/>
+      <c r="K40" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L40" s="138"/>
-      <c r="M40" s="137" t="s">
+      <c r="L40" s="129"/>
+      <c r="M40" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N40" s="138"/>
-      <c r="O40" s="137" t="s">
+      <c r="N40" s="129"/>
+      <c r="O40" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P40" s="138"/>
-      <c r="Q40" s="137" t="s">
+      <c r="P40" s="129"/>
+      <c r="Q40" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R40" s="138"/>
-      <c r="S40" s="137" t="s">
+      <c r="R40" s="129"/>
+      <c r="S40" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T40" s="138"/>
-      <c r="U40" s="137" t="s">
+      <c r="T40" s="129"/>
+      <c r="U40" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V40" s="138"/>
+      <c r="V40" s="129"/>
       <c r="W40" s="5" t="s">
         <v>12</v>
       </c>
@@ -16723,8 +16729,8 @@
       <c r="AA40" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="AB40" s="141"/>
-      <c r="AC40" s="142"/>
+      <c r="AB40" s="134"/>
+      <c r="AC40" s="135"/>
       <c r="AD40" s="6">
         <v>0</v>
       </c>
@@ -16734,8 +16740,8 @@
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
-      <c r="AK40" s="238"/>
-      <c r="AL40" s="239"/>
+      <c r="AK40" s="166"/>
+      <c r="AL40" s="167"/>
       <c r="AM40" s="12"/>
       <c r="AN40" s="12"/>
     </row>
@@ -16833,8 +16839,8 @@
       <c r="AH41" s="52"/>
       <c r="AI41" s="52"/>
       <c r="AJ41" s="52"/>
-      <c r="AK41" s="238"/>
-      <c r="AL41" s="239"/>
+      <c r="AK41" s="166"/>
+      <c r="AL41" s="167"/>
     </row>
     <row r="42" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A42" s="12"/>
@@ -16918,25 +16924,25 @@
       <c r="AA42" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="AB42" s="213">
+      <c r="AB42" s="188">
         <f>SUM(Y40:Y53)</f>
         <v>0</v>
       </c>
-      <c r="AC42" s="214"/>
+      <c r="AC42" s="189"/>
       <c r="AD42" s="16">
         <f t="shared" ref="AD42:AD59" si="16">X42</f>
         <v>0</v>
       </c>
       <c r="AE42" s="17"/>
-      <c r="AF42" s="177" t="s">
+      <c r="AF42" s="178" t="s">
         <v>61</v>
       </c>
-      <c r="AG42" s="178"/>
-      <c r="AH42" s="178"/>
-      <c r="AI42" s="178"/>
-      <c r="AJ42" s="225"/>
-      <c r="AK42" s="240"/>
-      <c r="AL42" s="239"/>
+      <c r="AG42" s="179"/>
+      <c r="AH42" s="179"/>
+      <c r="AI42" s="179"/>
+      <c r="AJ42" s="180"/>
+      <c r="AK42" s="168"/>
+      <c r="AL42" s="167"/>
     </row>
     <row r="43" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A43" s="12"/>
@@ -17020,8 +17026,8 @@
       <c r="AA43" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="AB43" s="213"/>
-      <c r="AC43" s="214"/>
+      <c r="AB43" s="188"/>
+      <c r="AC43" s="189"/>
       <c r="AD43" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17032,8 +17038,8 @@
       <c r="AH43" s="54"/>
       <c r="AI43" s="54"/>
       <c r="AJ43" s="55"/>
-      <c r="AK43" s="240"/>
-      <c r="AL43" s="239"/>
+      <c r="AK43" s="168"/>
+      <c r="AL43" s="167"/>
     </row>
     <row r="44" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A44" s="12"/>
@@ -17117,8 +17123,8 @@
       <c r="AA44" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="AB44" s="213"/>
-      <c r="AC44" s="214"/>
+      <c r="AB44" s="188"/>
+      <c r="AC44" s="189"/>
       <c r="AD44" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17129,8 +17135,8 @@
       <c r="AH44" s="54"/>
       <c r="AI44" s="54"/>
       <c r="AJ44" s="55"/>
-      <c r="AK44" s="240"/>
-      <c r="AL44" s="239"/>
+      <c r="AK44" s="168"/>
+      <c r="AL44" s="167"/>
     </row>
     <row r="45" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A45" s="12"/>
@@ -17214,8 +17220,8 @@
       <c r="AA45" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="AB45" s="213"/>
-      <c r="AC45" s="214"/>
+      <c r="AB45" s="188"/>
+      <c r="AC45" s="189"/>
       <c r="AD45" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17226,8 +17232,8 @@
       <c r="AH45" s="54"/>
       <c r="AI45" s="54"/>
       <c r="AJ45" s="55"/>
-      <c r="AK45" s="240"/>
-      <c r="AL45" s="239"/>
+      <c r="AK45" s="168"/>
+      <c r="AL45" s="167"/>
     </row>
     <row r="46" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A46" s="12"/>
@@ -17311,8 +17317,8 @@
       <c r="AA46" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="AB46" s="213"/>
-      <c r="AC46" s="214"/>
+      <c r="AB46" s="188"/>
+      <c r="AC46" s="189"/>
       <c r="AD46" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17323,8 +17329,8 @@
       <c r="AH46" s="54"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="55"/>
-      <c r="AK46" s="240"/>
-      <c r="AL46" s="239"/>
+      <c r="AK46" s="168"/>
+      <c r="AL46" s="167"/>
     </row>
     <row r="47" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A47" s="12"/>
@@ -17408,23 +17414,23 @@
       <c r="AA47" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AB47" s="213"/>
-      <c r="AC47" s="214"/>
+      <c r="AB47" s="188"/>
+      <c r="AC47" s="189"/>
       <c r="AD47" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE47" s="17"/>
-      <c r="AF47" s="218">
+      <c r="AF47" s="190">
         <f>SUM(AD41:AD53)</f>
         <v>0</v>
       </c>
-      <c r="AG47" s="216"/>
-      <c r="AH47" s="216"/>
-      <c r="AI47" s="216"/>
-      <c r="AJ47" s="217"/>
-      <c r="AK47" s="240"/>
-      <c r="AL47" s="239"/>
+      <c r="AG47" s="191"/>
+      <c r="AH47" s="191"/>
+      <c r="AI47" s="191"/>
+      <c r="AJ47" s="192"/>
+      <c r="AK47" s="168"/>
+      <c r="AL47" s="167"/>
     </row>
     <row r="48" spans="1:40" s="47" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A48" s="12"/>
@@ -17508,8 +17514,8 @@
       <c r="AA48" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AB48" s="213"/>
-      <c r="AC48" s="214"/>
+      <c r="AB48" s="188"/>
+      <c r="AC48" s="189"/>
       <c r="AD48" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17520,8 +17526,8 @@
       <c r="AH48" s="54"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="55"/>
-      <c r="AK48" s="240"/>
-      <c r="AL48" s="239"/>
+      <c r="AK48" s="168"/>
+      <c r="AL48" s="167"/>
     </row>
     <row r="49" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A49" s="12"/>
@@ -17605,8 +17611,8 @@
       <c r="AA49" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AB49" s="213"/>
-      <c r="AC49" s="214"/>
+      <c r="AB49" s="188"/>
+      <c r="AC49" s="189"/>
       <c r="AD49" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17617,8 +17623,8 @@
       <c r="AH49" s="54"/>
       <c r="AI49" s="54"/>
       <c r="AJ49" s="55"/>
-      <c r="AK49" s="240"/>
-      <c r="AL49" s="239"/>
+      <c r="AK49" s="168"/>
+      <c r="AL49" s="167"/>
     </row>
     <row r="50" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A50" s="12"/>
@@ -17702,8 +17708,8 @@
       <c r="AA50" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AB50" s="213"/>
-      <c r="AC50" s="214"/>
+      <c r="AB50" s="188"/>
+      <c r="AC50" s="189"/>
       <c r="AD50" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17714,8 +17720,8 @@
       <c r="AH50" s="54"/>
       <c r="AI50" s="54"/>
       <c r="AJ50" s="55"/>
-      <c r="AK50" s="240"/>
-      <c r="AL50" s="239"/>
+      <c r="AK50" s="168"/>
+      <c r="AL50" s="167"/>
     </row>
     <row r="51" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A51" s="12"/>
@@ -17799,8 +17805,8 @@
       <c r="AA51" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="AB51" s="213"/>
-      <c r="AC51" s="214"/>
+      <c r="AB51" s="188"/>
+      <c r="AC51" s="189"/>
       <c r="AD51" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17811,8 +17817,8 @@
       <c r="AH51" s="54"/>
       <c r="AI51" s="54"/>
       <c r="AJ51" s="55"/>
-      <c r="AK51" s="240"/>
-      <c r="AL51" s="239"/>
+      <c r="AK51" s="168"/>
+      <c r="AL51" s="167"/>
     </row>
     <row r="52" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A52" s="12"/>
@@ -17908,8 +17914,8 @@
       <c r="AH52" s="54"/>
       <c r="AI52" s="54"/>
       <c r="AJ52" s="55"/>
-      <c r="AK52" s="240"/>
-      <c r="AL52" s="239"/>
+      <c r="AK52" s="168"/>
+      <c r="AL52" s="167"/>
     </row>
     <row r="53" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A53" s="12"/>
@@ -18005,8 +18011,8 @@
       <c r="AH53" s="62"/>
       <c r="AI53" s="62"/>
       <c r="AJ53" s="63"/>
-      <c r="AK53" s="240"/>
-      <c r="AL53" s="239"/>
+      <c r="AK53" s="168"/>
+      <c r="AL53" s="167"/>
     </row>
     <row r="54" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A54" s="12"/>
@@ -18101,8 +18107,8 @@
       <c r="Y54" s="14"/>
       <c r="Z54" s="14"/>
       <c r="AA54" s="13"/>
-      <c r="AB54" s="223"/>
-      <c r="AC54" s="224"/>
+      <c r="AB54" s="183"/>
+      <c r="AC54" s="184"/>
       <c r="AD54" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -18113,8 +18119,8 @@
       <c r="AH54" s="54"/>
       <c r="AI54" s="54"/>
       <c r="AJ54" s="54"/>
-      <c r="AK54" s="238"/>
-      <c r="AL54" s="239"/>
+      <c r="AK54" s="166"/>
+      <c r="AL54" s="167"/>
     </row>
     <row r="55" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B55" s="13" t="s">
@@ -18197,8 +18203,8 @@
       <c r="AA55" s="13" t="s">
         <v>73</v>
       </c>
-      <c r="AB55" s="151"/>
-      <c r="AC55" s="152"/>
+      <c r="AB55" s="172"/>
+      <c r="AC55" s="173"/>
       <c r="AD55" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -18209,8 +18215,8 @@
       <c r="AH55" s="2"/>
       <c r="AI55" s="2"/>
       <c r="AJ55" s="2"/>
-      <c r="AK55" s="238"/>
-      <c r="AL55" s="239"/>
+      <c r="AK55" s="166"/>
+      <c r="AL55" s="167"/>
       <c r="AM55" s="4"/>
       <c r="AN55" s="4"/>
     </row>
@@ -18283,8 +18289,8 @@
       <c r="AH56" s="2"/>
       <c r="AI56" s="2"/>
       <c r="AJ56" s="2"/>
-      <c r="AK56" s="238"/>
-      <c r="AL56" s="239"/>
+      <c r="AK56" s="166"/>
+      <c r="AL56" s="167"/>
       <c r="AM56" s="67"/>
       <c r="AN56" s="67"/>
     </row>
@@ -18373,7 +18379,7 @@
         <f>Y57*4</f>
         <v>0</v>
       </c>
-      <c r="AC57" s="221">
+      <c r="AC57" s="159">
         <f>SUM(C59:W59)</f>
         <v>0</v>
       </c>
@@ -18384,8 +18390,8 @@
       <c r="AE57" s="17"/>
       <c r="AF57" s="69"/>
       <c r="AG57" s="69"/>
-      <c r="AK57" s="238"/>
-      <c r="AL57" s="239"/>
+      <c r="AK57" s="166"/>
+      <c r="AL57" s="167"/>
     </row>
     <row r="58" spans="1:40" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B58" s="15" t="s">
@@ -18472,14 +18478,14 @@
         <f>Y58*4</f>
         <v>0</v>
       </c>
-      <c r="AC58" s="222"/>
+      <c r="AC58" s="161"/>
       <c r="AD58" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE58" s="17"/>
-      <c r="AK58" s="238"/>
-      <c r="AL58" s="239"/>
+      <c r="AK58" s="166"/>
+      <c r="AL58" s="167"/>
     </row>
     <row r="59" spans="1:40" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B59" s="15"/>
@@ -18571,75 +18577,75 @@
       <c r="Y59" s="14"/>
       <c r="Z59" s="14"/>
       <c r="AA59" s="68"/>
-      <c r="AB59" s="145"/>
-      <c r="AC59" s="146"/>
+      <c r="AB59" s="193"/>
+      <c r="AC59" s="194"/>
       <c r="AD59" s="33">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE59" s="17"/>
-      <c r="AK59" s="238"/>
-      <c r="AL59" s="239"/>
+      <c r="AK59" s="166"/>
+      <c r="AL59" s="167"/>
     </row>
     <row r="60" spans="1:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B60" s="169" t="s">
+      <c r="B60" s="130" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="137" t="s">
+      <c r="C60" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D60" s="138"/>
-      <c r="E60" s="137" t="s">
+      <c r="D60" s="129"/>
+      <c r="E60" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F60" s="138"/>
-      <c r="G60" s="137" t="s">
+      <c r="F60" s="129"/>
+      <c r="G60" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H60" s="138"/>
-      <c r="I60" s="137" t="s">
+      <c r="H60" s="129"/>
+      <c r="I60" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J60" s="138"/>
-      <c r="K60" s="137" t="s">
+      <c r="J60" s="129"/>
+      <c r="K60" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L60" s="138"/>
-      <c r="M60" s="137" t="s">
+      <c r="L60" s="129"/>
+      <c r="M60" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N60" s="138"/>
-      <c r="O60" s="137" t="s">
+      <c r="N60" s="129"/>
+      <c r="O60" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P60" s="138"/>
-      <c r="Q60" s="137" t="s">
+      <c r="P60" s="129"/>
+      <c r="Q60" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R60" s="138"/>
-      <c r="S60" s="137" t="s">
+      <c r="R60" s="129"/>
+      <c r="S60" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T60" s="138"/>
-      <c r="U60" s="137" t="s">
+      <c r="T60" s="129"/>
+      <c r="U60" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V60" s="138"/>
-      <c r="W60" s="169" t="s">
+      <c r="V60" s="129"/>
+      <c r="W60" s="130" t="s">
         <v>12</v>
       </c>
       <c r="X60" s="110"/>
-      <c r="Y60" s="169" t="s">
+      <c r="Y60" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z60" s="169" t="s">
+      <c r="Z60" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA60" s="169" t="s">
+      <c r="AA60" s="130" t="s">
         <v>77</v>
       </c>
-      <c r="AB60" s="141"/>
-      <c r="AC60" s="142"/>
+      <c r="AB60" s="134"/>
+      <c r="AC60" s="135"/>
       <c r="AD60" s="6" t="s">
         <v>16</v>
       </c>
@@ -18648,7 +18654,7 @@
       <c r="AL60" s="71"/>
     </row>
     <row r="61" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B61" s="170"/>
+      <c r="B61" s="131"/>
       <c r="C61" s="9" t="s">
         <v>17</v>
       </c>
@@ -18709,11 +18715,11 @@
       <c r="V61" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W61" s="170"/>
+      <c r="W61" s="131"/>
       <c r="X61" s="111"/>
-      <c r="Y61" s="170"/>
-      <c r="Z61" s="170"/>
-      <c r="AA61" s="170"/>
+      <c r="Y61" s="131"/>
+      <c r="Z61" s="131"/>
+      <c r="AA61" s="131"/>
       <c r="AB61" s="10"/>
       <c r="AC61" s="11"/>
       <c r="AD61" s="6"/>
@@ -18807,11 +18813,11 @@
       <c r="AA62" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AB62" s="173">
+      <c r="AB62" s="174">
         <f>SUM(Y62:Y68)</f>
         <v>0</v>
       </c>
-      <c r="AC62" s="174"/>
+      <c r="AC62" s="175"/>
       <c r="AD62" s="16">
         <f>X62</f>
         <v>0</v>
@@ -18906,20 +18912,20 @@
       <c r="AA63" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AB63" s="213"/>
-      <c r="AC63" s="214"/>
+      <c r="AB63" s="188"/>
+      <c r="AC63" s="189"/>
       <c r="AD63" s="16">
         <f t="shared" ref="AD63:AD68" si="21">X63</f>
         <v>0</v>
       </c>
       <c r="AE63" s="17"/>
-      <c r="AF63" s="215" t="s">
+      <c r="AF63" s="195" t="s">
         <v>77</v>
       </c>
-      <c r="AG63" s="216"/>
-      <c r="AH63" s="216"/>
-      <c r="AI63" s="216"/>
-      <c r="AJ63" s="217"/>
+      <c r="AG63" s="191"/>
+      <c r="AH63" s="191"/>
+      <c r="AI63" s="191"/>
+      <c r="AJ63" s="192"/>
       <c r="AK63" s="70"/>
       <c r="AL63" s="71"/>
     </row>
@@ -19004,21 +19010,21 @@
       <c r="AA64" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AB64" s="213"/>
-      <c r="AC64" s="214"/>
+      <c r="AB64" s="188"/>
+      <c r="AC64" s="189"/>
       <c r="AD64" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE64" s="17"/>
-      <c r="AF64" s="218">
+      <c r="AF64" s="190">
         <f>SUM(AD62:AD68)</f>
         <v>0</v>
       </c>
-      <c r="AG64" s="219"/>
-      <c r="AH64" s="219"/>
-      <c r="AI64" s="219"/>
-      <c r="AJ64" s="220"/>
+      <c r="AG64" s="196"/>
+      <c r="AH64" s="196"/>
+      <c r="AI64" s="196"/>
+      <c r="AJ64" s="197"/>
       <c r="AK64" s="70"/>
       <c r="AL64" s="71"/>
     </row>
@@ -19103,8 +19109,8 @@
       <c r="AA65" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AB65" s="213"/>
-      <c r="AC65" s="214"/>
+      <c r="AB65" s="188"/>
+      <c r="AC65" s="189"/>
       <c r="AD65" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19199,8 +19205,8 @@
       <c r="AA66" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AB66" s="213"/>
-      <c r="AC66" s="214"/>
+      <c r="AB66" s="188"/>
+      <c r="AC66" s="189"/>
       <c r="AD66" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19295,8 +19301,8 @@
       <c r="AA67" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AB67" s="175"/>
-      <c r="AC67" s="176"/>
+      <c r="AB67" s="176"/>
+      <c r="AC67" s="177"/>
       <c r="AD67" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19391,8 +19397,8 @@
       <c r="AA68" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AB68" s="151"/>
-      <c r="AC68" s="152"/>
+      <c r="AB68" s="172"/>
+      <c r="AC68" s="173"/>
       <c r="AD68" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19496,8 +19502,8 @@
       <c r="Y69" s="14"/>
       <c r="Z69" s="14"/>
       <c r="AA69" s="13"/>
-      <c r="AB69" s="151"/>
-      <c r="AC69" s="152"/>
+      <c r="AB69" s="172"/>
+      <c r="AC69" s="173"/>
       <c r="AD69" s="16">
         <v>0</v>
       </c>
@@ -19514,46 +19520,46 @@
       <c r="B70" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C70" s="137" t="s">
+      <c r="C70" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D70" s="138"/>
-      <c r="E70" s="137" t="s">
+      <c r="D70" s="129"/>
+      <c r="E70" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F70" s="138"/>
-      <c r="G70" s="137" t="s">
+      <c r="F70" s="129"/>
+      <c r="G70" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H70" s="138"/>
-      <c r="I70" s="137" t="s">
+      <c r="H70" s="129"/>
+      <c r="I70" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J70" s="138"/>
-      <c r="K70" s="137" t="s">
+      <c r="J70" s="129"/>
+      <c r="K70" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L70" s="138"/>
-      <c r="M70" s="137" t="s">
+      <c r="L70" s="129"/>
+      <c r="M70" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N70" s="138"/>
-      <c r="O70" s="137" t="s">
+      <c r="N70" s="129"/>
+      <c r="O70" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P70" s="138"/>
-      <c r="Q70" s="137" t="s">
+      <c r="P70" s="129"/>
+      <c r="Q70" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R70" s="138"/>
-      <c r="S70" s="137" t="s">
+      <c r="R70" s="129"/>
+      <c r="S70" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T70" s="138"/>
-      <c r="U70" s="137" t="s">
+      <c r="T70" s="129"/>
+      <c r="U70" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V70" s="138"/>
+      <c r="V70" s="129"/>
       <c r="W70" s="9" t="s">
         <v>12</v>
       </c>
@@ -19567,8 +19573,8 @@
       <c r="AA70" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="AB70" s="141"/>
-      <c r="AC70" s="142"/>
+      <c r="AB70" s="134"/>
+      <c r="AC70" s="135"/>
       <c r="AD70" s="6" t="s">
         <v>16</v>
       </c>
@@ -19664,23 +19670,23 @@
       <c r="AA71" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="AB71" s="173">
+      <c r="AB71" s="174">
         <f>SUM(Y71:Y72)</f>
         <v>0</v>
       </c>
-      <c r="AC71" s="174"/>
+      <c r="AC71" s="175"/>
       <c r="AD71" s="16">
         <f>X71</f>
         <v>0</v>
       </c>
       <c r="AE71" s="17"/>
-      <c r="AF71" s="211" t="s">
+      <c r="AF71" s="198" t="s">
         <v>86</v>
       </c>
-      <c r="AG71" s="212"/>
-      <c r="AH71" s="212"/>
-      <c r="AI71" s="212"/>
-      <c r="AJ71" s="212"/>
+      <c r="AG71" s="199"/>
+      <c r="AH71" s="199"/>
+      <c r="AI71" s="199"/>
+      <c r="AJ71" s="199"/>
       <c r="AK71" s="203">
         <f>SUM(AD71:AD81)</f>
         <v>0</v>
@@ -19770,14 +19776,14 @@
       <c r="AA72" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="AB72" s="175"/>
-      <c r="AC72" s="176"/>
+      <c r="AB72" s="176"/>
+      <c r="AC72" s="177"/>
       <c r="AD72" s="16">
         <f t="shared" ref="AD72:AD86" si="23">X72</f>
         <v>0</v>
       </c>
       <c r="AE72" s="75"/>
-      <c r="AF72" s="199">
+      <c r="AF72" s="169">
         <f>+AD71+AD72</f>
         <v>0</v>
       </c>
@@ -19980,23 +19986,23 @@
       <c r="AA74" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="AB74" s="173">
+      <c r="AB74" s="174">
         <f>SUM(Y74:Y75)</f>
         <v>0</v>
       </c>
-      <c r="AC74" s="174"/>
+      <c r="AC74" s="175"/>
       <c r="AD74" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE74" s="17"/>
-      <c r="AF74" s="177" t="s">
+      <c r="AF74" s="178" t="s">
         <v>89</v>
       </c>
-      <c r="AG74" s="178"/>
-      <c r="AH74" s="178"/>
-      <c r="AI74" s="178"/>
-      <c r="AJ74" s="178"/>
+      <c r="AG74" s="179"/>
+      <c r="AH74" s="179"/>
+      <c r="AI74" s="179"/>
+      <c r="AJ74" s="179"/>
       <c r="AK74" s="205"/>
       <c r="AL74" s="206"/>
     </row>
@@ -20081,14 +20087,14 @@
       <c r="AA75" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AB75" s="175"/>
-      <c r="AC75" s="176"/>
+      <c r="AB75" s="176"/>
+      <c r="AC75" s="177"/>
       <c r="AD75" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE75" s="17"/>
-      <c r="AF75" s="199">
+      <c r="AF75" s="169">
         <f>+AD74+AD75</f>
         <v>0</v>
       </c>
@@ -20180,23 +20186,23 @@
       <c r="AA76" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="AB76" s="173">
+      <c r="AB76" s="174">
         <f>SUM(Y76:Y77)</f>
         <v>0</v>
       </c>
-      <c r="AC76" s="174"/>
+      <c r="AC76" s="175"/>
       <c r="AD76" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE76" s="17"/>
-      <c r="AF76" s="177" t="s">
+      <c r="AF76" s="178" t="s">
         <v>92</v>
       </c>
-      <c r="AG76" s="178"/>
-      <c r="AH76" s="178"/>
-      <c r="AI76" s="178"/>
-      <c r="AJ76" s="178"/>
+      <c r="AG76" s="179"/>
+      <c r="AH76" s="179"/>
+      <c r="AI76" s="179"/>
+      <c r="AJ76" s="179"/>
       <c r="AK76" s="205"/>
       <c r="AL76" s="206"/>
     </row>
@@ -20281,14 +20287,14 @@
       <c r="AA77" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB77" s="175"/>
-      <c r="AC77" s="176"/>
+      <c r="AB77" s="176"/>
+      <c r="AC77" s="177"/>
       <c r="AD77" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE77" s="17"/>
-      <c r="AF77" s="199">
+      <c r="AF77" s="169">
         <f>+AD76+AD77</f>
         <v>0</v>
       </c>
@@ -20301,7 +20307,7 @@
     </row>
     <row r="78" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B78" s="13" t="s">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="C78" s="14">
         <v>0</v>
@@ -20380,29 +20386,29 @@
       <c r="AA78" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="AB78" s="173">
+      <c r="AB78" s="174">
         <f>SUM(Y78:Y79)</f>
         <v>0</v>
       </c>
-      <c r="AC78" s="174"/>
+      <c r="AC78" s="175"/>
       <c r="AD78" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE78" s="17"/>
-      <c r="AF78" s="177" t="s">
+      <c r="AF78" s="178" t="s">
         <v>95</v>
       </c>
-      <c r="AG78" s="178"/>
-      <c r="AH78" s="178"/>
-      <c r="AI78" s="178"/>
-      <c r="AJ78" s="178"/>
+      <c r="AG78" s="179"/>
+      <c r="AH78" s="179"/>
+      <c r="AI78" s="179"/>
+      <c r="AJ78" s="179"/>
       <c r="AK78" s="205"/>
       <c r="AL78" s="206"/>
     </row>
     <row r="79" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B79" s="13" t="s">
-        <v>96</v>
+        <v>216</v>
       </c>
       <c r="C79" s="14">
         <v>0</v>
@@ -20481,14 +20487,14 @@
       <c r="AA79" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AB79" s="175"/>
-      <c r="AC79" s="176"/>
+      <c r="AB79" s="176"/>
+      <c r="AC79" s="177"/>
       <c r="AD79" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE79" s="17"/>
-      <c r="AF79" s="199">
+      <c r="AF79" s="169">
         <f>+AD78+AD79</f>
         <v>0</v>
       </c>
@@ -20501,7 +20507,7 @@
     </row>
     <row r="80" spans="2:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B80" s="13" t="s">
-        <v>97</v>
+        <v>217</v>
       </c>
       <c r="C80" s="14">
         <v>0</v>
@@ -20580,23 +20586,23 @@
       <c r="AA80" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="AB80" s="173">
+      <c r="AB80" s="174">
         <f>SUM(Y80:Y81)</f>
         <v>0</v>
       </c>
-      <c r="AC80" s="174"/>
+      <c r="AC80" s="175"/>
       <c r="AD80" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE80" s="17"/>
-      <c r="AF80" s="177" t="s">
+      <c r="AF80" s="178" t="s">
         <v>98</v>
       </c>
-      <c r="AG80" s="178"/>
-      <c r="AH80" s="178"/>
-      <c r="AI80" s="178"/>
-      <c r="AJ80" s="178"/>
+      <c r="AG80" s="179"/>
+      <c r="AH80" s="179"/>
+      <c r="AI80" s="179"/>
+      <c r="AJ80" s="179"/>
       <c r="AK80" s="201" t="s">
         <v>99</v>
       </c>
@@ -20604,7 +20610,7 @@
     </row>
     <row r="81" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B81" s="13" t="s">
-        <v>100</v>
+        <v>218</v>
       </c>
       <c r="C81" s="14">
         <v>0</v>
@@ -20683,14 +20689,14 @@
       <c r="AA81" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB81" s="175"/>
-      <c r="AC81" s="176"/>
+      <c r="AB81" s="176"/>
+      <c r="AC81" s="177"/>
       <c r="AD81" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE81" s="17"/>
-      <c r="AF81" s="199">
+      <c r="AF81" s="169">
         <f>+AD80+AD81</f>
         <v>0</v>
       </c>
@@ -20782,8 +20788,8 @@
       <c r="AA82" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="AB82" s="151"/>
-      <c r="AC82" s="152"/>
+      <c r="AB82" s="172"/>
+      <c r="AC82" s="173"/>
       <c r="AD82" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20878,8 +20884,8 @@
       <c r="AA83" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AB83" s="151"/>
-      <c r="AC83" s="152"/>
+      <c r="AB83" s="172"/>
+      <c r="AC83" s="173"/>
       <c r="AD83" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -20974,8 +20980,8 @@
       <c r="AA84" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="AB84" s="151"/>
-      <c r="AC84" s="152"/>
+      <c r="AB84" s="172"/>
+      <c r="AC84" s="173"/>
       <c r="AD84" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21070,8 +21076,8 @@
       <c r="AA85" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="AB85" s="151"/>
-      <c r="AC85" s="152"/>
+      <c r="AB85" s="172"/>
+      <c r="AC85" s="173"/>
       <c r="AD85" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21188,46 +21194,46 @@
       <c r="B87" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="C87" s="137" t="s">
+      <c r="C87" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D87" s="138"/>
-      <c r="E87" s="137" t="s">
+      <c r="D87" s="129"/>
+      <c r="E87" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F87" s="138"/>
-      <c r="G87" s="137" t="s">
+      <c r="F87" s="129"/>
+      <c r="G87" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H87" s="138"/>
-      <c r="I87" s="137" t="s">
+      <c r="H87" s="129"/>
+      <c r="I87" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J87" s="138"/>
-      <c r="K87" s="137" t="s">
+      <c r="J87" s="129"/>
+      <c r="K87" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L87" s="138"/>
-      <c r="M87" s="137" t="s">
+      <c r="L87" s="129"/>
+      <c r="M87" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N87" s="138"/>
-      <c r="O87" s="137" t="s">
+      <c r="N87" s="129"/>
+      <c r="O87" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P87" s="138"/>
-      <c r="Q87" s="137" t="s">
+      <c r="P87" s="129"/>
+      <c r="Q87" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R87" s="138"/>
-      <c r="S87" s="137" t="s">
+      <c r="R87" s="129"/>
+      <c r="S87" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T87" s="138"/>
-      <c r="U87" s="137" t="s">
+      <c r="T87" s="129"/>
+      <c r="U87" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V87" s="138"/>
+      <c r="V87" s="129"/>
       <c r="W87" s="9" t="s">
         <v>12</v>
       </c>
@@ -21241,17 +21247,17 @@
       <c r="AA87" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="AB87" s="141"/>
-      <c r="AC87" s="142"/>
+      <c r="AB87" s="134"/>
+      <c r="AC87" s="135"/>
       <c r="AD87" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AE87" s="7"/>
-      <c r="AK87" s="196">
+      <c r="AK87" s="211">
         <f>SUM(AD88:AD139)</f>
         <v>0</v>
       </c>
-      <c r="AL87" s="197"/>
+      <c r="AL87" s="212"/>
     </row>
     <row r="88" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B88" s="15" t="s">
@@ -21334,15 +21340,15 @@
       <c r="AA88" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="AB88" s="147"/>
-      <c r="AC88" s="148"/>
+      <c r="AB88" s="214"/>
+      <c r="AC88" s="215"/>
       <c r="AD88" s="16">
         <f>X88</f>
         <v>0</v>
       </c>
       <c r="AE88" s="7"/>
-      <c r="AK88" s="198"/>
-      <c r="AL88" s="197"/>
+      <c r="AK88" s="213"/>
+      <c r="AL88" s="212"/>
     </row>
     <row r="89" spans="1:38" s="64" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B89" s="65"/>
@@ -21385,8 +21391,8 @@
       <c r="AH89" s="2"/>
       <c r="AI89" s="2"/>
       <c r="AJ89" s="2"/>
-      <c r="AK89" s="198"/>
-      <c r="AL89" s="197"/>
+      <c r="AK89" s="213"/>
+      <c r="AL89" s="212"/>
     </row>
     <row r="90" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B90" s="13" t="s">
@@ -21469,8 +21475,8 @@
       <c r="AA90" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB90" s="151"/>
-      <c r="AC90" s="152"/>
+      <c r="AB90" s="172"/>
+      <c r="AC90" s="173"/>
       <c r="AD90" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21481,8 +21487,8 @@
       <c r="AH90" s="2"/>
       <c r="AI90" s="2"/>
       <c r="AJ90" s="2"/>
-      <c r="AK90" s="198"/>
-      <c r="AL90" s="197"/>
+      <c r="AK90" s="213"/>
+      <c r="AL90" s="212"/>
     </row>
     <row r="91" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B91" s="13" t="s">
@@ -21565,8 +21571,8 @@
       <c r="AA91" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AB91" s="151"/>
-      <c r="AC91" s="152"/>
+      <c r="AB91" s="172"/>
+      <c r="AC91" s="173"/>
       <c r="AD91" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21577,8 +21583,8 @@
       <c r="AH91" s="2"/>
       <c r="AI91" s="2"/>
       <c r="AJ91" s="2"/>
-      <c r="AK91" s="198"/>
-      <c r="AL91" s="197"/>
+      <c r="AK91" s="213"/>
+      <c r="AL91" s="212"/>
     </row>
     <row r="92" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B92" s="13" t="s">
@@ -21661,8 +21667,8 @@
       <c r="AA92" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="AB92" s="151"/>
-      <c r="AC92" s="152"/>
+      <c r="AB92" s="172"/>
+      <c r="AC92" s="173"/>
       <c r="AD92" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21673,8 +21679,8 @@
       <c r="AH92" s="2"/>
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
-      <c r="AK92" s="198"/>
-      <c r="AL92" s="197"/>
+      <c r="AK92" s="213"/>
+      <c r="AL92" s="212"/>
     </row>
     <row r="93" spans="1:38" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B93" s="13" t="s">
@@ -21757,11 +21763,11 @@
       <c r="AA93" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="AB93" s="156">
+      <c r="AB93" s="216">
         <f>SUM(Y93:Y102)</f>
         <v>0</v>
       </c>
-      <c r="AC93" s="157"/>
+      <c r="AC93" s="141"/>
       <c r="AD93" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21774,8 +21780,8 @@
       <c r="AH93" s="163"/>
       <c r="AI93" s="163"/>
       <c r="AJ93" s="164"/>
-      <c r="AK93" s="198"/>
-      <c r="AL93" s="197"/>
+      <c r="AK93" s="213"/>
+      <c r="AL93" s="212"/>
     </row>
     <row r="94" spans="1:38" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A94" s="12"/>
@@ -21859,20 +21865,20 @@
       <c r="AA94" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="AB94" s="158"/>
-      <c r="AC94" s="159"/>
+      <c r="AB94" s="217"/>
+      <c r="AC94" s="142"/>
       <c r="AD94" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE94" s="17"/>
       <c r="AF94" s="165"/>
-      <c r="AG94" s="166"/>
-      <c r="AH94" s="166"/>
-      <c r="AI94" s="166"/>
-      <c r="AJ94" s="167"/>
-      <c r="AK94" s="198"/>
-      <c r="AL94" s="197"/>
+      <c r="AG94" s="154"/>
+      <c r="AH94" s="154"/>
+      <c r="AI94" s="154"/>
+      <c r="AJ94" s="155"/>
+      <c r="AK94" s="213"/>
+      <c r="AL94" s="212"/>
     </row>
     <row r="95" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A95" s="12"/>
@@ -21956,20 +21962,20 @@
       <c r="AA95" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="AB95" s="158"/>
-      <c r="AC95" s="159"/>
+      <c r="AB95" s="217"/>
+      <c r="AC95" s="142"/>
       <c r="AD95" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE95" s="17"/>
       <c r="AF95" s="165"/>
-      <c r="AG95" s="166"/>
-      <c r="AH95" s="166"/>
-      <c r="AI95" s="166"/>
-      <c r="AJ95" s="167"/>
-      <c r="AK95" s="198"/>
-      <c r="AL95" s="197"/>
+      <c r="AG95" s="154"/>
+      <c r="AH95" s="154"/>
+      <c r="AI95" s="154"/>
+      <c r="AJ95" s="155"/>
+      <c r="AK95" s="213"/>
+      <c r="AL95" s="212"/>
     </row>
     <row r="96" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A96" s="12"/>
@@ -22053,20 +22059,20 @@
       <c r="AA96" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="AB96" s="158"/>
-      <c r="AC96" s="159"/>
+      <c r="AB96" s="217"/>
+      <c r="AC96" s="142"/>
       <c r="AD96" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE96" s="17"/>
       <c r="AF96" s="165"/>
-      <c r="AG96" s="166"/>
-      <c r="AH96" s="166"/>
-      <c r="AI96" s="166"/>
-      <c r="AJ96" s="167"/>
-      <c r="AK96" s="198"/>
-      <c r="AL96" s="197"/>
+      <c r="AG96" s="154"/>
+      <c r="AH96" s="154"/>
+      <c r="AI96" s="154"/>
+      <c r="AJ96" s="155"/>
+      <c r="AK96" s="213"/>
+      <c r="AL96" s="212"/>
     </row>
     <row r="97" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A97" s="12"/>
@@ -22150,20 +22156,20 @@
       <c r="AA97" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AB97" s="158"/>
-      <c r="AC97" s="159"/>
+      <c r="AB97" s="217"/>
+      <c r="AC97" s="142"/>
       <c r="AD97" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE97" s="17"/>
       <c r="AF97" s="165"/>
-      <c r="AG97" s="166"/>
-      <c r="AH97" s="166"/>
-      <c r="AI97" s="166"/>
-      <c r="AJ97" s="167"/>
-      <c r="AK97" s="198"/>
-      <c r="AL97" s="197"/>
+      <c r="AG97" s="154"/>
+      <c r="AH97" s="154"/>
+      <c r="AI97" s="154"/>
+      <c r="AJ97" s="155"/>
+      <c r="AK97" s="213"/>
+      <c r="AL97" s="212"/>
     </row>
     <row r="98" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A98" s="12"/>
@@ -22247,23 +22253,23 @@
       <c r="AA98" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AB98" s="158"/>
-      <c r="AC98" s="159"/>
+      <c r="AB98" s="217"/>
+      <c r="AC98" s="142"/>
       <c r="AD98" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE98" s="17"/>
-      <c r="AF98" s="185">
+      <c r="AF98" s="219">
         <f>SUM(AD93:AD102)</f>
         <v>0</v>
       </c>
-      <c r="AG98" s="186"/>
-      <c r="AH98" s="186"/>
-      <c r="AI98" s="186"/>
-      <c r="AJ98" s="187"/>
-      <c r="AK98" s="198"/>
-      <c r="AL98" s="197"/>
+      <c r="AG98" s="220"/>
+      <c r="AH98" s="220"/>
+      <c r="AI98" s="220"/>
+      <c r="AJ98" s="221"/>
+      <c r="AK98" s="213"/>
+      <c r="AL98" s="212"/>
     </row>
     <row r="99" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A99" s="12"/>
@@ -22347,8 +22353,8 @@
       <c r="AA99" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AB99" s="158"/>
-      <c r="AC99" s="159"/>
+      <c r="AB99" s="217"/>
+      <c r="AC99" s="142"/>
       <c r="AD99" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22359,8 +22365,8 @@
       <c r="AH99" s="24"/>
       <c r="AI99" s="24"/>
       <c r="AJ99" s="25"/>
-      <c r="AK99" s="198"/>
-      <c r="AL99" s="197"/>
+      <c r="AK99" s="213"/>
+      <c r="AL99" s="212"/>
     </row>
     <row r="100" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A100" s="12"/>
@@ -22444,20 +22450,20 @@
       <c r="AA100" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AB100" s="158"/>
-      <c r="AC100" s="159"/>
+      <c r="AB100" s="217"/>
+      <c r="AC100" s="142"/>
       <c r="AD100" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE100" s="17"/>
-      <c r="AF100" s="168"/>
-      <c r="AG100" s="166"/>
-      <c r="AH100" s="166"/>
-      <c r="AI100" s="166"/>
-      <c r="AJ100" s="167"/>
-      <c r="AK100" s="198"/>
-      <c r="AL100" s="197"/>
+      <c r="AF100" s="153"/>
+      <c r="AG100" s="154"/>
+      <c r="AH100" s="154"/>
+      <c r="AI100" s="154"/>
+      <c r="AJ100" s="155"/>
+      <c r="AK100" s="213"/>
+      <c r="AL100" s="212"/>
     </row>
     <row r="101" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A101" s="12"/>
@@ -22541,8 +22547,8 @@
       <c r="AA101" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="AB101" s="158"/>
-      <c r="AC101" s="159"/>
+      <c r="AB101" s="217"/>
+      <c r="AC101" s="142"/>
       <c r="AD101" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22553,8 +22559,8 @@
       <c r="AH101" s="27"/>
       <c r="AI101" s="27"/>
       <c r="AJ101" s="28"/>
-      <c r="AK101" s="198"/>
-      <c r="AL101" s="197"/>
+      <c r="AK101" s="213"/>
+      <c r="AL101" s="212"/>
     </row>
     <row r="102" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A102" s="12"/>
@@ -22638,8 +22644,8 @@
       <c r="AA102" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="AB102" s="160"/>
-      <c r="AC102" s="161"/>
+      <c r="AB102" s="218"/>
+      <c r="AC102" s="143"/>
       <c r="AD102" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22650,8 +22656,8 @@
       <c r="AH102" s="84"/>
       <c r="AI102" s="84"/>
       <c r="AJ102" s="85"/>
-      <c r="AK102" s="198"/>
-      <c r="AL102" s="197"/>
+      <c r="AK102" s="213"/>
+      <c r="AL102" s="212"/>
     </row>
     <row r="103" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A103" s="12"/>
@@ -22744,132 +22750,132 @@
       <c r="Y103" s="14"/>
       <c r="Z103" s="14"/>
       <c r="AA103" s="13"/>
-      <c r="AB103" s="188"/>
-      <c r="AC103" s="189"/>
+      <c r="AB103" s="181"/>
+      <c r="AC103" s="182"/>
       <c r="AD103" s="33"/>
       <c r="AE103" s="17"/>
-      <c r="AF103" s="190"/>
-      <c r="AG103" s="191"/>
-      <c r="AH103" s="191"/>
-      <c r="AI103" s="191"/>
-      <c r="AJ103" s="192"/>
-      <c r="AK103" s="198"/>
-      <c r="AL103" s="197"/>
+      <c r="AF103" s="144"/>
+      <c r="AG103" s="145"/>
+      <c r="AH103" s="145"/>
+      <c r="AI103" s="145"/>
+      <c r="AJ103" s="146"/>
+      <c r="AK103" s="213"/>
+      <c r="AL103" s="212"/>
     </row>
     <row r="104" spans="1:38" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="171" t="s">
-        <v>0</v>
-      </c>
-      <c r="C104" s="172"/>
-      <c r="D104" s="172"/>
-      <c r="E104" s="172"/>
-      <c r="F104" s="172"/>
-      <c r="G104" s="172"/>
-      <c r="H104" s="172"/>
-      <c r="I104" s="172"/>
-      <c r="J104" s="172"/>
-      <c r="K104" s="172"/>
-      <c r="L104" s="172"/>
-      <c r="M104" s="172"/>
-      <c r="N104" s="172"/>
-      <c r="O104" s="172"/>
-      <c r="P104" s="172"/>
-      <c r="Q104" s="172"/>
-      <c r="R104" s="172"/>
-      <c r="S104" s="172"/>
-      <c r="T104" s="172"/>
-      <c r="U104" s="172"/>
-      <c r="V104" s="172"/>
-      <c r="W104" s="172"/>
-      <c r="X104" s="172"/>
-      <c r="Y104" s="172"/>
-      <c r="Z104" s="172"/>
-      <c r="AA104" s="172"/>
-      <c r="AB104" s="172"/>
-      <c r="AC104" s="172"/>
-      <c r="AD104" s="172"/>
+      <c r="B104" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C104" s="133"/>
+      <c r="D104" s="133"/>
+      <c r="E104" s="133"/>
+      <c r="F104" s="133"/>
+      <c r="G104" s="133"/>
+      <c r="H104" s="133"/>
+      <c r="I104" s="133"/>
+      <c r="J104" s="133"/>
+      <c r="K104" s="133"/>
+      <c r="L104" s="133"/>
+      <c r="M104" s="133"/>
+      <c r="N104" s="133"/>
+      <c r="O104" s="133"/>
+      <c r="P104" s="133"/>
+      <c r="Q104" s="133"/>
+      <c r="R104" s="133"/>
+      <c r="S104" s="133"/>
+      <c r="T104" s="133"/>
+      <c r="U104" s="133"/>
+      <c r="V104" s="133"/>
+      <c r="W104" s="133"/>
+      <c r="X104" s="133"/>
+      <c r="Y104" s="133"/>
+      <c r="Z104" s="133"/>
+      <c r="AA104" s="133"/>
+      <c r="AB104" s="133"/>
+      <c r="AC104" s="133"/>
+      <c r="AD104" s="133"/>
       <c r="AE104" s="1"/>
-      <c r="AF104" s="193"/>
-      <c r="AG104" s="194"/>
-      <c r="AH104" s="194"/>
-      <c r="AI104" s="194"/>
-      <c r="AJ104" s="195"/>
-      <c r="AK104" s="198"/>
-      <c r="AL104" s="197"/>
+      <c r="AF104" s="147"/>
+      <c r="AG104" s="148"/>
+      <c r="AH104" s="148"/>
+      <c r="AI104" s="148"/>
+      <c r="AJ104" s="149"/>
+      <c r="AK104" s="213"/>
+      <c r="AL104" s="212"/>
     </row>
     <row r="105" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B105" s="169" t="s">
+      <c r="B105" s="130" t="s">
         <v>122</v>
       </c>
-      <c r="C105" s="137" t="s">
+      <c r="C105" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D105" s="138"/>
-      <c r="E105" s="137" t="s">
+      <c r="D105" s="129"/>
+      <c r="E105" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F105" s="138"/>
-      <c r="G105" s="137" t="s">
+      <c r="F105" s="129"/>
+      <c r="G105" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H105" s="138"/>
-      <c r="I105" s="137" t="s">
+      <c r="H105" s="129"/>
+      <c r="I105" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J105" s="138"/>
-      <c r="K105" s="137" t="s">
+      <c r="J105" s="129"/>
+      <c r="K105" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L105" s="138"/>
-      <c r="M105" s="137" t="s">
+      <c r="L105" s="129"/>
+      <c r="M105" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N105" s="138"/>
-      <c r="O105" s="137" t="s">
+      <c r="N105" s="129"/>
+      <c r="O105" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P105" s="138"/>
-      <c r="Q105" s="137" t="s">
+      <c r="P105" s="129"/>
+      <c r="Q105" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R105" s="138"/>
-      <c r="S105" s="137" t="s">
+      <c r="R105" s="129"/>
+      <c r="S105" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T105" s="138"/>
-      <c r="U105" s="137" t="s">
+      <c r="T105" s="129"/>
+      <c r="U105" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V105" s="138"/>
-      <c r="W105" s="169" t="s">
+      <c r="V105" s="129"/>
+      <c r="W105" s="130" t="s">
         <v>12</v>
       </c>
       <c r="X105" s="110"/>
-      <c r="Y105" s="169" t="s">
+      <c r="Y105" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z105" s="169" t="s">
+      <c r="Z105" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA105" s="169" t="s">
+      <c r="AA105" s="130" t="s">
         <v>122</v>
       </c>
-      <c r="AB105" s="141"/>
-      <c r="AC105" s="142"/>
+      <c r="AB105" s="134"/>
+      <c r="AC105" s="135"/>
       <c r="AD105" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AE105" s="7"/>
-      <c r="AF105" s="193"/>
-      <c r="AG105" s="194"/>
-      <c r="AH105" s="194"/>
-      <c r="AI105" s="194"/>
-      <c r="AJ105" s="195"/>
-      <c r="AK105" s="198"/>
-      <c r="AL105" s="197"/>
+      <c r="AF105" s="147"/>
+      <c r="AG105" s="148"/>
+      <c r="AH105" s="148"/>
+      <c r="AI105" s="148"/>
+      <c r="AJ105" s="149"/>
+      <c r="AK105" s="213"/>
+      <c r="AL105" s="212"/>
     </row>
     <row r="106" spans="1:38" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B106" s="170"/>
+      <c r="B106" s="131"/>
       <c r="C106" s="9" t="s">
         <v>17</v>
       </c>
@@ -22930,22 +22936,22 @@
       <c r="V106" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W106" s="170"/>
+      <c r="W106" s="131"/>
       <c r="X106" s="111"/>
-      <c r="Y106" s="170"/>
-      <c r="Z106" s="170"/>
-      <c r="AA106" s="170"/>
+      <c r="Y106" s="131"/>
+      <c r="Z106" s="131"/>
+      <c r="AA106" s="131"/>
       <c r="AB106" s="10"/>
       <c r="AC106" s="11"/>
       <c r="AD106" s="6"/>
       <c r="AE106" s="7"/>
-      <c r="AF106" s="193"/>
-      <c r="AG106" s="194"/>
-      <c r="AH106" s="194"/>
-      <c r="AI106" s="194"/>
-      <c r="AJ106" s="195"/>
-      <c r="AK106" s="198"/>
-      <c r="AL106" s="197"/>
+      <c r="AF106" s="147"/>
+      <c r="AG106" s="148"/>
+      <c r="AH106" s="148"/>
+      <c r="AI106" s="148"/>
+      <c r="AJ106" s="149"/>
+      <c r="AK106" s="213"/>
+      <c r="AL106" s="212"/>
     </row>
     <row r="107" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A107" s="12"/>
@@ -23029,23 +23035,23 @@
       <c r="AA107" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AB107" s="156">
+      <c r="AB107" s="216">
         <f>SUM(Y107:Y110)</f>
         <v>0</v>
       </c>
-      <c r="AC107" s="157"/>
+      <c r="AC107" s="141"/>
       <c r="AD107" s="16">
         <f>X107</f>
         <v>0</v>
       </c>
       <c r="AE107" s="17"/>
-      <c r="AF107" s="193"/>
-      <c r="AG107" s="194"/>
-      <c r="AH107" s="194"/>
-      <c r="AI107" s="194"/>
-      <c r="AJ107" s="195"/>
-      <c r="AK107" s="198"/>
-      <c r="AL107" s="197"/>
+      <c r="AF107" s="147"/>
+      <c r="AG107" s="148"/>
+      <c r="AH107" s="148"/>
+      <c r="AI107" s="148"/>
+      <c r="AJ107" s="149"/>
+      <c r="AK107" s="213"/>
+      <c r="AL107" s="212"/>
     </row>
     <row r="108" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A108" s="12"/>
@@ -23129,8 +23135,8 @@
       <c r="AA108" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AB108" s="158"/>
-      <c r="AC108" s="159"/>
+      <c r="AB108" s="217"/>
+      <c r="AC108" s="142"/>
       <c r="AD108" s="16">
         <f t="shared" ref="AD108:AD138" si="31">X108</f>
         <v>0</v>
@@ -23141,8 +23147,8 @@
       <c r="AH108" s="24"/>
       <c r="AI108" s="24"/>
       <c r="AJ108" s="25"/>
-      <c r="AK108" s="198"/>
-      <c r="AL108" s="197"/>
+      <c r="AK108" s="213"/>
+      <c r="AL108" s="212"/>
     </row>
     <row r="109" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A109" s="12"/>
@@ -23226,8 +23232,8 @@
       <c r="AA109" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AB109" s="158"/>
-      <c r="AC109" s="159"/>
+      <c r="AB109" s="217"/>
+      <c r="AC109" s="142"/>
       <c r="AD109" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23238,8 +23244,8 @@
       <c r="AH109" s="24"/>
       <c r="AI109" s="24"/>
       <c r="AJ109" s="25"/>
-      <c r="AK109" s="198"/>
-      <c r="AL109" s="197"/>
+      <c r="AK109" s="213"/>
+      <c r="AL109" s="212"/>
     </row>
     <row r="110" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A110" s="12"/>
@@ -23323,8 +23329,8 @@
       <c r="AA110" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="AB110" s="158"/>
-      <c r="AC110" s="159"/>
+      <c r="AB110" s="217"/>
+      <c r="AC110" s="142"/>
       <c r="AD110" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23335,8 +23341,8 @@
       <c r="AH110" s="24"/>
       <c r="AI110" s="24"/>
       <c r="AJ110" s="25"/>
-      <c r="AK110" s="198"/>
-      <c r="AL110" s="197"/>
+      <c r="AK110" s="213"/>
+      <c r="AL110" s="212"/>
     </row>
     <row r="111" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A111" s="12"/>
@@ -23429,20 +23435,20 @@
       <c r="Y111" s="14"/>
       <c r="Z111" s="14"/>
       <c r="AA111" s="13"/>
-      <c r="AB111" s="160"/>
-      <c r="AC111" s="161"/>
+      <c r="AB111" s="218"/>
+      <c r="AC111" s="143"/>
       <c r="AD111" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE111" s="17"/>
-      <c r="AF111" s="180"/>
-      <c r="AG111" s="181"/>
-      <c r="AH111" s="181"/>
-      <c r="AI111" s="181"/>
-      <c r="AJ111" s="182"/>
-      <c r="AK111" s="198"/>
-      <c r="AL111" s="197"/>
+      <c r="AF111" s="224"/>
+      <c r="AG111" s="225"/>
+      <c r="AH111" s="225"/>
+      <c r="AI111" s="225"/>
+      <c r="AJ111" s="226"/>
+      <c r="AK111" s="213"/>
+      <c r="AL111" s="212"/>
     </row>
     <row r="112" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B112" s="13" t="s">
@@ -23525,11 +23531,11 @@
       <c r="AA112" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="AB112" s="156">
+      <c r="AB112" s="216">
         <f>SUM(Y112:Y124)</f>
         <v>0</v>
       </c>
-      <c r="AC112" s="157"/>
+      <c r="AC112" s="141"/>
       <c r="AD112" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23542,8 +23548,8 @@
       <c r="AH112" s="163"/>
       <c r="AI112" s="163"/>
       <c r="AJ112" s="164"/>
-      <c r="AK112" s="198"/>
-      <c r="AL112" s="197"/>
+      <c r="AK112" s="213"/>
+      <c r="AL112" s="212"/>
     </row>
     <row r="113" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B113" s="13" t="s">
@@ -23626,22 +23632,22 @@
       <c r="AA113" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="AB113" s="158"/>
-      <c r="AC113" s="159"/>
+      <c r="AB113" s="217"/>
+      <c r="AC113" s="142"/>
       <c r="AD113" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE113" s="17"/>
       <c r="AF113" s="165"/>
-      <c r="AG113" s="166"/>
-      <c r="AH113" s="166"/>
-      <c r="AI113" s="166"/>
-      <c r="AJ113" s="167"/>
-      <c r="AK113" s="183" t="s">
+      <c r="AG113" s="154"/>
+      <c r="AH113" s="154"/>
+      <c r="AI113" s="154"/>
+      <c r="AJ113" s="155"/>
+      <c r="AK113" s="222" t="s">
         <v>130</v>
       </c>
-      <c r="AL113" s="184"/>
+      <c r="AL113" s="223"/>
     </row>
     <row r="114" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B114" s="13" t="s">
@@ -23724,20 +23730,20 @@
       <c r="AA114" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="AB114" s="158"/>
-      <c r="AC114" s="159"/>
+      <c r="AB114" s="217"/>
+      <c r="AC114" s="142"/>
       <c r="AD114" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE114" s="17"/>
       <c r="AF114" s="165"/>
-      <c r="AG114" s="166"/>
-      <c r="AH114" s="166"/>
-      <c r="AI114" s="166"/>
-      <c r="AJ114" s="167"/>
-      <c r="AK114" s="183"/>
-      <c r="AL114" s="184"/>
+      <c r="AG114" s="154"/>
+      <c r="AH114" s="154"/>
+      <c r="AI114" s="154"/>
+      <c r="AJ114" s="155"/>
+      <c r="AK114" s="222"/>
+      <c r="AL114" s="223"/>
     </row>
     <row r="115" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B115" s="13" t="s">
@@ -23820,20 +23826,20 @@
       <c r="AA115" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AB115" s="158"/>
-      <c r="AC115" s="159"/>
+      <c r="AB115" s="217"/>
+      <c r="AC115" s="142"/>
       <c r="AD115" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE115" s="17"/>
       <c r="AF115" s="165"/>
-      <c r="AG115" s="166"/>
-      <c r="AH115" s="166"/>
-      <c r="AI115" s="166"/>
-      <c r="AJ115" s="167"/>
-      <c r="AK115" s="183"/>
-      <c r="AL115" s="184"/>
+      <c r="AG115" s="154"/>
+      <c r="AH115" s="154"/>
+      <c r="AI115" s="154"/>
+      <c r="AJ115" s="155"/>
+      <c r="AK115" s="222"/>
+      <c r="AL115" s="223"/>
     </row>
     <row r="116" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B116" s="13" t="s">
@@ -23916,20 +23922,20 @@
       <c r="AA116" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AB116" s="158"/>
-      <c r="AC116" s="159"/>
+      <c r="AB116" s="217"/>
+      <c r="AC116" s="142"/>
       <c r="AD116" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE116" s="17"/>
       <c r="AF116" s="165"/>
-      <c r="AG116" s="166"/>
-      <c r="AH116" s="166"/>
-      <c r="AI116" s="166"/>
-      <c r="AJ116" s="167"/>
-      <c r="AK116" s="183"/>
-      <c r="AL116" s="184"/>
+      <c r="AG116" s="154"/>
+      <c r="AH116" s="154"/>
+      <c r="AI116" s="154"/>
+      <c r="AJ116" s="155"/>
+      <c r="AK116" s="222"/>
+      <c r="AL116" s="223"/>
     </row>
     <row r="117" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B117" s="13" t="s">
@@ -24012,20 +24018,20 @@
       <c r="AA117" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AB117" s="158"/>
-      <c r="AC117" s="159"/>
+      <c r="AB117" s="217"/>
+      <c r="AC117" s="142"/>
       <c r="AD117" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE117" s="17"/>
       <c r="AF117" s="165"/>
-      <c r="AG117" s="166"/>
-      <c r="AH117" s="166"/>
-      <c r="AI117" s="166"/>
-      <c r="AJ117" s="167"/>
-      <c r="AK117" s="183"/>
-      <c r="AL117" s="184"/>
+      <c r="AG117" s="154"/>
+      <c r="AH117" s="154"/>
+      <c r="AI117" s="154"/>
+      <c r="AJ117" s="155"/>
+      <c r="AK117" s="222"/>
+      <c r="AL117" s="223"/>
     </row>
     <row r="118" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A118" s="12"/>
@@ -24109,23 +24115,23 @@
       <c r="AA118" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="AB118" s="158"/>
-      <c r="AC118" s="159"/>
+      <c r="AB118" s="217"/>
+      <c r="AC118" s="142"/>
       <c r="AD118" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE118" s="17"/>
-      <c r="AF118" s="168">
+      <c r="AF118" s="153">
         <f>SUM(AD112:AD124)</f>
         <v>0</v>
       </c>
-      <c r="AG118" s="166"/>
-      <c r="AH118" s="166"/>
-      <c r="AI118" s="166"/>
-      <c r="AJ118" s="167"/>
-      <c r="AK118" s="183"/>
-      <c r="AL118" s="184"/>
+      <c r="AG118" s="154"/>
+      <c r="AH118" s="154"/>
+      <c r="AI118" s="154"/>
+      <c r="AJ118" s="155"/>
+      <c r="AK118" s="222"/>
+      <c r="AL118" s="223"/>
     </row>
     <row r="119" spans="1:38" s="47" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A119" s="12"/>
@@ -24209,20 +24215,20 @@
       <c r="AA119" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="AB119" s="158"/>
-      <c r="AC119" s="159"/>
+      <c r="AB119" s="217"/>
+      <c r="AC119" s="142"/>
       <c r="AD119" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE119" s="17"/>
-      <c r="AF119" s="168"/>
-      <c r="AG119" s="166"/>
-      <c r="AH119" s="166"/>
-      <c r="AI119" s="166"/>
-      <c r="AJ119" s="167"/>
-      <c r="AK119" s="183"/>
-      <c r="AL119" s="184"/>
+      <c r="AF119" s="153"/>
+      <c r="AG119" s="154"/>
+      <c r="AH119" s="154"/>
+      <c r="AI119" s="154"/>
+      <c r="AJ119" s="155"/>
+      <c r="AK119" s="222"/>
+      <c r="AL119" s="223"/>
     </row>
     <row r="120" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B120" s="13" t="s">
@@ -24305,8 +24311,8 @@
       <c r="AA120" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="AB120" s="158"/>
-      <c r="AC120" s="159"/>
+      <c r="AB120" s="217"/>
+      <c r="AC120" s="142"/>
       <c r="AD120" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24317,8 +24323,8 @@
       <c r="AH120" s="27"/>
       <c r="AI120" s="27"/>
       <c r="AJ120" s="28"/>
-      <c r="AK120" s="183"/>
-      <c r="AL120" s="184"/>
+      <c r="AK120" s="222"/>
+      <c r="AL120" s="223"/>
     </row>
     <row r="121" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B121" s="13" t="s">
@@ -24401,8 +24407,8 @@
       <c r="AA121" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AB121" s="158"/>
-      <c r="AC121" s="159"/>
+      <c r="AB121" s="217"/>
+      <c r="AC121" s="142"/>
       <c r="AD121" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24413,8 +24419,8 @@
       <c r="AH121" s="27"/>
       <c r="AI121" s="27"/>
       <c r="AJ121" s="28"/>
-      <c r="AK121" s="183"/>
-      <c r="AL121" s="184"/>
+      <c r="AK121" s="222"/>
+      <c r="AL121" s="223"/>
     </row>
     <row r="122" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B122" s="13" t="s">
@@ -24497,8 +24503,8 @@
       <c r="AA122" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AB122" s="158"/>
-      <c r="AC122" s="159"/>
+      <c r="AB122" s="217"/>
+      <c r="AC122" s="142"/>
       <c r="AD122" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24509,8 +24515,8 @@
       <c r="AH122" s="27"/>
       <c r="AI122" s="27"/>
       <c r="AJ122" s="28"/>
-      <c r="AK122" s="183"/>
-      <c r="AL122" s="184"/>
+      <c r="AK122" s="222"/>
+      <c r="AL122" s="223"/>
     </row>
     <row r="123" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B123" s="13" t="s">
@@ -24593,8 +24599,8 @@
       <c r="AA123" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AB123" s="158"/>
-      <c r="AC123" s="159"/>
+      <c r="AB123" s="217"/>
+      <c r="AC123" s="142"/>
       <c r="AD123" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24605,8 +24611,8 @@
       <c r="AH123" s="84"/>
       <c r="AI123" s="84"/>
       <c r="AJ123" s="85"/>
-      <c r="AK123" s="183"/>
-      <c r="AL123" s="184"/>
+      <c r="AK123" s="222"/>
+      <c r="AL123" s="223"/>
     </row>
     <row r="124" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B124" s="13" t="s">
@@ -24689,8 +24695,8 @@
       <c r="AA124" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AB124" s="158"/>
-      <c r="AC124" s="159"/>
+      <c r="AB124" s="217"/>
+      <c r="AC124" s="142"/>
       <c r="AD124" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24701,8 +24707,8 @@
       <c r="AH124" s="84"/>
       <c r="AI124" s="84"/>
       <c r="AJ124" s="85"/>
-      <c r="AK124" s="183"/>
-      <c r="AL124" s="184"/>
+      <c r="AK124" s="222"/>
+      <c r="AL124" s="223"/>
     </row>
     <row r="125" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B125" s="13"/>
@@ -24796,8 +24802,8 @@
       <c r="Y125" s="14"/>
       <c r="Z125" s="14"/>
       <c r="AA125" s="13"/>
-      <c r="AB125" s="160"/>
-      <c r="AC125" s="161"/>
+      <c r="AB125" s="218"/>
+      <c r="AC125" s="143"/>
       <c r="AD125" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24808,8 +24814,8 @@
       <c r="AH125" s="24"/>
       <c r="AI125" s="24"/>
       <c r="AJ125" s="25"/>
-      <c r="AK125" s="183"/>
-      <c r="AL125" s="184"/>
+      <c r="AK125" s="222"/>
+      <c r="AL125" s="223"/>
     </row>
     <row r="126" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B126" s="13" t="s">
@@ -24892,11 +24898,11 @@
       <c r="AA126" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AB126" s="156">
+      <c r="AB126" s="216">
         <f>SUM(Y126:Y137)</f>
         <v>0</v>
       </c>
-      <c r="AC126" s="157"/>
+      <c r="AC126" s="141"/>
       <c r="AD126" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24909,8 +24915,8 @@
       <c r="AH126" s="163"/>
       <c r="AI126" s="163"/>
       <c r="AJ126" s="164"/>
-      <c r="AK126" s="183"/>
-      <c r="AL126" s="184"/>
+      <c r="AK126" s="222"/>
+      <c r="AL126" s="223"/>
     </row>
     <row r="127" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B127" s="13" t="s">
@@ -24993,20 +24999,20 @@
       <c r="AA127" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="AB127" s="158"/>
-      <c r="AC127" s="159"/>
+      <c r="AB127" s="217"/>
+      <c r="AC127" s="142"/>
       <c r="AD127" s="16">
         <f>X127</f>
         <v>0</v>
       </c>
       <c r="AE127" s="17"/>
       <c r="AF127" s="165"/>
-      <c r="AG127" s="247"/>
-      <c r="AH127" s="247"/>
-      <c r="AI127" s="247"/>
-      <c r="AJ127" s="167"/>
-      <c r="AK127" s="183"/>
-      <c r="AL127" s="184"/>
+      <c r="AG127" s="154"/>
+      <c r="AH127" s="154"/>
+      <c r="AI127" s="154"/>
+      <c r="AJ127" s="155"/>
+      <c r="AK127" s="222"/>
+      <c r="AL127" s="223"/>
     </row>
     <row r="128" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B128" s="13" t="s">
@@ -25089,20 +25095,20 @@
       <c r="AA128" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="AB128" s="158"/>
-      <c r="AC128" s="159"/>
+      <c r="AB128" s="217"/>
+      <c r="AC128" s="142"/>
       <c r="AD128" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE128" s="17"/>
       <c r="AF128" s="165"/>
-      <c r="AG128" s="166"/>
-      <c r="AH128" s="166"/>
-      <c r="AI128" s="166"/>
-      <c r="AJ128" s="167"/>
-      <c r="AK128" s="183"/>
-      <c r="AL128" s="184"/>
+      <c r="AG128" s="154"/>
+      <c r="AH128" s="154"/>
+      <c r="AI128" s="154"/>
+      <c r="AJ128" s="155"/>
+      <c r="AK128" s="222"/>
+      <c r="AL128" s="223"/>
     </row>
     <row r="129" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B129" s="13" t="s">
@@ -25185,8 +25191,8 @@
       <c r="AA129" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="AB129" s="158"/>
-      <c r="AC129" s="159"/>
+      <c r="AB129" s="217"/>
+      <c r="AC129" s="142"/>
       <c r="AD129" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25197,8 +25203,8 @@
       <c r="AH129" s="24"/>
       <c r="AI129" s="24"/>
       <c r="AJ129" s="25"/>
-      <c r="AK129" s="183"/>
-      <c r="AL129" s="184"/>
+      <c r="AK129" s="222"/>
+      <c r="AL129" s="223"/>
     </row>
     <row r="130" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B130" s="13" t="s">
@@ -25281,23 +25287,23 @@
       <c r="AA130" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="AB130" s="158"/>
-      <c r="AC130" s="159"/>
+      <c r="AB130" s="217"/>
+      <c r="AC130" s="142"/>
       <c r="AD130" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE130" s="17"/>
-      <c r="AF130" s="168">
+      <c r="AF130" s="153">
         <f>SUM(AD126:AD137)</f>
         <v>0</v>
       </c>
-      <c r="AG130" s="166"/>
-      <c r="AH130" s="166"/>
-      <c r="AI130" s="166"/>
-      <c r="AJ130" s="167"/>
-      <c r="AK130" s="183"/>
-      <c r="AL130" s="184"/>
+      <c r="AG130" s="154"/>
+      <c r="AH130" s="154"/>
+      <c r="AI130" s="154"/>
+      <c r="AJ130" s="155"/>
+      <c r="AK130" s="222"/>
+      <c r="AL130" s="223"/>
     </row>
     <row r="131" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B131" s="13" t="s">
@@ -25380,8 +25386,8 @@
       <c r="AA131" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="AB131" s="158"/>
-      <c r="AC131" s="159"/>
+      <c r="AB131" s="217"/>
+      <c r="AC131" s="142"/>
       <c r="AD131" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25392,8 +25398,8 @@
       <c r="AH131" s="24"/>
       <c r="AI131" s="24"/>
       <c r="AJ131" s="25"/>
-      <c r="AK131" s="183"/>
-      <c r="AL131" s="184"/>
+      <c r="AK131" s="222"/>
+      <c r="AL131" s="223"/>
     </row>
     <row r="132" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B132" s="13" t="s">
@@ -25476,8 +25482,8 @@
       <c r="AA132" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AB132" s="158"/>
-      <c r="AC132" s="159"/>
+      <c r="AB132" s="217"/>
+      <c r="AC132" s="142"/>
       <c r="AD132" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25488,8 +25494,8 @@
       <c r="AH132" s="27"/>
       <c r="AI132" s="27"/>
       <c r="AJ132" s="28"/>
-      <c r="AK132" s="183"/>
-      <c r="AL132" s="184"/>
+      <c r="AK132" s="222"/>
+      <c r="AL132" s="223"/>
     </row>
     <row r="133" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B133" s="13" t="s">
@@ -25572,20 +25578,20 @@
       <c r="AA133" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="AB133" s="158"/>
-      <c r="AC133" s="159"/>
+      <c r="AB133" s="217"/>
+      <c r="AC133" s="142"/>
       <c r="AD133" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE133" s="17"/>
-      <c r="AF133" s="246"/>
+      <c r="AF133" s="27"/>
       <c r="AG133" s="27"/>
       <c r="AH133" s="27"/>
       <c r="AI133" s="27"/>
-      <c r="AJ133" s="246"/>
-      <c r="AK133" s="183"/>
-      <c r="AL133" s="184"/>
+      <c r="AJ133" s="27"/>
+      <c r="AK133" s="222"/>
+      <c r="AL133" s="223"/>
     </row>
     <row r="134" spans="1:40" s="12" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B134" s="13" t="s">
@@ -25668,8 +25674,8 @@
       <c r="AA134" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AB134" s="158"/>
-      <c r="AC134" s="159"/>
+      <c r="AB134" s="217"/>
+      <c r="AC134" s="142"/>
       <c r="AD134" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25680,8 +25686,8 @@
       <c r="AH134"/>
       <c r="AI134"/>
       <c r="AJ134"/>
-      <c r="AK134" s="183"/>
-      <c r="AL134" s="184"/>
+      <c r="AK134" s="222"/>
+      <c r="AL134" s="223"/>
     </row>
     <row r="135" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B135" s="13" t="s">
@@ -25764,8 +25770,8 @@
       <c r="AA135" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="AB135" s="158"/>
-      <c r="AC135" s="159"/>
+      <c r="AB135" s="217"/>
+      <c r="AC135" s="142"/>
       <c r="AD135" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25776,8 +25782,8 @@
       <c r="AH135" s="27"/>
       <c r="AI135" s="27"/>
       <c r="AJ135" s="28"/>
-      <c r="AK135" s="183"/>
-      <c r="AL135" s="184"/>
+      <c r="AK135" s="222"/>
+      <c r="AL135" s="223"/>
     </row>
     <row r="136" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B136" s="13" t="s">
@@ -25860,8 +25866,8 @@
       <c r="AA136" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="AB136" s="158"/>
-      <c r="AC136" s="159"/>
+      <c r="AB136" s="217"/>
+      <c r="AC136" s="142"/>
       <c r="AD136" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25872,8 +25878,8 @@
       <c r="AH136" s="27"/>
       <c r="AI136" s="27"/>
       <c r="AJ136" s="28"/>
-      <c r="AK136" s="183"/>
-      <c r="AL136" s="184"/>
+      <c r="AK136" s="222"/>
+      <c r="AL136" s="223"/>
     </row>
     <row r="137" spans="1:40" s="12" customFormat="1" ht="147" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B137" s="13" t="s">
@@ -25956,8 +25962,8 @@
       <c r="AA137" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="AB137" s="158"/>
-      <c r="AC137" s="159"/>
+      <c r="AB137" s="217"/>
+      <c r="AC137" s="142"/>
       <c r="AD137" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25968,8 +25974,8 @@
       <c r="AH137" s="84"/>
       <c r="AI137" s="84"/>
       <c r="AJ137" s="85"/>
-      <c r="AK137" s="183"/>
-      <c r="AL137" s="184"/>
+      <c r="AK137" s="222"/>
+      <c r="AL137" s="223"/>
     </row>
     <row r="138" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B138" s="13"/>
@@ -26063,22 +26069,22 @@
       <c r="Y138" s="14"/>
       <c r="Z138" s="14"/>
       <c r="AA138" s="13"/>
-      <c r="AB138" s="160"/>
-      <c r="AC138" s="161"/>
+      <c r="AB138" s="218"/>
+      <c r="AC138" s="143"/>
       <c r="AD138" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE138" s="17"/>
-      <c r="AF138" s="177" t="s">
+      <c r="AF138" s="178" t="s">
         <v>153</v>
       </c>
-      <c r="AG138" s="178"/>
-      <c r="AH138" s="178"/>
-      <c r="AI138" s="178"/>
-      <c r="AJ138" s="178"/>
-      <c r="AK138" s="183"/>
-      <c r="AL138" s="184"/>
+      <c r="AG138" s="179"/>
+      <c r="AH138" s="179"/>
+      <c r="AI138" s="179"/>
+      <c r="AJ138" s="179"/>
+      <c r="AK138" s="222"/>
+      <c r="AL138" s="223"/>
     </row>
     <row r="139" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B139" s="13" t="s">
@@ -26161,69 +26167,69 @@
       <c r="AA139" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="AB139" s="151"/>
-      <c r="AC139" s="152"/>
+      <c r="AB139" s="172"/>
+      <c r="AC139" s="173"/>
       <c r="AD139" s="16">
         <f>X139</f>
         <v>0</v>
       </c>
       <c r="AE139" s="17"/>
-      <c r="AF139" s="179">
+      <c r="AF139" s="229">
         <f>AD139</f>
         <v>0</v>
       </c>
-      <c r="AG139" s="178"/>
-      <c r="AH139" s="178"/>
-      <c r="AI139" s="178"/>
-      <c r="AJ139" s="178"/>
-      <c r="AK139" s="183"/>
-      <c r="AL139" s="184"/>
+      <c r="AG139" s="179"/>
+      <c r="AH139" s="179"/>
+      <c r="AI139" s="179"/>
+      <c r="AJ139" s="179"/>
+      <c r="AK139" s="222"/>
+      <c r="AL139" s="223"/>
     </row>
     <row r="140" spans="1:40" s="88" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A140"/>
       <c r="B140" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="C140" s="137" t="s">
+      <c r="C140" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D140" s="138"/>
-      <c r="E140" s="137" t="s">
+      <c r="D140" s="129"/>
+      <c r="E140" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F140" s="138"/>
-      <c r="G140" s="137" t="s">
+      <c r="F140" s="129"/>
+      <c r="G140" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H140" s="138"/>
-      <c r="I140" s="137" t="s">
+      <c r="H140" s="129"/>
+      <c r="I140" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J140" s="138"/>
-      <c r="K140" s="137" t="s">
+      <c r="J140" s="129"/>
+      <c r="K140" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L140" s="138"/>
-      <c r="M140" s="137" t="s">
+      <c r="L140" s="129"/>
+      <c r="M140" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N140" s="138"/>
-      <c r="O140" s="137" t="s">
+      <c r="N140" s="129"/>
+      <c r="O140" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P140" s="138"/>
-      <c r="Q140" s="137" t="s">
+      <c r="P140" s="129"/>
+      <c r="Q140" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R140" s="138"/>
-      <c r="S140" s="137" t="s">
+      <c r="R140" s="129"/>
+      <c r="S140" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T140" s="138"/>
-      <c r="U140" s="137" t="s">
+      <c r="T140" s="129"/>
+      <c r="U140" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V140" s="138"/>
+      <c r="V140" s="129"/>
       <c r="W140" s="9" t="s">
         <v>12</v>
       </c>
@@ -26237,8 +26243,8 @@
       <c r="AA140" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="AB140" s="154"/>
-      <c r="AC140" s="155"/>
+      <c r="AB140" s="227"/>
+      <c r="AC140" s="228"/>
       <c r="AD140" s="6" t="s">
         <v>16</v>
       </c>
@@ -26335,11 +26341,11 @@
       <c r="AA141" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="AB141" s="173">
+      <c r="AB141" s="174">
         <f>SUM(Y141:Y142)</f>
         <v>0</v>
       </c>
-      <c r="AC141" s="174"/>
+      <c r="AC141" s="175"/>
       <c r="AD141" s="16">
         <f>X141</f>
         <v>0</v>
@@ -26435,8 +26441,8 @@
       <c r="AA142" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AB142" s="175"/>
-      <c r="AC142" s="176"/>
+      <c r="AB142" s="176"/>
+      <c r="AC142" s="177"/>
       <c r="AD142" s="16">
         <f>X142</f>
         <v>0</v>
@@ -26457,46 +26463,46 @@
       <c r="B143" s="86" t="s">
         <v>212</v>
       </c>
-      <c r="C143" s="137" t="s">
+      <c r="C143" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D143" s="138"/>
-      <c r="E143" s="137" t="s">
+      <c r="D143" s="129"/>
+      <c r="E143" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F143" s="138"/>
-      <c r="G143" s="137" t="s">
+      <c r="F143" s="129"/>
+      <c r="G143" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H143" s="138"/>
-      <c r="I143" s="137" t="s">
+      <c r="H143" s="129"/>
+      <c r="I143" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J143" s="138"/>
-      <c r="K143" s="137" t="s">
+      <c r="J143" s="129"/>
+      <c r="K143" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L143" s="138"/>
-      <c r="M143" s="137" t="s">
+      <c r="L143" s="129"/>
+      <c r="M143" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N143" s="138"/>
-      <c r="O143" s="137" t="s">
+      <c r="N143" s="129"/>
+      <c r="O143" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P143" s="138"/>
-      <c r="Q143" s="137" t="s">
+      <c r="P143" s="129"/>
+      <c r="Q143" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R143" s="138"/>
-      <c r="S143" s="137" t="s">
+      <c r="R143" s="129"/>
+      <c r="S143" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T143" s="138"/>
-      <c r="U143" s="137" t="s">
+      <c r="T143" s="129"/>
+      <c r="U143" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V143" s="138"/>
+      <c r="V143" s="129"/>
       <c r="W143" s="9" t="s">
         <v>12</v>
       </c>
@@ -26510,8 +26516,8 @@
       <c r="AA143" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="AB143" s="154"/>
-      <c r="AC143" s="155"/>
+      <c r="AB143" s="227"/>
+      <c r="AC143" s="228"/>
       <c r="AD143" s="6" t="s">
         <v>16</v>
       </c>
@@ -26608,11 +26614,11 @@
       <c r="AA144" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="AB144" s="156">
+      <c r="AB144" s="216">
         <f>SUM(Y144:Y154)</f>
         <v>0</v>
       </c>
-      <c r="AC144" s="157"/>
+      <c r="AC144" s="141"/>
       <c r="AD144" s="16">
         <f>X144</f>
         <v>0</v>
@@ -26708,8 +26714,8 @@
       <c r="AA145" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="AB145" s="158"/>
-      <c r="AC145" s="159"/>
+      <c r="AB145" s="217"/>
+      <c r="AC145" s="142"/>
       <c r="AD145" s="16">
         <f t="shared" ref="AD145:AD154" si="41">X145</f>
         <v>0</v>
@@ -26805,8 +26811,8 @@
       <c r="AA146" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="AB146" s="158"/>
-      <c r="AC146" s="159"/>
+      <c r="AB146" s="217"/>
+      <c r="AC146" s="142"/>
       <c r="AD146" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26902,8 +26908,8 @@
       <c r="AA147" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="AB147" s="158"/>
-      <c r="AC147" s="159"/>
+      <c r="AB147" s="217"/>
+      <c r="AC147" s="142"/>
       <c r="AD147" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -26999,8 +27005,8 @@
       <c r="AA148" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="AB148" s="158"/>
-      <c r="AC148" s="159"/>
+      <c r="AB148" s="217"/>
+      <c r="AC148" s="142"/>
       <c r="AD148" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27096,8 +27102,8 @@
       <c r="AA149" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="AB149" s="158"/>
-      <c r="AC149" s="159"/>
+      <c r="AB149" s="217"/>
+      <c r="AC149" s="142"/>
       <c r="AD149" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27193,8 +27199,8 @@
       <c r="AA150" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="AB150" s="158"/>
-      <c r="AC150" s="159"/>
+      <c r="AB150" s="217"/>
+      <c r="AC150" s="142"/>
       <c r="AD150" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27290,8 +27296,8 @@
       <c r="AA151" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="AB151" s="158"/>
-      <c r="AC151" s="159"/>
+      <c r="AB151" s="217"/>
+      <c r="AC151" s="142"/>
       <c r="AD151" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27387,8 +27393,8 @@
       <c r="AA152" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="AB152" s="158"/>
-      <c r="AC152" s="159"/>
+      <c r="AB152" s="217"/>
+      <c r="AC152" s="142"/>
       <c r="AD152" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27484,8 +27490,8 @@
       <c r="AA153" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="AB153" s="158"/>
-      <c r="AC153" s="159"/>
+      <c r="AB153" s="217"/>
+      <c r="AC153" s="142"/>
       <c r="AD153" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27581,8 +27587,8 @@
       <c r="AA154" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="AB154" s="160"/>
-      <c r="AC154" s="161"/>
+      <c r="AB154" s="218"/>
+      <c r="AC154" s="143"/>
       <c r="AD154" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27688,8 +27694,8 @@
       <c r="Y155" s="14"/>
       <c r="Z155" s="14"/>
       <c r="AA155" s="13"/>
-      <c r="AB155" s="151"/>
-      <c r="AC155" s="152"/>
+      <c r="AB155" s="172"/>
+      <c r="AC155" s="173"/>
       <c r="AD155" s="16">
         <v>0</v>
       </c>
@@ -27703,101 +27709,101 @@
       <c r="AL155" s="92"/>
     </row>
     <row r="156" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="1.85">
-      <c r="B156" s="171" t="s">
-        <v>0</v>
-      </c>
-      <c r="C156" s="172"/>
-      <c r="D156" s="172"/>
-      <c r="E156" s="172"/>
-      <c r="F156" s="172"/>
-      <c r="G156" s="172"/>
-      <c r="H156" s="172"/>
-      <c r="I156" s="172"/>
-      <c r="J156" s="172"/>
-      <c r="K156" s="172"/>
-      <c r="L156" s="172"/>
-      <c r="M156" s="172"/>
-      <c r="N156" s="172"/>
-      <c r="O156" s="172"/>
-      <c r="P156" s="172"/>
-      <c r="Q156" s="172"/>
-      <c r="R156" s="172"/>
-      <c r="S156" s="172"/>
-      <c r="T156" s="172"/>
-      <c r="U156" s="172"/>
-      <c r="V156" s="172"/>
-      <c r="W156" s="172"/>
-      <c r="X156" s="172"/>
-      <c r="Y156" s="172"/>
-      <c r="Z156" s="172"/>
-      <c r="AA156" s="172"/>
-      <c r="AB156" s="172"/>
-      <c r="AC156" s="172"/>
-      <c r="AD156" s="172"/>
+      <c r="B156" s="132" t="s">
+        <v>0</v>
+      </c>
+      <c r="C156" s="133"/>
+      <c r="D156" s="133"/>
+      <c r="E156" s="133"/>
+      <c r="F156" s="133"/>
+      <c r="G156" s="133"/>
+      <c r="H156" s="133"/>
+      <c r="I156" s="133"/>
+      <c r="J156" s="133"/>
+      <c r="K156" s="133"/>
+      <c r="L156" s="133"/>
+      <c r="M156" s="133"/>
+      <c r="N156" s="133"/>
+      <c r="O156" s="133"/>
+      <c r="P156" s="133"/>
+      <c r="Q156" s="133"/>
+      <c r="R156" s="133"/>
+      <c r="S156" s="133"/>
+      <c r="T156" s="133"/>
+      <c r="U156" s="133"/>
+      <c r="V156" s="133"/>
+      <c r="W156" s="133"/>
+      <c r="X156" s="133"/>
+      <c r="Y156" s="133"/>
+      <c r="Z156" s="133"/>
+      <c r="AA156" s="133"/>
+      <c r="AB156" s="133"/>
+      <c r="AC156" s="133"/>
+      <c r="AD156" s="133"/>
       <c r="AE156" s="1"/>
       <c r="AK156" s="92"/>
       <c r="AL156" s="92"/>
     </row>
     <row r="157" spans="1:40" s="88" customFormat="1" ht="138.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A157"/>
-      <c r="B157" s="169" t="s">
+      <c r="B157" s="130" t="s">
         <v>170</v>
       </c>
-      <c r="C157" s="137" t="s">
+      <c r="C157" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D157" s="138"/>
-      <c r="E157" s="137" t="s">
+      <c r="D157" s="129"/>
+      <c r="E157" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F157" s="138"/>
-      <c r="G157" s="137" t="s">
+      <c r="F157" s="129"/>
+      <c r="G157" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H157" s="138"/>
-      <c r="I157" s="137" t="s">
+      <c r="H157" s="129"/>
+      <c r="I157" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J157" s="138"/>
-      <c r="K157" s="137" t="s">
+      <c r="J157" s="129"/>
+      <c r="K157" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L157" s="138"/>
-      <c r="M157" s="137" t="s">
+      <c r="L157" s="129"/>
+      <c r="M157" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N157" s="138"/>
-      <c r="O157" s="137" t="s">
+      <c r="N157" s="129"/>
+      <c r="O157" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P157" s="138"/>
-      <c r="Q157" s="137" t="s">
+      <c r="P157" s="129"/>
+      <c r="Q157" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R157" s="138"/>
-      <c r="S157" s="137" t="s">
+      <c r="R157" s="129"/>
+      <c r="S157" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T157" s="138"/>
-      <c r="U157" s="137" t="s">
+      <c r="T157" s="129"/>
+      <c r="U157" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V157" s="138"/>
-      <c r="W157" s="169" t="s">
+      <c r="V157" s="129"/>
+      <c r="W157" s="130" t="s">
         <v>12</v>
       </c>
       <c r="X157" s="110"/>
-      <c r="Y157" s="169" t="s">
+      <c r="Y157" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="Z157" s="169" t="s">
+      <c r="Z157" s="130" t="s">
         <v>14</v>
       </c>
-      <c r="AA157" s="169" t="s">
+      <c r="AA157" s="130" t="s">
         <v>170</v>
       </c>
-      <c r="AB157" s="154"/>
-      <c r="AC157" s="155"/>
+      <c r="AB157" s="227"/>
+      <c r="AC157" s="228"/>
       <c r="AD157" s="6" t="s">
         <v>16</v>
       </c>
@@ -27813,7 +27819,7 @@
       <c r="AN157" s="12"/>
     </row>
     <row r="158" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B158" s="170"/>
+      <c r="B158" s="131"/>
       <c r="C158" s="9" t="s">
         <v>17</v>
       </c>
@@ -27874,11 +27880,11 @@
       <c r="V158" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="W158" s="170"/>
+      <c r="W158" s="131"/>
       <c r="X158" s="111"/>
-      <c r="Y158" s="170"/>
-      <c r="Z158" s="170"/>
-      <c r="AA158" s="170"/>
+      <c r="Y158" s="131"/>
+      <c r="Z158" s="131"/>
+      <c r="AA158" s="131"/>
       <c r="AB158" s="10"/>
       <c r="AC158" s="11"/>
       <c r="AD158" s="6">
@@ -27974,11 +27980,11 @@
       <c r="AA159" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="AB159" s="156">
+      <c r="AB159" s="216">
         <f>SUM(Y159:Y164)</f>
         <v>0</v>
       </c>
-      <c r="AC159" s="157"/>
+      <c r="AC159" s="141"/>
       <c r="AD159" s="16">
         <f>X159</f>
         <v>0</v>
@@ -28073,8 +28079,8 @@
       <c r="AA160" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="AB160" s="158"/>
-      <c r="AC160" s="159"/>
+      <c r="AB160" s="217"/>
+      <c r="AC160" s="142"/>
       <c r="AD160" s="16">
         <f t="shared" ref="AD160:AD164" si="45">X160</f>
         <v>0</v>
@@ -28169,8 +28175,8 @@
       <c r="AA161" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="AB161" s="158"/>
-      <c r="AC161" s="159"/>
+      <c r="AB161" s="217"/>
+      <c r="AC161" s="142"/>
       <c r="AD161" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28265,8 +28271,8 @@
       <c r="AA162" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="AB162" s="158"/>
-      <c r="AC162" s="159"/>
+      <c r="AB162" s="217"/>
+      <c r="AC162" s="142"/>
       <c r="AD162" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28361,8 +28367,8 @@
       <c r="AA163" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="AB163" s="158"/>
-      <c r="AC163" s="159"/>
+      <c r="AB163" s="217"/>
+      <c r="AC163" s="142"/>
       <c r="AD163" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28457,8 +28463,8 @@
       <c r="AA164" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="AB164" s="160"/>
-      <c r="AC164" s="161"/>
+      <c r="AB164" s="218"/>
+      <c r="AC164" s="143"/>
       <c r="AD164" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28478,59 +28484,59 @@
       <c r="B165" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="C165" s="137" t="s">
+      <c r="C165" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D165" s="138"/>
-      <c r="E165" s="137" t="s">
+      <c r="D165" s="129"/>
+      <c r="E165" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F165" s="138"/>
-      <c r="G165" s="137" t="s">
+      <c r="F165" s="129"/>
+      <c r="G165" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H165" s="138"/>
-      <c r="I165" s="137" t="s">
+      <c r="H165" s="129"/>
+      <c r="I165" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J165" s="138"/>
-      <c r="K165" s="137" t="s">
+      <c r="J165" s="129"/>
+      <c r="K165" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L165" s="138"/>
-      <c r="M165" s="137" t="s">
+      <c r="L165" s="129"/>
+      <c r="M165" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N165" s="138"/>
-      <c r="O165" s="137" t="s">
+      <c r="N165" s="129"/>
+      <c r="O165" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P165" s="138"/>
-      <c r="Q165" s="137" t="s">
+      <c r="P165" s="129"/>
+      <c r="Q165" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R165" s="138"/>
-      <c r="S165" s="137" t="s">
+      <c r="R165" s="129"/>
+      <c r="S165" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T165" s="138"/>
-      <c r="U165" s="137" t="s">
+      <c r="T165" s="129"/>
+      <c r="U165" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V165" s="138"/>
+      <c r="V165" s="129"/>
       <c r="W165" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X165" s="117"/>
-      <c r="Y165" s="149" t="s">
+      <c r="Y165" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="Z165" s="150"/>
+      <c r="Z165" s="233"/>
       <c r="AA165" s="79" t="s">
         <v>178</v>
       </c>
-      <c r="AB165" s="141"/>
-      <c r="AC165" s="142"/>
+      <c r="AB165" s="134"/>
+      <c r="AC165" s="135"/>
       <c r="AD165" s="6" t="s">
         <v>16</v>
       </c>
@@ -28592,19 +28598,19 @@
       <c r="X166" s="120">
         <v>0</v>
       </c>
-      <c r="Y166" s="143">
+      <c r="Y166" s="230">
         <f t="shared" ref="Y166:Y189" si="46">SUM(C166:W166)</f>
         <v>0</v>
       </c>
-      <c r="Z166" s="144"/>
+      <c r="Z166" s="231"/>
       <c r="AA166" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="AB166" s="156">
+      <c r="AB166" s="216">
         <f>SUM(Y166:Y173)</f>
         <v>0</v>
       </c>
-      <c r="AC166" s="157"/>
+      <c r="AC166" s="141"/>
       <c r="AD166" s="16">
         <f>X166</f>
         <v>0</v>
@@ -28670,26 +28676,26 @@
       <c r="X167" s="120">
         <v>0</v>
       </c>
-      <c r="Y167" s="143">
+      <c r="Y167" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z167" s="144"/>
+      <c r="Z167" s="231"/>
       <c r="AA167" s="13" t="s">
         <v>181</v>
       </c>
-      <c r="AB167" s="158"/>
-      <c r="AC167" s="159"/>
+      <c r="AB167" s="217"/>
+      <c r="AC167" s="142"/>
       <c r="AD167" s="16">
         <f t="shared" ref="AD167:AD172" si="47">X167</f>
         <v>0</v>
       </c>
       <c r="AE167" s="94"/>
       <c r="AF167" s="165"/>
-      <c r="AG167" s="166"/>
-      <c r="AH167" s="166"/>
-      <c r="AI167" s="166"/>
-      <c r="AJ167" s="167"/>
+      <c r="AG167" s="154"/>
+      <c r="AH167" s="154"/>
+      <c r="AI167" s="154"/>
+      <c r="AJ167" s="155"/>
       <c r="AK167" s="8"/>
       <c r="AL167" s="8"/>
     </row>
@@ -28743,26 +28749,26 @@
       <c r="X168" s="120">
         <v>0</v>
       </c>
-      <c r="Y168" s="143">
+      <c r="Y168" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z168" s="144"/>
+      <c r="Z168" s="231"/>
       <c r="AA168" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="AB168" s="158"/>
-      <c r="AC168" s="159"/>
+      <c r="AB168" s="217"/>
+      <c r="AC168" s="142"/>
       <c r="AD168" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE168" s="94"/>
       <c r="AF168" s="165"/>
-      <c r="AG168" s="166"/>
-      <c r="AH168" s="166"/>
-      <c r="AI168" s="166"/>
-      <c r="AJ168" s="167"/>
+      <c r="AG168" s="154"/>
+      <c r="AH168" s="154"/>
+      <c r="AI168" s="154"/>
+      <c r="AJ168" s="155"/>
       <c r="AK168" s="8"/>
       <c r="AL168" s="8"/>
     </row>
@@ -28816,26 +28822,26 @@
       <c r="X169" s="120">
         <v>0</v>
       </c>
-      <c r="Y169" s="143">
+      <c r="Y169" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z169" s="144"/>
+      <c r="Z169" s="231"/>
       <c r="AA169" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="AB169" s="158"/>
-      <c r="AC169" s="159"/>
+      <c r="AB169" s="217"/>
+      <c r="AC169" s="142"/>
       <c r="AD169" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE169" s="94"/>
       <c r="AF169" s="165"/>
-      <c r="AG169" s="166"/>
-      <c r="AH169" s="166"/>
-      <c r="AI169" s="166"/>
-      <c r="AJ169" s="167"/>
+      <c r="AG169" s="154"/>
+      <c r="AH169" s="154"/>
+      <c r="AI169" s="154"/>
+      <c r="AJ169" s="155"/>
       <c r="AK169" s="8"/>
       <c r="AL169" s="8"/>
     </row>
@@ -28889,29 +28895,29 @@
       <c r="X170" s="120">
         <v>0</v>
       </c>
-      <c r="Y170" s="143">
+      <c r="Y170" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z170" s="144"/>
+      <c r="Z170" s="231"/>
       <c r="AA170" s="13" t="s">
         <v>184</v>
       </c>
-      <c r="AB170" s="158"/>
-      <c r="AC170" s="159"/>
+      <c r="AB170" s="217"/>
+      <c r="AC170" s="142"/>
       <c r="AD170" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE170" s="94"/>
-      <c r="AF170" s="168">
+      <c r="AF170" s="153">
         <f>SUM(AD166:AD173)</f>
         <v>0</v>
       </c>
-      <c r="AG170" s="166"/>
-      <c r="AH170" s="166"/>
-      <c r="AI170" s="166"/>
-      <c r="AJ170" s="167"/>
+      <c r="AG170" s="154"/>
+      <c r="AH170" s="154"/>
+      <c r="AI170" s="154"/>
+      <c r="AJ170" s="155"/>
       <c r="AK170" s="8"/>
       <c r="AL170" s="8"/>
     </row>
@@ -28965,16 +28971,16 @@
       <c r="X171" s="120">
         <v>0</v>
       </c>
-      <c r="Y171" s="143">
+      <c r="Y171" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z171" s="144"/>
+      <c r="Z171" s="231"/>
       <c r="AA171" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="AB171" s="158"/>
-      <c r="AC171" s="159"/>
+      <c r="AB171" s="217"/>
+      <c r="AC171" s="142"/>
       <c r="AD171" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -29038,16 +29044,16 @@
       <c r="X172" s="120">
         <v>0</v>
       </c>
-      <c r="Y172" s="143">
+      <c r="Y172" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z172" s="144"/>
+      <c r="Z172" s="231"/>
       <c r="AA172" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="AB172" s="158"/>
-      <c r="AC172" s="159"/>
+      <c r="AB172" s="217"/>
+      <c r="AC172" s="142"/>
       <c r="AD172" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -29111,16 +29117,16 @@
       <c r="X173" s="120">
         <v>0</v>
       </c>
-      <c r="Y173" s="143">
+      <c r="Y173" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z173" s="144"/>
+      <c r="Z173" s="231"/>
       <c r="AA173" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="AB173" s="160"/>
-      <c r="AC173" s="161"/>
+      <c r="AB173" s="218"/>
+      <c r="AC173" s="143"/>
       <c r="AD173" s="16">
         <f>X173</f>
         <v>0</v>
@@ -29193,16 +29199,16 @@
         <v>0</v>
       </c>
       <c r="X174" s="121"/>
-      <c r="Y174" s="149">
+      <c r="Y174" s="232">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z174" s="150"/>
+      <c r="Z174" s="233"/>
       <c r="AA174" s="86" t="s">
         <v>189</v>
       </c>
-      <c r="AB174" s="154"/>
-      <c r="AC174" s="155"/>
+      <c r="AB174" s="227"/>
+      <c r="AC174" s="228"/>
       <c r="AD174" s="6" t="s">
         <v>16</v>
       </c>
@@ -29258,16 +29264,16 @@
       <c r="X175" s="120">
         <v>0</v>
       </c>
-      <c r="Y175" s="143">
+      <c r="Y175" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z175" s="144"/>
+      <c r="Z175" s="231"/>
       <c r="AA175" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="AB175" s="151"/>
-      <c r="AC175" s="152"/>
+      <c r="AB175" s="172"/>
+      <c r="AC175" s="173"/>
       <c r="AD175" s="16">
         <f>X175</f>
         <v>0</v>
@@ -29331,16 +29337,16 @@
       <c r="X176" s="120">
         <v>0</v>
       </c>
-      <c r="Y176" s="143">
+      <c r="Y176" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z176" s="144"/>
+      <c r="Z176" s="231"/>
       <c r="AA176" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="AB176" s="151"/>
-      <c r="AC176" s="152"/>
+      <c r="AB176" s="172"/>
+      <c r="AC176" s="173"/>
       <c r="AD176" s="16">
         <f>X176</f>
         <v>0</v>
@@ -29404,16 +29410,16 @@
       <c r="X177" s="120">
         <v>0</v>
       </c>
-      <c r="Y177" s="143">
+      <c r="Y177" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z177" s="144"/>
+      <c r="Z177" s="231"/>
       <c r="AA177" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="AB177" s="151"/>
-      <c r="AC177" s="152"/>
+      <c r="AB177" s="172"/>
+      <c r="AC177" s="173"/>
       <c r="AD177" s="16">
         <f>X177</f>
         <v>0</v>
@@ -29477,16 +29483,16 @@
       <c r="X178" s="120">
         <v>0</v>
       </c>
-      <c r="Y178" s="143">
+      <c r="Y178" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z178" s="144"/>
+      <c r="Z178" s="231"/>
       <c r="AA178" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="AB178" s="151"/>
-      <c r="AC178" s="152"/>
+      <c r="AB178" s="172"/>
+      <c r="AC178" s="173"/>
       <c r="AD178" s="16">
         <f t="shared" ref="AD178:AD189" si="49">X178</f>
         <v>0</v>
@@ -29550,16 +29556,16 @@
       <c r="X179" s="120">
         <v>0</v>
       </c>
-      <c r="Y179" s="143">
+      <c r="Y179" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z179" s="144"/>
+      <c r="Z179" s="231"/>
       <c r="AA179" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="AB179" s="151"/>
-      <c r="AC179" s="152"/>
+      <c r="AB179" s="172"/>
+      <c r="AC179" s="173"/>
       <c r="AD179" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29623,25 +29629,25 @@
       <c r="X180" s="120">
         <v>0</v>
       </c>
-      <c r="Y180" s="143">
+      <c r="Y180" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z180" s="144"/>
+      <c r="Z180" s="231"/>
       <c r="AA180" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="AB180" s="151"/>
-      <c r="AC180" s="152"/>
+      <c r="AB180" s="172"/>
+      <c r="AC180" s="173"/>
       <c r="AD180" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE180" s="98"/>
       <c r="AF180" s="99"/>
-      <c r="AG180" s="153"/>
-      <c r="AH180" s="153"/>
-      <c r="AI180" s="153"/>
+      <c r="AG180" s="234"/>
+      <c r="AH180" s="234"/>
+      <c r="AI180" s="234"/>
       <c r="AJ180" s="99"/>
       <c r="AK180" s="8"/>
       <c r="AL180" s="8"/>
@@ -29696,16 +29702,16 @@
       <c r="X181" s="120">
         <v>0</v>
       </c>
-      <c r="Y181" s="143">
+      <c r="Y181" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z181" s="144"/>
+      <c r="Z181" s="231"/>
       <c r="AA181" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="AB181" s="151"/>
-      <c r="AC181" s="152"/>
+      <c r="AB181" s="172"/>
+      <c r="AC181" s="173"/>
       <c r="AD181" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29769,16 +29775,16 @@
       <c r="X182" s="120">
         <v>0</v>
       </c>
-      <c r="Y182" s="143">
+      <c r="Y182" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z182" s="144"/>
+      <c r="Z182" s="231"/>
       <c r="AA182" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="AB182" s="151"/>
-      <c r="AC182" s="152"/>
+      <c r="AB182" s="172"/>
+      <c r="AC182" s="173"/>
       <c r="AD182" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29842,16 +29848,16 @@
       <c r="X183" s="120">
         <v>0</v>
       </c>
-      <c r="Y183" s="143">
+      <c r="Y183" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z183" s="144"/>
+      <c r="Z183" s="231"/>
       <c r="AA183" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="AB183" s="151"/>
-      <c r="AC183" s="152"/>
+      <c r="AB183" s="172"/>
+      <c r="AC183" s="173"/>
       <c r="AD183" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -29915,11 +29921,11 @@
       <c r="X184" s="120">
         <v>0</v>
       </c>
-      <c r="Y184" s="143">
+      <c r="Y184" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z184" s="144"/>
+      <c r="Z184" s="231"/>
       <c r="AA184" s="13" t="s">
         <v>210</v>
       </c>
@@ -29990,16 +29996,16 @@
       <c r="X185" s="120">
         <v>0</v>
       </c>
-      <c r="Y185" s="143">
+      <c r="Y185" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z185" s="144"/>
+      <c r="Z185" s="231"/>
       <c r="AA185" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="AB185" s="151"/>
-      <c r="AC185" s="152"/>
+      <c r="AB185" s="172"/>
+      <c r="AC185" s="173"/>
       <c r="AD185" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30063,16 +30069,16 @@
       <c r="X186" s="120">
         <v>0</v>
       </c>
-      <c r="Y186" s="143">
+      <c r="Y186" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z186" s="144"/>
+      <c r="Z186" s="231"/>
       <c r="AA186" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="AB186" s="151"/>
-      <c r="AC186" s="152"/>
+      <c r="AB186" s="172"/>
+      <c r="AC186" s="173"/>
       <c r="AD186" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30136,16 +30142,16 @@
       <c r="X187" s="120">
         <v>0</v>
       </c>
-      <c r="Y187" s="143">
+      <c r="Y187" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z187" s="144"/>
+      <c r="Z187" s="231"/>
       <c r="AA187" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="AB187" s="151"/>
-      <c r="AC187" s="152"/>
+      <c r="AB187" s="172"/>
+      <c r="AC187" s="173"/>
       <c r="AD187" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30209,16 +30215,16 @@
       <c r="X188" s="120">
         <v>0</v>
       </c>
-      <c r="Y188" s="143">
+      <c r="Y188" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z188" s="144"/>
+      <c r="Z188" s="231"/>
       <c r="AA188" s="13" t="s">
         <v>202</v>
       </c>
-      <c r="AB188" s="151"/>
-      <c r="AC188" s="152"/>
+      <c r="AB188" s="172"/>
+      <c r="AC188" s="173"/>
       <c r="AD188" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30282,16 +30288,16 @@
       <c r="X189" s="120">
         <v>0</v>
       </c>
-      <c r="Y189" s="143">
+      <c r="Y189" s="230">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z189" s="144"/>
+      <c r="Z189" s="231"/>
       <c r="AA189" s="13" t="s">
         <v>203</v>
       </c>
-      <c r="AB189" s="151"/>
-      <c r="AC189" s="152"/>
+      <c r="AB189" s="172"/>
+      <c r="AC189" s="173"/>
       <c r="AD189" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30309,59 +30315,59 @@
       <c r="B190" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="C190" s="137" t="s">
+      <c r="C190" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D190" s="138"/>
-      <c r="E190" s="137" t="s">
+      <c r="D190" s="129"/>
+      <c r="E190" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F190" s="138"/>
-      <c r="G190" s="137" t="s">
+      <c r="F190" s="129"/>
+      <c r="G190" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H190" s="138"/>
-      <c r="I190" s="137" t="s">
+      <c r="H190" s="129"/>
+      <c r="I190" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J190" s="138"/>
-      <c r="K190" s="137" t="s">
+      <c r="J190" s="129"/>
+      <c r="K190" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L190" s="138"/>
-      <c r="M190" s="137" t="s">
+      <c r="L190" s="129"/>
+      <c r="M190" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N190" s="138"/>
-      <c r="O190" s="137" t="s">
+      <c r="N190" s="129"/>
+      <c r="O190" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P190" s="138"/>
-      <c r="Q190" s="137" t="s">
+      <c r="P190" s="129"/>
+      <c r="Q190" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R190" s="138"/>
-      <c r="S190" s="137" t="s">
+      <c r="R190" s="129"/>
+      <c r="S190" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T190" s="138"/>
-      <c r="U190" s="137" t="s">
+      <c r="T190" s="129"/>
+      <c r="U190" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V190" s="138"/>
+      <c r="V190" s="129"/>
       <c r="W190" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X190" s="117"/>
-      <c r="Y190" s="149" t="s">
+      <c r="Y190" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="Z190" s="150"/>
+      <c r="Z190" s="233"/>
       <c r="AA190" s="79" t="s">
         <v>106</v>
       </c>
-      <c r="AB190" s="141"/>
-      <c r="AC190" s="142"/>
+      <c r="AB190" s="134"/>
+      <c r="AC190" s="135"/>
       <c r="AD190" s="6" t="s">
         <v>16</v>
       </c>
@@ -30373,60 +30379,60 @@
       <c r="B191" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="C191" s="143">
-        <v>0</v>
-      </c>
-      <c r="D191" s="144"/>
-      <c r="E191" s="143">
-        <v>0</v>
-      </c>
-      <c r="F191" s="144"/>
-      <c r="G191" s="143">
-        <v>0</v>
-      </c>
-      <c r="H191" s="144"/>
-      <c r="I191" s="143">
-        <v>0</v>
-      </c>
-      <c r="J191" s="144"/>
-      <c r="K191" s="143">
-        <v>0</v>
-      </c>
-      <c r="L191" s="144"/>
-      <c r="M191" s="143">
-        <v>0</v>
-      </c>
-      <c r="N191" s="144"/>
-      <c r="O191" s="143">
-        <v>0</v>
-      </c>
-      <c r="P191" s="144"/>
-      <c r="Q191" s="143">
-        <v>0</v>
-      </c>
-      <c r="R191" s="144"/>
-      <c r="S191" s="143">
-        <v>0</v>
-      </c>
-      <c r="T191" s="144"/>
-      <c r="U191" s="143">
-        <v>0</v>
-      </c>
-      <c r="V191" s="144"/>
+      <c r="C191" s="230">
+        <v>0</v>
+      </c>
+      <c r="D191" s="231"/>
+      <c r="E191" s="230">
+        <v>0</v>
+      </c>
+      <c r="F191" s="231"/>
+      <c r="G191" s="230">
+        <v>0</v>
+      </c>
+      <c r="H191" s="231"/>
+      <c r="I191" s="230">
+        <v>0</v>
+      </c>
+      <c r="J191" s="231"/>
+      <c r="K191" s="230">
+        <v>0</v>
+      </c>
+      <c r="L191" s="231"/>
+      <c r="M191" s="230">
+        <v>0</v>
+      </c>
+      <c r="N191" s="231"/>
+      <c r="O191" s="230">
+        <v>0</v>
+      </c>
+      <c r="P191" s="231"/>
+      <c r="Q191" s="230">
+        <v>0</v>
+      </c>
+      <c r="R191" s="231"/>
+      <c r="S191" s="230">
+        <v>0</v>
+      </c>
+      <c r="T191" s="231"/>
+      <c r="U191" s="230">
+        <v>0</v>
+      </c>
+      <c r="V191" s="231"/>
       <c r="W191" s="14">
         <v>0</v>
       </c>
       <c r="X191" s="120"/>
-      <c r="Y191" s="143">
+      <c r="Y191" s="230">
         <f>SUM(C191:W191)</f>
         <v>0</v>
       </c>
-      <c r="Z191" s="144"/>
+      <c r="Z191" s="231"/>
       <c r="AA191" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="AB191" s="147"/>
-      <c r="AC191" s="148"/>
+      <c r="AB191" s="214"/>
+      <c r="AC191" s="215"/>
       <c r="AD191" s="16">
         <f>X191</f>
         <v>0</v>
@@ -30439,59 +30445,59 @@
       <c r="B192" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="C192" s="137" t="s">
+      <c r="C192" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D192" s="138"/>
-      <c r="E192" s="137" t="s">
+      <c r="D192" s="129"/>
+      <c r="E192" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F192" s="138"/>
-      <c r="G192" s="137" t="s">
+      <c r="F192" s="129"/>
+      <c r="G192" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H192" s="138"/>
-      <c r="I192" s="137" t="s">
+      <c r="H192" s="129"/>
+      <c r="I192" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J192" s="138"/>
-      <c r="K192" s="137" t="s">
+      <c r="J192" s="129"/>
+      <c r="K192" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L192" s="138"/>
-      <c r="M192" s="137" t="s">
+      <c r="L192" s="129"/>
+      <c r="M192" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N192" s="138"/>
-      <c r="O192" s="137" t="s">
+      <c r="N192" s="129"/>
+      <c r="O192" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P192" s="138"/>
-      <c r="Q192" s="137" t="s">
+      <c r="P192" s="129"/>
+      <c r="Q192" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R192" s="138"/>
-      <c r="S192" s="137" t="s">
+      <c r="R192" s="129"/>
+      <c r="S192" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T192" s="138"/>
-      <c r="U192" s="137" t="s">
+      <c r="T192" s="129"/>
+      <c r="U192" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V192" s="138"/>
+      <c r="V192" s="129"/>
       <c r="W192" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X192" s="117"/>
-      <c r="Y192" s="149" t="s">
+      <c r="Y192" s="232" t="s">
         <v>13</v>
       </c>
-      <c r="Z192" s="150"/>
+      <c r="Z192" s="233"/>
       <c r="AA192" s="79" t="s">
         <v>205</v>
       </c>
-      <c r="AB192" s="141"/>
-      <c r="AC192" s="142"/>
+      <c r="AB192" s="134"/>
+      <c r="AC192" s="135"/>
       <c r="AD192" s="6" t="s">
         <v>16</v>
       </c>
@@ -30556,16 +30562,16 @@
       <c r="X193" s="122">
         <v>0</v>
       </c>
-      <c r="Y193" s="143">
+      <c r="Y193" s="230">
         <f>SUM(C193:W193)</f>
         <v>0</v>
       </c>
-      <c r="Z193" s="144"/>
+      <c r="Z193" s="231"/>
       <c r="AA193" s="68" t="s">
         <v>206</v>
       </c>
-      <c r="AB193" s="145"/>
-      <c r="AC193" s="146"/>
+      <c r="AB193" s="193"/>
+      <c r="AC193" s="194"/>
       <c r="AD193" s="16">
         <f>X193</f>
         <v>0</v>
@@ -30575,58 +30581,58 @@
       <c r="AN193" s="2"/>
     </row>
     <row r="194" spans="2:40" s="2" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B194" s="139" t="s">
+      <c r="B194" s="235" t="s">
         <v>207</v>
       </c>
-      <c r="C194" s="137" t="s">
+      <c r="C194" s="128" t="s">
         <v>2</v>
       </c>
-      <c r="D194" s="138"/>
-      <c r="E194" s="137" t="s">
+      <c r="D194" s="129"/>
+      <c r="E194" s="128" t="s">
         <v>3</v>
       </c>
-      <c r="F194" s="138"/>
-      <c r="G194" s="137" t="s">
+      <c r="F194" s="129"/>
+      <c r="G194" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="H194" s="138"/>
-      <c r="I194" s="137" t="s">
+      <c r="H194" s="129"/>
+      <c r="I194" s="128" t="s">
         <v>5</v>
       </c>
-      <c r="J194" s="138"/>
-      <c r="K194" s="137" t="s">
+      <c r="J194" s="129"/>
+      <c r="K194" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="L194" s="138"/>
-      <c r="M194" s="137" t="s">
+      <c r="L194" s="129"/>
+      <c r="M194" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="N194" s="138"/>
-      <c r="O194" s="137" t="s">
+      <c r="N194" s="129"/>
+      <c r="O194" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="P194" s="138"/>
-      <c r="Q194" s="137" t="s">
+      <c r="P194" s="129"/>
+      <c r="Q194" s="128" t="s">
         <v>9</v>
       </c>
-      <c r="R194" s="138"/>
-      <c r="S194" s="137" t="s">
+      <c r="R194" s="129"/>
+      <c r="S194" s="128" t="s">
         <v>10</v>
       </c>
-      <c r="T194" s="138"/>
-      <c r="U194" s="137" t="s">
+      <c r="T194" s="129"/>
+      <c r="U194" s="128" t="s">
         <v>11</v>
       </c>
-      <c r="V194" s="138"/>
+      <c r="V194" s="129"/>
       <c r="W194" s="9" t="s">
         <v>12</v>
       </c>
       <c r="X194" s="117"/>
-      <c r="Y194" s="133" t="s">
+      <c r="Y194" s="243" t="s">
         <v>208</v>
       </c>
-      <c r="Z194" s="134"/>
-      <c r="AA194" s="135"/>
+      <c r="Z194" s="244"/>
+      <c r="AA194" s="245"/>
       <c r="AB194" s="101"/>
       <c r="AC194" s="101"/>
       <c r="AD194" s="102"/>
@@ -30637,35 +30643,35 @@
       <c r="AN194"/>
     </row>
     <row r="195" spans="2:40" s="105" customFormat="1" ht="255" x14ac:dyDescent="3.65">
-      <c r="B195" s="140"/>
-      <c r="C195" s="136"/>
-      <c r="D195" s="136"/>
-      <c r="E195" s="136"/>
-      <c r="F195" s="136"/>
-      <c r="G195" s="136"/>
-      <c r="H195" s="136"/>
-      <c r="I195" s="136"/>
-      <c r="J195" s="136"/>
-      <c r="K195" s="136"/>
-      <c r="L195" s="136"/>
-      <c r="M195" s="136"/>
-      <c r="N195" s="136"/>
-      <c r="O195" s="136"/>
-      <c r="P195" s="136"/>
-      <c r="Q195" s="136"/>
-      <c r="R195" s="136"/>
-      <c r="S195" s="136"/>
-      <c r="T195" s="136"/>
-      <c r="U195" s="136"/>
-      <c r="V195" s="136"/>
+      <c r="B195" s="236"/>
+      <c r="C195" s="237"/>
+      <c r="D195" s="237"/>
+      <c r="E195" s="237"/>
+      <c r="F195" s="237"/>
+      <c r="G195" s="237"/>
+      <c r="H195" s="237"/>
+      <c r="I195" s="237"/>
+      <c r="J195" s="237"/>
+      <c r="K195" s="237"/>
+      <c r="L195" s="237"/>
+      <c r="M195" s="237"/>
+      <c r="N195" s="237"/>
+      <c r="O195" s="237"/>
+      <c r="P195" s="237"/>
+      <c r="Q195" s="237"/>
+      <c r="R195" s="237"/>
+      <c r="S195" s="237"/>
+      <c r="T195" s="237"/>
+      <c r="U195" s="237"/>
+      <c r="V195" s="237"/>
       <c r="W195" s="127"/>
       <c r="X195" s="123"/>
-      <c r="Y195" s="128">
+      <c r="Y195" s="238">
         <f>SUM(C195:W195)</f>
         <v>0</v>
       </c>
-      <c r="Z195" s="129"/>
-      <c r="AA195" s="130"/>
+      <c r="Z195" s="239"/>
+      <c r="AA195" s="240"/>
       <c r="AB195" s="103"/>
       <c r="AC195" s="103"/>
       <c r="AD195" s="104"/>
@@ -30681,10 +30687,10 @@
       <c r="AN195" s="2"/>
     </row>
     <row r="197" spans="2:40" x14ac:dyDescent="2.35">
-      <c r="C197" s="131"/>
-      <c r="D197" s="131"/>
-      <c r="O197" s="132"/>
-      <c r="P197" s="132"/>
+      <c r="C197" s="241"/>
+      <c r="D197" s="241"/>
+      <c r="O197" s="242"/>
+      <c r="P197" s="242"/>
       <c r="R197" s="107"/>
       <c r="AA197" s="108"/>
     </row>
@@ -30693,24 +30699,306 @@
     </row>
   </sheetData>
   <mergeCells count="342">
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="B1:AD1"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="Y195:AA195"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="O197:P197"/>
+    <mergeCell ref="Y194:AA194"/>
+    <mergeCell ref="C195:D195"/>
+    <mergeCell ref="E195:F195"/>
+    <mergeCell ref="G195:H195"/>
+    <mergeCell ref="I195:J195"/>
+    <mergeCell ref="K195:L195"/>
+    <mergeCell ref="M195:N195"/>
+    <mergeCell ref="O195:P195"/>
+    <mergeCell ref="Q195:R195"/>
+    <mergeCell ref="M194:N194"/>
+    <mergeCell ref="O194:P194"/>
+    <mergeCell ref="Q194:R194"/>
+    <mergeCell ref="S194:T194"/>
+    <mergeCell ref="U194:V194"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="C194:D194"/>
+    <mergeCell ref="E194:F194"/>
+    <mergeCell ref="G194:H194"/>
+    <mergeCell ref="I194:J194"/>
+    <mergeCell ref="K194:L194"/>
+    <mergeCell ref="Q192:R192"/>
+    <mergeCell ref="S192:T192"/>
+    <mergeCell ref="U192:V192"/>
+    <mergeCell ref="S195:T195"/>
+    <mergeCell ref="U195:V195"/>
+    <mergeCell ref="AB192:AC192"/>
+    <mergeCell ref="Y193:Z193"/>
+    <mergeCell ref="AB193:AC193"/>
+    <mergeCell ref="Y191:Z191"/>
+    <mergeCell ref="AB191:AC191"/>
+    <mergeCell ref="C192:D192"/>
+    <mergeCell ref="E192:F192"/>
+    <mergeCell ref="G192:H192"/>
+    <mergeCell ref="I192:J192"/>
+    <mergeCell ref="K192:L192"/>
+    <mergeCell ref="M192:N192"/>
+    <mergeCell ref="O192:P192"/>
+    <mergeCell ref="M191:N191"/>
+    <mergeCell ref="O191:P191"/>
+    <mergeCell ref="Q191:R191"/>
+    <mergeCell ref="S191:T191"/>
+    <mergeCell ref="U191:V191"/>
+    <mergeCell ref="Y192:Z192"/>
+    <mergeCell ref="C191:D191"/>
+    <mergeCell ref="E191:F191"/>
+    <mergeCell ref="G191:H191"/>
+    <mergeCell ref="I191:J191"/>
+    <mergeCell ref="K191:L191"/>
+    <mergeCell ref="Y189:Z189"/>
+    <mergeCell ref="AB189:AC189"/>
+    <mergeCell ref="C190:D190"/>
+    <mergeCell ref="E190:F190"/>
+    <mergeCell ref="G190:H190"/>
+    <mergeCell ref="I190:J190"/>
+    <mergeCell ref="K190:L190"/>
+    <mergeCell ref="M190:N190"/>
+    <mergeCell ref="O190:P190"/>
+    <mergeCell ref="S190:T190"/>
+    <mergeCell ref="U190:V190"/>
+    <mergeCell ref="Y190:Z190"/>
+    <mergeCell ref="AB190:AC190"/>
+    <mergeCell ref="Q190:R190"/>
+    <mergeCell ref="Y186:Z186"/>
+    <mergeCell ref="AB186:AC186"/>
+    <mergeCell ref="Y187:Z187"/>
+    <mergeCell ref="AB187:AC187"/>
+    <mergeCell ref="Y188:Z188"/>
+    <mergeCell ref="AB188:AC188"/>
+    <mergeCell ref="Y182:Z182"/>
+    <mergeCell ref="AB182:AC182"/>
+    <mergeCell ref="Y183:Z183"/>
+    <mergeCell ref="AB183:AC183"/>
+    <mergeCell ref="Y185:Z185"/>
+    <mergeCell ref="AB185:AC185"/>
+    <mergeCell ref="Y184:Z184"/>
+    <mergeCell ref="Y179:Z179"/>
+    <mergeCell ref="AB179:AC179"/>
+    <mergeCell ref="Y180:Z180"/>
+    <mergeCell ref="AB180:AC180"/>
+    <mergeCell ref="AG180:AI180"/>
+    <mergeCell ref="Y181:Z181"/>
+    <mergeCell ref="AB181:AC181"/>
+    <mergeCell ref="Y176:Z176"/>
+    <mergeCell ref="AB176:AC176"/>
+    <mergeCell ref="Y177:Z177"/>
+    <mergeCell ref="AB177:AC177"/>
+    <mergeCell ref="Y178:Z178"/>
+    <mergeCell ref="AB178:AC178"/>
+    <mergeCell ref="Y171:Z171"/>
+    <mergeCell ref="Y172:Z172"/>
+    <mergeCell ref="Y173:Z173"/>
+    <mergeCell ref="Y174:Z174"/>
+    <mergeCell ref="AB174:AC174"/>
+    <mergeCell ref="Y175:Z175"/>
+    <mergeCell ref="AB175:AC175"/>
+    <mergeCell ref="Y165:Z165"/>
+    <mergeCell ref="AB165:AC165"/>
+    <mergeCell ref="Y166:Z166"/>
+    <mergeCell ref="AB166:AC173"/>
+    <mergeCell ref="AF166:AJ169"/>
+    <mergeCell ref="Y167:Z167"/>
+    <mergeCell ref="Y168:Z168"/>
+    <mergeCell ref="Y169:Z169"/>
+    <mergeCell ref="Y170:Z170"/>
+    <mergeCell ref="AF170:AJ170"/>
+    <mergeCell ref="M165:N165"/>
+    <mergeCell ref="O165:P165"/>
+    <mergeCell ref="Q165:R165"/>
+    <mergeCell ref="S165:T165"/>
+    <mergeCell ref="U165:V165"/>
+    <mergeCell ref="AB159:AC164"/>
+    <mergeCell ref="C165:D165"/>
+    <mergeCell ref="E165:F165"/>
+    <mergeCell ref="G165:H165"/>
+    <mergeCell ref="I165:J165"/>
+    <mergeCell ref="K165:L165"/>
+    <mergeCell ref="M157:N157"/>
+    <mergeCell ref="O157:P157"/>
+    <mergeCell ref="Q157:R157"/>
+    <mergeCell ref="S157:T157"/>
+    <mergeCell ref="U157:V157"/>
+    <mergeCell ref="W157:W158"/>
+    <mergeCell ref="C143:D143"/>
+    <mergeCell ref="E143:F143"/>
+    <mergeCell ref="G143:H143"/>
+    <mergeCell ref="I143:J143"/>
+    <mergeCell ref="K143:L143"/>
+    <mergeCell ref="AB144:AC154"/>
+    <mergeCell ref="AB155:AC155"/>
+    <mergeCell ref="B156:AD156"/>
+    <mergeCell ref="B157:B158"/>
+    <mergeCell ref="C157:D157"/>
+    <mergeCell ref="E157:F157"/>
+    <mergeCell ref="G157:H157"/>
+    <mergeCell ref="I157:J157"/>
+    <mergeCell ref="K157:L157"/>
+    <mergeCell ref="Y157:Y158"/>
+    <mergeCell ref="Z157:Z158"/>
+    <mergeCell ref="AA157:AA158"/>
+    <mergeCell ref="AB157:AC157"/>
+    <mergeCell ref="AB141:AC142"/>
+    <mergeCell ref="AF138:AJ138"/>
+    <mergeCell ref="AB139:AC139"/>
+    <mergeCell ref="AF139:AJ139"/>
+    <mergeCell ref="M143:N143"/>
+    <mergeCell ref="O143:P143"/>
+    <mergeCell ref="Q143:R143"/>
+    <mergeCell ref="S143:T143"/>
+    <mergeCell ref="U143:V143"/>
+    <mergeCell ref="AB143:AC143"/>
+    <mergeCell ref="C140:D140"/>
+    <mergeCell ref="E140:F140"/>
+    <mergeCell ref="G140:H140"/>
+    <mergeCell ref="I140:J140"/>
+    <mergeCell ref="K140:L140"/>
+    <mergeCell ref="M140:N140"/>
+    <mergeCell ref="AB107:AC111"/>
+    <mergeCell ref="AF111:AJ111"/>
+    <mergeCell ref="AB112:AC125"/>
+    <mergeCell ref="AF112:AJ117"/>
+    <mergeCell ref="O140:P140"/>
+    <mergeCell ref="Q140:R140"/>
+    <mergeCell ref="S140:T140"/>
+    <mergeCell ref="U140:V140"/>
+    <mergeCell ref="AB140:AC140"/>
+    <mergeCell ref="AK113:AL139"/>
+    <mergeCell ref="AF118:AJ118"/>
+    <mergeCell ref="AF119:AJ119"/>
+    <mergeCell ref="AB126:AC138"/>
+    <mergeCell ref="AF126:AJ128"/>
+    <mergeCell ref="AF130:AJ130"/>
+    <mergeCell ref="U105:V105"/>
+    <mergeCell ref="W105:W106"/>
+    <mergeCell ref="Y105:Y106"/>
+    <mergeCell ref="Z105:Z106"/>
+    <mergeCell ref="AA105:AA106"/>
+    <mergeCell ref="AB105:AC105"/>
+    <mergeCell ref="K105:L105"/>
+    <mergeCell ref="M105:N105"/>
+    <mergeCell ref="O105:P105"/>
+    <mergeCell ref="Q105:R105"/>
+    <mergeCell ref="S105:T105"/>
+    <mergeCell ref="AF98:AJ98"/>
+    <mergeCell ref="AF100:AJ100"/>
+    <mergeCell ref="AB103:AC103"/>
+    <mergeCell ref="AF103:AJ107"/>
+    <mergeCell ref="B104:AD104"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:D105"/>
+    <mergeCell ref="E105:F105"/>
+    <mergeCell ref="G105:H105"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="U87:V87"/>
+    <mergeCell ref="AB87:AC87"/>
+    <mergeCell ref="AK87:AL112"/>
+    <mergeCell ref="AB88:AC88"/>
+    <mergeCell ref="AB90:AC90"/>
+    <mergeCell ref="AB91:AC91"/>
+    <mergeCell ref="AB92:AC92"/>
+    <mergeCell ref="AB93:AC102"/>
+    <mergeCell ref="AF93:AJ97"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="E87:F87"/>
+    <mergeCell ref="G87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="K87:L87"/>
+    <mergeCell ref="M87:N87"/>
+    <mergeCell ref="O87:P87"/>
+    <mergeCell ref="Q87:R87"/>
+    <mergeCell ref="S87:T87"/>
+    <mergeCell ref="AF78:AJ78"/>
+    <mergeCell ref="AF79:AJ79"/>
+    <mergeCell ref="AB80:AC81"/>
+    <mergeCell ref="AF80:AJ80"/>
+    <mergeCell ref="AK80:AL86"/>
+    <mergeCell ref="AF81:AJ81"/>
+    <mergeCell ref="AB82:AC82"/>
+    <mergeCell ref="AB83:AC83"/>
+    <mergeCell ref="AB84:AC84"/>
+    <mergeCell ref="AB85:AC85"/>
+    <mergeCell ref="AK71:AL78"/>
+    <mergeCell ref="AF72:AJ72"/>
+    <mergeCell ref="AB73:AC73"/>
+    <mergeCell ref="AB74:AC75"/>
+    <mergeCell ref="AF74:AJ74"/>
+    <mergeCell ref="AF75:AJ75"/>
+    <mergeCell ref="AB76:AC77"/>
+    <mergeCell ref="AF76:AJ76"/>
+    <mergeCell ref="AF77:AJ77"/>
+    <mergeCell ref="AB78:AC79"/>
+    <mergeCell ref="AB86:AC86"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="S70:T70"/>
+    <mergeCell ref="U70:V70"/>
+    <mergeCell ref="AB70:AC70"/>
+    <mergeCell ref="AB71:AC72"/>
+    <mergeCell ref="AF71:AJ71"/>
+    <mergeCell ref="AB68:AC68"/>
+    <mergeCell ref="AB69:AC69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="G70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="M70:N70"/>
+    <mergeCell ref="O70:P70"/>
+    <mergeCell ref="AB62:AC67"/>
+    <mergeCell ref="AF63:AJ63"/>
+    <mergeCell ref="AF64:AJ64"/>
+    <mergeCell ref="M60:N60"/>
+    <mergeCell ref="O60:P60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="S60:T60"/>
+    <mergeCell ref="U60:V60"/>
+    <mergeCell ref="W60:W61"/>
+    <mergeCell ref="AB55:AC55"/>
+    <mergeCell ref="AC57:AC58"/>
+    <mergeCell ref="AB59:AC59"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="G60:H60"/>
+    <mergeCell ref="I60:J60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="Y60:Y61"/>
+    <mergeCell ref="Z60:Z61"/>
+    <mergeCell ref="AA60:AA61"/>
+    <mergeCell ref="AB60:AC60"/>
+    <mergeCell ref="AB48:AC51"/>
+    <mergeCell ref="AB54:AC54"/>
+    <mergeCell ref="AB42:AC47"/>
+    <mergeCell ref="AF42:AJ42"/>
+    <mergeCell ref="AF47:AJ47"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="AB40:AC40"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="AB33:AC34"/>
+    <mergeCell ref="AF33:AJ33"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AB24:AC25"/>
+    <mergeCell ref="AF24:AJ24"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AB36:AC37"/>
+    <mergeCell ref="AF36:AJ36"/>
+    <mergeCell ref="AF37:AJ37"/>
+    <mergeCell ref="AB38:AC38"/>
+    <mergeCell ref="AB39:AC39"/>
     <mergeCell ref="Z4:Z8"/>
     <mergeCell ref="AC4:AC8"/>
     <mergeCell ref="AF4:AJ6"/>
@@ -30735,306 +31023,24 @@
     <mergeCell ref="AB30:AC31"/>
     <mergeCell ref="AF30:AJ30"/>
     <mergeCell ref="AF31:AJ31"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="AB33:AC34"/>
-    <mergeCell ref="AF33:AJ33"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AB24:AC25"/>
-    <mergeCell ref="AF24:AJ24"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AB36:AC37"/>
-    <mergeCell ref="AF36:AJ36"/>
-    <mergeCell ref="AF37:AJ37"/>
-    <mergeCell ref="AB38:AC38"/>
-    <mergeCell ref="AB39:AC39"/>
-    <mergeCell ref="AB48:AC51"/>
-    <mergeCell ref="AB54:AC54"/>
-    <mergeCell ref="AB42:AC47"/>
-    <mergeCell ref="AF42:AJ42"/>
-    <mergeCell ref="AF47:AJ47"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="AB40:AC40"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="AC57:AC58"/>
-    <mergeCell ref="AB59:AC59"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="G60:H60"/>
-    <mergeCell ref="I60:J60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="Y60:Y61"/>
-    <mergeCell ref="Z60:Z61"/>
-    <mergeCell ref="AA60:AA61"/>
-    <mergeCell ref="AB60:AC60"/>
-    <mergeCell ref="AB62:AC67"/>
-    <mergeCell ref="AF63:AJ63"/>
-    <mergeCell ref="AF64:AJ64"/>
-    <mergeCell ref="M60:N60"/>
-    <mergeCell ref="O60:P60"/>
-    <mergeCell ref="Q60:R60"/>
-    <mergeCell ref="S60:T60"/>
-    <mergeCell ref="U60:V60"/>
-    <mergeCell ref="W60:W61"/>
-    <mergeCell ref="Q70:R70"/>
-    <mergeCell ref="S70:T70"/>
-    <mergeCell ref="U70:V70"/>
-    <mergeCell ref="AB70:AC70"/>
-    <mergeCell ref="AB71:AC72"/>
-    <mergeCell ref="AF71:AJ71"/>
-    <mergeCell ref="AB68:AC68"/>
-    <mergeCell ref="AB69:AC69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="M70:N70"/>
-    <mergeCell ref="O70:P70"/>
-    <mergeCell ref="AF78:AJ78"/>
-    <mergeCell ref="AF79:AJ79"/>
-    <mergeCell ref="AB80:AC81"/>
-    <mergeCell ref="AF80:AJ80"/>
-    <mergeCell ref="AK80:AL86"/>
-    <mergeCell ref="AF81:AJ81"/>
-    <mergeCell ref="AB82:AC82"/>
-    <mergeCell ref="AB83:AC83"/>
-    <mergeCell ref="AB84:AC84"/>
-    <mergeCell ref="AB85:AC85"/>
-    <mergeCell ref="AK71:AL78"/>
-    <mergeCell ref="AF72:AJ72"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AB74:AC75"/>
-    <mergeCell ref="AF74:AJ74"/>
-    <mergeCell ref="AF75:AJ75"/>
-    <mergeCell ref="AB76:AC77"/>
-    <mergeCell ref="AF76:AJ76"/>
-    <mergeCell ref="AF77:AJ77"/>
-    <mergeCell ref="AB78:AC79"/>
-    <mergeCell ref="AB86:AC86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="E87:F87"/>
-    <mergeCell ref="G87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="K87:L87"/>
-    <mergeCell ref="M87:N87"/>
-    <mergeCell ref="O87:P87"/>
-    <mergeCell ref="Q87:R87"/>
-    <mergeCell ref="S87:T87"/>
-    <mergeCell ref="U87:V87"/>
-    <mergeCell ref="AB87:AC87"/>
-    <mergeCell ref="AK87:AL112"/>
-    <mergeCell ref="AB88:AC88"/>
-    <mergeCell ref="AB90:AC90"/>
-    <mergeCell ref="AB91:AC91"/>
-    <mergeCell ref="AB92:AC92"/>
-    <mergeCell ref="AB93:AC102"/>
-    <mergeCell ref="AF93:AJ97"/>
-    <mergeCell ref="K105:L105"/>
-    <mergeCell ref="M105:N105"/>
-    <mergeCell ref="O105:P105"/>
-    <mergeCell ref="Q105:R105"/>
-    <mergeCell ref="S105:T105"/>
-    <mergeCell ref="AF98:AJ98"/>
-    <mergeCell ref="AF100:AJ100"/>
-    <mergeCell ref="AB103:AC103"/>
-    <mergeCell ref="AF103:AJ107"/>
-    <mergeCell ref="B104:AD104"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:D105"/>
-    <mergeCell ref="E105:F105"/>
-    <mergeCell ref="G105:H105"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="AK113:AL139"/>
-    <mergeCell ref="AF118:AJ118"/>
-    <mergeCell ref="AF119:AJ119"/>
-    <mergeCell ref="AB126:AC138"/>
-    <mergeCell ref="AF126:AJ128"/>
-    <mergeCell ref="AF130:AJ130"/>
-    <mergeCell ref="U105:V105"/>
-    <mergeCell ref="W105:W106"/>
-    <mergeCell ref="Y105:Y106"/>
-    <mergeCell ref="Z105:Z106"/>
-    <mergeCell ref="AA105:AA106"/>
-    <mergeCell ref="AB105:AC105"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="E140:F140"/>
-    <mergeCell ref="G140:H140"/>
-    <mergeCell ref="I140:J140"/>
-    <mergeCell ref="K140:L140"/>
-    <mergeCell ref="M140:N140"/>
-    <mergeCell ref="AB107:AC111"/>
-    <mergeCell ref="AF111:AJ111"/>
-    <mergeCell ref="AB112:AC125"/>
-    <mergeCell ref="AF112:AJ117"/>
-    <mergeCell ref="O140:P140"/>
-    <mergeCell ref="Q140:R140"/>
-    <mergeCell ref="S140:T140"/>
-    <mergeCell ref="U140:V140"/>
-    <mergeCell ref="AB140:AC140"/>
-    <mergeCell ref="AB141:AC142"/>
-    <mergeCell ref="AF138:AJ138"/>
-    <mergeCell ref="AB139:AC139"/>
-    <mergeCell ref="AF139:AJ139"/>
-    <mergeCell ref="M143:N143"/>
-    <mergeCell ref="O143:P143"/>
-    <mergeCell ref="Q143:R143"/>
-    <mergeCell ref="S143:T143"/>
-    <mergeCell ref="U143:V143"/>
-    <mergeCell ref="AB143:AC143"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="E143:F143"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="I143:J143"/>
-    <mergeCell ref="K143:L143"/>
-    <mergeCell ref="AB144:AC154"/>
-    <mergeCell ref="AB155:AC155"/>
-    <mergeCell ref="B156:AD156"/>
-    <mergeCell ref="B157:B158"/>
-    <mergeCell ref="C157:D157"/>
-    <mergeCell ref="E157:F157"/>
-    <mergeCell ref="G157:H157"/>
-    <mergeCell ref="I157:J157"/>
-    <mergeCell ref="K157:L157"/>
-    <mergeCell ref="Y157:Y158"/>
-    <mergeCell ref="Z157:Z158"/>
-    <mergeCell ref="AA157:AA158"/>
-    <mergeCell ref="AB157:AC157"/>
-    <mergeCell ref="AB159:AC164"/>
-    <mergeCell ref="C165:D165"/>
-    <mergeCell ref="E165:F165"/>
-    <mergeCell ref="G165:H165"/>
-    <mergeCell ref="I165:J165"/>
-    <mergeCell ref="K165:L165"/>
-    <mergeCell ref="M157:N157"/>
-    <mergeCell ref="O157:P157"/>
-    <mergeCell ref="Q157:R157"/>
-    <mergeCell ref="S157:T157"/>
-    <mergeCell ref="U157:V157"/>
-    <mergeCell ref="W157:W158"/>
-    <mergeCell ref="AF166:AJ169"/>
-    <mergeCell ref="Y167:Z167"/>
-    <mergeCell ref="Y168:Z168"/>
-    <mergeCell ref="Y169:Z169"/>
-    <mergeCell ref="Y170:Z170"/>
-    <mergeCell ref="AF170:AJ170"/>
-    <mergeCell ref="M165:N165"/>
-    <mergeCell ref="O165:P165"/>
-    <mergeCell ref="Q165:R165"/>
-    <mergeCell ref="S165:T165"/>
-    <mergeCell ref="U165:V165"/>
-    <mergeCell ref="Y171:Z171"/>
-    <mergeCell ref="Y172:Z172"/>
-    <mergeCell ref="Y173:Z173"/>
-    <mergeCell ref="Y174:Z174"/>
-    <mergeCell ref="AB174:AC174"/>
-    <mergeCell ref="Y175:Z175"/>
-    <mergeCell ref="AB175:AC175"/>
-    <mergeCell ref="Y165:Z165"/>
-    <mergeCell ref="AB165:AC165"/>
-    <mergeCell ref="Y166:Z166"/>
-    <mergeCell ref="AB166:AC173"/>
-    <mergeCell ref="Y179:Z179"/>
-    <mergeCell ref="AB179:AC179"/>
-    <mergeCell ref="Y180:Z180"/>
-    <mergeCell ref="AB180:AC180"/>
-    <mergeCell ref="AG180:AI180"/>
-    <mergeCell ref="Y181:Z181"/>
-    <mergeCell ref="AB181:AC181"/>
-    <mergeCell ref="Y176:Z176"/>
-    <mergeCell ref="AB176:AC176"/>
-    <mergeCell ref="Y177:Z177"/>
-    <mergeCell ref="AB177:AC177"/>
-    <mergeCell ref="Y178:Z178"/>
-    <mergeCell ref="AB178:AC178"/>
-    <mergeCell ref="Y186:Z186"/>
-    <mergeCell ref="AB186:AC186"/>
-    <mergeCell ref="Y187:Z187"/>
-    <mergeCell ref="AB187:AC187"/>
-    <mergeCell ref="Y188:Z188"/>
-    <mergeCell ref="AB188:AC188"/>
-    <mergeCell ref="Y182:Z182"/>
-    <mergeCell ref="AB182:AC182"/>
-    <mergeCell ref="Y183:Z183"/>
-    <mergeCell ref="AB183:AC183"/>
-    <mergeCell ref="Y185:Z185"/>
-    <mergeCell ref="AB185:AC185"/>
-    <mergeCell ref="Y184:Z184"/>
-    <mergeCell ref="Y189:Z189"/>
-    <mergeCell ref="AB189:AC189"/>
-    <mergeCell ref="C190:D190"/>
-    <mergeCell ref="E190:F190"/>
-    <mergeCell ref="G190:H190"/>
-    <mergeCell ref="I190:J190"/>
-    <mergeCell ref="K190:L190"/>
-    <mergeCell ref="M190:N190"/>
-    <mergeCell ref="O190:P190"/>
-    <mergeCell ref="S190:T190"/>
-    <mergeCell ref="U190:V190"/>
-    <mergeCell ref="Y190:Z190"/>
-    <mergeCell ref="AB190:AC190"/>
-    <mergeCell ref="Q190:R190"/>
-    <mergeCell ref="AB192:AC192"/>
-    <mergeCell ref="Y193:Z193"/>
-    <mergeCell ref="AB193:AC193"/>
-    <mergeCell ref="Y191:Z191"/>
-    <mergeCell ref="AB191:AC191"/>
-    <mergeCell ref="C192:D192"/>
-    <mergeCell ref="E192:F192"/>
-    <mergeCell ref="G192:H192"/>
-    <mergeCell ref="I192:J192"/>
-    <mergeCell ref="K192:L192"/>
-    <mergeCell ref="M192:N192"/>
-    <mergeCell ref="O192:P192"/>
-    <mergeCell ref="M191:N191"/>
-    <mergeCell ref="O191:P191"/>
-    <mergeCell ref="Q191:R191"/>
-    <mergeCell ref="S191:T191"/>
-    <mergeCell ref="U191:V191"/>
-    <mergeCell ref="Y192:Z192"/>
-    <mergeCell ref="C191:D191"/>
-    <mergeCell ref="E191:F191"/>
-    <mergeCell ref="G191:H191"/>
-    <mergeCell ref="I191:J191"/>
-    <mergeCell ref="K191:L191"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="C194:D194"/>
-    <mergeCell ref="E194:F194"/>
-    <mergeCell ref="G194:H194"/>
-    <mergeCell ref="I194:J194"/>
-    <mergeCell ref="K194:L194"/>
-    <mergeCell ref="Q192:R192"/>
-    <mergeCell ref="S192:T192"/>
-    <mergeCell ref="U192:V192"/>
-    <mergeCell ref="S195:T195"/>
-    <mergeCell ref="U195:V195"/>
-    <mergeCell ref="Y195:AA195"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="O197:P197"/>
-    <mergeCell ref="Y194:AA194"/>
-    <mergeCell ref="C195:D195"/>
-    <mergeCell ref="E195:F195"/>
-    <mergeCell ref="G195:H195"/>
-    <mergeCell ref="I195:J195"/>
-    <mergeCell ref="K195:L195"/>
-    <mergeCell ref="M195:N195"/>
-    <mergeCell ref="O195:P195"/>
-    <mergeCell ref="Q195:R195"/>
-    <mergeCell ref="M194:N194"/>
-    <mergeCell ref="O194:P194"/>
-    <mergeCell ref="Q194:R194"/>
-    <mergeCell ref="S194:T194"/>
-    <mergeCell ref="U194:V194"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="B1:AD1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="X2:X3"/>
   </mergeCells>
   <pageMargins left="1.1023622047244095" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="10" orientation="landscape" verticalDpi="0" r:id="rId1"/>

--- a/base/base_0.xlsx
+++ b/base/base_0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\ELIECER\scripts\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48318A8C-9AAB-4AED-A94D-5E6B840BF3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167E7B28-17FB-47B1-B8C4-DBA35DEDF3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="base_0" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">base_0!$B$1:$AN$201</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">base_0!$B$1:$AN$202</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="226">
   <si>
     <t>PRODUCTO</t>
   </si>
@@ -709,6 +709,9 @@
   </si>
   <si>
     <t>SODA FRUTOS VERDES</t>
+  </si>
+  <si>
+    <t>TORTA 18 PX NUTELLA</t>
   </si>
 </sst>
 </file>
@@ -1503,11 +1506,128 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1521,35 +1641,56 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1569,154 +1710,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1752,110 +1755,110 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="6" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12059,13 +12062,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>635000</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>79375</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>144</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -12117,13 +12120,13 @@
     <xdr:from>
       <xdr:col>30</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>169</xdr:row>
+      <xdr:row>170</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>2063750</xdr:colOff>
-      <xdr:row>176</xdr:row>
+      <xdr:row>177</xdr:row>
       <xdr:rowOff>840442</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -12935,7 +12938,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2C16D61-1387-43E7-AAB8-12891EF5AEBF}">
-  <dimension ref="A1:AN204"/>
+  <dimension ref="A1:AN205"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="165" x14ac:dyDescent="2.35"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
@@ -12959,103 +12962,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B1" s="138" t="s">
+      <c r="B1" s="177" t="s">
         <v>220</v>
       </c>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="139"/>
-      <c r="O1" s="139"/>
-      <c r="P1" s="139"/>
-      <c r="Q1" s="139"/>
-      <c r="R1" s="139"/>
-      <c r="S1" s="139"/>
-      <c r="T1" s="139"/>
-      <c r="U1" s="139"/>
-      <c r="V1" s="139"/>
-      <c r="W1" s="139"/>
-      <c r="X1" s="139"/>
-      <c r="Y1" s="139"/>
-      <c r="Z1" s="139"/>
-      <c r="AA1" s="139"/>
-      <c r="AB1" s="139"/>
-      <c r="AC1" s="139"/>
-      <c r="AD1" s="139"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
+      <c r="H1" s="178"/>
+      <c r="I1" s="178"/>
+      <c r="J1" s="178"/>
+      <c r="K1" s="178"/>
+      <c r="L1" s="178"/>
+      <c r="M1" s="178"/>
+      <c r="N1" s="178"/>
+      <c r="O1" s="178"/>
+      <c r="P1" s="178"/>
+      <c r="Q1" s="178"/>
+      <c r="R1" s="178"/>
+      <c r="S1" s="178"/>
+      <c r="T1" s="178"/>
+      <c r="U1" s="178"/>
+      <c r="V1" s="178"/>
+      <c r="W1" s="178"/>
+      <c r="X1" s="178"/>
+      <c r="Y1" s="178"/>
+      <c r="Z1" s="178"/>
+      <c r="AA1" s="178"/>
+      <c r="AB1" s="178"/>
+      <c r="AC1" s="178"/>
+      <c r="AD1" s="178"/>
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
     <row r="2" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B2" s="136" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="134" t="s">
+      <c r="B2" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="135"/>
-      <c r="E2" s="134" t="s">
+      <c r="D2" s="144"/>
+      <c r="E2" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="135"/>
-      <c r="G2" s="134" t="s">
+      <c r="F2" s="144"/>
+      <c r="G2" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="135"/>
-      <c r="I2" s="134" t="s">
+      <c r="H2" s="144"/>
+      <c r="I2" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="135"/>
-      <c r="K2" s="134" t="s">
+      <c r="J2" s="144"/>
+      <c r="K2" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="135"/>
-      <c r="M2" s="134" t="s">
+      <c r="L2" s="144"/>
+      <c r="M2" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="135"/>
-      <c r="O2" s="134" t="s">
+      <c r="N2" s="144"/>
+      <c r="O2" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="135"/>
-      <c r="Q2" s="134" t="s">
+      <c r="P2" s="144"/>
+      <c r="Q2" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R2" s="135"/>
-      <c r="S2" s="134" t="s">
+      <c r="R2" s="144"/>
+      <c r="S2" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T2" s="135"/>
-      <c r="U2" s="134" t="s">
+      <c r="T2" s="144"/>
+      <c r="U2" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V2" s="135"/>
-      <c r="W2" s="136" t="s">
+      <c r="V2" s="144"/>
+      <c r="W2" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="X2" s="142" t="s">
+      <c r="X2" s="250" t="s">
         <v>208</v>
       </c>
-      <c r="Y2" s="136" t="s">
+      <c r="Y2" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="Z2" s="136" t="s">
+      <c r="Z2" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="AA2" s="136" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="140" t="s">
+      <c r="AA2" s="175" t="s">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="147" t="s">
         <v>14</v>
       </c>
-      <c r="AC2" s="141"/>
+      <c r="AC2" s="148"/>
       <c r="AD2" s="6" t="s">
         <v>15</v>
       </c>
@@ -13069,7 +13072,7 @@
       <c r="AL2" s="8"/>
     </row>
     <row r="3" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B3" s="137"/>
+      <c r="B3" s="176"/>
       <c r="C3" s="9" t="s">
         <v>16</v>
       </c>
@@ -13130,11 +13133,11 @@
       <c r="V3" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="137"/>
-      <c r="X3" s="143"/>
-      <c r="Y3" s="137"/>
-      <c r="Z3" s="137"/>
-      <c r="AA3" s="137"/>
+      <c r="W3" s="176"/>
+      <c r="X3" s="251"/>
+      <c r="Y3" s="176"/>
+      <c r="Z3" s="176"/>
+      <c r="AA3" s="176"/>
       <c r="AB3" s="10"/>
       <c r="AC3" s="11"/>
       <c r="AD3" s="6"/>
@@ -13221,14 +13224,14 @@
         <f>SUM(C4,E4,G4,I4,K4,,M4,O4,Q4,S4,U4,W4)</f>
         <v>0</v>
       </c>
-      <c r="Z4" s="144">
+      <c r="Z4" s="234">
         <f>SUM(D9,F9,H9,J9,L9,,N9,P9,R9,T9,V9)</f>
         <v>0</v>
       </c>
       <c r="AA4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="AC4" s="147">
+      <c r="AC4" s="163">
         <f>SUM(Y4,AB5,AB6,AB7,AB8)</f>
         <v>0</v>
       </c>
@@ -13237,18 +13240,18 @@
         <v>0</v>
       </c>
       <c r="AE4" s="17"/>
-      <c r="AF4" s="150" t="s">
+      <c r="AF4" s="196" t="s">
         <v>19</v>
       </c>
-      <c r="AG4" s="151"/>
-      <c r="AH4" s="151"/>
-      <c r="AI4" s="151"/>
-      <c r="AJ4" s="152"/>
-      <c r="AK4" s="156">
+      <c r="AG4" s="197"/>
+      <c r="AH4" s="197"/>
+      <c r="AI4" s="197"/>
+      <c r="AJ4" s="198"/>
+      <c r="AK4" s="237">
         <f>SUM(AD4:AD62)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AL4" s="157"/>
+      <c r="AL4" s="238"/>
     </row>
     <row r="5" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B5" s="13" t="s">
@@ -13304,7 +13307,7 @@
         <f>SUM(C5:W5)</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="145"/>
+      <c r="Z5" s="235"/>
       <c r="AA5" s="13" t="s">
         <v>20</v>
       </c>
@@ -13312,19 +13315,19 @@
         <f>Y5*4</f>
         <v>0</v>
       </c>
-      <c r="AC5" s="148"/>
+      <c r="AC5" s="165"/>
       <c r="AD5" s="16">
         <f>X5</f>
         <v>0</v>
       </c>
       <c r="AE5" s="17"/>
-      <c r="AF5" s="153"/>
-      <c r="AG5" s="154"/>
-      <c r="AH5" s="154"/>
-      <c r="AI5" s="154"/>
-      <c r="AJ5" s="155"/>
-      <c r="AK5" s="158"/>
-      <c r="AL5" s="157"/>
+      <c r="AF5" s="199"/>
+      <c r="AG5" s="200"/>
+      <c r="AH5" s="200"/>
+      <c r="AI5" s="200"/>
+      <c r="AJ5" s="201"/>
+      <c r="AK5" s="239"/>
+      <c r="AL5" s="238"/>
     </row>
     <row r="6" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B6" s="13" t="s">
@@ -13380,7 +13383,7 @@
         <f>SUM(C6:W6)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="145"/>
+      <c r="Z6" s="235"/>
       <c r="AA6" s="15" t="s">
         <v>22</v>
       </c>
@@ -13388,19 +13391,19 @@
         <f>Y6*8</f>
         <v>0</v>
       </c>
-      <c r="AC6" s="148"/>
+      <c r="AC6" s="165"/>
       <c r="AD6" s="16">
         <f t="shared" ref="AD6:AD7" si="0">X6</f>
         <v>0</v>
       </c>
       <c r="AE6" s="17"/>
-      <c r="AF6" s="153"/>
-      <c r="AG6" s="154"/>
-      <c r="AH6" s="154"/>
-      <c r="AI6" s="154"/>
-      <c r="AJ6" s="155"/>
-      <c r="AK6" s="158"/>
-      <c r="AL6" s="157"/>
+      <c r="AF6" s="199"/>
+      <c r="AG6" s="200"/>
+      <c r="AH6" s="200"/>
+      <c r="AI6" s="200"/>
+      <c r="AJ6" s="201"/>
+      <c r="AK6" s="239"/>
+      <c r="AL6" s="238"/>
     </row>
     <row r="7" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B7" s="13" t="s">
@@ -13456,7 +13459,7 @@
         <f>SUM(C7:W7)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="145"/>
+      <c r="Z7" s="235"/>
       <c r="AA7" s="15" t="s">
         <v>24</v>
       </c>
@@ -13464,22 +13467,22 @@
         <f>Y7*12</f>
         <v>0</v>
       </c>
-      <c r="AC7" s="148"/>
+      <c r="AC7" s="165"/>
       <c r="AD7" s="16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AE7" s="17"/>
-      <c r="AF7" s="159">
+      <c r="AF7" s="174">
         <f>SUM(AD4:AD8)</f>
         <v>0</v>
       </c>
-      <c r="AG7" s="160"/>
-      <c r="AH7" s="160"/>
-      <c r="AI7" s="160"/>
-      <c r="AJ7" s="161"/>
-      <c r="AK7" s="158"/>
-      <c r="AL7" s="157"/>
+      <c r="AG7" s="172"/>
+      <c r="AH7" s="172"/>
+      <c r="AI7" s="172"/>
+      <c r="AJ7" s="173"/>
+      <c r="AK7" s="239"/>
+      <c r="AL7" s="238"/>
     </row>
     <row r="8" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B8" s="13" t="s">
@@ -13535,7 +13538,7 @@
         <f>SUM(C8:W8)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="146"/>
+      <c r="Z8" s="236"/>
       <c r="AA8" s="15" t="s">
         <v>26</v>
       </c>
@@ -13543,7 +13546,7 @@
         <f>Y8*16</f>
         <v>0</v>
       </c>
-      <c r="AC8" s="149"/>
+      <c r="AC8" s="167"/>
       <c r="AD8" s="16">
         <f>X8</f>
         <v>0</v>
@@ -13554,8 +13557,8 @@
       <c r="AH8" s="27"/>
       <c r="AI8" s="27"/>
       <c r="AJ8" s="28"/>
-      <c r="AK8" s="158"/>
-      <c r="AL8" s="157"/>
+      <c r="AK8" s="239"/>
+      <c r="AL8" s="238"/>
       <c r="AM8" s="29"/>
       <c r="AN8" s="29"/>
     </row>
@@ -13661,8 +13664,8 @@
       <c r="AH9" s="35"/>
       <c r="AI9" s="35"/>
       <c r="AJ9" s="36"/>
-      <c r="AK9" s="158"/>
-      <c r="AL9" s="157"/>
+      <c r="AK9" s="239"/>
+      <c r="AL9" s="238"/>
       <c r="AM9" s="29"/>
       <c r="AN9" s="29"/>
     </row>
@@ -13747,11 +13750,11 @@
       <c r="AA10" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="AB10" s="162">
+      <c r="AB10" s="240">
         <f>SUM(Y10:Y13)</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="165">
+      <c r="AC10" s="227">
         <f>SUM(AB10,AB15)</f>
         <v>0</v>
       </c>
@@ -13767,8 +13770,8 @@
       <c r="AH10" s="169"/>
       <c r="AI10" s="169"/>
       <c r="AJ10" s="170"/>
-      <c r="AK10" s="158"/>
-      <c r="AL10" s="157"/>
+      <c r="AK10" s="239"/>
+      <c r="AL10" s="238"/>
       <c r="AM10" s="12"/>
       <c r="AN10" s="12"/>
     </row>
@@ -13856,20 +13859,20 @@
       <c r="AA11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="AB11" s="163"/>
-      <c r="AC11" s="166"/>
+      <c r="AB11" s="241"/>
+      <c r="AC11" s="243"/>
       <c r="AD11" s="16">
         <f t="shared" ref="AD11:AD13" si="1">X11</f>
         <v>0</v>
       </c>
       <c r="AE11" s="17"/>
       <c r="AF11" s="171"/>
-      <c r="AG11" s="160"/>
-      <c r="AH11" s="160"/>
-      <c r="AI11" s="160"/>
-      <c r="AJ11" s="161"/>
-      <c r="AK11" s="158"/>
-      <c r="AL11" s="157"/>
+      <c r="AG11" s="172"/>
+      <c r="AH11" s="172"/>
+      <c r="AI11" s="172"/>
+      <c r="AJ11" s="173"/>
+      <c r="AK11" s="239"/>
+      <c r="AL11" s="238"/>
     </row>
     <row r="12" spans="1:40" s="12" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B12" s="13" t="s">
@@ -13952,20 +13955,20 @@
       <c r="AA12" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="AB12" s="163"/>
-      <c r="AC12" s="166"/>
+      <c r="AB12" s="241"/>
+      <c r="AC12" s="243"/>
       <c r="AD12" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE12" s="17"/>
       <c r="AF12" s="171"/>
-      <c r="AG12" s="160"/>
-      <c r="AH12" s="160"/>
-      <c r="AI12" s="160"/>
-      <c r="AJ12" s="161"/>
-      <c r="AK12" s="158"/>
-      <c r="AL12" s="157"/>
+      <c r="AG12" s="172"/>
+      <c r="AH12" s="172"/>
+      <c r="AI12" s="172"/>
+      <c r="AJ12" s="173"/>
+      <c r="AK12" s="239"/>
+      <c r="AL12" s="238"/>
     </row>
     <row r="13" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B13" s="13" t="s">
@@ -14048,20 +14051,20 @@
       <c r="AA13" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="AB13" s="164"/>
-      <c r="AC13" s="166"/>
+      <c r="AB13" s="242"/>
+      <c r="AC13" s="243"/>
       <c r="AD13" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AE13" s="17"/>
       <c r="AF13" s="171"/>
-      <c r="AG13" s="160"/>
-      <c r="AH13" s="160"/>
-      <c r="AI13" s="160"/>
-      <c r="AJ13" s="161"/>
-      <c r="AK13" s="158"/>
-      <c r="AL13" s="157"/>
+      <c r="AG13" s="172"/>
+      <c r="AH13" s="172"/>
+      <c r="AI13" s="172"/>
+      <c r="AJ13" s="173"/>
+      <c r="AK13" s="239"/>
+      <c r="AL13" s="238"/>
     </row>
     <row r="14" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B14" s="13"/>
@@ -14154,16 +14157,16 @@
       <c r="Z14" s="41"/>
       <c r="AA14" s="42"/>
       <c r="AB14" s="13"/>
-      <c r="AC14" s="166"/>
+      <c r="AC14" s="243"/>
       <c r="AD14" s="33"/>
       <c r="AE14" s="17"/>
       <c r="AF14" s="171"/>
-      <c r="AG14" s="160"/>
-      <c r="AH14" s="160"/>
-      <c r="AI14" s="160"/>
-      <c r="AJ14" s="161"/>
-      <c r="AK14" s="158"/>
-      <c r="AL14" s="157"/>
+      <c r="AG14" s="172"/>
+      <c r="AH14" s="172"/>
+      <c r="AI14" s="172"/>
+      <c r="AJ14" s="173"/>
+      <c r="AK14" s="239"/>
+      <c r="AL14" s="238"/>
     </row>
     <row r="15" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B15" s="13" t="s">
@@ -14246,26 +14249,26 @@
       <c r="AA15" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AB15" s="162">
+      <c r="AB15" s="240">
         <f>SUM(Y15:Y18)</f>
         <v>0</v>
       </c>
-      <c r="AC15" s="166"/>
+      <c r="AC15" s="243"/>
       <c r="AD15" s="16">
         <f>X15</f>
         <v>0</v>
       </c>
       <c r="AE15" s="17"/>
-      <c r="AF15" s="159">
+      <c r="AF15" s="174">
         <f>SUM(AD10:AD20)-AD20</f>
         <v>0</v>
       </c>
-      <c r="AG15" s="160"/>
-      <c r="AH15" s="160"/>
-      <c r="AI15" s="160"/>
-      <c r="AJ15" s="161"/>
-      <c r="AK15" s="158"/>
-      <c r="AL15" s="157"/>
+      <c r="AG15" s="172"/>
+      <c r="AH15" s="172"/>
+      <c r="AI15" s="172"/>
+      <c r="AJ15" s="173"/>
+      <c r="AK15" s="239"/>
+      <c r="AL15" s="238"/>
     </row>
     <row r="16" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B16" s="13" t="s">
@@ -14348,8 +14351,8 @@
       <c r="AA16" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="AB16" s="163"/>
-      <c r="AC16" s="166"/>
+      <c r="AB16" s="241"/>
+      <c r="AC16" s="243"/>
       <c r="AD16" s="16">
         <f t="shared" ref="AD16:AD20" si="5">X16</f>
         <v>0</v>
@@ -14360,8 +14363,8 @@
       <c r="AH16" s="27"/>
       <c r="AI16" s="27"/>
       <c r="AJ16" s="28"/>
-      <c r="AK16" s="158"/>
-      <c r="AL16" s="157"/>
+      <c r="AK16" s="239"/>
+      <c r="AL16" s="238"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B17" s="13" t="s">
@@ -14444,8 +14447,8 @@
       <c r="AA17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="AB17" s="163"/>
-      <c r="AC17" s="166"/>
+      <c r="AB17" s="241"/>
+      <c r="AC17" s="243"/>
       <c r="AD17" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14456,8 +14459,8 @@
       <c r="AH17" s="27"/>
       <c r="AI17" s="27"/>
       <c r="AJ17" s="28"/>
-      <c r="AK17" s="158"/>
-      <c r="AL17" s="157"/>
+      <c r="AK17" s="239"/>
+      <c r="AL17" s="238"/>
     </row>
     <row r="18" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B18" s="13" t="s">
@@ -14540,8 +14543,8 @@
       <c r="AA18" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="AB18" s="163"/>
-      <c r="AC18" s="166"/>
+      <c r="AB18" s="241"/>
+      <c r="AC18" s="243"/>
       <c r="AD18" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14552,8 +14555,8 @@
       <c r="AH18" s="27"/>
       <c r="AI18" s="27"/>
       <c r="AJ18" s="28"/>
-      <c r="AK18" s="158"/>
-      <c r="AL18" s="157"/>
+      <c r="AK18" s="239"/>
+      <c r="AL18" s="238"/>
     </row>
     <row r="19" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B19" s="13" t="s">
@@ -14636,8 +14639,8 @@
       <c r="AA19" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AB19" s="163"/>
-      <c r="AC19" s="166"/>
+      <c r="AB19" s="241"/>
+      <c r="AC19" s="243"/>
       <c r="AD19" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14648,8 +14651,8 @@
       <c r="AH19" s="27"/>
       <c r="AI19" s="27"/>
       <c r="AJ19" s="28"/>
-      <c r="AK19" s="158"/>
-      <c r="AL19" s="157"/>
+      <c r="AK19" s="239"/>
+      <c r="AL19" s="238"/>
     </row>
     <row r="20" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B20" s="13" t="s">
@@ -14732,8 +14735,8 @@
       <c r="AA20" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AB20" s="164"/>
-      <c r="AC20" s="167"/>
+      <c r="AB20" s="242"/>
+      <c r="AC20" s="228"/>
       <c r="AD20" s="16">
         <f t="shared" si="5"/>
         <v>0</v>
@@ -14744,8 +14747,8 @@
       <c r="AH20" s="27"/>
       <c r="AI20" s="27"/>
       <c r="AJ20" s="28"/>
-      <c r="AK20" s="158"/>
-      <c r="AL20" s="157"/>
+      <c r="AK20" s="239"/>
+      <c r="AL20" s="238"/>
     </row>
     <row r="21" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B21" s="13"/>
@@ -14837,8 +14840,8 @@
       <c r="Y21" s="14"/>
       <c r="Z21" s="14"/>
       <c r="AA21" s="42"/>
-      <c r="AB21" s="187"/>
-      <c r="AC21" s="188"/>
+      <c r="AB21" s="194"/>
+      <c r="AC21" s="195"/>
       <c r="AD21" s="33"/>
       <c r="AE21" s="17"/>
       <c r="AF21" s="168" t="s">
@@ -14848,8 +14851,8 @@
       <c r="AH21" s="169"/>
       <c r="AI21" s="169"/>
       <c r="AJ21" s="170"/>
-      <c r="AK21" s="158"/>
-      <c r="AL21" s="157"/>
+      <c r="AK21" s="239"/>
+      <c r="AL21" s="238"/>
     </row>
     <row r="22" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B22" s="13" t="s">
@@ -14932,21 +14935,21 @@
       <c r="AA22" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AB22" s="189"/>
-      <c r="AC22" s="190"/>
+      <c r="AB22" s="229"/>
+      <c r="AC22" s="230"/>
       <c r="AD22" s="16">
         <f>X22</f>
         <v>0</v>
       </c>
       <c r="AE22" s="17"/>
-      <c r="AF22" s="191">
+      <c r="AF22" s="247">
         <f>SUM(AD22:AE22)</f>
         <v>0</v>
       </c>
-      <c r="AG22" s="192"/>
-      <c r="AH22" s="192"/>
-      <c r="AI22" s="192"/>
-      <c r="AJ22" s="193"/>
+      <c r="AG22" s="248"/>
+      <c r="AH22" s="248"/>
+      <c r="AI22" s="248"/>
+      <c r="AJ22" s="249"/>
       <c r="AK22" s="22"/>
       <c r="AL22" s="18"/>
     </row>
@@ -15040,8 +15043,8 @@
       <c r="Y23" s="14"/>
       <c r="Z23" s="14"/>
       <c r="AA23" s="42"/>
-      <c r="AB23" s="178"/>
-      <c r="AC23" s="179"/>
+      <c r="AB23" s="157"/>
+      <c r="AC23" s="158"/>
       <c r="AD23" s="16">
         <f t="shared" ref="AD23:AD39" si="8">X23</f>
         <v>0</v>
@@ -15139,27 +15142,27 @@
       <c r="AA24" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AB24" s="180">
+      <c r="AB24" s="179">
         <f>SUM(Y24:Y25)</f>
         <v>0</v>
       </c>
-      <c r="AC24" s="181"/>
+      <c r="AC24" s="180"/>
       <c r="AD24" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE24" s="17"/>
-      <c r="AF24" s="184" t="s">
+      <c r="AF24" s="183" t="s">
         <v>41</v>
       </c>
-      <c r="AG24" s="185"/>
-      <c r="AH24" s="185"/>
-      <c r="AI24" s="185"/>
-      <c r="AJ24" s="186"/>
-      <c r="AK24" s="172" t="s">
+      <c r="AG24" s="184"/>
+      <c r="AH24" s="184"/>
+      <c r="AI24" s="184"/>
+      <c r="AJ24" s="231"/>
+      <c r="AK24" s="244" t="s">
         <v>42</v>
       </c>
-      <c r="AL24" s="173"/>
+      <c r="AL24" s="245"/>
     </row>
     <row r="25" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A25" s="12">
@@ -15245,23 +15248,23 @@
       <c r="AA25" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="AB25" s="182"/>
-      <c r="AC25" s="183"/>
+      <c r="AB25" s="181"/>
+      <c r="AC25" s="182"/>
       <c r="AD25" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE25" s="17"/>
-      <c r="AF25" s="175">
+      <c r="AF25" s="205">
         <f>SUM(AD24:AD25)</f>
         <v>0</v>
       </c>
-      <c r="AG25" s="176"/>
-      <c r="AH25" s="176"/>
-      <c r="AI25" s="176"/>
-      <c r="AJ25" s="177"/>
-      <c r="AK25" s="172"/>
-      <c r="AL25" s="173"/>
+      <c r="AG25" s="232"/>
+      <c r="AH25" s="232"/>
+      <c r="AI25" s="232"/>
+      <c r="AJ25" s="233"/>
+      <c r="AK25" s="244"/>
+      <c r="AL25" s="245"/>
     </row>
     <row r="26" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B26" s="13"/>
@@ -15353,8 +15356,8 @@
       <c r="Y26" s="14"/>
       <c r="Z26" s="14"/>
       <c r="AA26" s="13"/>
-      <c r="AB26" s="178"/>
-      <c r="AC26" s="179"/>
+      <c r="AB26" s="157"/>
+      <c r="AC26" s="158"/>
       <c r="AD26" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15365,8 +15368,8 @@
       <c r="AH26" s="45"/>
       <c r="AI26" s="45"/>
       <c r="AJ26" s="46"/>
-      <c r="AK26" s="172"/>
-      <c r="AL26" s="173"/>
+      <c r="AK26" s="244"/>
+      <c r="AL26" s="245"/>
     </row>
     <row r="27" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A27" s="12">
@@ -15452,25 +15455,25 @@
       <c r="AA27" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="AB27" s="180">
+      <c r="AB27" s="179">
         <f>SUM(Y26:Y28)</f>
         <v>0</v>
       </c>
-      <c r="AC27" s="181"/>
+      <c r="AC27" s="180"/>
       <c r="AD27" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE27" s="17"/>
-      <c r="AF27" s="184" t="s">
+      <c r="AF27" s="183" t="s">
         <v>45</v>
       </c>
-      <c r="AG27" s="185"/>
-      <c r="AH27" s="185"/>
-      <c r="AI27" s="185"/>
-      <c r="AJ27" s="186"/>
-      <c r="AK27" s="172"/>
-      <c r="AL27" s="173"/>
+      <c r="AG27" s="184"/>
+      <c r="AH27" s="184"/>
+      <c r="AI27" s="184"/>
+      <c r="AJ27" s="231"/>
+      <c r="AK27" s="244"/>
+      <c r="AL27" s="245"/>
     </row>
     <row r="28" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A28" s="12">
@@ -15556,23 +15559,23 @@
       <c r="AA28" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="AB28" s="182"/>
-      <c r="AC28" s="183"/>
+      <c r="AB28" s="181"/>
+      <c r="AC28" s="182"/>
       <c r="AD28" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE28" s="17"/>
-      <c r="AF28" s="175">
+      <c r="AF28" s="205">
         <f>+AD27+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG28" s="176"/>
-      <c r="AH28" s="176"/>
-      <c r="AI28" s="176"/>
-      <c r="AJ28" s="177"/>
-      <c r="AK28" s="172"/>
-      <c r="AL28" s="173"/>
+      <c r="AG28" s="232"/>
+      <c r="AH28" s="232"/>
+      <c r="AI28" s="232"/>
+      <c r="AJ28" s="233"/>
+      <c r="AK28" s="244"/>
+      <c r="AL28" s="245"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B29" s="13"/>
@@ -15664,8 +15667,8 @@
       <c r="Y29" s="14"/>
       <c r="Z29" s="14"/>
       <c r="AA29" s="13"/>
-      <c r="AB29" s="178"/>
-      <c r="AC29" s="179"/>
+      <c r="AB29" s="157"/>
+      <c r="AC29" s="158"/>
       <c r="AD29" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15676,8 +15679,8 @@
       <c r="AH29" s="45"/>
       <c r="AI29" s="45"/>
       <c r="AJ29" s="45"/>
-      <c r="AK29" s="172"/>
-      <c r="AL29" s="173"/>
+      <c r="AK29" s="244"/>
+      <c r="AL29" s="245"/>
     </row>
     <row r="30" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A30" s="12">
@@ -15763,25 +15766,25 @@
       <c r="AA30" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="AB30" s="180">
+      <c r="AB30" s="179">
         <f>SUM(Y29:Y31)</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="181"/>
+      <c r="AC30" s="180"/>
       <c r="AD30" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE30" s="17"/>
-      <c r="AF30" s="184" t="s">
+      <c r="AF30" s="183" t="s">
         <v>48</v>
       </c>
-      <c r="AG30" s="185"/>
-      <c r="AH30" s="185"/>
-      <c r="AI30" s="185"/>
-      <c r="AJ30" s="185"/>
-      <c r="AK30" s="172"/>
-      <c r="AL30" s="173"/>
+      <c r="AG30" s="184"/>
+      <c r="AH30" s="184"/>
+      <c r="AI30" s="184"/>
+      <c r="AJ30" s="184"/>
+      <c r="AK30" s="244"/>
+      <c r="AL30" s="245"/>
     </row>
     <row r="31" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A31" s="12">
@@ -15867,23 +15870,23 @@
       <c r="AA31" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="AB31" s="182"/>
-      <c r="AC31" s="183"/>
+      <c r="AB31" s="181"/>
+      <c r="AC31" s="182"/>
       <c r="AD31" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE31" s="17"/>
-      <c r="AF31" s="175">
+      <c r="AF31" s="205">
         <f>+AD30+AD31</f>
         <v>0</v>
       </c>
-      <c r="AG31" s="176"/>
-      <c r="AH31" s="176"/>
-      <c r="AI31" s="176"/>
-      <c r="AJ31" s="177"/>
-      <c r="AK31" s="172"/>
-      <c r="AL31" s="173"/>
+      <c r="AG31" s="232"/>
+      <c r="AH31" s="232"/>
+      <c r="AI31" s="232"/>
+      <c r="AJ31" s="233"/>
+      <c r="AK31" s="244"/>
+      <c r="AL31" s="245"/>
     </row>
     <row r="32" spans="1:38" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B32" s="13"/>
@@ -15975,8 +15978,8 @@
       <c r="Y32" s="14"/>
       <c r="Z32" s="14"/>
       <c r="AA32" s="13"/>
-      <c r="AB32" s="178"/>
-      <c r="AC32" s="179"/>
+      <c r="AB32" s="157"/>
+      <c r="AC32" s="158"/>
       <c r="AD32" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -15987,8 +15990,8 @@
       <c r="AH32" s="45"/>
       <c r="AI32" s="45"/>
       <c r="AJ32" s="45"/>
-      <c r="AK32" s="172"/>
-      <c r="AL32" s="173"/>
+      <c r="AK32" s="244"/>
+      <c r="AL32" s="245"/>
     </row>
     <row r="33" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A33" s="12">
@@ -16074,25 +16077,25 @@
       <c r="AA33" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AB33" s="180">
+      <c r="AB33" s="179">
         <f>SUM(Y32:Y34)</f>
         <v>0</v>
       </c>
-      <c r="AC33" s="181"/>
+      <c r="AC33" s="180"/>
       <c r="AD33" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE33" s="17"/>
-      <c r="AF33" s="184" t="s">
+      <c r="AF33" s="183" t="s">
         <v>51</v>
       </c>
-      <c r="AG33" s="185"/>
-      <c r="AH33" s="185"/>
-      <c r="AI33" s="185"/>
-      <c r="AJ33" s="185"/>
-      <c r="AK33" s="172"/>
-      <c r="AL33" s="173"/>
+      <c r="AG33" s="184"/>
+      <c r="AH33" s="184"/>
+      <c r="AI33" s="184"/>
+      <c r="AJ33" s="184"/>
+      <c r="AK33" s="244"/>
+      <c r="AL33" s="245"/>
     </row>
     <row r="34" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A34" s="12">
@@ -16178,23 +16181,23 @@
       <c r="AA34" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AB34" s="182"/>
-      <c r="AC34" s="183"/>
+      <c r="AB34" s="181"/>
+      <c r="AC34" s="182"/>
       <c r="AD34" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE34" s="17"/>
-      <c r="AF34" s="175">
+      <c r="AF34" s="205">
         <f>+AD33+AD34</f>
         <v>0</v>
       </c>
-      <c r="AG34" s="176"/>
-      <c r="AH34" s="176"/>
-      <c r="AI34" s="176"/>
-      <c r="AJ34" s="177"/>
-      <c r="AK34" s="172"/>
-      <c r="AL34" s="173"/>
+      <c r="AG34" s="232"/>
+      <c r="AH34" s="232"/>
+      <c r="AI34" s="232"/>
+      <c r="AJ34" s="233"/>
+      <c r="AK34" s="244"/>
+      <c r="AL34" s="245"/>
     </row>
     <row r="35" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B35" s="13"/>
@@ -16286,8 +16289,8 @@
       <c r="Y35" s="14"/>
       <c r="Z35" s="14"/>
       <c r="AA35" s="13"/>
-      <c r="AB35" s="178"/>
-      <c r="AC35" s="179"/>
+      <c r="AB35" s="157"/>
+      <c r="AC35" s="158"/>
       <c r="AD35" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16298,8 +16301,8 @@
       <c r="AH35" s="45"/>
       <c r="AI35" s="45"/>
       <c r="AJ35" s="45"/>
-      <c r="AK35" s="172"/>
-      <c r="AL35" s="173"/>
+      <c r="AK35" s="244"/>
+      <c r="AL35" s="245"/>
     </row>
     <row r="36" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B36" s="13" t="s">
@@ -16382,25 +16385,25 @@
       <c r="AA36" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AB36" s="180">
+      <c r="AB36" s="179">
         <f>SUM(Y35:Y37)</f>
         <v>0</v>
       </c>
-      <c r="AC36" s="181"/>
+      <c r="AC36" s="180"/>
       <c r="AD36" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE36" s="17"/>
-      <c r="AF36" s="184" t="s">
+      <c r="AF36" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="AG36" s="185"/>
-      <c r="AH36" s="185"/>
-      <c r="AI36" s="185"/>
-      <c r="AJ36" s="185"/>
-      <c r="AK36" s="172"/>
-      <c r="AL36" s="173"/>
+      <c r="AG36" s="184"/>
+      <c r="AH36" s="184"/>
+      <c r="AI36" s="184"/>
+      <c r="AJ36" s="184"/>
+      <c r="AK36" s="244"/>
+      <c r="AL36" s="245"/>
     </row>
     <row r="37" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B37" s="13" t="s">
@@ -16483,23 +16486,23 @@
       <c r="AA37" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="AB37" s="182"/>
-      <c r="AC37" s="183"/>
+      <c r="AB37" s="181"/>
+      <c r="AC37" s="182"/>
       <c r="AD37" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="AE37" s="17"/>
-      <c r="AF37" s="175">
+      <c r="AF37" s="205">
         <f>+AD36+AD37</f>
         <v>0</v>
       </c>
-      <c r="AG37" s="176"/>
-      <c r="AH37" s="176"/>
-      <c r="AI37" s="176"/>
-      <c r="AJ37" s="177"/>
-      <c r="AK37" s="172"/>
-      <c r="AL37" s="173"/>
+      <c r="AG37" s="232"/>
+      <c r="AH37" s="232"/>
+      <c r="AI37" s="232"/>
+      <c r="AJ37" s="233"/>
+      <c r="AK37" s="244"/>
+      <c r="AL37" s="245"/>
       <c r="AM37" s="47"/>
       <c r="AN37" s="47"/>
     </row>
@@ -16593,8 +16596,8 @@
       <c r="Y38" s="14"/>
       <c r="Z38" s="14"/>
       <c r="AA38" s="13"/>
-      <c r="AB38" s="178"/>
-      <c r="AC38" s="179"/>
+      <c r="AB38" s="157"/>
+      <c r="AC38" s="158"/>
       <c r="AD38" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16605,8 +16608,8 @@
       <c r="AH38" s="45"/>
       <c r="AI38" s="45"/>
       <c r="AJ38" s="45"/>
-      <c r="AK38" s="172"/>
-      <c r="AL38" s="173"/>
+      <c r="AK38" s="244"/>
+      <c r="AL38" s="245"/>
       <c r="AM38" s="47"/>
       <c r="AN38" s="47"/>
     </row>
@@ -16691,8 +16694,8 @@
       <c r="AA39" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="AB39" s="178"/>
-      <c r="AC39" s="179"/>
+      <c r="AB39" s="157"/>
+      <c r="AC39" s="158"/>
       <c r="AD39" s="16">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -16703,8 +16706,8 @@
       <c r="AH39" s="45"/>
       <c r="AI39" s="45"/>
       <c r="AJ39" s="45"/>
-      <c r="AK39" s="172"/>
-      <c r="AL39" s="173"/>
+      <c r="AK39" s="244"/>
+      <c r="AL39" s="245"/>
       <c r="AM39" s="47"/>
       <c r="AN39" s="47"/>
     </row>
@@ -16712,46 +16715,46 @@
       <c r="B40" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="134" t="s">
+      <c r="C40" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D40" s="135"/>
-      <c r="E40" s="134" t="s">
+      <c r="D40" s="144"/>
+      <c r="E40" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F40" s="135"/>
-      <c r="G40" s="134" t="s">
+      <c r="F40" s="144"/>
+      <c r="G40" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H40" s="135"/>
-      <c r="I40" s="134" t="s">
+      <c r="H40" s="144"/>
+      <c r="I40" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J40" s="135"/>
-      <c r="K40" s="134" t="s">
+      <c r="J40" s="144"/>
+      <c r="K40" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L40" s="135"/>
-      <c r="M40" s="134" t="s">
+      <c r="L40" s="144"/>
+      <c r="M40" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N40" s="135"/>
-      <c r="O40" s="134" t="s">
+      <c r="N40" s="144"/>
+      <c r="O40" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P40" s="135"/>
-      <c r="Q40" s="134" t="s">
+      <c r="P40" s="144"/>
+      <c r="Q40" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R40" s="135"/>
-      <c r="S40" s="134" t="s">
+      <c r="R40" s="144"/>
+      <c r="S40" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T40" s="135"/>
-      <c r="U40" s="134" t="s">
+      <c r="T40" s="144"/>
+      <c r="U40" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V40" s="135"/>
+      <c r="V40" s="144"/>
       <c r="W40" s="5" t="s">
         <v>11</v>
       </c>
@@ -16765,8 +16768,8 @@
       <c r="AA40" s="48" t="s">
         <v>57</v>
       </c>
-      <c r="AB40" s="140"/>
-      <c r="AC40" s="141"/>
+      <c r="AB40" s="147"/>
+      <c r="AC40" s="148"/>
       <c r="AD40" s="6">
         <v>0</v>
       </c>
@@ -16776,8 +16779,8 @@
       <c r="AH40" s="2"/>
       <c r="AI40" s="2"/>
       <c r="AJ40" s="2"/>
-      <c r="AK40" s="172"/>
-      <c r="AL40" s="173"/>
+      <c r="AK40" s="244"/>
+      <c r="AL40" s="245"/>
       <c r="AM40" s="12"/>
       <c r="AN40" s="12"/>
     </row>
@@ -16875,8 +16878,8 @@
       <c r="AH41" s="52"/>
       <c r="AI41" s="52"/>
       <c r="AJ41" s="52"/>
-      <c r="AK41" s="172"/>
-      <c r="AL41" s="173"/>
+      <c r="AK41" s="244"/>
+      <c r="AL41" s="245"/>
     </row>
     <row r="42" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A42" s="12"/>
@@ -16960,25 +16963,25 @@
       <c r="AA42" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="AB42" s="194">
+      <c r="AB42" s="219">
         <f>SUM(Y40:Y54)</f>
         <v>0</v>
       </c>
-      <c r="AC42" s="195"/>
+      <c r="AC42" s="220"/>
       <c r="AD42" s="16">
         <f t="shared" ref="AD42:AD62" si="16">X42</f>
         <v>0</v>
       </c>
       <c r="AE42" s="17"/>
-      <c r="AF42" s="184" t="s">
+      <c r="AF42" s="183" t="s">
         <v>60</v>
       </c>
-      <c r="AG42" s="185"/>
-      <c r="AH42" s="185"/>
-      <c r="AI42" s="185"/>
-      <c r="AJ42" s="186"/>
-      <c r="AK42" s="174"/>
-      <c r="AL42" s="173"/>
+      <c r="AG42" s="184"/>
+      <c r="AH42" s="184"/>
+      <c r="AI42" s="184"/>
+      <c r="AJ42" s="231"/>
+      <c r="AK42" s="246"/>
+      <c r="AL42" s="245"/>
     </row>
     <row r="43" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A43" s="12"/>
@@ -17062,8 +17065,8 @@
       <c r="AA43" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="AB43" s="194"/>
-      <c r="AC43" s="195"/>
+      <c r="AB43" s="219"/>
+      <c r="AC43" s="220"/>
       <c r="AD43" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17074,8 +17077,8 @@
       <c r="AH43" s="54"/>
       <c r="AI43" s="54"/>
       <c r="AJ43" s="55"/>
-      <c r="AK43" s="174"/>
-      <c r="AL43" s="173"/>
+      <c r="AK43" s="246"/>
+      <c r="AL43" s="245"/>
     </row>
     <row r="44" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A44" s="12"/>
@@ -17159,8 +17162,8 @@
       <c r="AA44" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="AB44" s="194"/>
-      <c r="AC44" s="195"/>
+      <c r="AB44" s="219"/>
+      <c r="AC44" s="220"/>
       <c r="AD44" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17171,8 +17174,8 @@
       <c r="AH44" s="54"/>
       <c r="AI44" s="54"/>
       <c r="AJ44" s="55"/>
-      <c r="AK44" s="174"/>
-      <c r="AL44" s="173"/>
+      <c r="AK44" s="246"/>
+      <c r="AL44" s="245"/>
     </row>
     <row r="45" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A45" s="12"/>
@@ -17256,8 +17259,8 @@
       <c r="AA45" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="AB45" s="194"/>
-      <c r="AC45" s="195"/>
+      <c r="AB45" s="219"/>
+      <c r="AC45" s="220"/>
       <c r="AD45" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17268,8 +17271,8 @@
       <c r="AH45" s="54"/>
       <c r="AI45" s="54"/>
       <c r="AJ45" s="55"/>
-      <c r="AK45" s="174"/>
-      <c r="AL45" s="173"/>
+      <c r="AK45" s="246"/>
+      <c r="AL45" s="245"/>
     </row>
     <row r="46" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A46" s="12"/>
@@ -17353,8 +17356,8 @@
       <c r="AA46" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="AB46" s="194"/>
-      <c r="AC46" s="195"/>
+      <c r="AB46" s="219"/>
+      <c r="AC46" s="220"/>
       <c r="AD46" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17365,8 +17368,8 @@
       <c r="AH46" s="54"/>
       <c r="AI46" s="54"/>
       <c r="AJ46" s="55"/>
-      <c r="AK46" s="174"/>
-      <c r="AL46" s="173"/>
+      <c r="AK46" s="246"/>
+      <c r="AL46" s="245"/>
     </row>
     <row r="47" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A47" s="12"/>
@@ -17450,23 +17453,23 @@
       <c r="AA47" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="AB47" s="194"/>
-      <c r="AC47" s="195"/>
+      <c r="AB47" s="219"/>
+      <c r="AC47" s="220"/>
       <c r="AD47" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE47" s="17"/>
-      <c r="AF47" s="196">
+      <c r="AF47" s="224">
         <f>SUM(AD41:AD54)</f>
         <v>0</v>
       </c>
-      <c r="AG47" s="197"/>
-      <c r="AH47" s="197"/>
-      <c r="AI47" s="197"/>
-      <c r="AJ47" s="198"/>
-      <c r="AK47" s="174"/>
-      <c r="AL47" s="173"/>
+      <c r="AG47" s="222"/>
+      <c r="AH47" s="222"/>
+      <c r="AI47" s="222"/>
+      <c r="AJ47" s="223"/>
+      <c r="AK47" s="246"/>
+      <c r="AL47" s="245"/>
     </row>
     <row r="48" spans="1:40" s="47" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A48" s="12"/>
@@ -17550,8 +17553,8 @@
       <c r="AA48" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="AB48" s="194"/>
-      <c r="AC48" s="195"/>
+      <c r="AB48" s="219"/>
+      <c r="AC48" s="220"/>
       <c r="AD48" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17562,8 +17565,8 @@
       <c r="AH48" s="54"/>
       <c r="AI48" s="54"/>
       <c r="AJ48" s="55"/>
-      <c r="AK48" s="174"/>
-      <c r="AL48" s="173"/>
+      <c r="AK48" s="246"/>
+      <c r="AL48" s="245"/>
     </row>
     <row r="49" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A49" s="12"/>
@@ -17647,8 +17650,8 @@
       <c r="AA49" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="AB49" s="194"/>
-      <c r="AC49" s="195"/>
+      <c r="AB49" s="219"/>
+      <c r="AC49" s="220"/>
       <c r="AD49" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17659,8 +17662,8 @@
       <c r="AH49" s="54"/>
       <c r="AI49" s="54"/>
       <c r="AJ49" s="55"/>
-      <c r="AK49" s="174"/>
-      <c r="AL49" s="173"/>
+      <c r="AK49" s="246"/>
+      <c r="AL49" s="245"/>
     </row>
     <row r="50" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A50" s="12"/>
@@ -17744,8 +17747,8 @@
       <c r="AA50" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="AB50" s="194"/>
-      <c r="AC50" s="195"/>
+      <c r="AB50" s="219"/>
+      <c r="AC50" s="220"/>
       <c r="AD50" s="16">
         <f>X50</f>
         <v>0</v>
@@ -17756,8 +17759,8 @@
       <c r="AH50" s="54"/>
       <c r="AI50" s="54"/>
       <c r="AJ50" s="55"/>
-      <c r="AK50" s="174"/>
-      <c r="AL50" s="173"/>
+      <c r="AK50" s="246"/>
+      <c r="AL50" s="245"/>
     </row>
     <row r="51" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A51" s="12"/>
@@ -17841,8 +17844,8 @@
       <c r="AA51" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="AB51" s="194"/>
-      <c r="AC51" s="195"/>
+      <c r="AB51" s="219"/>
+      <c r="AC51" s="220"/>
       <c r="AD51" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17853,8 +17856,8 @@
       <c r="AH51" s="54"/>
       <c r="AI51" s="54"/>
       <c r="AJ51" s="55"/>
-      <c r="AK51" s="174"/>
-      <c r="AL51" s="173"/>
+      <c r="AK51" s="246"/>
+      <c r="AL51" s="245"/>
     </row>
     <row r="52" spans="1:40" s="47" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="A52" s="12"/>
@@ -17938,8 +17941,8 @@
       <c r="AA52" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="AB52" s="194"/>
-      <c r="AC52" s="195"/>
+      <c r="AB52" s="219"/>
+      <c r="AC52" s="220"/>
       <c r="AD52" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -17950,8 +17953,8 @@
       <c r="AH52" s="54"/>
       <c r="AI52" s="54"/>
       <c r="AJ52" s="55"/>
-      <c r="AK52" s="174"/>
-      <c r="AL52" s="173"/>
+      <c r="AK52" s="246"/>
+      <c r="AL52" s="245"/>
     </row>
     <row r="53" spans="1:40" s="47" customFormat="1" ht="146.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A53" s="12"/>
@@ -18047,8 +18050,8 @@
       <c r="AH53" s="54"/>
       <c r="AI53" s="54"/>
       <c r="AJ53" s="55"/>
-      <c r="AK53" s="174"/>
-      <c r="AL53" s="173"/>
+      <c r="AK53" s="246"/>
+      <c r="AL53" s="245"/>
     </row>
     <row r="54" spans="1:40" s="47" customFormat="1" ht="108.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A54" s="12"/>
@@ -18144,8 +18147,8 @@
       <c r="AH54" s="62"/>
       <c r="AI54" s="62"/>
       <c r="AJ54" s="63"/>
-      <c r="AK54" s="174"/>
-      <c r="AL54" s="173"/>
+      <c r="AK54" s="246"/>
+      <c r="AL54" s="245"/>
     </row>
     <row r="55" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A55" s="12"/>
@@ -18240,8 +18243,8 @@
       <c r="Y55" s="14"/>
       <c r="Z55" s="14"/>
       <c r="AA55" s="13"/>
-      <c r="AB55" s="189"/>
-      <c r="AC55" s="190"/>
+      <c r="AB55" s="229"/>
+      <c r="AC55" s="230"/>
       <c r="AD55" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
@@ -18252,8 +18255,8 @@
       <c r="AH55" s="54"/>
       <c r="AI55" s="54"/>
       <c r="AJ55" s="54"/>
-      <c r="AK55" s="172"/>
-      <c r="AL55" s="173"/>
+      <c r="AK55" s="244"/>
+      <c r="AL55" s="245"/>
     </row>
     <row r="56" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A56" s="12"/>
@@ -18349,8 +18352,8 @@
       <c r="AH56" s="54"/>
       <c r="AI56" s="54"/>
       <c r="AJ56" s="54"/>
-      <c r="AK56" s="172"/>
-      <c r="AL56" s="173"/>
+      <c r="AK56" s="244"/>
+      <c r="AL56" s="245"/>
     </row>
     <row r="57" spans="1:40" s="47" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A57" s="12"/>
@@ -18446,8 +18449,8 @@
       <c r="AH57" s="54"/>
       <c r="AI57" s="54"/>
       <c r="AJ57" s="54"/>
-      <c r="AK57" s="172"/>
-      <c r="AL57" s="173"/>
+      <c r="AK57" s="244"/>
+      <c r="AL57" s="245"/>
     </row>
     <row r="58" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B58" s="13" t="s">
@@ -18530,8 +18533,8 @@
       <c r="AA58" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="AB58" s="178"/>
-      <c r="AC58" s="179"/>
+      <c r="AB58" s="157"/>
+      <c r="AC58" s="158"/>
       <c r="AD58" s="16">
         <f>X58</f>
         <v>0</v>
@@ -18542,8 +18545,8 @@
       <c r="AH58" s="2"/>
       <c r="AI58" s="2"/>
       <c r="AJ58" s="2"/>
-      <c r="AK58" s="172"/>
-      <c r="AL58" s="173"/>
+      <c r="AK58" s="244"/>
+      <c r="AL58" s="245"/>
       <c r="AM58" s="4"/>
       <c r="AN58" s="4"/>
     </row>
@@ -18616,8 +18619,8 @@
       <c r="AH59" s="2"/>
       <c r="AI59" s="2"/>
       <c r="AJ59" s="2"/>
-      <c r="AK59" s="172"/>
-      <c r="AL59" s="173"/>
+      <c r="AK59" s="244"/>
+      <c r="AL59" s="245"/>
       <c r="AM59" s="67"/>
       <c r="AN59" s="67"/>
     </row>
@@ -18706,7 +18709,7 @@
         <f>Y60*4</f>
         <v>0</v>
       </c>
-      <c r="AC60" s="165">
+      <c r="AC60" s="227">
         <f>SUM(C62:W62)</f>
         <v>0</v>
       </c>
@@ -18717,8 +18720,8 @@
       <c r="AE60" s="17"/>
       <c r="AF60" s="69"/>
       <c r="AG60" s="69"/>
-      <c r="AK60" s="172"/>
-      <c r="AL60" s="173"/>
+      <c r="AK60" s="244"/>
+      <c r="AL60" s="245"/>
     </row>
     <row r="61" spans="1:40" ht="108.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B61" s="15" t="s">
@@ -18805,14 +18808,14 @@
         <f>Y61*4</f>
         <v>0</v>
       </c>
-      <c r="AC61" s="167"/>
+      <c r="AC61" s="228"/>
       <c r="AD61" s="16">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE61" s="17"/>
-      <c r="AK61" s="172"/>
-      <c r="AL61" s="173"/>
+      <c r="AK61" s="244"/>
+      <c r="AL61" s="245"/>
     </row>
     <row r="62" spans="1:40" ht="110.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B62" s="15"/>
@@ -18904,75 +18907,75 @@
       <c r="Y62" s="14"/>
       <c r="Z62" s="14"/>
       <c r="AA62" s="68"/>
-      <c r="AB62" s="199"/>
-      <c r="AC62" s="200"/>
+      <c r="AB62" s="151"/>
+      <c r="AC62" s="152"/>
       <c r="AD62" s="33">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AE62" s="17"/>
-      <c r="AK62" s="172"/>
-      <c r="AL62" s="173"/>
+      <c r="AK62" s="244"/>
+      <c r="AL62" s="245"/>
     </row>
     <row r="63" spans="1:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B63" s="136" t="s">
+      <c r="B63" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="C63" s="134" t="s">
+      <c r="C63" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D63" s="135"/>
-      <c r="E63" s="134" t="s">
+      <c r="D63" s="144"/>
+      <c r="E63" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F63" s="135"/>
-      <c r="G63" s="134" t="s">
+      <c r="F63" s="144"/>
+      <c r="G63" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H63" s="135"/>
-      <c r="I63" s="134" t="s">
+      <c r="H63" s="144"/>
+      <c r="I63" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J63" s="135"/>
-      <c r="K63" s="134" t="s">
+      <c r="J63" s="144"/>
+      <c r="K63" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L63" s="135"/>
-      <c r="M63" s="134" t="s">
+      <c r="L63" s="144"/>
+      <c r="M63" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N63" s="135"/>
-      <c r="O63" s="134" t="s">
+      <c r="N63" s="144"/>
+      <c r="O63" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P63" s="135"/>
-      <c r="Q63" s="134" t="s">
+      <c r="P63" s="144"/>
+      <c r="Q63" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R63" s="135"/>
-      <c r="S63" s="134" t="s">
+      <c r="R63" s="144"/>
+      <c r="S63" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T63" s="135"/>
-      <c r="U63" s="134" t="s">
+      <c r="T63" s="144"/>
+      <c r="U63" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V63" s="135"/>
-      <c r="W63" s="136" t="s">
+      <c r="V63" s="144"/>
+      <c r="W63" s="175" t="s">
         <v>11</v>
       </c>
       <c r="X63" s="110"/>
-      <c r="Y63" s="136" t="s">
+      <c r="Y63" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="Z63" s="136" t="s">
+      <c r="Z63" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="AA63" s="136" t="s">
+      <c r="AA63" s="175" t="s">
         <v>76</v>
       </c>
-      <c r="AB63" s="140"/>
-      <c r="AC63" s="141"/>
+      <c r="AB63" s="147"/>
+      <c r="AC63" s="148"/>
       <c r="AD63" s="6" t="s">
         <v>15</v>
       </c>
@@ -18981,7 +18984,7 @@
       <c r="AL63" s="71"/>
     </row>
     <row r="64" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B64" s="137"/>
+      <c r="B64" s="176"/>
       <c r="C64" s="9" t="s">
         <v>16</v>
       </c>
@@ -19042,11 +19045,11 @@
       <c r="V64" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="W64" s="137"/>
+      <c r="W64" s="176"/>
       <c r="X64" s="111"/>
-      <c r="Y64" s="137"/>
-      <c r="Z64" s="137"/>
-      <c r="AA64" s="137"/>
+      <c r="Y64" s="176"/>
+      <c r="Z64" s="176"/>
+      <c r="AA64" s="176"/>
       <c r="AB64" s="10"/>
       <c r="AC64" s="11"/>
       <c r="AD64" s="6"/>
@@ -19140,11 +19143,11 @@
       <c r="AA65" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="AB65" s="180">
+      <c r="AB65" s="179">
         <f>SUM(Y65:Y71)</f>
         <v>0</v>
       </c>
-      <c r="AC65" s="181"/>
+      <c r="AC65" s="180"/>
       <c r="AD65" s="16">
         <f>X65</f>
         <v>0</v>
@@ -19239,20 +19242,20 @@
       <c r="AA66" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="AB66" s="194"/>
-      <c r="AC66" s="195"/>
+      <c r="AB66" s="219"/>
+      <c r="AC66" s="220"/>
       <c r="AD66" s="16">
         <f t="shared" ref="AD66:AD71" si="21">X66</f>
         <v>0</v>
       </c>
       <c r="AE66" s="17"/>
-      <c r="AF66" s="201" t="s">
+      <c r="AF66" s="221" t="s">
         <v>76</v>
       </c>
-      <c r="AG66" s="197"/>
-      <c r="AH66" s="197"/>
-      <c r="AI66" s="197"/>
-      <c r="AJ66" s="198"/>
+      <c r="AG66" s="222"/>
+      <c r="AH66" s="222"/>
+      <c r="AI66" s="222"/>
+      <c r="AJ66" s="223"/>
       <c r="AK66" s="70"/>
       <c r="AL66" s="71"/>
     </row>
@@ -19337,21 +19340,21 @@
       <c r="AA67" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="AB67" s="194"/>
-      <c r="AC67" s="195"/>
+      <c r="AB67" s="219"/>
+      <c r="AC67" s="220"/>
       <c r="AD67" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AE67" s="17"/>
-      <c r="AF67" s="196">
+      <c r="AF67" s="224">
         <f>SUM(AD65:AD71)</f>
         <v>0</v>
       </c>
-      <c r="AG67" s="202"/>
-      <c r="AH67" s="202"/>
-      <c r="AI67" s="202"/>
-      <c r="AJ67" s="203"/>
+      <c r="AG67" s="225"/>
+      <c r="AH67" s="225"/>
+      <c r="AI67" s="225"/>
+      <c r="AJ67" s="226"/>
       <c r="AK67" s="70"/>
       <c r="AL67" s="71"/>
     </row>
@@ -19436,8 +19439,8 @@
       <c r="AA68" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="AB68" s="194"/>
-      <c r="AC68" s="195"/>
+      <c r="AB68" s="219"/>
+      <c r="AC68" s="220"/>
       <c r="AD68" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19532,8 +19535,8 @@
       <c r="AA69" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="AB69" s="194"/>
-      <c r="AC69" s="195"/>
+      <c r="AB69" s="219"/>
+      <c r="AC69" s="220"/>
       <c r="AD69" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19628,8 +19631,8 @@
       <c r="AA70" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="AB70" s="182"/>
-      <c r="AC70" s="183"/>
+      <c r="AB70" s="181"/>
+      <c r="AC70" s="182"/>
       <c r="AD70" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19724,8 +19727,8 @@
       <c r="AA71" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="AB71" s="178"/>
-      <c r="AC71" s="179"/>
+      <c r="AB71" s="157"/>
+      <c r="AC71" s="158"/>
       <c r="AD71" s="16">
         <f t="shared" si="21"/>
         <v>0</v>
@@ -19829,8 +19832,8 @@
       <c r="Y72" s="14"/>
       <c r="Z72" s="14"/>
       <c r="AA72" s="13"/>
-      <c r="AB72" s="178"/>
-      <c r="AC72" s="179"/>
+      <c r="AB72" s="157"/>
+      <c r="AC72" s="158"/>
       <c r="AD72" s="16">
         <v>0</v>
       </c>
@@ -19847,46 +19850,46 @@
       <c r="B73" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="C73" s="134" t="s">
+      <c r="C73" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D73" s="135"/>
-      <c r="E73" s="134" t="s">
+      <c r="D73" s="144"/>
+      <c r="E73" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F73" s="135"/>
-      <c r="G73" s="134" t="s">
+      <c r="F73" s="144"/>
+      <c r="G73" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H73" s="135"/>
-      <c r="I73" s="134" t="s">
+      <c r="H73" s="144"/>
+      <c r="I73" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J73" s="135"/>
-      <c r="K73" s="134" t="s">
+      <c r="J73" s="144"/>
+      <c r="K73" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L73" s="135"/>
-      <c r="M73" s="134" t="s">
+      <c r="L73" s="144"/>
+      <c r="M73" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N73" s="135"/>
-      <c r="O73" s="134" t="s">
+      <c r="N73" s="144"/>
+      <c r="O73" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P73" s="135"/>
-      <c r="Q73" s="134" t="s">
+      <c r="P73" s="144"/>
+      <c r="Q73" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R73" s="135"/>
-      <c r="S73" s="134" t="s">
+      <c r="R73" s="144"/>
+      <c r="S73" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T73" s="135"/>
-      <c r="U73" s="134" t="s">
+      <c r="T73" s="144"/>
+      <c r="U73" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V73" s="135"/>
+      <c r="V73" s="144"/>
       <c r="W73" s="9" t="s">
         <v>11</v>
       </c>
@@ -19900,8 +19903,8 @@
       <c r="AA73" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="AB73" s="140"/>
-      <c r="AC73" s="141"/>
+      <c r="AB73" s="147"/>
+      <c r="AC73" s="148"/>
       <c r="AD73" s="6" t="s">
         <v>15</v>
       </c>
@@ -19997,23 +20000,23 @@
       <c r="AA74" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="AB74" s="180">
+      <c r="AB74" s="179">
         <f>SUM(Y74:Y75)</f>
         <v>0</v>
       </c>
-      <c r="AC74" s="181"/>
+      <c r="AC74" s="180"/>
       <c r="AD74" s="16">
         <f>X74</f>
         <v>0</v>
       </c>
       <c r="AE74" s="17"/>
-      <c r="AF74" s="204" t="s">
+      <c r="AF74" s="217" t="s">
         <v>85</v>
       </c>
-      <c r="AG74" s="205"/>
-      <c r="AH74" s="205"/>
-      <c r="AI74" s="205"/>
-      <c r="AJ74" s="205"/>
+      <c r="AG74" s="218"/>
+      <c r="AH74" s="218"/>
+      <c r="AI74" s="218"/>
+      <c r="AJ74" s="218"/>
       <c r="AK74" s="209">
         <f>SUM(AD74:AD84)</f>
         <v>0</v>
@@ -20103,14 +20106,14 @@
       <c r="AA75" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="AB75" s="182"/>
-      <c r="AC75" s="183"/>
+      <c r="AB75" s="181"/>
+      <c r="AC75" s="182"/>
       <c r="AD75" s="16">
         <f t="shared" ref="AD75:AD89" si="23">X75</f>
         <v>0</v>
       </c>
       <c r="AE75" s="75"/>
-      <c r="AF75" s="175">
+      <c r="AF75" s="205">
         <f>+AD74+AD75</f>
         <v>0</v>
       </c>
@@ -20313,23 +20316,23 @@
       <c r="AA77" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="AB77" s="180">
+      <c r="AB77" s="179">
         <f>SUM(Y77:Y78)</f>
         <v>0</v>
       </c>
-      <c r="AC77" s="181"/>
+      <c r="AC77" s="180"/>
       <c r="AD77" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE77" s="17"/>
-      <c r="AF77" s="184" t="s">
+      <c r="AF77" s="183" t="s">
         <v>88</v>
       </c>
-      <c r="AG77" s="185"/>
-      <c r="AH77" s="185"/>
-      <c r="AI77" s="185"/>
-      <c r="AJ77" s="185"/>
+      <c r="AG77" s="184"/>
+      <c r="AH77" s="184"/>
+      <c r="AI77" s="184"/>
+      <c r="AJ77" s="184"/>
       <c r="AK77" s="211"/>
       <c r="AL77" s="212"/>
     </row>
@@ -20414,14 +20417,14 @@
       <c r="AA78" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="AB78" s="182"/>
-      <c r="AC78" s="183"/>
+      <c r="AB78" s="181"/>
+      <c r="AC78" s="182"/>
       <c r="AD78" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE78" s="17"/>
-      <c r="AF78" s="175">
+      <c r="AF78" s="205">
         <f>+AD77+AD78</f>
         <v>0</v>
       </c>
@@ -20513,23 +20516,23 @@
       <c r="AA79" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="AB79" s="180">
+      <c r="AB79" s="179">
         <f>SUM(Y79:Y80)</f>
         <v>0</v>
       </c>
-      <c r="AC79" s="181"/>
+      <c r="AC79" s="180"/>
       <c r="AD79" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE79" s="17"/>
-      <c r="AF79" s="184" t="s">
+      <c r="AF79" s="183" t="s">
         <v>91</v>
       </c>
-      <c r="AG79" s="185"/>
-      <c r="AH79" s="185"/>
-      <c r="AI79" s="185"/>
-      <c r="AJ79" s="185"/>
+      <c r="AG79" s="184"/>
+      <c r="AH79" s="184"/>
+      <c r="AI79" s="184"/>
+      <c r="AJ79" s="184"/>
       <c r="AK79" s="211"/>
       <c r="AL79" s="212"/>
     </row>
@@ -20614,14 +20617,14 @@
       <c r="AA80" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="AB80" s="182"/>
-      <c r="AC80" s="183"/>
+      <c r="AB80" s="181"/>
+      <c r="AC80" s="182"/>
       <c r="AD80" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE80" s="17"/>
-      <c r="AF80" s="175">
+      <c r="AF80" s="205">
         <f>+AD79+AD80</f>
         <v>0</v>
       </c>
@@ -20713,23 +20716,23 @@
       <c r="AA81" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="AB81" s="180">
+      <c r="AB81" s="179">
         <f>SUM(Y81:Y82)</f>
         <v>0</v>
       </c>
-      <c r="AC81" s="181"/>
+      <c r="AC81" s="180"/>
       <c r="AD81" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE81" s="17"/>
-      <c r="AF81" s="184" t="s">
+      <c r="AF81" s="183" t="s">
         <v>94</v>
       </c>
-      <c r="AG81" s="185"/>
-      <c r="AH81" s="185"/>
-      <c r="AI81" s="185"/>
-      <c r="AJ81" s="185"/>
+      <c r="AG81" s="184"/>
+      <c r="AH81" s="184"/>
+      <c r="AI81" s="184"/>
+      <c r="AJ81" s="184"/>
       <c r="AK81" s="211"/>
       <c r="AL81" s="212"/>
     </row>
@@ -20814,14 +20817,14 @@
       <c r="AA82" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="AB82" s="182"/>
-      <c r="AC82" s="183"/>
+      <c r="AB82" s="181"/>
+      <c r="AC82" s="182"/>
       <c r="AD82" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE82" s="17"/>
-      <c r="AF82" s="175">
+      <c r="AF82" s="205">
         <f>+AD81+AD82</f>
         <v>0</v>
       </c>
@@ -20913,23 +20916,23 @@
       <c r="AA83" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="AB83" s="180">
+      <c r="AB83" s="179">
         <f>SUM(Y83:Y84)</f>
         <v>0</v>
       </c>
-      <c r="AC83" s="181"/>
+      <c r="AC83" s="180"/>
       <c r="AD83" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE83" s="17"/>
-      <c r="AF83" s="184" t="s">
+      <c r="AF83" s="183" t="s">
         <v>97</v>
       </c>
-      <c r="AG83" s="185"/>
-      <c r="AH83" s="185"/>
-      <c r="AI83" s="185"/>
-      <c r="AJ83" s="185"/>
+      <c r="AG83" s="184"/>
+      <c r="AH83" s="184"/>
+      <c r="AI83" s="184"/>
+      <c r="AJ83" s="184"/>
       <c r="AK83" s="207" t="s">
         <v>98</v>
       </c>
@@ -21016,14 +21019,14 @@
       <c r="AA84" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AB84" s="182"/>
-      <c r="AC84" s="183"/>
+      <c r="AB84" s="181"/>
+      <c r="AC84" s="182"/>
       <c r="AD84" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="AE84" s="17"/>
-      <c r="AF84" s="175">
+      <c r="AF84" s="205">
         <f>+AD83+AD84</f>
         <v>0</v>
       </c>
@@ -21115,8 +21118,8 @@
       <c r="AA85" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB85" s="178"/>
-      <c r="AC85" s="179"/>
+      <c r="AB85" s="157"/>
+      <c r="AC85" s="158"/>
       <c r="AD85" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21211,8 +21214,8 @@
       <c r="AA86" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="AB86" s="178"/>
-      <c r="AC86" s="179"/>
+      <c r="AB86" s="157"/>
+      <c r="AC86" s="158"/>
       <c r="AD86" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21307,8 +21310,8 @@
       <c r="AA87" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AB87" s="178"/>
-      <c r="AC87" s="179"/>
+      <c r="AB87" s="157"/>
+      <c r="AC87" s="158"/>
       <c r="AD87" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21403,8 +21406,8 @@
       <c r="AA88" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="AB88" s="178"/>
-      <c r="AC88" s="179"/>
+      <c r="AB88" s="157"/>
+      <c r="AC88" s="158"/>
       <c r="AD88" s="16">
         <f t="shared" si="23"/>
         <v>0</v>
@@ -21521,46 +21524,46 @@
       <c r="B90" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="C90" s="134" t="s">
+      <c r="C90" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D90" s="135"/>
-      <c r="E90" s="134" t="s">
+      <c r="D90" s="144"/>
+      <c r="E90" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F90" s="135"/>
-      <c r="G90" s="134" t="s">
+      <c r="F90" s="144"/>
+      <c r="G90" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H90" s="135"/>
-      <c r="I90" s="134" t="s">
+      <c r="H90" s="144"/>
+      <c r="I90" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J90" s="135"/>
-      <c r="K90" s="134" t="s">
+      <c r="J90" s="144"/>
+      <c r="K90" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L90" s="135"/>
-      <c r="M90" s="134" t="s">
+      <c r="L90" s="144"/>
+      <c r="M90" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N90" s="135"/>
-      <c r="O90" s="134" t="s">
+      <c r="N90" s="144"/>
+      <c r="O90" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P90" s="135"/>
-      <c r="Q90" s="134" t="s">
+      <c r="P90" s="144"/>
+      <c r="Q90" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R90" s="135"/>
-      <c r="S90" s="134" t="s">
+      <c r="R90" s="144"/>
+      <c r="S90" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T90" s="135"/>
-      <c r="U90" s="134" t="s">
+      <c r="T90" s="144"/>
+      <c r="U90" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V90" s="135"/>
+      <c r="V90" s="144"/>
       <c r="W90" s="9" t="s">
         <v>11</v>
       </c>
@@ -21574,17 +21577,17 @@
       <c r="AA90" s="79" t="s">
         <v>105</v>
       </c>
-      <c r="AB90" s="140"/>
-      <c r="AC90" s="141"/>
+      <c r="AB90" s="147"/>
+      <c r="AC90" s="148"/>
       <c r="AD90" s="6" t="s">
         <v>15</v>
       </c>
       <c r="AE90" s="7"/>
-      <c r="AK90" s="217">
-        <f>SUM(AD91:AD143)</f>
-        <v>0</v>
-      </c>
-      <c r="AL90" s="218"/>
+      <c r="AK90" s="202">
+        <f>SUM(AD91:AD144)</f>
+        <v>0</v>
+      </c>
+      <c r="AL90" s="203"/>
     </row>
     <row r="91" spans="2:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B91" s="15" t="s">
@@ -21667,15 +21670,15 @@
       <c r="AA91" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="AB91" s="220"/>
-      <c r="AC91" s="221"/>
+      <c r="AB91" s="153"/>
+      <c r="AC91" s="154"/>
       <c r="AD91" s="16">
         <f>X91</f>
         <v>0</v>
       </c>
       <c r="AE91" s="7"/>
-      <c r="AK91" s="219"/>
-      <c r="AL91" s="218"/>
+      <c r="AK91" s="204"/>
+      <c r="AL91" s="203"/>
     </row>
     <row r="92" spans="2:38" s="64" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B92" s="65"/>
@@ -21718,8 +21721,8 @@
       <c r="AH92" s="2"/>
       <c r="AI92" s="2"/>
       <c r="AJ92" s="2"/>
-      <c r="AK92" s="219"/>
-      <c r="AL92" s="218"/>
+      <c r="AK92" s="204"/>
+      <c r="AL92" s="203"/>
     </row>
     <row r="93" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B93" s="13" t="s">
@@ -21802,8 +21805,8 @@
       <c r="AA93" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="AB93" s="178"/>
-      <c r="AC93" s="179"/>
+      <c r="AB93" s="157"/>
+      <c r="AC93" s="158"/>
       <c r="AD93" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21814,8 +21817,8 @@
       <c r="AH93" s="2"/>
       <c r="AI93" s="2"/>
       <c r="AJ93" s="2"/>
-      <c r="AK93" s="219"/>
-      <c r="AL93" s="218"/>
+      <c r="AK93" s="204"/>
+      <c r="AL93" s="203"/>
     </row>
     <row r="94" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B94" s="13" t="s">
@@ -21898,8 +21901,8 @@
       <c r="AA94" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AB94" s="178"/>
-      <c r="AC94" s="179"/>
+      <c r="AB94" s="157"/>
+      <c r="AC94" s="158"/>
       <c r="AD94" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -21910,8 +21913,8 @@
       <c r="AH94" s="2"/>
       <c r="AI94" s="2"/>
       <c r="AJ94" s="2"/>
-      <c r="AK94" s="219"/>
-      <c r="AL94" s="218"/>
+      <c r="AK94" s="204"/>
+      <c r="AL94" s="203"/>
     </row>
     <row r="95" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B95" s="13" t="s">
@@ -21994,8 +21997,8 @@
       <c r="AA95" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="AB95" s="178"/>
-      <c r="AC95" s="179"/>
+      <c r="AB95" s="157"/>
+      <c r="AC95" s="158"/>
       <c r="AD95" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22006,8 +22009,8 @@
       <c r="AH95" s="2"/>
       <c r="AI95" s="2"/>
       <c r="AJ95" s="2"/>
-      <c r="AK95" s="219"/>
-      <c r="AL95" s="218"/>
+      <c r="AK95" s="204"/>
+      <c r="AL95" s="203"/>
     </row>
     <row r="96" spans="2:38" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B96" s="13" t="s">
@@ -22090,11 +22093,11 @@
       <c r="AA96" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="AB96" s="222">
+      <c r="AB96" s="162">
         <f>SUM(Y96:Y105)</f>
         <v>0</v>
       </c>
-      <c r="AC96" s="147"/>
+      <c r="AC96" s="163"/>
       <c r="AD96" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22107,8 +22110,8 @@
       <c r="AH96" s="169"/>
       <c r="AI96" s="169"/>
       <c r="AJ96" s="170"/>
-      <c r="AK96" s="219"/>
-      <c r="AL96" s="218"/>
+      <c r="AK96" s="204"/>
+      <c r="AL96" s="203"/>
     </row>
     <row r="97" spans="1:38" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A97" s="12"/>
@@ -22192,20 +22195,20 @@
       <c r="AA97" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="AB97" s="223"/>
-      <c r="AC97" s="148"/>
+      <c r="AB97" s="164"/>
+      <c r="AC97" s="165"/>
       <c r="AD97" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE97" s="17"/>
       <c r="AF97" s="171"/>
-      <c r="AG97" s="160"/>
-      <c r="AH97" s="160"/>
-      <c r="AI97" s="160"/>
-      <c r="AJ97" s="161"/>
-      <c r="AK97" s="219"/>
-      <c r="AL97" s="218"/>
+      <c r="AG97" s="172"/>
+      <c r="AH97" s="172"/>
+      <c r="AI97" s="172"/>
+      <c r="AJ97" s="173"/>
+      <c r="AK97" s="204"/>
+      <c r="AL97" s="203"/>
     </row>
     <row r="98" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A98" s="12"/>
@@ -22289,20 +22292,20 @@
       <c r="AA98" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="AB98" s="223"/>
-      <c r="AC98" s="148"/>
+      <c r="AB98" s="164"/>
+      <c r="AC98" s="165"/>
       <c r="AD98" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE98" s="17"/>
       <c r="AF98" s="171"/>
-      <c r="AG98" s="160"/>
-      <c r="AH98" s="160"/>
-      <c r="AI98" s="160"/>
-      <c r="AJ98" s="161"/>
-      <c r="AK98" s="219"/>
-      <c r="AL98" s="218"/>
+      <c r="AG98" s="172"/>
+      <c r="AH98" s="172"/>
+      <c r="AI98" s="172"/>
+      <c r="AJ98" s="173"/>
+      <c r="AK98" s="204"/>
+      <c r="AL98" s="203"/>
     </row>
     <row r="99" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A99" s="12"/>
@@ -22386,20 +22389,20 @@
       <c r="AA99" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="AB99" s="223"/>
-      <c r="AC99" s="148"/>
+      <c r="AB99" s="164"/>
+      <c r="AC99" s="165"/>
       <c r="AD99" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE99" s="17"/>
       <c r="AF99" s="171"/>
-      <c r="AG99" s="160"/>
-      <c r="AH99" s="160"/>
-      <c r="AI99" s="160"/>
-      <c r="AJ99" s="161"/>
-      <c r="AK99" s="219"/>
-      <c r="AL99" s="218"/>
+      <c r="AG99" s="172"/>
+      <c r="AH99" s="172"/>
+      <c r="AI99" s="172"/>
+      <c r="AJ99" s="173"/>
+      <c r="AK99" s="204"/>
+      <c r="AL99" s="203"/>
     </row>
     <row r="100" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A100" s="12"/>
@@ -22483,20 +22486,20 @@
       <c r="AA100" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="AB100" s="223"/>
-      <c r="AC100" s="148"/>
+      <c r="AB100" s="164"/>
+      <c r="AC100" s="165"/>
       <c r="AD100" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE100" s="17"/>
       <c r="AF100" s="171"/>
-      <c r="AG100" s="160"/>
-      <c r="AH100" s="160"/>
-      <c r="AI100" s="160"/>
-      <c r="AJ100" s="161"/>
-      <c r="AK100" s="219"/>
-      <c r="AL100" s="218"/>
+      <c r="AG100" s="172"/>
+      <c r="AH100" s="172"/>
+      <c r="AI100" s="172"/>
+      <c r="AJ100" s="173"/>
+      <c r="AK100" s="204"/>
+      <c r="AL100" s="203"/>
     </row>
     <row r="101" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A101" s="12"/>
@@ -22580,23 +22583,23 @@
       <c r="AA101" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="AB101" s="223"/>
-      <c r="AC101" s="148"/>
+      <c r="AB101" s="164"/>
+      <c r="AC101" s="165"/>
       <c r="AD101" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE101" s="17"/>
-      <c r="AF101" s="225">
+      <c r="AF101" s="191">
         <f>SUM(AD96:AD105)</f>
         <v>0</v>
       </c>
-      <c r="AG101" s="226"/>
-      <c r="AH101" s="226"/>
-      <c r="AI101" s="226"/>
-      <c r="AJ101" s="227"/>
-      <c r="AK101" s="219"/>
-      <c r="AL101" s="218"/>
+      <c r="AG101" s="192"/>
+      <c r="AH101" s="192"/>
+      <c r="AI101" s="192"/>
+      <c r="AJ101" s="193"/>
+      <c r="AK101" s="204"/>
+      <c r="AL101" s="203"/>
     </row>
     <row r="102" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A102" s="12"/>
@@ -22680,8 +22683,8 @@
       <c r="AA102" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="AB102" s="223"/>
-      <c r="AC102" s="148"/>
+      <c r="AB102" s="164"/>
+      <c r="AC102" s="165"/>
       <c r="AD102" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22692,8 +22695,8 @@
       <c r="AH102" s="24"/>
       <c r="AI102" s="24"/>
       <c r="AJ102" s="25"/>
-      <c r="AK102" s="219"/>
-      <c r="AL102" s="218"/>
+      <c r="AK102" s="204"/>
+      <c r="AL102" s="203"/>
     </row>
     <row r="103" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A103" s="12"/>
@@ -22777,20 +22780,20 @@
       <c r="AA103" s="13" t="s">
         <v>118</v>
       </c>
-      <c r="AB103" s="223"/>
-      <c r="AC103" s="148"/>
+      <c r="AB103" s="164"/>
+      <c r="AC103" s="165"/>
       <c r="AD103" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE103" s="17"/>
-      <c r="AF103" s="159"/>
-      <c r="AG103" s="160"/>
-      <c r="AH103" s="160"/>
-      <c r="AI103" s="160"/>
-      <c r="AJ103" s="161"/>
-      <c r="AK103" s="219"/>
-      <c r="AL103" s="218"/>
+      <c r="AF103" s="174"/>
+      <c r="AG103" s="172"/>
+      <c r="AH103" s="172"/>
+      <c r="AI103" s="172"/>
+      <c r="AJ103" s="173"/>
+      <c r="AK103" s="204"/>
+      <c r="AL103" s="203"/>
     </row>
     <row r="104" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A104" s="12"/>
@@ -22874,8 +22877,8 @@
       <c r="AA104" s="13" t="s">
         <v>119</v>
       </c>
-      <c r="AB104" s="223"/>
-      <c r="AC104" s="148"/>
+      <c r="AB104" s="164"/>
+      <c r="AC104" s="165"/>
       <c r="AD104" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22886,8 +22889,8 @@
       <c r="AH104" s="27"/>
       <c r="AI104" s="27"/>
       <c r="AJ104" s="28"/>
-      <c r="AK104" s="219"/>
-      <c r="AL104" s="218"/>
+      <c r="AK104" s="204"/>
+      <c r="AL104" s="203"/>
     </row>
     <row r="105" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A105" s="12"/>
@@ -22971,8 +22974,8 @@
       <c r="AA105" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="AB105" s="224"/>
-      <c r="AC105" s="149"/>
+      <c r="AB105" s="166"/>
+      <c r="AC105" s="167"/>
       <c r="AD105" s="16">
         <f t="shared" si="27"/>
         <v>0</v>
@@ -22983,8 +22986,8 @@
       <c r="AH105" s="84"/>
       <c r="AI105" s="84"/>
       <c r="AJ105" s="85"/>
-      <c r="AK105" s="219"/>
-      <c r="AL105" s="218"/>
+      <c r="AK105" s="204"/>
+      <c r="AL105" s="203"/>
     </row>
     <row r="106" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A106" s="12"/>
@@ -23077,132 +23080,132 @@
       <c r="Y106" s="14"/>
       <c r="Z106" s="14"/>
       <c r="AA106" s="13"/>
-      <c r="AB106" s="187"/>
-      <c r="AC106" s="188"/>
+      <c r="AB106" s="194"/>
+      <c r="AC106" s="195"/>
       <c r="AD106" s="33"/>
       <c r="AE106" s="17"/>
-      <c r="AF106" s="150"/>
-      <c r="AG106" s="151"/>
-      <c r="AH106" s="151"/>
-      <c r="AI106" s="151"/>
-      <c r="AJ106" s="152"/>
-      <c r="AK106" s="219"/>
-      <c r="AL106" s="218"/>
+      <c r="AF106" s="196"/>
+      <c r="AG106" s="197"/>
+      <c r="AH106" s="197"/>
+      <c r="AI106" s="197"/>
+      <c r="AJ106" s="198"/>
+      <c r="AK106" s="204"/>
+      <c r="AL106" s="203"/>
     </row>
     <row r="107" spans="1:38" ht="126" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="138" t="s">
+      <c r="B107" s="177" t="s">
         <v>220</v>
       </c>
-      <c r="C107" s="139"/>
-      <c r="D107" s="139"/>
-      <c r="E107" s="139"/>
-      <c r="F107" s="139"/>
-      <c r="G107" s="139"/>
-      <c r="H107" s="139"/>
-      <c r="I107" s="139"/>
-      <c r="J107" s="139"/>
-      <c r="K107" s="139"/>
-      <c r="L107" s="139"/>
-      <c r="M107" s="139"/>
-      <c r="N107" s="139"/>
-      <c r="O107" s="139"/>
-      <c r="P107" s="139"/>
-      <c r="Q107" s="139"/>
-      <c r="R107" s="139"/>
-      <c r="S107" s="139"/>
-      <c r="T107" s="139"/>
-      <c r="U107" s="139"/>
-      <c r="V107" s="139"/>
-      <c r="W107" s="139"/>
-      <c r="X107" s="139"/>
-      <c r="Y107" s="139"/>
-      <c r="Z107" s="139"/>
-      <c r="AA107" s="139"/>
-      <c r="AB107" s="139"/>
-      <c r="AC107" s="139"/>
-      <c r="AD107" s="139"/>
+      <c r="C107" s="178"/>
+      <c r="D107" s="178"/>
+      <c r="E107" s="178"/>
+      <c r="F107" s="178"/>
+      <c r="G107" s="178"/>
+      <c r="H107" s="178"/>
+      <c r="I107" s="178"/>
+      <c r="J107" s="178"/>
+      <c r="K107" s="178"/>
+      <c r="L107" s="178"/>
+      <c r="M107" s="178"/>
+      <c r="N107" s="178"/>
+      <c r="O107" s="178"/>
+      <c r="P107" s="178"/>
+      <c r="Q107" s="178"/>
+      <c r="R107" s="178"/>
+      <c r="S107" s="178"/>
+      <c r="T107" s="178"/>
+      <c r="U107" s="178"/>
+      <c r="V107" s="178"/>
+      <c r="W107" s="178"/>
+      <c r="X107" s="178"/>
+      <c r="Y107" s="178"/>
+      <c r="Z107" s="178"/>
+      <c r="AA107" s="178"/>
+      <c r="AB107" s="178"/>
+      <c r="AC107" s="178"/>
+      <c r="AD107" s="178"/>
       <c r="AE107" s="1"/>
-      <c r="AF107" s="153"/>
-      <c r="AG107" s="154"/>
-      <c r="AH107" s="154"/>
-      <c r="AI107" s="154"/>
-      <c r="AJ107" s="155"/>
-      <c r="AK107" s="219"/>
-      <c r="AL107" s="218"/>
+      <c r="AF107" s="199"/>
+      <c r="AG107" s="200"/>
+      <c r="AH107" s="200"/>
+      <c r="AI107" s="200"/>
+      <c r="AJ107" s="201"/>
+      <c r="AK107" s="204"/>
+      <c r="AL107" s="203"/>
     </row>
     <row r="108" spans="1:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B108" s="136" t="s">
+      <c r="B108" s="175" t="s">
         <v>121</v>
       </c>
-      <c r="C108" s="134" t="s">
+      <c r="C108" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D108" s="135"/>
-      <c r="E108" s="134" t="s">
+      <c r="D108" s="144"/>
+      <c r="E108" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F108" s="135"/>
-      <c r="G108" s="134" t="s">
+      <c r="F108" s="144"/>
+      <c r="G108" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H108" s="135"/>
-      <c r="I108" s="134" t="s">
+      <c r="H108" s="144"/>
+      <c r="I108" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J108" s="135"/>
-      <c r="K108" s="134" t="s">
+      <c r="J108" s="144"/>
+      <c r="K108" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L108" s="135"/>
-      <c r="M108" s="134" t="s">
+      <c r="L108" s="144"/>
+      <c r="M108" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N108" s="135"/>
-      <c r="O108" s="134" t="s">
+      <c r="N108" s="144"/>
+      <c r="O108" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P108" s="135"/>
-      <c r="Q108" s="134" t="s">
+      <c r="P108" s="144"/>
+      <c r="Q108" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R108" s="135"/>
-      <c r="S108" s="134" t="s">
+      <c r="R108" s="144"/>
+      <c r="S108" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T108" s="135"/>
-      <c r="U108" s="134" t="s">
+      <c r="T108" s="144"/>
+      <c r="U108" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V108" s="135"/>
-      <c r="W108" s="136" t="s">
+      <c r="V108" s="144"/>
+      <c r="W108" s="175" t="s">
         <v>11</v>
       </c>
       <c r="X108" s="110"/>
-      <c r="Y108" s="136" t="s">
+      <c r="Y108" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="Z108" s="136" t="s">
+      <c r="Z108" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="AA108" s="136" t="s">
+      <c r="AA108" s="175" t="s">
         <v>121</v>
       </c>
-      <c r="AB108" s="140"/>
-      <c r="AC108" s="141"/>
+      <c r="AB108" s="147"/>
+      <c r="AC108" s="148"/>
       <c r="AD108" s="6" t="s">
         <v>15</v>
       </c>
       <c r="AE108" s="7"/>
-      <c r="AF108" s="153"/>
-      <c r="AG108" s="154"/>
-      <c r="AH108" s="154"/>
-      <c r="AI108" s="154"/>
-      <c r="AJ108" s="155"/>
-      <c r="AK108" s="219"/>
-      <c r="AL108" s="218"/>
+      <c r="AF108" s="199"/>
+      <c r="AG108" s="200"/>
+      <c r="AH108" s="200"/>
+      <c r="AI108" s="200"/>
+      <c r="AJ108" s="201"/>
+      <c r="AK108" s="204"/>
+      <c r="AL108" s="203"/>
     </row>
     <row r="109" spans="1:38" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B109" s="137"/>
+      <c r="B109" s="176"/>
       <c r="C109" s="9" t="s">
         <v>16</v>
       </c>
@@ -23263,22 +23266,22 @@
       <c r="V109" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="W109" s="137"/>
+      <c r="W109" s="176"/>
       <c r="X109" s="111"/>
-      <c r="Y109" s="137"/>
-      <c r="Z109" s="137"/>
-      <c r="AA109" s="137"/>
+      <c r="Y109" s="176"/>
+      <c r="Z109" s="176"/>
+      <c r="AA109" s="176"/>
       <c r="AB109" s="10"/>
       <c r="AC109" s="11"/>
       <c r="AD109" s="6"/>
       <c r="AE109" s="7"/>
-      <c r="AF109" s="153"/>
-      <c r="AG109" s="154"/>
-      <c r="AH109" s="154"/>
-      <c r="AI109" s="154"/>
-      <c r="AJ109" s="155"/>
-      <c r="AK109" s="219"/>
-      <c r="AL109" s="218"/>
+      <c r="AF109" s="199"/>
+      <c r="AG109" s="200"/>
+      <c r="AH109" s="200"/>
+      <c r="AI109" s="200"/>
+      <c r="AJ109" s="201"/>
+      <c r="AK109" s="204"/>
+      <c r="AL109" s="203"/>
     </row>
     <row r="110" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A110" s="12"/>
@@ -23362,23 +23365,23 @@
       <c r="AA110" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="AB110" s="222">
+      <c r="AB110" s="162">
         <f>SUM(Y110:Y113)</f>
         <v>0</v>
       </c>
-      <c r="AC110" s="147"/>
+      <c r="AC110" s="163"/>
       <c r="AD110" s="16">
         <f>X110</f>
         <v>0</v>
       </c>
       <c r="AE110" s="17"/>
-      <c r="AF110" s="153"/>
-      <c r="AG110" s="154"/>
-      <c r="AH110" s="154"/>
-      <c r="AI110" s="154"/>
-      <c r="AJ110" s="155"/>
-      <c r="AK110" s="219"/>
-      <c r="AL110" s="218"/>
+      <c r="AF110" s="199"/>
+      <c r="AG110" s="200"/>
+      <c r="AH110" s="200"/>
+      <c r="AI110" s="200"/>
+      <c r="AJ110" s="201"/>
+      <c r="AK110" s="204"/>
+      <c r="AL110" s="203"/>
     </row>
     <row r="111" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A111" s="12"/>
@@ -23462,8 +23465,8 @@
       <c r="AA111" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="AB111" s="223"/>
-      <c r="AC111" s="148"/>
+      <c r="AB111" s="164"/>
+      <c r="AC111" s="165"/>
       <c r="AD111" s="16">
         <f t="shared" ref="AD111:AD141" si="31">X111</f>
         <v>0</v>
@@ -23474,8 +23477,8 @@
       <c r="AH111" s="24"/>
       <c r="AI111" s="24"/>
       <c r="AJ111" s="25"/>
-      <c r="AK111" s="219"/>
-      <c r="AL111" s="218"/>
+      <c r="AK111" s="204"/>
+      <c r="AL111" s="203"/>
     </row>
     <row r="112" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A112" s="12"/>
@@ -23559,8 +23562,8 @@
       <c r="AA112" s="13" t="s">
         <v>124</v>
       </c>
-      <c r="AB112" s="223"/>
-      <c r="AC112" s="148"/>
+      <c r="AB112" s="164"/>
+      <c r="AC112" s="165"/>
       <c r="AD112" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23571,8 +23574,8 @@
       <c r="AH112" s="24"/>
       <c r="AI112" s="24"/>
       <c r="AJ112" s="25"/>
-      <c r="AK112" s="219"/>
-      <c r="AL112" s="218"/>
+      <c r="AK112" s="204"/>
+      <c r="AL112" s="203"/>
     </row>
     <row r="113" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A113" s="12"/>
@@ -23656,8 +23659,8 @@
       <c r="AA113" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="AB113" s="223"/>
-      <c r="AC113" s="148"/>
+      <c r="AB113" s="164"/>
+      <c r="AC113" s="165"/>
       <c r="AD113" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23668,8 +23671,8 @@
       <c r="AH113" s="24"/>
       <c r="AI113" s="24"/>
       <c r="AJ113" s="25"/>
-      <c r="AK113" s="219"/>
-      <c r="AL113" s="218"/>
+      <c r="AK113" s="204"/>
+      <c r="AL113" s="203"/>
     </row>
     <row r="114" spans="1:38" s="47" customFormat="1" ht="111" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="A114" s="12"/>
@@ -23762,20 +23765,20 @@
       <c r="Y114" s="14"/>
       <c r="Z114" s="14"/>
       <c r="AA114" s="13"/>
-      <c r="AB114" s="224"/>
-      <c r="AC114" s="149"/>
+      <c r="AB114" s="166"/>
+      <c r="AC114" s="167"/>
       <c r="AD114" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE114" s="17"/>
-      <c r="AF114" s="230"/>
-      <c r="AG114" s="231"/>
-      <c r="AH114" s="231"/>
-      <c r="AI114" s="231"/>
-      <c r="AJ114" s="232"/>
-      <c r="AK114" s="219"/>
-      <c r="AL114" s="218"/>
+      <c r="AF114" s="186"/>
+      <c r="AG114" s="187"/>
+      <c r="AH114" s="187"/>
+      <c r="AI114" s="187"/>
+      <c r="AJ114" s="188"/>
+      <c r="AK114" s="204"/>
+      <c r="AL114" s="203"/>
     </row>
     <row r="115" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B115" s="13" t="s">
@@ -23858,11 +23861,11 @@
       <c r="AA115" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="AB115" s="222">
+      <c r="AB115" s="162">
         <f>SUM(Y115:Y127)</f>
         <v>0</v>
       </c>
-      <c r="AC115" s="147"/>
+      <c r="AC115" s="163"/>
       <c r="AD115" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -23875,8 +23878,8 @@
       <c r="AH115" s="169"/>
       <c r="AI115" s="169"/>
       <c r="AJ115" s="170"/>
-      <c r="AK115" s="219"/>
-      <c r="AL115" s="218"/>
+      <c r="AK115" s="204"/>
+      <c r="AL115" s="203"/>
     </row>
     <row r="116" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B116" s="13" t="s">
@@ -23959,22 +23962,22 @@
       <c r="AA116" s="13" t="s">
         <v>128</v>
       </c>
-      <c r="AB116" s="223"/>
-      <c r="AC116" s="148"/>
+      <c r="AB116" s="164"/>
+      <c r="AC116" s="165"/>
       <c r="AD116" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE116" s="17"/>
       <c r="AF116" s="171"/>
-      <c r="AG116" s="160"/>
-      <c r="AH116" s="160"/>
-      <c r="AI116" s="160"/>
-      <c r="AJ116" s="161"/>
-      <c r="AK116" s="228" t="s">
+      <c r="AG116" s="172"/>
+      <c r="AH116" s="172"/>
+      <c r="AI116" s="172"/>
+      <c r="AJ116" s="173"/>
+      <c r="AK116" s="189" t="s">
         <v>129</v>
       </c>
-      <c r="AL116" s="229"/>
+      <c r="AL116" s="190"/>
     </row>
     <row r="117" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B117" s="13" t="s">
@@ -24057,20 +24060,20 @@
       <c r="AA117" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="AB117" s="223"/>
-      <c r="AC117" s="148"/>
+      <c r="AB117" s="164"/>
+      <c r="AC117" s="165"/>
       <c r="AD117" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE117" s="17"/>
       <c r="AF117" s="171"/>
-      <c r="AG117" s="160"/>
-      <c r="AH117" s="160"/>
-      <c r="AI117" s="160"/>
-      <c r="AJ117" s="161"/>
-      <c r="AK117" s="228"/>
-      <c r="AL117" s="229"/>
+      <c r="AG117" s="172"/>
+      <c r="AH117" s="172"/>
+      <c r="AI117" s="172"/>
+      <c r="AJ117" s="173"/>
+      <c r="AK117" s="189"/>
+      <c r="AL117" s="190"/>
     </row>
     <row r="118" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B118" s="13" t="s">
@@ -24153,20 +24156,20 @@
       <c r="AA118" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="AB118" s="223"/>
-      <c r="AC118" s="148"/>
+      <c r="AB118" s="164"/>
+      <c r="AC118" s="165"/>
       <c r="AD118" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE118" s="17"/>
       <c r="AF118" s="171"/>
-      <c r="AG118" s="160"/>
-      <c r="AH118" s="160"/>
-      <c r="AI118" s="160"/>
-      <c r="AJ118" s="161"/>
-      <c r="AK118" s="228"/>
-      <c r="AL118" s="229"/>
+      <c r="AG118" s="172"/>
+      <c r="AH118" s="172"/>
+      <c r="AI118" s="172"/>
+      <c r="AJ118" s="173"/>
+      <c r="AK118" s="189"/>
+      <c r="AL118" s="190"/>
     </row>
     <row r="119" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B119" s="13" t="s">
@@ -24249,20 +24252,20 @@
       <c r="AA119" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="AB119" s="223"/>
-      <c r="AC119" s="148"/>
+      <c r="AB119" s="164"/>
+      <c r="AC119" s="165"/>
       <c r="AD119" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE119" s="17"/>
       <c r="AF119" s="171"/>
-      <c r="AG119" s="160"/>
-      <c r="AH119" s="160"/>
-      <c r="AI119" s="160"/>
-      <c r="AJ119" s="161"/>
-      <c r="AK119" s="228"/>
-      <c r="AL119" s="229"/>
+      <c r="AG119" s="172"/>
+      <c r="AH119" s="172"/>
+      <c r="AI119" s="172"/>
+      <c r="AJ119" s="173"/>
+      <c r="AK119" s="189"/>
+      <c r="AL119" s="190"/>
     </row>
     <row r="120" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B120" s="13" t="s">
@@ -24345,20 +24348,20 @@
       <c r="AA120" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="AB120" s="223"/>
-      <c r="AC120" s="148"/>
+      <c r="AB120" s="164"/>
+      <c r="AC120" s="165"/>
       <c r="AD120" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE120" s="17"/>
       <c r="AF120" s="171"/>
-      <c r="AG120" s="160"/>
-      <c r="AH120" s="160"/>
-      <c r="AI120" s="160"/>
-      <c r="AJ120" s="161"/>
-      <c r="AK120" s="228"/>
-      <c r="AL120" s="229"/>
+      <c r="AG120" s="172"/>
+      <c r="AH120" s="172"/>
+      <c r="AI120" s="172"/>
+      <c r="AJ120" s="173"/>
+      <c r="AK120" s="189"/>
+      <c r="AL120" s="190"/>
     </row>
     <row r="121" spans="1:38" s="47" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A121" s="12"/>
@@ -24442,23 +24445,23 @@
       <c r="AA121" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AB121" s="223"/>
-      <c r="AC121" s="148"/>
+      <c r="AB121" s="164"/>
+      <c r="AC121" s="165"/>
       <c r="AD121" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE121" s="17"/>
-      <c r="AF121" s="159">
+      <c r="AF121" s="174">
         <f>SUM(AD115:AD127)</f>
         <v>0</v>
       </c>
-      <c r="AG121" s="160"/>
-      <c r="AH121" s="160"/>
-      <c r="AI121" s="160"/>
-      <c r="AJ121" s="161"/>
-      <c r="AK121" s="228"/>
-      <c r="AL121" s="229"/>
+      <c r="AG121" s="172"/>
+      <c r="AH121" s="172"/>
+      <c r="AI121" s="172"/>
+      <c r="AJ121" s="173"/>
+      <c r="AK121" s="189"/>
+      <c r="AL121" s="190"/>
     </row>
     <row r="122" spans="1:38" s="47" customFormat="1" ht="120.75" customHeight="1" x14ac:dyDescent="2.1">
       <c r="A122" s="12"/>
@@ -24542,20 +24545,20 @@
       <c r="AA122" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="AB122" s="223"/>
-      <c r="AC122" s="148"/>
+      <c r="AB122" s="164"/>
+      <c r="AC122" s="165"/>
       <c r="AD122" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE122" s="17"/>
-      <c r="AF122" s="159"/>
-      <c r="AG122" s="160"/>
-      <c r="AH122" s="160"/>
-      <c r="AI122" s="160"/>
-      <c r="AJ122" s="161"/>
-      <c r="AK122" s="228"/>
-      <c r="AL122" s="229"/>
+      <c r="AF122" s="174"/>
+      <c r="AG122" s="172"/>
+      <c r="AH122" s="172"/>
+      <c r="AI122" s="172"/>
+      <c r="AJ122" s="173"/>
+      <c r="AK122" s="189"/>
+      <c r="AL122" s="190"/>
     </row>
     <row r="123" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B123" s="13" t="s">
@@ -24638,8 +24641,8 @@
       <c r="AA123" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="AB123" s="223"/>
-      <c r="AC123" s="148"/>
+      <c r="AB123" s="164"/>
+      <c r="AC123" s="165"/>
       <c r="AD123" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24650,8 +24653,8 @@
       <c r="AH123" s="27"/>
       <c r="AI123" s="27"/>
       <c r="AJ123" s="28"/>
-      <c r="AK123" s="228"/>
-      <c r="AL123" s="229"/>
+      <c r="AK123" s="189"/>
+      <c r="AL123" s="190"/>
     </row>
     <row r="124" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B124" s="13" t="s">
@@ -24734,8 +24737,8 @@
       <c r="AA124" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="AB124" s="223"/>
-      <c r="AC124" s="148"/>
+      <c r="AB124" s="164"/>
+      <c r="AC124" s="165"/>
       <c r="AD124" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24746,8 +24749,8 @@
       <c r="AH124" s="27"/>
       <c r="AI124" s="27"/>
       <c r="AJ124" s="28"/>
-      <c r="AK124" s="228"/>
-      <c r="AL124" s="229"/>
+      <c r="AK124" s="189"/>
+      <c r="AL124" s="190"/>
     </row>
     <row r="125" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B125" s="13" t="s">
@@ -24830,8 +24833,8 @@
       <c r="AA125" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AB125" s="223"/>
-      <c r="AC125" s="148"/>
+      <c r="AB125" s="164"/>
+      <c r="AC125" s="165"/>
       <c r="AD125" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24842,8 +24845,8 @@
       <c r="AH125" s="27"/>
       <c r="AI125" s="27"/>
       <c r="AJ125" s="28"/>
-      <c r="AK125" s="228"/>
-      <c r="AL125" s="229"/>
+      <c r="AK125" s="189"/>
+      <c r="AL125" s="190"/>
     </row>
     <row r="126" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B126" s="13" t="s">
@@ -24926,8 +24929,8 @@
       <c r="AA126" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="AB126" s="223"/>
-      <c r="AC126" s="148"/>
+      <c r="AB126" s="164"/>
+      <c r="AC126" s="165"/>
       <c r="AD126" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -24938,8 +24941,8 @@
       <c r="AH126" s="84"/>
       <c r="AI126" s="84"/>
       <c r="AJ126" s="85"/>
-      <c r="AK126" s="228"/>
-      <c r="AL126" s="229"/>
+      <c r="AK126" s="189"/>
+      <c r="AL126" s="190"/>
     </row>
     <row r="127" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B127" s="13" t="s">
@@ -25022,8 +25025,8 @@
       <c r="AA127" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AB127" s="223"/>
-      <c r="AC127" s="148"/>
+      <c r="AB127" s="164"/>
+      <c r="AC127" s="165"/>
       <c r="AD127" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25034,8 +25037,8 @@
       <c r="AH127" s="84"/>
       <c r="AI127" s="84"/>
       <c r="AJ127" s="85"/>
-      <c r="AK127" s="228"/>
-      <c r="AL127" s="229"/>
+      <c r="AK127" s="189"/>
+      <c r="AL127" s="190"/>
     </row>
     <row r="128" spans="1:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B128" s="13"/>
@@ -25129,8 +25132,8 @@
       <c r="Y128" s="14"/>
       <c r="Z128" s="14"/>
       <c r="AA128" s="13"/>
-      <c r="AB128" s="224"/>
-      <c r="AC128" s="149"/>
+      <c r="AB128" s="166"/>
+      <c r="AC128" s="167"/>
       <c r="AD128" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25141,10 +25144,10 @@
       <c r="AH128" s="24"/>
       <c r="AI128" s="24"/>
       <c r="AJ128" s="25"/>
-      <c r="AK128" s="228"/>
-      <c r="AL128" s="229"/>
+      <c r="AK128" s="189"/>
+      <c r="AL128" s="190"/>
     </row>
-    <row r="129" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="129" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B129" s="13" t="s">
         <v>141</v>
       </c>
@@ -25225,11 +25228,11 @@
       <c r="AA129" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="AB129" s="222">
+      <c r="AB129" s="162">
         <f>SUM(Y129:Y140)</f>
         <v>0</v>
       </c>
-      <c r="AC129" s="147"/>
+      <c r="AC129" s="163"/>
       <c r="AD129" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25242,10 +25245,10 @@
       <c r="AH129" s="169"/>
       <c r="AI129" s="169"/>
       <c r="AJ129" s="170"/>
-      <c r="AK129" s="228"/>
-      <c r="AL129" s="229"/>
+      <c r="AK129" s="189"/>
+      <c r="AL129" s="190"/>
     </row>
-    <row r="130" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="130" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B130" s="13" t="s">
         <v>213</v>
       </c>
@@ -25326,22 +25329,22 @@
       <c r="AA130" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="AB130" s="223"/>
-      <c r="AC130" s="148"/>
+      <c r="AB130" s="164"/>
+      <c r="AC130" s="165"/>
       <c r="AD130" s="16">
         <f>X130</f>
         <v>0</v>
       </c>
       <c r="AE130" s="17"/>
       <c r="AF130" s="171"/>
-      <c r="AG130" s="160"/>
-      <c r="AH130" s="160"/>
-      <c r="AI130" s="160"/>
-      <c r="AJ130" s="161"/>
-      <c r="AK130" s="228"/>
-      <c r="AL130" s="229"/>
+      <c r="AG130" s="172"/>
+      <c r="AH130" s="172"/>
+      <c r="AI130" s="172"/>
+      <c r="AJ130" s="173"/>
+      <c r="AK130" s="189"/>
+      <c r="AL130" s="190"/>
     </row>
-    <row r="131" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="131" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B131" s="13" t="s">
         <v>143</v>
       </c>
@@ -25422,22 +25425,22 @@
       <c r="AA131" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="AB131" s="223"/>
-      <c r="AC131" s="148"/>
+      <c r="AB131" s="164"/>
+      <c r="AC131" s="165"/>
       <c r="AD131" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE131" s="17"/>
       <c r="AF131" s="171"/>
-      <c r="AG131" s="160"/>
-      <c r="AH131" s="160"/>
-      <c r="AI131" s="160"/>
-      <c r="AJ131" s="161"/>
-      <c r="AK131" s="228"/>
-      <c r="AL131" s="229"/>
+      <c r="AG131" s="172"/>
+      <c r="AH131" s="172"/>
+      <c r="AI131" s="172"/>
+      <c r="AJ131" s="173"/>
+      <c r="AK131" s="189"/>
+      <c r="AL131" s="190"/>
     </row>
-    <row r="132" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="132" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B132" s="13" t="s">
         <v>144</v>
       </c>
@@ -25518,8 +25521,8 @@
       <c r="AA132" s="13" t="s">
         <v>144</v>
       </c>
-      <c r="AB132" s="223"/>
-      <c r="AC132" s="148"/>
+      <c r="AB132" s="164"/>
+      <c r="AC132" s="165"/>
       <c r="AD132" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25530,10 +25533,10 @@
       <c r="AH132" s="24"/>
       <c r="AI132" s="24"/>
       <c r="AJ132" s="25"/>
-      <c r="AK132" s="228"/>
-      <c r="AL132" s="229"/>
+      <c r="AK132" s="189"/>
+      <c r="AL132" s="190"/>
     </row>
-    <row r="133" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="133" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B133" s="13" t="s">
         <v>145</v>
       </c>
@@ -25614,25 +25617,25 @@
       <c r="AA133" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="AB133" s="223"/>
-      <c r="AC133" s="148"/>
+      <c r="AB133" s="164"/>
+      <c r="AC133" s="165"/>
       <c r="AD133" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE133" s="17"/>
-      <c r="AF133" s="159">
+      <c r="AF133" s="174">
         <f>SUM(AD129:AD140)</f>
         <v>0</v>
       </c>
-      <c r="AG133" s="160"/>
-      <c r="AH133" s="160"/>
-      <c r="AI133" s="160"/>
-      <c r="AJ133" s="161"/>
-      <c r="AK133" s="228"/>
-      <c r="AL133" s="229"/>
+      <c r="AG133" s="172"/>
+      <c r="AH133" s="172"/>
+      <c r="AI133" s="172"/>
+      <c r="AJ133" s="173"/>
+      <c r="AK133" s="189"/>
+      <c r="AL133" s="190"/>
     </row>
-    <row r="134" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="134" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B134" s="13" t="s">
         <v>146</v>
       </c>
@@ -25713,8 +25716,8 @@
       <c r="AA134" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="AB134" s="223"/>
-      <c r="AC134" s="148"/>
+      <c r="AB134" s="164"/>
+      <c r="AC134" s="165"/>
       <c r="AD134" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25725,10 +25728,10 @@
       <c r="AH134" s="24"/>
       <c r="AI134" s="24"/>
       <c r="AJ134" s="25"/>
-      <c r="AK134" s="228"/>
-      <c r="AL134" s="229"/>
+      <c r="AK134" s="189"/>
+      <c r="AL134" s="190"/>
     </row>
-    <row r="135" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="135" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B135" s="13" t="s">
         <v>147</v>
       </c>
@@ -25809,8 +25812,8 @@
       <c r="AA135" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="AB135" s="223"/>
-      <c r="AC135" s="148"/>
+      <c r="AB135" s="164"/>
+      <c r="AC135" s="165"/>
       <c r="AD135" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25821,10 +25824,10 @@
       <c r="AH135" s="27"/>
       <c r="AI135" s="27"/>
       <c r="AJ135" s="28"/>
-      <c r="AK135" s="228"/>
-      <c r="AL135" s="229"/>
+      <c r="AK135" s="189"/>
+      <c r="AL135" s="190"/>
     </row>
-    <row r="136" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="136" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B136" s="13" t="s">
         <v>212</v>
       </c>
@@ -25905,8 +25908,8 @@
       <c r="AA136" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="AB136" s="223"/>
-      <c r="AC136" s="148"/>
+      <c r="AB136" s="164"/>
+      <c r="AC136" s="165"/>
       <c r="AD136" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -25917,10 +25920,10 @@
       <c r="AH136" s="27"/>
       <c r="AI136" s="27"/>
       <c r="AJ136" s="27"/>
-      <c r="AK136" s="228"/>
-      <c r="AL136" s="229"/>
+      <c r="AK136" s="189"/>
+      <c r="AL136" s="190"/>
     </row>
-    <row r="137" spans="1:40" s="12" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="2.1">
+    <row r="137" spans="2:38" s="12" customFormat="1" ht="94.5" customHeight="1" x14ac:dyDescent="2.1">
       <c r="B137" s="13" t="s">
         <v>148</v>
       </c>
@@ -26001,8 +26004,8 @@
       <c r="AA137" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="AB137" s="223"/>
-      <c r="AC137" s="148"/>
+      <c r="AB137" s="164"/>
+      <c r="AC137" s="165"/>
       <c r="AD137" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -26013,10 +26016,10 @@
       <c r="AH137"/>
       <c r="AI137"/>
       <c r="AJ137"/>
-      <c r="AK137" s="228"/>
-      <c r="AL137" s="229"/>
+      <c r="AK137" s="189"/>
+      <c r="AL137" s="190"/>
     </row>
-    <row r="138" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
+    <row r="138" spans="2:38" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B138" s="13" t="s">
         <v>149</v>
       </c>
@@ -26097,8 +26100,8 @@
       <c r="AA138" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="AB138" s="223"/>
-      <c r="AC138" s="148"/>
+      <c r="AB138" s="164"/>
+      <c r="AC138" s="165"/>
       <c r="AD138" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -26109,10 +26112,10 @@
       <c r="AH138" s="27"/>
       <c r="AI138" s="27"/>
       <c r="AJ138" s="28"/>
-      <c r="AK138" s="228"/>
-      <c r="AL138" s="229"/>
+      <c r="AK138" s="189"/>
+      <c r="AL138" s="190"/>
     </row>
-    <row r="139" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
+    <row r="139" spans="2:38" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
       <c r="B139" s="13" t="s">
         <v>150</v>
       </c>
@@ -26193,8 +26196,8 @@
       <c r="AA139" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="AB139" s="223"/>
-      <c r="AC139" s="148"/>
+      <c r="AB139" s="164"/>
+      <c r="AC139" s="165"/>
       <c r="AD139" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -26205,10 +26208,10 @@
       <c r="AH139" s="27"/>
       <c r="AI139" s="27"/>
       <c r="AJ139" s="28"/>
-      <c r="AK139" s="228"/>
-      <c r="AL139" s="229"/>
+      <c r="AK139" s="189"/>
+      <c r="AL139" s="190"/>
     </row>
-    <row r="140" spans="1:40" s="12" customFormat="1" ht="147" thickBot="1" x14ac:dyDescent="2.15">
+    <row r="140" spans="2:38" s="12" customFormat="1" ht="147" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B140" s="13" t="s">
         <v>151</v>
       </c>
@@ -26289,8 +26292,8 @@
       <c r="AA140" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="AB140" s="223"/>
-      <c r="AC140" s="148"/>
+      <c r="AB140" s="164"/>
+      <c r="AC140" s="165"/>
       <c r="AD140" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
@@ -26301,10 +26304,10 @@
       <c r="AH140" s="84"/>
       <c r="AI140" s="84"/>
       <c r="AJ140" s="85"/>
-      <c r="AK140" s="228"/>
-      <c r="AL140" s="229"/>
+      <c r="AK140" s="189"/>
+      <c r="AL140" s="190"/>
     </row>
-    <row r="141" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
+    <row r="141" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B141" s="13"/>
       <c r="C141" s="30">
         <f>SUM(C129:C140)</f>
@@ -26396,24 +26399,24 @@
       <c r="Y141" s="14"/>
       <c r="Z141" s="14"/>
       <c r="AA141" s="13"/>
-      <c r="AB141" s="224"/>
-      <c r="AC141" s="149"/>
+      <c r="AB141" s="166"/>
+      <c r="AC141" s="167"/>
       <c r="AD141" s="16">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AE141" s="17"/>
-      <c r="AF141" s="184" t="s">
+      <c r="AF141" s="183" t="s">
         <v>152</v>
       </c>
-      <c r="AG141" s="185"/>
-      <c r="AH141" s="185"/>
-      <c r="AI141" s="185"/>
-      <c r="AJ141" s="185"/>
-      <c r="AK141" s="228"/>
-      <c r="AL141" s="229"/>
+      <c r="AG141" s="184"/>
+      <c r="AH141" s="184"/>
+      <c r="AI141" s="184"/>
+      <c r="AJ141" s="184"/>
+      <c r="AK141" s="189"/>
+      <c r="AL141" s="190"/>
     </row>
-    <row r="142" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
+    <row r="142" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B142" s="13" t="s">
         <v>223</v>
       </c>
@@ -26506,12 +26509,12 @@
       <c r="AH142" s="133"/>
       <c r="AI142" s="133"/>
       <c r="AJ142" s="133"/>
-      <c r="AK142" s="228"/>
-      <c r="AL142" s="229"/>
+      <c r="AK142" s="189"/>
+      <c r="AL142" s="190"/>
     </row>
-    <row r="143" spans="1:40" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
+    <row r="143" spans="2:38" s="12" customFormat="1" ht="113.25" customHeight="1" thickBot="1" x14ac:dyDescent="2.15">
       <c r="B143" s="13" t="s">
-        <v>153</v>
+        <v>225</v>
       </c>
       <c r="C143" s="14">
         <v>0</v>
@@ -26576,7 +26579,7 @@
       <c r="W143" s="14">
         <v>0</v>
       </c>
-      <c r="X143" s="112">
+      <c r="X143" s="113">
         <v>0</v>
       </c>
       <c r="Y143" s="14">
@@ -26588,192 +26591,186 @@
         <v>0</v>
       </c>
       <c r="AA143" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="AB143" s="178"/>
-      <c r="AC143" s="179"/>
+        <v>225</v>
+      </c>
+      <c r="AB143" s="130"/>
+      <c r="AC143" s="131"/>
       <c r="AD143" s="16">
         <f>X143</f>
         <v>0</v>
       </c>
       <c r="AE143" s="17"/>
-      <c r="AF143" s="235">
-        <f>AD143+AD142</f>
-        <v>0</v>
-      </c>
-      <c r="AG143" s="185"/>
-      <c r="AH143" s="185"/>
-      <c r="AI143" s="185"/>
-      <c r="AJ143" s="185"/>
-      <c r="AK143" s="228"/>
-      <c r="AL143" s="229"/>
+      <c r="AF143" s="132"/>
+      <c r="AG143" s="133"/>
+      <c r="AH143" s="133"/>
+      <c r="AI143" s="133"/>
+      <c r="AJ143" s="133"/>
+      <c r="AK143" s="189"/>
+      <c r="AL143" s="190"/>
     </row>
-    <row r="144" spans="1:40" s="88" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="A144"/>
-      <c r="B144" s="86" t="s">
+    <row r="144" spans="2:38" s="12" customFormat="1" ht="146.25" x14ac:dyDescent="2.1">
+      <c r="B144" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C144" s="14">
+        <v>0</v>
+      </c>
+      <c r="D144" s="14">
+        <v>0</v>
+      </c>
+      <c r="E144" s="14">
+        <v>0</v>
+      </c>
+      <c r="F144" s="14">
+        <v>0</v>
+      </c>
+      <c r="G144" s="14">
+        <v>0</v>
+      </c>
+      <c r="H144" s="14">
+        <v>0</v>
+      </c>
+      <c r="I144" s="14">
+        <v>0</v>
+      </c>
+      <c r="J144" s="14">
+        <v>0</v>
+      </c>
+      <c r="K144" s="14">
+        <v>0</v>
+      </c>
+      <c r="L144" s="14">
+        <v>0</v>
+      </c>
+      <c r="M144" s="14">
+        <v>0</v>
+      </c>
+      <c r="N144" s="14">
+        <v>0</v>
+      </c>
+      <c r="O144" s="14">
+        <v>0</v>
+      </c>
+      <c r="P144" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q144" s="14">
+        <v>0</v>
+      </c>
+      <c r="R144" s="14">
+        <v>0</v>
+      </c>
+      <c r="S144" s="14">
+        <v>0</v>
+      </c>
+      <c r="T144" s="14">
+        <v>0</v>
+      </c>
+      <c r="U144" s="14">
+        <v>0</v>
+      </c>
+      <c r="V144" s="14">
+        <v>0</v>
+      </c>
+      <c r="W144" s="14">
+        <v>0</v>
+      </c>
+      <c r="X144" s="112">
+        <v>0</v>
+      </c>
+      <c r="Y144" s="14">
+        <f>SUM(C144,E144,G144,I144,K144,,M144,O144,Q144,S144,U144,W144)</f>
+        <v>0</v>
+      </c>
+      <c r="Z144" s="14">
+        <f>SUM(D144,F144,H144,J144,L144,,N144,P144,R144,T144,V144)</f>
+        <v>0</v>
+      </c>
+      <c r="AA144" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB144" s="157"/>
+      <c r="AC144" s="158"/>
+      <c r="AD144" s="16">
+        <f>X144</f>
+        <v>0</v>
+      </c>
+      <c r="AE144" s="17"/>
+      <c r="AF144" s="185">
+        <f>AD144+AD142</f>
+        <v>0</v>
+      </c>
+      <c r="AG144" s="184"/>
+      <c r="AH144" s="184"/>
+      <c r="AI144" s="184"/>
+      <c r="AJ144" s="184"/>
+      <c r="AK144" s="189"/>
+      <c r="AL144" s="190"/>
+    </row>
+    <row r="145" spans="1:40" s="88" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="A145"/>
+      <c r="B145" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="C144" s="134" t="s">
+      <c r="C145" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D144" s="135"/>
-      <c r="E144" s="134" t="s">
+      <c r="D145" s="144"/>
+      <c r="E145" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F144" s="135"/>
-      <c r="G144" s="134" t="s">
+      <c r="F145" s="144"/>
+      <c r="G145" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H144" s="135"/>
-      <c r="I144" s="134" t="s">
+      <c r="H145" s="144"/>
+      <c r="I145" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J144" s="135"/>
-      <c r="K144" s="134" t="s">
+      <c r="J145" s="144"/>
+      <c r="K145" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L144" s="135"/>
-      <c r="M144" s="134" t="s">
+      <c r="L145" s="144"/>
+      <c r="M145" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N144" s="135"/>
-      <c r="O144" s="134" t="s">
+      <c r="N145" s="144"/>
+      <c r="O145" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P144" s="135"/>
-      <c r="Q144" s="134" t="s">
+      <c r="P145" s="144"/>
+      <c r="Q145" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R144" s="135"/>
-      <c r="S144" s="134" t="s">
+      <c r="R145" s="144"/>
+      <c r="S145" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T144" s="135"/>
-      <c r="U144" s="134" t="s">
+      <c r="T145" s="144"/>
+      <c r="U145" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V144" s="135"/>
-      <c r="W144" s="9" t="s">
+      <c r="V145" s="144"/>
+      <c r="W145" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="X144" s="118"/>
-      <c r="Y144" s="49" t="s">
+      <c r="X145" s="118"/>
+      <c r="Y145" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="Z144" s="49" t="s">
+      <c r="Z145" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AA144" s="86" t="s">
+      <c r="AA145" s="86" t="s">
         <v>154</v>
       </c>
-      <c r="AB144" s="233"/>
-      <c r="AC144" s="234"/>
-      <c r="AD144" s="6" t="s">
+      <c r="AB145" s="160"/>
+      <c r="AC145" s="161"/>
+      <c r="AD145" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AE144" s="7"/>
-      <c r="AF144" s="2"/>
-      <c r="AG144" s="2"/>
-      <c r="AH144" s="2"/>
-      <c r="AI144" s="2"/>
-      <c r="AJ144" s="2"/>
-      <c r="AK144" s="87"/>
-      <c r="AL144" s="87"/>
-      <c r="AM144" s="47"/>
-      <c r="AN144" s="47"/>
-    </row>
-    <row r="145" spans="1:40" s="47" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="A145" s="12"/>
-      <c r="B145" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C145" s="14">
-        <v>0</v>
-      </c>
-      <c r="D145" s="14">
-        <v>0</v>
-      </c>
-      <c r="E145" s="14">
-        <v>0</v>
-      </c>
-      <c r="F145" s="14">
-        <v>0</v>
-      </c>
-      <c r="G145" s="14">
-        <v>0</v>
-      </c>
-      <c r="H145" s="14">
-        <v>0</v>
-      </c>
-      <c r="I145" s="14">
-        <v>0</v>
-      </c>
-      <c r="J145" s="14">
-        <v>0</v>
-      </c>
-      <c r="K145" s="14">
-        <v>0</v>
-      </c>
-      <c r="L145" s="14">
-        <v>0</v>
-      </c>
-      <c r="M145" s="14">
-        <v>0</v>
-      </c>
-      <c r="N145" s="14">
-        <v>0</v>
-      </c>
-      <c r="O145" s="14">
-        <v>0</v>
-      </c>
-      <c r="P145" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q145" s="14">
-        <v>0</v>
-      </c>
-      <c r="R145" s="14">
-        <v>0</v>
-      </c>
-      <c r="S145" s="14">
-        <v>0</v>
-      </c>
-      <c r="T145" s="14">
-        <v>0</v>
-      </c>
-      <c r="U145" s="14">
-        <v>0</v>
-      </c>
-      <c r="V145" s="14">
-        <v>0</v>
-      </c>
-      <c r="W145" s="14">
-        <v>0</v>
-      </c>
-      <c r="X145" s="112">
-        <v>0</v>
-      </c>
-      <c r="Y145" s="14">
-        <f>SUM(C145,E145,G145,I145,K145,,M145,O145,Q145,S145,U145,W145)</f>
-        <v>0</v>
-      </c>
-      <c r="Z145" s="14">
-        <f>SUM(D145,F145,H145,J145,L145,,N145,P145,R145,T145,V145)</f>
-        <v>0</v>
-      </c>
-      <c r="AA145" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="AB145" s="180">
-        <f>SUM(Y145:Y146)</f>
-        <v>0</v>
-      </c>
-      <c r="AC145" s="181"/>
-      <c r="AD145" s="16">
-        <f>X145</f>
-        <v>0</v>
-      </c>
-      <c r="AE145" s="17"/>
+      <c r="AE145" s="7"/>
       <c r="AF145" s="2"/>
       <c r="AG145" s="2"/>
       <c r="AH145" s="2"/>
@@ -26781,11 +26778,13 @@
       <c r="AJ145" s="2"/>
       <c r="AK145" s="87"/>
       <c r="AL145" s="87"/>
+      <c r="AM145" s="47"/>
+      <c r="AN145" s="47"/>
     </row>
     <row r="146" spans="1:40" s="47" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A146" s="12"/>
       <c r="B146" s="13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C146" s="14">
         <v>0</v>
@@ -26862,10 +26861,13 @@
         <v>0</v>
       </c>
       <c r="AA146" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="AB146" s="182"/>
-      <c r="AC146" s="183"/>
+        <v>155</v>
+      </c>
+      <c r="AB146" s="179">
+        <f>SUM(Y146:Y147)</f>
+        <v>0</v>
+      </c>
+      <c r="AC146" s="180"/>
       <c r="AD146" s="16">
         <f>X146</f>
         <v>0</v>
@@ -26876,177 +26878,172 @@
       <c r="AH146" s="2"/>
       <c r="AI146" s="2"/>
       <c r="AJ146" s="2"/>
-      <c r="AK146" s="89"/>
-      <c r="AL146" s="89"/>
-      <c r="AM146" s="88"/>
-      <c r="AN146" s="88"/>
+      <c r="AK146" s="87"/>
+      <c r="AL146" s="87"/>
     </row>
-    <row r="147" spans="1:40" s="88" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="A147"/>
-      <c r="B147" s="86" t="s">
-        <v>211</v>
-      </c>
-      <c r="C147" s="134" t="s">
-        <v>1</v>
-      </c>
-      <c r="D147" s="135"/>
-      <c r="E147" s="134" t="s">
-        <v>2</v>
-      </c>
-      <c r="F147" s="135"/>
-      <c r="G147" s="134" t="s">
-        <v>3</v>
-      </c>
-      <c r="H147" s="135"/>
-      <c r="I147" s="134" t="s">
-        <v>4</v>
-      </c>
-      <c r="J147" s="135"/>
-      <c r="K147" s="134" t="s">
-        <v>5</v>
-      </c>
-      <c r="L147" s="135"/>
-      <c r="M147" s="134" t="s">
-        <v>6</v>
-      </c>
-      <c r="N147" s="135"/>
-      <c r="O147" s="134" t="s">
-        <v>7</v>
-      </c>
-      <c r="P147" s="135"/>
-      <c r="Q147" s="134" t="s">
-        <v>8</v>
-      </c>
-      <c r="R147" s="135"/>
-      <c r="S147" s="134" t="s">
-        <v>9</v>
-      </c>
-      <c r="T147" s="135"/>
-      <c r="U147" s="134" t="s">
-        <v>10</v>
-      </c>
-      <c r="V147" s="135"/>
-      <c r="W147" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="X147" s="118"/>
-      <c r="Y147" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z147" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="AA147" s="86" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB147" s="233"/>
-      <c r="AC147" s="234"/>
-      <c r="AD147" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE147" s="7"/>
+    <row r="147" spans="1:40" s="47" customFormat="1" ht="112.5" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="A147" s="12"/>
+      <c r="B147" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="C147" s="14">
+        <v>0</v>
+      </c>
+      <c r="D147" s="14">
+        <v>0</v>
+      </c>
+      <c r="E147" s="14">
+        <v>0</v>
+      </c>
+      <c r="F147" s="14">
+        <v>0</v>
+      </c>
+      <c r="G147" s="14">
+        <v>0</v>
+      </c>
+      <c r="H147" s="14">
+        <v>0</v>
+      </c>
+      <c r="I147" s="14">
+        <v>0</v>
+      </c>
+      <c r="J147" s="14">
+        <v>0</v>
+      </c>
+      <c r="K147" s="14">
+        <v>0</v>
+      </c>
+      <c r="L147" s="14">
+        <v>0</v>
+      </c>
+      <c r="M147" s="14">
+        <v>0</v>
+      </c>
+      <c r="N147" s="14">
+        <v>0</v>
+      </c>
+      <c r="O147" s="14">
+        <v>0</v>
+      </c>
+      <c r="P147" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q147" s="14">
+        <v>0</v>
+      </c>
+      <c r="R147" s="14">
+        <v>0</v>
+      </c>
+      <c r="S147" s="14">
+        <v>0</v>
+      </c>
+      <c r="T147" s="14">
+        <v>0</v>
+      </c>
+      <c r="U147" s="14">
+        <v>0</v>
+      </c>
+      <c r="V147" s="14">
+        <v>0</v>
+      </c>
+      <c r="W147" s="14">
+        <v>0</v>
+      </c>
+      <c r="X147" s="112">
+        <v>0</v>
+      </c>
+      <c r="Y147" s="14">
+        <f>SUM(C147,E147,G147,I147,K147,,M147,O147,Q147,S147,U147,W147)</f>
+        <v>0</v>
+      </c>
+      <c r="Z147" s="14">
+        <f>SUM(D147,F147,H147,J147,L147,,N147,P147,R147,T147,V147)</f>
+        <v>0</v>
+      </c>
+      <c r="AA147" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="AB147" s="181"/>
+      <c r="AC147" s="182"/>
+      <c r="AD147" s="16">
+        <f>X147</f>
+        <v>0</v>
+      </c>
+      <c r="AE147" s="17"/>
       <c r="AF147" s="2"/>
       <c r="AG147" s="2"/>
       <c r="AH147" s="2"/>
       <c r="AI147" s="2"/>
       <c r="AJ147" s="2"/>
-      <c r="AK147" s="87"/>
-      <c r="AL147" s="87"/>
-      <c r="AM147" s="47"/>
-      <c r="AN147" s="47"/>
+      <c r="AK147" s="89"/>
+      <c r="AL147" s="89"/>
+      <c r="AM147" s="88"/>
+      <c r="AN147" s="88"/>
     </row>
-    <row r="148" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="A148" s="12"/>
-      <c r="B148" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C148" s="14">
-        <v>0</v>
-      </c>
-      <c r="D148" s="14">
-        <v>0</v>
-      </c>
-      <c r="E148" s="14">
-        <v>0</v>
-      </c>
-      <c r="F148" s="14">
-        <v>0</v>
-      </c>
-      <c r="G148" s="14">
-        <v>0</v>
-      </c>
-      <c r="H148" s="14">
-        <v>0</v>
-      </c>
-      <c r="I148" s="14">
-        <v>0</v>
-      </c>
-      <c r="J148" s="14">
-        <v>0</v>
-      </c>
-      <c r="K148" s="14">
-        <v>0</v>
-      </c>
-      <c r="L148" s="14">
-        <v>0</v>
-      </c>
-      <c r="M148" s="14">
-        <v>0</v>
-      </c>
-      <c r="N148" s="14">
-        <v>0</v>
-      </c>
-      <c r="O148" s="14">
-        <v>0</v>
-      </c>
-      <c r="P148" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q148" s="14">
-        <v>0</v>
-      </c>
-      <c r="R148" s="14">
-        <v>0</v>
-      </c>
-      <c r="S148" s="14">
-        <v>0</v>
-      </c>
-      <c r="T148" s="14">
-        <v>0</v>
-      </c>
-      <c r="U148" s="14">
-        <v>0</v>
-      </c>
-      <c r="V148" s="14">
-        <v>0</v>
-      </c>
-      <c r="W148" s="14">
-        <v>0</v>
-      </c>
-      <c r="X148" s="112">
-        <v>0</v>
-      </c>
-      <c r="Y148" s="14">
-        <f t="shared" ref="Y148:Y158" si="39">SUM(C148,E148,G148,I148,K148,,M148,O148,Q148,S148,U148,W148)</f>
-        <v>0</v>
-      </c>
-      <c r="Z148" s="14">
-        <f t="shared" ref="Z148:Z158" si="40">SUM(D148,F148,H148,J148,L148,,N148,P148,R148,T148,V148)</f>
-        <v>0</v>
-      </c>
-      <c r="AA148" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="AB148" s="222">
-        <f>SUM(Y148:Y158)</f>
-        <v>0</v>
-      </c>
-      <c r="AC148" s="147"/>
-      <c r="AD148" s="16">
-        <f>X148</f>
-        <v>0</v>
-      </c>
-      <c r="AE148" s="17"/>
+    <row r="148" spans="1:40" s="88" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="A148"/>
+      <c r="B148" s="86" t="s">
+        <v>211</v>
+      </c>
+      <c r="C148" s="143" t="s">
+        <v>1</v>
+      </c>
+      <c r="D148" s="144"/>
+      <c r="E148" s="143" t="s">
+        <v>2</v>
+      </c>
+      <c r="F148" s="144"/>
+      <c r="G148" s="143" t="s">
+        <v>3</v>
+      </c>
+      <c r="H148" s="144"/>
+      <c r="I148" s="143" t="s">
+        <v>4</v>
+      </c>
+      <c r="J148" s="144"/>
+      <c r="K148" s="143" t="s">
+        <v>5</v>
+      </c>
+      <c r="L148" s="144"/>
+      <c r="M148" s="143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N148" s="144"/>
+      <c r="O148" s="143" t="s">
+        <v>7</v>
+      </c>
+      <c r="P148" s="144"/>
+      <c r="Q148" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="R148" s="144"/>
+      <c r="S148" s="143" t="s">
+        <v>9</v>
+      </c>
+      <c r="T148" s="144"/>
+      <c r="U148" s="143" t="s">
+        <v>10</v>
+      </c>
+      <c r="V148" s="144"/>
+      <c r="W148" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="X148" s="118"/>
+      <c r="Y148" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z148" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA148" s="86" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB148" s="160"/>
+      <c r="AC148" s="161"/>
+      <c r="AD148" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE148" s="7"/>
       <c r="AF148" s="2"/>
       <c r="AG148" s="2"/>
       <c r="AH148" s="2"/>
@@ -27054,11 +27051,13 @@
       <c r="AJ148" s="2"/>
       <c r="AK148" s="87"/>
       <c r="AL148" s="87"/>
+      <c r="AM148" s="47"/>
+      <c r="AN148" s="47"/>
     </row>
     <row r="149" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A149" s="12"/>
       <c r="B149" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C149" s="14">
         <v>0</v>
@@ -27127,20 +27126,23 @@
         <v>0</v>
       </c>
       <c r="Y149" s="14">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="Y149:Y159" si="39">SUM(C149,E149,G149,I149,K149,,M149,O149,Q149,S149,U149,W149)</f>
         <v>0</v>
       </c>
       <c r="Z149" s="14">
-        <f t="shared" si="40"/>
+        <f t="shared" ref="Z149:Z159" si="40">SUM(D149,F149,H149,J149,L149,,N149,P149,R149,T149,V149)</f>
         <v>0</v>
       </c>
       <c r="AA149" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="AB149" s="223"/>
-      <c r="AC149" s="148"/>
+        <v>158</v>
+      </c>
+      <c r="AB149" s="162">
+        <f>SUM(Y149:Y159)</f>
+        <v>0</v>
+      </c>
+      <c r="AC149" s="163"/>
       <c r="AD149" s="16">
-        <f t="shared" ref="AD149:AD158" si="41">X149</f>
+        <f>X149</f>
         <v>0</v>
       </c>
       <c r="AE149" s="17"/>
@@ -27152,10 +27154,10 @@
       <c r="AK149" s="87"/>
       <c r="AL149" s="87"/>
     </row>
-    <row r="150" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="2.35">
+    <row r="150" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A150" s="12"/>
       <c r="B150" s="13" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C150" s="14">
         <v>0</v>
@@ -27232,12 +27234,12 @@
         <v>0</v>
       </c>
       <c r="AA150" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="AB150" s="223"/>
-      <c r="AC150" s="148"/>
+        <v>157</v>
+      </c>
+      <c r="AB150" s="164"/>
+      <c r="AC150" s="165"/>
       <c r="AD150" s="16">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="AD150:AD159" si="41">X150</f>
         <v>0</v>
       </c>
       <c r="AE150" s="17"/>
@@ -27249,10 +27251,10 @@
       <c r="AK150" s="87"/>
       <c r="AL150" s="87"/>
     </row>
-    <row r="151" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
+    <row r="151" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="2.35">
       <c r="A151" s="12"/>
       <c r="B151" s="13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C151" s="14">
         <v>0</v>
@@ -27329,10 +27331,10 @@
         <v>0</v>
       </c>
       <c r="AA151" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="AB151" s="223"/>
-      <c r="AC151" s="148"/>
+        <v>159</v>
+      </c>
+      <c r="AB151" s="164"/>
+      <c r="AC151" s="165"/>
       <c r="AD151" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27349,7 +27351,7 @@
     <row r="152" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A152" s="12"/>
       <c r="B152" s="13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C152" s="14">
         <v>0</v>
@@ -27426,10 +27428,10 @@
         <v>0</v>
       </c>
       <c r="AA152" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="AB152" s="223"/>
-      <c r="AC152" s="148"/>
+        <v>160</v>
+      </c>
+      <c r="AB152" s="164"/>
+      <c r="AC152" s="165"/>
       <c r="AD152" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27446,7 +27448,7 @@
     <row r="153" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A153" s="12"/>
       <c r="B153" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C153" s="14">
         <v>0</v>
@@ -27523,10 +27525,10 @@
         <v>0</v>
       </c>
       <c r="AA153" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="AB153" s="223"/>
-      <c r="AC153" s="148"/>
+        <v>161</v>
+      </c>
+      <c r="AB153" s="164"/>
+      <c r="AC153" s="165"/>
       <c r="AD153" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27543,7 +27545,7 @@
     <row r="154" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A154" s="12"/>
       <c r="B154" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C154" s="14">
         <v>0</v>
@@ -27620,10 +27622,10 @@
         <v>0</v>
       </c>
       <c r="AA154" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB154" s="223"/>
-      <c r="AC154" s="148"/>
+        <v>162</v>
+      </c>
+      <c r="AB154" s="164"/>
+      <c r="AC154" s="165"/>
       <c r="AD154" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27640,7 +27642,7 @@
     <row r="155" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A155" s="12"/>
       <c r="B155" s="13" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C155" s="14">
         <v>0</v>
@@ -27717,10 +27719,10 @@
         <v>0</v>
       </c>
       <c r="AA155" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="AB155" s="223"/>
-      <c r="AC155" s="148"/>
+        <v>163</v>
+      </c>
+      <c r="AB155" s="164"/>
+      <c r="AC155" s="165"/>
       <c r="AD155" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27734,10 +27736,10 @@
       <c r="AK155" s="87"/>
       <c r="AL155" s="87"/>
     </row>
-    <row r="156" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="2.35">
+    <row r="156" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="A156" s="12"/>
       <c r="B156" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C156" s="14">
         <v>0</v>
@@ -27814,10 +27816,10 @@
         <v>0</v>
       </c>
       <c r="AA156" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="AB156" s="223"/>
-      <c r="AC156" s="148"/>
+        <v>164</v>
+      </c>
+      <c r="AB156" s="164"/>
+      <c r="AC156" s="165"/>
       <c r="AD156" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27834,7 +27836,7 @@
     <row r="157" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="2.35">
       <c r="A157" s="12"/>
       <c r="B157" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C157" s="14">
         <v>0</v>
@@ -27911,10 +27913,10 @@
         <v>0</v>
       </c>
       <c r="AA157" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="AB157" s="223"/>
-      <c r="AC157" s="148"/>
+        <v>165</v>
+      </c>
+      <c r="AB157" s="164"/>
+      <c r="AC157" s="165"/>
       <c r="AD157" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -27928,10 +27930,10 @@
       <c r="AK157" s="87"/>
       <c r="AL157" s="87"/>
     </row>
-    <row r="158" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
+    <row r="158" spans="1:40" s="47" customFormat="1" x14ac:dyDescent="2.35">
       <c r="A158" s="12"/>
       <c r="B158" s="13" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C158" s="14">
         <v>0</v>
@@ -28008,10 +28010,10 @@
         <v>0</v>
       </c>
       <c r="AA158" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="AB158" s="224"/>
-      <c r="AC158" s="149"/>
+        <v>167</v>
+      </c>
+      <c r="AB158" s="164"/>
+      <c r="AC158" s="165"/>
       <c r="AD158" s="16">
         <f t="shared" si="41"/>
         <v>0</v>
@@ -28022,104 +28024,95 @@
       <c r="AH158" s="2"/>
       <c r="AI158" s="2"/>
       <c r="AJ158" s="2"/>
-      <c r="AK158" s="90"/>
-      <c r="AL158" s="90"/>
-      <c r="AM158" s="91"/>
-      <c r="AN158" s="88"/>
+      <c r="AK158" s="87"/>
+      <c r="AL158" s="87"/>
     </row>
-    <row r="159" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
-      <c r="B159" s="13"/>
-      <c r="C159" s="30">
-        <f t="shared" ref="C159:W159" si="42">SUM(C148:C158)</f>
-        <v>0</v>
-      </c>
-      <c r="D159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="E159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="F159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="G159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="H159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="I159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="J159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="K159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="L159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="M159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="N159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="O159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="P159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="Q159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="R159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="S159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="T159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="U159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="V159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="W159" s="30">
-        <f t="shared" si="42"/>
-        <v>0</v>
-      </c>
-      <c r="X159" s="113"/>
-      <c r="Y159" s="14"/>
-      <c r="Z159" s="14"/>
-      <c r="AA159" s="13"/>
-      <c r="AB159" s="178"/>
-      <c r="AC159" s="179"/>
+    <row r="159" spans="1:40" s="47" customFormat="1" ht="116.25" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="A159" s="12"/>
+      <c r="B159" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="C159" s="14">
+        <v>0</v>
+      </c>
+      <c r="D159" s="14">
+        <v>0</v>
+      </c>
+      <c r="E159" s="14">
+        <v>0</v>
+      </c>
+      <c r="F159" s="14">
+        <v>0</v>
+      </c>
+      <c r="G159" s="14">
+        <v>0</v>
+      </c>
+      <c r="H159" s="14">
+        <v>0</v>
+      </c>
+      <c r="I159" s="14">
+        <v>0</v>
+      </c>
+      <c r="J159" s="14">
+        <v>0</v>
+      </c>
+      <c r="K159" s="14">
+        <v>0</v>
+      </c>
+      <c r="L159" s="14">
+        <v>0</v>
+      </c>
+      <c r="M159" s="14">
+        <v>0</v>
+      </c>
+      <c r="N159" s="14">
+        <v>0</v>
+      </c>
+      <c r="O159" s="14">
+        <v>0</v>
+      </c>
+      <c r="P159" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q159" s="14">
+        <v>0</v>
+      </c>
+      <c r="R159" s="14">
+        <v>0</v>
+      </c>
+      <c r="S159" s="14">
+        <v>0</v>
+      </c>
+      <c r="T159" s="14">
+        <v>0</v>
+      </c>
+      <c r="U159" s="14">
+        <v>0</v>
+      </c>
+      <c r="V159" s="14">
+        <v>0</v>
+      </c>
+      <c r="W159" s="14">
+        <v>0</v>
+      </c>
+      <c r="X159" s="112">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="14">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
+      <c r="Z159" s="14">
+        <f t="shared" si="40"/>
+        <v>0</v>
+      </c>
+      <c r="AA159" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB159" s="166"/>
+      <c r="AC159" s="167"/>
       <c r="AD159" s="16">
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="AE159" s="17"/>
@@ -28128,190 +28121,213 @@
       <c r="AH159" s="2"/>
       <c r="AI159" s="2"/>
       <c r="AJ159" s="2"/>
-      <c r="AK159" s="92"/>
-      <c r="AL159" s="92"/>
+      <c r="AK159" s="90"/>
+      <c r="AL159" s="90"/>
+      <c r="AM159" s="91"/>
+      <c r="AN159" s="88"/>
     </row>
-    <row r="160" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="1.85">
-      <c r="B160" s="138" t="s">
-        <v>220</v>
-      </c>
-      <c r="C160" s="139"/>
-      <c r="D160" s="139"/>
-      <c r="E160" s="139"/>
-      <c r="F160" s="139"/>
-      <c r="G160" s="139"/>
-      <c r="H160" s="139"/>
-      <c r="I160" s="139"/>
-      <c r="J160" s="139"/>
-      <c r="K160" s="139"/>
-      <c r="L160" s="139"/>
-      <c r="M160" s="139"/>
-      <c r="N160" s="139"/>
-      <c r="O160" s="139"/>
-      <c r="P160" s="139"/>
-      <c r="Q160" s="139"/>
-      <c r="R160" s="139"/>
-      <c r="S160" s="139"/>
-      <c r="T160" s="139"/>
-      <c r="U160" s="139"/>
-      <c r="V160" s="139"/>
-      <c r="W160" s="139"/>
-      <c r="X160" s="139"/>
-      <c r="Y160" s="139"/>
-      <c r="Z160" s="139"/>
-      <c r="AA160" s="139"/>
-      <c r="AB160" s="139"/>
-      <c r="AC160" s="139"/>
-      <c r="AD160" s="139"/>
-      <c r="AE160" s="1"/>
+    <row r="160" spans="1:40" s="12" customFormat="1" ht="113.25" customHeight="1" x14ac:dyDescent="2.1">
+      <c r="B160" s="13"/>
+      <c r="C160" s="30">
+        <f t="shared" ref="C160:W160" si="42">SUM(C149:C159)</f>
+        <v>0</v>
+      </c>
+      <c r="D160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="E160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="F160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="G160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="H160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="I160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="J160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="K160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="L160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="M160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="N160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="O160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="P160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="Q160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="R160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="S160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="T160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="U160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="V160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="W160" s="30">
+        <f t="shared" si="42"/>
+        <v>0</v>
+      </c>
+      <c r="X160" s="113"/>
+      <c r="Y160" s="14"/>
+      <c r="Z160" s="14"/>
+      <c r="AA160" s="13"/>
+      <c r="AB160" s="157"/>
+      <c r="AC160" s="158"/>
+      <c r="AD160" s="16">
+        <v>0</v>
+      </c>
+      <c r="AE160" s="17"/>
+      <c r="AF160" s="2"/>
+      <c r="AG160" s="2"/>
+      <c r="AH160" s="2"/>
+      <c r="AI160" s="2"/>
+      <c r="AJ160" s="2"/>
       <c r="AK160" s="92"/>
       <c r="AL160" s="92"/>
     </row>
-    <row r="161" spans="1:40" s="88" customFormat="1" ht="138.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="A161"/>
-      <c r="B161" s="136" t="s">
+    <row r="161" spans="1:40" ht="126" customHeight="1" x14ac:dyDescent="1.85">
+      <c r="B161" s="177" t="s">
+        <v>220</v>
+      </c>
+      <c r="C161" s="178"/>
+      <c r="D161" s="178"/>
+      <c r="E161" s="178"/>
+      <c r="F161" s="178"/>
+      <c r="G161" s="178"/>
+      <c r="H161" s="178"/>
+      <c r="I161" s="178"/>
+      <c r="J161" s="178"/>
+      <c r="K161" s="178"/>
+      <c r="L161" s="178"/>
+      <c r="M161" s="178"/>
+      <c r="N161" s="178"/>
+      <c r="O161" s="178"/>
+      <c r="P161" s="178"/>
+      <c r="Q161" s="178"/>
+      <c r="R161" s="178"/>
+      <c r="S161" s="178"/>
+      <c r="T161" s="178"/>
+      <c r="U161" s="178"/>
+      <c r="V161" s="178"/>
+      <c r="W161" s="178"/>
+      <c r="X161" s="178"/>
+      <c r="Y161" s="178"/>
+      <c r="Z161" s="178"/>
+      <c r="AA161" s="178"/>
+      <c r="AB161" s="178"/>
+      <c r="AC161" s="178"/>
+      <c r="AD161" s="178"/>
+      <c r="AE161" s="1"/>
+      <c r="AK161" s="92"/>
+      <c r="AL161" s="92"/>
+    </row>
+    <row r="162" spans="1:40" s="88" customFormat="1" ht="138.75" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="A162"/>
+      <c r="B162" s="175" t="s">
         <v>169</v>
       </c>
-      <c r="C161" s="134" t="s">
+      <c r="C162" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D161" s="135"/>
-      <c r="E161" s="134" t="s">
+      <c r="D162" s="144"/>
+      <c r="E162" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F161" s="135"/>
-      <c r="G161" s="134" t="s">
+      <c r="F162" s="144"/>
+      <c r="G162" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H161" s="135"/>
-      <c r="I161" s="134" t="s">
+      <c r="H162" s="144"/>
+      <c r="I162" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J161" s="135"/>
-      <c r="K161" s="134" t="s">
+      <c r="J162" s="144"/>
+      <c r="K162" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L161" s="135"/>
-      <c r="M161" s="134" t="s">
+      <c r="L162" s="144"/>
+      <c r="M162" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N161" s="135"/>
-      <c r="O161" s="134" t="s">
+      <c r="N162" s="144"/>
+      <c r="O162" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P161" s="135"/>
-      <c r="Q161" s="134" t="s">
+      <c r="P162" s="144"/>
+      <c r="Q162" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R161" s="135"/>
-      <c r="S161" s="134" t="s">
+      <c r="R162" s="144"/>
+      <c r="S162" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T161" s="135"/>
-      <c r="U161" s="134" t="s">
+      <c r="T162" s="144"/>
+      <c r="U162" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V161" s="135"/>
-      <c r="W161" s="136" t="s">
+      <c r="V162" s="144"/>
+      <c r="W162" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="X161" s="110"/>
-      <c r="Y161" s="136" t="s">
+      <c r="X162" s="110"/>
+      <c r="Y162" s="175" t="s">
         <v>12</v>
       </c>
-      <c r="Z161" s="136" t="s">
+      <c r="Z162" s="175" t="s">
         <v>13</v>
       </c>
-      <c r="AA161" s="136" t="s">
+      <c r="AA162" s="175" t="s">
         <v>169</v>
       </c>
-      <c r="AB161" s="233"/>
-      <c r="AC161" s="234"/>
-      <c r="AD161" s="6" t="s">
+      <c r="AB162" s="160"/>
+      <c r="AC162" s="161"/>
+      <c r="AD162" s="6" t="s">
         <v>15</v>
-      </c>
-      <c r="AE161" s="7"/>
-      <c r="AF161" s="2"/>
-      <c r="AG161" s="2"/>
-      <c r="AH161" s="2"/>
-      <c r="AI161" s="2"/>
-      <c r="AJ161" s="2"/>
-      <c r="AK161" s="8"/>
-      <c r="AL161" s="8"/>
-      <c r="AM161" s="12"/>
-      <c r="AN161" s="12"/>
-    </row>
-    <row r="162" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B162" s="137"/>
-      <c r="C162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="K162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="N162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="P162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="R162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="S162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="T162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="U162" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="V162" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="W162" s="137"/>
-      <c r="X162" s="111"/>
-      <c r="Y162" s="137"/>
-      <c r="Z162" s="137"/>
-      <c r="AA162" s="137"/>
-      <c r="AB162" s="10"/>
-      <c r="AC162" s="11"/>
-      <c r="AD162" s="6">
-        <v>0</v>
       </c>
       <c r="AE162" s="7"/>
       <c r="AF162" s="2"/>
@@ -28321,98 +28337,82 @@
       <c r="AJ162" s="2"/>
       <c r="AK162" s="8"/>
       <c r="AL162" s="8"/>
+      <c r="AM162" s="12"/>
+      <c r="AN162" s="12"/>
     </row>
-    <row r="163" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B163" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="C163" s="14">
-        <v>0</v>
-      </c>
-      <c r="D163" s="14">
-        <v>0</v>
-      </c>
-      <c r="E163" s="14">
-        <v>0</v>
-      </c>
-      <c r="F163" s="14">
-        <v>0</v>
-      </c>
-      <c r="G163" s="14">
-        <v>0</v>
-      </c>
-      <c r="H163" s="14">
-        <v>0</v>
-      </c>
-      <c r="I163" s="14">
-        <v>0</v>
-      </c>
-      <c r="J163" s="14">
-        <v>0</v>
-      </c>
-      <c r="K163" s="14">
-        <v>0</v>
-      </c>
-      <c r="L163" s="14">
-        <v>0</v>
-      </c>
-      <c r="M163" s="14">
-        <v>0</v>
-      </c>
-      <c r="N163" s="14">
-        <v>0</v>
-      </c>
-      <c r="O163" s="14">
-        <v>0</v>
-      </c>
-      <c r="P163" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q163" s="14">
-        <v>0</v>
-      </c>
-      <c r="R163" s="14">
-        <v>0</v>
-      </c>
-      <c r="S163" s="14">
-        <v>0</v>
-      </c>
-      <c r="T163" s="14">
-        <v>0</v>
-      </c>
-      <c r="U163" s="14">
-        <v>0</v>
-      </c>
-      <c r="V163" s="14">
-        <v>0</v>
-      </c>
-      <c r="W163" s="14">
-        <v>0</v>
-      </c>
-      <c r="X163" s="112">
-        <v>0</v>
-      </c>
-      <c r="Y163" s="14">
-        <f t="shared" ref="Y163:Y168" si="43">SUM(C163,E163,G163,I163,K163,,M163,O163,Q163,S163,U163,W163)</f>
-        <v>0</v>
-      </c>
-      <c r="Z163" s="14">
-        <f t="shared" ref="Z163:Z168" si="44">SUM(D163,F163,H163,J163,L163,,N163,P163,R163,T163,V163)</f>
-        <v>0</v>
-      </c>
-      <c r="AA163" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="AB163" s="222">
-        <f>SUM(Y163:Y168)</f>
-        <v>0</v>
-      </c>
-      <c r="AC163" s="147"/>
-      <c r="AD163" s="16">
-        <f>X163</f>
-        <v>0</v>
-      </c>
-      <c r="AE163" s="17"/>
+    <row r="163" spans="1:40" s="4" customFormat="1" ht="138" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B163" s="176"/>
+      <c r="C163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="J163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="L163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="P163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="R163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="S163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="T163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="U163" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="V163" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="W163" s="176"/>
+      <c r="X163" s="111"/>
+      <c r="Y163" s="176"/>
+      <c r="Z163" s="176"/>
+      <c r="AA163" s="176"/>
+      <c r="AB163" s="10"/>
+      <c r="AC163" s="11"/>
+      <c r="AD163" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE163" s="7"/>
       <c r="AF163" s="2"/>
       <c r="AG163" s="2"/>
       <c r="AH163" s="2"/>
@@ -28423,7 +28423,7 @@
     </row>
     <row r="164" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B164" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C164" s="14">
         <v>0</v>
@@ -28492,20 +28492,23 @@
         <v>0</v>
       </c>
       <c r="Y164" s="14">
-        <f t="shared" si="43"/>
+        <f t="shared" ref="Y164:Y169" si="43">SUM(C164,E164,G164,I164,K164,,M164,O164,Q164,S164,U164,W164)</f>
         <v>0</v>
       </c>
       <c r="Z164" s="14">
-        <f t="shared" si="44"/>
+        <f t="shared" ref="Z164:Z169" si="44">SUM(D164,F164,H164,J164,L164,,N164,P164,R164,T164,V164)</f>
         <v>0</v>
       </c>
       <c r="AA164" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB164" s="223"/>
-      <c r="AC164" s="148"/>
+        <v>171</v>
+      </c>
+      <c r="AB164" s="162">
+        <f>SUM(Y164:Y169)</f>
+        <v>0</v>
+      </c>
+      <c r="AC164" s="163"/>
       <c r="AD164" s="16">
-        <f t="shared" ref="AD164:AD168" si="45">X164</f>
+        <f>X164</f>
         <v>0</v>
       </c>
       <c r="AE164" s="17"/>
@@ -28519,7 +28522,7 @@
     </row>
     <row r="165" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B165" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C165" s="14">
         <v>0</v>
@@ -28596,12 +28599,12 @@
         <v>0</v>
       </c>
       <c r="AA165" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="AB165" s="223"/>
-      <c r="AC165" s="148"/>
+        <v>172</v>
+      </c>
+      <c r="AB165" s="164"/>
+      <c r="AC165" s="165"/>
       <c r="AD165" s="16">
-        <f t="shared" si="45"/>
+        <f t="shared" ref="AD165:AD169" si="45">X165</f>
         <v>0</v>
       </c>
       <c r="AE165" s="17"/>
@@ -28615,7 +28618,7 @@
     </row>
     <row r="166" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B166" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C166" s="14">
         <v>0</v>
@@ -28692,10 +28695,10 @@
         <v>0</v>
       </c>
       <c r="AA166" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="AB166" s="223"/>
-      <c r="AC166" s="148"/>
+        <v>173</v>
+      </c>
+      <c r="AB166" s="164"/>
+      <c r="AC166" s="165"/>
       <c r="AD166" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28711,7 +28714,7 @@
     </row>
     <row r="167" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B167" s="13" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C167" s="14">
         <v>0</v>
@@ -28788,10 +28791,10 @@
         <v>0</v>
       </c>
       <c r="AA167" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="AB167" s="223"/>
-      <c r="AC167" s="148"/>
+        <v>174</v>
+      </c>
+      <c r="AB167" s="164"/>
+      <c r="AC167" s="165"/>
       <c r="AD167" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28807,7 +28810,7 @@
     </row>
     <row r="168" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B168" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C168" s="14">
         <v>0</v>
@@ -28884,10 +28887,10 @@
         <v>0</v>
       </c>
       <c r="AA168" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="AB168" s="224"/>
-      <c r="AC168" s="149"/>
+        <v>175</v>
+      </c>
+      <c r="AB168" s="164"/>
+      <c r="AC168" s="165"/>
       <c r="AD168" s="16">
         <f t="shared" si="45"/>
         <v>0</v>
@@ -28898,160 +28901,178 @@
       <c r="AH168" s="2"/>
       <c r="AI168" s="2"/>
       <c r="AJ168" s="2"/>
-      <c r="AK168" s="3"/>
-      <c r="AL168" s="3"/>
-      <c r="AM168" s="2"/>
-      <c r="AN168" s="2"/>
+      <c r="AK168" s="8"/>
+      <c r="AL168" s="8"/>
     </row>
-    <row r="169" spans="1:40" s="2" customFormat="1" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
-      <c r="B169" s="79" t="s">
+    <row r="169" spans="1:40" s="12" customFormat="1" ht="110.25" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B169" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C169" s="14">
+        <v>0</v>
+      </c>
+      <c r="D169" s="14">
+        <v>0</v>
+      </c>
+      <c r="E169" s="14">
+        <v>0</v>
+      </c>
+      <c r="F169" s="14">
+        <v>0</v>
+      </c>
+      <c r="G169" s="14">
+        <v>0</v>
+      </c>
+      <c r="H169" s="14">
+        <v>0</v>
+      </c>
+      <c r="I169" s="14">
+        <v>0</v>
+      </c>
+      <c r="J169" s="14">
+        <v>0</v>
+      </c>
+      <c r="K169" s="14">
+        <v>0</v>
+      </c>
+      <c r="L169" s="14">
+        <v>0</v>
+      </c>
+      <c r="M169" s="14">
+        <v>0</v>
+      </c>
+      <c r="N169" s="14">
+        <v>0</v>
+      </c>
+      <c r="O169" s="14">
+        <v>0</v>
+      </c>
+      <c r="P169" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q169" s="14">
+        <v>0</v>
+      </c>
+      <c r="R169" s="14">
+        <v>0</v>
+      </c>
+      <c r="S169" s="14">
+        <v>0</v>
+      </c>
+      <c r="T169" s="14">
+        <v>0</v>
+      </c>
+      <c r="U169" s="14">
+        <v>0</v>
+      </c>
+      <c r="V169" s="14">
+        <v>0</v>
+      </c>
+      <c r="W169" s="14">
+        <v>0</v>
+      </c>
+      <c r="X169" s="112">
+        <v>0</v>
+      </c>
+      <c r="Y169" s="14">
+        <f t="shared" si="43"/>
+        <v>0</v>
+      </c>
+      <c r="Z169" s="14">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="AA169" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB169" s="166"/>
+      <c r="AC169" s="167"/>
+      <c r="AD169" s="16">
+        <f t="shared" si="45"/>
+        <v>0</v>
+      </c>
+      <c r="AE169" s="17"/>
+      <c r="AF169" s="2"/>
+      <c r="AG169" s="2"/>
+      <c r="AH169" s="2"/>
+      <c r="AI169" s="2"/>
+      <c r="AJ169" s="2"/>
+      <c r="AK169" s="3"/>
+      <c r="AL169" s="3"/>
+      <c r="AM169" s="2"/>
+      <c r="AN169" s="2"/>
+    </row>
+    <row r="170" spans="1:40" s="2" customFormat="1" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
+      <c r="B170" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="C169" s="134" t="s">
+      <c r="C170" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D169" s="135"/>
-      <c r="E169" s="134" t="s">
+      <c r="D170" s="144"/>
+      <c r="E170" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F169" s="135"/>
-      <c r="G169" s="134" t="s">
+      <c r="F170" s="144"/>
+      <c r="G170" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H169" s="135"/>
-      <c r="I169" s="134" t="s">
+      <c r="H170" s="144"/>
+      <c r="I170" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J169" s="135"/>
-      <c r="K169" s="134" t="s">
+      <c r="J170" s="144"/>
+      <c r="K170" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L169" s="135"/>
-      <c r="M169" s="134" t="s">
+      <c r="L170" s="144"/>
+      <c r="M170" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N169" s="135"/>
-      <c r="O169" s="134" t="s">
+      <c r="N170" s="144"/>
+      <c r="O170" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P169" s="135"/>
-      <c r="Q169" s="134" t="s">
+      <c r="P170" s="144"/>
+      <c r="Q170" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R169" s="135"/>
-      <c r="S169" s="134" t="s">
+      <c r="R170" s="144"/>
+      <c r="S170" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T169" s="135"/>
-      <c r="U169" s="134" t="s">
+      <c r="T170" s="144"/>
+      <c r="U170" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V169" s="135"/>
-      <c r="W169" s="9" t="s">
+      <c r="V170" s="144"/>
+      <c r="W170" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="X169" s="117"/>
-      <c r="Y169" s="238" t="s">
+      <c r="X170" s="117"/>
+      <c r="Y170" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="Z169" s="239"/>
-      <c r="AA169" s="79" t="s">
+      <c r="Z170" s="156"/>
+      <c r="AA170" s="79" t="s">
         <v>177</v>
       </c>
-      <c r="AB169" s="140"/>
-      <c r="AC169" s="141"/>
-      <c r="AD169" s="6" t="s">
+      <c r="AB170" s="147"/>
+      <c r="AC170" s="148"/>
+      <c r="AD170" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AE169" s="7"/>
-      <c r="AF169" s="93"/>
-      <c r="AG169" s="93"/>
-      <c r="AK169" s="8"/>
-      <c r="AL169" s="8"/>
-      <c r="AM169" s="12"/>
-      <c r="AN169" s="12"/>
-    </row>
-    <row r="170" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B170" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="C170" s="19">
-        <v>0</v>
-      </c>
-      <c r="D170" s="20"/>
-      <c r="E170" s="19">
-        <v>0</v>
-      </c>
-      <c r="F170" s="20"/>
-      <c r="G170" s="19">
-        <v>0</v>
-      </c>
-      <c r="H170" s="20"/>
-      <c r="I170" s="19">
-        <v>0</v>
-      </c>
-      <c r="J170" s="20"/>
-      <c r="K170" s="19">
-        <v>0</v>
-      </c>
-      <c r="L170" s="20"/>
-      <c r="M170" s="19">
-        <v>0</v>
-      </c>
-      <c r="N170" s="20"/>
-      <c r="O170" s="19">
-        <v>0</v>
-      </c>
-      <c r="P170" s="20"/>
-      <c r="Q170" s="19">
-        <v>0</v>
-      </c>
-      <c r="R170" s="20"/>
-      <c r="S170" s="19">
-        <v>0</v>
-      </c>
-      <c r="T170" s="20"/>
-      <c r="U170" s="19">
-        <v>0</v>
-      </c>
-      <c r="V170" s="20"/>
-      <c r="W170" s="14">
-        <v>0</v>
-      </c>
-      <c r="X170" s="120">
-        <v>0</v>
-      </c>
-      <c r="Y170" s="236">
-        <f t="shared" ref="Y170:Y195" si="46">SUM(C170:W170)</f>
-        <v>0</v>
-      </c>
-      <c r="Z170" s="237"/>
-      <c r="AA170" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="AB170" s="222">
-        <f>SUM(Y170:Y177)</f>
-        <v>0</v>
-      </c>
-      <c r="AC170" s="147"/>
-      <c r="AD170" s="16">
-        <f>X170</f>
-        <v>0</v>
-      </c>
-      <c r="AE170" s="94"/>
-      <c r="AF170" s="168" t="s">
-        <v>179</v>
-      </c>
-      <c r="AG170" s="169"/>
-      <c r="AH170" s="169"/>
-      <c r="AI170" s="169"/>
-      <c r="AJ170" s="170"/>
+      <c r="AE170" s="7"/>
+      <c r="AF170" s="93"/>
+      <c r="AG170" s="93"/>
       <c r="AK170" s="8"/>
       <c r="AL170" s="8"/>
+      <c r="AM170" s="12"/>
+      <c r="AN170" s="12"/>
     </row>
     <row r="171" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B171" s="13" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C171" s="19">
         <v>0</v>
@@ -29099,32 +29120,37 @@
       <c r="X171" s="120">
         <v>0</v>
       </c>
-      <c r="Y171" s="236">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="Z171" s="237"/>
+      <c r="Y171" s="149">
+        <f t="shared" ref="Y171:Y196" si="46">SUM(C171:W171)</f>
+        <v>0</v>
+      </c>
+      <c r="Z171" s="150"/>
       <c r="AA171" s="13" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB171" s="223"/>
-      <c r="AC171" s="148"/>
+        <v>178</v>
+      </c>
+      <c r="AB171" s="162">
+        <f>SUM(Y171:Y178)</f>
+        <v>0</v>
+      </c>
+      <c r="AC171" s="163"/>
       <c r="AD171" s="16">
-        <f t="shared" ref="AD171:AD176" si="47">X171</f>
+        <f>X171</f>
         <v>0</v>
       </c>
       <c r="AE171" s="94"/>
-      <c r="AF171" s="171"/>
-      <c r="AG171" s="160"/>
-      <c r="AH171" s="160"/>
-      <c r="AI171" s="160"/>
-      <c r="AJ171" s="161"/>
+      <c r="AF171" s="168" t="s">
+        <v>179</v>
+      </c>
+      <c r="AG171" s="169"/>
+      <c r="AH171" s="169"/>
+      <c r="AI171" s="169"/>
+      <c r="AJ171" s="170"/>
       <c r="AK171" s="8"/>
       <c r="AL171" s="8"/>
     </row>
     <row r="172" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B172" s="13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C172" s="19">
         <v>0</v>
@@ -29172,32 +29198,32 @@
       <c r="X172" s="120">
         <v>0</v>
       </c>
-      <c r="Y172" s="236">
+      <c r="Y172" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z172" s="237"/>
+      <c r="Z172" s="150"/>
       <c r="AA172" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB172" s="223"/>
-      <c r="AC172" s="148"/>
+        <v>180</v>
+      </c>
+      <c r="AB172" s="164"/>
+      <c r="AC172" s="165"/>
       <c r="AD172" s="16">
-        <f t="shared" si="47"/>
+        <f t="shared" ref="AD172:AD177" si="47">X172</f>
         <v>0</v>
       </c>
       <c r="AE172" s="94"/>
       <c r="AF172" s="171"/>
-      <c r="AG172" s="160"/>
-      <c r="AH172" s="160"/>
-      <c r="AI172" s="160"/>
-      <c r="AJ172" s="161"/>
+      <c r="AG172" s="172"/>
+      <c r="AH172" s="172"/>
+      <c r="AI172" s="172"/>
+      <c r="AJ172" s="173"/>
       <c r="AK172" s="8"/>
       <c r="AL172" s="8"/>
     </row>
     <row r="173" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B173" s="13" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C173" s="19">
         <v>0</v>
@@ -29245,32 +29271,32 @@
       <c r="X173" s="120">
         <v>0</v>
       </c>
-      <c r="Y173" s="236">
+      <c r="Y173" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z173" s="237"/>
+      <c r="Z173" s="150"/>
       <c r="AA173" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="AB173" s="223"/>
-      <c r="AC173" s="148"/>
+        <v>181</v>
+      </c>
+      <c r="AB173" s="164"/>
+      <c r="AC173" s="165"/>
       <c r="AD173" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE173" s="94"/>
       <c r="AF173" s="171"/>
-      <c r="AG173" s="160"/>
-      <c r="AH173" s="160"/>
-      <c r="AI173" s="160"/>
-      <c r="AJ173" s="161"/>
+      <c r="AG173" s="172"/>
+      <c r="AH173" s="172"/>
+      <c r="AI173" s="172"/>
+      <c r="AJ173" s="173"/>
       <c r="AK173" s="8"/>
       <c r="AL173" s="8"/>
     </row>
     <row r="174" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B174" s="13" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C174" s="19">
         <v>0</v>
@@ -29318,35 +29344,32 @@
       <c r="X174" s="120">
         <v>0</v>
       </c>
-      <c r="Y174" s="236">
+      <c r="Y174" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z174" s="237"/>
+      <c r="Z174" s="150"/>
       <c r="AA174" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB174" s="223"/>
-      <c r="AC174" s="148"/>
+        <v>182</v>
+      </c>
+      <c r="AB174" s="164"/>
+      <c r="AC174" s="165"/>
       <c r="AD174" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE174" s="94"/>
-      <c r="AF174" s="159">
-        <f>SUM(AD170:AD177)</f>
-        <v>0</v>
-      </c>
-      <c r="AG174" s="160"/>
-      <c r="AH174" s="160"/>
-      <c r="AI174" s="160"/>
-      <c r="AJ174" s="161"/>
+      <c r="AF174" s="171"/>
+      <c r="AG174" s="172"/>
+      <c r="AH174" s="172"/>
+      <c r="AI174" s="172"/>
+      <c r="AJ174" s="173"/>
       <c r="AK174" s="8"/>
       <c r="AL174" s="8"/>
     </row>
     <row r="175" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B175" s="13" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C175" s="19">
         <v>0</v>
@@ -29394,32 +29417,35 @@
       <c r="X175" s="120">
         <v>0</v>
       </c>
-      <c r="Y175" s="236">
+      <c r="Y175" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z175" s="237"/>
+      <c r="Z175" s="150"/>
       <c r="AA175" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="AB175" s="223"/>
-      <c r="AC175" s="148"/>
+        <v>183</v>
+      </c>
+      <c r="AB175" s="164"/>
+      <c r="AC175" s="165"/>
       <c r="AD175" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE175" s="94"/>
-      <c r="AF175" s="26"/>
-      <c r="AG175" s="27"/>
-      <c r="AH175" s="27"/>
-      <c r="AI175" s="27"/>
-      <c r="AJ175" s="28"/>
+      <c r="AF175" s="174">
+        <f>SUM(AD171:AD178)</f>
+        <v>0</v>
+      </c>
+      <c r="AG175" s="172"/>
+      <c r="AH175" s="172"/>
+      <c r="AI175" s="172"/>
+      <c r="AJ175" s="173"/>
       <c r="AK175" s="8"/>
       <c r="AL175" s="8"/>
     </row>
-    <row r="176" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
+    <row r="176" spans="1:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B176" s="13" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C176" s="19">
         <v>0</v>
@@ -29467,32 +29493,32 @@
       <c r="X176" s="120">
         <v>0</v>
       </c>
-      <c r="Y176" s="236">
+      <c r="Y176" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z176" s="237"/>
+      <c r="Z176" s="150"/>
       <c r="AA176" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB176" s="223"/>
-      <c r="AC176" s="148"/>
+        <v>184</v>
+      </c>
+      <c r="AB176" s="164"/>
+      <c r="AC176" s="165"/>
       <c r="AD176" s="16">
         <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE176" s="94"/>
-      <c r="AF176" s="83"/>
-      <c r="AG176" s="84"/>
-      <c r="AH176" s="84"/>
-      <c r="AI176" s="84"/>
-      <c r="AJ176" s="85"/>
+      <c r="AF176" s="26"/>
+      <c r="AG176" s="27"/>
+      <c r="AH176" s="27"/>
+      <c r="AI176" s="27"/>
+      <c r="AJ176" s="28"/>
       <c r="AK176" s="8"/>
       <c r="AL176" s="8"/>
     </row>
-    <row r="177" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+    <row r="177" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" thickBot="1" x14ac:dyDescent="2.4">
       <c r="B177" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C177" s="19">
         <v>0</v>
@@ -29540,179 +29566,179 @@
       <c r="X177" s="120">
         <v>0</v>
       </c>
-      <c r="Y177" s="236">
+      <c r="Y177" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z177" s="237"/>
+      <c r="Z177" s="150"/>
       <c r="AA177" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB177" s="224"/>
-      <c r="AC177" s="149"/>
+        <v>185</v>
+      </c>
+      <c r="AB177" s="164"/>
+      <c r="AC177" s="165"/>
       <c r="AD177" s="16">
-        <f>X177</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AE177" s="94"/>
-      <c r="AF177" s="24"/>
-      <c r="AG177" s="24"/>
-      <c r="AH177" s="24"/>
-      <c r="AI177" s="24"/>
-      <c r="AJ177" s="24"/>
+      <c r="AF177" s="83"/>
+      <c r="AG177" s="84"/>
+      <c r="AH177" s="84"/>
+      <c r="AI177" s="84"/>
+      <c r="AJ177" s="85"/>
       <c r="AK177" s="8"/>
       <c r="AL177" s="8"/>
     </row>
-    <row r="178" spans="2:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B178" s="86" t="s">
+    <row r="178" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B178" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C178" s="19">
+        <v>0</v>
+      </c>
+      <c r="D178" s="20"/>
+      <c r="E178" s="19">
+        <v>0</v>
+      </c>
+      <c r="F178" s="20"/>
+      <c r="G178" s="19">
+        <v>0</v>
+      </c>
+      <c r="H178" s="20"/>
+      <c r="I178" s="19">
+        <v>0</v>
+      </c>
+      <c r="J178" s="20"/>
+      <c r="K178" s="19">
+        <v>0</v>
+      </c>
+      <c r="L178" s="20"/>
+      <c r="M178" s="19">
+        <v>0</v>
+      </c>
+      <c r="N178" s="20"/>
+      <c r="O178" s="19">
+        <v>0</v>
+      </c>
+      <c r="P178" s="20"/>
+      <c r="Q178" s="19">
+        <v>0</v>
+      </c>
+      <c r="R178" s="20"/>
+      <c r="S178" s="19">
+        <v>0</v>
+      </c>
+      <c r="T178" s="20"/>
+      <c r="U178" s="19">
+        <v>0</v>
+      </c>
+      <c r="V178" s="20"/>
+      <c r="W178" s="14">
+        <v>0</v>
+      </c>
+      <c r="X178" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y178" s="149">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Z178" s="150"/>
+      <c r="AA178" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="AB178" s="166"/>
+      <c r="AC178" s="167"/>
+      <c r="AD178" s="16">
+        <f>X178</f>
+        <v>0</v>
+      </c>
+      <c r="AE178" s="94"/>
+      <c r="AF178" s="24"/>
+      <c r="AG178" s="24"/>
+      <c r="AH178" s="24"/>
+      <c r="AI178" s="24"/>
+      <c r="AJ178" s="24"/>
+      <c r="AK178" s="8"/>
+      <c r="AL178" s="8"/>
+    </row>
+    <row r="179" spans="2:38" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B179" s="86" t="s">
         <v>187</v>
       </c>
-      <c r="C178" s="95">
-        <f>SUM(C170:C177)</f>
-        <v>0</v>
-      </c>
-      <c r="D178" s="96"/>
-      <c r="E178" s="95">
-        <f t="shared" ref="E178:W178" si="48">SUM(E170:E177)</f>
-        <v>0</v>
-      </c>
-      <c r="F178" s="96"/>
-      <c r="G178" s="95">
+      <c r="C179" s="95">
+        <f>SUM(C171:C178)</f>
+        <v>0</v>
+      </c>
+      <c r="D179" s="96"/>
+      <c r="E179" s="95">
+        <f t="shared" ref="E179:W179" si="48">SUM(E171:E178)</f>
+        <v>0</v>
+      </c>
+      <c r="F179" s="96"/>
+      <c r="G179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="H178" s="96"/>
-      <c r="I178" s="95">
+      <c r="H179" s="96"/>
+      <c r="I179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="J178" s="96"/>
-      <c r="K178" s="95">
+      <c r="J179" s="96"/>
+      <c r="K179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="L178" s="96"/>
-      <c r="M178" s="95">
+      <c r="L179" s="96"/>
+      <c r="M179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="N178" s="96"/>
-      <c r="O178" s="95">
+      <c r="N179" s="96"/>
+      <c r="O179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="P178" s="96"/>
-      <c r="Q178" s="95">
+      <c r="P179" s="96"/>
+      <c r="Q179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="R178" s="96"/>
-      <c r="S178" s="95">
+      <c r="R179" s="96"/>
+      <c r="S179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="T178" s="96"/>
-      <c r="U178" s="95">
+      <c r="T179" s="96"/>
+      <c r="U179" s="95">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="V178" s="96"/>
-      <c r="W178" s="97">
+      <c r="V179" s="96"/>
+      <c r="W179" s="97">
         <f t="shared" si="48"/>
         <v>0</v>
       </c>
-      <c r="X178" s="121"/>
-      <c r="Y178" s="238">
+      <c r="X179" s="121"/>
+      <c r="Y179" s="155">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z178" s="239"/>
-      <c r="AA178" s="86" t="s">
+      <c r="Z179" s="156"/>
+      <c r="AA179" s="86" t="s">
         <v>188</v>
       </c>
-      <c r="AB178" s="233"/>
-      <c r="AC178" s="234"/>
-      <c r="AD178" s="6" t="s">
+      <c r="AB179" s="160"/>
+      <c r="AC179" s="161"/>
+      <c r="AD179" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="AE178" s="7"/>
-    </row>
-    <row r="179" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B179" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="C179" s="19">
-        <v>0</v>
-      </c>
-      <c r="D179" s="20"/>
-      <c r="E179" s="19">
-        <v>0</v>
-      </c>
-      <c r="F179" s="20"/>
-      <c r="G179" s="19">
-        <v>0</v>
-      </c>
-      <c r="H179" s="20"/>
-      <c r="I179" s="19">
-        <v>0</v>
-      </c>
-      <c r="J179" s="20"/>
-      <c r="K179" s="19">
-        <v>0</v>
-      </c>
-      <c r="L179" s="20"/>
-      <c r="M179" s="19">
-        <v>0</v>
-      </c>
-      <c r="N179" s="20"/>
-      <c r="O179" s="19">
-        <v>0</v>
-      </c>
-      <c r="P179" s="20"/>
-      <c r="Q179" s="19">
-        <v>0</v>
-      </c>
-      <c r="R179" s="20"/>
-      <c r="S179" s="19">
-        <v>0</v>
-      </c>
-      <c r="T179" s="20"/>
-      <c r="U179" s="19">
-        <v>0</v>
-      </c>
-      <c r="V179" s="20"/>
-      <c r="W179" s="14">
-        <v>0</v>
-      </c>
-      <c r="X179" s="120">
-        <v>0</v>
-      </c>
-      <c r="Y179" s="236">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="Z179" s="237"/>
-      <c r="AA179" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="AB179" s="178"/>
-      <c r="AC179" s="179"/>
-      <c r="AD179" s="16">
-        <f>X179</f>
-        <v>0</v>
-      </c>
-      <c r="AE179" s="98"/>
-      <c r="AF179" s="99"/>
-      <c r="AG179" s="99"/>
-      <c r="AH179" s="99"/>
-      <c r="AI179" s="99"/>
-      <c r="AJ179" s="99"/>
-      <c r="AK179" s="8"/>
-      <c r="AL179" s="8"/>
+      <c r="AE179" s="7"/>
     </row>
     <row r="180" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B180" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C180" s="19">
         <v>0</v>
@@ -29760,16 +29786,16 @@
       <c r="X180" s="120">
         <v>0</v>
       </c>
-      <c r="Y180" s="236">
+      <c r="Y180" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z180" s="237"/>
+      <c r="Z180" s="150"/>
       <c r="AA180" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="AB180" s="178"/>
-      <c r="AC180" s="179"/>
+        <v>189</v>
+      </c>
+      <c r="AB180" s="157"/>
+      <c r="AC180" s="158"/>
       <c r="AD180" s="16">
         <f>X180</f>
         <v>0</v>
@@ -29785,7 +29811,7 @@
     </row>
     <row r="181" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B181" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C181" s="19">
         <v>0</v>
@@ -29833,16 +29859,16 @@
       <c r="X181" s="120">
         <v>0</v>
       </c>
-      <c r="Y181" s="236">
+      <c r="Y181" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z181" s="237"/>
+      <c r="Z181" s="150"/>
       <c r="AA181" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="AB181" s="178"/>
-      <c r="AC181" s="179"/>
+        <v>190</v>
+      </c>
+      <c r="AB181" s="157"/>
+      <c r="AC181" s="158"/>
       <c r="AD181" s="16">
         <f>X181</f>
         <v>0</v>
@@ -29858,7 +29884,7 @@
     </row>
     <row r="182" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B182" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C182" s="19">
         <v>0</v>
@@ -29906,18 +29932,18 @@
       <c r="X182" s="120">
         <v>0</v>
       </c>
-      <c r="Y182" s="236">
+      <c r="Y182" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z182" s="237"/>
+      <c r="Z182" s="150"/>
       <c r="AA182" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="AB182" s="178"/>
-      <c r="AC182" s="179"/>
+        <v>191</v>
+      </c>
+      <c r="AB182" s="157"/>
+      <c r="AC182" s="158"/>
       <c r="AD182" s="16">
-        <f t="shared" ref="AD182:AD195" si="49">X182</f>
+        <f>X182</f>
         <v>0</v>
       </c>
       <c r="AE182" s="98"/>
@@ -29931,7 +29957,7 @@
     </row>
     <row r="183" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B183" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C183" s="19">
         <v>0</v>
@@ -29979,18 +30005,18 @@
       <c r="X183" s="120">
         <v>0</v>
       </c>
-      <c r="Y183" s="236">
+      <c r="Y183" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z183" s="237"/>
+      <c r="Z183" s="150"/>
       <c r="AA183" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="AB183" s="178"/>
-      <c r="AC183" s="179"/>
+        <v>192</v>
+      </c>
+      <c r="AB183" s="157"/>
+      <c r="AC183" s="158"/>
       <c r="AD183" s="16">
-        <f t="shared" si="49"/>
+        <f t="shared" ref="AD183:AD196" si="49">X183</f>
         <v>0</v>
       </c>
       <c r="AE183" s="98"/>
@@ -30004,7 +30030,7 @@
     </row>
     <row r="184" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B184" s="13" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C184" s="19">
         <v>0</v>
@@ -30052,32 +30078,32 @@
       <c r="X184" s="120">
         <v>0</v>
       </c>
-      <c r="Y184" s="236">
+      <c r="Y184" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z184" s="237"/>
+      <c r="Z184" s="150"/>
       <c r="AA184" s="13" t="s">
-        <v>194</v>
-      </c>
-      <c r="AB184" s="178"/>
-      <c r="AC184" s="179"/>
+        <v>193</v>
+      </c>
+      <c r="AB184" s="157"/>
+      <c r="AC184" s="158"/>
       <c r="AD184" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE184" s="98"/>
       <c r="AF184" s="99"/>
-      <c r="AG184" s="240"/>
-      <c r="AH184" s="240"/>
-      <c r="AI184" s="240"/>
+      <c r="AG184" s="99"/>
+      <c r="AH184" s="99"/>
+      <c r="AI184" s="99"/>
       <c r="AJ184" s="99"/>
       <c r="AK184" s="8"/>
       <c r="AL184" s="8"/>
     </row>
-    <row r="185" spans="2:38" s="12" customFormat="1" ht="127.5" customHeight="1" x14ac:dyDescent="2.35">
+    <row r="185" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B185" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C185" s="19">
         <v>0</v>
@@ -30125,32 +30151,32 @@
       <c r="X185" s="120">
         <v>0</v>
       </c>
-      <c r="Y185" s="236">
+      <c r="Y185" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z185" s="237"/>
+      <c r="Z185" s="150"/>
       <c r="AA185" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="AB185" s="178"/>
-      <c r="AC185" s="179"/>
+        <v>194</v>
+      </c>
+      <c r="AB185" s="157"/>
+      <c r="AC185" s="158"/>
       <c r="AD185" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE185" s="98"/>
       <c r="AF185" s="99"/>
-      <c r="AG185" s="99"/>
-      <c r="AH185" s="99"/>
-      <c r="AI185" s="99"/>
+      <c r="AG185" s="159"/>
+      <c r="AH185" s="159"/>
+      <c r="AI185" s="159"/>
       <c r="AJ185" s="99"/>
       <c r="AK185" s="8"/>
       <c r="AL185" s="8"/>
     </row>
-    <row r="186" spans="2:38" s="12" customFormat="1" ht="135" customHeight="1" x14ac:dyDescent="2.35">
+    <row r="186" spans="2:38" s="12" customFormat="1" ht="127.5" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B186" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C186" s="19">
         <v>0</v>
@@ -30198,16 +30224,16 @@
       <c r="X186" s="120">
         <v>0</v>
       </c>
-      <c r="Y186" s="236">
+      <c r="Y186" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z186" s="237"/>
+      <c r="Z186" s="150"/>
       <c r="AA186" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="AB186" s="178"/>
-      <c r="AC186" s="179"/>
+        <v>195</v>
+      </c>
+      <c r="AB186" s="157"/>
+      <c r="AC186" s="158"/>
       <c r="AD186" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30221,9 +30247,9 @@
       <c r="AK186" s="8"/>
       <c r="AL186" s="8"/>
     </row>
-    <row r="187" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+    <row r="187" spans="2:38" s="12" customFormat="1" ht="135" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B187" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C187" s="19">
         <v>0</v>
@@ -30271,16 +30297,16 @@
       <c r="X187" s="120">
         <v>0</v>
       </c>
-      <c r="Y187" s="236">
+      <c r="Y187" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z187" s="237"/>
+      <c r="Z187" s="150"/>
       <c r="AA187" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="AB187" s="178"/>
-      <c r="AC187" s="179"/>
+        <v>196</v>
+      </c>
+      <c r="AB187" s="157"/>
+      <c r="AC187" s="158"/>
       <c r="AD187" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30296,7 +30322,7 @@
     </row>
     <row r="188" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B188" s="13" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="C188" s="19">
         <v>0</v>
@@ -30344,18 +30370,16 @@
       <c r="X188" s="120">
         <v>0</v>
       </c>
-      <c r="Y188" s="236">
-        <f>SUM(C188:W188)</f>
-        <v>0</v>
-      </c>
-      <c r="Z188" s="237"/>
+      <c r="Y188" s="149">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Z188" s="150"/>
       <c r="AA188" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="AB188" s="125" t="s">
-        <v>210</v>
-      </c>
-      <c r="AC188" s="126"/>
+        <v>197</v>
+      </c>
+      <c r="AB188" s="157"/>
+      <c r="AC188" s="158"/>
       <c r="AD188" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30371,7 +30395,7 @@
     </row>
     <row r="189" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B189" s="13" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C189" s="19">
         <v>0</v>
@@ -30419,18 +30443,20 @@
       <c r="X189" s="120">
         <v>0</v>
       </c>
-      <c r="Y189" s="236">
+      <c r="Y189" s="149">
         <f>SUM(C189:W189)</f>
         <v>0</v>
       </c>
-      <c r="Z189" s="237"/>
+      <c r="Z189" s="150"/>
       <c r="AA189" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="AB189" s="125"/>
+        <v>209</v>
+      </c>
+      <c r="AB189" s="125" t="s">
+        <v>210</v>
+      </c>
       <c r="AC189" s="126"/>
       <c r="AD189" s="16">
-        <f>X189</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE189" s="98"/>
@@ -30444,7 +30470,7 @@
     </row>
     <row r="190" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B190" s="13" t="s">
-        <v>198</v>
+        <v>221</v>
       </c>
       <c r="C190" s="19">
         <v>0</v>
@@ -30492,18 +30518,18 @@
       <c r="X190" s="120">
         <v>0</v>
       </c>
-      <c r="Y190" s="236">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="Z190" s="237"/>
+      <c r="Y190" s="149">
+        <f>SUM(C190:W190)</f>
+        <v>0</v>
+      </c>
+      <c r="Z190" s="150"/>
       <c r="AA190" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="AB190" s="178"/>
-      <c r="AC190" s="179"/>
+        <v>221</v>
+      </c>
+      <c r="AB190" s="125"/>
+      <c r="AC190" s="126"/>
       <c r="AD190" s="16">
-        <f t="shared" si="49"/>
+        <f>X190</f>
         <v>0</v>
       </c>
       <c r="AE190" s="98"/>
@@ -30517,7 +30543,7 @@
     </row>
     <row r="191" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B191" s="13" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C191" s="19">
         <v>0</v>
@@ -30565,16 +30591,16 @@
       <c r="X191" s="120">
         <v>0</v>
       </c>
-      <c r="Y191" s="236">
+      <c r="Y191" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z191" s="237"/>
+      <c r="Z191" s="150"/>
       <c r="AA191" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="AB191" s="178"/>
-      <c r="AC191" s="179"/>
+        <v>198</v>
+      </c>
+      <c r="AB191" s="157"/>
+      <c r="AC191" s="158"/>
       <c r="AD191" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30590,7 +30616,7 @@
     </row>
     <row r="192" spans="2:38" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B192" s="13" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C192" s="19">
         <v>0</v>
@@ -30638,16 +30664,16 @@
       <c r="X192" s="120">
         <v>0</v>
       </c>
-      <c r="Y192" s="236">
+      <c r="Y192" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z192" s="237"/>
+      <c r="Z192" s="150"/>
       <c r="AA192" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="AB192" s="178"/>
-      <c r="AC192" s="179"/>
+        <v>199</v>
+      </c>
+      <c r="AB192" s="157"/>
+      <c r="AC192" s="158"/>
       <c r="AD192" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30663,7 +30689,7 @@
     </row>
     <row r="193" spans="2:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B193" s="13" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="C193" s="19">
         <v>0</v>
@@ -30711,18 +30737,18 @@
       <c r="X193" s="120">
         <v>0</v>
       </c>
-      <c r="Y193" s="236">
-        <f t="shared" ref="Y193" si="50">SUM(C193:W193)</f>
-        <v>0</v>
-      </c>
-      <c r="Z193" s="237"/>
+      <c r="Y193" s="149">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Z193" s="150"/>
       <c r="AA193" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="AB193" s="125"/>
-      <c r="AC193" s="126"/>
+        <v>200</v>
+      </c>
+      <c r="AB193" s="157"/>
+      <c r="AC193" s="158"/>
       <c r="AD193" s="16">
-        <f>X193</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AE193" s="98"/>
@@ -30736,7 +30762,7 @@
     </row>
     <row r="194" spans="2:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B194" s="13" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="C194" s="19">
         <v>0</v>
@@ -30784,21 +30810,21 @@
       <c r="X194" s="120">
         <v>0</v>
       </c>
-      <c r="Y194" s="236">
-        <f t="shared" si="46"/>
-        <v>0</v>
-      </c>
-      <c r="Z194" s="237"/>
+      <c r="Y194" s="149">
+        <f t="shared" ref="Y194" si="50">SUM(C194:W194)</f>
+        <v>0</v>
+      </c>
+      <c r="Z194" s="150"/>
       <c r="AA194" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB194" s="178"/>
-      <c r="AC194" s="179"/>
+        <v>224</v>
+      </c>
+      <c r="AB194" s="125"/>
+      <c r="AC194" s="126"/>
       <c r="AD194" s="16">
-        <f t="shared" si="49"/>
-        <v>0</v>
-      </c>
-      <c r="AE194" s="100"/>
+        <f>X194</f>
+        <v>0</v>
+      </c>
+      <c r="AE194" s="98"/>
       <c r="AF194" s="99"/>
       <c r="AG194" s="99"/>
       <c r="AH194" s="99"/>
@@ -30809,7 +30835,7 @@
     </row>
     <row r="195" spans="2:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
       <c r="B195" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C195" s="19">
         <v>0</v>
@@ -30857,16 +30883,16 @@
       <c r="X195" s="120">
         <v>0</v>
       </c>
-      <c r="Y195" s="236">
+      <c r="Y195" s="149">
         <f t="shared" si="46"/>
         <v>0</v>
       </c>
-      <c r="Z195" s="237"/>
+      <c r="Z195" s="150"/>
       <c r="AA195" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="AB195" s="178"/>
-      <c r="AC195" s="179"/>
+        <v>201</v>
+      </c>
+      <c r="AB195" s="157"/>
+      <c r="AC195" s="158"/>
       <c r="AD195" s="16">
         <f t="shared" si="49"/>
         <v>0</v>
@@ -30880,696 +30906,485 @@
       <c r="AK195" s="8"/>
       <c r="AL195" s="8"/>
     </row>
-    <row r="196" spans="2:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B196" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="C196" s="134" t="s">
-        <v>1</v>
-      </c>
-      <c r="D196" s="135"/>
-      <c r="E196" s="134" t="s">
-        <v>2</v>
-      </c>
-      <c r="F196" s="135"/>
-      <c r="G196" s="134" t="s">
-        <v>3</v>
-      </c>
-      <c r="H196" s="135"/>
-      <c r="I196" s="134" t="s">
-        <v>4</v>
-      </c>
-      <c r="J196" s="135"/>
-      <c r="K196" s="134" t="s">
-        <v>5</v>
-      </c>
-      <c r="L196" s="135"/>
-      <c r="M196" s="134" t="s">
-        <v>6</v>
-      </c>
-      <c r="N196" s="135"/>
-      <c r="O196" s="134" t="s">
-        <v>7</v>
-      </c>
-      <c r="P196" s="135"/>
-      <c r="Q196" s="134" t="s">
-        <v>8</v>
-      </c>
-      <c r="R196" s="135"/>
-      <c r="S196" s="134" t="s">
-        <v>9</v>
-      </c>
-      <c r="T196" s="135"/>
-      <c r="U196" s="134" t="s">
-        <v>10</v>
-      </c>
-      <c r="V196" s="135"/>
-      <c r="W196" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="X196" s="117"/>
-      <c r="Y196" s="238" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z196" s="239"/>
-      <c r="AA196" s="79" t="s">
-        <v>105</v>
-      </c>
-      <c r="AB196" s="140"/>
-      <c r="AC196" s="141"/>
-      <c r="AD196" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE196" s="7"/>
+    <row r="196" spans="2:40" s="12" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B196" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="C196" s="19">
+        <v>0</v>
+      </c>
+      <c r="D196" s="20"/>
+      <c r="E196" s="19">
+        <v>0</v>
+      </c>
+      <c r="F196" s="20"/>
+      <c r="G196" s="19">
+        <v>0</v>
+      </c>
+      <c r="H196" s="20"/>
+      <c r="I196" s="19">
+        <v>0</v>
+      </c>
+      <c r="J196" s="20"/>
+      <c r="K196" s="19">
+        <v>0</v>
+      </c>
+      <c r="L196" s="20"/>
+      <c r="M196" s="19">
+        <v>0</v>
+      </c>
+      <c r="N196" s="20"/>
+      <c r="O196" s="19">
+        <v>0</v>
+      </c>
+      <c r="P196" s="20"/>
+      <c r="Q196" s="19">
+        <v>0</v>
+      </c>
+      <c r="R196" s="20"/>
+      <c r="S196" s="19">
+        <v>0</v>
+      </c>
+      <c r="T196" s="20"/>
+      <c r="U196" s="19">
+        <v>0</v>
+      </c>
+      <c r="V196" s="20"/>
+      <c r="W196" s="14">
+        <v>0</v>
+      </c>
+      <c r="X196" s="120">
+        <v>0</v>
+      </c>
+      <c r="Y196" s="149">
+        <f t="shared" si="46"/>
+        <v>0</v>
+      </c>
+      <c r="Z196" s="150"/>
+      <c r="AA196" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB196" s="157"/>
+      <c r="AC196" s="158"/>
+      <c r="AD196" s="16">
+        <f t="shared" si="49"/>
+        <v>0</v>
+      </c>
+      <c r="AE196" s="100"/>
+      <c r="AF196" s="99"/>
+      <c r="AG196" s="99"/>
+      <c r="AH196" s="99"/>
+      <c r="AI196" s="99"/>
+      <c r="AJ196" s="99"/>
       <c r="AK196" s="8"/>
       <c r="AL196" s="8"/>
     </row>
     <row r="197" spans="2:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B197" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="C197" s="236">
-        <v>0</v>
-      </c>
-      <c r="D197" s="237"/>
-      <c r="E197" s="236">
-        <v>0</v>
-      </c>
-      <c r="F197" s="237"/>
-      <c r="G197" s="236">
-        <v>0</v>
-      </c>
-      <c r="H197" s="237"/>
-      <c r="I197" s="236">
-        <v>0</v>
-      </c>
-      <c r="J197" s="237"/>
-      <c r="K197" s="236">
-        <v>0</v>
-      </c>
-      <c r="L197" s="237"/>
-      <c r="M197" s="236">
-        <v>0</v>
-      </c>
-      <c r="N197" s="237"/>
-      <c r="O197" s="236">
-        <v>0</v>
-      </c>
-      <c r="P197" s="237"/>
-      <c r="Q197" s="236">
-        <v>0</v>
-      </c>
-      <c r="R197" s="237"/>
-      <c r="S197" s="236">
-        <v>0</v>
-      </c>
-      <c r="T197" s="237"/>
-      <c r="U197" s="236">
-        <v>0</v>
-      </c>
-      <c r="V197" s="237"/>
-      <c r="W197" s="14">
-        <v>0</v>
-      </c>
-      <c r="X197" s="120"/>
-      <c r="Y197" s="236">
-        <f>SUM(C197:W197)</f>
-        <v>0</v>
-      </c>
-      <c r="Z197" s="237"/>
-      <c r="AA197" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="AB197" s="220"/>
-      <c r="AC197" s="221"/>
-      <c r="AD197" s="16">
-        <f>X197</f>
-        <v>0</v>
+      <c r="B197" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="C197" s="143" t="s">
+        <v>1</v>
+      </c>
+      <c r="D197" s="144"/>
+      <c r="E197" s="143" t="s">
+        <v>2</v>
+      </c>
+      <c r="F197" s="144"/>
+      <c r="G197" s="143" t="s">
+        <v>3</v>
+      </c>
+      <c r="H197" s="144"/>
+      <c r="I197" s="143" t="s">
+        <v>4</v>
+      </c>
+      <c r="J197" s="144"/>
+      <c r="K197" s="143" t="s">
+        <v>5</v>
+      </c>
+      <c r="L197" s="144"/>
+      <c r="M197" s="143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N197" s="144"/>
+      <c r="O197" s="143" t="s">
+        <v>7</v>
+      </c>
+      <c r="P197" s="144"/>
+      <c r="Q197" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="R197" s="144"/>
+      <c r="S197" s="143" t="s">
+        <v>9</v>
+      </c>
+      <c r="T197" s="144"/>
+      <c r="U197" s="143" t="s">
+        <v>10</v>
+      </c>
+      <c r="V197" s="144"/>
+      <c r="W197" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="X197" s="117"/>
+      <c r="Y197" s="155" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z197" s="156"/>
+      <c r="AA197" s="79" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB197" s="147"/>
+      <c r="AC197" s="148"/>
+      <c r="AD197" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="AE197" s="7"/>
       <c r="AK197" s="8"/>
       <c r="AL197" s="8"/>
     </row>
-    <row r="198" spans="2:40" s="2" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B198" s="79" t="s">
-        <v>204</v>
-      </c>
-      <c r="C198" s="134" t="s">
-        <v>1</v>
-      </c>
-      <c r="D198" s="135"/>
-      <c r="E198" s="134" t="s">
-        <v>2</v>
-      </c>
-      <c r="F198" s="135"/>
-      <c r="G198" s="134" t="s">
-        <v>3</v>
-      </c>
-      <c r="H198" s="135"/>
-      <c r="I198" s="134" t="s">
-        <v>4</v>
-      </c>
-      <c r="J198" s="135"/>
-      <c r="K198" s="134" t="s">
-        <v>5</v>
-      </c>
-      <c r="L198" s="135"/>
-      <c r="M198" s="134" t="s">
-        <v>6</v>
-      </c>
-      <c r="N198" s="135"/>
-      <c r="O198" s="134" t="s">
-        <v>7</v>
-      </c>
-      <c r="P198" s="135"/>
-      <c r="Q198" s="134" t="s">
-        <v>8</v>
-      </c>
-      <c r="R198" s="135"/>
-      <c r="S198" s="134" t="s">
-        <v>9</v>
-      </c>
-      <c r="T198" s="135"/>
-      <c r="U198" s="134" t="s">
-        <v>10</v>
-      </c>
-      <c r="V198" s="135"/>
-      <c r="W198" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="X198" s="117"/>
-      <c r="Y198" s="238" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z198" s="239"/>
-      <c r="AA198" s="79" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB198" s="140"/>
-      <c r="AC198" s="141"/>
-      <c r="AD198" s="6" t="s">
-        <v>15</v>
+    <row r="198" spans="2:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B198" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C198" s="149">
+        <v>0</v>
+      </c>
+      <c r="D198" s="150"/>
+      <c r="E198" s="149">
+        <v>0</v>
+      </c>
+      <c r="F198" s="150"/>
+      <c r="G198" s="149">
+        <v>0</v>
+      </c>
+      <c r="H198" s="150"/>
+      <c r="I198" s="149">
+        <v>0</v>
+      </c>
+      <c r="J198" s="150"/>
+      <c r="K198" s="149">
+        <v>0</v>
+      </c>
+      <c r="L198" s="150"/>
+      <c r="M198" s="149">
+        <v>0</v>
+      </c>
+      <c r="N198" s="150"/>
+      <c r="O198" s="149">
+        <v>0</v>
+      </c>
+      <c r="P198" s="150"/>
+      <c r="Q198" s="149">
+        <v>0</v>
+      </c>
+      <c r="R198" s="150"/>
+      <c r="S198" s="149">
+        <v>0</v>
+      </c>
+      <c r="T198" s="150"/>
+      <c r="U198" s="149">
+        <v>0</v>
+      </c>
+      <c r="V198" s="150"/>
+      <c r="W198" s="14">
+        <v>0</v>
+      </c>
+      <c r="X198" s="120"/>
+      <c r="Y198" s="149">
+        <f>SUM(C198:W198)</f>
+        <v>0</v>
+      </c>
+      <c r="Z198" s="150"/>
+      <c r="AA198" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB198" s="153"/>
+      <c r="AC198" s="154"/>
+      <c r="AD198" s="16">
+        <f>X198</f>
+        <v>0</v>
       </c>
       <c r="AE198" s="7"/>
-      <c r="AF198" s="99"/>
-      <c r="AG198" s="99"/>
-      <c r="AH198" s="99"/>
-      <c r="AI198" s="99"/>
-      <c r="AJ198" s="99"/>
       <c r="AK198" s="8"/>
       <c r="AL198" s="8"/>
-      <c r="AM198" s="12"/>
-      <c r="AN198" s="12"/>
     </row>
-    <row r="199" spans="2:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B199" s="13" t="s">
+    <row r="199" spans="2:40" s="2" customFormat="1" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B199" s="79" t="s">
+        <v>204</v>
+      </c>
+      <c r="C199" s="143" t="s">
+        <v>1</v>
+      </c>
+      <c r="D199" s="144"/>
+      <c r="E199" s="143" t="s">
+        <v>2</v>
+      </c>
+      <c r="F199" s="144"/>
+      <c r="G199" s="143" t="s">
+        <v>3</v>
+      </c>
+      <c r="H199" s="144"/>
+      <c r="I199" s="143" t="s">
+        <v>4</v>
+      </c>
+      <c r="J199" s="144"/>
+      <c r="K199" s="143" t="s">
+        <v>5</v>
+      </c>
+      <c r="L199" s="144"/>
+      <c r="M199" s="143" t="s">
+        <v>6</v>
+      </c>
+      <c r="N199" s="144"/>
+      <c r="O199" s="143" t="s">
+        <v>7</v>
+      </c>
+      <c r="P199" s="144"/>
+      <c r="Q199" s="143" t="s">
+        <v>8</v>
+      </c>
+      <c r="R199" s="144"/>
+      <c r="S199" s="143" t="s">
+        <v>9</v>
+      </c>
+      <c r="T199" s="144"/>
+      <c r="U199" s="143" t="s">
+        <v>10</v>
+      </c>
+      <c r="V199" s="144"/>
+      <c r="W199" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="X199" s="117"/>
+      <c r="Y199" s="155" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z199" s="156"/>
+      <c r="AA199" s="79" t="s">
+        <v>204</v>
+      </c>
+      <c r="AB199" s="147"/>
+      <c r="AC199" s="148"/>
+      <c r="AD199" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE199" s="7"/>
+      <c r="AF199" s="99"/>
+      <c r="AG199" s="99"/>
+      <c r="AH199" s="99"/>
+      <c r="AI199" s="99"/>
+      <c r="AJ199" s="99"/>
+      <c r="AK199" s="8"/>
+      <c r="AL199" s="8"/>
+      <c r="AM199" s="12"/>
+      <c r="AN199" s="12"/>
+    </row>
+    <row r="200" spans="2:40" ht="123.75" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B200" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C199" s="19">
-        <v>0</v>
-      </c>
-      <c r="D199" s="20"/>
-      <c r="E199" s="19">
-        <v>0</v>
-      </c>
-      <c r="F199" s="20"/>
-      <c r="G199" s="19">
-        <v>0</v>
-      </c>
-      <c r="H199" s="20"/>
-      <c r="I199" s="19">
-        <v>0</v>
-      </c>
-      <c r="J199" s="20"/>
-      <c r="K199" s="19">
-        <v>0</v>
-      </c>
-      <c r="L199" s="20"/>
-      <c r="M199" s="19">
-        <v>0</v>
-      </c>
-      <c r="N199" s="20"/>
-      <c r="O199" s="19">
-        <v>0</v>
-      </c>
-      <c r="P199" s="20"/>
-      <c r="Q199" s="19">
-        <v>0</v>
-      </c>
-      <c r="R199" s="20"/>
-      <c r="S199" s="19">
-        <v>0</v>
-      </c>
-      <c r="T199" s="20"/>
-      <c r="U199" s="19">
-        <v>0</v>
-      </c>
-      <c r="V199" s="20"/>
-      <c r="W199" s="14">
-        <v>0</v>
-      </c>
-      <c r="X199" s="122">
-        <v>0</v>
-      </c>
-      <c r="Y199" s="236">
-        <f>SUM(C199:W199)</f>
-        <v>0</v>
-      </c>
-      <c r="Z199" s="237"/>
-      <c r="AA199" s="68" t="s">
+      <c r="C200" s="19">
+        <v>0</v>
+      </c>
+      <c r="D200" s="20"/>
+      <c r="E200" s="19">
+        <v>0</v>
+      </c>
+      <c r="F200" s="20"/>
+      <c r="G200" s="19">
+        <v>0</v>
+      </c>
+      <c r="H200" s="20"/>
+      <c r="I200" s="19">
+        <v>0</v>
+      </c>
+      <c r="J200" s="20"/>
+      <c r="K200" s="19">
+        <v>0</v>
+      </c>
+      <c r="L200" s="20"/>
+      <c r="M200" s="19">
+        <v>0</v>
+      </c>
+      <c r="N200" s="20"/>
+      <c r="O200" s="19">
+        <v>0</v>
+      </c>
+      <c r="P200" s="20"/>
+      <c r="Q200" s="19">
+        <v>0</v>
+      </c>
+      <c r="R200" s="20"/>
+      <c r="S200" s="19">
+        <v>0</v>
+      </c>
+      <c r="T200" s="20"/>
+      <c r="U200" s="19">
+        <v>0</v>
+      </c>
+      <c r="V200" s="20"/>
+      <c r="W200" s="14">
+        <v>0</v>
+      </c>
+      <c r="X200" s="122">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="149">
+        <f>SUM(C200:W200)</f>
+        <v>0</v>
+      </c>
+      <c r="Z200" s="150"/>
+      <c r="AA200" s="68" t="s">
         <v>205</v>
       </c>
-      <c r="AB199" s="199"/>
-      <c r="AC199" s="200"/>
-      <c r="AD199" s="16">
-        <f>X199</f>
-        <v>0</v>
-      </c>
-      <c r="AE199" s="17"/>
-      <c r="AM199" s="2"/>
-      <c r="AN199" s="2"/>
+      <c r="AB200" s="151"/>
+      <c r="AC200" s="152"/>
+      <c r="AD200" s="16">
+        <f>X200</f>
+        <v>0</v>
+      </c>
+      <c r="AE200" s="17"/>
+      <c r="AM200" s="2"/>
+      <c r="AN200" s="2"/>
     </row>
-    <row r="200" spans="2:40" s="2" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="2.35">
-      <c r="B200" s="241" t="s">
+    <row r="201" spans="2:40" s="2" customFormat="1" ht="165" customHeight="1" x14ac:dyDescent="2.35">
+      <c r="B201" s="145" t="s">
         <v>206</v>
       </c>
-      <c r="C200" s="134" t="s">
+      <c r="C201" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="D200" s="135"/>
-      <c r="E200" s="134" t="s">
+      <c r="D201" s="144"/>
+      <c r="E201" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="F200" s="135"/>
-      <c r="G200" s="134" t="s">
+      <c r="F201" s="144"/>
+      <c r="G201" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="H200" s="135"/>
-      <c r="I200" s="134" t="s">
+      <c r="H201" s="144"/>
+      <c r="I201" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="J200" s="135"/>
-      <c r="K200" s="134" t="s">
+      <c r="J201" s="144"/>
+      <c r="K201" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="L200" s="135"/>
-      <c r="M200" s="134" t="s">
+      <c r="L201" s="144"/>
+      <c r="M201" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="N200" s="135"/>
-      <c r="O200" s="134" t="s">
+      <c r="N201" s="144"/>
+      <c r="O201" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="P200" s="135"/>
-      <c r="Q200" s="134" t="s">
+      <c r="P201" s="144"/>
+      <c r="Q201" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="R200" s="135"/>
-      <c r="S200" s="134" t="s">
+      <c r="R201" s="144"/>
+      <c r="S201" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="T200" s="135"/>
-      <c r="U200" s="134" t="s">
+      <c r="T201" s="144"/>
+      <c r="U201" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="V200" s="135"/>
-      <c r="W200" s="9" t="s">
+      <c r="V201" s="144"/>
+      <c r="W201" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="X200" s="117"/>
-      <c r="Y200" s="249" t="s">
+      <c r="X201" s="117"/>
+      <c r="Y201" s="139" t="s">
         <v>207</v>
       </c>
-      <c r="Z200" s="250"/>
-      <c r="AA200" s="251"/>
-      <c r="AB200" s="101"/>
-      <c r="AC200" s="101"/>
-      <c r="AD200" s="102"/>
-      <c r="AE200" s="17"/>
-      <c r="AK200" s="3"/>
-      <c r="AL200" s="3"/>
-      <c r="AM200"/>
-      <c r="AN200"/>
-    </row>
-    <row r="201" spans="2:40" s="105" customFormat="1" ht="255" x14ac:dyDescent="3.65">
-      <c r="B201" s="242"/>
-      <c r="C201" s="243"/>
-      <c r="D201" s="243"/>
-      <c r="E201" s="243"/>
-      <c r="F201" s="243"/>
-      <c r="G201" s="243"/>
-      <c r="H201" s="243"/>
-      <c r="I201" s="243"/>
-      <c r="J201" s="243"/>
-      <c r="K201" s="243"/>
-      <c r="L201" s="243"/>
-      <c r="M201" s="243"/>
-      <c r="N201" s="243"/>
-      <c r="O201" s="243"/>
-      <c r="P201" s="243"/>
-      <c r="Q201" s="243"/>
-      <c r="R201" s="243"/>
-      <c r="S201" s="243"/>
-      <c r="T201" s="243"/>
-      <c r="U201" s="243"/>
-      <c r="V201" s="243"/>
-      <c r="W201" s="127"/>
-      <c r="X201" s="123"/>
-      <c r="Y201" s="244">
-        <f>SUM(C201:W201)</f>
-        <v>0</v>
-      </c>
-      <c r="Z201" s="245"/>
-      <c r="AA201" s="246"/>
-      <c r="AB201" s="103"/>
-      <c r="AC201" s="103"/>
-      <c r="AD201" s="104"/>
-      <c r="AE201" s="102"/>
-      <c r="AF201" s="2"/>
-      <c r="AG201" s="2"/>
-      <c r="AH201" s="2"/>
-      <c r="AI201" s="2"/>
-      <c r="AJ201" s="2"/>
+      <c r="Z201" s="140"/>
+      <c r="AA201" s="141"/>
+      <c r="AB201" s="101"/>
+      <c r="AC201" s="101"/>
+      <c r="AD201" s="102"/>
+      <c r="AE201" s="17"/>
       <c r="AK201" s="3"/>
       <c r="AL201" s="3"/>
-      <c r="AM201" s="2"/>
-      <c r="AN201" s="2"/>
+      <c r="AM201"/>
+      <c r="AN201"/>
     </row>
-    <row r="203" spans="2:40" x14ac:dyDescent="2.35">
-      <c r="C203" s="247"/>
-      <c r="D203" s="247"/>
-      <c r="O203" s="248"/>
-      <c r="P203" s="248"/>
-      <c r="R203" s="107"/>
-      <c r="AA203" s="108"/>
+    <row r="202" spans="2:40" s="105" customFormat="1" ht="255" x14ac:dyDescent="3.65">
+      <c r="B202" s="146"/>
+      <c r="C202" s="142"/>
+      <c r="D202" s="142"/>
+      <c r="E202" s="142"/>
+      <c r="F202" s="142"/>
+      <c r="G202" s="142"/>
+      <c r="H202" s="142"/>
+      <c r="I202" s="142"/>
+      <c r="J202" s="142"/>
+      <c r="K202" s="142"/>
+      <c r="L202" s="142"/>
+      <c r="M202" s="142"/>
+      <c r="N202" s="142"/>
+      <c r="O202" s="142"/>
+      <c r="P202" s="142"/>
+      <c r="Q202" s="142"/>
+      <c r="R202" s="142"/>
+      <c r="S202" s="142"/>
+      <c r="T202" s="142"/>
+      <c r="U202" s="142"/>
+      <c r="V202" s="142"/>
+      <c r="W202" s="127"/>
+      <c r="X202" s="123"/>
+      <c r="Y202" s="134">
+        <f>SUM(C202:W202)</f>
+        <v>0</v>
+      </c>
+      <c r="Z202" s="135"/>
+      <c r="AA202" s="136"/>
+      <c r="AB202" s="103"/>
+      <c r="AC202" s="103"/>
+      <c r="AD202" s="104"/>
+      <c r="AE202" s="102"/>
+      <c r="AF202" s="2"/>
+      <c r="AG202" s="2"/>
+      <c r="AH202" s="2"/>
+      <c r="AI202" s="2"/>
+      <c r="AJ202" s="2"/>
+      <c r="AK202" s="3"/>
+      <c r="AL202" s="3"/>
+      <c r="AM202" s="2"/>
+      <c r="AN202" s="2"/>
     </row>
     <row r="204" spans="2:40" x14ac:dyDescent="2.35">
+      <c r="C204" s="137"/>
+      <c r="D204" s="137"/>
+      <c r="O204" s="138"/>
+      <c r="P204" s="138"/>
+      <c r="R204" s="107"/>
       <c r="AA204" s="108"/>
+    </row>
+    <row r="205" spans="2:40" x14ac:dyDescent="2.35">
+      <c r="AA205" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="344">
-    <mergeCell ref="Y201:AA201"/>
-    <mergeCell ref="C203:D203"/>
-    <mergeCell ref="O203:P203"/>
-    <mergeCell ref="Y200:AA200"/>
-    <mergeCell ref="C201:D201"/>
-    <mergeCell ref="E201:F201"/>
-    <mergeCell ref="G201:H201"/>
-    <mergeCell ref="I201:J201"/>
-    <mergeCell ref="K201:L201"/>
-    <mergeCell ref="M201:N201"/>
-    <mergeCell ref="O201:P201"/>
-    <mergeCell ref="Q201:R201"/>
-    <mergeCell ref="M200:N200"/>
-    <mergeCell ref="O200:P200"/>
-    <mergeCell ref="Q200:R200"/>
-    <mergeCell ref="S200:T200"/>
-    <mergeCell ref="U200:V200"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="C200:D200"/>
-    <mergeCell ref="E200:F200"/>
-    <mergeCell ref="G200:H200"/>
-    <mergeCell ref="I200:J200"/>
-    <mergeCell ref="K200:L200"/>
-    <mergeCell ref="Q198:R198"/>
-    <mergeCell ref="S198:T198"/>
-    <mergeCell ref="U198:V198"/>
-    <mergeCell ref="S201:T201"/>
-    <mergeCell ref="U201:V201"/>
-    <mergeCell ref="AB198:AC198"/>
-    <mergeCell ref="Y199:Z199"/>
-    <mergeCell ref="AB199:AC199"/>
-    <mergeCell ref="Y197:Z197"/>
-    <mergeCell ref="AB197:AC197"/>
-    <mergeCell ref="C198:D198"/>
-    <mergeCell ref="E198:F198"/>
-    <mergeCell ref="G198:H198"/>
-    <mergeCell ref="I198:J198"/>
-    <mergeCell ref="K198:L198"/>
-    <mergeCell ref="M198:N198"/>
-    <mergeCell ref="O198:P198"/>
-    <mergeCell ref="M197:N197"/>
-    <mergeCell ref="O197:P197"/>
-    <mergeCell ref="Q197:R197"/>
-    <mergeCell ref="S197:T197"/>
-    <mergeCell ref="U197:V197"/>
-    <mergeCell ref="Y198:Z198"/>
-    <mergeCell ref="C197:D197"/>
-    <mergeCell ref="E197:F197"/>
-    <mergeCell ref="G197:H197"/>
-    <mergeCell ref="I197:J197"/>
-    <mergeCell ref="K197:L197"/>
-    <mergeCell ref="Y195:Z195"/>
-    <mergeCell ref="AB195:AC195"/>
-    <mergeCell ref="C196:D196"/>
-    <mergeCell ref="E196:F196"/>
-    <mergeCell ref="G196:H196"/>
-    <mergeCell ref="I196:J196"/>
-    <mergeCell ref="K196:L196"/>
-    <mergeCell ref="M196:N196"/>
-    <mergeCell ref="O196:P196"/>
-    <mergeCell ref="S196:T196"/>
-    <mergeCell ref="U196:V196"/>
-    <mergeCell ref="Y196:Z196"/>
-    <mergeCell ref="AB196:AC196"/>
-    <mergeCell ref="Q196:R196"/>
-    <mergeCell ref="Y191:Z191"/>
-    <mergeCell ref="AB191:AC191"/>
-    <mergeCell ref="Y192:Z192"/>
-    <mergeCell ref="AB192:AC192"/>
-    <mergeCell ref="Y194:Z194"/>
-    <mergeCell ref="AB194:AC194"/>
-    <mergeCell ref="Y186:Z186"/>
-    <mergeCell ref="AB186:AC186"/>
-    <mergeCell ref="Y187:Z187"/>
-    <mergeCell ref="AB187:AC187"/>
-    <mergeCell ref="Y190:Z190"/>
-    <mergeCell ref="AB190:AC190"/>
-    <mergeCell ref="Y188:Z188"/>
-    <mergeCell ref="Y189:Z189"/>
-    <mergeCell ref="Y193:Z193"/>
-    <mergeCell ref="Y183:Z183"/>
-    <mergeCell ref="AB183:AC183"/>
-    <mergeCell ref="Y184:Z184"/>
-    <mergeCell ref="AB184:AC184"/>
-    <mergeCell ref="AG184:AI184"/>
-    <mergeCell ref="Y185:Z185"/>
-    <mergeCell ref="AB185:AC185"/>
-    <mergeCell ref="Y180:Z180"/>
-    <mergeCell ref="AB180:AC180"/>
-    <mergeCell ref="Y181:Z181"/>
-    <mergeCell ref="AB181:AC181"/>
-    <mergeCell ref="Y182:Z182"/>
-    <mergeCell ref="AB182:AC182"/>
-    <mergeCell ref="Y175:Z175"/>
-    <mergeCell ref="Y176:Z176"/>
-    <mergeCell ref="Y177:Z177"/>
-    <mergeCell ref="Y178:Z178"/>
-    <mergeCell ref="AB178:AC178"/>
-    <mergeCell ref="Y179:Z179"/>
-    <mergeCell ref="AB179:AC179"/>
-    <mergeCell ref="Y169:Z169"/>
-    <mergeCell ref="AB169:AC169"/>
-    <mergeCell ref="Y170:Z170"/>
-    <mergeCell ref="AB170:AC177"/>
-    <mergeCell ref="AF170:AJ173"/>
-    <mergeCell ref="Y171:Z171"/>
-    <mergeCell ref="Y172:Z172"/>
-    <mergeCell ref="Y173:Z173"/>
-    <mergeCell ref="Y174:Z174"/>
-    <mergeCell ref="AF174:AJ174"/>
-    <mergeCell ref="M169:N169"/>
-    <mergeCell ref="O169:P169"/>
-    <mergeCell ref="Q169:R169"/>
-    <mergeCell ref="S169:T169"/>
-    <mergeCell ref="U169:V169"/>
-    <mergeCell ref="AB163:AC168"/>
-    <mergeCell ref="C169:D169"/>
-    <mergeCell ref="E169:F169"/>
-    <mergeCell ref="G169:H169"/>
-    <mergeCell ref="I169:J169"/>
-    <mergeCell ref="K169:L169"/>
-    <mergeCell ref="M161:N161"/>
-    <mergeCell ref="O161:P161"/>
-    <mergeCell ref="Q161:R161"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="U161:V161"/>
-    <mergeCell ref="W161:W162"/>
-    <mergeCell ref="C147:D147"/>
-    <mergeCell ref="E147:F147"/>
-    <mergeCell ref="G147:H147"/>
-    <mergeCell ref="I147:J147"/>
-    <mergeCell ref="K147:L147"/>
-    <mergeCell ref="AB148:AC158"/>
-    <mergeCell ref="AB159:AC159"/>
-    <mergeCell ref="B160:AD160"/>
-    <mergeCell ref="B161:B162"/>
-    <mergeCell ref="C161:D161"/>
-    <mergeCell ref="E161:F161"/>
-    <mergeCell ref="G161:H161"/>
-    <mergeCell ref="I161:J161"/>
-    <mergeCell ref="K161:L161"/>
-    <mergeCell ref="Y161:Y162"/>
-    <mergeCell ref="Z161:Z162"/>
-    <mergeCell ref="AA161:AA162"/>
-    <mergeCell ref="AB161:AC161"/>
-    <mergeCell ref="AB145:AC146"/>
-    <mergeCell ref="AF141:AJ141"/>
-    <mergeCell ref="AB143:AC143"/>
-    <mergeCell ref="AF143:AJ143"/>
-    <mergeCell ref="M147:N147"/>
-    <mergeCell ref="O147:P147"/>
-    <mergeCell ref="Q147:R147"/>
-    <mergeCell ref="S147:T147"/>
-    <mergeCell ref="U147:V147"/>
-    <mergeCell ref="AB147:AC147"/>
-    <mergeCell ref="C144:D144"/>
-    <mergeCell ref="E144:F144"/>
-    <mergeCell ref="G144:H144"/>
-    <mergeCell ref="I144:J144"/>
-    <mergeCell ref="K144:L144"/>
-    <mergeCell ref="M144:N144"/>
-    <mergeCell ref="AB110:AC114"/>
-    <mergeCell ref="AF114:AJ114"/>
-    <mergeCell ref="AB115:AC128"/>
-    <mergeCell ref="AF115:AJ120"/>
-    <mergeCell ref="O144:P144"/>
-    <mergeCell ref="Q144:R144"/>
-    <mergeCell ref="S144:T144"/>
-    <mergeCell ref="U144:V144"/>
-    <mergeCell ref="AB144:AC144"/>
-    <mergeCell ref="AK116:AL143"/>
-    <mergeCell ref="AF121:AJ121"/>
-    <mergeCell ref="AF122:AJ122"/>
-    <mergeCell ref="AB129:AC141"/>
-    <mergeCell ref="AF129:AJ131"/>
-    <mergeCell ref="AF133:AJ133"/>
-    <mergeCell ref="U108:V108"/>
-    <mergeCell ref="W108:W109"/>
-    <mergeCell ref="Y108:Y109"/>
-    <mergeCell ref="Z108:Z109"/>
-    <mergeCell ref="AA108:AA109"/>
-    <mergeCell ref="AB108:AC108"/>
-    <mergeCell ref="K108:L108"/>
-    <mergeCell ref="M108:N108"/>
-    <mergeCell ref="O108:P108"/>
-    <mergeCell ref="Q108:R108"/>
-    <mergeCell ref="S108:T108"/>
-    <mergeCell ref="AF101:AJ101"/>
-    <mergeCell ref="AF103:AJ103"/>
-    <mergeCell ref="AB106:AC106"/>
-    <mergeCell ref="AF106:AJ110"/>
-    <mergeCell ref="B107:AD107"/>
-    <mergeCell ref="B108:B109"/>
-    <mergeCell ref="C108:D108"/>
-    <mergeCell ref="E108:F108"/>
-    <mergeCell ref="G108:H108"/>
-    <mergeCell ref="I108:J108"/>
-    <mergeCell ref="U90:V90"/>
-    <mergeCell ref="AB90:AC90"/>
-    <mergeCell ref="AK90:AL115"/>
-    <mergeCell ref="AB91:AC91"/>
-    <mergeCell ref="AB93:AC93"/>
-    <mergeCell ref="AB94:AC94"/>
-    <mergeCell ref="AB95:AC95"/>
-    <mergeCell ref="AB96:AC105"/>
-    <mergeCell ref="AF96:AJ100"/>
-    <mergeCell ref="C90:D90"/>
-    <mergeCell ref="E90:F90"/>
-    <mergeCell ref="G90:H90"/>
-    <mergeCell ref="I90:J90"/>
-    <mergeCell ref="K90:L90"/>
-    <mergeCell ref="M90:N90"/>
-    <mergeCell ref="O90:P90"/>
-    <mergeCell ref="Q90:R90"/>
-    <mergeCell ref="S90:T90"/>
-    <mergeCell ref="AF81:AJ81"/>
-    <mergeCell ref="AF82:AJ82"/>
-    <mergeCell ref="AB83:AC84"/>
-    <mergeCell ref="AF83:AJ83"/>
-    <mergeCell ref="AK83:AL89"/>
-    <mergeCell ref="AF84:AJ84"/>
-    <mergeCell ref="AB85:AC85"/>
-    <mergeCell ref="AB86:AC86"/>
-    <mergeCell ref="AB87:AC87"/>
-    <mergeCell ref="AB88:AC88"/>
-    <mergeCell ref="AK74:AL81"/>
-    <mergeCell ref="AF75:AJ75"/>
-    <mergeCell ref="AB76:AC76"/>
-    <mergeCell ref="AB77:AC78"/>
-    <mergeCell ref="AF77:AJ77"/>
-    <mergeCell ref="AF78:AJ78"/>
-    <mergeCell ref="AB79:AC80"/>
-    <mergeCell ref="AF79:AJ79"/>
-    <mergeCell ref="AF80:AJ80"/>
-    <mergeCell ref="AB81:AC82"/>
-    <mergeCell ref="AB89:AC89"/>
-    <mergeCell ref="Q73:R73"/>
-    <mergeCell ref="S73:T73"/>
-    <mergeCell ref="U73:V73"/>
-    <mergeCell ref="AB73:AC73"/>
-    <mergeCell ref="AB74:AC75"/>
-    <mergeCell ref="AF74:AJ74"/>
-    <mergeCell ref="AB71:AC71"/>
-    <mergeCell ref="AB72:AC72"/>
-    <mergeCell ref="C73:D73"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="K73:L73"/>
-    <mergeCell ref="M73:N73"/>
-    <mergeCell ref="O73:P73"/>
-    <mergeCell ref="AB65:AC70"/>
-    <mergeCell ref="AF66:AJ66"/>
-    <mergeCell ref="AF67:AJ67"/>
-    <mergeCell ref="M63:N63"/>
-    <mergeCell ref="O63:P63"/>
-    <mergeCell ref="Q63:R63"/>
-    <mergeCell ref="S63:T63"/>
-    <mergeCell ref="U63:V63"/>
-    <mergeCell ref="W63:W64"/>
-    <mergeCell ref="AB58:AC58"/>
-    <mergeCell ref="AC60:AC61"/>
-    <mergeCell ref="AB62:AC62"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="G63:H63"/>
-    <mergeCell ref="I63:J63"/>
-    <mergeCell ref="K63:L63"/>
-    <mergeCell ref="Y63:Y64"/>
-    <mergeCell ref="Z63:Z64"/>
-    <mergeCell ref="AA63:AA64"/>
-    <mergeCell ref="AB63:AC63"/>
-    <mergeCell ref="AB48:AC52"/>
-    <mergeCell ref="AB55:AC55"/>
-    <mergeCell ref="AB42:AC47"/>
-    <mergeCell ref="AF42:AJ42"/>
-    <mergeCell ref="AF47:AJ47"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="O40:P40"/>
-    <mergeCell ref="Q40:R40"/>
-    <mergeCell ref="S40:T40"/>
-    <mergeCell ref="U40:V40"/>
-    <mergeCell ref="AB40:AC40"/>
-    <mergeCell ref="AB32:AC32"/>
-    <mergeCell ref="AB33:AC34"/>
-    <mergeCell ref="AF33:AJ33"/>
-    <mergeCell ref="AF34:AJ34"/>
-    <mergeCell ref="AB23:AC23"/>
-    <mergeCell ref="AB24:AC25"/>
-    <mergeCell ref="AF24:AJ24"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="AB35:AC35"/>
-    <mergeCell ref="AB36:AC37"/>
-    <mergeCell ref="AF36:AJ36"/>
-    <mergeCell ref="AF37:AJ37"/>
-    <mergeCell ref="AB38:AC38"/>
-    <mergeCell ref="AB39:AC39"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="W2:W3"/>
+    <mergeCell ref="Y2:Y3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="B1:AD1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="X2:X3"/>
     <mergeCell ref="Z4:Z8"/>
     <mergeCell ref="AC4:AC8"/>
     <mergeCell ref="AF4:AJ6"/>
@@ -31594,24 +31409,308 @@
     <mergeCell ref="AB30:AC31"/>
     <mergeCell ref="AF30:AJ30"/>
     <mergeCell ref="AF31:AJ31"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="W2:W3"/>
-    <mergeCell ref="Y2:Y3"/>
-    <mergeCell ref="Z2:Z3"/>
-    <mergeCell ref="B1:AD1"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="AA2:AA3"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="X2:X3"/>
+    <mergeCell ref="AB32:AC32"/>
+    <mergeCell ref="AB33:AC34"/>
+    <mergeCell ref="AF33:AJ33"/>
+    <mergeCell ref="AF34:AJ34"/>
+    <mergeCell ref="AB23:AC23"/>
+    <mergeCell ref="AB24:AC25"/>
+    <mergeCell ref="AF24:AJ24"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="AB35:AC35"/>
+    <mergeCell ref="AB36:AC37"/>
+    <mergeCell ref="AF36:AJ36"/>
+    <mergeCell ref="AF37:AJ37"/>
+    <mergeCell ref="AB38:AC38"/>
+    <mergeCell ref="AB39:AC39"/>
+    <mergeCell ref="AB48:AC52"/>
+    <mergeCell ref="AB55:AC55"/>
+    <mergeCell ref="AB42:AC47"/>
+    <mergeCell ref="AF42:AJ42"/>
+    <mergeCell ref="AF47:AJ47"/>
+    <mergeCell ref="M40:N40"/>
+    <mergeCell ref="O40:P40"/>
+    <mergeCell ref="Q40:R40"/>
+    <mergeCell ref="S40:T40"/>
+    <mergeCell ref="U40:V40"/>
+    <mergeCell ref="AB40:AC40"/>
+    <mergeCell ref="AB58:AC58"/>
+    <mergeCell ref="AC60:AC61"/>
+    <mergeCell ref="AB62:AC62"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="G63:H63"/>
+    <mergeCell ref="I63:J63"/>
+    <mergeCell ref="K63:L63"/>
+    <mergeCell ref="Y63:Y64"/>
+    <mergeCell ref="Z63:Z64"/>
+    <mergeCell ref="AA63:AA64"/>
+    <mergeCell ref="AB63:AC63"/>
+    <mergeCell ref="AB65:AC70"/>
+    <mergeCell ref="AF66:AJ66"/>
+    <mergeCell ref="AF67:AJ67"/>
+    <mergeCell ref="M63:N63"/>
+    <mergeCell ref="O63:P63"/>
+    <mergeCell ref="Q63:R63"/>
+    <mergeCell ref="S63:T63"/>
+    <mergeCell ref="U63:V63"/>
+    <mergeCell ref="W63:W64"/>
+    <mergeCell ref="Q73:R73"/>
+    <mergeCell ref="S73:T73"/>
+    <mergeCell ref="U73:V73"/>
+    <mergeCell ref="AB73:AC73"/>
+    <mergeCell ref="AB74:AC75"/>
+    <mergeCell ref="AF74:AJ74"/>
+    <mergeCell ref="AB71:AC71"/>
+    <mergeCell ref="AB72:AC72"/>
+    <mergeCell ref="C73:D73"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="G73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="K73:L73"/>
+    <mergeCell ref="M73:N73"/>
+    <mergeCell ref="O73:P73"/>
+    <mergeCell ref="AF81:AJ81"/>
+    <mergeCell ref="AF82:AJ82"/>
+    <mergeCell ref="AB83:AC84"/>
+    <mergeCell ref="AF83:AJ83"/>
+    <mergeCell ref="AK83:AL89"/>
+    <mergeCell ref="AF84:AJ84"/>
+    <mergeCell ref="AB85:AC85"/>
+    <mergeCell ref="AB86:AC86"/>
+    <mergeCell ref="AB87:AC87"/>
+    <mergeCell ref="AB88:AC88"/>
+    <mergeCell ref="AK74:AL81"/>
+    <mergeCell ref="AF75:AJ75"/>
+    <mergeCell ref="AB76:AC76"/>
+    <mergeCell ref="AB77:AC78"/>
+    <mergeCell ref="AF77:AJ77"/>
+    <mergeCell ref="AF78:AJ78"/>
+    <mergeCell ref="AB79:AC80"/>
+    <mergeCell ref="AF79:AJ79"/>
+    <mergeCell ref="AF80:AJ80"/>
+    <mergeCell ref="AB81:AC82"/>
+    <mergeCell ref="AB89:AC89"/>
+    <mergeCell ref="C90:D90"/>
+    <mergeCell ref="E90:F90"/>
+    <mergeCell ref="G90:H90"/>
+    <mergeCell ref="I90:J90"/>
+    <mergeCell ref="K90:L90"/>
+    <mergeCell ref="M90:N90"/>
+    <mergeCell ref="O90:P90"/>
+    <mergeCell ref="Q90:R90"/>
+    <mergeCell ref="S90:T90"/>
+    <mergeCell ref="U90:V90"/>
+    <mergeCell ref="AB90:AC90"/>
+    <mergeCell ref="AK90:AL115"/>
+    <mergeCell ref="AB91:AC91"/>
+    <mergeCell ref="AB93:AC93"/>
+    <mergeCell ref="AB94:AC94"/>
+    <mergeCell ref="AB95:AC95"/>
+    <mergeCell ref="AB96:AC105"/>
+    <mergeCell ref="AF96:AJ100"/>
+    <mergeCell ref="K108:L108"/>
+    <mergeCell ref="M108:N108"/>
+    <mergeCell ref="O108:P108"/>
+    <mergeCell ref="Q108:R108"/>
+    <mergeCell ref="S108:T108"/>
+    <mergeCell ref="AF101:AJ101"/>
+    <mergeCell ref="AF103:AJ103"/>
+    <mergeCell ref="AB106:AC106"/>
+    <mergeCell ref="AF106:AJ110"/>
+    <mergeCell ref="B107:AD107"/>
+    <mergeCell ref="B108:B109"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="E108:F108"/>
+    <mergeCell ref="G108:H108"/>
+    <mergeCell ref="I108:J108"/>
+    <mergeCell ref="AK116:AL144"/>
+    <mergeCell ref="AF121:AJ121"/>
+    <mergeCell ref="AF122:AJ122"/>
+    <mergeCell ref="AB129:AC141"/>
+    <mergeCell ref="AF129:AJ131"/>
+    <mergeCell ref="AF133:AJ133"/>
+    <mergeCell ref="U108:V108"/>
+    <mergeCell ref="W108:W109"/>
+    <mergeCell ref="Y108:Y109"/>
+    <mergeCell ref="Z108:Z109"/>
+    <mergeCell ref="AA108:AA109"/>
+    <mergeCell ref="AB108:AC108"/>
+    <mergeCell ref="C145:D145"/>
+    <mergeCell ref="E145:F145"/>
+    <mergeCell ref="G145:H145"/>
+    <mergeCell ref="I145:J145"/>
+    <mergeCell ref="K145:L145"/>
+    <mergeCell ref="M145:N145"/>
+    <mergeCell ref="AB110:AC114"/>
+    <mergeCell ref="AF114:AJ114"/>
+    <mergeCell ref="AB115:AC128"/>
+    <mergeCell ref="AF115:AJ120"/>
+    <mergeCell ref="O145:P145"/>
+    <mergeCell ref="Q145:R145"/>
+    <mergeCell ref="S145:T145"/>
+    <mergeCell ref="U145:V145"/>
+    <mergeCell ref="AB145:AC145"/>
+    <mergeCell ref="AB146:AC147"/>
+    <mergeCell ref="AF141:AJ141"/>
+    <mergeCell ref="AB144:AC144"/>
+    <mergeCell ref="AF144:AJ144"/>
+    <mergeCell ref="M148:N148"/>
+    <mergeCell ref="O148:P148"/>
+    <mergeCell ref="Q148:R148"/>
+    <mergeCell ref="S148:T148"/>
+    <mergeCell ref="U148:V148"/>
+    <mergeCell ref="AB148:AC148"/>
+    <mergeCell ref="C148:D148"/>
+    <mergeCell ref="E148:F148"/>
+    <mergeCell ref="G148:H148"/>
+    <mergeCell ref="I148:J148"/>
+    <mergeCell ref="K148:L148"/>
+    <mergeCell ref="AB149:AC159"/>
+    <mergeCell ref="AB160:AC160"/>
+    <mergeCell ref="B161:AD161"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="C162:D162"/>
+    <mergeCell ref="E162:F162"/>
+    <mergeCell ref="G162:H162"/>
+    <mergeCell ref="I162:J162"/>
+    <mergeCell ref="K162:L162"/>
+    <mergeCell ref="Y162:Y163"/>
+    <mergeCell ref="Z162:Z163"/>
+    <mergeCell ref="AA162:AA163"/>
+    <mergeCell ref="AB162:AC162"/>
+    <mergeCell ref="AB164:AC169"/>
+    <mergeCell ref="C170:D170"/>
+    <mergeCell ref="E170:F170"/>
+    <mergeCell ref="G170:H170"/>
+    <mergeCell ref="I170:J170"/>
+    <mergeCell ref="K170:L170"/>
+    <mergeCell ref="M162:N162"/>
+    <mergeCell ref="O162:P162"/>
+    <mergeCell ref="Q162:R162"/>
+    <mergeCell ref="S162:T162"/>
+    <mergeCell ref="U162:V162"/>
+    <mergeCell ref="W162:W163"/>
+    <mergeCell ref="AF171:AJ174"/>
+    <mergeCell ref="Y172:Z172"/>
+    <mergeCell ref="Y173:Z173"/>
+    <mergeCell ref="Y174:Z174"/>
+    <mergeCell ref="Y175:Z175"/>
+    <mergeCell ref="AF175:AJ175"/>
+    <mergeCell ref="M170:N170"/>
+    <mergeCell ref="O170:P170"/>
+    <mergeCell ref="Q170:R170"/>
+    <mergeCell ref="S170:T170"/>
+    <mergeCell ref="U170:V170"/>
+    <mergeCell ref="Y176:Z176"/>
+    <mergeCell ref="Y177:Z177"/>
+    <mergeCell ref="Y178:Z178"/>
+    <mergeCell ref="Y179:Z179"/>
+    <mergeCell ref="AB179:AC179"/>
+    <mergeCell ref="Y180:Z180"/>
+    <mergeCell ref="AB180:AC180"/>
+    <mergeCell ref="Y170:Z170"/>
+    <mergeCell ref="AB170:AC170"/>
+    <mergeCell ref="Y171:Z171"/>
+    <mergeCell ref="AB171:AC178"/>
+    <mergeCell ref="Y184:Z184"/>
+    <mergeCell ref="AB184:AC184"/>
+    <mergeCell ref="Y185:Z185"/>
+    <mergeCell ref="AB185:AC185"/>
+    <mergeCell ref="AG185:AI185"/>
+    <mergeCell ref="Y186:Z186"/>
+    <mergeCell ref="AB186:AC186"/>
+    <mergeCell ref="Y181:Z181"/>
+    <mergeCell ref="AB181:AC181"/>
+    <mergeCell ref="Y182:Z182"/>
+    <mergeCell ref="AB182:AC182"/>
+    <mergeCell ref="Y183:Z183"/>
+    <mergeCell ref="AB183:AC183"/>
+    <mergeCell ref="Y192:Z192"/>
+    <mergeCell ref="AB192:AC192"/>
+    <mergeCell ref="Y193:Z193"/>
+    <mergeCell ref="AB193:AC193"/>
+    <mergeCell ref="Y195:Z195"/>
+    <mergeCell ref="AB195:AC195"/>
+    <mergeCell ref="Y187:Z187"/>
+    <mergeCell ref="AB187:AC187"/>
+    <mergeCell ref="Y188:Z188"/>
+    <mergeCell ref="AB188:AC188"/>
+    <mergeCell ref="Y191:Z191"/>
+    <mergeCell ref="AB191:AC191"/>
+    <mergeCell ref="Y189:Z189"/>
+    <mergeCell ref="Y190:Z190"/>
+    <mergeCell ref="Y194:Z194"/>
+    <mergeCell ref="Y196:Z196"/>
+    <mergeCell ref="AB196:AC196"/>
+    <mergeCell ref="C197:D197"/>
+    <mergeCell ref="E197:F197"/>
+    <mergeCell ref="G197:H197"/>
+    <mergeCell ref="I197:J197"/>
+    <mergeCell ref="K197:L197"/>
+    <mergeCell ref="M197:N197"/>
+    <mergeCell ref="O197:P197"/>
+    <mergeCell ref="S197:T197"/>
+    <mergeCell ref="U197:V197"/>
+    <mergeCell ref="Y197:Z197"/>
+    <mergeCell ref="AB197:AC197"/>
+    <mergeCell ref="Q197:R197"/>
+    <mergeCell ref="AB199:AC199"/>
+    <mergeCell ref="Y200:Z200"/>
+    <mergeCell ref="AB200:AC200"/>
+    <mergeCell ref="Y198:Z198"/>
+    <mergeCell ref="AB198:AC198"/>
+    <mergeCell ref="C199:D199"/>
+    <mergeCell ref="E199:F199"/>
+    <mergeCell ref="G199:H199"/>
+    <mergeCell ref="I199:J199"/>
+    <mergeCell ref="K199:L199"/>
+    <mergeCell ref="M199:N199"/>
+    <mergeCell ref="O199:P199"/>
+    <mergeCell ref="M198:N198"/>
+    <mergeCell ref="O198:P198"/>
+    <mergeCell ref="Q198:R198"/>
+    <mergeCell ref="S198:T198"/>
+    <mergeCell ref="U198:V198"/>
+    <mergeCell ref="Y199:Z199"/>
+    <mergeCell ref="C198:D198"/>
+    <mergeCell ref="E198:F198"/>
+    <mergeCell ref="G198:H198"/>
+    <mergeCell ref="I198:J198"/>
+    <mergeCell ref="K198:L198"/>
+    <mergeCell ref="B201:B202"/>
+    <mergeCell ref="C201:D201"/>
+    <mergeCell ref="E201:F201"/>
+    <mergeCell ref="G201:H201"/>
+    <mergeCell ref="I201:J201"/>
+    <mergeCell ref="K201:L201"/>
+    <mergeCell ref="Q199:R199"/>
+    <mergeCell ref="S199:T199"/>
+    <mergeCell ref="U199:V199"/>
+    <mergeCell ref="S202:T202"/>
+    <mergeCell ref="U202:V202"/>
+    <mergeCell ref="Y202:AA202"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="O204:P204"/>
+    <mergeCell ref="Y201:AA201"/>
+    <mergeCell ref="C202:D202"/>
+    <mergeCell ref="E202:F202"/>
+    <mergeCell ref="G202:H202"/>
+    <mergeCell ref="I202:J202"/>
+    <mergeCell ref="K202:L202"/>
+    <mergeCell ref="M202:N202"/>
+    <mergeCell ref="O202:P202"/>
+    <mergeCell ref="Q202:R202"/>
+    <mergeCell ref="M201:N201"/>
+    <mergeCell ref="O201:P201"/>
+    <mergeCell ref="Q201:R201"/>
+    <mergeCell ref="S201:T201"/>
+    <mergeCell ref="U201:V201"/>
   </mergeCells>
   <pageMargins left="1.1023622047244095" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="10" orientation="landscape" verticalDpi="0" r:id="rId1"/>
@@ -31619,7 +31718,7 @@
     <brk id="39" min="1" max="40" man="1"/>
     <brk id="62" min="1" max="41" man="1"/>
     <brk id="106" min="1" max="40" man="1"/>
-    <brk id="159" min="1" max="40" man="1"/>
+    <brk id="160" min="1" max="40" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
